--- a/c/9班资料.xlsx
+++ b/c/9班资料.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480" activeTab="2"/>
+    <workbookView windowWidth="20750" windowHeight="10480" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="七下拖课" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="280">
   <si>
     <t>拖课统计表</t>
   </si>
@@ -142,6 +142,9 @@
     <t>刘必艳</t>
   </si>
   <si>
+    <t>张敏润</t>
+  </si>
+  <si>
     <t>张榕杰</t>
   </si>
   <si>
@@ -391,7 +394,7 @@
     <t>郭沁诗</t>
   </si>
   <si>
-    <t>郭沁涛、国庆节、诗诗</t>
+    <t>郭沁涛、国庆节、狗狗</t>
   </si>
   <si>
     <t>黄丰泽</t>
@@ -463,7 +466,7 @@
     <t>林奕扬</t>
   </si>
   <si>
-    <t>骚包、黑皮体育生、汪汪男</t>
+    <t>骚包</t>
   </si>
   <si>
     <t>张桢烨</t>
@@ -676,7 +679,7 @@
     <t>黄恩亚爸爸、刘必艳</t>
   </si>
   <si>
-    <t>聊天记录</t>
+    <t>微信聊天记录</t>
   </si>
   <si>
     <t>黄恩亚爸爸：@班主任-刘老师 13646014074 今天恩亚肚子疼，本想请假一节课，但他还是坚持赶去上课了，到校门口是7点25分，我是鼓励他了，并且最近我都有把关到校时间没有迟到的，多次迟到是什么意思？
@@ -3965,8 +3968,12 @@
       <c r="AM3" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="AN3" s="67"/>
-      <c r="AO3" s="68"/>
+      <c r="AN3" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO3" s="68">
+        <v>0.75</v>
+      </c>
       <c r="AP3" s="67"/>
       <c r="AQ3" s="68"/>
       <c r="AR3" s="67"/>
@@ -4665,8 +4672,12 @@
       <c r="AM5" s="74">
         <v>0.25</v>
       </c>
-      <c r="AN5" s="73"/>
-      <c r="AO5" s="74"/>
+      <c r="AN5" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO5" s="74" t="s">
+        <v>3</v>
+      </c>
       <c r="AP5" s="73"/>
       <c r="AQ5" s="74"/>
       <c r="AR5" s="73"/>
@@ -5694,8 +5705,12 @@
       <c r="AM8" s="74">
         <v>1.25</v>
       </c>
-      <c r="AN8" s="78"/>
-      <c r="AO8" s="74"/>
+      <c r="AN8" s="78" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO8" s="74" t="s">
+        <v>3</v>
+      </c>
       <c r="AP8" s="78"/>
       <c r="AQ8" s="74"/>
       <c r="AR8" s="78"/>
@@ -6398,8 +6413,12 @@
       <c r="AM10" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="AN10" s="73"/>
-      <c r="AO10" s="74"/>
+      <c r="AN10" s="73" t="s">
+        <v>2</v>
+      </c>
+      <c r="AO10" s="74">
+        <v>0.5</v>
+      </c>
       <c r="AP10" s="73"/>
       <c r="AQ10" s="74"/>
       <c r="AR10" s="73"/>
@@ -7094,8 +7113,12 @@
       <c r="AM12" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="AN12" s="73"/>
-      <c r="AO12" s="74"/>
+      <c r="AN12" s="73" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO12" s="74" t="s">
+        <v>3</v>
+      </c>
       <c r="AP12" s="73"/>
       <c r="AQ12" s="74"/>
       <c r="AR12" s="73"/>
@@ -7790,8 +7813,12 @@
       <c r="AM14" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="AN14" s="73"/>
-      <c r="AO14" s="74"/>
+      <c r="AN14" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO14" s="74" t="s">
+        <v>3</v>
+      </c>
       <c r="AP14" s="73"/>
       <c r="AQ14" s="74"/>
       <c r="AR14" s="73"/>
@@ -8486,8 +8513,12 @@
       <c r="AM16" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="AN16" s="73"/>
-      <c r="AO16" s="74"/>
+      <c r="AN16" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="AO16" s="74">
+        <v>2.25</v>
+      </c>
       <c r="AP16" s="73"/>
       <c r="AQ16" s="74"/>
       <c r="AR16" s="73"/>
@@ -9182,8 +9213,12 @@
       <c r="AM18" s="74">
         <v>0.5</v>
       </c>
-      <c r="AN18" s="73"/>
-      <c r="AO18" s="74"/>
+      <c r="AN18" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO18" s="74">
+        <v>0.75</v>
+      </c>
       <c r="AP18" s="73"/>
       <c r="AQ18" s="74"/>
       <c r="AR18" s="73"/>
@@ -9874,8 +9909,12 @@
       <c r="AM20" s="74">
         <v>1</v>
       </c>
-      <c r="AN20" s="73"/>
-      <c r="AO20" s="74"/>
+      <c r="AN20" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO20" s="74" t="s">
+        <v>3</v>
+      </c>
       <c r="AP20" s="73"/>
       <c r="AQ20" s="74"/>
       <c r="AR20" s="73"/>
@@ -11808,7 +11847,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM10 AM11 AM12 AM13 AK14 AM14 AK15 AM15 AK16 AM16 AK17 AK18 AK19 AK20 AK21 C3:C21 E3:E21 G3:G21 I3:I21 K3:K21 M3:M21 O3:O21 Q3:Q21 S3:S21 U3:U21 W3:W21 Y3:Y21 AA3:AA21 AC3:AC21 AE3:AE21 AG3:AG21 AI3:AI21 AK3:AK13 AM3:AM9 AM17:AM21 AO3:AO21 AQ3:AQ21 AS3:AS21 AU3:AU21 AW3:AW21 AY3:AY21 BA3:BA21 BC3:BC21 BE3:BE21 BG3:BG21 BI3:BI21 BK3:BK21 BM3:BM21 BO3:BO21 BQ3:BQ21 BS3:BS21 BU3:BU21 BW3:BW21 BY3:BY21 CA3:CA21 CC3:CC21 CE3:CE21 CG3:CG21 CI3:CI21 CK3:CK21 CM3:CM21 CO3:CO21 CQ3:CQ21 CS3:CS21 CU3:CU21 CW3:CW21 CY3:CY21 DA3:DA21 DC3:DC21 DE3:DE21 DG3:DG21 DI3:DI21 DK3:DK21 DM3:DM21 DO3:DO21 DQ3:DQ21 DS3:DS21 DU3:DU21 DW3:DW21 DY3:DY21 EA3:EA21 EC3:EC21 EE3:EE21 EG3:EG21 EI3:EI21 EK3:EK21 EM3:EM21 EO3:EO21 EQ3:EQ21 ES3:ES21 EU3:EU21 EW3:EW21 EY3:EY21 FA3:FA21 FC3:FC21 FE3:FE21 FG3:FG21 FI3:FI21 FK3:FK21 FM3:FM21 FO3:FO21 FQ3:FQ21 FS3:FS21 FU3:FU21 FW3:FW21 FY3:FY21 GA3:GA21 GC3:GC21 GE3:GE21 GG3:GG21 GI3:GI21 GK3:GK21 GM3:GM21 GO3:GO21 GQ3:GQ21 GS3:GS21 GU3:GU21 GW3:GW21 GY3:GY21 HA3:HA21 HC3:HC21 HE3:HE21 HG3:HG21 HI3:HI21 HK3:HK21 HM3:HM21 HO3:HO21 HQ3:HQ21 HS3:HS21 HU3:HU21 HW3:HW21 HY3:HY21 IA3:IA21 IC3:IC21 IE3:IE21 IG3:IG21 II3:II21 IK3:IK21 IM3:IM21 IO3:IO21 IQ3:IQ21 IS3:IS21 IU3:IU21 IW3:IW21 IY3:IY21 JA3:JA21 JC3:JC21 JE3:JE21 JG3:JG21 JI3:JI21 JK3:JK21 JM3:JM21 JO3:JO21 JQ3:JQ21 JS3:JS21 JU3:JU21 JW3:JW21 JY3:JY21 KA3:KA21 KC3:KC21 KE3:KE21 KG3:KG21 KI3:KI21 KK3:KK21 KM3:KM21 KO3:KO21 KQ3:KQ21 KS3:KS21 KU3:KU21 KW3:KW21 KY3:KY21 LA3:LA21 LC3:LC21 LE3:LE21 LG3:LG21 LI3:LI21">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO8 AO12 AO13 AO14 AO20 AO21 C3:C21 E3:E21 G3:G21 I3:I21 K3:K21 M3:M21 O3:O21 Q3:Q21 S3:S21 U3:U21 W3:W21 Y3:Y21 AA3:AA21 AC3:AC21 AE3:AE21 AG3:AG21 AI3:AI21 AK3:AK21 AM3:AM21 AO3:AO7 AO9:AO11 AO15:AO19 AQ3:AQ21 AS3:AS21 AU3:AU21 AW3:AW21 AY3:AY21 BA3:BA21 BC3:BC21 BE3:BE21 BG3:BG21 BI3:BI21 BK3:BK21 BM3:BM21 BO3:BO21 BQ3:BQ21 BS3:BS21 BU3:BU21 BW3:BW21 BY3:BY21 CA3:CA21 CC3:CC21 CE3:CE21 CG3:CG21 CI3:CI21 CK3:CK21 CM3:CM21 CO3:CO21 CQ3:CQ21 CS3:CS21 CU3:CU21 CW3:CW21 CY3:CY21 DA3:DA21 DC3:DC21 DE3:DE21 DG3:DG21 DI3:DI21 DK3:DK21 DM3:DM21 DO3:DO21 DQ3:DQ21 DS3:DS21 DU3:DU21 DW3:DW21 DY3:DY21 EA3:EA21 EC3:EC21 EE3:EE21 EG3:EG21 EI3:EI21 EK3:EK21 EM3:EM21 EO3:EO21 EQ3:EQ21 ES3:ES21 EU3:EU21 EW3:EW21 EY3:EY21 FA3:FA21 FC3:FC21 FE3:FE21 FG3:FG21 FI3:FI21 FK3:FK21 FM3:FM21 FO3:FO21 FQ3:FQ21 FS3:FS21 FU3:FU21 FW3:FW21 FY3:FY21 GA3:GA21 GC3:GC21 GE3:GE21 GG3:GG21 GI3:GI21 GK3:GK21 GM3:GM21 GO3:GO21 GQ3:GQ21 GS3:GS21 GU3:GU21 GW3:GW21 GY3:GY21 HA3:HA21 HC3:HC21 HE3:HE21 HG3:HG21 HI3:HI21 HK3:HK21 HM3:HM21 HO3:HO21 HQ3:HQ21 HS3:HS21 HU3:HU21 HW3:HW21 HY3:HY21 IA3:IA21 IC3:IC21 IE3:IE21 IG3:IG21 II3:II21 IK3:IK21 IM3:IM21 IO3:IO21 IQ3:IQ21 IS3:IS21 IU3:IU21 IW3:IW21 IY3:IY21 JA3:JA21 JC3:JC21 JE3:JE21 JG3:JG21 JI3:JI21 JK3:JK21 JM3:JM21 JO3:JO21 JQ3:JQ21 JS3:JS21 JU3:JU21 JW3:JW21 JY3:JY21 KA3:KA21 KC3:KC21 KE3:KE21 KG3:KG21 KI3:KI21 KK3:KK21 KM3:KM21 KO3:KO21 KQ3:KQ21 KS3:KS21 KU3:KU21 KW3:KW21 KY3:KY21 LA3:LA21 LC3:LC21 LE3:LE21 LG3:LG21 LI3:LI21">
       <formula1>数据!$B$1:$B$55</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C22 E22 G22 I22 K22 M22 O22 Q22 S22 U22 W22 Y22 AA22 AC22 AE22 AG22 AI22 AK22 AM22 AO22 AQ22 AS22 AU22 AW22 AY22 BA22 BC22 BE22 BG22 BI22 BK22 BM22 BO22 BQ22 BS22 BU22 BW22 BY22 CA22 CC22 CE22 CG22 CI22 CK22 CM22 CO22 CQ22 CS22 CU22 CW22 CY22 DA22 DC22 DE22 DG22 DI22 DK22 DM22 DO22 DQ22 DS22 DU22 DW22 DY22 EA22 EC22 EE22 EG22 EI22 EK22 EM22 EO22 EQ22 ES22 EU22 EW22 EY22 FA22 FC22 FE22 FG22 FI22 FK22 FM22 FO22 FQ22 FS22 FU22 FW22 FY22 GA22 GC22 GE22 GG22 GI22 GK22 GM22 GO22 GQ22 GS22 GU22 GW22 GY22 HA22 HC22 HE22 HG22 HI22 HK22 HM22 HO22 HQ22 HS22 HU22 HW22 HY22 IA22 IC22 IE22 IG22 II22 IK22 IM22 IO22 IQ22 IS22 IU22 IW22 IY22 JA22 JC22 JE22 JG22 JI22 JK22 JM22 JO22 JQ22 JS22 JU22 JW22 JY22 KA22 KC22 KE22 KG22 KI22 KK22 KM22 KO22 KQ22 KS22 KU22 KW22 KY22 LA22 LC22 LE22 LG22 LI22">
@@ -11938,7 +11977,9 @@
       <c r="A7" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="45"/>
+      <c r="B7" s="45" t="s">
+        <v>34</v>
+      </c>
       <c r="C7" s="45"/>
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
@@ -11965,7 +12006,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
@@ -12016,10 +12057,10 @@
     </row>
     <row r="13" ht="16.5" spans="1:9">
       <c r="A13" s="36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" s="49"/>
       <c r="D13" s="49"/>
@@ -12028,10 +12069,10 @@
     </row>
     <row r="14" ht="16.5" spans="1:9">
       <c r="A14" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="50" t="s">
         <v>37</v>
-      </c>
-      <c r="B14" s="50" t="s">
-        <v>36</v>
       </c>
       <c r="C14" s="50"/>
       <c r="D14" s="50"/>
@@ -12100,13 +12141,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -12114,280 +12155,280 @@
         <v>24</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="34"/>
       <c r="B3" s="29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="34"/>
       <c r="B4" s="29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="34"/>
       <c r="B5" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="34"/>
       <c r="B6" s="29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="34"/>
       <c r="B7" s="29" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="34"/>
       <c r="B8" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="34"/>
       <c r="B9" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="34"/>
       <c r="B10" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="34"/>
       <c r="B11" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C11" s="30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="34"/>
       <c r="B12" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="34"/>
       <c r="B13" s="29" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C13" s="30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="34"/>
       <c r="B14" s="29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="34"/>
       <c r="B15" s="29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C15" s="30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="34"/>
       <c r="B16" s="29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C16" s="30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="34"/>
       <c r="B17" s="29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="34"/>
       <c r="B18" s="29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C18" s="30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="34"/>
       <c r="B19" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C19" s="30" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="34"/>
       <c r="B20" s="29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="34"/>
       <c r="B21" s="29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C21" s="30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="34"/>
       <c r="B22" s="29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C22" s="30" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="34"/>
       <c r="B23" s="29" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C23" s="30" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="34"/>
       <c r="B24" s="29" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C24" s="30" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="34"/>
       <c r="B25" s="29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C25" s="30" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="34"/>
       <c r="B26" s="29" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C26" s="30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="34"/>
       <c r="B27" s="29" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="34"/>
       <c r="B28" s="29" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C28" s="30" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="34"/>
       <c r="B29" s="29" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="34"/>
       <c r="B30" s="29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C30" s="30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="34"/>
       <c r="B31" s="29" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="34"/>
       <c r="B32" s="29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -12395,28 +12436,28 @@
         <v>25</v>
       </c>
       <c r="B33" s="29" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C33" s="30" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="31"/>
       <c r="B34" s="29" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="31"/>
       <c r="B35" s="29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C35" s="30" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="1:1">
@@ -12506,16 +12547,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -12523,13 +12564,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C2" s="25">
         <v>20111216</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -12537,13 +12578,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C3" s="26">
         <v>20111227</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -12551,13 +12592,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C4" s="26">
         <v>20120518</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -12565,7 +12606,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C5" s="26">
         <v>20120714</v>
@@ -12576,7 +12617,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C6" s="26">
         <v>20120504</v>
@@ -12590,13 +12631,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C7" s="26">
         <v>20120809</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -12604,7 +12645,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" s="26">
         <v>20120227</v>
@@ -12615,13 +12656,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C9" s="26">
         <v>20120127</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -12629,13 +12670,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C10" s="26">
         <v>20111202</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -12643,7 +12684,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C11" s="26">
         <v>20120623</v>
@@ -12654,13 +12695,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C12" s="26">
         <v>20111024</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -12668,13 +12709,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C13" s="26">
         <v>20110908</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -12682,13 +12723,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C14" s="26">
         <v>20120228</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -12696,7 +12737,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C15" s="26">
         <v>20110904</v>
@@ -12707,7 +12748,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C16" s="25">
         <v>20111201</v>
@@ -12718,7 +12759,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C17" s="26">
         <v>20120722</v>
@@ -12729,7 +12770,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C18" s="26">
         <v>20111215</v>
@@ -12740,7 +12781,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C19" s="26">
         <v>20120509</v>
@@ -12751,7 +12792,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C20" s="26">
         <v>20120530</v>
@@ -12762,13 +12803,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C21" s="26">
         <v>20120827</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -12776,7 +12817,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C22" s="26">
         <v>20120816</v>
@@ -12787,7 +12828,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C23" s="26">
         <v>20120518</v>
@@ -12798,13 +12839,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C24" s="26">
         <v>20120413</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -12812,13 +12853,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C25" s="26">
         <v>20120629</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -12826,13 +12867,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C26" s="26">
         <v>20111105</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -12840,13 +12881,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C27" s="26">
         <v>20120112</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -12854,13 +12895,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C28" s="26">
         <v>20111119</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -12868,7 +12909,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C29" s="26">
         <v>20120110</v>
@@ -12879,13 +12920,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C30" s="26">
         <v>20120331</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -12893,13 +12934,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C31" s="26">
         <v>20111109</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -12907,13 +12948,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C32" s="26">
         <v>20120824</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -12921,7 +12962,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C33" s="26">
         <v>20120425</v>
@@ -12932,13 +12973,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C34" s="26">
         <v>20120624</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -12946,7 +12987,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C35" s="26">
         <v>20120507</v>
@@ -12957,13 +12998,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C36" s="26">
         <v>20120603</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -12971,13 +13012,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C37" s="25">
         <v>20120326</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -12985,13 +13026,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C38" s="26">
         <v>20111106</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -12999,13 +13040,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C39" s="26">
         <v>20120811</v>
       </c>
       <c r="D39" s="27" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -13013,13 +13054,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C40" s="26">
         <v>20111217</v>
       </c>
       <c r="D40" s="27" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -13027,13 +13068,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C41" s="26">
         <v>20111013</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -13041,7 +13082,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C42" s="26">
         <v>20111027</v>
@@ -13052,13 +13093,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C43" s="26">
         <v>20120207</v>
       </c>
       <c r="D43" s="18" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -13066,7 +13107,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C44" s="25">
         <v>20120508</v>
@@ -13077,13 +13118,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C45" s="26">
         <v>20110929</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -13091,7 +13132,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C46" s="26">
         <v>20111205</v>
@@ -13102,13 +13143,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C47" s="26">
         <v>20120108</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -13116,13 +13157,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C48" s="26">
         <v>20120311</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -13130,7 +13171,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="24" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C49" s="26">
         <v>20110902</v>
@@ -13141,13 +13182,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="24" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C50" s="26">
         <v>20120723</v>
       </c>
       <c r="D50" s="18" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -13155,7 +13196,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="24" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C51" s="26">
         <v>20120101</v>
@@ -13166,13 +13207,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="24" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C52" s="26">
         <v>20111220</v>
       </c>
       <c r="D52" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -13202,70 +13243,70 @@
   <sheetData>
     <row r="1" ht="14" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" ht="217" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>24</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" ht="356.5" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>24</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" ht="108.5" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -13439,7 +13480,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B15">
         <v>3.5</v>
@@ -13450,7 +13491,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B16">
         <v>3.75</v>
@@ -13461,7 +13502,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B17">
         <v>4</v>
@@ -13472,7 +13513,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B18">
         <v>4.25</v>
@@ -13483,7 +13524,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B19">
         <v>4.5</v>
@@ -13494,7 +13535,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B20">
         <v>4.75</v>
@@ -13505,7 +13546,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B21">
         <v>5</v>
@@ -13516,7 +13557,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B22">
         <v>5.25</v>
@@ -13527,7 +13568,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B23">
         <v>5.5</v>
@@ -13538,7 +13579,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B24">
         <v>5.75</v>
@@ -13549,7 +13590,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B25">
         <v>6</v>
@@ -13576,7 +13617,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B28">
         <v>6.75</v>
@@ -13584,7 +13625,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B29">
         <v>7</v>
@@ -13592,7 +13633,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B30">
         <v>7.25</v>
@@ -13600,7 +13641,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B31">
         <v>7.5</v>
@@ -13608,7 +13649,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B32">
         <v>7.75</v>
@@ -13616,7 +13657,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B33">
         <v>8</v>
@@ -13624,7 +13665,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B34">
         <v>9</v>
@@ -13632,7 +13673,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B35">
         <v>10</v>
@@ -13640,7 +13681,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B36">
         <v>11</v>
@@ -13648,7 +13689,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B37">
         <v>12</v>
@@ -13656,7 +13697,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B38">
         <v>13</v>
@@ -13664,7 +13705,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B39">
         <v>14</v>
@@ -13672,7 +13713,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B40">
         <v>15</v>
@@ -13680,7 +13721,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B41">
         <v>16</v>
@@ -13688,7 +13729,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B42">
         <v>17</v>
@@ -13696,7 +13737,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B43">
         <v>18</v>
@@ -13704,7 +13745,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B44">
         <v>19</v>
@@ -13712,7 +13753,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B45">
         <v>20</v>
@@ -13720,7 +13761,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B46">
         <v>21</v>
@@ -13728,7 +13769,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B47">
         <v>22</v>
@@ -13736,7 +13777,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B48">
         <v>23</v>
@@ -13744,7 +13785,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B49">
         <v>24</v>
@@ -13752,7 +13793,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B50">
         <v>25</v>
@@ -13760,7 +13801,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B51">
         <v>26</v>
@@ -13768,7 +13809,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B52">
         <v>27</v>
@@ -13776,7 +13817,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B53">
         <v>28</v>
@@ -13784,7 +13825,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B54">
         <v>29</v>
@@ -13792,7 +13833,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B55">
         <v>30</v>
@@ -13800,152 +13841,152 @@
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="86" spans="1:1">
@@ -13955,7 +13996,7 @@
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="88" spans="1:1">

--- a/c/9班资料.xlsx
+++ b/c/9班资料.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480" activeTab="8"/>
+    <workbookView windowWidth="20750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="七下拖课" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="281">
   <si>
     <t>拖课统计表</t>
   </si>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t>语文</t>
+  </si>
+  <si>
+    <t>无法统计</t>
   </si>
   <si>
     <t>跑操</t>
@@ -2282,14 +2285,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFF2F2F2"/>
+          <bgColor rgb="FFE3F2D9"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFE3F2D9"/>
+          <bgColor rgb="FFF2F2F2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3974,8 +3977,12 @@
       <c r="AO3" s="68">
         <v>0.75</v>
       </c>
-      <c r="AP3" s="67"/>
-      <c r="AQ3" s="68"/>
+      <c r="AP3" s="67" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ3" s="68" t="s">
+        <v>5</v>
+      </c>
       <c r="AR3" s="67"/>
       <c r="AS3" s="68"/>
       <c r="AT3" s="67"/>
@@ -4678,8 +4685,12 @@
       <c r="AO5" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="AP5" s="73"/>
-      <c r="AQ5" s="74"/>
+      <c r="AP5" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ5" s="74">
+        <v>3</v>
+      </c>
       <c r="AR5" s="73"/>
       <c r="AS5" s="74"/>
       <c r="AT5" s="73"/>
@@ -5284,7 +5295,7 @@
     </row>
     <row r="7" s="58" customFormat="1" ht="15" customHeight="1" spans="1:321">
       <c r="A7" s="75" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="76"/>
       <c r="C7" s="77"/>
@@ -5616,7 +5627,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="78" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" s="74" t="s">
         <v>3</v>
@@ -5626,7 +5637,7 @@
       <c r="F8" s="78"/>
       <c r="G8" s="74"/>
       <c r="H8" s="78" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I8" s="74" t="s">
         <v>3</v>
@@ -5638,19 +5649,19 @@
         <v>3.25</v>
       </c>
       <c r="L8" s="78" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M8" s="74" t="s">
         <v>3</v>
       </c>
       <c r="N8" s="78" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O8" s="74">
         <v>2.5</v>
       </c>
       <c r="P8" s="78" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q8" s="74" t="s">
         <v>3</v>
@@ -5660,7 +5671,7 @@
       <c r="T8" s="78"/>
       <c r="U8" s="74"/>
       <c r="V8" s="78" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W8" s="74" t="s">
         <v>3</v>
@@ -5672,19 +5683,19 @@
         <v>3</v>
       </c>
       <c r="Z8" s="78" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA8" s="74" t="s">
         <v>3</v>
       </c>
       <c r="AB8" s="78" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC8" s="74">
         <v>1</v>
       </c>
       <c r="AD8" s="78" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE8" s="74" t="s">
         <v>3</v>
@@ -5694,7 +5705,7 @@
       <c r="AH8" s="78"/>
       <c r="AI8" s="74"/>
       <c r="AJ8" s="78" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK8" s="74">
         <v>0.75</v>
@@ -5706,13 +5717,17 @@
         <v>1.25</v>
       </c>
       <c r="AN8" s="78" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO8" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="AP8" s="78"/>
-      <c r="AQ8" s="74"/>
+      <c r="AP8" s="78" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ8" s="74" t="s">
+        <v>3</v>
+      </c>
       <c r="AR8" s="78"/>
       <c r="AS8" s="74"/>
       <c r="AT8" s="78"/>
@@ -6324,7 +6339,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="73" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" s="74" t="s">
         <v>3</v>
@@ -6340,7 +6355,7 @@
         <v>1.75</v>
       </c>
       <c r="J10" s="73" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K10" s="74" t="s">
         <v>3</v>
@@ -6352,13 +6367,13 @@
         <v>3</v>
       </c>
       <c r="N10" s="73" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O10" s="74" t="s">
         <v>3</v>
       </c>
       <c r="P10" s="73" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q10" s="74">
         <v>1.25</v>
@@ -6374,7 +6389,7 @@
         <v>3</v>
       </c>
       <c r="X10" s="73" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y10" s="74" t="s">
         <v>3</v>
@@ -6386,13 +6401,13 @@
         <v>2.5</v>
       </c>
       <c r="AB10" s="73" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC10" s="74" t="s">
         <v>3</v>
       </c>
       <c r="AD10" s="73" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE10" s="74" t="s">
         <v>3</v>
@@ -6408,7 +6423,7 @@
         <v>1</v>
       </c>
       <c r="AL10" s="73" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM10" s="74" t="s">
         <v>3</v>
@@ -6419,8 +6434,12 @@
       <c r="AO10" s="74">
         <v>0.5</v>
       </c>
-      <c r="AP10" s="73"/>
-      <c r="AQ10" s="74"/>
+      <c r="AP10" s="73" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ10" s="74" t="s">
+        <v>3</v>
+      </c>
       <c r="AR10" s="73"/>
       <c r="AS10" s="74"/>
       <c r="AT10" s="73"/>
@@ -7025,7 +7044,7 @@
     </row>
     <row r="12" s="57" customFormat="1" ht="25" customHeight="1" spans="1:321">
       <c r="A12" s="72" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" s="73"/>
       <c r="C12" s="74"/>
@@ -7034,7 +7053,7 @@
       <c r="F12" s="73"/>
       <c r="G12" s="74"/>
       <c r="H12" s="73" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I12" s="74" t="s">
         <v>3</v>
@@ -7068,7 +7087,7 @@
       <c r="T12" s="73"/>
       <c r="U12" s="74"/>
       <c r="V12" s="73" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W12" s="74" t="s">
         <v>3</v>
@@ -7102,7 +7121,7 @@
       <c r="AH12" s="73"/>
       <c r="AI12" s="74"/>
       <c r="AJ12" s="73" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK12" s="74" t="s">
         <v>3</v>
@@ -7114,13 +7133,17 @@
         <v>3</v>
       </c>
       <c r="AN12" s="73" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO12" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="AP12" s="73"/>
-      <c r="AQ12" s="74"/>
+      <c r="AP12" s="73" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ12" s="74" t="s">
+        <v>3</v>
+      </c>
       <c r="AR12" s="73"/>
       <c r="AS12" s="74"/>
       <c r="AT12" s="73"/>
@@ -7734,13 +7757,13 @@
       <c r="F14" s="73"/>
       <c r="G14" s="74"/>
       <c r="H14" s="73" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I14" s="74" t="s">
         <v>3</v>
       </c>
       <c r="J14" s="73" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K14" s="74" t="s">
         <v>3</v>
@@ -7758,7 +7781,7 @@
         <v>3</v>
       </c>
       <c r="P14" s="73" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q14" s="74" t="s">
         <v>3</v>
@@ -7768,13 +7791,13 @@
       <c r="T14" s="73"/>
       <c r="U14" s="74"/>
       <c r="V14" s="73" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W14" s="74" t="s">
         <v>3</v>
       </c>
       <c r="X14" s="73" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y14" s="74">
         <v>1</v>
@@ -7792,7 +7815,7 @@
         <v>3</v>
       </c>
       <c r="AD14" s="73" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE14" s="74" t="s">
         <v>3</v>
@@ -7802,13 +7825,13 @@
       <c r="AH14" s="73"/>
       <c r="AI14" s="74"/>
       <c r="AJ14" s="73" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK14" s="74" t="s">
         <v>3</v>
       </c>
       <c r="AL14" s="73" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM14" s="74" t="s">
         <v>3</v>
@@ -7819,8 +7842,12 @@
       <c r="AO14" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="AP14" s="73"/>
-      <c r="AQ14" s="74"/>
+      <c r="AP14" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ14" s="74" t="s">
+        <v>3</v>
+      </c>
       <c r="AR14" s="73"/>
       <c r="AS14" s="74"/>
       <c r="AT14" s="73"/>
@@ -8440,13 +8467,13 @@
         <v>3</v>
       </c>
       <c r="J16" s="73" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K16" s="74" t="s">
         <v>3</v>
       </c>
       <c r="L16" s="73" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M16" s="74">
         <v>2</v>
@@ -8458,7 +8485,7 @@
         <v>3</v>
       </c>
       <c r="P16" s="73" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q16" s="74">
         <v>1.25</v>
@@ -8474,13 +8501,13 @@
         <v>3</v>
       </c>
       <c r="X16" s="73" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y16" s="74" t="s">
         <v>3</v>
       </c>
       <c r="Z16" s="73" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA16" s="74">
         <v>3</v>
@@ -8492,7 +8519,7 @@
         <v>3</v>
       </c>
       <c r="AD16" s="73" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE16" s="74">
         <v>4</v>
@@ -8508,19 +8535,23 @@
         <v>3</v>
       </c>
       <c r="AL16" s="73" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM16" s="74" t="s">
         <v>3</v>
       </c>
       <c r="AN16" s="73" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO16" s="74">
         <v>2.25</v>
       </c>
-      <c r="AP16" s="73"/>
-      <c r="AQ16" s="74"/>
+      <c r="AP16" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ16" s="74" t="s">
+        <v>3</v>
+      </c>
       <c r="AR16" s="73"/>
       <c r="AS16" s="74"/>
       <c r="AT16" s="73"/>
@@ -9134,7 +9165,7 @@
       <c r="F18" s="73"/>
       <c r="G18" s="74"/>
       <c r="H18" s="73" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I18" s="74" t="s">
         <v>3</v>
@@ -9152,7 +9183,7 @@
         <v>1.75</v>
       </c>
       <c r="N18" s="73" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O18" s="74">
         <v>1</v>
@@ -9168,7 +9199,7 @@
       <c r="T18" s="73"/>
       <c r="U18" s="74"/>
       <c r="V18" s="73" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W18" s="74" t="s">
         <v>3</v>
@@ -9186,7 +9217,7 @@
         <v>3</v>
       </c>
       <c r="AB18" s="73" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC18" s="74" t="s">
         <v>3</v>
@@ -9202,7 +9233,7 @@
       <c r="AH18" s="73"/>
       <c r="AI18" s="74"/>
       <c r="AJ18" s="73" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK18" s="74" t="s">
         <v>3</v>
@@ -9219,8 +9250,12 @@
       <c r="AO18" s="74">
         <v>0.75</v>
       </c>
-      <c r="AP18" s="73"/>
-      <c r="AQ18" s="74"/>
+      <c r="AP18" s="73" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ18" s="74" t="s">
+        <v>3</v>
+      </c>
       <c r="AR18" s="73"/>
       <c r="AS18" s="74"/>
       <c r="AT18" s="73"/>
@@ -9858,7 +9893,7 @@
         <v>3</v>
       </c>
       <c r="P20" s="73" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q20" s="74" t="s">
         <v>3</v>
@@ -9886,11 +9921,11 @@
         <v>3</v>
       </c>
       <c r="AB20" s="73" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC20" s="74"/>
       <c r="AD20" s="73" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE20" s="74"/>
       <c r="AF20" s="73"/>
@@ -9915,7 +9950,9 @@
       <c r="AO20" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="AP20" s="73"/>
+      <c r="AP20" s="73" t="s">
+        <v>21</v>
+      </c>
       <c r="AQ20" s="74"/>
       <c r="AR20" s="73"/>
       <c r="AS20" s="74"/>
@@ -10526,649 +10563,649 @@
     <row r="22" ht="17.5" spans="1:321">
       <c r="A22" s="82"/>
       <c r="B22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C22" s="84"/>
       <c r="D22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E22" s="84"/>
       <c r="F22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G22" s="84"/>
       <c r="H22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I22" s="84"/>
       <c r="J22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K22" s="84"/>
       <c r="L22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M22" s="84"/>
       <c r="N22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O22" s="84"/>
       <c r="P22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q22" s="84"/>
       <c r="R22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S22" s="84"/>
       <c r="T22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U22" s="84"/>
       <c r="V22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W22" s="84"/>
       <c r="X22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y22" s="84"/>
       <c r="Z22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA22" s="84">
         <v>6</v>
       </c>
       <c r="AB22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC22" s="84"/>
       <c r="AD22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE22" s="84">
         <v>7</v>
       </c>
       <c r="AF22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG22" s="84"/>
       <c r="AH22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI22" s="84"/>
       <c r="AJ22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK22" s="84"/>
       <c r="AL22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM22" s="84">
         <v>8</v>
       </c>
       <c r="AN22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO22" s="84"/>
       <c r="AP22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ22" s="84"/>
       <c r="AR22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS22" s="84"/>
       <c r="AT22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU22" s="84"/>
       <c r="AV22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW22" s="84"/>
       <c r="AX22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY22" s="84"/>
       <c r="AZ22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA22" s="84"/>
       <c r="BB22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC22" s="84"/>
       <c r="BD22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE22" s="84"/>
       <c r="BF22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BG22" s="84"/>
       <c r="BH22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BI22" s="84"/>
       <c r="BJ22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BK22" s="84"/>
       <c r="BL22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BM22" s="84"/>
       <c r="BN22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BO22" s="84"/>
       <c r="BP22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BQ22" s="84"/>
       <c r="BR22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BS22" s="84"/>
       <c r="BT22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BU22" s="84"/>
       <c r="BV22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BW22" s="84"/>
       <c r="BX22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BY22" s="84"/>
       <c r="BZ22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CA22" s="84"/>
       <c r="CB22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CC22" s="84"/>
       <c r="CD22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CE22" s="84"/>
       <c r="CF22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CG22" s="84"/>
       <c r="CH22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CI22" s="84"/>
       <c r="CJ22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CK22" s="84"/>
       <c r="CL22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CM22" s="84"/>
       <c r="CN22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CO22" s="84"/>
       <c r="CP22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CQ22" s="84"/>
       <c r="CR22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CS22" s="84"/>
       <c r="CT22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CU22" s="84"/>
       <c r="CV22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CW22" s="84"/>
       <c r="CX22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CY22" s="84"/>
       <c r="CZ22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DA22" s="84"/>
       <c r="DB22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DC22" s="84"/>
       <c r="DD22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DE22" s="84"/>
       <c r="DF22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DG22" s="84"/>
       <c r="DH22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DI22" s="84"/>
       <c r="DJ22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DK22" s="84"/>
       <c r="DL22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DM22" s="84"/>
       <c r="DN22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DO22" s="84"/>
       <c r="DP22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DQ22" s="84"/>
       <c r="DR22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DS22" s="84"/>
       <c r="DT22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DU22" s="84"/>
       <c r="DV22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DW22" s="84"/>
       <c r="DX22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DY22" s="84"/>
       <c r="DZ22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="EA22" s="84"/>
       <c r="EB22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="EC22" s="84"/>
       <c r="ED22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="EE22" s="84"/>
       <c r="EF22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="EG22" s="84"/>
       <c r="EH22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="EI22" s="84"/>
       <c r="EJ22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="EK22" s="84"/>
       <c r="EL22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="EM22" s="84"/>
       <c r="EN22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="EO22" s="84"/>
       <c r="EP22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="EQ22" s="84"/>
       <c r="ER22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="ES22" s="84"/>
       <c r="ET22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="EU22" s="84"/>
       <c r="EV22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="EW22" s="84"/>
       <c r="EX22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="EY22" s="84"/>
       <c r="EZ22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="FA22" s="84"/>
       <c r="FB22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="FC22" s="84"/>
       <c r="FD22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="FE22" s="84"/>
       <c r="FF22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="FG22" s="84"/>
       <c r="FH22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="FI22" s="84"/>
       <c r="FJ22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="FK22" s="84"/>
       <c r="FL22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="FM22" s="84"/>
       <c r="FN22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="FO22" s="84"/>
       <c r="FP22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="FQ22" s="84"/>
       <c r="FR22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="FS22" s="84"/>
       <c r="FT22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="FU22" s="84"/>
       <c r="FV22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="FW22" s="84"/>
       <c r="FX22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="FY22" s="84"/>
       <c r="FZ22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="GA22" s="84"/>
       <c r="GB22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="GC22" s="84"/>
       <c r="GD22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="GE22" s="84"/>
       <c r="GF22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="GG22" s="84"/>
       <c r="GH22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="GI22" s="84"/>
       <c r="GJ22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="GK22" s="84"/>
       <c r="GL22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="GM22" s="84"/>
       <c r="GN22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="GO22" s="84"/>
       <c r="GP22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="GQ22" s="84"/>
       <c r="GR22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="GS22" s="84"/>
       <c r="GT22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="GU22" s="84"/>
       <c r="GV22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="GW22" s="84"/>
       <c r="GX22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="GY22" s="84"/>
       <c r="GZ22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="HA22" s="84"/>
       <c r="HB22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="HC22" s="84"/>
       <c r="HD22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="HE22" s="84"/>
       <c r="HF22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="HG22" s="84"/>
       <c r="HH22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="HI22" s="84"/>
       <c r="HJ22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="HK22" s="84"/>
       <c r="HL22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="HM22" s="84"/>
       <c r="HN22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="HO22" s="84"/>
       <c r="HP22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="HQ22" s="84"/>
       <c r="HR22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="HS22" s="84"/>
       <c r="HT22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="HU22" s="84"/>
       <c r="HV22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="HW22" s="84"/>
       <c r="HX22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="HY22" s="84"/>
       <c r="HZ22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="IA22" s="84"/>
       <c r="IB22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="IC22" s="84"/>
       <c r="ID22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="IE22" s="84"/>
       <c r="IF22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="IG22" s="84"/>
       <c r="IH22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="II22" s="84"/>
       <c r="IJ22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="IK22" s="84"/>
       <c r="IL22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="IM22" s="84"/>
       <c r="IN22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="IO22" s="84"/>
       <c r="IP22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="IQ22" s="84"/>
       <c r="IR22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="IS22" s="84"/>
       <c r="IT22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="IU22" s="84"/>
       <c r="IV22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="IW22" s="84"/>
       <c r="IX22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="IY22" s="84"/>
       <c r="IZ22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="JA22" s="84"/>
       <c r="JB22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="JC22" s="84"/>
       <c r="JD22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="JE22" s="84"/>
       <c r="JF22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="JG22" s="84"/>
       <c r="JH22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="JI22" s="84"/>
       <c r="JJ22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="JK22" s="84"/>
       <c r="JL22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="JM22" s="84"/>
       <c r="JN22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="JO22" s="84"/>
       <c r="JP22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="JQ22" s="84"/>
       <c r="JR22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="JS22" s="84"/>
       <c r="JT22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="JU22" s="84"/>
       <c r="JV22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="JW22" s="84"/>
       <c r="JX22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="JY22" s="84"/>
       <c r="JZ22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="KA22" s="84"/>
       <c r="KB22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="KC22" s="84"/>
       <c r="KD22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="KE22" s="84"/>
       <c r="KF22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="KG22" s="84"/>
       <c r="KH22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="KI22" s="84"/>
       <c r="KJ22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="KK22" s="84"/>
       <c r="KL22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="KM22" s="84"/>
       <c r="KN22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="KO22" s="84"/>
       <c r="KP22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="KQ22" s="84"/>
       <c r="KR22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="KS22" s="84"/>
       <c r="KT22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="KU22" s="84"/>
       <c r="KV22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="KW22" s="84"/>
       <c r="KX22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="KY22" s="84"/>
       <c r="KZ22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="LA22" s="84"/>
       <c r="LB22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="LC22" s="84"/>
       <c r="LD22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="LE22" s="84"/>
       <c r="LF22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="LG22" s="84"/>
       <c r="LH22" s="83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="LI22" s="84"/>
     </row>
@@ -11208,7 +11245,7 @@
       <c r="AH23" s="85"/>
       <c r="AI23" s="86"/>
       <c r="AJ23" s="85" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK23" s="86"/>
       <c r="AL23" s="85"/>
@@ -11828,14 +11865,14 @@
       <formula>NOT(ISERROR(SEARCH("占",B3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3 C5 G5 E5 G3 E3 I3 I5 K3 M3 K5 M5 LI5 LG5 LE5 LC5 LA5 KY5 KW5 KU5 KS5 KQ5 O3 Q3 S3 U3 W3 Y3 AA3 AC3 AE3 AG3 AI3 AK3 AM3 AO3 AQ3 AS3 AU3 AW3 AY3 BA3 BC3 BE3 BG3 BI3 BK3 BM3 BO3 BQ3 BS3 BU3 BW3 BY3 CA3 CC3 CE3 CG3 CI3 CK3 CM3 CO3 CQ3 CS3 CU3 CW3 CY3 DA3 DC3 DE3 DG3 DI3 DK3 DM3 DO3 DQ3 DS3 DU3 DW3 DY3 EA3 EC3 EE3 EG3 EI3 EK3 EM3 EO3 EQ3 ES3 EU3 EW3 EY3 FA3 FC3 FE3 FG3 FI3 FK3 FM3 FO3 FQ3 FS3 FU3 FW3 FY3 GA3 GC3 GE3 GG3 GI3 GK3 GM3 GO3 GQ3 GS3 GU3 GW3 GY3 HA3 HC3 HE3 HG3 HI3 HK3 HM3 HO3 HQ3 HS3 HU3 HW3 HY3 IA3 IC3 IE3 IG3 II3 IK3 IM3 IO3 IQ3 IS3 IU3 IW3 IY3 JA3 JC3 JE3 JG3 JI3 JK3 JM3 JO3 JQ3 JS3 JU3 JW3 JY3 KA3 KC3 KE3 KG3 KI3 KK3 KM3 KO3 KQ3 KS3 KU3 KW3 KY3 LA3 LC3 LE3 LG3 LI3 KO5 KM5 KK5 KI5 O5 Q5 S5 U5 W5 Y5 AA5 AC5 AE5 AG5 AI5 AK5 AM5 AO5 AQ5 AS5 AU5 AW5 AY5 BA5 BC5 BE5 BG5 BI5 BK5 BM5 BO5 BQ5 BS5 BU5 BW5 BY5 CA5 CC5 CE5 CG5 CI5 CK5 CM5 CO5 CQ5 CS5 CU5 CW5 CY5 DA5 DC5 DE5 DG5 DI5 DK5 DM5 DO5 DQ5 DS5 DU5 DW5 DY5 EA5 EC5 EE5 EG5 EI5 EK5 EM5 EO5 EQ5 ES5 EU5 EW5 EY5 FA5 FC5 FE5 FG5 FI5 FK5 FM5 FO5 FQ5 FS5 FU5 FW5 FY5 GA5 GC5 GE5 GG5 GI5 GK5 GM5 GO5 GQ5 GS5 GU5 GW5 GY5 HA5 HC5 HE5 HG5 HI5 HK5 HM5 HO5 HQ5 HS5 HU5 HW5 HY5 IA5 IC5 IE5 IG5 II5 IK5 IM5 IO5 IQ5 IS5 IU5 IW5 IY5 JA5 JC5 JE5 JG5 JI5 JK5 JM5 JO5 JQ5 JS5 JU5 JW5 JY5 KA5 KC5 KE5 KG5 C8 G10 E10 G8 E8 G20 E20 G18 E18 G16 E16 G14 E14 G12 E12 C10 C12 C14 C16 C18 C20 I12 I14 I16 I18 I20 I8 I10 LI20 LG20 LE20 LC20 K8 M8 K10 M10 K12 M12 K14 M14 K16 M16 K18 M18 K20 M20 HW20 HU20 HS20 HQ20 HO20 HM20 HK20 HI20 HG20 HE20 HC20 HA20 GY20 GW20 GU20 GS20 GQ20 GO20 GM20 GK20 GI20 GG20 GE20 GC20 GA20 FY20 FW20 FU20 FS20 FQ20 FO20 FM20 FK20 FI20 FG20 FE20 FC20 FA20 EY20 EW20 EU20 ES20 EQ20 EO20 EM20 EK20 EI20 EG20 EE20 EC20 EA20 DY20 DW20 DU20 DS20 DQ20 DO20 DM20 DK20 DI20 DG20 DE20 DC20 DA20 CY20 CW20 CU20 CS20 CQ20 CO20 CM20 CK20 CI20 CG20 CE20 CC20 CA20 BY20 BW20 BU20 BS20 BQ20 BO20 BM20 BK20 BI20 BG20 BE20 BC20 BA20 AY20 AW20 AU20 AS20 AQ20 AO20 AM20 AK20 AI20 AG20 AE20 AC20 AA20 Y20 W20 U20 S20 Q20 O20 HY20 IA20 JI20 JK20 LI18 LG18 LE18 LC18 LA18 KY18 KW18 KU18 KS18 KQ18 KO18 KM18 KK18 KI18 KG18 KE18 KC18 KA18 JY18 JW18 JU18 JS18 JQ18 JO18 JM18 JK18 JI18 JG18 JE18 JC18 JA18 IY18 IW18 IU18 IS18 IQ18 IO18 IM18 IK18 II18 IG18 IE18 IC18 IA18 HY18 HW18 HU18 HS18 HQ18 HO18 HM18 HK18 HI18 HG18 HE18 HC18 HA18 GY18 GW18 GU18 GS18 GQ18 GO18 GM18 GK18 GI18 GG18 GE18 GC18 GA18 FY18 FW18 FU18 FS18 FQ18 FO18 FM18 FK18 FI18 FG18 FE18 FC18 FA18 EY18 EW18 EU18 ES18 EQ18 EO18 EM18 EK18 EI18 EG18 EE18 EC18 EA18 DY18 DW18 DU18 DS18 DQ18 DO18 DM18 DK18 DI18 DG18 DE18 DC18 DA18 CY18 CW18 CU18 CS18 CQ18 CO18 CM18 CK18 CI18 CG18 CE18 CC18 CA18 BY18 BW18 BU18 BS18 BQ18 BO18 BM18 BK18 BI18 BG18 BE18 BC18 BA18 AY18 AW18 AU18 AS18 AQ18 AO18 AM18 AK18 AI18 AG18 AE18 AC18 AA18 Y18 W18 U18 S18 Q18 O18 IC20 IE20 JM20 JO20 LI16 LG16 LE16 LC16 LA16 KY16 KW16 KU16 KS16 KQ16 KO16 KM16 KK16 KI16 KG16 KE16 KC16 KA16 JY16 JW16 JU16 JS16 JQ16 JO16 JM16 JK16 JI16 JG16 JE16 JC16 JA16 IY16 IW16 IU16 IS16 IQ16 IO16 IM16 IK16 II16 IG16 IE16 IC16 IA16 HY16 HW16 HU16 HS16 HQ16 HO16 HM16 HK16 HI16 HG16 HE16 HC16 HA16 GY16 GW16 GU16 GS16 GQ16 GO16 GM16 GK16 GI16 GG16 GE16 GC16 GA16 FY16 FW16 FU16 FS16 FQ16 FO16 FM16 FK16 FI16 FG16 FE16 FC16 FA16 EY16 EW16 EU16 ES16 EQ16 EO16 EM16 EK16 EI16 EG16 EE16 EC16 EA16 DY16 DW16 DU16 DS16 DQ16 DO16 DM16 DK16 DI16 DG16 DE16 DC16 DA16 CY16 CW16 CU16 CS16 CQ16 CO16 CM16 CK16 CI16 CG16 CE16 CC16 CA16 BY16 BW16 BU16 BS16 BQ16 BO16 BM16 BK16 BI16 BG16 BE16 BC16 BA16 AY16 AW16 AU16 AS16 AQ16 AO16 AM16 AK16 AI16 AG16 AE16 AC16 AA16 Y16 W16 U16 S16 Q16 O16 IG20 II20 JQ20 JS20 LI14 LG14 LE14 LC14 LA14 KY14 KW14 KU14 KS14 KQ14 KO14 KM14 KK14 KI14 KG14 KE14 KC14 KA14 JY14 JW14 JU14 JS14 JQ14 JO14 JM14 JK14 JI14 JG14 JE14 JC14 JA14 IY14 IW14 IU14 IS14 IQ14 IO14 IM14 IK14 II14 IG14 IE14 IC14 IA14 HY14 HW14 HU14 HS14 HQ14 HO14 HM14 HK14 HI14 HG14 HE14 HC14 HA14 GY14 GW14 GU14 GS14 GQ14 GO14 GM14 GK14 GI14 GG14 GE14 GC14 GA14 FY14 FW14 FU14 FS14 FQ14 FO14 FM14 FK14 FI14 FG14 FE14 FC14 FA14 EY14 EW14 EU14 ES14 EQ14 EO14 EM14 EK14 EI14 EG14 EE14 EC14 EA14 DY14 DW14 DU14 DS14 DQ14 DO14 DM14 DK14 DI14 DG14 DE14 DC14 DA14 CY14 CW14 CU14 CS14 CQ14 CO14 CM14 CK14 CI14 CG14 CE14 CC14 CA14 BY14 BW14 BU14 BS14 BQ14 BO14 BM14 BK14 BI14 BG14 BE14 BC14 BA14 AY14 AW14 AU14 AS14 AQ14 AO14 AM14 AK14 AI14 AG14 AE14 AC14 AA14 Y14 W14 U14 S14 Q14 O14 IK20 IM20 JU20 JW20 LI12 LG12 LE12 LC12 LA12 KY12 KW12 KU12 KS12 KQ12 KO12 KM12 KK12 KI12 KG12 KE12 KC12 KA12 JY12 JW12 JU12 JS12 JQ12 JO12 JM12 JK12 JI12 JG12 JE12 JC12 JA12 IY12 IW12 IU12 IS12 IQ12 IO12 IM12 IK12 II12 IG12 IE12 IC12 IA12 HY12 HW12 HU12 HS12 HQ12 HO12 HM12 HK12 HI12 HG12 HE12 HC12 HA12 GY12 GW12 GU12 GS12 GQ12 GO12 GM12 GK12 GI12 GG12 GE12 GC12 GA12 FY12 FW12 FU12 FS12 FQ12 FO12 FM12 FK12 FI12 FG12 FE12 FC12 FA12 EY12 EW12 EU12 ES12 EQ12 EO12 EM12 EK12 EI12 EG12 EE12 EC12 EA12 DY12 DW12 DU12 DS12 DQ12 DO12 DM12 DK12 DI12 DG12 DE12 DC12 DA12 CY12 CW12 CU12 CS12 CQ12 CO12 CM12 CK12 CI12 CG12 CE12 CC12 CA12 BY12 BW12 BU12 BS12 BQ12 BO12 BM12 BK12 BI12 BG12 BE12 BC12 BA12 AY12 AW12 AU12 AS12 AQ12 AO12 AM12 AK12 AI12 AG12 AE12 AC12 AA12 Y12 W12 U12 S12 Q12 O12 IO20 IQ20 JY20 KA20 LI10 LG10 LE10 LC10 LA10 KY10 KW10 KU10 KS10 KQ10 KO10 KM10 KK10 KI10 KG10 KE10 KC10 KA10 JY10 JW10 JU10 JS10 JQ10 JO10 JM10 JK10 JI10 JG10 JE10 JC10 JA10 IY10 IW10 IU10 IS10 IQ10 IO10 IM10 IK10 II10 IG10 IE10 IC10 IA10 HY10 HW10 HU10 HS10 HQ10 HO10 HM10 HK10 HI10 HG10 HE10 HC10 HA10 GY10 GW10 GU10 GS10 GQ10 GO10 GM10 GK10 GI10 GG10 GE10 GC10 GA10 FY10 FW10 FU10 FS10 FQ10 FO10 FM10 FK10 FI10 FG10 FE10 FC10 FA10 EY10 EW10 EU10 ES10 EQ10 EO10 EM10 EK10 EI10 EG10 EE10 EC10 EA10 DY10 DW10 DU10 DS10 DQ10 DO10 DM10 DK10 DI10 DG10 DE10 DC10 DA10 CY10 CW10 CU10 CS10 CQ10 CO10 CM10 CK10 CI10 CG10 CE10 CC10 CA10 BY10 BW10 BU10 BS10 BQ10 BO10 BM10 BK10 BI10 BG10 BE10 BC10 BA10 AY10 AW10 AU10 AS10 AQ10 AO10 AM10 AK10 AI10 AG10 AE10 AC10 AA10 Y10 W10 U10 S10 Q10 O10 IS20 IU20 KC20 KE20 LI8 LG8 LE8 LC8 LA8 KY8 KW8 KU8 KS8 KQ8 KO8 KM8 KK8 KI8 KG8 KE8 KC8 KA8 JY8 JW8 JU8 JS8 JQ8 JO8 JM8 JK8 JI8 JG8 JE8 JC8 JA8 IY8 IW8 IU8 IS8 IQ8 IO8 IM8 IK8 II8 IG8 IE8 IC8 IA8 HY8 HW8 HU8 HS8 HQ8 HO8 HM8 HK8 HI8 HG8 HE8 HC8 HA8 GY8 GW8 GU8 GS8 GQ8 GO8 GM8 GK8 GI8 GG8 GE8 GC8 GA8 FY8 FW8 FU8 FS8 FQ8 FO8 FM8 FK8 FI8 FG8 FE8 FC8 FA8 EY8 EW8 EU8 ES8 EQ8 EO8 EM8 EK8 EI8 EG8 EE8 EC8 EA8 DY8 DW8 DU8 DS8 DQ8 DO8 DM8 DK8 DI8 DG8 DE8 DC8 DA8 CY8 CW8 CU8 CS8 CQ8 CO8 CM8 CK8 CI8 CG8 CE8 CC8 CA8 BY8 BW8 BU8 BS8 BQ8 BO8 BM8 BK8 BI8 BG8 BE8 BC8 BA8 AY8 AW8 AU8 AS8 AQ8 AO8 AM8 AK8 AI8 AG8 AE8 AC8 AA8 Y8 W8 U8 S8 Q8 O8 IW20 IY20 KG20 KI20 LA20 KY20 KW20 KU20 KS20 KQ20 KO20 JG20 JE20 KM20 KK20 JC20 JA20">
-    <cfRule type="containsBlanks" dxfId="1" priority="3">
-      <formula>LEN(TRIM(C3))=0</formula>
+  <conditionalFormatting sqref="C3:C21 KY3:KY10 E3:E21 KW3:KW21 LI3:LI21 KU3:KU21 KS3:KS21 G3:G21 KQ3:KQ21 LG3:LG10 KO3:KO21 KM3:KM21 I3:I21 KK3:KK21 LE3:LE10 KI3:KI21 KG3:KG21 K3:K21 KE3:KE21 LC3:LC10 KC3:KC21 KA3:KA21 M3:M21 JY3:JY21 LA3:LA10 JW3:JW21 JU3:JU21 O3:O21 JS3:JS21 Q3:Q21 JQ3:JQ21 S3:S21 JO3:JO21 U3:U21 JM3:JM21 W3:W21 JK3:JK21 Y3:Y21 JI3:JI21 JG3:JG21 AA3:AA21 JE3:JE21 JC3:JC21 AC3:AC21 JA3:JA21 IY3:IY21 AE3:AE21 IW3:IW21 IU3:IU21 AG3:AG21 IS3:IS21 IQ3:IQ21 AI3:AI21 IO3:IO21 IM3:IM21 AK3:AK21 IK3:IK21 II3:II21 AM3:AM21 IG3:IG21 IE3:IE21 AO3:AO21 IC3:IC21 IA3:IA21 AQ3:AQ21 HY3:HY21 HW3:HW21 AS3:AS21 HU3:HU21 HS3:HS21 AU3:AU21 HQ3:HQ21 HO3:HO21 AW3:AW21 HM3:HM21 HK3:HK21 AY3:AY21 HI3:HI21 HG3:HG21 BA3:BA21 HE3:HE21 HC3:HC21 BC3:BC21 HA3:HA21 GY3:GY21 BE3:BE21 GW3:GW21 GU3:GU21 BG3:BG21 GS3:GS21 GQ3:GQ21 BI3:BI21 GO3:GO21 GM3:GM21 BK3:BK21 GK3:GK21 GI3:GI21 BM3:BM21 GG3:GG21 GE3:GE21 BO3:BO21 GC3:GC21 GA3:GA21 BQ3:BQ21 FY3:FY21 FW3:FW21 BS3:BS21 FU3:FU21 FS3:FS21 BU3:BU21 FQ3:FQ21 FO3:FO21 BW3:BW21 FM3:FM21 FK3:FK21 BY3:BY21 FI3:FI21 FG3:FG21 CA3:CA21 FE3:FE21 FC3:FC21 CC3:CC21 FA3:FA21 EY3:EY21 CE3:CE21 EW3:EW21 EU3:EU21 CG3:CG21 ES3:ES21 EQ3:EQ21 CI3:CI21 EO3:EO21 EM3:EM21 CK3:CK21 EK3:EK21 EI3:EI21 CM3:CM21 EG3:EG21 EE3:EE21 CO3:CO21 EC3:EC21 EA3:EA21 CQ3:CQ21 DY3:DY21 DW3:DW21 CS3:CS21 DU3:DU21 DS3:DS21 CU3:CU21 DQ3:DQ21 DO3:DO21 CW3:CW21 DM3:DM21 DK3:DK21 CY3:CY21 DI3:DI21 DG3:DG21 DA3:DA21 DE3:DE21 DC3:DC21 KY12:KY21 KV11 KT11 KX11:LH11 KR11 KP11 KN11 LG12:LG21 KL11 KJ11 KH11 LE12:LE21 KF11 KD11 KB11 LC12:LC21 JZ11 JX11 JV11 LA12:LA21 JT11 JR11 JP11 JN11 JL11 JJ11 JH11 X11 JF11 JD11 Z11 JB11 IZ11 AB11 IX11 IV11 AD11 IT11 IR11 AF11 IP11 IN11 AH11 IL11 IJ11 AJ11 IH11 IF11 AL11 ID11 IB11 AN11 HZ11 HX11 AP11 HV11 HT11 AR11 HR11 HP11 AT11 HN11 HL11 AV11 HJ11 HH11 AX11 HF11 HD11 AZ11 HB11 GZ11 BB11 GX11 GV11 BD11 GT11 GR11 BF11 GP11 GN11 BH11 GL11 GJ11 BJ11 GH11 GF11 BL11 GD11 GB11 BN11 FZ11 FX11 BP11 FV11 FT11 BR11 FR11 FP11 BT11 FN11 FL11 BV11 FJ11 FH11 BX11 FF11 FD11 BZ11 FB11 EZ11 CB11 EX11 EV11 CD11 ET11 ER11 CF11 EP11 EN11 CH11 EL11 EJ11 CJ11 EH11 EF11 CL11 ED11 EB11 CN11 DZ11 DX11 CP11 DV11 DT11 CR11 DR11 DP11 CT11 DN11 DL11 CV11 DJ11 DH11 CX11 DF11 DD11 CZ11 DB11">
+    <cfRule type="containsText" dxfId="1" priority="4" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",C3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C21 KY3:KY10 E3:E21 KW3:KW21 LI3:LI21 KU3:KU21 KS3:KS21 G3:G21 KQ3:KQ21 LG3:LG10 KO3:KO21 KM3:KM21 I3:I21 KK3:KK21 LE3:LE10 KI3:KI21 KG3:KG21 K3:K21 KE3:KE21 LC3:LC10 KC3:KC21 KA3:KA21 M3:M21 JY3:JY21 LA3:LA10 JW3:JW21 JU3:JU21 O3:O21 JS3:JS21 Q3:Q21 JQ3:JQ21 S3:S21 JO3:JO21 U3:U21 JM3:JM21 W3:W21 JK3:JK21 Y3:Y21 JI3:JI21 JG3:JG21 AA3:AA21 JE3:JE21 JC3:JC21 AC3:AC21 JA3:JA21 IY3:IY21 AE3:AE21 IW3:IW21 IU3:IU21 AG3:AG21 IS3:IS21 IQ3:IQ21 AI3:AI21 IO3:IO21 IM3:IM21 AK3:AK21 IK3:IK21 II3:II21 AM3:AM21 IG3:IG21 IE3:IE21 AO3:AO21 IC3:IC21 IA3:IA21 AQ3:AQ21 HY3:HY21 HW3:HW21 AS3:AS21 HU3:HU21 HS3:HS21 AU3:AU21 HQ3:HQ21 HO3:HO21 AW3:AW21 HM3:HM21 HK3:HK21 AY3:AY21 HI3:HI21 HG3:HG21 BA3:BA21 HE3:HE21 HC3:HC21 BC3:BC21 HA3:HA21 GY3:GY21 BE3:BE21 GW3:GW21 GU3:GU21 BG3:BG21 GS3:GS21 GQ3:GQ21 BI3:BI21 GO3:GO21 GM3:GM21 BK3:BK21 GK3:GK21 GI3:GI21 BM3:BM21 GG3:GG21 GE3:GE21 BO3:BO21 GC3:GC21 GA3:GA21 BQ3:BQ21 FY3:FY21 FW3:FW21 BS3:BS21 FU3:FU21 FS3:FS21 BU3:BU21 FQ3:FQ21 FO3:FO21 BW3:BW21 FM3:FM21 FK3:FK21 BY3:BY21 FI3:FI21 FG3:FG21 CA3:CA21 FE3:FE21 FC3:FC21 CC3:CC21 FA3:FA21 EY3:EY21 CE3:CE21 EW3:EW21 EU3:EU21 CG3:CG21 ES3:ES21 EQ3:EQ21 CI3:CI21 EO3:EO21 EM3:EM21 CK3:CK21 EK3:EK21 EI3:EI21 CM3:CM21 EG3:EG21 EE3:EE21 CO3:CO21 EC3:EC21 EA3:EA21 CQ3:CQ21 DY3:DY21 DW3:DW21 CS3:CS21 DU3:DU21 DS3:DS21 CU3:CU21 DQ3:DQ21 DO3:DO21 CW3:CW21 DM3:DM21 DK3:DK21 CY3:CY21 DI3:DI21 DG3:DG21 DA3:DA21 DE3:DE21 DC3:DC21 KY12:KY21 KV11 KT11 KX11:LH11 KR11 KP11 KN11 LG12:LG21 KL11 KJ11 KH11 LE12:LE21 KF11 KD11 KB11 LC12:LC21 JZ11 JX11 JV11 LA12:LA21 JT11 JR11 JP11 JN11 JL11 JJ11 JH11 X11 JF11 JD11 Z11 JB11 IZ11 AB11 IX11 IV11 AD11 IT11 IR11 AF11 IP11 IN11 AH11 IL11 IJ11 AJ11 IH11 IF11 AL11 ID11 IB11 AN11 HZ11 HX11 AP11 HV11 HT11 AR11 HR11 HP11 AT11 HN11 HL11 AV11 HJ11 HH11 AX11 HF11 HD11 AZ11 HB11 GZ11 BB11 GX11 GV11 BD11 GT11 GR11 BF11 GP11 GN11 BH11 GL11 GJ11 BJ11 GH11 GF11 BL11 GD11 GB11 BN11 FZ11 FX11 BP11 FV11 FT11 BR11 FR11 FP11 BT11 FN11 FL11 BV11 FJ11 FH11 BX11 FF11 FD11 BZ11 FB11 EZ11 CB11 EX11 EV11 CD11 ET11 ER11 CF11 EP11 EN11 CH11 EL11 EJ11 CJ11 EH11 EF11 CL11 ED11 EB11 CN11 DZ11 DX11 CP11 DV11 DT11 CR11 DR11 DP11 CT11 DN11 DL11 CV11 DJ11 DH11 CX11 DF11 DD11 CZ11 DB11">
-    <cfRule type="containsText" dxfId="2" priority="4" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",C3)))</formula>
+  <conditionalFormatting sqref="C3 C5 G5 E5 G3 E3 I3 I5 K3 M3 K5 M5 LI5 LG5 LE5 LC5 LA5 KY5 KW5 KU5 KS5 KQ5 O3 Q3 S3 U3 W3 Y3 AA3 AC3 AE3 AG3 AI3 AK3 AM3 AO3 AQ3 AS3 AU3 AW3 AY3 BA3 BC3 BE3 BG3 BI3 BK3 BM3 BO3 BQ3 BS3 BU3 BW3 BY3 CA3 CC3 CE3 CG3 CI3 CK3 CM3 CO3 CQ3 CS3 CU3 CW3 CY3 DA3 DC3 DE3 DG3 DI3 DK3 DM3 DO3 DQ3 DS3 DU3 DW3 DY3 EA3 EC3 EE3 EG3 EI3 EK3 EM3 EO3 EQ3 ES3 EU3 EW3 EY3 FA3 FC3 FE3 FG3 FI3 FK3 FM3 FO3 FQ3 FS3 FU3 FW3 FY3 GA3 GC3 GE3 GG3 GI3 GK3 GM3 GO3 GQ3 GS3 GU3 GW3 GY3 HA3 HC3 HE3 HG3 HI3 HK3 HM3 HO3 HQ3 HS3 HU3 HW3 HY3 IA3 IC3 IE3 IG3 II3 IK3 IM3 IO3 IQ3 IS3 IU3 IW3 IY3 JA3 JC3 JE3 JG3 JI3 JK3 JM3 JO3 JQ3 JS3 JU3 JW3 JY3 KA3 KC3 KE3 KG3 KI3 KK3 KM3 KO3 KQ3 KS3 KU3 KW3 KY3 LA3 LC3 LE3 LG3 LI3 KO5 KM5 KK5 KI5 O5 Q5 S5 U5 W5 Y5 AA5 AC5 AE5 AG5 AI5 AK5 AM5 AO5 AQ5 AS5 AU5 AW5 AY5 BA5 BC5 BE5 BG5 BI5 BK5 BM5 BO5 BQ5 BS5 BU5 BW5 BY5 CA5 CC5 CE5 CG5 CI5 CK5 CM5 CO5 CQ5 CS5 CU5 CW5 CY5 DA5 DC5 DE5 DG5 DI5 DK5 DM5 DO5 DQ5 DS5 DU5 DW5 DY5 EA5 EC5 EE5 EG5 EI5 EK5 EM5 EO5 EQ5 ES5 EU5 EW5 EY5 FA5 FC5 FE5 FG5 FI5 FK5 FM5 FO5 FQ5 FS5 FU5 FW5 FY5 GA5 GC5 GE5 GG5 GI5 GK5 GM5 GO5 GQ5 GS5 GU5 GW5 GY5 HA5 HC5 HE5 HG5 HI5 HK5 HM5 HO5 HQ5 HS5 HU5 HW5 HY5 IA5 IC5 IE5 IG5 II5 IK5 IM5 IO5 IQ5 IS5 IU5 IW5 IY5 JA5 JC5 JE5 JG5 JI5 JK5 JM5 JO5 JQ5 JS5 JU5 JW5 JY5 KA5 KC5 KE5 KG5 C8 G10 E10 G8 E8 G20 E20 G18 E18 G16 E16 G14 E14 G12 E12 C10 C12 C14 C16 C18 C20 I12 I14 I16 I18 I20 I8 I10 LI20 LG20 LE20 LC20 K8 M8 K10 M10 K12 M12 K14 M14 K16 M16 K18 M18 K20 M20 HW20 HU20 HS20 HQ20 HO20 HM20 HK20 HI20 HG20 HE20 HC20 HA20 GY20 GW20 GU20 GS20 GQ20 GO20 GM20 GK20 GI20 GG20 GE20 GC20 GA20 FY20 FW20 FU20 FS20 FQ20 FO20 FM20 FK20 FI20 FG20 FE20 FC20 FA20 EY20 EW20 EU20 ES20 EQ20 EO20 EM20 EK20 EI20 EG20 EE20 EC20 EA20 DY20 DW20 DU20 DS20 DQ20 DO20 DM20 DK20 DI20 DG20 DE20 DC20 DA20 CY20 CW20 CU20 CS20 CQ20 CO20 CM20 CK20 CI20 CG20 CE20 CC20 CA20 BY20 BW20 BU20 BS20 BQ20 BO20 BM20 BK20 BI20 BG20 BE20 BC20 BA20 AY20 AW20 AU20 AS20 AQ20 AO20 AM20 AK20 AI20 AG20 AE20 AC20 AA20 Y20 W20 U20 S20 Q20 O20 HY20 IA20 JI20 JK20 LI18 LG18 LE18 LC18 LA18 KY18 KW18 KU18 KS18 KQ18 KO18 KM18 KK18 KI18 KG18 KE18 KC18 KA18 JY18 JW18 JU18 JS18 JQ18 JO18 JM18 JK18 JI18 JG18 JE18 JC18 JA18 IY18 IW18 IU18 IS18 IQ18 IO18 IM18 IK18 II18 IG18 IE18 IC18 IA18 HY18 HW18 HU18 HS18 HQ18 HO18 HM18 HK18 HI18 HG18 HE18 HC18 HA18 GY18 GW18 GU18 GS18 GQ18 GO18 GM18 GK18 GI18 GG18 GE18 GC18 GA18 FY18 FW18 FU18 FS18 FQ18 FO18 FM18 FK18 FI18 FG18 FE18 FC18 FA18 EY18 EW18 EU18 ES18 EQ18 EO18 EM18 EK18 EI18 EG18 EE18 EC18 EA18 DY18 DW18 DU18 DS18 DQ18 DO18 DM18 DK18 DI18 DG18 DE18 DC18 DA18 CY18 CW18 CU18 CS18 CQ18 CO18 CM18 CK18 CI18 CG18 CE18 CC18 CA18 BY18 BW18 BU18 BS18 BQ18 BO18 BM18 BK18 BI18 BG18 BE18 BC18 BA18 AY18 AW18 AU18 AS18 AQ18 AO18 AM18 AK18 AI18 AG18 AE18 AC18 AA18 Y18 W18 U18 S18 Q18 O18 IC20 IE20 JM20 JO20 LI16 LG16 LE16 LC16 LA16 KY16 KW16 KU16 KS16 KQ16 KO16 KM16 KK16 KI16 KG16 KE16 KC16 KA16 JY16 JW16 JU16 JS16 JQ16 JO16 JM16 JK16 JI16 JG16 JE16 JC16 JA16 IY16 IW16 IU16 IS16 IQ16 IO16 IM16 IK16 II16 IG16 IE16 IC16 IA16 HY16 HW16 HU16 HS16 HQ16 HO16 HM16 HK16 HI16 HG16 HE16 HC16 HA16 GY16 GW16 GU16 GS16 GQ16 GO16 GM16 GK16 GI16 GG16 GE16 GC16 GA16 FY16 FW16 FU16 FS16 FQ16 FO16 FM16 FK16 FI16 FG16 FE16 FC16 FA16 EY16 EW16 EU16 ES16 EQ16 EO16 EM16 EK16 EI16 EG16 EE16 EC16 EA16 DY16 DW16 DU16 DS16 DQ16 DO16 DM16 DK16 DI16 DG16 DE16 DC16 DA16 CY16 CW16 CU16 CS16 CQ16 CO16 CM16 CK16 CI16 CG16 CE16 CC16 CA16 BY16 BW16 BU16 BS16 BQ16 BO16 BM16 BK16 BI16 BG16 BE16 BC16 BA16 AY16 AW16 AU16 AS16 AQ16 AO16 AM16 AK16 AI16 AG16 AE16 AC16 AA16 Y16 W16 U16 S16 Q16 O16 IG20 II20 JQ20 JS20 LI14 LG14 LE14 LC14 LA14 KY14 KW14 KU14 KS14 KQ14 KO14 KM14 KK14 KI14 KG14 KE14 KC14 KA14 JY14 JW14 JU14 JS14 JQ14 JO14 JM14 JK14 JI14 JG14 JE14 JC14 JA14 IY14 IW14 IU14 IS14 IQ14 IO14 IM14 IK14 II14 IG14 IE14 IC14 IA14 HY14 HW14 HU14 HS14 HQ14 HO14 HM14 HK14 HI14 HG14 HE14 HC14 HA14 GY14 GW14 GU14 GS14 GQ14 GO14 GM14 GK14 GI14 GG14 GE14 GC14 GA14 FY14 FW14 FU14 FS14 FQ14 FO14 FM14 FK14 FI14 FG14 FE14 FC14 FA14 EY14 EW14 EU14 ES14 EQ14 EO14 EM14 EK14 EI14 EG14 EE14 EC14 EA14 DY14 DW14 DU14 DS14 DQ14 DO14 DM14 DK14 DI14 DG14 DE14 DC14 DA14 CY14 CW14 CU14 CS14 CQ14 CO14 CM14 CK14 CI14 CG14 CE14 CC14 CA14 BY14 BW14 BU14 BS14 BQ14 BO14 BM14 BK14 BI14 BG14 BE14 BC14 BA14 AY14 AW14 AU14 AS14 AQ14 AO14 AM14 AK14 AI14 AG14 AE14 AC14 AA14 Y14 W14 U14 S14 Q14 O14 IK20 IM20 JU20 JW20 LI12 LG12 LE12 LC12 LA12 KY12 KW12 KU12 KS12 KQ12 KO12 KM12 KK12 KI12 KG12 KE12 KC12 KA12 JY12 JW12 JU12 JS12 JQ12 JO12 JM12 JK12 JI12 JG12 JE12 JC12 JA12 IY12 IW12 IU12 IS12 IQ12 IO12 IM12 IK12 II12 IG12 IE12 IC12 IA12 HY12 HW12 HU12 HS12 HQ12 HO12 HM12 HK12 HI12 HG12 HE12 HC12 HA12 GY12 GW12 GU12 GS12 GQ12 GO12 GM12 GK12 GI12 GG12 GE12 GC12 GA12 FY12 FW12 FU12 FS12 FQ12 FO12 FM12 FK12 FI12 FG12 FE12 FC12 FA12 EY12 EW12 EU12 ES12 EQ12 EO12 EM12 EK12 EI12 EG12 EE12 EC12 EA12 DY12 DW12 DU12 DS12 DQ12 DO12 DM12 DK12 DI12 DG12 DE12 DC12 DA12 CY12 CW12 CU12 CS12 CQ12 CO12 CM12 CK12 CI12 CG12 CE12 CC12 CA12 BY12 BW12 BU12 BS12 BQ12 BO12 BM12 BK12 BI12 BG12 BE12 BC12 BA12 AY12 AW12 AU12 AS12 AQ12 AO12 AM12 AK12 AI12 AG12 AE12 AC12 AA12 Y12 W12 U12 S12 Q12 O12 IO20 IQ20 JY20 KA20 LI10 LG10 LE10 LC10 LA10 KY10 KW10 KU10 KS10 KQ10 KO10 KM10 KK10 KI10 KG10 KE10 KC10 KA10 JY10 JW10 JU10 JS10 JQ10 JO10 JM10 JK10 JI10 JG10 JE10 JC10 JA10 IY10 IW10 IU10 IS10 IQ10 IO10 IM10 IK10 II10 IG10 IE10 IC10 IA10 HY10 HW10 HU10 HS10 HQ10 HO10 HM10 HK10 HI10 HG10 HE10 HC10 HA10 GY10 GW10 GU10 GS10 GQ10 GO10 GM10 GK10 GI10 GG10 GE10 GC10 GA10 FY10 FW10 FU10 FS10 FQ10 FO10 FM10 FK10 FI10 FG10 FE10 FC10 FA10 EY10 EW10 EU10 ES10 EQ10 EO10 EM10 EK10 EI10 EG10 EE10 EC10 EA10 DY10 DW10 DU10 DS10 DQ10 DO10 DM10 DK10 DI10 DG10 DE10 DC10 DA10 CY10 CW10 CU10 CS10 CQ10 CO10 CM10 CK10 CI10 CG10 CE10 CC10 CA10 BY10 BW10 BU10 BS10 BQ10 BO10 BM10 BK10 BI10 BG10 BE10 BC10 BA10 AY10 AW10 AU10 AS10 AQ10 AO10 AM10 AK10 AI10 AG10 AE10 AC10 AA10 Y10 W10 U10 S10 Q10 O10 IS20 IU20 KC20 KE20 LI8 LG8 LE8 LC8 LA8 KY8 KW8 KU8 KS8 KQ8 KO8 KM8 KK8 KI8 KG8 KE8 KC8 KA8 JY8 JW8 JU8 JS8 JQ8 JO8 JM8 JK8 JI8 JG8 JE8 JC8 JA8 IY8 IW8 IU8 IS8 IQ8 IO8 IM8 IK8 II8 IG8 IE8 IC8 IA8 HY8 HW8 HU8 HS8 HQ8 HO8 HM8 HK8 HI8 HG8 HE8 HC8 HA8 GY8 GW8 GU8 GS8 GQ8 GO8 GM8 GK8 GI8 GG8 GE8 GC8 GA8 FY8 FW8 FU8 FS8 FQ8 FO8 FM8 FK8 FI8 FG8 FE8 FC8 FA8 EY8 EW8 EU8 ES8 EQ8 EO8 EM8 EK8 EI8 EG8 EE8 EC8 EA8 DY8 DW8 DU8 DS8 DQ8 DO8 DM8 DK8 DI8 DG8 DE8 DC8 DA8 CY8 CW8 CU8 CS8 CQ8 CO8 CM8 CK8 CI8 CG8 CE8 CC8 CA8 BY8 BW8 BU8 BS8 BQ8 BO8 BM8 BK8 BI8 BG8 BE8 BC8 BA8 AY8 AW8 AU8 AS8 AQ8 AO8 AM8 AK8 AI8 AG8 AE8 AC8 AA8 Y8 W8 U8 S8 Q8 O8 IW20 IY20 KG20 KI20 LA20 KY20 KW20 KU20 KS20 KQ20 KO20 JG20 JE20 KM20 KK20 JC20 JA20">
+    <cfRule type="containsBlanks" dxfId="2" priority="3">
+      <formula>LEN(TRIM(C3))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22 LI22 LG22 LE22 LC22 LA22 KY22 KW22 KU22 KS22 KQ22 KO22 KM22 KK22 KI22 KG22 KE22 KC22 KA22 JY22 JW22 JU22 JS22 JQ22 JO22 JM22 JK22 JI22 JG22 JE22 JC22 JA22 IY22 IW22 IU22 IS22 IQ22 IO22 IM22 IK22 II22 IG22 IE22 IC22 IA22 HY22 HW22 HU22 HS22 HQ22 HO22 HM22 HK22 HI22 HG22 HE22 HC22 HA22 GY22 GW22 GU22 GS22 GQ22 GO22 GM22 GK22 GI22 GG22 GE22 GC22 GA22 FY22 FW22 FU22 FS22 FQ22 FO22 FM22 FK22 FI22 FG22 FE22 FC22 FA22 EY22 EW22 EU22 ES22 EQ22 EO22 EM22 EK22 EI22 EG22 EE22 EC22 EA22 DY22 DW22 DU22 DS22 DQ22 DO22 DM22 DK22 DI22 DG22 DE22 DC22 DA22 CY22 CW22 CU22 CS22 CQ22 CO22 CM22 CK22 CI22 CG22 CE22 CC22 CA22 BY22 BW22 BU22 BS22 BQ22 BO22 BM22 BK22 BI22 BG22 BE22 BC22 BA22 AY22 AW22 AU22 AS22 AQ22 AO22 AM22 AK22 AI22 AG22 AE22 AC22 AA22 Y22 W22 U22 S22 Q22 O22 M22 K22 I22 G22 E22">
@@ -11847,8 +11884,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO8 AO12 AO13 AO14 AO20 AO21 C3:C21 E3:E21 G3:G21 I3:I21 K3:K21 M3:M21 O3:O21 Q3:Q21 S3:S21 U3:U21 W3:W21 Y3:Y21 AA3:AA21 AC3:AC21 AE3:AE21 AG3:AG21 AI3:AI21 AK3:AK21 AM3:AM21 AO3:AO7 AO9:AO11 AO15:AO19 AQ3:AQ21 AS3:AS21 AU3:AU21 AW3:AW21 AY3:AY21 BA3:BA21 BC3:BC21 BE3:BE21 BG3:BG21 BI3:BI21 BK3:BK21 BM3:BM21 BO3:BO21 BQ3:BQ21 BS3:BS21 BU3:BU21 BW3:BW21 BY3:BY21 CA3:CA21 CC3:CC21 CE3:CE21 CG3:CG21 CI3:CI21 CK3:CK21 CM3:CM21 CO3:CO21 CQ3:CQ21 CS3:CS21 CU3:CU21 CW3:CW21 CY3:CY21 DA3:DA21 DC3:DC21 DE3:DE21 DG3:DG21 DI3:DI21 DK3:DK21 DM3:DM21 DO3:DO21 DQ3:DQ21 DS3:DS21 DU3:DU21 DW3:DW21 DY3:DY21 EA3:EA21 EC3:EC21 EE3:EE21 EG3:EG21 EI3:EI21 EK3:EK21 EM3:EM21 EO3:EO21 EQ3:EQ21 ES3:ES21 EU3:EU21 EW3:EW21 EY3:EY21 FA3:FA21 FC3:FC21 FE3:FE21 FG3:FG21 FI3:FI21 FK3:FK21 FM3:FM21 FO3:FO21 FQ3:FQ21 FS3:FS21 FU3:FU21 FW3:FW21 FY3:FY21 GA3:GA21 GC3:GC21 GE3:GE21 GG3:GG21 GI3:GI21 GK3:GK21 GM3:GM21 GO3:GO21 GQ3:GQ21 GS3:GS21 GU3:GU21 GW3:GW21 GY3:GY21 HA3:HA21 HC3:HC21 HE3:HE21 HG3:HG21 HI3:HI21 HK3:HK21 HM3:HM21 HO3:HO21 HQ3:HQ21 HS3:HS21 HU3:HU21 HW3:HW21 HY3:HY21 IA3:IA21 IC3:IC21 IE3:IE21 IG3:IG21 II3:II21 IK3:IK21 IM3:IM21 IO3:IO21 IQ3:IQ21 IS3:IS21 IU3:IU21 IW3:IW21 IY3:IY21 JA3:JA21 JC3:JC21 JE3:JE21 JG3:JG21 JI3:JI21 JK3:JK21 JM3:JM21 JO3:JO21 JQ3:JQ21 JS3:JS21 JU3:JU21 JW3:JW21 JY3:JY21 KA3:KA21 KC3:KC21 KE3:KE21 KG3:KG21 KI3:KI21 KK3:KK21 KM3:KM21 KO3:KO21 KQ3:KQ21 KS3:KS21 KU3:KU21 KW3:KW21 KY3:KY21 LA3:LA21 LC3:LC21 LE3:LE21 LG3:LG21 LI3:LI21">
-      <formula1>数据!$B$1:$B$55</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ10 AQ11 AQ12 AQ13 AQ14 AQ15 AQ16 AQ17 AQ18 C3:C21 E3:E21 G3:G21 I3:I21 K3:K21 M3:M21 O3:O21 Q3:Q21 S3:S21 U3:U21 W3:W21 Y3:Y21 AA3:AA21 AC3:AC21 AE3:AE21 AG3:AG21 AI3:AI21 AK3:AK21 AM3:AM21 AO3:AO21 AQ3:AQ9 AQ19:AQ21 AS3:AS21 AU3:AU21 AW3:AW21 AY3:AY21 BA3:BA21 BC3:BC21 BE3:BE21 BG3:BG21 BI3:BI21 BK3:BK21 BM3:BM21 BO3:BO21 BQ3:BQ21 BS3:BS21 BU3:BU21 BW3:BW21 BY3:BY21 CA3:CA21 CC3:CC21 CE3:CE21 CG3:CG21 CI3:CI21 CK3:CK21 CM3:CM21 CO3:CO21 CQ3:CQ21 CS3:CS21 CU3:CU21 CW3:CW21 CY3:CY21 DA3:DA21 DC3:DC21 DE3:DE21 DG3:DG21 DI3:DI21 DK3:DK21 DM3:DM21 DO3:DO21 DQ3:DQ21 DS3:DS21 DU3:DU21 DW3:DW21 DY3:DY21 EA3:EA21 EC3:EC21 EE3:EE21 EG3:EG21 EI3:EI21 EK3:EK21 EM3:EM21 EO3:EO21 EQ3:EQ21 ES3:ES21 EU3:EU21 EW3:EW21 EY3:EY21 FA3:FA21 FC3:FC21 FE3:FE21 FG3:FG21 FI3:FI21 FK3:FK21 FM3:FM21 FO3:FO21 FQ3:FQ21 FS3:FS21 FU3:FU21 FW3:FW21 FY3:FY21 GA3:GA21 GC3:GC21 GE3:GE21 GG3:GG21 GI3:GI21 GK3:GK21 GM3:GM21 GO3:GO21 GQ3:GQ21 GS3:GS21 GU3:GU21 GW3:GW21 GY3:GY21 HA3:HA21 HC3:HC21 HE3:HE21 HG3:HG21 HI3:HI21 HK3:HK21 HM3:HM21 HO3:HO21 HQ3:HQ21 HS3:HS21 HU3:HU21 HW3:HW21 HY3:HY21 IA3:IA21 IC3:IC21 IE3:IE21 IG3:IG21 II3:II21 IK3:IK21 IM3:IM21 IO3:IO21 IQ3:IQ21 IS3:IS21 IU3:IU21 IW3:IW21 IY3:IY21 JA3:JA21 JC3:JC21 JE3:JE21 JG3:JG21 JI3:JI21 JK3:JK21 JM3:JM21 JO3:JO21 JQ3:JQ21 JS3:JS21 JU3:JU21 JW3:JW21 JY3:JY21 KA3:KA21 KC3:KC21 KE3:KE21 KG3:KG21 KI3:KI21 KK3:KK21 KM3:KM21 KO3:KO21 KQ3:KQ21 KS3:KS21 KU3:KU21 KW3:KW21 KY3:KY21 LA3:LA21 LC3:LC21 LE3:LE21 LG3:LG21 LI3:LI21">
+      <formula1>数据!$B$1:$B$56</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C22 E22 G22 I22 K22 M22 O22 Q22 S22 U22 W22 Y22 AA22 AC22 AE22 AG22 AI22 AK22 AM22 AO22 AQ22 AS22 AU22 AW22 AY22 BA22 BC22 BE22 BG22 BI22 BK22 BM22 BO22 BQ22 BS22 BU22 BW22 BY22 CA22 CC22 CE22 CG22 CI22 CK22 CM22 CO22 CQ22 CS22 CU22 CW22 CY22 DA22 DC22 DE22 DG22 DI22 DK22 DM22 DO22 DQ22 DS22 DU22 DW22 DY22 EA22 EC22 EE22 EG22 EI22 EK22 EM22 EO22 EQ22 ES22 EU22 EW22 EY22 FA22 FC22 FE22 FG22 FI22 FK22 FM22 FO22 FQ22 FS22 FU22 FW22 FY22 GA22 GC22 GE22 GG22 GI22 GK22 GM22 GO22 GQ22 GS22 GU22 GW22 GY22 HA22 HC22 HE22 HG22 HI22 HK22 HM22 HO22 HQ22 HS22 HU22 HW22 HY22 IA22 IC22 IE22 IG22 II22 IK22 IM22 IO22 IQ22 IS22 IU22 IW22 IY22 JA22 JC22 JE22 JG22 JI22 JK22 JM22 JO22 JQ22 JS22 JU22 JW22 JY22 KA22 KC22 KE22 KG22 KI22 KK22 KM22 KO22 KQ22 KS22 KU22 KW22 KY22 LA22 LC22 LE22 LG22 LI22">
       <formula1>数据!$C$1:$C$25</formula1>
@@ -11878,24 +11915,24 @@
     <row r="1" ht="16.5" spans="1:9">
       <c r="A1" s="35"/>
       <c r="B1" s="36" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" s="36"/>
       <c r="D1" s="36" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="36"/>
       <c r="F1" s="36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H1" s="36" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I1" s="36" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:9">
@@ -11903,14 +11940,14 @@
         <v>4</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="38" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" s="39"/>
       <c r="E2" s="37" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2" s="35"/>
       <c r="G2" s="35"/>
@@ -11922,7 +11959,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="40" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="40"/>
       <c r="D3" s="40"/>
@@ -11937,7 +11974,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4" s="41"/>
       <c r="D4" s="41"/>
@@ -11949,7 +11986,7 @@
     </row>
     <row r="5" ht="16.5" spans="1:9">
       <c r="A5" s="36" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="42"/>
       <c r="C5" s="42"/>
@@ -11962,7 +11999,7 @@
     </row>
     <row r="6" ht="16.5" spans="1:9">
       <c r="A6" s="36" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="44"/>
       <c r="C6" s="44"/>
@@ -11975,10 +12012,10 @@
     </row>
     <row r="7" ht="16.5" spans="1:9">
       <c r="A7" s="36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="45" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C7" s="45"/>
       <c r="D7" s="45"/>
@@ -11990,7 +12027,7 @@
     </row>
     <row r="8" ht="16.5" spans="1:9">
       <c r="A8" s="36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="46"/>
       <c r="C8" s="46"/>
@@ -12003,10 +12040,10 @@
     </row>
     <row r="9" ht="16.5" spans="1:9">
       <c r="A9" s="36" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
@@ -12018,7 +12055,7 @@
     </row>
     <row r="10" ht="16.5" spans="1:9">
       <c r="A10" s="36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="40"/>
       <c r="C10" s="40"/>
@@ -12031,7 +12068,7 @@
     </row>
     <row r="11" ht="16.5" spans="1:9">
       <c r="A11" s="36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="41"/>
       <c r="C11" s="41"/>
@@ -12044,7 +12081,7 @@
     </row>
     <row r="12" ht="16.5" spans="1:9">
       <c r="A12" s="36" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" s="42"/>
       <c r="C12" s="42"/>
@@ -12057,10 +12094,10 @@
     </row>
     <row r="13" ht="16.5" spans="1:9">
       <c r="A13" s="36" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13" s="49"/>
       <c r="D13" s="49"/>
@@ -12069,10 +12106,10 @@
     </row>
     <row r="14" ht="16.5" spans="1:9">
       <c r="A14" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="50" t="s">
         <v>38</v>
-      </c>
-      <c r="B14" s="50" t="s">
-        <v>37</v>
       </c>
       <c r="C14" s="50"/>
       <c r="D14" s="50"/>
@@ -12141,323 +12178,323 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="31" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="34"/>
       <c r="B3" s="29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="34"/>
       <c r="B4" s="29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="34"/>
       <c r="B5" s="29" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="34"/>
       <c r="B6" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="34"/>
       <c r="B7" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="34"/>
       <c r="B8" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="34"/>
       <c r="B9" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="34"/>
       <c r="B10" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="34"/>
       <c r="B11" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11" s="30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="34"/>
       <c r="B12" s="29" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="34"/>
       <c r="B13" s="29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C13" s="30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="34"/>
       <c r="B14" s="29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="34"/>
       <c r="B15" s="29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C15" s="30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="34"/>
       <c r="B16" s="29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C16" s="30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="34"/>
       <c r="B17" s="29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="34"/>
       <c r="B18" s="29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C18" s="30" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="34"/>
       <c r="B19" s="29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C19" s="30" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="34"/>
       <c r="B20" s="29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="34"/>
       <c r="B21" s="29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C21" s="30" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="34"/>
       <c r="B22" s="29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C22" s="30" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="34"/>
       <c r="B23" s="29" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C23" s="30" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="34"/>
       <c r="B24" s="29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C24" s="30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="34"/>
       <c r="B25" s="29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C25" s="30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="34"/>
       <c r="B26" s="29" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C26" s="30" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="34"/>
       <c r="B27" s="29" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="34"/>
       <c r="B28" s="29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C28" s="30" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="34"/>
       <c r="B29" s="29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="34"/>
       <c r="B30" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C30" s="30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="34"/>
       <c r="B31" s="29" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="34"/>
       <c r="B32" s="29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B33" s="29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C33" s="30" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="31"/>
       <c r="B34" s="29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="31"/>
       <c r="B35" s="29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C35" s="30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36" spans="1:1">
@@ -12547,16 +12584,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -12564,13 +12601,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C2" s="25">
         <v>20111216</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -12578,13 +12615,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C3" s="26">
         <v>20111227</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -12592,13 +12629,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C4" s="26">
         <v>20120518</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -12606,7 +12643,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C5" s="26">
         <v>20120714</v>
@@ -12617,13 +12654,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C6" s="26">
         <v>20120504</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -12631,13 +12668,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C7" s="26">
         <v>20120809</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -12645,7 +12682,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C8" s="26">
         <v>20120227</v>
@@ -12656,13 +12693,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C9" s="26">
         <v>20120127</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -12670,13 +12707,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C10" s="26">
         <v>20111202</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -12684,7 +12721,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C11" s="26">
         <v>20120623</v>
@@ -12695,13 +12732,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C12" s="26">
         <v>20111024</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -12709,13 +12746,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C13" s="26">
         <v>20110908</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -12723,13 +12760,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C14" s="26">
         <v>20120228</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -12737,7 +12774,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C15" s="26">
         <v>20110904</v>
@@ -12748,7 +12785,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C16" s="25">
         <v>20111201</v>
@@ -12759,7 +12796,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C17" s="26">
         <v>20120722</v>
@@ -12770,7 +12807,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C18" s="26">
         <v>20111215</v>
@@ -12781,7 +12818,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C19" s="26">
         <v>20120509</v>
@@ -12792,7 +12829,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C20" s="26">
         <v>20120530</v>
@@ -12803,13 +12840,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C21" s="26">
         <v>20120827</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -12817,7 +12854,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C22" s="26">
         <v>20120816</v>
@@ -12828,7 +12865,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C23" s="26">
         <v>20120518</v>
@@ -12839,13 +12876,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C24" s="26">
         <v>20120413</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -12853,13 +12890,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C25" s="26">
         <v>20120629</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -12867,13 +12904,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C26" s="26">
         <v>20111105</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -12881,13 +12918,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C27" s="26">
         <v>20120112</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -12895,13 +12932,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C28" s="26">
         <v>20111119</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -12909,7 +12946,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C29" s="26">
         <v>20120110</v>
@@ -12920,13 +12957,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C30" s="26">
         <v>20120331</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -12934,13 +12971,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C31" s="26">
         <v>20111109</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -12948,13 +12985,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C32" s="26">
         <v>20120824</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -12962,7 +12999,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C33" s="26">
         <v>20120425</v>
@@ -12973,13 +13010,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C34" s="26">
         <v>20120624</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -12987,7 +13024,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C35" s="26">
         <v>20120507</v>
@@ -12998,13 +13035,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C36" s="26">
         <v>20120603</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -13012,13 +13049,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C37" s="25">
         <v>20120326</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -13026,13 +13063,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C38" s="26">
         <v>20111106</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -13040,13 +13077,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C39" s="26">
         <v>20120811</v>
       </c>
       <c r="D39" s="27" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -13054,13 +13091,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C40" s="26">
         <v>20111217</v>
       </c>
       <c r="D40" s="27" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -13068,13 +13105,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C41" s="26">
         <v>20111013</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -13082,7 +13119,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C42" s="26">
         <v>20111027</v>
@@ -13093,13 +13130,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C43" s="26">
         <v>20120207</v>
       </c>
       <c r="D43" s="18" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -13107,7 +13144,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C44" s="25">
         <v>20120508</v>
@@ -13118,13 +13155,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C45" s="26">
         <v>20110929</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -13132,7 +13169,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C46" s="26">
         <v>20111205</v>
@@ -13143,13 +13180,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C47" s="26">
         <v>20120108</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -13157,13 +13194,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C48" s="26">
         <v>20120311</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -13171,7 +13208,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="24" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C49" s="26">
         <v>20110902</v>
@@ -13182,13 +13219,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="24" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C50" s="26">
         <v>20120723</v>
       </c>
       <c r="D50" s="18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -13196,7 +13233,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="24" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C51" s="26">
         <v>20120101</v>
@@ -13207,13 +13244,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="24" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C52" s="26">
         <v>20111220</v>
       </c>
       <c r="D52" s="18" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -13243,70 +13280,70 @@
   <sheetData>
     <row r="1" ht="14" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" ht="217" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" ht="356.5" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" ht="108.5" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -13359,7 +13396,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4">
         <v>0.75</v>
@@ -13370,7 +13407,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -13381,7 +13418,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>1.25</v>
@@ -13392,7 +13429,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7">
         <v>1.5</v>
@@ -13403,7 +13440,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8">
         <v>1.75</v>
@@ -13414,7 +13451,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -13425,7 +13462,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10">
         <v>2.25</v>
@@ -13436,7 +13473,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11">
         <v>2.5</v>
@@ -13447,7 +13484,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12">
         <v>2.75</v>
@@ -13458,7 +13495,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -13469,7 +13506,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14">
         <v>3.25</v>
@@ -13480,7 +13517,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B15">
         <v>3.5</v>
@@ -13491,7 +13528,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B16">
         <v>3.75</v>
@@ -13502,7 +13539,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B17">
         <v>4</v>
@@ -13513,7 +13550,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B18">
         <v>4.25</v>
@@ -13524,7 +13561,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B19">
         <v>4.5</v>
@@ -13535,7 +13572,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B20">
         <v>4.75</v>
@@ -13546,7 +13583,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B21">
         <v>5</v>
@@ -13557,7 +13594,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B22">
         <v>5.25</v>
@@ -13568,7 +13605,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B23">
         <v>5.5</v>
@@ -13579,7 +13616,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B24">
         <v>5.75</v>
@@ -13590,7 +13627,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B25">
         <v>6</v>
@@ -13601,7 +13638,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B26">
         <v>6.25</v>
@@ -13609,7 +13646,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B27">
         <v>6.5</v>
@@ -13617,7 +13654,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B28">
         <v>6.75</v>
@@ -13625,7 +13662,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B29">
         <v>7</v>
@@ -13633,7 +13670,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B30">
         <v>7.25</v>
@@ -13641,7 +13678,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B31">
         <v>7.5</v>
@@ -13649,7 +13686,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B32">
         <v>7.75</v>
@@ -13657,7 +13694,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B33">
         <v>8</v>
@@ -13665,7 +13702,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B34">
         <v>9</v>
@@ -13673,7 +13710,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B35">
         <v>10</v>
@@ -13681,7 +13718,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B36">
         <v>11</v>
@@ -13689,7 +13726,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B37">
         <v>12</v>
@@ -13697,7 +13734,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B38">
         <v>13</v>
@@ -13705,7 +13742,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B39">
         <v>14</v>
@@ -13713,7 +13750,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B40">
         <v>15</v>
@@ -13721,7 +13758,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B41">
         <v>16</v>
@@ -13729,7 +13766,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B42">
         <v>17</v>
@@ -13737,7 +13774,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B43">
         <v>18</v>
@@ -13745,7 +13782,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B44">
         <v>19</v>
@@ -13753,7 +13790,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B45">
         <v>20</v>
@@ -13761,7 +13798,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B46">
         <v>21</v>
@@ -13769,7 +13806,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B47">
         <v>22</v>
@@ -13777,7 +13814,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B48">
         <v>23</v>
@@ -13785,7 +13822,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B49">
         <v>24</v>
@@ -13793,7 +13830,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B50">
         <v>25</v>
@@ -13801,7 +13838,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B51">
         <v>26</v>
@@ -13809,7 +13846,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B52">
         <v>27</v>
@@ -13817,7 +13854,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B53">
         <v>28</v>
@@ -13825,7 +13862,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B54">
         <v>29</v>
@@ -13833,175 +13870,178 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B55">
         <v>30</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
+      </c>
+      <c r="B56" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="89" spans="1:1">

--- a/c/9班资料.xlsx
+++ b/c/9班资料.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480"/>
+    <workbookView windowWidth="20750" windowHeight="10480" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="七下拖课" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="316">
   <si>
     <t>拖课统计表</t>
   </si>
@@ -601,7 +601,7 @@
     <t>洪鑫洋</t>
   </si>
   <si>
-    <t>巨乳</t>
+    <t>巨乳、信仰</t>
   </si>
   <si>
     <t>游武毅</t>
@@ -1237,6 +1237,70 @@
       </rPr>
       <t>陈子岩又称“女明星”，时时刻刻都会做出一些“明星”的行为。
 他还有一位“经纪人”，也就是李梦妍。当时李梦妍还特地把陈子岩的一些事件做成热搜榜，让人写评论。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">海参
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>有人说，陈睿卓每天吃得都很补，整天中午吃海参。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>口水</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+蔡华楷讲话时经常会喷口水。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">早读
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>一段时间内，洪鑫洋很喜欢读《孙权劝学》和《木兰诗》，于是大家读的时候就开始把人物替换成“鑫洋”，如：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>仰辞以军中多务
+问仰何所思，问仰何所忆。仰亦无所思，仰亦无所忆。
+小弟闻姊来，磨刀霍霍向鑫洋。
+同行十二年，不知鑫洋是女郎。
+双兔傍地走，安能辨我是鑫洋。</t>
     </r>
   </si>
   <si>
@@ -1931,18 +1995,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF000033"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000033"/>
       <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1956,6 +2015,11 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="56">
@@ -4758,10 +4822,18 @@
       <c r="BI3" s="97"/>
       <c r="BJ3" s="96"/>
       <c r="BK3" s="97"/>
-      <c r="BL3" s="96"/>
-      <c r="BM3" s="97"/>
-      <c r="BN3" s="96"/>
-      <c r="BO3" s="97"/>
+      <c r="BL3" s="96" t="s">
+        <v>4</v>
+      </c>
+      <c r="BM3" s="97" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN3" s="96" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO3" s="97" t="s">
+        <v>3</v>
+      </c>
       <c r="BP3" s="96"/>
       <c r="BQ3" s="97"/>
       <c r="BR3" s="96"/>
@@ -5398,10 +5470,18 @@
       <c r="BI5" s="103"/>
       <c r="BJ5" s="102"/>
       <c r="BK5" s="103"/>
-      <c r="BL5" s="102"/>
-      <c r="BM5" s="103"/>
-      <c r="BN5" s="102"/>
-      <c r="BO5" s="103"/>
+      <c r="BL5" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="BM5" s="103" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN5" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="BO5" s="103">
+        <v>6</v>
+      </c>
       <c r="BP5" s="102"/>
       <c r="BQ5" s="103"/>
       <c r="BR5" s="102"/>
@@ -6321,10 +6401,18 @@
       <c r="BI8" s="103"/>
       <c r="BJ8" s="107"/>
       <c r="BK8" s="103"/>
-      <c r="BL8" s="107"/>
-      <c r="BM8" s="103"/>
-      <c r="BN8" s="107"/>
-      <c r="BO8" s="103"/>
+      <c r="BL8" s="107" t="s">
+        <v>9</v>
+      </c>
+      <c r="BM8" s="103" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN8" s="107" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO8" s="103" t="s">
+        <v>3</v>
+      </c>
       <c r="BP8" s="107"/>
       <c r="BQ8" s="103"/>
       <c r="BR8" s="107"/>
@@ -6965,10 +7053,18 @@
       <c r="BI10" s="103"/>
       <c r="BJ10" s="102"/>
       <c r="BK10" s="103"/>
-      <c r="BL10" s="102"/>
-      <c r="BM10" s="103"/>
-      <c r="BN10" s="102"/>
-      <c r="BO10" s="103"/>
+      <c r="BL10" s="102" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM10" s="103" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN10" s="102" t="s">
+        <v>9</v>
+      </c>
+      <c r="BO10" s="103" t="s">
+        <v>3</v>
+      </c>
       <c r="BP10" s="102"/>
       <c r="BQ10" s="103"/>
       <c r="BR10" s="102"/>
@@ -7601,10 +7697,18 @@
       <c r="BI12" s="103"/>
       <c r="BJ12" s="102"/>
       <c r="BK12" s="103"/>
-      <c r="BL12" s="102"/>
-      <c r="BM12" s="103"/>
-      <c r="BN12" s="102"/>
-      <c r="BO12" s="103"/>
+      <c r="BL12" s="102" t="s">
+        <v>16</v>
+      </c>
+      <c r="BM12" s="103" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN12" s="102" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO12" s="103" t="s">
+        <v>3</v>
+      </c>
       <c r="BP12" s="102"/>
       <c r="BQ12" s="103"/>
       <c r="BR12" s="102"/>
@@ -8237,10 +8341,18 @@
       <c r="BI14" s="103"/>
       <c r="BJ14" s="102"/>
       <c r="BK14" s="103"/>
-      <c r="BL14" s="102"/>
-      <c r="BM14" s="103"/>
-      <c r="BN14" s="102"/>
-      <c r="BO14" s="103"/>
+      <c r="BL14" s="102" t="s">
+        <v>14</v>
+      </c>
+      <c r="BM14" s="103" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN14" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="BO14" s="103" t="s">
+        <v>3</v>
+      </c>
       <c r="BP14" s="102"/>
       <c r="BQ14" s="103"/>
       <c r="BR14" s="102"/>
@@ -8873,10 +8985,18 @@
       <c r="BI16" s="103"/>
       <c r="BJ16" s="102"/>
       <c r="BK16" s="103"/>
-      <c r="BL16" s="102"/>
-      <c r="BM16" s="103"/>
-      <c r="BN16" s="102"/>
-      <c r="BO16" s="103"/>
+      <c r="BL16" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="BM16" s="103" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN16" s="102" t="s">
+        <v>6</v>
+      </c>
+      <c r="BO16" s="103" t="s">
+        <v>3</v>
+      </c>
       <c r="BP16" s="102"/>
       <c r="BQ16" s="103"/>
       <c r="BR16" s="102"/>
@@ -9509,10 +9629,18 @@
       <c r="BI18" s="103"/>
       <c r="BJ18" s="102"/>
       <c r="BK18" s="103"/>
-      <c r="BL18" s="102"/>
-      <c r="BM18" s="103"/>
-      <c r="BN18" s="102"/>
-      <c r="BO18" s="103"/>
+      <c r="BL18" s="102" t="s">
+        <v>16</v>
+      </c>
+      <c r="BM18" s="103" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN18" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="BO18" s="103" t="s">
+        <v>3</v>
+      </c>
       <c r="BP18" s="102"/>
       <c r="BQ18" s="103"/>
       <c r="BR18" s="102"/>
@@ -10137,10 +10265,18 @@
       <c r="BI20" s="103"/>
       <c r="BJ20" s="102"/>
       <c r="BK20" s="103"/>
-      <c r="BL20" s="102"/>
-      <c r="BM20" s="103"/>
-      <c r="BN20" s="102"/>
-      <c r="BO20" s="103"/>
+      <c r="BL20" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="BM20" s="103" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN20" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="BO20" s="103">
+        <v>3</v>
+      </c>
       <c r="BP20" s="102"/>
       <c r="BQ20" s="103"/>
       <c r="BR20" s="102"/>
@@ -10744,15 +10880,21 @@
       <c r="AZ22" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="BA22" s="113"/>
+      <c r="BA22" s="113">
+        <v>7</v>
+      </c>
       <c r="BB22" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="BC22" s="113"/>
+      <c r="BC22" s="113">
+        <v>7</v>
+      </c>
       <c r="BD22" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="BE22" s="113"/>
+      <c r="BE22" s="113">
+        <v>7</v>
+      </c>
       <c r="BF22" s="112" t="s">
         <v>23</v>
       </c>
@@ -11265,7 +11407,9 @@
       <c r="BI23" s="115"/>
       <c r="BJ23" s="114"/>
       <c r="BK23" s="115"/>
-      <c r="BL23" s="114"/>
+      <c r="BL23" s="114" t="s">
+        <v>25</v>
+      </c>
       <c r="BM23" s="115"/>
       <c r="BN23" s="114"/>
       <c r="BO23" s="115"/>
@@ -11783,14 +11927,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BG5 BG8 BG14 BG18 C3:C21 E3:E21 G3:G21 I3:I21 K3:K21 M3:M21 O3:O21 Q3:Q21 S3:S21 U3:U21 W3:W21 Y3:Y21 AA3:AA21 AC3:AC21 AE3:AE21 AG3:AG21 AI3:AI21 AK3:AK21 AM3:AM21 AO3:AO21 AQ3:AQ21 AS3:AS21 AU3:AU21 AW3:AW21 AY3:AY21 BA3:BA21 BC3:BC21 BE3:BE21 BG3:BG4 BG6:BG7 BG9:BG13 BG15:BG17 BG19:BG21 BI3:BI21 BK3:BK21 BM3:BM21 BO3:BO21 BQ3:BQ21 BS3:BS21 BU3:BU21 BW3:BW21 BY3:BY21 CA3:CA21 CC3:CC21 CE3:CE21 CG3:CG21 CI3:CI21 CK3:CK21 CM3:CM21 CO3:CO21 CQ3:CQ21 CS3:CS21 CU3:CU21 CW3:CW21 CY3:CY21 DA3:DA21 DC3:DC21 DE3:DE21 DG3:DG21 DI3:DI21 DK3:DK21 DM3:DM21 DO3:DO21 DQ3:DQ21 DS3:DS21 DU3:DU21 DW3:DW21 DY3:DY21 EA3:EA21 EC3:EC21 EE3:EE21 EG3:EG21 EI3:EI21 EK3:EK21 EM3:EM21 EO3:EO21 EQ3:EQ21 ES3:ES21 EU3:EU21 EW3:EW21 EY3:EY21 FA3:FA21 FC3:FC21 FE3:FE21 FG3:FG21 FI3:FI21 FK3:FK21 FM3:FM21 FO3:FO21 FQ3:FQ21 FS3:FS21 FU3:FU21 FW3:FW21 FY3:FY21 GA3:GA21 GC3:GC21 GE3:GE21 GG3:GG21 GI3:GI21 GK3:GK21 GM3:GM21 GO3:GO21 GQ3:GQ21 GS3:GS21 GU3:GU21 GW3:GW21 GY3:GY21 HA3:HA21 HC3:HC21 HE3:HE21 HG3:HG21 HI3:HI21 HK3:HK21 HM3:HM21 HO3:HO21 HQ3:HQ21 HS3:HS21 HU3:HU21 HW3:HW21 HY3:HY21 IA3:IA21 IC3:IC21 IE3:IE21 IG3:IG21 II3:II21 IK3:IK21 IM3:IM21 IO3:IO21 IQ3:IQ21 IS3:IS21 IU3:IU21 IW3:IW21 IY3:IY21 JA3:JA21 JC3:JC21 JE3:JE21 JG3:JG21 JI3:JI21 JK3:JK21 JM3:JM21 JO3:JO21">
-      <formula1>数据!$B$1:$B$62</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C22 E22 G22 I22 K22 M22 O22 Q22 S22 U22 W22 Y22 AA22 AC22 AE22 AG22 AI22 AK22 AM22 AO22 AQ22 AS22 AU22 AW22 AY22 BA22 BC22 BE22 BG22 BI22 BK22 BM22 BO22 BQ22 BS22 BU22 BW22 BY22 CA22 CC22 CE22 CG22 CI22 CK22 CM22 CO22 CQ22 CS22 CU22 CW22 CY22 DA22 DC22 DE22 DG22 DI22 DK22 DM22 DO22 DQ22 DS22 DU22 DW22 DY22 EA22 EC22 EE22 EG22 EI22 EK22 EM22 EO22 EQ22 ES22 EU22 EW22 EY22 FA22 FC22 FE22 FG22 FI22 FK22 FM22 FO22 FQ22 FS22 FU22 FW22 FY22 GA22 GC22 GE22 GG22 GI22 GK22 GM22 GO22 GQ22 GS22 GU22 GW22 GY22 HA22 HC22 HE22 HG22 HI22 HK22 HM22 HO22 HQ22 HS22 HU22 HW22 HY22 IA22 IC22 IE22 IG22 II22 IK22 IM22 IO22 IQ22 IS22 IU22 IW22 IY22 JA22 JC22 JE22 JG22 JI22 JK22 JM22 JO22">
       <formula1>数据!$C$1:$C$25</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B21 D3:D21 F3:F21 H3:H21 J3:J21 L3:L21 N3:N21 P3:P21 R3:R21 T3:T21 V3:V21 X3:X21 Z3:Z21 AB3:AB21 AD3:AD21 AF3:AF21 AH3:AH21 AJ3:AJ21 AL3:AL21 AN3:AN21 AP3:AP21 AR3:AR21 AT3:AT21 AV3:AV21 AX3:AX21 AZ3:AZ21 BB3:BB21 BD3:BD21 BF3:BF21 BH3:BH21 BJ3:BJ21 BL3:BL21 BN3:BN21 BP3:BP21 BR3:BR21 BT3:BT21 BV3:BV21 BX3:BX21 BZ3:BZ21 CB3:CB21 CD3:CD21 CF3:CF21 CH3:CH21 CJ3:CJ21 CL3:CL21 CN3:CN21 CP3:CP21 CR3:CR21 CT3:CT21 CV3:CV21 CX3:CX21 CZ3:CZ21 DB3:DB21 DD3:DD21 DF3:DF21 DH3:DH21 DJ3:DJ21 DL3:DL21 DN3:DN21 DP3:DP21 DR3:DR21 DT3:DT21 DV3:DV21 DX3:DX21 DZ3:DZ21 EB3:EB21 ED3:ED21 EF3:EF21 EH3:EH21 EJ3:EJ21 EL3:EL21 EN3:EN21 EP3:EP21 ER3:ER21 ET3:ET21 EV3:EV21 EX3:EX21 EZ3:EZ21 FB3:FB21 FD3:FD21 FF3:FF21 FH3:FH21 FJ3:FJ21 FL3:FL21 FN3:FN21 FP3:FP21 FR3:FR21 FT3:FT21 FV3:FV21 FX3:FX21 FZ3:FZ21 GB3:GB21 GD3:GD21 GF3:GF21 GH3:GH21 GJ3:GJ21 GL3:GL21 GN3:GN21 GP3:GP21 GR3:GR21 GT3:GT21 GV3:GV21 GX3:GX21 GZ3:GZ21 HB3:HB21 HD3:HD21 HF3:HF21 HH3:HH21 HJ3:HJ21 HL3:HL21 HN3:HN21 HP3:HP21 HR3:HR21 HT3:HT21 HV3:HV21 HX3:HX21 HZ3:HZ21 IB3:IB21 ID3:ID21 IF3:IF21 IH3:IH21 IJ3:IJ21 IL3:IL21 IN3:IN21 IP3:IP21 IR3:IR21 IT3:IT21 IV3:IV21 IX3:IX21 IZ3:IZ21 JB3:JB21 JD3:JD21 JF3:JF21 JH3:JH21 JJ3:JJ21 JL3:JL21 JN3:JN21">
       <formula1>数据!$A$1:$A$88</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C21 E3:E21 G3:G21 I3:I21 K3:K21 M3:M21 O3:O21 Q3:Q21 S3:S21 U3:U21 W3:W21 Y3:Y21 AA3:AA21 AC3:AC21 AE3:AE21 AG3:AG21 AI3:AI21 AK3:AK21 AM3:AM21 AO3:AO21 AQ3:AQ21 AS3:AS21 AU3:AU21 AW3:AW21 AY3:AY21 BA3:BA21 BC3:BC21 BE3:BE21 BG3:BG21 BI3:BI21 BK3:BK21 BM3:BM21 BO3:BO21 BQ3:BQ21 BS3:BS21 BU3:BU21 BW3:BW21 BY3:BY21 CA3:CA21 CC3:CC21 CE3:CE21 CG3:CG21 CI3:CI21 CK3:CK21 CM3:CM21 CO3:CO21 CQ3:CQ21 CS3:CS21 CU3:CU21 CW3:CW21 CY3:CY21 DA3:DA21 DC3:DC21 DE3:DE21 DG3:DG21 DI3:DI21 DK3:DK21 DM3:DM21 DO3:DO21 DQ3:DQ21 DS3:DS21 DU3:DU21 DW3:DW21 DY3:DY21 EA3:EA21 EC3:EC21 EE3:EE21 EG3:EG21 EI3:EI21 EK3:EK21 EM3:EM21 EO3:EO21 EQ3:EQ21 ES3:ES21 EU3:EU21 EW3:EW21 EY3:EY21 FA3:FA21 FC3:FC21 FE3:FE21 FG3:FG21 FI3:FI21 FK3:FK21 FM3:FM21 FO3:FO21 FQ3:FQ21 FS3:FS21 FU3:FU21 FW3:FW21 FY3:FY21 GA3:GA21 GC3:GC21 GE3:GE21 GG3:GG21 GI3:GI21 GK3:GK21 GM3:GM21 GO3:GO21 GQ3:GQ21 GS3:GS21 GU3:GU21 GW3:GW21 GY3:GY21 HA3:HA21 HC3:HC21 HE3:HE21 HG3:HG21 HI3:HI21 HK3:HK21 HM3:HM21 HO3:HO21 HQ3:HQ21 HS3:HS21 HU3:HU21 HW3:HW21 HY3:HY21 IA3:IA21 IC3:IC21 IE3:IE21 IG3:IG21 II3:II21 IK3:IK21 IM3:IM21 IO3:IO21 IQ3:IQ21 IS3:IS21 IU3:IU21 IW3:IW21 IY3:IY21 JA3:JA21 JC3:JC21 JE3:JE21 JG3:JG21 JI3:JI21 JK3:JK21 JM3:JM21 JO3:JO21">
+      <formula1>数据!$B$1:$B$62</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11963,7 +12107,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B15">
         <v>3.5</v>
@@ -11974,7 +12118,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B16">
         <v>3.75</v>
@@ -11985,7 +12129,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B17">
         <v>4</v>
@@ -11996,7 +12140,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B18">
         <v>4.25</v>
@@ -12007,7 +12151,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B19">
         <v>4.5</v>
@@ -12018,7 +12162,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B20">
         <v>4.75</v>
@@ -12029,7 +12173,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B21">
         <v>5</v>
@@ -12040,7 +12184,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B22">
         <v>5.25</v>
@@ -12051,7 +12195,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B23">
         <v>5.5</v>
@@ -12062,7 +12206,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B24">
         <v>5.75</v>
@@ -12073,7 +12217,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B25">
         <v>6</v>
@@ -12100,7 +12244,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B28">
         <v>6.75</v>
@@ -12108,7 +12252,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B29">
         <v>7</v>
@@ -12116,7 +12260,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B30">
         <v>7.25</v>
@@ -12124,7 +12268,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B31">
         <v>7.5</v>
@@ -12132,7 +12276,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B32">
         <v>7.75</v>
@@ -12140,7 +12284,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B33">
         <v>8</v>
@@ -12148,7 +12292,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B34">
         <v>8.25</v>
@@ -12156,7 +12300,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B35">
         <v>8.5</v>
@@ -12164,7 +12308,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B36">
         <v>8.75</v>
@@ -12172,7 +12316,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B37">
         <v>9</v>
@@ -12180,7 +12324,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B38">
         <v>9.25</v>
@@ -12188,7 +12332,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B39">
         <v>9.5</v>
@@ -12196,7 +12340,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B40">
         <v>9.75</v>
@@ -12204,7 +12348,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B41">
         <v>10</v>
@@ -12212,7 +12356,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B42">
         <v>11</v>
@@ -12220,7 +12364,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B43">
         <v>12</v>
@@ -12228,7 +12372,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B44">
         <v>13</v>
@@ -12236,7 +12380,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B45">
         <v>14</v>
@@ -12244,7 +12388,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B46">
         <v>15</v>
@@ -12252,7 +12396,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B47">
         <v>16</v>
@@ -12260,7 +12404,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B48">
         <v>17</v>
@@ -12268,7 +12412,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B49">
         <v>18</v>
@@ -12276,7 +12420,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B50">
         <v>19</v>
@@ -12284,7 +12428,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B51">
         <v>20</v>
@@ -12292,7 +12436,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B52">
         <v>21</v>
@@ -12300,7 +12444,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B53">
         <v>22</v>
@@ -12308,7 +12452,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B54">
         <v>23</v>
@@ -12316,7 +12460,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B55">
         <v>24</v>
@@ -12324,7 +12468,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B56">
         <v>25</v>
@@ -12332,7 +12476,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B57">
         <v>26</v>
@@ -12340,7 +12484,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B58">
         <v>27</v>
@@ -12348,7 +12492,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B59">
         <v>28</v>
@@ -12356,7 +12500,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B60">
         <v>29</v>
@@ -12364,7 +12508,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B61">
         <v>30</v>
@@ -12372,7 +12516,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B62" t="s">
         <v>5</v>
@@ -12380,117 +12524,117 @@
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="86" spans="1:1">
@@ -12500,7 +12644,7 @@
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -14245,9 +14389,12 @@
         <v>221</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" ht="28" spans="1:3">
       <c r="A37" s="30" t="s">
         <v>170</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -14260,14 +14407,20 @@
         <v>174</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" ht="28" spans="1:2">
       <c r="A40" s="30" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="41" spans="1:1">
+      <c r="B40" s="23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="41" ht="112" spans="1:3">
       <c r="A41" s="30" t="s">
         <v>178</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -14290,7 +14443,7 @@
         <v>184</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="46" spans="1:1">
@@ -14328,7 +14481,7 @@
         <v>195</v>
       </c>
       <c r="B52" s="23" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -14356,7 +14509,7 @@
   <sheetData>
     <row r="1" s="2" customFormat="1" spans="1:8">
       <c r="A1" s="6" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="2" t="s">
@@ -14380,10 +14533,10 @@
     </row>
     <row r="2" s="3" customFormat="1" spans="1:4">
       <c r="A2" s="8" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>115</v>
@@ -14393,7 +14546,7 @@
     <row r="3" s="3" customFormat="1" spans="1:4">
       <c r="A3" s="12"/>
       <c r="B3" s="9" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>131</v>
@@ -14411,7 +14564,7 @@
     <row r="5" s="3" customFormat="1" spans="1:4">
       <c r="A5" s="12"/>
       <c r="B5" s="9" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>135</v>
@@ -14421,7 +14574,7 @@
     <row r="6" s="3" customFormat="1" spans="1:4">
       <c r="A6" s="12"/>
       <c r="B6" s="9" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>123</v>
@@ -14443,7 +14596,7 @@
     <row r="8" s="3" customFormat="1" spans="1:4">
       <c r="A8" s="12"/>
       <c r="B8" s="9" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>121</v>
@@ -14455,7 +14608,7 @@
     <row r="9" s="3" customFormat="1" spans="1:4">
       <c r="A9" s="12"/>
       <c r="B9" s="9" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>126</v>
@@ -14465,7 +14618,7 @@
     <row r="10" s="3" customFormat="1" spans="1:4">
       <c r="A10" s="12"/>
       <c r="B10" s="9" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>138</v>
@@ -14475,7 +14628,7 @@
     <row r="11" s="3" customFormat="1" spans="1:4">
       <c r="A11" s="14"/>
       <c r="B11" s="9" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>160</v>
@@ -14484,10 +14637,10 @@
     </row>
     <row r="12" s="4" customFormat="1" spans="1:4">
       <c r="A12" s="15" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>178</v>
@@ -14505,17 +14658,17 @@
     <row r="14" s="4" customFormat="1" spans="1:4">
       <c r="A14" s="19"/>
       <c r="B14" s="16" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D14" s="18"/>
     </row>
     <row r="15" s="4" customFormat="1" spans="1:4">
       <c r="A15" s="19"/>
       <c r="B15" s="16" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>117</v>
@@ -14533,7 +14686,7 @@
     <row r="17" s="4" customFormat="1" spans="1:4">
       <c r="A17" s="19"/>
       <c r="B17" s="16" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>130</v>
@@ -14543,7 +14696,7 @@
     <row r="18" s="4" customFormat="1" spans="1:4">
       <c r="A18" s="19"/>
       <c r="B18" s="16" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>142</v>
@@ -14553,7 +14706,7 @@
     <row r="19" s="4" customFormat="1" spans="1:4">
       <c r="A19" s="19"/>
       <c r="B19" s="16" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>174</v>
@@ -14563,7 +14716,7 @@
     <row r="20" s="4" customFormat="1" spans="1:4">
       <c r="A20" s="20"/>
       <c r="B20" s="16" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>176</v>

--- a/c/9班资料.xlsx
+++ b/c/9班资料.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480"/>
+    <workbookView windowWidth="20750" windowHeight="10480" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="七下拖课" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="469">
   <si>
     <t>拖课统计表</t>
   </si>
@@ -811,6 +811,27 @@
 同时，活页本还要记积累的单词，于是又叫“积累本”。</t>
   </si>
   <si>
+    <t>单词</t>
+  </si>
+  <si>
+    <t>在正式上某节课前，刘必艳会把这节课的单词讲掉，主要方法是：
+1.跟读（像这样：
+师：monkey,monkey
+生：monkey,monkey
+师：monkey,monkey
+生：monkey,monkey
+师：mon
+生：m，o，n
+师：key
+生：k，e，y
+师：monkey
+生：m，o，n，k，e，y
+师：monkey,monkey
+生：monkey,monkey，noun，猴子）
+2.其他（词性转化、复数、三单、过去式、现在进行时、反义词、词组、巨型、补充中文）
+讲单词时，刘必艳随机叫人并将书投影。</t>
+  </si>
+  <si>
     <t>作业</t>
   </si>
   <si>
@@ -2961,13 +2982,201 @@
   </si>
   <si>
     <r>
+      <t>25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>郑锦熠</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF76923C"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 黄丰泽</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9B891D"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>陈  婕</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9B891D"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 倪浩宇</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF31849B"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>37</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>杨依诺</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF31849B"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>郑永泽</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9B891D"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>俞昕辰</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9B891D"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>徐嘉明</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>31</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>季仁槿</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF31849B"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>李欢颜</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FFE36C09"/>
         <rFont val="黑体"/>
         <charset val="134"/>
       </rPr>
-      <t>25</t>
+      <t>15</t>
     </r>
     <r>
       <rPr>
@@ -2976,7 +3185,27 @@
         <rFont val="黑体"/>
         <charset val="134"/>
       </rPr>
-      <t>郑锦熠</t>
+      <t>江允儿</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFE36C09"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>46</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>唐家祺</t>
     </r>
   </si>
   <si>
@@ -2987,7 +3216,7 @@
         <rFont val="黑体"/>
         <charset val="134"/>
       </rPr>
-      <t>4</t>
+      <t>32</t>
     </r>
     <r>
       <rPr>
@@ -2996,7 +3225,7 @@
         <rFont val="黑体"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> 黄丰泽</t>
+      <t>张梦琪</t>
     </r>
   </si>
   <si>
@@ -3007,7 +3236,7 @@
         <rFont val="黑体"/>
         <charset val="134"/>
       </rPr>
-      <t>14</t>
+      <t>34</t>
     </r>
     <r>
       <rPr>
@@ -3016,7 +3245,7 @@
         <rFont val="黑体"/>
         <charset val="134"/>
       </rPr>
-      <t>陈  婕</t>
+      <t>颜哲铭</t>
     </r>
   </si>
   <si>
@@ -3027,7 +3256,7 @@
         <rFont val="黑体"/>
         <charset val="134"/>
       </rPr>
-      <t>8</t>
+      <t>11</t>
     </r>
     <r>
       <rPr>
@@ -3036,18 +3265,18 @@
         <rFont val="黑体"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> 倪浩宇</t>
+      <t>郑诗语</t>
     </r>
   </si>
   <si>
     <r>
       <rPr>
         <sz val="12"/>
-        <color rgb="FF31849B"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>37</t>
+        <color rgb="FFE36C09"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>27</t>
     </r>
     <r>
       <rPr>
@@ -3056,18 +3285,18 @@
         <rFont val="黑体"/>
         <charset val="134"/>
       </rPr>
-      <t>杨依诺</t>
+      <t>黄恩亚</t>
     </r>
   </si>
   <si>
     <r>
       <rPr>
         <sz val="12"/>
-        <color rgb="FF31849B"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>12</t>
+        <color rgb="FF9B891D"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>39</t>
     </r>
     <r>
       <rPr>
@@ -3076,7 +3305,127 @@
         <rFont val="黑体"/>
         <charset val="134"/>
       </rPr>
-      <t>郑永泽</t>
+      <t>蔡华楷</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFE36C09"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>42</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>崔宇臣</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFE36C09"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>41</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>游武毅</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF76923C"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 郭沁诗</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF948A54"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>郑  炜</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFE36C09"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>47</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>刘天馨</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF76923C"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>郑熠菲</t>
     </r>
   </si>
   <si>
@@ -3087,7 +3436,7 @@
         <rFont val="黑体"/>
         <charset val="134"/>
       </rPr>
-      <t>17</t>
+      <t>51</t>
     </r>
     <r>
       <rPr>
@@ -3096,18 +3445,28 @@
         <rFont val="黑体"/>
         <charset val="134"/>
       </rPr>
-      <t>俞昕辰</t>
-    </r>
-  </si>
-  <si>
+      <t>蒲林豪</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>23</t>
+    </r>
     <r>
       <rPr>
         <sz val="12"/>
-        <color rgb="FF9B891D"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>16</t>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>李映辰</t>
+    </r>
+  </si>
+  <si>
+    <t>第三轮</t>
+  </si>
+  <si>
+    <r>
+      <t>19</t>
     </r>
     <r>
       <rPr>
@@ -3116,18 +3475,12 @@
         <rFont val="黑体"/>
         <charset val="134"/>
       </rPr>
-      <t>徐嘉明</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF31849B"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>18</t>
+      <t>廖成羲</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>50</t>
     </r>
     <r>
       <rPr>
@@ -3136,7 +3489,7 @@
         <rFont val="黑体"/>
         <charset val="134"/>
       </rPr>
-      <t>李欢颜</t>
+      <t>曹世强</t>
     </r>
   </si>
   <si>
@@ -3147,7 +3500,7 @@
         <rFont val="黑体"/>
         <charset val="134"/>
       </rPr>
-      <t>15</t>
+      <t>25</t>
     </r>
     <r>
       <rPr>
@@ -3156,290 +3509,21 @@
         <rFont val="黑体"/>
         <charset val="134"/>
       </rPr>
-      <t>江允儿</t>
-    </r>
-  </si>
-  <si>
+      <t>郑锦熠</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>51</t>
+    </r>
     <r>
       <rPr>
         <sz val="12"/>
-        <color rgb="FFE36C09"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>46</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>唐家祺</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF76923C"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>32</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>张梦琪</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9B891D"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>34</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>颜哲铭</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9B891D"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>郑诗语</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFE36C09"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>27</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>黄恩亚</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9B891D"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>39</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>蔡华楷</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFE36C09"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>42</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>崔宇臣</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFE36C09"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>41</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>游武毅</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF76923C"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 郭沁诗</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF948A54"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>26</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>郑  炜</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFE36C09"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>47</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>刘天馨</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF76923C"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>29</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>郑熠菲</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9B891D"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>51</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
         <rFont val="黑体"/>
         <charset val="134"/>
       </rPr>
       <t>蒲林豪</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="9"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>51</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>蒲林豪</t>
-    </r>
-  </si>
-  <si>
-    <t>第三轮</t>
   </si>
   <si>
     <t>音乐（语占）</t>
@@ -3659,7 +3743,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="55">
+  <fonts count="56">
     <font>
       <sz val="11"/>
       <name val="宋体"/>
@@ -3980,9 +4064,9 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="5"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -3997,14 +4081,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000033"/>
       <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFC0504D"/>
-      <name val="黑体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -4012,6 +4096,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFC0504D"/>
+      <name val="黑体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="61">
@@ -4673,7 +4763,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4819,6 +4909,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4904,6 +4997,10 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5069,15 +5166,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5343,7 +5437,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
     <cellStyle name="货币" xfId="2" builtinId="4"/>
@@ -5393,6 +5487,7 @@
     <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="样式 1" xfId="49"/>
   </cellStyles>
   <dxfs count="5">
     <dxf>
@@ -5405,14 +5500,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFF2F2F2"/>
+          <bgColor rgb="FFE3F2D9"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFE3F2D9"/>
+          <bgColor rgb="FFF2F2F2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7045,10 +7140,18 @@
       <c r="BW3" s="152"/>
       <c r="BX3" s="151"/>
       <c r="BY3" s="152"/>
-      <c r="BZ3" s="151"/>
-      <c r="CA3" s="152"/>
-      <c r="CB3" s="151"/>
-      <c r="CC3" s="152"/>
+      <c r="BZ3" s="151" t="s">
+        <v>4</v>
+      </c>
+      <c r="CA3" s="152" t="s">
+        <v>3</v>
+      </c>
+      <c r="CB3" s="151" t="s">
+        <v>2</v>
+      </c>
+      <c r="CC3" s="152">
+        <v>1.25</v>
+      </c>
       <c r="CD3" s="151"/>
       <c r="CE3" s="152"/>
       <c r="CF3" s="151"/>
@@ -7705,10 +7808,18 @@
       <c r="BW5" s="158"/>
       <c r="BX5" s="157"/>
       <c r="BY5" s="158"/>
-      <c r="BZ5" s="157"/>
-      <c r="CA5" s="158"/>
-      <c r="CB5" s="157"/>
-      <c r="CC5" s="158"/>
+      <c r="BZ5" s="157" t="s">
+        <v>2</v>
+      </c>
+      <c r="CA5" s="158">
+        <v>7.25</v>
+      </c>
+      <c r="CB5" s="157" t="s">
+        <v>4</v>
+      </c>
+      <c r="CC5" s="158" t="s">
+        <v>3</v>
+      </c>
       <c r="CD5" s="157"/>
       <c r="CE5" s="158"/>
       <c r="CF5" s="157"/>
@@ -8648,10 +8759,18 @@
       <c r="BW8" s="158"/>
       <c r="BX8" s="162"/>
       <c r="BY8" s="158"/>
-      <c r="BZ8" s="162"/>
-      <c r="CA8" s="158"/>
-      <c r="CB8" s="162"/>
-      <c r="CC8" s="158"/>
+      <c r="BZ8" s="162" t="s">
+        <v>9</v>
+      </c>
+      <c r="CA8" s="158" t="s">
+        <v>3</v>
+      </c>
+      <c r="CB8" s="162" t="s">
+        <v>1</v>
+      </c>
+      <c r="CC8" s="158">
+        <v>3.25</v>
+      </c>
       <c r="CD8" s="162"/>
       <c r="CE8" s="158"/>
       <c r="CF8" s="162"/>
@@ -9312,10 +9431,18 @@
       <c r="BW10" s="158"/>
       <c r="BX10" s="157"/>
       <c r="BY10" s="158"/>
-      <c r="BZ10" s="157"/>
-      <c r="CA10" s="158"/>
-      <c r="CB10" s="157"/>
-      <c r="CC10" s="158"/>
+      <c r="BZ10" s="157" t="s">
+        <v>1</v>
+      </c>
+      <c r="CA10" s="158">
+        <v>1.75</v>
+      </c>
+      <c r="CB10" s="157" t="s">
+        <v>9</v>
+      </c>
+      <c r="CC10" s="158" t="s">
+        <v>3</v>
+      </c>
       <c r="CD10" s="157"/>
       <c r="CE10" s="158"/>
       <c r="CF10" s="157"/>
@@ -9968,10 +10095,18 @@
       <c r="BW12" s="158"/>
       <c r="BX12" s="157"/>
       <c r="BY12" s="158"/>
-      <c r="BZ12" s="157"/>
-      <c r="CA12" s="158"/>
-      <c r="CB12" s="157"/>
-      <c r="CC12" s="158"/>
+      <c r="BZ12" s="157" t="s">
+        <v>16</v>
+      </c>
+      <c r="CA12" s="158" t="s">
+        <v>3</v>
+      </c>
+      <c r="CB12" s="157" t="s">
+        <v>1</v>
+      </c>
+      <c r="CC12" s="158" t="s">
+        <v>3</v>
+      </c>
       <c r="CD12" s="157"/>
       <c r="CE12" s="158"/>
       <c r="CF12" s="157"/>
@@ -10624,10 +10759,18 @@
       <c r="BW14" s="158"/>
       <c r="BX14" s="157"/>
       <c r="BY14" s="158"/>
-      <c r="BZ14" s="157"/>
-      <c r="CA14" s="158"/>
-      <c r="CB14" s="157"/>
-      <c r="CC14" s="158"/>
+      <c r="BZ14" s="157" t="s">
+        <v>14</v>
+      </c>
+      <c r="CA14" s="158">
+        <v>0.25</v>
+      </c>
+      <c r="CB14" s="157" t="s">
+        <v>17</v>
+      </c>
+      <c r="CC14" s="158" t="s">
+        <v>3</v>
+      </c>
       <c r="CD14" s="157"/>
       <c r="CE14" s="158"/>
       <c r="CF14" s="157"/>
@@ -11284,10 +11427,18 @@
       <c r="BW16" s="158"/>
       <c r="BX16" s="157"/>
       <c r="BY16" s="158"/>
-      <c r="BZ16" s="157"/>
-      <c r="CA16" s="158"/>
-      <c r="CB16" s="157"/>
-      <c r="CC16" s="158"/>
+      <c r="BZ16" s="157" t="s">
+        <v>2</v>
+      </c>
+      <c r="CA16" s="158">
+        <v>2</v>
+      </c>
+      <c r="CB16" s="157" t="s">
+        <v>6</v>
+      </c>
+      <c r="CC16" s="158" t="s">
+        <v>3</v>
+      </c>
       <c r="CD16" s="157"/>
       <c r="CE16" s="158"/>
       <c r="CF16" s="157"/>
@@ -11940,10 +12091,18 @@
       <c r="BW18" s="158"/>
       <c r="BX18" s="157"/>
       <c r="BY18" s="158"/>
-      <c r="BZ18" s="157"/>
-      <c r="CA18" s="158"/>
-      <c r="CB18" s="157"/>
-      <c r="CC18" s="158"/>
+      <c r="BZ18" s="157" t="s">
+        <v>16</v>
+      </c>
+      <c r="CA18" s="158">
+        <v>3.5</v>
+      </c>
+      <c r="CB18" s="157" t="s">
+        <v>2</v>
+      </c>
+      <c r="CC18" s="158" t="s">
+        <v>3</v>
+      </c>
       <c r="CD18" s="157"/>
       <c r="CE18" s="158"/>
       <c r="CF18" s="157"/>
@@ -13243,7 +13402,9 @@
       <c r="CB22" s="167" t="s">
         <v>23</v>
       </c>
-      <c r="CC22" s="168"/>
+      <c r="CC22" s="168">
+        <v>8</v>
+      </c>
       <c r="CD22" s="167" t="s">
         <v>23</v>
       </c>
@@ -14209,14 +14370,14 @@
       <formula>NOT(ISERROR(SEARCH("占",B3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3 C5 G5 E5 G3 E3 I3 I5 K3 M3 K5 M5 LI5 LG5 LE5 LC5 LA5 KY5 KW5 KU5 KS5 KQ5 O3 Q3 S3 U3 W3 Y3 AA3 AC3 AE3 AG3 AI3 AK3 AM3 AO3 AQ3 AS3 AU3 AW3 AY3 BA3 BC3 BE3 BG3 BI3 BK3 BM3 BO3 BQ3 BS3 BU3 BW3 BY3 CA3 CC3 CE3 CG3 CI3 CK3 CM3 CO3 CQ3 CS3 CU3 CW3 CY3 DA3 DC3 DE3 DG3 DI3 DK3 DM3 DO3 DQ3 DS3 DU3 DW3 DY3 EA3 EC3 EE3 EG3 EI3 EK3 EM3 EO3 EQ3 ES3 EU3 EW3 EY3 FA3 FC3 FE3 FG3 FI3 FK3 FM3 FO3 FQ3 FS3 FU3 FW3 FY3 GA3 GC3 GE3 GG3 GI3 GK3 GM3 GO3 GQ3 GS3 GU3 GW3 GY3 HA3 HC3 HE3 HG3 HI3 HK3 HM3 HO3 HQ3 HS3 HU3 HW3 HY3 IA3 IC3 IE3 IG3 II3 IK3 IM3 IO3 IQ3 IS3 IU3 IW3 IY3 JA3 JC3 JE3 JG3 JI3 JK3 JM3 JO3 JQ3 JS3 JU3 JW3 JY3 KA3 KC3 KE3 KG3 KI3 KK3 KM3 KO3 KQ3 KS3 KU3 KW3 KY3 LA3 LC3 LE3 LG3 LI3 KO5 KM5 KK5 KI5 O5 Q5 S5 U5 W5 Y5 AA5 AC5 AE5 AG5 AI5 AK5 AM5 AO5 AQ5 AS5 AU5 AW5 AY5 BA5 BC5 BE5 BG5 BI5 BK5 BM5 BO5 BQ5 BS5 BU5 BW5 BY5 CA5 CC5 CE5 CG5 CI5 CK5 CM5 CO5 CQ5 CS5 CU5 CW5 CY5 DA5 DC5 DE5 DG5 DI5 DK5 DM5 DO5 DQ5 DS5 DU5 DW5 DY5 EA5 EC5 EE5 EG5 EI5 EK5 EM5 EO5 EQ5 ES5 EU5 EW5 EY5 FA5 FC5 FE5 FG5 FI5 FK5 FM5 FO5 FQ5 FS5 FU5 FW5 FY5 GA5 GC5 GE5 GG5 GI5 GK5 GM5 GO5 GQ5 GS5 GU5 GW5 GY5 HA5 HC5 HE5 HG5 HI5 HK5 HM5 HO5 HQ5 HS5 HU5 HW5 HY5 IA5 IC5 IE5 IG5 II5 IK5 IM5 IO5 IQ5 IS5 IU5 IW5 IY5 JA5 JC5 JE5 JG5 JI5 JK5 JM5 JO5 JQ5 JS5 JU5 JW5 JY5 KA5 KC5 KE5 KG5 C8 G10 E10 G8 E8 G20 E20 G18 E18 G16 E16 G14 E14 G12 E12 C10 C12 C14 C16 C18 C20 I12 I14 I16 I18 I20 I8 I10 LI20 LG20 LE20 LC20 K8 M8 K10 M10 K12 M12 K14 M14 K16 M16 K18 M18 K20 M20 HW20 HU20 HS20 HQ20 HO20 HM20 HK20 HI20 HG20 HE20 HC20 HA20 GY20 GW20 GU20 GS20 GQ20 GO20 GM20 GK20 GI20 GG20 GE20 GC20 GA20 FY20 FW20 FU20 FS20 FQ20 FO20 FM20 FK20 FI20 FG20 FE20 FC20 FA20 EY20 EW20 EU20 ES20 EQ20 EO20 EM20 EK20 EI20 EG20 EE20 EC20 EA20 DY20 DW20 DU20 DS20 DQ20 DO20 DM20 DK20 DI20 DG20 DE20 DC20 DA20 CY20 CW20 CU20 CS20 CQ20 CO20 CM20 CK20 CI20 CG20 CE20 CC20 CA20 BY20 BW20 BU20 BS20 BQ20 BO20 BM20 BK20 BI20 BG20 BE20 BC20 BA20 AY20 AW20 AU20 AS20 AQ20 AO20 AM20 AK20 AI20 AG20 AE20 AC20 AA20 Y20 W20 U20 S20 Q20 O20 HY20 IA20 JI20 JK20 LI18 LG18 LE18 LC18 LA18 KY18 KW18 KU18 KS18 KQ18 KO18 KM18 KK18 KI18 KG18 KE18 KC18 KA18 JY18 JW18 JU18 JS18 JQ18 JO18 JM18 JK18 JI18 JG18 JE18 JC18 JA18 IY18 IW18 IU18 IS18 IQ18 IO18 IM18 IK18 II18 IG18 IE18 IC18 IA18 HY18 HW18 HU18 HS18 HQ18 HO18 HM18 HK18 HI18 HG18 HE18 HC18 HA18 GY18 GW18 GU18 GS18 GQ18 GO18 GM18 GK18 GI18 GG18 GE18 GC18 GA18 FY18 FW18 FU18 FS18 FQ18 FO18 FM18 FK18 FI18 FG18 FE18 FC18 FA18 EY18 EW18 EU18 ES18 EQ18 EO18 EM18 EK18 EI18 EG18 EE18 EC18 EA18 DY18 DW18 DU18 DS18 DQ18 DO18 DM18 DK18 DI18 DG18 DE18 DC18 DA18 CY18 CW18 CU18 CS18 CQ18 CO18 CM18 CK18 CI18 CG18 CE18 CC18 CA18 BY18 BW18 BU18 BS18 BQ18 BO18 BM18 BK18 BI18 BG18 BE18 BC18 BA18 AY18 AW18 AU18 AS18 AQ18 AO18 AM18 AK18 AI18 AG18 AE18 AC18 AA18 Y18 W18 U18 S18 Q18 O18 IC20 IE20 JM20 JO20 LI16 LG16 LE16 LC16 LA16 KY16 KW16 KU16 KS16 KQ16 KO16 KM16 KK16 KI16 KG16 KE16 KC16 KA16 JY16 JW16 JU16 JS16 JQ16 JO16 JM16 JK16 JI16 JG16 JE16 JC16 JA16 IY16 IW16 IU16 IS16 IQ16 IO16 IM16 IK16 II16 IG16 IE16 IC16 IA16 HY16 HW16 HU16 HS16 HQ16 HO16 HM16 HK16 HI16 HG16 HE16 HC16 HA16 GY16 GW16 GU16 GS16 GQ16 GO16 GM16 GK16 GI16 GG16 GE16 GC16 GA16 FY16 FW16 FU16 FS16 FQ16 FO16 FM16 FK16 FI16 FG16 FE16 FC16 FA16 EY16 EW16 EU16 ES16 EQ16 EO16 EM16 EK16 EI16 EG16 EE16 EC16 EA16 DY16 DW16 DU16 DS16 DQ16 DO16 DM16 DK16 DI16 DG16 DE16 DC16 DA16 CY16 CW16 CU16 CS16 CQ16 CO16 CM16 CK16 CI16 CG16 CE16 CC16 CA16 BY16 BW16 BU16 BS16 BQ16 BO16 BM16 BK16 BI16 BG16 BE16 BC16 BA16 AY16 AW16 AU16 AS16 AQ16 AO16 AM16 AK16 AI16 AG16 AE16 AC16 AA16 Y16 W16 U16 S16 Q16 O16 IG20 II20 JQ20 JS20 LI14 LG14 LE14 LC14 LA14 KY14 KW14 KU14 KS14 KQ14 KO14 KM14 KK14 KI14 KG14 KE14 KC14 KA14 JY14 JW14 JU14 JS14 JQ14 JO14 JM14 JK14 JI14 JG14 JE14 JC14 JA14 IY14 IW14 IU14 IS14 IQ14 IO14 IM14 IK14 II14 IG14 IE14 IC14 IA14 HY14 HW14 HU14 HS14 HQ14 HO14 HM14 HK14 HI14 HG14 HE14 HC14 HA14 GY14 GW14 GU14 GS14 GQ14 GO14 GM14 GK14 GI14 GG14 GE14 GC14 GA14 FY14 FW14 FU14 FS14 FQ14 FO14 FM14 FK14 FI14 FG14 FE14 FC14 FA14 EY14 EW14 EU14 ES14 EQ14 EO14 EM14 EK14 EI14 EG14 EE14 EC14 EA14 DY14 DW14 DU14 DS14 DQ14 DO14 DM14 DK14 DI14 DG14 DE14 DC14 DA14 CY14 CW14 CU14 CS14 CQ14 CO14 CM14 CK14 CI14 CG14 CE14 CC14 CA14 BY14 BW14 BU14 BS14 BQ14 BO14 BM14 BK14 BI14 BG14 BE14 BC14 BA14 AY14 AW14 AU14 AS14 AQ14 AO14 AM14 AK14 AI14 AG14 AE14 AC14 AA14 Y14 W14 U14 S14 Q14 O14 IK20 IM20 JU20 JW20 LI12 LG12 LE12 LC12 LA12 KY12 KW12 KU12 KS12 KQ12 KO12 KM12 KK12 KI12 KG12 KE12 KC12 KA12 JY12 JW12 JU12 JS12 JQ12 JO12 JM12 JK12 JI12 JG12 JE12 JC12 JA12 IY12 IW12 IU12 IS12 IQ12 IO12 IM12 IK12 II12 IG12 IE12 IC12 IA12 HY12 HW12 HU12 HS12 HQ12 HO12 HM12 HK12 HI12 HG12 HE12 HC12 HA12 GY12 GW12 GU12 GS12 GQ12 GO12 GM12 GK12 GI12 GG12 GE12 GC12 GA12 FY12 FW12 FU12 FS12 FQ12 FO12 FM12 FK12 FI12 FG12 FE12 FC12 FA12 EY12 EW12 EU12 ES12 EQ12 EO12 EM12 EK12 EI12 EG12 EE12 EC12 EA12 DY12 DW12 DU12 DS12 DQ12 DO12 DM12 DK12 DI12 DG12 DE12 DC12 DA12 CY12 CW12 CU12 CS12 CQ12 CO12 CM12 CK12 CI12 CG12 CE12 CC12 CA12 BY12 BW12 BU12 BS12 BQ12 BO12 BM12 BK12 BI12 BG12 BE12 BC12 BA12 AY12 AW12 AU12 AS12 AQ12 AO12 AM12 AK12 AI12 AG12 AE12 AC12 AA12 Y12 W12 U12 S12 Q12 O12 IO20 IQ20 JY20 KA20 LI10 LG10 LE10 LC10 LA10 KY10 KW10 KU10 KS10 KQ10 KO10 KM10 KK10 KI10 KG10 KE10 KC10 KA10 JY10 JW10 JU10 JS10 JQ10 JO10 JM10 JK10 JI10 JG10 JE10 JC10 JA10 IY10 IW10 IU10 IS10 IQ10 IO10 IM10 IK10 II10 IG10 IE10 IC10 IA10 HY10 HW10 HU10 HS10 HQ10 HO10 HM10 HK10 HI10 HG10 HE10 HC10 HA10 GY10 GW10 GU10 GS10 GQ10 GO10 GM10 GK10 GI10 GG10 GE10 GC10 GA10 FY10 FW10 FU10 FS10 FQ10 FO10 FM10 FK10 FI10 FG10 FE10 FC10 FA10 EY10 EW10 EU10 ES10 EQ10 EO10 EM10 EK10 EI10 EG10 EE10 EC10 EA10 DY10 DW10 DU10 DS10 DQ10 DO10 DM10 DK10 DI10 DG10 DE10 DC10 DA10 CY10 CW10 CU10 CS10 CQ10 CO10 CM10 CK10 CI10 CG10 CE10 CC10 CA10 BY10 BW10 BU10 BS10 BQ10 BO10 BM10 BK10 BI10 BG10 BE10 BC10 BA10 AY10 AW10 AU10 AS10 AQ10 AO10 AM10 AK10 AI10 AG10 AE10 AC10 AA10 Y10 W10 U10 S10 Q10 O10 IS20 IU20 KC20 KE20 LI8 LG8 LE8 LC8 LA8 KY8 KW8 KU8 KS8 KQ8 KO8 KM8 KK8 KI8 KG8 KE8 KC8 KA8 JY8 JW8 JU8 JS8 JQ8 JO8 JM8 JK8 JI8 JG8 JE8 JC8 JA8 IY8 IW8 IU8 IS8 IQ8 IO8 IM8 IK8 II8 IG8 IE8 IC8 IA8 HY8 HW8 HU8 HS8 HQ8 HO8 HM8 HK8 HI8 HG8 HE8 HC8 HA8 GY8 GW8 GU8 GS8 GQ8 GO8 GM8 GK8 GI8 GG8 GE8 GC8 GA8 FY8 FW8 FU8 FS8 FQ8 FO8 FM8 FK8 FI8 FG8 FE8 FC8 FA8 EY8 EW8 EU8 ES8 EQ8 EO8 EM8 EK8 EI8 EG8 EE8 EC8 EA8 DY8 DW8 DU8 DS8 DQ8 DO8 DM8 DK8 DI8 DG8 DE8 DC8 DA8 CY8 CW8 CU8 CS8 CQ8 CO8 CM8 CK8 CI8 CG8 CE8 CC8 CA8 BY8 BW8 BU8 BS8 BQ8 BO8 BM8 BK8 BI8 BG8 BE8 BC8 BA8 AY8 AW8 AU8 AS8 AQ8 AO8 AM8 AK8 AI8 AG8 AE8 AC8 AA8 Y8 W8 U8 S8 Q8 O8 IW20 IY20 KG20 KI20 LA20 KY20 KW20 KU20 KS20 KQ20 KO20 JG20 JE20 KM20 KK20 JC20 JA20">
-    <cfRule type="containsBlanks" dxfId="1" priority="3">
-      <formula>LEN(TRIM(C3))=0</formula>
+  <conditionalFormatting sqref="C3:C21 E3:E21 KW3:KW21 LI3:LI21 KU3:KU21 KS3:KS21 G3:G21 KQ3:KQ21 KO3:KO21 KM3:KM21 I3:I21 KK3:KK21 KI3:KI21 KG3:KG21 K3:K21 KE3:KE21 KC3:KC21 KA3:KA21 M3:M21 JY3:JY21 JW3:JW21 JU3:JU21 O3:O21 JS3:JS21 Q3:Q21 JQ3:JQ21 S3:S21 JO3:JO21 U3:U21 JM3:JM21 W3:W21 JK3:JK21 Y3:Y21 JI3:JI21 JG3:JG21 AA3:AA21 JE3:JE21 JC3:JC21 AC3:AC21 JA3:JA21 IY3:IY21 AE3:AE21 IW3:IW21 IU3:IU21 AG3:AG21 IS3:IS21 IQ3:IQ21 AI3:AI21 IO3:IO21 IM3:IM21 AK3:AK21 IK3:IK21 II3:II21 AM3:AM21 IG3:IG21 IE3:IE21 AO3:AO21 IC3:IC21 IA3:IA21 AQ3:AQ21 HY3:HY21 HW3:HW21 AS3:AS21 HU3:HU21 HS3:HS21 AU3:AU21 HQ3:HQ21 HO3:HO21 AW3:AW21 HM3:HM21 HK3:HK21 AY3:AY21 HI3:HI21 HG3:HG21 BA3:BA21 HE3:HE21 HC3:HC21 BC3:BC21 HA3:HA21 GY3:GY21 BE3:BE21 GW3:GW21 GU3:GU21 BG3:BG21 GS3:GS21 GQ3:GQ21 BI3:BI21 GO3:GO21 GM3:GM21 BK3:BK21 GK3:GK21 GI3:GI21 BM3:BM21 GG3:GG21 GE3:GE21 BO3:BO21 GC3:GC21 GA3:GA21 BQ3:BQ21 FY3:FY21 FW3:FW21 BS3:BS21 FU3:FU21 FS3:FS21 BU3:BU21 FQ3:FQ21 FO3:FO21 BW3:BW21 FM3:FM21 FK3:FK21 BY3:BY21 FI3:FI21 FG3:FG21 CA3:CA21 FE3:FE21 FC3:FC21 CC3:CC21 FA3:FA21 EY3:EY21 CE3:CE21 EW3:EW21 EU3:EU21 CG3:CG21 ES3:ES21 EQ3:EQ21 CI3:CI21 EO3:EO21 EM3:EM21 CK3:CK21 EK3:EK21 EI3:EI21 CM3:CM21 EG3:EG21 EE3:EE21 CO3:CO21 EC3:EC21 EA3:EA21 CQ3:CQ21 DY3:DY21 DW3:DW21 CS3:CS21 DU3:DU21 DS3:DS21 CU3:CU21 DQ3:DQ21 DO3:DO21 CW3:CW21 DM3:DM21 DK3:DK21 CY3:CY21 DI3:DI21 DG3:DG21 DA3:DA21 DE3:DE21 DC3:DC21 KV11 KT11 KX11:LH11 KR11 KP11 KN11 LG12:LG21 KL11 KJ11 KH11 LE12:LE21 KF11 KD11 KB11 LC12:LC21 JZ11 JX11 JV11 LA12:LA21 JT11 JR11 JP11 JN11 JL11 JJ11 JH11 X11 JF11 JD11 Z11 JB11 IZ11 AB11 IX11 IV11 AD11 IT11 IR11 AF11 IP11 IN11 AH11 IL11 IJ11 AJ11 IH11 IF11 AL11 ID11 IB11 AN11 HZ11 HX11 AP11 HV11 HT11 AR11 HR11 HP11 AT11 HN11 HL11 AV11 HJ11 HH11 AX11 HF11 HD11 AZ11 HB11 GZ11 BB11 GX11 GV11 BD11 GT11 GR11 BF11 GP11 GN11 BH11 GL11 GJ11 BJ11 GH11 GF11 BL11 GD11 GB11 BN11 FZ11 FX11 BP11 FV11 FT11 BR11 FR11 FP11 BT11 FN11 FL11 BV11 FJ11 FH11 BX11 FF11 FD11 BZ11 FB11 EZ11 CB11 EX11 EV11 CD11 ET11 ER11 CF11 EP11 EN11 CH11 EL11 EJ11 CJ11 EH11 EF11 CL11 ED11 EB11 CN11 DZ11 DX11 CP11 DV11 DT11 CR11 DR11 DP11 CT11 DN11 DL11 CV11 DJ11 DH11 CX11 DF11 DD11 CZ11 DB11 KY3:KY10 KY12:KY21 LA3:LA10 LC3:LC10 LE3:LE10 LG3:LG10">
+    <cfRule type="containsText" dxfId="1" priority="4" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",C3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C21 E3:E21 KW3:KW21 LI3:LI21 KU3:KU21 KS3:KS21 G3:G21 KQ3:KQ21 KO3:KO21 KM3:KM21 I3:I21 KK3:KK21 KI3:KI21 KG3:KG21 K3:K21 KE3:KE21 KC3:KC21 KA3:KA21 M3:M21 JY3:JY21 JW3:JW21 JU3:JU21 O3:O21 JS3:JS21 Q3:Q21 JQ3:JQ21 S3:S21 JO3:JO21 U3:U21 JM3:JM21 W3:W21 JK3:JK21 Y3:Y21 JI3:JI21 JG3:JG21 AA3:AA21 JE3:JE21 JC3:JC21 AC3:AC21 JA3:JA21 IY3:IY21 AE3:AE21 IW3:IW21 IU3:IU21 AG3:AG21 IS3:IS21 IQ3:IQ21 AI3:AI21 IO3:IO21 IM3:IM21 AK3:AK21 IK3:IK21 II3:II21 AM3:AM21 IG3:IG21 IE3:IE21 AO3:AO21 IC3:IC21 IA3:IA21 AQ3:AQ21 HY3:HY21 HW3:HW21 AS3:AS21 HU3:HU21 HS3:HS21 AU3:AU21 HQ3:HQ21 HO3:HO21 AW3:AW21 HM3:HM21 HK3:HK21 AY3:AY21 HI3:HI21 HG3:HG21 BA3:BA21 HE3:HE21 HC3:HC21 BC3:BC21 HA3:HA21 GY3:GY21 BE3:BE21 GW3:GW21 GU3:GU21 BG3:BG21 GS3:GS21 GQ3:GQ21 BI3:BI21 GO3:GO21 GM3:GM21 BK3:BK21 GK3:GK21 GI3:GI21 BM3:BM21 GG3:GG21 GE3:GE21 BO3:BO21 GC3:GC21 GA3:GA21 BQ3:BQ21 FY3:FY21 FW3:FW21 BS3:BS21 FU3:FU21 FS3:FS21 BU3:BU21 FQ3:FQ21 FO3:FO21 BW3:BW21 FM3:FM21 FK3:FK21 BY3:BY21 FI3:FI21 FG3:FG21 CA3:CA21 FE3:FE21 FC3:FC21 CC3:CC21 FA3:FA21 EY3:EY21 CE3:CE21 EW3:EW21 EU3:EU21 CG3:CG21 ES3:ES21 EQ3:EQ21 CI3:CI21 EO3:EO21 EM3:EM21 CK3:CK21 EK3:EK21 EI3:EI21 CM3:CM21 EG3:EG21 EE3:EE21 CO3:CO21 EC3:EC21 EA3:EA21 CQ3:CQ21 DY3:DY21 DW3:DW21 CS3:CS21 DU3:DU21 DS3:DS21 CU3:CU21 DQ3:DQ21 DO3:DO21 CW3:CW21 DM3:DM21 DK3:DK21 CY3:CY21 DI3:DI21 DG3:DG21 DA3:DA21 DE3:DE21 DC3:DC21 KV11 KT11 KX11:LH11 KR11 KP11 KN11 LG12:LG21 KL11 KJ11 KH11 LE12:LE21 KF11 KD11 KB11 LC12:LC21 JZ11 JX11 JV11 LA12:LA21 JT11 JR11 JP11 JN11 JL11 JJ11 JH11 X11 JF11 JD11 Z11 JB11 IZ11 AB11 IX11 IV11 AD11 IT11 IR11 AF11 IP11 IN11 AH11 IL11 IJ11 AJ11 IH11 IF11 AL11 ID11 IB11 AN11 HZ11 HX11 AP11 HV11 HT11 AR11 HR11 HP11 AT11 HN11 HL11 AV11 HJ11 HH11 AX11 HF11 HD11 AZ11 HB11 GZ11 BB11 GX11 GV11 BD11 GT11 GR11 BF11 GP11 GN11 BH11 GL11 GJ11 BJ11 GH11 GF11 BL11 GD11 GB11 BN11 FZ11 FX11 BP11 FV11 FT11 BR11 FR11 FP11 BT11 FN11 FL11 BV11 FJ11 FH11 BX11 FF11 FD11 BZ11 FB11 EZ11 CB11 EX11 EV11 CD11 ET11 ER11 CF11 EP11 EN11 CH11 EL11 EJ11 CJ11 EH11 EF11 CL11 ED11 EB11 CN11 DZ11 DX11 CP11 DV11 DT11 CR11 DR11 DP11 CT11 DN11 DL11 CV11 DJ11 DH11 CX11 DF11 DD11 CZ11 DB11 KY3:KY10 KY12:KY21 LA3:LA10 LC3:LC10 LE3:LE10 LG3:LG10">
-    <cfRule type="containsText" dxfId="2" priority="4" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",C3)))</formula>
+  <conditionalFormatting sqref="C3 C5 G5 E5 G3 E3 I3 I5 K3 M3 K5 M5 LI5 LG5 LE5 LC5 LA5 KY5 KW5 KU5 KS5 KQ5 O3 Q3 S3 U3 W3 Y3 AA3 AC3 AE3 AG3 AI3 AK3 AM3 AO3 AQ3 AS3 AU3 AW3 AY3 BA3 BC3 BE3 BG3 BI3 BK3 BM3 BO3 BQ3 BS3 BU3 BW3 BY3 CA3 CC3 CE3 CG3 CI3 CK3 CM3 CO3 CQ3 CS3 CU3 CW3 CY3 DA3 DC3 DE3 DG3 DI3 DK3 DM3 DO3 DQ3 DS3 DU3 DW3 DY3 EA3 EC3 EE3 EG3 EI3 EK3 EM3 EO3 EQ3 ES3 EU3 EW3 EY3 FA3 FC3 FE3 FG3 FI3 FK3 FM3 FO3 FQ3 FS3 FU3 FW3 FY3 GA3 GC3 GE3 GG3 GI3 GK3 GM3 GO3 GQ3 GS3 GU3 GW3 GY3 HA3 HC3 HE3 HG3 HI3 HK3 HM3 HO3 HQ3 HS3 HU3 HW3 HY3 IA3 IC3 IE3 IG3 II3 IK3 IM3 IO3 IQ3 IS3 IU3 IW3 IY3 JA3 JC3 JE3 JG3 JI3 JK3 JM3 JO3 JQ3 JS3 JU3 JW3 JY3 KA3 KC3 KE3 KG3 KI3 KK3 KM3 KO3 KQ3 KS3 KU3 KW3 KY3 LA3 LC3 LE3 LG3 LI3 KO5 KM5 KK5 KI5 O5 Q5 S5 U5 W5 Y5 AA5 AC5 AE5 AG5 AI5 AK5 AM5 AO5 AQ5 AS5 AU5 AW5 AY5 BA5 BC5 BE5 BG5 BI5 BK5 BM5 BO5 BQ5 BS5 BU5 BW5 BY5 CA5 CC5 CE5 CG5 CI5 CK5 CM5 CO5 CQ5 CS5 CU5 CW5 CY5 DA5 DC5 DE5 DG5 DI5 DK5 DM5 DO5 DQ5 DS5 DU5 DW5 DY5 EA5 EC5 EE5 EG5 EI5 EK5 EM5 EO5 EQ5 ES5 EU5 EW5 EY5 FA5 FC5 FE5 FG5 FI5 FK5 FM5 FO5 FQ5 FS5 FU5 FW5 FY5 GA5 GC5 GE5 GG5 GI5 GK5 GM5 GO5 GQ5 GS5 GU5 GW5 GY5 HA5 HC5 HE5 HG5 HI5 HK5 HM5 HO5 HQ5 HS5 HU5 HW5 HY5 IA5 IC5 IE5 IG5 II5 IK5 IM5 IO5 IQ5 IS5 IU5 IW5 IY5 JA5 JC5 JE5 JG5 JI5 JK5 JM5 JO5 JQ5 JS5 JU5 JW5 JY5 KA5 KC5 KE5 KG5 C8 G10 E10 G8 E8 G20 E20 G18 E18 G16 E16 G14 E14 G12 E12 C10 C12 C14 C16 C18 C20 I12 I14 I16 I18 I20 I8 I10 LI20 LG20 LE20 LC20 K8 M8 K10 M10 K12 M12 K14 M14 K16 M16 K18 M18 K20 M20 HW20 HU20 HS20 HQ20 HO20 HM20 HK20 HI20 HG20 HE20 HC20 HA20 GY20 GW20 GU20 GS20 GQ20 GO20 GM20 GK20 GI20 GG20 GE20 GC20 GA20 FY20 FW20 FU20 FS20 FQ20 FO20 FM20 FK20 FI20 FG20 FE20 FC20 FA20 EY20 EW20 EU20 ES20 EQ20 EO20 EM20 EK20 EI20 EG20 EE20 EC20 EA20 DY20 DW20 DU20 DS20 DQ20 DO20 DM20 DK20 DI20 DG20 DE20 DC20 DA20 CY20 CW20 CU20 CS20 CQ20 CO20 CM20 CK20 CI20 CG20 CE20 CC20 CA20 BY20 BW20 BU20 BS20 BQ20 BO20 BM20 BK20 BI20 BG20 BE20 BC20 BA20 AY20 AW20 AU20 AS20 AQ20 AO20 AM20 AK20 AI20 AG20 AE20 AC20 AA20 Y20 W20 U20 S20 Q20 O20 HY20 IA20 JI20 JK20 LI18 LG18 LE18 LC18 LA18 KY18 KW18 KU18 KS18 KQ18 KO18 KM18 KK18 KI18 KG18 KE18 KC18 KA18 JY18 JW18 JU18 JS18 JQ18 JO18 JM18 JK18 JI18 JG18 JE18 JC18 JA18 IY18 IW18 IU18 IS18 IQ18 IO18 IM18 IK18 II18 IG18 IE18 IC18 IA18 HY18 HW18 HU18 HS18 HQ18 HO18 HM18 HK18 HI18 HG18 HE18 HC18 HA18 GY18 GW18 GU18 GS18 GQ18 GO18 GM18 GK18 GI18 GG18 GE18 GC18 GA18 FY18 FW18 FU18 FS18 FQ18 FO18 FM18 FK18 FI18 FG18 FE18 FC18 FA18 EY18 EW18 EU18 ES18 EQ18 EO18 EM18 EK18 EI18 EG18 EE18 EC18 EA18 DY18 DW18 DU18 DS18 DQ18 DO18 DM18 DK18 DI18 DG18 DE18 DC18 DA18 CY18 CW18 CU18 CS18 CQ18 CO18 CM18 CK18 CI18 CG18 CE18 CC18 CA18 BY18 BW18 BU18 BS18 BQ18 BO18 BM18 BK18 BI18 BG18 BE18 BC18 BA18 AY18 AW18 AU18 AS18 AQ18 AO18 AM18 AK18 AI18 AG18 AE18 AC18 AA18 Y18 W18 U18 S18 Q18 O18 IC20 IE20 JM20 JO20 LI16 LG16 LE16 LC16 LA16 KY16 KW16 KU16 KS16 KQ16 KO16 KM16 KK16 KI16 KG16 KE16 KC16 KA16 JY16 JW16 JU16 JS16 JQ16 JO16 JM16 JK16 JI16 JG16 JE16 JC16 JA16 IY16 IW16 IU16 IS16 IQ16 IO16 IM16 IK16 II16 IG16 IE16 IC16 IA16 HY16 HW16 HU16 HS16 HQ16 HO16 HM16 HK16 HI16 HG16 HE16 HC16 HA16 GY16 GW16 GU16 GS16 GQ16 GO16 GM16 GK16 GI16 GG16 GE16 GC16 GA16 FY16 FW16 FU16 FS16 FQ16 FO16 FM16 FK16 FI16 FG16 FE16 FC16 FA16 EY16 EW16 EU16 ES16 EQ16 EO16 EM16 EK16 EI16 EG16 EE16 EC16 EA16 DY16 DW16 DU16 DS16 DQ16 DO16 DM16 DK16 DI16 DG16 DE16 DC16 DA16 CY16 CW16 CU16 CS16 CQ16 CO16 CM16 CK16 CI16 CG16 CE16 CC16 CA16 BY16 BW16 BU16 BS16 BQ16 BO16 BM16 BK16 BI16 BG16 BE16 BC16 BA16 AY16 AW16 AU16 AS16 AQ16 AO16 AM16 AK16 AI16 AG16 AE16 AC16 AA16 Y16 W16 U16 S16 Q16 O16 IG20 II20 JQ20 JS20 LI14 LG14 LE14 LC14 LA14 KY14 KW14 KU14 KS14 KQ14 KO14 KM14 KK14 KI14 KG14 KE14 KC14 KA14 JY14 JW14 JU14 JS14 JQ14 JO14 JM14 JK14 JI14 JG14 JE14 JC14 JA14 IY14 IW14 IU14 IS14 IQ14 IO14 IM14 IK14 II14 IG14 IE14 IC14 IA14 HY14 HW14 HU14 HS14 HQ14 HO14 HM14 HK14 HI14 HG14 HE14 HC14 HA14 GY14 GW14 GU14 GS14 GQ14 GO14 GM14 GK14 GI14 GG14 GE14 GC14 GA14 FY14 FW14 FU14 FS14 FQ14 FO14 FM14 FK14 FI14 FG14 FE14 FC14 FA14 EY14 EW14 EU14 ES14 EQ14 EO14 EM14 EK14 EI14 EG14 EE14 EC14 EA14 DY14 DW14 DU14 DS14 DQ14 DO14 DM14 DK14 DI14 DG14 DE14 DC14 DA14 CY14 CW14 CU14 CS14 CQ14 CO14 CM14 CK14 CI14 CG14 CE14 CC14 CA14 BY14 BW14 BU14 BS14 BQ14 BO14 BM14 BK14 BI14 BG14 BE14 BC14 BA14 AY14 AW14 AU14 AS14 AQ14 AO14 AM14 AK14 AI14 AG14 AE14 AC14 AA14 Y14 W14 U14 S14 Q14 O14 IK20 IM20 JU20 JW20 LI12 LG12 LE12 LC12 LA12 KY12 KW12 KU12 KS12 KQ12 KO12 KM12 KK12 KI12 KG12 KE12 KC12 KA12 JY12 JW12 JU12 JS12 JQ12 JO12 JM12 JK12 JI12 JG12 JE12 JC12 JA12 IY12 IW12 IU12 IS12 IQ12 IO12 IM12 IK12 II12 IG12 IE12 IC12 IA12 HY12 HW12 HU12 HS12 HQ12 HO12 HM12 HK12 HI12 HG12 HE12 HC12 HA12 GY12 GW12 GU12 GS12 GQ12 GO12 GM12 GK12 GI12 GG12 GE12 GC12 GA12 FY12 FW12 FU12 FS12 FQ12 FO12 FM12 FK12 FI12 FG12 FE12 FC12 FA12 EY12 EW12 EU12 ES12 EQ12 EO12 EM12 EK12 EI12 EG12 EE12 EC12 EA12 DY12 DW12 DU12 DS12 DQ12 DO12 DM12 DK12 DI12 DG12 DE12 DC12 DA12 CY12 CW12 CU12 CS12 CQ12 CO12 CM12 CK12 CI12 CG12 CE12 CC12 CA12 BY12 BW12 BU12 BS12 BQ12 BO12 BM12 BK12 BI12 BG12 BE12 BC12 BA12 AY12 AW12 AU12 AS12 AQ12 AO12 AM12 AK12 AI12 AG12 AE12 AC12 AA12 Y12 W12 U12 S12 Q12 O12 IO20 IQ20 JY20 KA20 LI10 LG10 LE10 LC10 LA10 KY10 KW10 KU10 KS10 KQ10 KO10 KM10 KK10 KI10 KG10 KE10 KC10 KA10 JY10 JW10 JU10 JS10 JQ10 JO10 JM10 JK10 JI10 JG10 JE10 JC10 JA10 IY10 IW10 IU10 IS10 IQ10 IO10 IM10 IK10 II10 IG10 IE10 IC10 IA10 HY10 HW10 HU10 HS10 HQ10 HO10 HM10 HK10 HI10 HG10 HE10 HC10 HA10 GY10 GW10 GU10 GS10 GQ10 GO10 GM10 GK10 GI10 GG10 GE10 GC10 GA10 FY10 FW10 FU10 FS10 FQ10 FO10 FM10 FK10 FI10 FG10 FE10 FC10 FA10 EY10 EW10 EU10 ES10 EQ10 EO10 EM10 EK10 EI10 EG10 EE10 EC10 EA10 DY10 DW10 DU10 DS10 DQ10 DO10 DM10 DK10 DI10 DG10 DE10 DC10 DA10 CY10 CW10 CU10 CS10 CQ10 CO10 CM10 CK10 CI10 CG10 CE10 CC10 CA10 BY10 BW10 BU10 BS10 BQ10 BO10 BM10 BK10 BI10 BG10 BE10 BC10 BA10 AY10 AW10 AU10 AS10 AQ10 AO10 AM10 AK10 AI10 AG10 AE10 AC10 AA10 Y10 W10 U10 S10 Q10 O10 IS20 IU20 KC20 KE20 LI8 LG8 LE8 LC8 LA8 KY8 KW8 KU8 KS8 KQ8 KO8 KM8 KK8 KI8 KG8 KE8 KC8 KA8 JY8 JW8 JU8 JS8 JQ8 JO8 JM8 JK8 JI8 JG8 JE8 JC8 JA8 IY8 IW8 IU8 IS8 IQ8 IO8 IM8 IK8 II8 IG8 IE8 IC8 IA8 HY8 HW8 HU8 HS8 HQ8 HO8 HM8 HK8 HI8 HG8 HE8 HC8 HA8 GY8 GW8 GU8 GS8 GQ8 GO8 GM8 GK8 GI8 GG8 GE8 GC8 GA8 FY8 FW8 FU8 FS8 FQ8 FO8 FM8 FK8 FI8 FG8 FE8 FC8 FA8 EY8 EW8 EU8 ES8 EQ8 EO8 EM8 EK8 EI8 EG8 EE8 EC8 EA8 DY8 DW8 DU8 DS8 DQ8 DO8 DM8 DK8 DI8 DG8 DE8 DC8 DA8 CY8 CW8 CU8 CS8 CQ8 CO8 CM8 CK8 CI8 CG8 CE8 CC8 CA8 BY8 BW8 BU8 BS8 BQ8 BO8 BM8 BK8 BI8 BG8 BE8 BC8 BA8 AY8 AW8 AU8 AS8 AQ8 AO8 AM8 AK8 AI8 AG8 AE8 AC8 AA8 Y8 W8 U8 S8 Q8 O8 IW20 IY20 KG20 KI20 LA20 KY20 KW20 KU20 KS20 KQ20 KO20 JG20 JE20 KM20 KK20 JC20 JA20">
+    <cfRule type="containsBlanks" dxfId="2" priority="3">
+      <formula>LEN(TRIM(C3))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22 JO22 JM22 JK22 JI22 JG22 JE22 JC22 JA22 IY22 IW22 IU22 IS22 IQ22 IO22 IM22 IK22 II22 IG22 IE22 IC22 IA22 HY22 HW22 HU22 HS22 HQ22 HO22 HM22 HK22 HI22 HG22 HE22 HC22 HA22 GY22 GW22 GU22 GS22 GQ22 GO22 GM22 GK22 GI22 GG22 GE22 GC22 GA22 FY22 FW22 FU22 FS22 FQ22 FO22 FM22 FK22 FI22 FG22 FE22 FC22 FA22 EY22 EW22 EU22 ES22 EQ22 EO22 EM22 EK22 EI22 EG22 EE22 EC22 EA22 DY22 DW22 DU22 DS22 DQ22 DO22 DM22 DK22 DI22 DG22 DE22 DC22 DA22 CY22 CW22 CU22 CS22 CQ22 CO22 CM22 CK22 CI22 CG22 CE22 CC22 CA22 BY22 BW22 BU22 BS22 BQ22 BO22 BM22 BK22 BI22 BG22 BE22 BC22 BA22 AY22 AW22 AU22 AS22 AQ22 AO22 AM22 AK22 AI22 AG22 AE22 AC22 AA22 Y22 W22 U22 S22 Q22 O22 M22 K22 I22 G22 E22">
@@ -14228,14 +14389,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CA3 CC5 CA8 CC10 CC11 CA12 CC12 CC13 CC14 CC15 CC16 CC17 CC18 C3:C21 E3:E21 G3:G21 I3:I21 K3:K21 M3:M21 O3:O21 Q3:Q21 S3:S21 U3:U21 W3:W21 Y3:Y21 AA3:AA21 AC3:AC21 AE3:AE21 AG3:AG21 AI3:AI21 AK3:AK21 AM3:AM21 AO3:AO21 AQ3:AQ21 AS3:AS21 AU3:AU21 AW3:AW21 AY3:AY21 BA3:BA21 BC3:BC21 BE3:BE21 BG3:BG21 BI3:BI21 BK3:BK21 BM3:BM21 BO3:BO21 BQ3:BQ21 BS3:BS21 BU3:BU21 BW3:BW21 BY3:BY21 CA4:CA7 CA9:CA11 CA13:CA21 CC3:CC4 CC6:CC9 CC19:CC21 CE3:CE21 CG3:CG21 CI3:CI21 CK3:CK21 CM3:CM21 CO3:CO21 CQ3:CQ21 CS3:CS21 CU3:CU21 CW3:CW21 CY3:CY21 DA3:DA21 DC3:DC21 DE3:DE21 DG3:DG21 DI3:DI21 DK3:DK21 DM3:DM21 DO3:DO21 DQ3:DQ21 DS3:DS21 DU3:DU21 DW3:DW21 DY3:DY21 EA3:EA21 EC3:EC21 EE3:EE21 EG3:EG21 EI3:EI21 EK3:EK21 EM3:EM21 EO3:EO21 EQ3:EQ21 ES3:ES21 EU3:EU21 EW3:EW21 EY3:EY21 FA3:FA21 FC3:FC21 FE3:FE21 FG3:FG21 FI3:FI21 FK3:FK21 FM3:FM21 FO3:FO21 FQ3:FQ21 FS3:FS21 FU3:FU21 FW3:FW21 FY3:FY21 GA3:GA21 GC3:GC21 GE3:GE21 GG3:GG21 GI3:GI21 GK3:GK21 GM3:GM21 GO3:GO21 GQ3:GQ21 GS3:GS21 GU3:GU21 GW3:GW21 GY3:GY21 HA3:HA21 HC3:HC21 HE3:HE21 HG3:HG21 HI3:HI21 HK3:HK21 HM3:HM21 HO3:HO21 HQ3:HQ21 HS3:HS21 HU3:HU21 HW3:HW21 HY3:HY21 IA3:IA21 IC3:IC21 IE3:IE21 IG3:IG21 II3:II21 IK3:IK21 IM3:IM21 IO3:IO21 IQ3:IQ21 IS3:IS21 IU3:IU21 IW3:IW21 IY3:IY21 JA3:JA21 JC3:JC21 JE3:JE21 JG3:JG21 JI3:JI21 JK3:JK21 JM3:JM21 JO3:JO21">
+      <formula1>数据!$B$1:$B$62</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C22 E22 G22 I22 K22 M22 O22 Q22 S22 U22 W22 Y22 AA22 AC22 AE22 AG22 AI22 AK22 AM22 AO22 AQ22 AS22 AU22 AW22 AY22 BA22 BC22 BE22 BG22 BI22 BK22 BM22 BO22 BQ22 BS22 BU22 BW22 BY22 CA22 CC22 CE22 CG22 CI22 CK22 CM22 CO22 CQ22 CS22 CU22 CW22 CY22 DA22 DC22 DE22 DG22 DI22 DK22 DM22 DO22 DQ22 DS22 DU22 DW22 DY22 EA22 EC22 EE22 EG22 EI22 EK22 EM22 EO22 EQ22 ES22 EU22 EW22 EY22 FA22 FC22 FE22 FG22 FI22 FK22 FM22 FO22 FQ22 FS22 FU22 FW22 FY22 GA22 GC22 GE22 GG22 GI22 GK22 GM22 GO22 GQ22 GS22 GU22 GW22 GY22 HA22 HC22 HE22 HG22 HI22 HK22 HM22 HO22 HQ22 HS22 HU22 HW22 HY22 IA22 IC22 IE22 IG22 II22 IK22 IM22 IO22 IQ22 IS22 IU22 IW22 IY22 JA22 JC22 JE22 JG22 JI22 JK22 JM22 JO22">
       <formula1>数据!$C$1:$C$25</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B21 D3:D21 F3:F21 H3:H21 J3:J21 L3:L21 N3:N21 P3:P21 R3:R21 T3:T21 V3:V21 X3:X21 Z3:Z21 AB3:AB21 AD3:AD21 AF3:AF21 AH3:AH21 AJ3:AJ21 AL3:AL21 AN3:AN21 AP3:AP21 AR3:AR21 AT3:AT21 AV3:AV21 AX3:AX21 AZ3:AZ21 BB3:BB21 BD3:BD21 BF3:BF21 BH3:BH21 BJ3:BJ21 BL3:BL21 BN3:BN21 BP3:BP21 BR3:BR21 BT3:BT21 BV3:BV21 BX3:BX21 BZ3:BZ21 CB3:CB21 CD3:CD21 CF3:CF21 CH3:CH21 CJ3:CJ21 CL3:CL21 CN3:CN21 CP3:CP21 CR3:CR21 CT3:CT21 CV3:CV21 CX3:CX21 CZ3:CZ21 DB3:DB21 DD3:DD21 DF3:DF21 DH3:DH21 DJ3:DJ21 DL3:DL21 DN3:DN21 DP3:DP21 DR3:DR21 DT3:DT21 DV3:DV21 DX3:DX21 DZ3:DZ21 EB3:EB21 ED3:ED21 EF3:EF21 EH3:EH21 EJ3:EJ21 EL3:EL21 EN3:EN21 EP3:EP21 ER3:ER21 ET3:ET21 EV3:EV21 EX3:EX21 EZ3:EZ21 FB3:FB21 FD3:FD21 FF3:FF21 FH3:FH21 FJ3:FJ21 FL3:FL21 FN3:FN21 FP3:FP21 FR3:FR21 FT3:FT21 FV3:FV21 FX3:FX21 FZ3:FZ21 GB3:GB21 GD3:GD21 GF3:GF21 GH3:GH21 GJ3:GJ21 GL3:GL21 GN3:GN21 GP3:GP21 GR3:GR21 GT3:GT21 GV3:GV21 GX3:GX21 GZ3:GZ21 HB3:HB21 HD3:HD21 HF3:HF21 HH3:HH21 HJ3:HJ21 HL3:HL21 HN3:HN21 HP3:HP21 HR3:HR21 HT3:HT21 HV3:HV21 HX3:HX21 HZ3:HZ21 IB3:IB21 ID3:ID21 IF3:IF21 IH3:IH21 IJ3:IJ21 IL3:IL21 IN3:IN21 IP3:IP21 IR3:IR21 IT3:IT21 IV3:IV21 IX3:IX21 IZ3:IZ21 JB3:JB21 JD3:JD21 JF3:JF21 JH3:JH21 JJ3:JJ21 JL3:JL21 JN3:JN21">
       <formula1>数据!$A$1:$A$88</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C21 E3:E21 G3:G21 I3:I21 K3:K21 M3:M21 O3:O21 Q3:Q21 S3:S21 U3:U21 W3:W21 Y3:Y21 AA3:AA21 AC3:AC21 AE3:AE21 AG3:AG21 AI3:AI21 AK3:AK21 AM3:AM21 AO3:AO21 AQ3:AQ21 AS3:AS21 AU3:AU21 AW3:AW21 AY3:AY21 BA3:BA21 BC3:BC21 BE3:BE21 BG3:BG21 BI3:BI21 BK3:BK21 BM3:BM21 BO3:BO21 BQ3:BQ21 BS3:BS21 BU3:BU21 BW3:BW21 BY3:BY21 CA3:CA21 CC3:CC21 CE3:CE21 CG3:CG21 CI3:CI21 CK3:CK21 CM3:CM21 CO3:CO21 CQ3:CQ21 CS3:CS21 CU3:CU21 CW3:CW21 CY3:CY21 DA3:DA21 DC3:DC21 DE3:DE21 DG3:DG21 DI3:DI21 DK3:DK21 DM3:DM21 DO3:DO21 DQ3:DQ21 DS3:DS21 DU3:DU21 DW3:DW21 DY3:DY21 EA3:EA21 EC3:EC21 EE3:EE21 EG3:EG21 EI3:EI21 EK3:EK21 EM3:EM21 EO3:EO21 EQ3:EQ21 ES3:ES21 EU3:EU21 EW3:EW21 EY3:EY21 FA3:FA21 FC3:FC21 FE3:FE21 FG3:FG21 FI3:FI21 FK3:FK21 FM3:FM21 FO3:FO21 FQ3:FQ21 FS3:FS21 FU3:FU21 FW3:FW21 FY3:FY21 GA3:GA21 GC3:GC21 GE3:GE21 GG3:GG21 GI3:GI21 GK3:GK21 GM3:GM21 GO3:GO21 GQ3:GQ21 GS3:GS21 GU3:GU21 GW3:GW21 GY3:GY21 HA3:HA21 HC3:HC21 HE3:HE21 HG3:HG21 HI3:HI21 HK3:HK21 HM3:HM21 HO3:HO21 HQ3:HQ21 HS3:HS21 HU3:HU21 HW3:HW21 HY3:HY21 IA3:IA21 IC3:IC21 IE3:IE21 IG3:IG21 II3:II21 IK3:IK21 IM3:IM21 IO3:IO21 IQ3:IQ21 IS3:IS21 IU3:IU21 IW3:IW21 IY3:IY21 JA3:JA21 JC3:JC21 JE3:JE21 JG3:JG21 JI3:JI21 JK3:JK21 JM3:JM21 JO3:JO21">
-      <formula1>数据!$B$1:$B$62</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14256,7 +14417,7 @@
   <sheetData>
     <row r="1" s="2" customFormat="1" customHeight="1" spans="1:16">
       <c r="A1" s="5" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -14295,15 +14456,15 @@
     </row>
     <row r="3" customHeight="1" spans="1:9">
       <c r="A3" s="11" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="13"/>
       <c r="D3" s="14" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F3" s="15"/>
       <c r="G3" s="15"/>
@@ -14313,163 +14474,163 @@
     <row r="4" customHeight="1" spans="1:9">
       <c r="A4" s="17"/>
       <c r="B4" s="18" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:9">
       <c r="A5" s="17"/>
       <c r="B5" s="18" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:9">
       <c r="A6" s="17"/>
       <c r="B6" s="18" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:9">
       <c r="A7" s="17"/>
       <c r="B7" s="18" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:9">
       <c r="A8" s="17"/>
       <c r="B8" s="18" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:9">
       <c r="A9" s="17"/>
       <c r="B9" s="18" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:9">
@@ -14477,25 +14638,25 @@
       <c r="B10" s="20"/>
       <c r="C10" s="21"/>
       <c r="D10" s="22" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="24"/>
       <c r="G10" s="24"/>
       <c r="H10" s="24"/>
-      <c r="I10" s="27"/>
+      <c r="I10" s="28"/>
     </row>
     <row r="11" customHeight="1" spans="1:9">
       <c r="A11" s="11" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="13"/>
       <c r="D11" s="14" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
@@ -14505,163 +14666,163 @@
     <row r="12" customHeight="1" spans="1:9">
       <c r="A12" s="17"/>
       <c r="B12" s="18" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:9">
       <c r="A13" s="17"/>
       <c r="B13" s="18" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:9">
       <c r="A14" s="17"/>
       <c r="B14" s="18" t="s">
-        <v>332</v>
+        <v>378</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:9">
       <c r="A15" s="17"/>
       <c r="B15" s="18" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:9">
       <c r="A16" s="17"/>
       <c r="B16" s="18" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>354</v>
-      </c>
-      <c r="I16" s="28" t="s">
-        <v>387</v>
+        <v>356</v>
+      </c>
+      <c r="I16" s="29" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:9">
       <c r="A17" s="17"/>
       <c r="B17" s="18" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:9">
@@ -14669,105 +14830,205 @@
       <c r="B18" s="20"/>
       <c r="C18" s="21"/>
       <c r="D18" s="22" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E18" s="23"/>
       <c r="F18" s="24"/>
       <c r="G18" s="24"/>
       <c r="H18" s="24"/>
-      <c r="I18" s="27"/>
+      <c r="I18" s="28"/>
     </row>
     <row r="19" customHeight="1" spans="1:9">
       <c r="A19" s="11" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B19" s="12"/>
       <c r="C19" s="13"/>
-      <c r="D19" s="14"/>
+      <c r="D19" s="14" t="s">
+        <v>396</v>
+      </c>
       <c r="E19" s="14"/>
-      <c r="F19" s="25"/>
+      <c r="F19" s="25" t="s">
+        <v>317</v>
+      </c>
       <c r="G19" s="25"/>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
     </row>
     <row r="20" customHeight="1" spans="1:9">
       <c r="A20" s="17"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
+      <c r="B20" s="27" t="s">
+        <v>373</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>372</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>323</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>398</v>
+      </c>
     </row>
     <row r="21" customHeight="1" spans="1:9">
       <c r="A21" s="17"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
+      <c r="B21" s="18" t="s">
+        <v>322</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>320</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>374</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>377</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>321</v>
+      </c>
     </row>
     <row r="22" customHeight="1" spans="1:9">
       <c r="A22" s="17"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
+      <c r="B22" s="18" t="s">
+        <v>383</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>334</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>380</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>339</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="23" customHeight="1" spans="1:9">
       <c r="A23" s="17"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
+      <c r="B23" s="18" t="s">
+        <v>342</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>386</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>382</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>385</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>388</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>381</v>
+      </c>
     </row>
     <row r="24" customHeight="1" spans="1:9">
       <c r="A24" s="17"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="28"/>
+      <c r="B24" s="18" t="s">
+        <v>390</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>350</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>361</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>355</v>
+      </c>
+      <c r="I24" s="29" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="25" customHeight="1" spans="1:9">
       <c r="A25" s="17"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
+      <c r="B25" s="18" t="s">
+        <v>391</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>365</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="G25" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>358</v>
+      </c>
+      <c r="I25" s="16" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="26" customHeight="1" spans="1:9">
       <c r="A26" s="19"/>
       <c r="B26" s="20"/>
       <c r="C26" s="21"/>
       <c r="D26" s="22" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="E26" s="23"/>
       <c r="F26" s="24"/>
       <c r="G26" s="24"/>
       <c r="H26" s="24"/>
-      <c r="I26" s="27"/>
+      <c r="I26" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -14956,7 +15217,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B15">
         <v>3.5</v>
@@ -14967,7 +15228,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="B16">
         <v>3.75</v>
@@ -14978,7 +15239,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="B17">
         <v>4</v>
@@ -14989,7 +15250,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="B18">
         <v>4.25</v>
@@ -15000,7 +15261,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="B19">
         <v>4.5</v>
@@ -15011,7 +15272,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="B20">
         <v>4.75</v>
@@ -15022,7 +15283,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="B21">
         <v>5</v>
@@ -15033,7 +15294,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="B22">
         <v>5.25</v>
@@ -15044,7 +15305,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="B23">
         <v>5.5</v>
@@ -15055,7 +15316,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="B24">
         <v>5.75</v>
@@ -15066,7 +15327,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="B25">
         <v>6</v>
@@ -15093,7 +15354,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="B28">
         <v>6.75</v>
@@ -15101,7 +15362,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="B29">
         <v>7</v>
@@ -15109,7 +15370,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="B30">
         <v>7.25</v>
@@ -15117,7 +15378,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="B31">
         <v>7.5</v>
@@ -15125,7 +15386,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="B32">
         <v>7.75</v>
@@ -15133,7 +15394,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="B33">
         <v>8</v>
@@ -15141,7 +15402,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="B34">
         <v>8.25</v>
@@ -15149,7 +15410,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="B35">
         <v>8.5</v>
@@ -15157,7 +15418,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="B36">
         <v>8.75</v>
@@ -15165,7 +15426,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="B37">
         <v>9</v>
@@ -15173,7 +15434,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="B38">
         <v>9.25</v>
@@ -15181,7 +15442,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="B39">
         <v>9.5</v>
@@ -15189,7 +15450,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="B40">
         <v>9.75</v>
@@ -15197,7 +15458,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="B41">
         <v>10</v>
@@ -15205,7 +15466,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="B42">
         <v>11</v>
@@ -15213,7 +15474,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="B43">
         <v>12</v>
@@ -15221,7 +15482,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="B44">
         <v>13</v>
@@ -15229,7 +15490,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="B45">
         <v>14</v>
@@ -15237,7 +15498,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="B46">
         <v>15</v>
@@ -15245,7 +15506,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="B47">
         <v>16</v>
@@ -15253,7 +15514,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="B48">
         <v>17</v>
@@ -15261,7 +15522,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="B49">
         <v>18</v>
@@ -15269,7 +15530,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="B50">
         <v>19</v>
@@ -15277,7 +15538,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="B51">
         <v>20</v>
@@ -15285,7 +15546,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="B52">
         <v>21</v>
@@ -15293,7 +15554,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="B53">
         <v>22</v>
@@ -15301,7 +15562,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="B54">
         <v>23</v>
@@ -15309,7 +15570,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="B55">
         <v>24</v>
@@ -15317,7 +15578,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="B56">
         <v>25</v>
@@ -15325,7 +15586,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="B57">
         <v>26</v>
@@ -15333,7 +15594,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="B58">
         <v>27</v>
@@ -15341,7 +15602,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="B59">
         <v>28</v>
@@ -15349,7 +15610,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="B60">
         <v>29</v>
@@ -15357,7 +15618,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="B61">
         <v>30</v>
@@ -15365,7 +15626,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="B62" t="s">
         <v>5</v>
@@ -15373,117 +15634,117 @@
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="1" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="1" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
     </row>
     <row r="86" spans="1:1">
@@ -15493,7 +15754,7 @@
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -16903,10 +17164,10 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="15.5" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="15.4181818181818" style="60" customWidth="1"/>
-    <col min="2" max="2" width="8.72727272727273" style="62"/>
-    <col min="3" max="3" width="10.4272727272727" style="29" customWidth="1"/>
-    <col min="4" max="4" width="10.4272727272727" style="30" customWidth="1"/>
+    <col min="1" max="1" width="15.4181818181818" style="61" customWidth="1"/>
+    <col min="2" max="2" width="8.72727272727273" style="63"/>
+    <col min="3" max="3" width="10.4272727272727" style="30" customWidth="1"/>
+    <col min="4" max="4" width="10.4272727272727" style="31" customWidth="1"/>
     <col min="5" max="5" width="102.927272727273" style="92" customWidth="1"/>
   </cols>
   <sheetData>
@@ -16928,16 +17189,16 @@
       </c>
     </row>
     <row r="2" ht="217" spans="1:5">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="61" t="s">
         <v>206</v>
       </c>
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="63" t="s">
         <v>157</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="62" t="s">
         <v>207</v>
       </c>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="41" t="s">
         <v>26</v>
       </c>
       <c r="E2" s="98" t="s">
@@ -16945,16 +17206,16 @@
       </c>
     </row>
     <row r="3" ht="356.5" spans="1:5">
-      <c r="A3" s="60" t="s">
+      <c r="A3" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="63" t="s">
         <v>209</v>
       </c>
-      <c r="C3" s="61" t="s">
+      <c r="C3" s="62" t="s">
         <v>210</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="41" t="s">
         <v>26</v>
       </c>
       <c r="E3" s="98" t="s">
@@ -16962,16 +17223,16 @@
       </c>
     </row>
     <row r="4" ht="108.5" spans="1:5">
-      <c r="A4" s="60" t="s">
+      <c r="A4" s="61" t="s">
         <v>212</v>
       </c>
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="63" t="s">
         <v>213</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="30" t="s">
         <v>214</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="31" t="s">
         <v>26</v>
       </c>
       <c r="E4" s="98" t="s">
@@ -16998,539 +17259,550 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="5.17272727272727" style="65" customWidth="1"/>
-    <col min="2" max="2" width="8.72727272727273" style="66"/>
-    <col min="3" max="3" width="7.55454545454545" style="67" customWidth="1"/>
-    <col min="4" max="4" width="8.72727272727273" style="68"/>
-    <col min="5" max="5" width="77.2727272727273" style="69" customWidth="1"/>
-    <col min="6" max="16384" width="8.72727272727273" style="70"/>
+    <col min="1" max="1" width="5.17272727272727" style="66" customWidth="1"/>
+    <col min="2" max="2" width="8.72727272727273" style="67"/>
+    <col min="3" max="3" width="7.55454545454545" style="68" customWidth="1"/>
+    <col min="4" max="4" width="8.72727272727273" style="69"/>
+    <col min="5" max="5" width="77.2727272727273" style="70" customWidth="1"/>
+    <col min="6" max="16384" width="8.72727272727273" style="71"/>
   </cols>
   <sheetData>
-    <row r="1" s="64" customFormat="1" spans="1:5">
-      <c r="A1" s="71" t="s">
+    <row r="1" s="65" customFormat="1" spans="1:5">
+      <c r="A1" s="72" t="s">
         <v>216</v>
       </c>
-      <c r="B1" s="72" t="s">
+      <c r="B1" s="73" t="s">
         <v>217</v>
       </c>
-      <c r="C1" s="73" t="s">
+      <c r="C1" s="74" t="s">
         <v>218</v>
       </c>
-      <c r="D1" s="74"/>
-      <c r="E1" s="75" t="s">
+      <c r="D1" s="75"/>
+      <c r="E1" s="76" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="2" ht="409" customHeight="1" spans="1:5">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="78" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="79" t="s">
         <v>220</v>
       </c>
-      <c r="D2" s="68" t="s">
+      <c r="D2" s="69" t="s">
         <v>221</v>
       </c>
-      <c r="E2" s="69" t="s">
+      <c r="E2" s="70" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="3" ht="56" spans="1:5">
-      <c r="A3" s="79"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="68" t="s">
+      <c r="A3" s="80"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="69" t="s">
         <v>223</v>
       </c>
-      <c r="E3" s="69" t="s">
+      <c r="E3" s="70" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="79"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="81"/>
-      <c r="D4" s="68" t="s">
+      <c r="A4" s="80"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="69" t="s">
         <v>225</v>
       </c>
-      <c r="E4" s="69" t="s">
+      <c r="E4" s="70" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="5" ht="56" spans="1:5">
-      <c r="A5" s="79"/>
-      <c r="B5" s="80"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="68" t="s">
+      <c r="A5" s="80"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="69" t="s">
         <v>227</v>
       </c>
-      <c r="E5" s="69" t="s">
+      <c r="E5" s="70" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="6" ht="210" spans="1:5">
-      <c r="A6" s="79"/>
-      <c r="B6" s="80"/>
-      <c r="C6" s="78" t="s">
+    <row r="6" ht="238" spans="1:5">
+      <c r="A6" s="80"/>
+      <c r="B6" s="81"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="69" t="s">
         <v>229</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="E6" s="70" t="s">
         <v>230</v>
       </c>
-      <c r="E6" s="69" t="s">
+    </row>
+    <row r="7" ht="210" spans="1:5">
+      <c r="A7" s="80"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="79" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="7" ht="56" spans="1:5">
-      <c r="A7" s="79"/>
-      <c r="B7" s="80"/>
-      <c r="C7" s="81"/>
-      <c r="D7" s="68" t="s">
+      <c r="D7" s="69" t="s">
         <v>232</v>
       </c>
-      <c r="E7" s="69" t="s">
+      <c r="E7" s="70" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="8" ht="84" spans="1:5">
-      <c r="A8" s="79"/>
-      <c r="B8" s="80"/>
-      <c r="C8" s="81"/>
-      <c r="D8" s="68" t="s">
+    <row r="8" ht="56" spans="1:5">
+      <c r="A8" s="80"/>
+      <c r="B8" s="81"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="69" t="s">
         <v>234</v>
       </c>
-      <c r="E8" s="69" t="s">
+      <c r="E8" s="70" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="9" ht="28" spans="1:5">
-      <c r="A9" s="79"/>
-      <c r="B9" s="80"/>
-      <c r="C9" s="81"/>
-      <c r="D9" s="68" t="s">
+    <row r="9" ht="84" spans="1:5">
+      <c r="A9" s="80"/>
+      <c r="B9" s="81"/>
+      <c r="C9" s="82"/>
+      <c r="D9" s="69" t="s">
         <v>236</v>
       </c>
-      <c r="E9" s="69" t="s">
+      <c r="E9" s="70" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="79"/>
-      <c r="B10" s="80"/>
+    <row r="10" ht="28" spans="1:5">
+      <c r="A10" s="80"/>
+      <c r="B10" s="81"/>
       <c r="C10" s="82"/>
-      <c r="D10" s="68" t="s">
+      <c r="D10" s="69" t="s">
         <v>238</v>
       </c>
-      <c r="E10" s="69" t="s">
+      <c r="E10" s="70" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="11" ht="154" spans="1:5">
-      <c r="A11" s="79"/>
-      <c r="B11" s="80"/>
-      <c r="C11" s="83"/>
-      <c r="D11" s="84" t="s">
+    <row r="11" spans="1:5">
+      <c r="A11" s="80"/>
+      <c r="B11" s="81"/>
+      <c r="C11" s="84"/>
+      <c r="D11" s="69" t="s">
         <v>240</v>
       </c>
-      <c r="E11" s="69" t="s">
+      <c r="E11" s="70" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="12" ht="56" spans="1:5">
-      <c r="A12" s="79"/>
-      <c r="B12" s="80"/>
-      <c r="C12" s="85" t="s">
+    <row r="12" ht="154" spans="1:5">
+      <c r="A12" s="80"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="69" t="s">
         <v>242</v>
       </c>
-      <c r="D12" s="74"/>
-      <c r="E12" s="69" t="s">
+      <c r="E12" s="70" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="13" ht="84" spans="1:5">
-      <c r="A13" s="79"/>
-      <c r="B13" s="80"/>
+    <row r="13" ht="56" spans="1:5">
+      <c r="A13" s="80"/>
+      <c r="B13" s="81"/>
       <c r="C13" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="D13" s="74"/>
-      <c r="E13" s="69" t="s">
+      <c r="D13" s="75"/>
+      <c r="E13" s="70" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="14" ht="28" spans="1:5">
-      <c r="A14" s="79"/>
-      <c r="B14" s="80"/>
+    <row r="14" ht="84" spans="1:5">
+      <c r="A14" s="80"/>
+      <c r="B14" s="81"/>
       <c r="C14" s="85" t="s">
         <v>246</v>
       </c>
-      <c r="D14" s="74"/>
-      <c r="E14" s="69" t="s">
+      <c r="D14" s="75"/>
+      <c r="E14" s="70" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="79"/>
-      <c r="B15" s="80"/>
+    <row r="15" ht="28" spans="1:5">
+      <c r="A15" s="80"/>
+      <c r="B15" s="81"/>
       <c r="C15" s="85" t="s">
         <v>248</v>
       </c>
-      <c r="D15" s="74"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="70" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="79"/>
-      <c r="B16" s="80"/>
+      <c r="A16" s="80"/>
+      <c r="B16" s="81"/>
       <c r="C16" s="85" t="s">
-        <v>249</v>
-      </c>
-      <c r="D16" s="74"/>
+        <v>250</v>
+      </c>
+      <c r="D16" s="75"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="79"/>
-      <c r="B17" s="80"/>
-      <c r="C17" s="78" t="s">
-        <v>250</v>
-      </c>
-      <c r="D17" s="68" t="s">
+      <c r="A17" s="80"/>
+      <c r="B17" s="81"/>
+      <c r="C17" s="85" t="s">
         <v>251</v>
       </c>
+      <c r="D17" s="75"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="79"/>
-      <c r="B18" s="80"/>
-      <c r="C18" s="82"/>
-      <c r="D18" s="68" t="s">
+      <c r="A18" s="80"/>
+      <c r="B18" s="81"/>
+      <c r="C18" s="79" t="s">
         <v>252</v>
       </c>
+      <c r="D18" s="69" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="79"/>
-      <c r="B19" s="80"/>
-      <c r="C19" s="85" t="s">
-        <v>253</v>
-      </c>
-      <c r="D19" s="74"/>
+      <c r="A19" s="80"/>
+      <c r="B19" s="81"/>
+      <c r="C19" s="84"/>
+      <c r="D19" s="69" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="86"/>
-      <c r="B20" s="87"/>
+      <c r="A20" s="80"/>
+      <c r="B20" s="81"/>
       <c r="C20" s="85" t="s">
-        <v>254</v>
-      </c>
-      <c r="D20" s="74"/>
+        <v>255</v>
+      </c>
+      <c r="D20" s="75"/>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="76" t="s">
+      <c r="A21" s="86"/>
+      <c r="B21" s="87"/>
+      <c r="C21" s="85" t="s">
+        <v>256</v>
+      </c>
+      <c r="D21" s="75"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="77" t="s">
+      <c r="B22" s="78" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="78" t="s">
+      <c r="C22" s="79" t="s">
         <v>220</v>
       </c>
-      <c r="D21" s="68" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="86"/>
-      <c r="B22" s="87"/>
-      <c r="C22" s="82"/>
-      <c r="D22" s="68" t="s">
-        <v>256</v>
+      <c r="D22" s="69" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="76" t="s">
+      <c r="A23" s="86"/>
+      <c r="B23" s="87"/>
+      <c r="C23" s="84"/>
+      <c r="D23" s="69" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="77" t="s">
+      <c r="B24" s="78" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="78" t="s">
+      <c r="C24" s="79" t="s">
         <v>220</v>
       </c>
-      <c r="D23" s="68" t="s">
+      <c r="D24" s="69" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="79"/>
-      <c r="B24" s="80"/>
-      <c r="C24" s="81"/>
-      <c r="D24" s="68" t="s">
+    <row r="25" spans="1:4">
+      <c r="A25" s="80"/>
+      <c r="B25" s="81"/>
+      <c r="C25" s="82"/>
+      <c r="D25" s="69" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="80"/>
+      <c r="B26" s="81"/>
+      <c r="C26" s="82"/>
+      <c r="D26" s="69" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="79"/>
-      <c r="B25" s="80"/>
-      <c r="C25" s="81"/>
-      <c r="D25" s="68" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="79"/>
-      <c r="B26" s="80"/>
-      <c r="C26" s="82"/>
-      <c r="D26" s="68" t="s">
-        <v>258</v>
-      </c>
-    </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="79"/>
-      <c r="B27" s="87"/>
-      <c r="C27" s="85" t="s">
-        <v>229</v>
-      </c>
-      <c r="D27" s="88"/>
+      <c r="A27" s="80"/>
+      <c r="B27" s="81"/>
+      <c r="C27" s="84"/>
+      <c r="D27" s="69" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="79"/>
-      <c r="B28" s="77" t="s">
-        <v>259</v>
-      </c>
+      <c r="A28" s="80"/>
+      <c r="B28" s="87"/>
       <c r="C28" s="85" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D28" s="88"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="86"/>
-      <c r="B29" s="87"/>
+      <c r="A29" s="80"/>
+      <c r="B29" s="78" t="s">
+        <v>261</v>
+      </c>
       <c r="C29" s="85" t="s">
+        <v>231</v>
+      </c>
+      <c r="D29" s="88"/>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="86"/>
+      <c r="B30" s="87"/>
+      <c r="C30" s="85" t="s">
         <v>220</v>
       </c>
-      <c r="D29" s="88"/>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="76" t="s">
+      <c r="D30" s="88"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="B30" s="89" t="s">
-        <v>260</v>
-      </c>
-      <c r="C30" s="90"/>
-      <c r="D30" s="91"/>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="86"/>
       <c r="B31" s="89" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C31" s="90"/>
       <c r="D31" s="91"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="65" t="s">
-        <v>6</v>
-      </c>
+      <c r="A32" s="86"/>
       <c r="B32" s="89" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C32" s="90"/>
       <c r="D32" s="91"/>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="76" t="s">
+      <c r="A33" s="66" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="89" t="s">
+        <v>264</v>
+      </c>
+      <c r="C33" s="90"/>
+      <c r="D33" s="91"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="B33" s="77" t="s">
-        <v>263</v>
-      </c>
-      <c r="C33" s="78" t="s">
+      <c r="B34" s="78" t="s">
+        <v>265</v>
+      </c>
+      <c r="C34" s="79" t="s">
         <v>220</v>
       </c>
-      <c r="D33" s="68" t="s">
+      <c r="D34" s="69" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="80"/>
+      <c r="B35" s="81"/>
+      <c r="C35" s="84"/>
+      <c r="D35" s="69" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="80"/>
+      <c r="B36" s="81"/>
+      <c r="C36" s="85" t="s">
+        <v>268</v>
+      </c>
+      <c r="D36" s="88"/>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="86"/>
+      <c r="B37" s="87"/>
+      <c r="C37" s="85" t="s">
+        <v>231</v>
+      </c>
+      <c r="D37" s="88"/>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="77" t="s">
+        <v>16</v>
+      </c>
+      <c r="B38" s="78" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="79"/>
-      <c r="B34" s="80"/>
-      <c r="C34" s="82"/>
-      <c r="D34" s="68" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="79"/>
-      <c r="B35" s="80"/>
-      <c r="C35" s="85" t="s">
-        <v>266</v>
-      </c>
-      <c r="D35" s="88"/>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="86"/>
-      <c r="B36" s="87"/>
-      <c r="C36" s="85" t="s">
-        <v>229</v>
-      </c>
-      <c r="D36" s="88"/>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="76" t="s">
-        <v>16</v>
-      </c>
-      <c r="B37" s="77" t="s">
-        <v>262</v>
-      </c>
-      <c r="C37" s="85" t="s">
-        <v>267</v>
-      </c>
-      <c r="D37" s="88"/>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="79"/>
-      <c r="B38" s="80"/>
-      <c r="C38" s="78" t="s">
+      <c r="C38" s="85" t="s">
+        <v>269</v>
+      </c>
+      <c r="D38" s="88"/>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="80"/>
+      <c r="B39" s="81"/>
+      <c r="C39" s="79" t="s">
         <v>220</v>
       </c>
-      <c r="D38" s="68" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="79"/>
-      <c r="B39" s="87"/>
-      <c r="C39" s="82"/>
-      <c r="D39" s="68" t="s">
-        <v>269</v>
+      <c r="D39" s="69" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="86"/>
-      <c r="B40" s="89" t="s">
-        <v>270</v>
-      </c>
-      <c r="C40" s="90"/>
-      <c r="D40" s="91"/>
+      <c r="A40" s="80"/>
+      <c r="B40" s="87"/>
+      <c r="C40" s="84"/>
+      <c r="D40" s="69" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="76" t="s">
+      <c r="A41" s="86"/>
+      <c r="B41" s="89" t="s">
+        <v>272</v>
+      </c>
+      <c r="C41" s="90"/>
+      <c r="D41" s="91"/>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="B41" s="77" t="s">
+      <c r="B42" s="78" t="s">
+        <v>273</v>
+      </c>
+      <c r="C42" s="79" t="s">
+        <v>220</v>
+      </c>
+      <c r="D42" s="69" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="80"/>
+      <c r="B43" s="81"/>
+      <c r="C43" s="82"/>
+      <c r="D43" s="69" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="86"/>
+      <c r="B44" s="87"/>
+      <c r="C44" s="84"/>
+      <c r="D44" s="69" t="s">
         <v>271</v>
       </c>
-      <c r="C41" s="78" t="s">
-        <v>220</v>
-      </c>
-      <c r="D41" s="68" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="79"/>
-      <c r="B42" s="80"/>
-      <c r="C42" s="81"/>
-      <c r="D42" s="68" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="86"/>
-      <c r="B43" s="87"/>
-      <c r="C43" s="82"/>
-      <c r="D43" s="68" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="65" t="s">
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="66" t="s">
         <v>9</v>
-      </c>
-      <c r="B44" s="89"/>
-      <c r="C44" s="90"/>
-      <c r="D44" s="91"/>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="76" t="s">
-        <v>17</v>
       </c>
       <c r="B45" s="89"/>
       <c r="C45" s="90"/>
       <c r="D45" s="91"/>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="86"/>
+      <c r="A46" s="77" t="s">
+        <v>17</v>
+      </c>
       <c r="B46" s="89"/>
       <c r="C46" s="90"/>
       <c r="D46" s="91"/>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="65" t="s">
-        <v>12</v>
-      </c>
+      <c r="A47" s="86"/>
       <c r="B47" s="89"/>
       <c r="C47" s="90"/>
       <c r="D47" s="91"/>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="65" t="s">
-        <v>10</v>
+      <c r="A48" s="66" t="s">
+        <v>12</v>
       </c>
       <c r="B48" s="89"/>
       <c r="C48" s="90"/>
       <c r="D48" s="91"/>
     </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="B49" s="89"/>
+      <c r="C49" s="90"/>
+      <c r="D49" s="91"/>
+    </row>
   </sheetData>
   <mergeCells count="46">
     <mergeCell ref="C1:D1"/>
-    <mergeCell ref="C12:D12"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="C29:D29"/>
-    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B32:D32"/>
-    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="C37:D37"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="B41:D41"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B46:D46"/>
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="B48:D48"/>
-    <mergeCell ref="A2:A20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A23:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A33:A36"/>
-    <mergeCell ref="A37:A40"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B2:B20"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="B23:B27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="B33:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B41:B43"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="A2:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B2:B21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="B38:B40"/>
+    <mergeCell ref="B42:B44"/>
     <mergeCell ref="C2:C5"/>
-    <mergeCell ref="C6:C10"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="C23:C26"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="C7:C11"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="C24:C27"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C42:C44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -17543,349 +17815,349 @@
   <dimension ref="A1:G52"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="8.72727272727273" style="49"/>
-    <col min="2" max="2" width="61.8090909090909" style="50" customWidth="1"/>
-    <col min="3" max="3" width="61.8090909090909" style="51" customWidth="1"/>
-    <col min="4" max="4" width="61.8090909090909" style="52" customWidth="1"/>
-    <col min="5" max="5" width="61.8090909090909" style="53" customWidth="1"/>
-    <col min="6" max="6" width="61.8090909090909" style="54" customWidth="1"/>
-    <col min="7" max="7" width="61.8090909090909" style="55" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="56"/>
+    <col min="1" max="1" width="8.72727272727273" style="50"/>
+    <col min="2" max="2" width="61.8090909090909" style="51" customWidth="1"/>
+    <col min="3" max="3" width="61.8090909090909" style="52" customWidth="1"/>
+    <col min="4" max="4" width="61.8090909090909" style="53" customWidth="1"/>
+    <col min="5" max="5" width="61.8090909090909" style="54" customWidth="1"/>
+    <col min="6" max="6" width="61.8090909090909" style="55" customWidth="1"/>
+    <col min="7" max="7" width="61.8090909090909" style="56" customWidth="1"/>
+    <col min="8" max="16384" width="8.72727272727273" style="57"/>
   </cols>
   <sheetData>
-    <row r="1" s="48" customFormat="1" spans="1:7">
-      <c r="A1" s="57" t="s">
+    <row r="1" s="49" customFormat="1" spans="1:7">
+      <c r="A1" s="58" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="58" t="s">
+      <c r="C1" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="59" t="s">
+      <c r="D1" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="60" t="s">
+      <c r="E1" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="61" t="s">
+      <c r="F1" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="62" t="s">
+      <c r="G1" s="63" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" ht="70" spans="1:2">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="58" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="63" t="s">
-        <v>274</v>
+      <c r="B2" s="64" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="58" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="57" t="s">
+      <c r="A4" s="58" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="57" t="s">
+      <c r="A5" s="58" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="57" t="s">
+      <c r="A6" s="58" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="58" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="57" t="s">
+      <c r="A8" s="58" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="57" t="s">
+      <c r="A9" s="58" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="10" ht="42" spans="1:2">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="58" t="s">
         <v>132</v>
       </c>
-      <c r="B10" s="50" t="s">
-        <v>275</v>
+      <c r="B10" s="51" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="57" t="s">
+      <c r="A11" s="58" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="57" t="s">
+      <c r="A12" s="58" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="57" t="s">
+      <c r="A13" s="58" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="14" ht="42" spans="1:2">
-      <c r="A14" s="57" t="s">
+      <c r="A14" s="58" t="s">
         <v>139</v>
       </c>
-      <c r="B14" s="50" t="s">
-        <v>276</v>
+      <c r="B14" s="51" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="57" t="s">
+      <c r="A15" s="58" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="57" t="s">
+      <c r="A16" s="58" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="17" ht="28" spans="1:3">
-      <c r="A17" s="57" t="s">
+      <c r="A17" s="58" t="s">
         <v>143</v>
       </c>
-      <c r="C17" s="51" t="s">
-        <v>277</v>
+      <c r="C17" s="52" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="57" t="s">
+      <c r="A18" s="58" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="57" t="s">
+      <c r="A19" s="58" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="20" ht="70" spans="1:2">
-      <c r="A20" s="57" t="s">
+      <c r="A20" s="58" t="s">
         <v>146</v>
       </c>
-      <c r="B20" s="50" t="s">
-        <v>278</v>
+      <c r="B20" s="51" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="21" ht="252" spans="1:3">
-      <c r="A21" s="57" t="s">
+      <c r="A21" s="58" t="s">
         <v>147</v>
       </c>
-      <c r="B21" s="50" t="s">
-        <v>279</v>
-      </c>
-      <c r="C21" s="51" t="s">
-        <v>280</v>
+      <c r="B21" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="C21" s="52" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="57" t="s">
+      <c r="A22" s="58" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="23" ht="112" spans="1:2">
-      <c r="A23" s="57" t="s">
+      <c r="A23" s="58" t="s">
         <v>150</v>
       </c>
-      <c r="B23" s="50" t="s">
-        <v>281</v>
+      <c r="B23" s="51" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="24" ht="126" spans="1:3">
-      <c r="A24" s="57" t="s">
+      <c r="A24" s="58" t="s">
         <v>151</v>
       </c>
-      <c r="B24" s="50" t="s">
-        <v>282</v>
-      </c>
-      <c r="C24" s="51" t="s">
-        <v>283</v>
+      <c r="B24" s="51" t="s">
+        <v>284</v>
+      </c>
+      <c r="C24" s="52" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="57" t="s">
+      <c r="A25" s="58" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="57" t="s">
+      <c r="A26" s="58" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="27" ht="112" spans="1:3">
-      <c r="A27" s="57" t="s">
+      <c r="A27" s="58" t="s">
         <v>157</v>
       </c>
-      <c r="B27" s="50" t="s">
-        <v>284</v>
-      </c>
-      <c r="C27" s="51" t="s">
-        <v>285</v>
+      <c r="B27" s="51" t="s">
+        <v>286</v>
+      </c>
+      <c r="C27" s="52" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="28" ht="409" customHeight="1" spans="1:2">
-      <c r="A28" s="57" t="s">
+      <c r="A28" s="58" t="s">
         <v>159</v>
       </c>
-      <c r="B28" s="50" t="s">
-        <v>286</v>
+      <c r="B28" s="51" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="57" t="s">
+      <c r="A29" s="58" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="57" t="s">
+      <c r="A30" s="58" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="57" t="s">
+      <c r="A31" s="58" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="57" t="s">
+      <c r="A32" s="58" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="57" t="s">
+      <c r="A33" s="58" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="57" t="s">
+      <c r="A34" s="58" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="57" t="s">
+      <c r="A35" s="58" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="36" ht="56" spans="1:2">
-      <c r="A36" s="57" t="s">
+      <c r="A36" s="58" t="s">
         <v>172</v>
       </c>
-      <c r="B36" s="50" t="s">
-        <v>287</v>
+      <c r="B36" s="51" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="37" ht="28" spans="1:3">
-      <c r="A37" s="57" t="s">
+      <c r="A37" s="58" t="s">
         <v>174</v>
       </c>
-      <c r="C37" s="51" t="s">
-        <v>288</v>
+      <c r="C37" s="52" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="57" t="s">
+      <c r="A38" s="58" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="57" t="s">
+      <c r="A39" s="58" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="40" ht="28" spans="1:2">
-      <c r="A40" s="57" t="s">
+      <c r="A40" s="58" t="s">
         <v>180</v>
       </c>
-      <c r="B40" s="50" t="s">
-        <v>289</v>
+      <c r="B40" s="51" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="41" ht="112" spans="1:3">
-      <c r="A41" s="57" t="s">
+      <c r="A41" s="58" t="s">
         <v>182</v>
       </c>
-      <c r="C41" s="51" t="s">
-        <v>290</v>
+      <c r="C41" s="52" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="57" t="s">
+      <c r="A42" s="58" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="57" t="s">
+      <c r="A43" s="58" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="57" t="s">
+      <c r="A44" s="58" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="45" ht="387" spans="1:2">
-      <c r="A45" s="57" t="s">
+      <c r="A45" s="58" t="s">
         <v>188</v>
       </c>
-      <c r="B45" s="50" t="s">
-        <v>291</v>
+      <c r="B45" s="51" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="57" t="s">
+      <c r="A46" s="58" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="57" t="s">
+      <c r="A47" s="58" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="57" t="s">
+      <c r="A48" s="58" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="57" t="s">
+      <c r="A49" s="58" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="57" t="s">
+      <c r="A50" s="58" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="57" t="s">
+      <c r="A51" s="58" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="52" ht="224" spans="1:2">
-      <c r="A52" s="57" t="s">
+      <c r="A52" s="58" t="s">
         <v>199</v>
       </c>
-      <c r="B52" s="50" t="s">
-        <v>292</v>
+      <c r="B52" s="51" t="s">
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -17906,226 +18178,226 @@
   <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="6.58181818181818" style="32" customWidth="1"/>
-    <col min="2" max="2" width="12.4545454545455" style="32" customWidth="1"/>
-    <col min="3" max="16384" width="8.72727272727273" style="32"/>
+    <col min="1" max="1" width="6.58181818181818" style="33" customWidth="1"/>
+    <col min="2" max="2" width="12.4545454545455" style="33" customWidth="1"/>
+    <col min="3" max="16384" width="8.72727272727273" style="33"/>
   </cols>
   <sheetData>
-    <row r="1" s="29" customFormat="1" spans="1:8">
-      <c r="A1" s="33" t="s">
-        <v>293</v>
-      </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="29" t="s">
+    <row r="1" s="30" customFormat="1" spans="1:8">
+      <c r="A1" s="34" t="s">
+        <v>295</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="29" t="s">
+      <c r="H1" s="30" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" s="30" customFormat="1" spans="1:4">
-      <c r="A2" s="35" t="s">
-        <v>294</v>
-      </c>
-      <c r="B2" s="36" t="s">
-        <v>295</v>
-      </c>
-      <c r="C2" s="37" t="s">
+    <row r="2" s="31" customFormat="1" spans="1:4">
+      <c r="A2" s="36" t="s">
+        <v>296</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>297</v>
+      </c>
+      <c r="C2" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="D2" s="38"/>
-    </row>
-    <row r="3" s="30" customFormat="1" spans="1:4">
-      <c r="A3" s="39"/>
-      <c r="B3" s="36" t="s">
-        <v>296</v>
-      </c>
-      <c r="C3" s="37" t="s">
+      <c r="D2" s="39"/>
+    </row>
+    <row r="3" s="31" customFormat="1" spans="1:4">
+      <c r="A3" s="40"/>
+      <c r="B3" s="37" t="s">
+        <v>298</v>
+      </c>
+      <c r="C3" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="38"/>
-    </row>
-    <row r="4" s="30" customFormat="1" spans="1:4">
-      <c r="A4" s="39"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="37" t="s">
+      <c r="D3" s="39"/>
+    </row>
+    <row r="4" s="31" customFormat="1" spans="1:4">
+      <c r="A4" s="40"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="D4" s="38"/>
-    </row>
-    <row r="5" s="30" customFormat="1" spans="1:4">
-      <c r="A5" s="39"/>
-      <c r="B5" s="36" t="s">
-        <v>297</v>
-      </c>
-      <c r="C5" s="37" t="s">
+      <c r="D4" s="39"/>
+    </row>
+    <row r="5" s="31" customFormat="1" spans="1:4">
+      <c r="A5" s="40"/>
+      <c r="B5" s="37" t="s">
+        <v>299</v>
+      </c>
+      <c r="C5" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="D5" s="38"/>
-    </row>
-    <row r="6" s="30" customFormat="1" spans="1:4">
-      <c r="A6" s="39"/>
-      <c r="B6" s="36" t="s">
-        <v>298</v>
-      </c>
-      <c r="C6" s="40" t="s">
+      <c r="D5" s="39"/>
+    </row>
+    <row r="6" s="31" customFormat="1" spans="1:4">
+      <c r="A6" s="40"/>
+      <c r="B6" s="37" t="s">
+        <v>300</v>
+      </c>
+      <c r="C6" s="41" t="s">
         <v>127</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="31" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="7" s="30" customFormat="1" spans="1:4">
-      <c r="A7" s="39"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="40" t="s">
+    <row r="7" s="31" customFormat="1" spans="1:4">
+      <c r="A7" s="40"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="31" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="8" s="30" customFormat="1" spans="1:4">
-      <c r="A8" s="39"/>
-      <c r="B8" s="36" t="s">
-        <v>299</v>
-      </c>
-      <c r="C8" s="40" t="s">
+    <row r="8" s="31" customFormat="1" spans="1:4">
+      <c r="A8" s="40"/>
+      <c r="B8" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="C8" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="31" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="9" s="30" customFormat="1" spans="1:4">
-      <c r="A9" s="39"/>
-      <c r="B9" s="36" t="s">
-        <v>300</v>
-      </c>
-      <c r="C9" s="37" t="s">
+    <row r="9" s="31" customFormat="1" spans="1:4">
+      <c r="A9" s="40"/>
+      <c r="B9" s="37" t="s">
+        <v>302</v>
+      </c>
+      <c r="C9" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="D9" s="38"/>
-    </row>
-    <row r="10" s="30" customFormat="1" spans="1:4">
-      <c r="A10" s="39"/>
-      <c r="B10" s="36" t="s">
-        <v>301</v>
-      </c>
-      <c r="C10" s="37" t="s">
+      <c r="D9" s="39"/>
+    </row>
+    <row r="10" s="31" customFormat="1" spans="1:4">
+      <c r="A10" s="40"/>
+      <c r="B10" s="37" t="s">
+        <v>303</v>
+      </c>
+      <c r="C10" s="38" t="s">
         <v>142</v>
       </c>
-      <c r="D10" s="38"/>
-    </row>
-    <row r="11" s="30" customFormat="1" spans="1:4">
-      <c r="A11" s="41"/>
-      <c r="B11" s="36" t="s">
-        <v>302</v>
-      </c>
-      <c r="C11" s="37" t="s">
+      <c r="D10" s="39"/>
+    </row>
+    <row r="11" s="31" customFormat="1" spans="1:4">
+      <c r="A11" s="42"/>
+      <c r="B11" s="37" t="s">
+        <v>304</v>
+      </c>
+      <c r="C11" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="D11" s="38"/>
-    </row>
-    <row r="12" s="31" customFormat="1" spans="1:4">
-      <c r="A12" s="42" t="s">
-        <v>303</v>
-      </c>
-      <c r="B12" s="43" t="s">
-        <v>304</v>
-      </c>
-      <c r="C12" s="44" t="s">
+      <c r="D11" s="39"/>
+    </row>
+    <row r="12" s="32" customFormat="1" spans="1:4">
+      <c r="A12" s="43" t="s">
+        <v>305</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>306</v>
+      </c>
+      <c r="C12" s="45" t="s">
         <v>182</v>
       </c>
-      <c r="D12" s="45"/>
-    </row>
-    <row r="13" s="31" customFormat="1" spans="1:4">
-      <c r="A13" s="46"/>
-      <c r="B13" s="43"/>
-      <c r="C13" s="44" t="s">
+      <c r="D12" s="46"/>
+    </row>
+    <row r="13" s="32" customFormat="1" spans="1:4">
+      <c r="A13" s="47"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="45" t="s">
         <v>144</v>
       </c>
-      <c r="D13" s="45"/>
-    </row>
-    <row r="14" s="31" customFormat="1" spans="1:4">
-      <c r="A14" s="46"/>
-      <c r="B14" s="43" t="s">
-        <v>305</v>
-      </c>
-      <c r="C14" s="44" t="s">
-        <v>306</v>
-      </c>
-      <c r="D14" s="45"/>
-    </row>
-    <row r="15" s="31" customFormat="1" spans="1:4">
-      <c r="A15" s="46"/>
-      <c r="B15" s="43" t="s">
+      <c r="D13" s="46"/>
+    </row>
+    <row r="14" s="32" customFormat="1" spans="1:4">
+      <c r="A14" s="47"/>
+      <c r="B14" s="44" t="s">
         <v>307</v>
       </c>
-      <c r="C15" s="44" t="s">
+      <c r="C14" s="45" t="s">
+        <v>308</v>
+      </c>
+      <c r="D14" s="46"/>
+    </row>
+    <row r="15" s="32" customFormat="1" spans="1:4">
+      <c r="A15" s="47"/>
+      <c r="B15" s="44" t="s">
+        <v>309</v>
+      </c>
+      <c r="C15" s="45" t="s">
         <v>121</v>
       </c>
-      <c r="D15" s="45"/>
-    </row>
-    <row r="16" s="31" customFormat="1" spans="1:4">
-      <c r="A16" s="46"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="44" t="s">
+      <c r="D15" s="46"/>
+    </row>
+    <row r="16" s="32" customFormat="1" spans="1:4">
+      <c r="A16" s="47"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="D16" s="45"/>
-    </row>
-    <row r="17" s="31" customFormat="1" spans="1:4">
-      <c r="A17" s="46"/>
-      <c r="B17" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="C17" s="44" t="s">
+      <c r="D16" s="46"/>
+    </row>
+    <row r="17" s="32" customFormat="1" spans="1:4">
+      <c r="A17" s="47"/>
+      <c r="B17" s="44" t="s">
+        <v>310</v>
+      </c>
+      <c r="C17" s="45" t="s">
         <v>134</v>
       </c>
-      <c r="D17" s="45"/>
-    </row>
-    <row r="18" s="31" customFormat="1" spans="1:4">
-      <c r="A18" s="46"/>
-      <c r="B18" s="43" t="s">
-        <v>309</v>
-      </c>
-      <c r="C18" s="44" t="s">
+      <c r="D17" s="46"/>
+    </row>
+    <row r="18" s="32" customFormat="1" spans="1:4">
+      <c r="A18" s="47"/>
+      <c r="B18" s="44" t="s">
+        <v>311</v>
+      </c>
+      <c r="C18" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="D18" s="45"/>
-    </row>
-    <row r="19" s="31" customFormat="1" spans="1:4">
-      <c r="A19" s="46"/>
-      <c r="B19" s="43" t="s">
-        <v>310</v>
-      </c>
-      <c r="C19" s="44" t="s">
+      <c r="D18" s="46"/>
+    </row>
+    <row r="19" s="32" customFormat="1" spans="1:4">
+      <c r="A19" s="47"/>
+      <c r="B19" s="44" t="s">
+        <v>312</v>
+      </c>
+      <c r="C19" s="45" t="s">
         <v>178</v>
       </c>
-      <c r="D19" s="45"/>
-    </row>
-    <row r="20" s="31" customFormat="1" spans="1:4">
-      <c r="A20" s="47"/>
-      <c r="B20" s="43" t="s">
-        <v>311</v>
-      </c>
-      <c r="C20" s="44" t="s">
+      <c r="D19" s="46"/>
+    </row>
+    <row r="20" s="32" customFormat="1" spans="1:4">
+      <c r="A20" s="48"/>
+      <c r="B20" s="44" t="s">
+        <v>313</v>
+      </c>
+      <c r="C20" s="45" t="s">
         <v>180</v>
       </c>
-      <c r="D20" s="45"/>
+      <c r="D20" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="23">

--- a/c/9班资料.xlsx
+++ b/c/9班资料.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480"/>
+    <workbookView windowWidth="20750" windowHeight="10480" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="七下拖课" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="474">
   <si>
     <t>拖课统计表</t>
   </si>
@@ -780,7 +780,7 @@
 5.F+(不过关）
 6.F,F-(不过关，大量错误）
 7.无等级（不过关）
-不过关者需在下课/午托/放学时找刘必艳订正并重测，直至过关。
+不过关者需在下课/午托/放学时找刘必艳订正并重测，直至过关。七下时，刘必艳会写“CTMO”（come to my office），代表到办公室找她。
 过关者需将小测在错题旁订正1遍并在背面订正3遍（蓝笔）。
 一般刘必艳这样下达指令：
 Close your books and test.
@@ -937,13 +937,46 @@
     <t>讲评</t>
   </si>
   <si>
+    <t>数学老师会说：“作业拿出来。”然后打开展台，走到3、4组过道寻找作业。找到的作业会被他拿去投影（他会将名字折起来），拍照后归还。</t>
+  </si>
+  <si>
     <t>课件</t>
   </si>
   <si>
+    <t>数学老师的课件基本上是去网上找的，因此内容五花八门。</t>
+  </si>
+  <si>
+    <t>导学案</t>
+  </si>
+  <si>
+    <t>数学老师会说：“导学案拿出来。”并让大家做题。午托时可能会让大家做完某页，否则不要睡觉。</t>
+  </si>
+  <si>
+    <t>方翔曾发明“防伪标志”，但目前仅用过1次。
+班上有一个习俗：念小测满分名单时，大家会根据那个人在班上的地位用“哇”或“咦”起哄。如郑永泽、王淮、张雨希是“哇”，郑致辰、林芷琪、林奕扬是“咦”。</t>
+  </si>
+  <si>
     <t>课文</t>
   </si>
   <si>
+    <t>她讲课文时，会：
+1.播放课文朗诵音频（选）
+2.让大家齐读全文（选，到后面会出现只有几个人读的情况）
+3.讲解课文
+前两项操作主打一个浪费时间。</t>
+  </si>
+  <si>
+    <t>七上时，她讲评作业实则是让大家核对答案；七下时就会进行讲解。</t>
+  </si>
+  <si>
     <t>声音</t>
+  </si>
+  <si>
+    <t>方翔称自己从不使用小蜜蜂，且“自己的嗓门对面的楼的人都能听见”。她可能讲着讲着，突然就提高音调，把走神的人吓一跳。但平时的声音有催眠效果。</t>
+  </si>
+  <si>
+    <t>七上时，她批改校本/金牌只是看有没有写，有的话就打勾并写上“阅”，有时空一些题都没关系；七下时干脆让组长检查。
+方翔的周末固定作业是练字1张。</t>
   </si>
   <si>
     <t>郑××</t>
@@ -4032,19 +4065,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000033"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
+      <sz val="11"/>
+      <color rgb="FF000033"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -4057,6 +4085,11 @@
       <sz val="12"/>
       <color rgb="FFC0504D"/>
       <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -4871,7 +4904,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5388,12 +5421,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -13167,10 +13194,10 @@
       <c r="AA21" s="166"/>
       <c r="AB21" s="165"/>
       <c r="AC21" s="166"/>
-      <c r="AD21" s="172" t="s">
+      <c r="AD21" s="165" t="s">
         <v>2</v>
       </c>
-      <c r="AE21" s="173">
+      <c r="AE21" s="166">
         <v>4.5</v>
       </c>
       <c r="AF21" s="165"/>
@@ -14606,14 +14633,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CG5 CQ5 CS5 CI8 CO8 CS8 CU8 CI9 CU9 CG10 CI10 CQ10 CU10 CG11 CI11 CQ11 CU11 CG12 CI12 CO12 CQ12 CS12 CU12 CG13 CI13 CO13 CQ13 CG14 CI14 CO14 CQ14 CG15 CQ15 CG16 CQ16 CU16 CG17 CU17 CG18 CI18 CU18 CO20 CO21 C3:C21 E3:E21 G3:G21 I3:I21 K3:K21 M3:M21 O3:O21 Q3:Q21 S3:S21 U3:U21 W3:W21 Y3:Y21 AA3:AA21 AC3:AC21 AE3:AE21 AG3:AG21 AI3:AI21 AK3:AK21 AM3:AM21 AO3:AO21 AQ3:AQ21 AS3:AS21 AU3:AU21 AW3:AW21 AY3:AY21 BA3:BA21 BC3:BC21 BE3:BE21 BG3:BG21 BI3:BI21 BK3:BK21 BM3:BM21 BO3:BO21 BQ3:BQ21 BS3:BS21 BU3:BU21 BW3:BW21 BY3:BY21 CA3:CA21 CC3:CC21 CE3:CE21 CG3:CG4 CG6:CG9 CG19:CG21 CI3:CI7 CI15:CI17 CI19:CI21 CK3:CK21 CM3:CM21 CO3:CO7 CO9:CO11 CO15:CO19 CQ3:CQ4 CQ6:CQ9 CQ17:CQ21 CS3:CS4 CS6:CS7 CS9:CS11 CS13:CS21 CU3:CU7 CU13:CU15 CU19:CU21 CW3:CW21 CY3:CY21 DA3:DA21 DC3:DC21 DE3:DE21 DG3:DG21 DI3:DI21 DK3:DK21 DM3:DM21 DO3:DO21 DQ3:DQ21 DS3:DS21 DU3:DU21 DW3:DW21 DY3:DY21 EA3:EA21 EC3:EC21 EE3:EE21 EG3:EG21 EI3:EI21 EK3:EK21 EM3:EM21 EO3:EO21 EQ3:EQ21 ES3:ES21 EU3:EU21 EW3:EW21 EY3:EY21 FA3:FA21 FC3:FC21 FE3:FE21 FG3:FG21 FI3:FI21 FK3:FK21 FM3:FM21 FO3:FO21 FQ3:FQ21 FS3:FS21 FU3:FU21 FW3:FW21 FY3:FY21 GA3:GA21 GC3:GC21 GE3:GE21 GG3:GG21 GI3:GI21 GK3:GK21 GM3:GM21 GO3:GO21 GQ3:GQ21 GS3:GS21 GU3:GU21 GW3:GW21 GY3:GY21 HA3:HA21 HC3:HC21 HE3:HE21 HG3:HG21 HI3:HI21 HK3:HK21 HM3:HM21 HO3:HO21 HQ3:HQ21 HS3:HS21 HU3:HU21 HW3:HW21 HY3:HY21 IA3:IA21 IC3:IC21 IE3:IE21 IG3:IG21 II3:II21 IK3:IK21 IM3:IM21 IO3:IO21 IQ3:IQ21 IS3:IS21 IU3:IU21 IW3:IW21 IY3:IY21 JA3:JA21 JC3:JC21 JE3:JE21 JG3:JG21 JI3:JI21 JK3:JK21 JM3:JM21 JO3:JO21">
-      <formula1>数据!$B$1:$B$62</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C22 E22 G22 I22 K22 M22 O22 Q22 S22 U22 W22 Y22 AA22 AC22 AE22 AG22 AI22 AK22 AM22 AO22 AQ22 AS22 AU22 AW22 AY22 BA22 BC22 BE22 BG22 BI22 BK22 BM22 BO22 BQ22 BS22 BU22 BW22 BY22 CA22 CC22 CE22 CG22 CI22 CK22 CM22 CO22 CQ22 CS22 CU22 CW22 CY22 DA22 DC22 DE22 DG22 DI22 DK22 DM22 DO22 DQ22 DS22 DU22 DW22 DY22 EA22 EC22 EE22 EG22 EI22 EK22 EM22 EO22 EQ22 ES22 EU22 EW22 EY22 FA22 FC22 FE22 FG22 FI22 FK22 FM22 FO22 FQ22 FS22 FU22 FW22 FY22 GA22 GC22 GE22 GG22 GI22 GK22 GM22 GO22 GQ22 GS22 GU22 GW22 GY22 HA22 HC22 HE22 HG22 HI22 HK22 HM22 HO22 HQ22 HS22 HU22 HW22 HY22 IA22 IC22 IE22 IG22 II22 IK22 IM22 IO22 IQ22 IS22 IU22 IW22 IY22 JA22 JC22 JE22 JG22 JI22 JK22 JM22 JO22">
+      <formula1>数据!$C$1:$C$25</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CP21 CR21 CT21 B3:B21 D3:D21 F3:F21 H3:H21 J3:J21 L3:L21 N3:N21 P3:P21 R3:R21 T3:T21 V3:V21 X3:X21 Z3:Z21 AB3:AB21 AD3:AD21 AF3:AF21 AH3:AH21 AJ3:AJ21 AL3:AL21 AN3:AN21 AP3:AP21 AR3:AR21 AT3:AT21 AV3:AV21 AX3:AX21 AZ3:AZ21 BB3:BB21 BD3:BD21 BF3:BF21 BH3:BH21 BJ3:BJ21 BL3:BL21 BN3:BN21 BP3:BP21 BR3:BR21 BT3:BT21 BV3:BV21 BX3:BX21 BZ3:BZ21 CB3:CB21 CD3:CD21 CF3:CF21 CH3:CH21 CJ3:CJ21 CL3:CL21 CN3:CN21 CP3:CP20 CR3:CR20 CT3:CT20 CV3:CV21 CX3:CX21 CZ3:CZ21 DB3:DB21 DD3:DD21 DF3:DF21 DH3:DH21 DJ3:DJ21 DL3:DL21 DN3:DN21 DP3:DP21 DR3:DR21 DT3:DT21 DV3:DV21 DX3:DX21 DZ3:DZ21 EB3:EB21 ED3:ED21 EF3:EF21 EH3:EH21 EJ3:EJ21 EL3:EL21 EN3:EN21 EP3:EP21 ER3:ER21 ET3:ET21 EV3:EV21 EX3:EX21 EZ3:EZ21 FB3:FB21 FD3:FD21 FF3:FF21 FH3:FH21 FJ3:FJ21 FL3:FL21 FN3:FN21 FP3:FP21 FR3:FR21 FT3:FT21 FV3:FV21 FX3:FX21 FZ3:FZ21 GB3:GB21 GD3:GD21 GF3:GF21 GH3:GH21 GJ3:GJ21 GL3:GL21 GN3:GN21 GP3:GP21 GR3:GR21 GT3:GT21 GV3:GV21 GX3:GX21 GZ3:GZ21 HB3:HB21 HD3:HD21 HF3:HF21 HH3:HH21 HJ3:HJ21 HL3:HL21 HN3:HN21 HP3:HP21 HR3:HR21 HT3:HT21 HV3:HV21 HX3:HX21 HZ3:HZ21 IB3:IB21 ID3:ID21 IF3:IF21 IH3:IH21 IJ3:IJ21 IL3:IL21 IN3:IN21 IP3:IP21 IR3:IR21 IT3:IT21 IV3:IV21 IX3:IX21 IZ3:IZ21 JB3:JB21 JD3:JD21 JF3:JF21 JH3:JH21 JJ3:JJ21 JL3:JL21 JN3:JN21">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B21 D3:D21 F3:F21 H3:H21 J3:J21 L3:L21 N3:N21 P3:P21 R3:R21 T3:T21 V3:V21 X3:X21 Z3:Z21 AB3:AB21 AD3:AD21 AF3:AF21 AH3:AH21 AJ3:AJ21 AL3:AL21 AN3:AN21 AP3:AP21 AR3:AR21 AT3:AT21 AV3:AV21 AX3:AX21 AZ3:AZ21 BB3:BB21 BD3:BD21 BF3:BF21 BH3:BH21 BJ3:BJ21 BL3:BL21 BN3:BN21 BP3:BP21 BR3:BR21 BT3:BT21 BV3:BV21 BX3:BX21 BZ3:BZ21 CB3:CB21 CD3:CD21 CF3:CF21 CH3:CH21 CJ3:CJ21 CL3:CL21 CN3:CN21 CP3:CP21 CR3:CR21 CT3:CT21 CV3:CV21 CX3:CX21 CZ3:CZ21 DB3:DB21 DD3:DD21 DF3:DF21 DH3:DH21 DJ3:DJ21 DL3:DL21 DN3:DN21 DP3:DP21 DR3:DR21 DT3:DT21 DV3:DV21 DX3:DX21 DZ3:DZ21 EB3:EB21 ED3:ED21 EF3:EF21 EH3:EH21 EJ3:EJ21 EL3:EL21 EN3:EN21 EP3:EP21 ER3:ER21 ET3:ET21 EV3:EV21 EX3:EX21 EZ3:EZ21 FB3:FB21 FD3:FD21 FF3:FF21 FH3:FH21 FJ3:FJ21 FL3:FL21 FN3:FN21 FP3:FP21 FR3:FR21 FT3:FT21 FV3:FV21 FX3:FX21 FZ3:FZ21 GB3:GB21 GD3:GD21 GF3:GF21 GH3:GH21 GJ3:GJ21 GL3:GL21 GN3:GN21 GP3:GP21 GR3:GR21 GT3:GT21 GV3:GV21 GX3:GX21 GZ3:GZ21 HB3:HB21 HD3:HD21 HF3:HF21 HH3:HH21 HJ3:HJ21 HL3:HL21 HN3:HN21 HP3:HP21 HR3:HR21 HT3:HT21 HV3:HV21 HX3:HX21 HZ3:HZ21 IB3:IB21 ID3:ID21 IF3:IF21 IH3:IH21 IJ3:IJ21 IL3:IL21 IN3:IN21 IP3:IP21 IR3:IR21 IT3:IT21 IV3:IV21 IX3:IX21 IZ3:IZ21 JB3:JB21 JD3:JD21 JF3:JF21 JH3:JH21 JJ3:JJ21 JL3:JL21 JN3:JN21">
       <formula1>数据!$A$1:$A$88</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C22 E22 G22 I22 K22 M22 O22 Q22 S22 U22 W22 Y22 AA22 AC22 AE22 AG22 AI22 AK22 AM22 AO22 AQ22 AS22 AU22 AW22 AY22 BA22 BC22 BE22 BG22 BI22 BK22 BM22 BO22 BQ22 BS22 BU22 BW22 BY22 CA22 CC22 CE22 CG22 CI22 CK22 CM22 CO22 CQ22 CS22 CU22 CW22 CY22 DA22 DC22 DE22 DG22 DI22 DK22 DM22 DO22 DQ22 DS22 DU22 DW22 DY22 EA22 EC22 EE22 EG22 EI22 EK22 EM22 EO22 EQ22 ES22 EU22 EW22 EY22 FA22 FC22 FE22 FG22 FI22 FK22 FM22 FO22 FQ22 FS22 FU22 FW22 FY22 GA22 GC22 GE22 GG22 GI22 GK22 GM22 GO22 GQ22 GS22 GU22 GW22 GY22 HA22 HC22 HE22 HG22 HI22 HK22 HM22 HO22 HQ22 HS22 HU22 HW22 HY22 IA22 IC22 IE22 IG22 II22 IK22 IM22 IO22 IQ22 IS22 IU22 IW22 IY22 JA22 JC22 JE22 JG22 JI22 JK22 JM22 JO22">
-      <formula1>数据!$C$1:$C$25</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C21 E3:E21 G3:G21 I3:I21 K3:K21 M3:M21 O3:O21 Q3:Q21 S3:S21 U3:U21 W3:W21 Y3:Y21 AA3:AA21 AC3:AC21 AE3:AE21 AG3:AG21 AI3:AI21 AK3:AK21 AM3:AM21 AO3:AO21 AQ3:AQ21 AS3:AS21 AU3:AU21 AW3:AW21 AY3:AY21 BA3:BA21 BC3:BC21 BE3:BE21 BG3:BG21 BI3:BI21 BK3:BK21 BM3:BM21 BO3:BO21 BQ3:BQ21 BS3:BS21 BU3:BU21 BW3:BW21 BY3:BY21 CA3:CA21 CC3:CC21 CE3:CE21 CG3:CG21 CI3:CI21 CK3:CK21 CM3:CM21 CO3:CO21 CQ3:CQ21 CS3:CS21 CU3:CU21 CW3:CW21 CY3:CY21 DA3:DA21 DC3:DC21 DE3:DE21 DG3:DG21 DI3:DI21 DK3:DK21 DM3:DM21 DO3:DO21 DQ3:DQ21 DS3:DS21 DU3:DU21 DW3:DW21 DY3:DY21 EA3:EA21 EC3:EC21 EE3:EE21 EG3:EG21 EI3:EI21 EK3:EK21 EM3:EM21 EO3:EO21 EQ3:EQ21 ES3:ES21 EU3:EU21 EW3:EW21 EY3:EY21 FA3:FA21 FC3:FC21 FE3:FE21 FG3:FG21 FI3:FI21 FK3:FK21 FM3:FM21 FO3:FO21 FQ3:FQ21 FS3:FS21 FU3:FU21 FW3:FW21 FY3:FY21 GA3:GA21 GC3:GC21 GE3:GE21 GG3:GG21 GI3:GI21 GK3:GK21 GM3:GM21 GO3:GO21 GQ3:GQ21 GS3:GS21 GU3:GU21 GW3:GW21 GY3:GY21 HA3:HA21 HC3:HC21 HE3:HE21 HG3:HG21 HI3:HI21 HK3:HK21 HM3:HM21 HO3:HO21 HQ3:HQ21 HS3:HS21 HU3:HU21 HW3:HW21 HY3:HY21 IA3:IA21 IC3:IC21 IE3:IE21 IG3:IG21 II3:II21 IK3:IK21 IM3:IM21 IO3:IO21 IQ3:IQ21 IS3:IS21 IU3:IU21 IW3:IW21 IY3:IY21 JA3:JA21 JC3:JC21 JE3:JE21 JG3:JG21 JI3:JI21 JK3:JK21 JM3:JM21 JO3:JO21">
+      <formula1>数据!$B$1:$B$62</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14634,7 +14661,7 @@
   <sheetData>
     <row r="1" s="2" customFormat="1" customHeight="1" spans="1:16">
       <c r="A1" s="5" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -14673,15 +14700,15 @@
     </row>
     <row r="3" customHeight="1" spans="1:9">
       <c r="A3" s="11" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="13"/>
       <c r="D3" s="14" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="F3" s="15"/>
       <c r="G3" s="15"/>
@@ -14691,163 +14718,163 @@
     <row r="4" customHeight="1" spans="1:9">
       <c r="A4" s="17"/>
       <c r="B4" s="18" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:9">
       <c r="A5" s="17"/>
       <c r="B5" s="18" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:9">
       <c r="A6" s="17"/>
       <c r="B6" s="18" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:9">
       <c r="A7" s="17"/>
       <c r="B7" s="18" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:9">
       <c r="A8" s="17"/>
       <c r="B8" s="18" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:9">
       <c r="A9" s="17"/>
       <c r="B9" s="18" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:9">
@@ -14855,7 +14882,7 @@
       <c r="B10" s="20"/>
       <c r="C10" s="21"/>
       <c r="D10" s="22" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="24"/>
@@ -14865,15 +14892,15 @@
     </row>
     <row r="11" customHeight="1" spans="1:9">
       <c r="A11" s="11" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="13"/>
       <c r="D11" s="14" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
@@ -14883,163 +14910,163 @@
     <row r="12" customHeight="1" spans="1:9">
       <c r="A12" s="17"/>
       <c r="B12" s="18" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:9">
       <c r="A13" s="17"/>
       <c r="B13" s="18" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:9">
       <c r="A14" s="17"/>
       <c r="B14" s="18" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:9">
       <c r="A15" s="17"/>
       <c r="B15" s="18" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:9">
       <c r="A16" s="17"/>
       <c r="B16" s="18" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="I16" s="30" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:9">
       <c r="A17" s="17"/>
       <c r="B17" s="18" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:9">
@@ -15047,7 +15074,7 @@
       <c r="B18" s="20"/>
       <c r="C18" s="21"/>
       <c r="D18" s="22" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="E18" s="23"/>
       <c r="F18" s="24"/>
@@ -15057,16 +15084,16 @@
     </row>
     <row r="19" customHeight="1" spans="1:9">
       <c r="A19" s="11" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="B19" s="12"/>
       <c r="C19" s="13"/>
       <c r="D19" s="14" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="E19" s="14"/>
       <c r="F19" s="25" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="G19" s="25"/>
       <c r="H19" s="26"/>
@@ -15075,163 +15102,163 @@
     <row r="20" customHeight="1" spans="1:9">
       <c r="A20" s="17"/>
       <c r="B20" s="27" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:9">
       <c r="A21" s="17"/>
       <c r="B21" s="18" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:9">
       <c r="A22" s="17"/>
       <c r="B22" s="18" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="F22" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="G22" s="15" t="s">
         <v>339</v>
       </c>
-      <c r="G22" s="15" t="s">
-        <v>330</v>
-      </c>
       <c r="H22" s="16" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:9">
       <c r="A23" s="17"/>
       <c r="B23" s="18" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="I23" s="16" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:9">
       <c r="A24" s="17"/>
       <c r="B24" s="18" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="I24" s="30" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:9">
       <c r="A25" s="17"/>
       <c r="B25" s="18" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="I25" s="16" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:9">
@@ -15239,7 +15266,7 @@
       <c r="B26" s="20"/>
       <c r="C26" s="21"/>
       <c r="D26" s="22" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="E26" s="23"/>
       <c r="F26" s="24"/>
@@ -15434,7 +15461,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="B15">
         <v>3.5</v>
@@ -15445,7 +15472,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="B16">
         <v>3.75</v>
@@ -15456,7 +15483,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="B17">
         <v>4</v>
@@ -15467,7 +15494,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="B18">
         <v>4.25</v>
@@ -15478,7 +15505,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="B19">
         <v>4.5</v>
@@ -15489,7 +15516,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="B20">
         <v>4.75</v>
@@ -15500,7 +15527,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="B21">
         <v>5</v>
@@ -15511,7 +15538,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="B22">
         <v>5.25</v>
@@ -15522,7 +15549,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="B23">
         <v>5.5</v>
@@ -15533,7 +15560,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="B24">
         <v>5.75</v>
@@ -15544,7 +15571,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="B25">
         <v>6</v>
@@ -15571,7 +15598,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="B28">
         <v>6.75</v>
@@ -15579,7 +15606,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="B29">
         <v>7</v>
@@ -15587,7 +15614,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="B30">
         <v>7.25</v>
@@ -15595,7 +15622,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="B31">
         <v>7.5</v>
@@ -15603,7 +15630,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="B32">
         <v>7.75</v>
@@ -15611,7 +15638,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="B33">
         <v>8</v>
@@ -15619,7 +15646,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="B34">
         <v>8.25</v>
@@ -15627,7 +15654,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="B35">
         <v>8.5</v>
@@ -15635,7 +15662,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="B36">
         <v>8.75</v>
@@ -15643,7 +15670,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="B37">
         <v>9</v>
@@ -15651,7 +15678,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="B38">
         <v>9.25</v>
@@ -15659,7 +15686,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="B39">
         <v>9.5</v>
@@ -15667,7 +15694,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="B40">
         <v>9.75</v>
@@ -15675,7 +15702,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="B41">
         <v>10</v>
@@ -15683,7 +15710,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="B42">
         <v>11</v>
@@ -15691,7 +15718,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="B43">
         <v>12</v>
@@ -15699,7 +15726,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="B44">
         <v>13</v>
@@ -15707,7 +15734,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="B45">
         <v>14</v>
@@ -15715,7 +15742,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="B46">
         <v>15</v>
@@ -15723,7 +15750,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="B47">
         <v>16</v>
@@ -15731,7 +15758,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="B48">
         <v>17</v>
@@ -15739,7 +15766,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="B49">
         <v>18</v>
@@ -15747,7 +15774,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="B50">
         <v>19</v>
@@ -15755,7 +15782,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="B51">
         <v>20</v>
@@ -15763,7 +15790,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="B52">
         <v>21</v>
@@ -15771,7 +15798,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="B53">
         <v>22</v>
@@ -15779,7 +15806,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="B54">
         <v>23</v>
@@ -15787,7 +15814,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="B55">
         <v>24</v>
@@ -15795,7 +15822,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="B56">
         <v>25</v>
@@ -15803,7 +15830,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B57">
         <v>26</v>
@@ -15811,7 +15838,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="B58">
         <v>27</v>
@@ -15819,7 +15846,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="B59">
         <v>28</v>
@@ -15827,7 +15854,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="B60">
         <v>29</v>
@@ -15835,7 +15862,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="B61">
         <v>30</v>
@@ -15843,7 +15870,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="B62" t="s">
         <v>5</v>
@@ -15851,117 +15878,117 @@
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="1" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="1" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
     </row>
     <row r="86" spans="1:1">
@@ -15971,7 +15998,7 @@
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -17476,7 +17503,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="5.17272727272727" style="67" customWidth="1"/>
@@ -17714,7 +17741,7 @@
       </c>
       <c r="D21" s="76"/>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" ht="28" spans="1:5">
       <c r="A22" s="78" t="s">
         <v>1</v>
       </c>
@@ -17727,250 +17754,292 @@
       <c r="D22" s="70" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="86"/>
-      <c r="B23" s="87"/>
-      <c r="C23" s="84"/>
+      <c r="E22" s="71" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="81"/>
+      <c r="B23" s="82"/>
+      <c r="C23" s="83"/>
       <c r="D23" s="70" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="E23" s="71" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="24" ht="28" spans="1:5">
+      <c r="A24" s="81"/>
+      <c r="B24" s="82"/>
+      <c r="C24" s="83"/>
+      <c r="D24" s="70" t="s">
+        <v>261</v>
+      </c>
+      <c r="E24" s="71" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="25" ht="42" spans="1:5">
+      <c r="A25" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="79" t="s">
+      <c r="B25" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="80" t="s">
+      <c r="C25" s="80" t="s">
         <v>220</v>
       </c>
-      <c r="D24" s="70" t="s">
+      <c r="D25" s="70" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="81"/>
-      <c r="B25" s="82"/>
-      <c r="C25" s="83"/>
-      <c r="D25" s="70" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="E25" s="71" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="26" ht="70" spans="1:5">
       <c r="A26" s="81"/>
       <c r="B26" s="82"/>
       <c r="C26" s="83"/>
       <c r="D26" s="70" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+        <v>264</v>
+      </c>
+      <c r="E26" s="71" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" s="81"/>
       <c r="B27" s="82"/>
-      <c r="C27" s="84"/>
+      <c r="C27" s="83"/>
       <c r="D27" s="70" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+        <v>257</v>
+      </c>
+      <c r="E27" s="71" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="28" ht="28" spans="1:5">
       <c r="A28" s="81"/>
-      <c r="B28" s="87"/>
-      <c r="C28" s="85" t="s">
-        <v>231</v>
-      </c>
-      <c r="D28" s="88"/>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="B28" s="82"/>
+      <c r="C28" s="84"/>
+      <c r="D28" s="70" t="s">
+        <v>267</v>
+      </c>
+      <c r="E28" s="71" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="29" ht="42" spans="1:5">
       <c r="A29" s="81"/>
-      <c r="B29" s="79" t="s">
-        <v>261</v>
-      </c>
+      <c r="B29" s="87"/>
       <c r="C29" s="85" t="s">
         <v>231</v>
       </c>
       <c r="D29" s="88"/>
+      <c r="E29" s="71" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="86"/>
-      <c r="B30" s="87"/>
+      <c r="A30" s="81"/>
+      <c r="B30" s="79" t="s">
+        <v>270</v>
+      </c>
       <c r="C30" s="85" t="s">
+        <v>231</v>
+      </c>
+      <c r="D30" s="88"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="86"/>
+      <c r="B31" s="87"/>
+      <c r="C31" s="85" t="s">
         <v>220</v>
       </c>
-      <c r="D30" s="88"/>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="78" t="s">
+      <c r="D31" s="88"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="78" t="s">
         <v>14</v>
       </c>
-      <c r="B31" s="89" t="s">
-        <v>262</v>
-      </c>
-      <c r="C31" s="90"/>
-      <c r="D31" s="91"/>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="86"/>
       <c r="B32" s="89" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="C32" s="90"/>
       <c r="D32" s="91"/>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="67" t="s">
-        <v>6</v>
-      </c>
+      <c r="A33" s="86"/>
       <c r="B33" s="89" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C33" s="90"/>
       <c r="D33" s="91"/>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="78" t="s">
+      <c r="A34" s="67" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="89" t="s">
+        <v>273</v>
+      </c>
+      <c r="C34" s="90"/>
+      <c r="D34" s="91"/>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="79" t="s">
-        <v>265</v>
-      </c>
-      <c r="C34" s="80" t="s">
+      <c r="B35" s="79" t="s">
+        <v>274</v>
+      </c>
+      <c r="C35" s="80" t="s">
         <v>220</v>
       </c>
-      <c r="D34" s="70" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="81"/>
-      <c r="B35" s="82"/>
-      <c r="C35" s="84"/>
       <c r="D35" s="70" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="81"/>
       <c r="B36" s="82"/>
-      <c r="C36" s="85" t="s">
-        <v>268</v>
-      </c>
-      <c r="D36" s="88"/>
+      <c r="C36" s="84"/>
+      <c r="D36" s="70" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="86"/>
-      <c r="B37" s="87"/>
+      <c r="A37" s="81"/>
+      <c r="B37" s="82"/>
       <c r="C37" s="85" t="s">
+        <v>277</v>
+      </c>
+      <c r="D37" s="88"/>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="86"/>
+      <c r="B38" s="87"/>
+      <c r="C38" s="85" t="s">
         <v>231</v>
       </c>
-      <c r="D37" s="88"/>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="78" t="s">
+      <c r="D38" s="88"/>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="B38" s="79" t="s">
-        <v>264</v>
-      </c>
-      <c r="C38" s="85" t="s">
-        <v>269</v>
-      </c>
-      <c r="D38" s="88"/>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="81"/>
-      <c r="B39" s="82"/>
-      <c r="C39" s="80" t="s">
-        <v>220</v>
-      </c>
-      <c r="D39" s="70" t="s">
-        <v>270</v>
-      </c>
+      <c r="B39" s="79" t="s">
+        <v>273</v>
+      </c>
+      <c r="C39" s="85" t="s">
+        <v>278</v>
+      </c>
+      <c r="D39" s="88"/>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="81"/>
-      <c r="B40" s="87"/>
-      <c r="C40" s="84"/>
+      <c r="B40" s="82"/>
+      <c r="C40" s="80" t="s">
+        <v>220</v>
+      </c>
       <c r="D40" s="70" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="86"/>
-      <c r="B41" s="89" t="s">
-        <v>272</v>
-      </c>
-      <c r="C41" s="90"/>
-      <c r="D41" s="91"/>
+      <c r="A41" s="81"/>
+      <c r="B41" s="87"/>
+      <c r="C41" s="84"/>
+      <c r="D41" s="70" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="78" t="s">
+      <c r="A42" s="86"/>
+      <c r="B42" s="89" t="s">
+        <v>281</v>
+      </c>
+      <c r="C42" s="90"/>
+      <c r="D42" s="91"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="B42" s="79" t="s">
-        <v>273</v>
-      </c>
-      <c r="C42" s="80" t="s">
+      <c r="B43" s="79" t="s">
+        <v>282</v>
+      </c>
+      <c r="C43" s="80" t="s">
         <v>220</v>
       </c>
-      <c r="D42" s="70" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="81"/>
-      <c r="B43" s="82"/>
-      <c r="C43" s="83"/>
       <c r="D43" s="70" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="86"/>
-      <c r="B44" s="87"/>
-      <c r="C44" s="84"/>
+      <c r="A44" s="81"/>
+      <c r="B44" s="82"/>
+      <c r="C44" s="83"/>
       <c r="D44" s="70" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="67" t="s">
+      <c r="A45" s="86"/>
+      <c r="B45" s="87"/>
+      <c r="C45" s="84"/>
+      <c r="D45" s="70" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="B45" s="89"/>
-      <c r="C45" s="90"/>
-      <c r="D45" s="91"/>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="78" t="s">
-        <v>17</v>
-      </c>
-      <c r="B46" s="89"/>
+      <c r="B46" s="89" t="s">
+        <v>37</v>
+      </c>
       <c r="C46" s="90"/>
       <c r="D46" s="91"/>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="86"/>
-      <c r="B47" s="89"/>
+      <c r="A47" s="78" t="s">
+        <v>17</v>
+      </c>
+      <c r="B47" s="89" t="s">
+        <v>273</v>
+      </c>
       <c r="C47" s="90"/>
       <c r="D47" s="91"/>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="B48" s="89"/>
+      <c r="A48" s="86"/>
+      <c r="B48" s="89" t="s">
+        <v>273</v>
+      </c>
       <c r="C48" s="90"/>
       <c r="D48" s="91"/>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="B49" s="89"/>
+        <v>12</v>
+      </c>
+      <c r="B49" s="89" t="s">
+        <v>273</v>
+      </c>
       <c r="C49" s="90"/>
       <c r="D49" s="91"/>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="B50" s="89" t="s">
+        <v>273</v>
+      </c>
+      <c r="C50" s="90"/>
+      <c r="D50" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="46">
@@ -17982,44 +18051,44 @@
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C28:D28"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="C30:D30"/>
-    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="C31:D31"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B33:D33"/>
-    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="C38:D38"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B46:D46"/>
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="B48:D48"/>
     <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B50:D50"/>
     <mergeCell ref="A2:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="A43:A45"/>
+    <mergeCell ref="A47:A48"/>
     <mergeCell ref="B2:B21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="B38:B40"/>
-    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="B25:B29"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="B43:B45"/>
     <mergeCell ref="C2:C5"/>
     <mergeCell ref="C7:C11"/>
     <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="C24:C27"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="C25:C28"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="C43:C45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -18070,7 +18139,7 @@
         <v>119</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -18113,7 +18182,7 @@
         <v>132</v>
       </c>
       <c r="B10" s="52" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -18136,7 +18205,7 @@
         <v>139</v>
       </c>
       <c r="B14" s="52" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
     </row>
     <row r="15" spans="1:1">
@@ -18154,7 +18223,7 @@
         <v>143</v>
       </c>
       <c r="C17" s="53" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -18172,7 +18241,7 @@
         <v>146</v>
       </c>
       <c r="B20" s="52" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
     </row>
     <row r="21" ht="252" spans="1:3">
@@ -18180,10 +18249,10 @@
         <v>147</v>
       </c>
       <c r="B21" s="52" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -18196,7 +18265,7 @@
         <v>150</v>
       </c>
       <c r="B23" s="52" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
     </row>
     <row r="24" ht="126" spans="1:3">
@@ -18204,10 +18273,10 @@
         <v>151</v>
       </c>
       <c r="B24" s="52" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="C24" s="53" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
     </row>
     <row r="25" spans="1:1">
@@ -18225,10 +18294,10 @@
         <v>157</v>
       </c>
       <c r="B27" s="52" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="C27" s="53" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28" ht="409" customHeight="1" spans="1:2">
@@ -18236,7 +18305,7 @@
         <v>159</v>
       </c>
       <c r="B28" s="52" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29" spans="1:1">
@@ -18279,7 +18348,7 @@
         <v>172</v>
       </c>
       <c r="B36" s="52" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" ht="28" spans="1:3">
@@ -18287,7 +18356,7 @@
         <v>174</v>
       </c>
       <c r="C37" s="53" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -18305,7 +18374,7 @@
         <v>180</v>
       </c>
       <c r="B40" s="52" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" ht="112" spans="1:3">
@@ -18313,7 +18382,7 @@
         <v>182</v>
       </c>
       <c r="C41" s="53" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -18336,7 +18405,7 @@
         <v>188</v>
       </c>
       <c r="B45" s="52" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
     </row>
     <row r="46" spans="1:1">
@@ -18374,7 +18443,7 @@
         <v>199</v>
       </c>
       <c r="B52" s="52" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -18402,7 +18471,7 @@
   <sheetData>
     <row r="1" s="31" customFormat="1" spans="1:8">
       <c r="A1" s="35" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="B1" s="36"/>
       <c r="C1" s="31" t="s">
@@ -18426,10 +18495,10 @@
     </row>
     <row r="2" s="32" customFormat="1" spans="1:4">
       <c r="A2" s="37" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="C2" s="39" t="s">
         <v>119</v>
@@ -18439,7 +18508,7 @@
     <row r="3" s="32" customFormat="1" spans="1:4">
       <c r="A3" s="41"/>
       <c r="B3" s="38" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="C3" s="39" t="s">
         <v>135</v>
@@ -18457,7 +18526,7 @@
     <row r="5" s="32" customFormat="1" spans="1:4">
       <c r="A5" s="41"/>
       <c r="B5" s="38" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="C5" s="39" t="s">
         <v>139</v>
@@ -18467,7 +18536,7 @@
     <row r="6" s="32" customFormat="1" spans="1:4">
       <c r="A6" s="41"/>
       <c r="B6" s="38" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="C6" s="42" t="s">
         <v>127</v>
@@ -18489,7 +18558,7 @@
     <row r="8" s="32" customFormat="1" spans="1:4">
       <c r="A8" s="41"/>
       <c r="B8" s="38" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="C8" s="42" t="s">
         <v>125</v>
@@ -18501,7 +18570,7 @@
     <row r="9" s="32" customFormat="1" spans="1:4">
       <c r="A9" s="41"/>
       <c r="B9" s="38" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="C9" s="39" t="s">
         <v>130</v>
@@ -18511,7 +18580,7 @@
     <row r="10" s="32" customFormat="1" spans="1:4">
       <c r="A10" s="41"/>
       <c r="B10" s="38" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="C10" s="39" t="s">
         <v>142</v>
@@ -18521,7 +18590,7 @@
     <row r="11" s="32" customFormat="1" spans="1:4">
       <c r="A11" s="43"/>
       <c r="B11" s="38" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="C11" s="39" t="s">
         <v>164</v>
@@ -18530,10 +18599,10 @@
     </row>
     <row r="12" s="33" customFormat="1" spans="1:4">
       <c r="A12" s="44" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="C12" s="46" t="s">
         <v>182</v>
@@ -18551,17 +18620,17 @@
     <row r="14" s="33" customFormat="1" spans="1:4">
       <c r="A14" s="48"/>
       <c r="B14" s="45" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="C14" s="46" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="D14" s="47"/>
     </row>
     <row r="15" s="33" customFormat="1" spans="1:4">
       <c r="A15" s="48"/>
       <c r="B15" s="45" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="C15" s="46" t="s">
         <v>121</v>
@@ -18579,7 +18648,7 @@
     <row r="17" s="33" customFormat="1" spans="1:4">
       <c r="A17" s="48"/>
       <c r="B17" s="45" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="C17" s="46" t="s">
         <v>134</v>
@@ -18589,7 +18658,7 @@
     <row r="18" s="33" customFormat="1" spans="1:4">
       <c r="A18" s="48"/>
       <c r="B18" s="45" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="C18" s="46" t="s">
         <v>146</v>
@@ -18599,7 +18668,7 @@
     <row r="19" s="33" customFormat="1" spans="1:4">
       <c r="A19" s="48"/>
       <c r="B19" s="45" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="C19" s="46" t="s">
         <v>178</v>
@@ -18609,7 +18678,7 @@
     <row r="20" s="33" customFormat="1" spans="1:4">
       <c r="A20" s="49"/>
       <c r="B20" s="45" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="C20" s="46" t="s">
         <v>180</v>

--- a/c/9班资料.xlsx
+++ b/c/9班资料.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480" activeTab="6"/>
+    <workbookView windowWidth="20750" windowHeight="10480" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="七下拖课" sheetId="1" r:id="rId1"/>
@@ -1158,11 +1158,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
       <t xml:space="preserve">变态
 </t>
     </r>
@@ -1246,6 +1241,24 @@
         <charset val="134"/>
       </rPr>
       <t>自从英语老师说“体育课要带衣服换”之后，林奕扬就经常上演“换衣服”绝活，而且通常都是在上课时换。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+摇头
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>林奕扬被老师罚站时会不自觉摇头。</t>
     </r>
   </si>
   <si>
@@ -1458,11 +1471,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
       <t xml:space="preserve">体香
 </t>
     </r>
@@ -1587,6 +1595,15 @@
 黄恩亚爸爸的微信头像是黄恩亚在黑暗中拉小提琴，结果当英语老师问班上的人有什么特长时，学生齐声大喊：“黄恩亚会拉小提琴！”然后就把黄恩亚逼急了，连忙说：“我不会啊！”“我早就忘了！”
 黄恩亚喜欢骂脏话，尤其“操”这个字。
 黄恩亚叫别人，喜欢叫后两个字，如：“子岩”“致辰”等。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+黄恩亚外八走路。</t>
     </r>
   </si>
   <si>
@@ -4058,9 +4075,26 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color rgb="FF4F81BD"/>
       <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFC0504D"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -4073,23 +4107,6 @@
       <sz val="11"/>
       <color rgb="FF000033"/>
       <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFC0504D"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -18244,7 +18261,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="21" ht="252" spans="1:3">
+    <row r="21" ht="280" spans="1:3">
       <c r="A21" s="59" t="s">
         <v>147</v>
       </c>

--- a/c/9班资料.xlsx
+++ b/c/9班资料.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="476">
   <si>
     <t>拖课统计表</t>
   </si>
@@ -1158,6 +1158,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">变态
 </t>
     </r>
@@ -1471,6 +1476,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">体香
 </t>
     </r>
@@ -1608,6 +1618,20 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">数学书
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>黄恩亚喜欢带六下北师大版的数学书。</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <rPr>
         <sz val="11"/>
         <rFont val="黑体"/>
@@ -1643,6 +1667,20 @@
         <charset val="134"/>
       </rPr>
       <t>有人说，陈睿卓每天吃得都很补，整天中午吃海参。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">嘴甜
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>薛阅晨在政治课上被成为“嘴甜的人”。</t>
     </r>
   </si>
   <si>
@@ -4076,14 +4114,8 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF4F81BD"/>
-      <name val="黑体"/>
+      <color rgb="FF000033"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -4093,8 +4125,20 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF4F81BD"/>
+      <name val="黑体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -4102,12 +4146,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000033"/>
-      <name val="等线"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="61">
@@ -14678,7 +14716,7 @@
   <sheetData>
     <row r="1" s="2" customFormat="1" customHeight="1" spans="1:16">
       <c r="A1" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -14717,15 +14755,15 @@
     </row>
     <row r="3" customHeight="1" spans="1:9">
       <c r="A3" s="11" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="13"/>
       <c r="D3" s="14" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F3" s="15"/>
       <c r="G3" s="15"/>
@@ -14735,163 +14773,163 @@
     <row r="4" customHeight="1" spans="1:9">
       <c r="A4" s="17"/>
       <c r="B4" s="18" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:9">
       <c r="A5" s="17"/>
       <c r="B5" s="18" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:9">
       <c r="A6" s="17"/>
       <c r="B6" s="18" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:9">
       <c r="A7" s="17"/>
       <c r="B7" s="18" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:9">
       <c r="A8" s="17"/>
       <c r="B8" s="18" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:9">
       <c r="A9" s="17"/>
       <c r="B9" s="18" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:9">
@@ -14899,7 +14937,7 @@
       <c r="B10" s="20"/>
       <c r="C10" s="21"/>
       <c r="D10" s="22" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="24"/>
@@ -14909,15 +14947,15 @@
     </row>
     <row r="11" customHeight="1" spans="1:9">
       <c r="A11" s="11" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="13"/>
       <c r="D11" s="14" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
@@ -14927,163 +14965,163 @@
     <row r="12" customHeight="1" spans="1:9">
       <c r="A12" s="17"/>
       <c r="B12" s="18" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:9">
       <c r="A13" s="17"/>
       <c r="B13" s="18" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:9">
       <c r="A14" s="17"/>
       <c r="B14" s="18" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:9">
       <c r="A15" s="17"/>
       <c r="B15" s="18" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:9">
       <c r="A16" s="17"/>
       <c r="B16" s="18" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="I16" s="30" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:9">
       <c r="A17" s="17"/>
       <c r="B17" s="18" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:9">
@@ -15091,7 +15129,7 @@
       <c r="B18" s="20"/>
       <c r="C18" s="21"/>
       <c r="D18" s="22" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E18" s="23"/>
       <c r="F18" s="24"/>
@@ -15101,16 +15139,16 @@
     </row>
     <row r="19" customHeight="1" spans="1:9">
       <c r="A19" s="11" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B19" s="12"/>
       <c r="C19" s="13"/>
       <c r="D19" s="14" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E19" s="14"/>
       <c r="F19" s="25" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G19" s="25"/>
       <c r="H19" s="26"/>
@@ -15119,163 +15157,163 @@
     <row r="20" customHeight="1" spans="1:9">
       <c r="A20" s="17"/>
       <c r="B20" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>383</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="H20" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="I20" s="16" t="s">
         <v>381</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>337</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>332</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>377</v>
-      </c>
-      <c r="G20" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>380</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:9">
       <c r="A21" s="17"/>
       <c r="B21" s="18" t="s">
+        <v>333</v>
+      </c>
+      <c r="C21" s="18" t="s">
         <v>331</v>
       </c>
-      <c r="C21" s="18" t="s">
-        <v>329</v>
-      </c>
       <c r="D21" s="14" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="G21" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="H21" s="16" t="s">
         <v>387</v>
       </c>
-      <c r="H21" s="16" t="s">
-        <v>385</v>
-      </c>
       <c r="I21" s="16" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:9">
       <c r="A22" s="17"/>
       <c r="B22" s="18" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:9">
       <c r="A23" s="17"/>
       <c r="B23" s="18" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="I23" s="16" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:9">
       <c r="A24" s="17"/>
       <c r="B24" s="18" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I24" s="30" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:9">
       <c r="A25" s="17"/>
       <c r="B25" s="18" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="I25" s="16" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:9">
@@ -15283,7 +15321,7 @@
       <c r="B26" s="20"/>
       <c r="C26" s="21"/>
       <c r="D26" s="22" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E26" s="23"/>
       <c r="F26" s="24"/>
@@ -15489,7 +15527,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B16">
         <v>3.75</v>
@@ -15500,7 +15538,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B17">
         <v>4</v>
@@ -15511,7 +15549,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B18">
         <v>4.25</v>
@@ -15522,7 +15560,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B19">
         <v>4.5</v>
@@ -15533,7 +15571,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B20">
         <v>4.75</v>
@@ -15544,7 +15582,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B21">
         <v>5</v>
@@ -15555,7 +15593,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B22">
         <v>5.25</v>
@@ -15566,7 +15604,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B23">
         <v>5.5</v>
@@ -15577,7 +15615,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B24">
         <v>5.75</v>
@@ -15588,7 +15626,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B25">
         <v>6</v>
@@ -15615,7 +15653,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B28">
         <v>6.75</v>
@@ -15623,7 +15661,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B29">
         <v>7</v>
@@ -15631,7 +15669,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B30">
         <v>7.25</v>
@@ -15639,7 +15677,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B31">
         <v>7.5</v>
@@ -15647,7 +15685,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B32">
         <v>7.75</v>
@@ -15655,7 +15693,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B33">
         <v>8</v>
@@ -15663,7 +15701,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B34">
         <v>8.25</v>
@@ -15671,7 +15709,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B35">
         <v>8.5</v>
@@ -15679,7 +15717,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B36">
         <v>8.75</v>
@@ -15687,7 +15725,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B37">
         <v>9</v>
@@ -15695,7 +15733,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B38">
         <v>9.25</v>
@@ -15703,7 +15741,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B39">
         <v>9.5</v>
@@ -15711,7 +15749,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B40">
         <v>9.75</v>
@@ -15719,7 +15757,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B41">
         <v>10</v>
@@ -15727,7 +15765,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B42">
         <v>11</v>
@@ -15735,7 +15773,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B43">
         <v>12</v>
@@ -15743,7 +15781,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B44">
         <v>13</v>
@@ -15751,7 +15789,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B45">
         <v>14</v>
@@ -15759,7 +15797,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B46">
         <v>15</v>
@@ -15767,7 +15805,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B47">
         <v>16</v>
@@ -15775,7 +15813,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B48">
         <v>17</v>
@@ -15783,7 +15821,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B49">
         <v>18</v>
@@ -15791,7 +15829,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B50">
         <v>19</v>
@@ -15799,7 +15837,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B51">
         <v>20</v>
@@ -15807,7 +15845,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B52">
         <v>21</v>
@@ -15815,7 +15853,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B53">
         <v>22</v>
@@ -15823,7 +15861,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B54">
         <v>23</v>
@@ -15831,7 +15869,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B55">
         <v>24</v>
@@ -15839,7 +15877,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B56">
         <v>25</v>
@@ -15847,7 +15885,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B57">
         <v>26</v>
@@ -15855,7 +15893,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B58">
         <v>27</v>
@@ -15863,7 +15901,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B59">
         <v>28</v>
@@ -15871,7 +15909,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B60">
         <v>29</v>
@@ -15879,7 +15917,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B61">
         <v>30</v>
@@ -15887,7 +15925,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B62" t="s">
         <v>5</v>
@@ -15895,117 +15933,117 @@
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="86" spans="1:1">
@@ -16015,7 +16053,7 @@
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -18317,12 +18355,15 @@
         <v>296</v>
       </c>
     </row>
-    <row r="28" ht="409" customHeight="1" spans="1:2">
+    <row r="28" ht="409" customHeight="1" spans="1:3">
       <c r="A28" s="59" t="s">
         <v>159</v>
       </c>
       <c r="B28" s="52" t="s">
         <v>297</v>
+      </c>
+      <c r="C28" s="53" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="29" spans="1:1">
@@ -18365,7 +18406,7 @@
         <v>172</v>
       </c>
       <c r="B36" s="52" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" ht="28" spans="1:3">
@@ -18373,7 +18414,7 @@
         <v>174</v>
       </c>
       <c r="C37" s="53" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -18381,9 +18422,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" ht="28" spans="1:3">
       <c r="A39" s="59" t="s">
         <v>178</v>
+      </c>
+      <c r="C39" s="53" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="40" ht="28" spans="1:2">
@@ -18391,7 +18435,7 @@
         <v>180</v>
       </c>
       <c r="B40" s="52" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" ht="112" spans="1:3">
@@ -18399,7 +18443,7 @@
         <v>182</v>
       </c>
       <c r="C41" s="53" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -18422,7 +18466,7 @@
         <v>188</v>
       </c>
       <c r="B45" s="52" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="46" spans="1:1">
@@ -18460,7 +18504,7 @@
         <v>199</v>
       </c>
       <c r="B52" s="52" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -18488,7 +18532,7 @@
   <sheetData>
     <row r="1" s="31" customFormat="1" spans="1:8">
       <c r="A1" s="35" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B1" s="36"/>
       <c r="C1" s="31" t="s">
@@ -18512,10 +18556,10 @@
     </row>
     <row r="2" s="32" customFormat="1" spans="1:4">
       <c r="A2" s="37" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C2" s="39" t="s">
         <v>119</v>
@@ -18525,7 +18569,7 @@
     <row r="3" s="32" customFormat="1" spans="1:4">
       <c r="A3" s="41"/>
       <c r="B3" s="38" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C3" s="39" t="s">
         <v>135</v>
@@ -18543,7 +18587,7 @@
     <row r="5" s="32" customFormat="1" spans="1:4">
       <c r="A5" s="41"/>
       <c r="B5" s="38" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C5" s="39" t="s">
         <v>139</v>
@@ -18553,7 +18597,7 @@
     <row r="6" s="32" customFormat="1" spans="1:4">
       <c r="A6" s="41"/>
       <c r="B6" s="38" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C6" s="42" t="s">
         <v>127</v>
@@ -18575,7 +18619,7 @@
     <row r="8" s="32" customFormat="1" spans="1:4">
       <c r="A8" s="41"/>
       <c r="B8" s="38" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C8" s="42" t="s">
         <v>125</v>
@@ -18587,7 +18631,7 @@
     <row r="9" s="32" customFormat="1" spans="1:4">
       <c r="A9" s="41"/>
       <c r="B9" s="38" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C9" s="39" t="s">
         <v>130</v>
@@ -18597,7 +18641,7 @@
     <row r="10" s="32" customFormat="1" spans="1:4">
       <c r="A10" s="41"/>
       <c r="B10" s="38" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C10" s="39" t="s">
         <v>142</v>
@@ -18607,7 +18651,7 @@
     <row r="11" s="32" customFormat="1" spans="1:4">
       <c r="A11" s="43"/>
       <c r="B11" s="38" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C11" s="39" t="s">
         <v>164</v>
@@ -18616,10 +18660,10 @@
     </row>
     <row r="12" s="33" customFormat="1" spans="1:4">
       <c r="A12" s="44" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C12" s="46" t="s">
         <v>182</v>
@@ -18637,17 +18681,17 @@
     <row r="14" s="33" customFormat="1" spans="1:4">
       <c r="A14" s="48"/>
       <c r="B14" s="45" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C14" s="46" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D14" s="47"/>
     </row>
     <row r="15" s="33" customFormat="1" spans="1:4">
       <c r="A15" s="48"/>
       <c r="B15" s="45" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C15" s="46" t="s">
         <v>121</v>
@@ -18665,7 +18709,7 @@
     <row r="17" s="33" customFormat="1" spans="1:4">
       <c r="A17" s="48"/>
       <c r="B17" s="45" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C17" s="46" t="s">
         <v>134</v>
@@ -18675,7 +18719,7 @@
     <row r="18" s="33" customFormat="1" spans="1:4">
       <c r="A18" s="48"/>
       <c r="B18" s="45" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C18" s="46" t="s">
         <v>146</v>
@@ -18685,7 +18729,7 @@
     <row r="19" s="33" customFormat="1" spans="1:4">
       <c r="A19" s="48"/>
       <c r="B19" s="45" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C19" s="46" t="s">
         <v>178</v>
@@ -18695,7 +18739,7 @@
     <row r="20" s="33" customFormat="1" spans="1:4">
       <c r="A20" s="49"/>
       <c r="B20" s="45" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C20" s="46" t="s">
         <v>180</v>

--- a/c/9班资料.xlsx
+++ b/c/9班资料.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480"/>
+    <workbookView windowWidth="20750" windowHeight="10480" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="七下拖课" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1486" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="481">
   <si>
     <t>拖课统计表</t>
   </si>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>劳技（数、英占½）</t>
+  </si>
+  <si>
+    <t>劳技（英占）</t>
   </si>
   <si>
     <t>地理</t>
@@ -1702,11 +1705,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
       <t xml:space="preserve">海参
 </t>
     </r>
@@ -1718,14 +1716,27 @@
       </rPr>
       <t>有人说，陈睿卓每天吃得都很补，整天中午吃海参。</t>
     </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="黑体"/>
         <charset val="134"/>
       </rPr>
+      <t xml:space="preserve">
+唱歌
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>陈睿卓被称“林俊卓”，唱歌时会摇头摆手。</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">嘴甜
 </t>
     </r>
@@ -1736,6 +1747,24 @@
         <charset val="134"/>
       </rPr>
       <t>薛阅晨在政治课上被成为“嘴甜的人”。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+和郑永泽
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>薛阅晨喜欢“黏着”郑永泽，如下课和郑永泽出去、体育课和郑永泽用同一个垫子。</t>
     </r>
   </si>
   <si>
@@ -3765,9 +3794,6 @@
   </si>
   <si>
     <t>信息（数占）</t>
-  </si>
-  <si>
-    <t>劳技（英占）</t>
   </si>
   <si>
     <t>信息（英占）</t>
@@ -4277,10 +4303,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF4F81BD"/>
-      <name val="黑体"/>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4295,21 +4321,21 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000033"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="宋体"/>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
-      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF4F81BD"/>
+      <name val="黑体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="61">
@@ -7480,10 +7506,18 @@
       <c r="EA3" s="154"/>
       <c r="EB3" s="153"/>
       <c r="EC3" s="154"/>
-      <c r="ED3" s="153"/>
-      <c r="EE3" s="154"/>
-      <c r="EF3" s="153"/>
-      <c r="EG3" s="154"/>
+      <c r="ED3" s="153" t="s">
+        <v>4</v>
+      </c>
+      <c r="EE3" s="154">
+        <v>3.5</v>
+      </c>
+      <c r="EF3" s="153" t="s">
+        <v>4</v>
+      </c>
+      <c r="EG3" s="154" t="s">
+        <v>3</v>
+      </c>
       <c r="EH3" s="153"/>
       <c r="EI3" s="154"/>
       <c r="EJ3" s="153"/>
@@ -8216,10 +8250,18 @@
       <c r="EA5" s="160"/>
       <c r="EB5" s="159"/>
       <c r="EC5" s="160"/>
-      <c r="ED5" s="159"/>
-      <c r="EE5" s="160"/>
-      <c r="EF5" s="159"/>
-      <c r="EG5" s="160"/>
+      <c r="ED5" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="EE5" s="160">
+        <v>1</v>
+      </c>
+      <c r="EF5" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="EG5" s="160" t="s">
+        <v>3</v>
+      </c>
       <c r="EH5" s="159"/>
       <c r="EI5" s="160"/>
       <c r="EJ5" s="159"/>
@@ -9235,10 +9277,18 @@
       <c r="EA8" s="160"/>
       <c r="EB8" s="164"/>
       <c r="EC8" s="160"/>
-      <c r="ED8" s="164"/>
-      <c r="EE8" s="160"/>
-      <c r="EF8" s="164"/>
-      <c r="EG8" s="160"/>
+      <c r="ED8" s="164" t="s">
+        <v>9</v>
+      </c>
+      <c r="EE8" s="160" t="s">
+        <v>3</v>
+      </c>
+      <c r="EF8" s="164" t="s">
+        <v>1</v>
+      </c>
+      <c r="EG8" s="160" t="s">
+        <v>3</v>
+      </c>
       <c r="EH8" s="164"/>
       <c r="EI8" s="160"/>
       <c r="EJ8" s="164"/>
@@ -9975,10 +10025,18 @@
       <c r="EA10" s="160"/>
       <c r="EB10" s="159"/>
       <c r="EC10" s="160"/>
-      <c r="ED10" s="159"/>
-      <c r="EE10" s="160"/>
-      <c r="EF10" s="159"/>
-      <c r="EG10" s="160"/>
+      <c r="ED10" s="159" t="s">
+        <v>1</v>
+      </c>
+      <c r="EE10" s="160">
+        <v>2.75</v>
+      </c>
+      <c r="EF10" s="159" t="s">
+        <v>9</v>
+      </c>
+      <c r="EG10" s="160" t="s">
+        <v>3</v>
+      </c>
       <c r="EH10" s="159"/>
       <c r="EI10" s="160"/>
       <c r="EJ10" s="159"/>
@@ -10711,10 +10769,18 @@
       <c r="EA12" s="160"/>
       <c r="EB12" s="159"/>
       <c r="EC12" s="160"/>
-      <c r="ED12" s="159"/>
-      <c r="EE12" s="160"/>
-      <c r="EF12" s="159"/>
-      <c r="EG12" s="160"/>
+      <c r="ED12" s="159" t="s">
+        <v>17</v>
+      </c>
+      <c r="EE12" s="160" t="s">
+        <v>3</v>
+      </c>
+      <c r="EF12" s="159" t="s">
+        <v>1</v>
+      </c>
+      <c r="EG12" s="160" t="s">
+        <v>3</v>
+      </c>
       <c r="EH12" s="159"/>
       <c r="EI12" s="160"/>
       <c r="EJ12" s="159"/>
@@ -11445,10 +11511,18 @@
       <c r="EA14" s="160"/>
       <c r="EB14" s="159"/>
       <c r="EC14" s="160"/>
-      <c r="ED14" s="159"/>
-      <c r="EE14" s="160"/>
-      <c r="EF14" s="159"/>
-      <c r="EG14" s="160"/>
+      <c r="ED14" s="159" t="s">
+        <v>14</v>
+      </c>
+      <c r="EE14" s="160" t="s">
+        <v>3</v>
+      </c>
+      <c r="EF14" s="159" t="s">
+        <v>20</v>
+      </c>
+      <c r="EG14" s="160" t="s">
+        <v>3</v>
+      </c>
       <c r="EH14" s="159"/>
       <c r="EI14" s="160"/>
       <c r="EJ14" s="159"/>
@@ -11892,7 +11966,7 @@
         <v>3</v>
       </c>
       <c r="L16" s="159" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M16" s="160">
         <v>2</v>
@@ -11904,7 +11978,7 @@
         <v>3</v>
       </c>
       <c r="P16" s="159" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q16" s="160">
         <v>1.25</v>
@@ -11926,7 +12000,7 @@
         <v>3</v>
       </c>
       <c r="Z16" s="159" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA16" s="160">
         <v>3</v>
@@ -11938,7 +12012,7 @@
         <v>3</v>
       </c>
       <c r="AD16" s="159" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE16" s="160">
         <v>4</v>
@@ -11960,7 +12034,7 @@
         <v>3</v>
       </c>
       <c r="AN16" s="159" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO16" s="160">
         <v>2.25</v>
@@ -11972,7 +12046,7 @@
         <v>3</v>
       </c>
       <c r="AR16" s="159" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS16" s="160">
         <v>2.25</v>
@@ -11994,7 +12068,7 @@
         <v>3</v>
       </c>
       <c r="BB16" s="159" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC16" s="160">
         <v>2.75</v>
@@ -12006,7 +12080,7 @@
         <v>3</v>
       </c>
       <c r="BF16" s="159" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG16" s="160">
         <v>1.5</v>
@@ -12028,7 +12102,7 @@
         <v>3</v>
       </c>
       <c r="BP16" s="159" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ16" s="160">
         <v>2.25</v>
@@ -12040,7 +12114,7 @@
         <v>3</v>
       </c>
       <c r="BT16" s="159" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BU16" s="160">
         <v>5</v>
@@ -12062,7 +12136,7 @@
         <v>3</v>
       </c>
       <c r="CD16" s="159" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CE16" s="160">
         <v>4</v>
@@ -12074,7 +12148,7 @@
         <v>3</v>
       </c>
       <c r="CH16" s="159" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CI16" s="160">
         <v>1</v>
@@ -12096,7 +12170,7 @@
         <v>3</v>
       </c>
       <c r="CR16" s="159" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CS16" s="160">
         <v>4</v>
@@ -12126,7 +12200,7 @@
         <v>3</v>
       </c>
       <c r="DF16" s="159" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DG16" s="160" t="s">
         <v>3</v>
@@ -12138,7 +12212,7 @@
         <v>3</v>
       </c>
       <c r="DJ16" s="159" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DK16" s="160" t="s">
         <v>3</v>
@@ -12160,7 +12234,7 @@
         <v>3</v>
       </c>
       <c r="DT16" s="159" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DU16" s="160" t="s">
         <v>3</v>
@@ -12172,7 +12246,7 @@
         <v>3</v>
       </c>
       <c r="DX16" s="159" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DY16" s="160">
         <v>1</v>
@@ -12181,10 +12255,18 @@
       <c r="EA16" s="160"/>
       <c r="EB16" s="159"/>
       <c r="EC16" s="160"/>
-      <c r="ED16" s="159"/>
-      <c r="EE16" s="160"/>
-      <c r="EF16" s="159"/>
-      <c r="EG16" s="160"/>
+      <c r="ED16" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="EE16" s="160">
+        <v>2.25</v>
+      </c>
+      <c r="EF16" s="159" t="s">
+        <v>6</v>
+      </c>
+      <c r="EG16" s="160" t="s">
+        <v>3</v>
+      </c>
       <c r="EH16" s="159"/>
       <c r="EI16" s="160"/>
       <c r="EJ16" s="159"/>
@@ -12909,10 +12991,18 @@
       <c r="EA18" s="160"/>
       <c r="EB18" s="159"/>
       <c r="EC18" s="160"/>
-      <c r="ED18" s="159"/>
-      <c r="EE18" s="160"/>
-      <c r="EF18" s="159"/>
-      <c r="EG18" s="160"/>
+      <c r="ED18" s="159" t="s">
+        <v>17</v>
+      </c>
+      <c r="EE18" s="160">
+        <v>3.5</v>
+      </c>
+      <c r="EF18" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="EG18" s="160" t="s">
+        <v>3</v>
+      </c>
       <c r="EH18" s="159"/>
       <c r="EI18" s="160"/>
       <c r="EJ18" s="159"/>
@@ -13364,7 +13454,7 @@
         <v>3</v>
       </c>
       <c r="P20" s="159" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q20" s="160" t="s">
         <v>3</v>
@@ -13392,11 +13482,11 @@
         <v>3</v>
       </c>
       <c r="AB20" s="159" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC20" s="160"/>
       <c r="AD20" s="159" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE20" s="160"/>
       <c r="AF20" s="159"/>
@@ -13422,7 +13512,7 @@
         <v>3</v>
       </c>
       <c r="AP20" s="159" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ20" s="160"/>
       <c r="AR20" s="159" t="s">
@@ -13454,7 +13544,7 @@
         <v>3</v>
       </c>
       <c r="BD20" s="159" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE20" s="160"/>
       <c r="BF20" s="159" t="s">
@@ -13486,7 +13576,7 @@
         <v>3</v>
       </c>
       <c r="BR20" s="159" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BS20" s="160"/>
       <c r="BT20" s="159" t="s">
@@ -13506,7 +13596,7 @@
       <c r="CD20" s="159"/>
       <c r="CE20" s="160"/>
       <c r="CF20" s="159" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CG20" s="160"/>
       <c r="CH20" s="159"/>
@@ -13534,7 +13624,7 @@
         <v>2.25</v>
       </c>
       <c r="CT20" s="159" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CU20" s="160"/>
       <c r="CV20" s="159"/>
@@ -13609,10 +13699,18 @@
       <c r="EA20" s="160"/>
       <c r="EB20" s="159"/>
       <c r="EC20" s="160"/>
-      <c r="ED20" s="159"/>
-      <c r="EE20" s="160"/>
-      <c r="EF20" s="159"/>
-      <c r="EG20" s="160"/>
+      <c r="ED20" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="EE20" s="160">
+        <v>4.5</v>
+      </c>
+      <c r="EF20" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="EG20" s="160">
+        <v>2</v>
+      </c>
       <c r="EH20" s="159"/>
       <c r="EI20" s="160"/>
       <c r="EJ20" s="159"/>
@@ -14040,579 +14138,579 @@
     <row r="22" ht="17.5" spans="1:275">
       <c r="A22" s="168"/>
       <c r="B22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C22" s="170"/>
       <c r="D22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E22" s="170"/>
       <c r="F22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G22" s="170"/>
       <c r="H22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I22" s="170"/>
       <c r="J22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K22" s="170"/>
       <c r="L22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M22" s="170"/>
       <c r="N22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O22" s="170"/>
       <c r="P22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q22" s="170"/>
       <c r="R22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S22" s="170"/>
       <c r="T22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U22" s="170"/>
       <c r="V22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="W22" s="170"/>
       <c r="X22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y22" s="170"/>
       <c r="Z22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA22" s="170">
         <v>6</v>
       </c>
       <c r="AB22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AC22" s="170"/>
       <c r="AD22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE22" s="170">
         <v>7</v>
       </c>
       <c r="AF22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG22" s="170"/>
       <c r="AH22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI22" s="170"/>
       <c r="AJ22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK22" s="170"/>
       <c r="AL22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM22" s="170">
         <v>8</v>
       </c>
       <c r="AN22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO22" s="170"/>
       <c r="AP22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ22" s="170"/>
       <c r="AR22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS22" s="170">
         <v>8</v>
       </c>
       <c r="AT22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU22" s="170"/>
       <c r="AV22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW22" s="170"/>
       <c r="AX22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY22" s="170"/>
       <c r="AZ22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA22" s="170">
         <v>7</v>
       </c>
       <c r="BB22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC22" s="170">
         <v>7</v>
       </c>
       <c r="BD22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE22" s="170">
         <v>7</v>
       </c>
       <c r="BF22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG22" s="170"/>
       <c r="BH22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BI22" s="170"/>
       <c r="BJ22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BK22" s="170"/>
       <c r="BL22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BM22" s="170"/>
       <c r="BN22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BO22" s="170"/>
       <c r="BP22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BQ22" s="170">
         <v>8</v>
       </c>
       <c r="BR22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BS22" s="170"/>
       <c r="BT22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BU22" s="170"/>
       <c r="BV22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BW22" s="170"/>
       <c r="BX22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BY22" s="170"/>
       <c r="BZ22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CA22" s="170"/>
       <c r="CB22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CC22" s="170">
         <v>8</v>
       </c>
       <c r="CD22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CE22" s="170"/>
       <c r="CF22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CG22" s="170">
         <v>7</v>
       </c>
       <c r="CH22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CI22" s="170">
         <v>7</v>
       </c>
       <c r="CJ22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CK22" s="170"/>
       <c r="CL22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CM22" s="170"/>
       <c r="CN22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CO22" s="170"/>
       <c r="CP22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CQ22" s="170">
         <v>7</v>
       </c>
       <c r="CR22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CS22" s="170">
         <v>7</v>
       </c>
       <c r="CT22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CU22" s="170">
         <v>9</v>
       </c>
       <c r="CV22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CW22" s="170"/>
       <c r="CX22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CY22" s="170"/>
       <c r="CZ22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DA22" s="170"/>
       <c r="DB22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DC22" s="170"/>
       <c r="DD22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DE22" s="170"/>
       <c r="DF22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DG22" s="170"/>
       <c r="DH22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DI22" s="170"/>
       <c r="DJ22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DK22" s="170"/>
       <c r="DL22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DM22" s="170"/>
       <c r="DN22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DO22" s="170"/>
       <c r="DP22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DQ22" s="170"/>
       <c r="DR22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DS22" s="170"/>
       <c r="DT22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DU22" s="170"/>
       <c r="DV22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DW22" s="170"/>
       <c r="DX22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DY22" s="170"/>
       <c r="DZ22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="EA22" s="170"/>
       <c r="EB22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="EC22" s="170"/>
       <c r="ED22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="EE22" s="170"/>
       <c r="EF22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="EG22" s="170"/>
       <c r="EH22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="EI22" s="170"/>
       <c r="EJ22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="EK22" s="170"/>
       <c r="EL22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="EM22" s="170"/>
       <c r="EN22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="EO22" s="170"/>
       <c r="EP22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="EQ22" s="170"/>
       <c r="ER22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="ES22" s="170"/>
       <c r="ET22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="EU22" s="170"/>
       <c r="EV22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="EW22" s="170"/>
       <c r="EX22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="EY22" s="170"/>
       <c r="EZ22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="FA22" s="170"/>
       <c r="FB22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="FC22" s="170"/>
       <c r="FD22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="FE22" s="170"/>
       <c r="FF22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="FG22" s="170"/>
       <c r="FH22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="FI22" s="170"/>
       <c r="FJ22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="FK22" s="170"/>
       <c r="FL22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="FM22" s="170"/>
       <c r="FN22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="FO22" s="170"/>
       <c r="FP22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="FQ22" s="170"/>
       <c r="FR22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="FS22" s="170"/>
       <c r="FT22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="FU22" s="170"/>
       <c r="FV22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="FW22" s="170"/>
       <c r="FX22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="FY22" s="170"/>
       <c r="FZ22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="GA22" s="170"/>
       <c r="GB22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="GC22" s="170"/>
       <c r="GD22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="GE22" s="170"/>
       <c r="GF22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="GG22" s="170"/>
       <c r="GH22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="GI22" s="170"/>
       <c r="GJ22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="GK22" s="170"/>
       <c r="GL22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="GM22" s="170"/>
       <c r="GN22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="GO22" s="170"/>
       <c r="GP22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="GQ22" s="170"/>
       <c r="GR22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="GS22" s="170"/>
       <c r="GT22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="GU22" s="170"/>
       <c r="GV22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="GW22" s="170"/>
       <c r="GX22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="GY22" s="170"/>
       <c r="GZ22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="HA22" s="170"/>
       <c r="HB22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="HC22" s="170"/>
       <c r="HD22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="HE22" s="170"/>
       <c r="HF22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="HG22" s="170"/>
       <c r="HH22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="HI22" s="170"/>
       <c r="HJ22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="HK22" s="170"/>
       <c r="HL22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="HM22" s="170"/>
       <c r="HN22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="HO22" s="170"/>
       <c r="HP22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="HQ22" s="170"/>
       <c r="HR22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="HS22" s="170"/>
       <c r="HT22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="HU22" s="170"/>
       <c r="HV22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="HW22" s="170"/>
       <c r="HX22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="HY22" s="170"/>
       <c r="HZ22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="IA22" s="170"/>
       <c r="IB22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="IC22" s="170"/>
       <c r="ID22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="IE22" s="170"/>
       <c r="IF22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="IG22" s="170"/>
       <c r="IH22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="II22" s="170"/>
       <c r="IJ22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="IK22" s="170"/>
       <c r="IL22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="IM22" s="170"/>
       <c r="IN22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="IO22" s="170"/>
       <c r="IP22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="IQ22" s="170"/>
       <c r="IR22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="IS22" s="170"/>
       <c r="IT22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="IU22" s="170"/>
       <c r="IV22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="IW22" s="170"/>
       <c r="IX22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="IY22" s="170"/>
       <c r="IZ22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="JA22" s="170"/>
       <c r="JB22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="JC22" s="170"/>
       <c r="JD22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="JE22" s="170"/>
       <c r="JF22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="JG22" s="170"/>
       <c r="JH22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="JI22" s="170"/>
       <c r="JJ22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="JK22" s="170"/>
       <c r="JL22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="JM22" s="170"/>
       <c r="JN22" s="169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="JO22" s="170"/>
     </row>
@@ -14652,7 +14750,7 @@
       <c r="AH23" s="171"/>
       <c r="AI23" s="172"/>
       <c r="AJ23" s="171" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK23" s="172"/>
       <c r="AL23" s="171"/>
@@ -14668,23 +14766,23 @@
       <c r="AV23" s="171"/>
       <c r="AW23" s="172"/>
       <c r="AX23" s="171" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY23" s="172"/>
       <c r="AZ23" s="171" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA23" s="172"/>
       <c r="BB23" s="171" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC23" s="172"/>
       <c r="BD23" s="171" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE23" s="172"/>
       <c r="BF23" s="171" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BG23" s="172"/>
       <c r="BH23" s="171"/>
@@ -14692,7 +14790,7 @@
       <c r="BJ23" s="171"/>
       <c r="BK23" s="172"/>
       <c r="BL23" s="171" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BM23" s="172"/>
       <c r="BN23" s="171"/>
@@ -15188,515 +15286,610 @@
     <mergeCell ref="JN23:JO23"/>
   </mergeCells>
   <conditionalFormatting sqref="DE5">
-    <cfRule type="containsText" dxfId="0" priority="90" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="113" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="89">
+    <cfRule type="containsBlanks" dxfId="1" priority="112">
       <formula>LEN(TRIM(DE5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG5">
-    <cfRule type="containsText" dxfId="0" priority="88" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="111" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="87">
+    <cfRule type="containsBlanks" dxfId="1" priority="110">
       <formula>LEN(TRIM(DG5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DU5">
-    <cfRule type="containsText" dxfId="0" priority="28" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="51" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DU5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="27">
+    <cfRule type="containsBlanks" dxfId="1" priority="50">
       <formula>LEN(TRIM(DU5))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="EG5">
+    <cfRule type="containsText" dxfId="0" priority="14" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EG5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="13">
+      <formula>LEN(TRIM(EG5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="DC8">
-    <cfRule type="containsText" dxfId="0" priority="110" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="133" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DC8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="109">
+    <cfRule type="containsBlanks" dxfId="1" priority="132">
       <formula>LEN(TRIM(DC8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DE8">
-    <cfRule type="containsText" dxfId="0" priority="92" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="115" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="91">
+    <cfRule type="containsBlanks" dxfId="1" priority="114">
       <formula>LEN(TRIM(DE8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG8">
-    <cfRule type="containsText" dxfId="0" priority="86" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="109" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="85">
+    <cfRule type="containsBlanks" dxfId="1" priority="108">
       <formula>LEN(TRIM(DG8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI8">
-    <cfRule type="containsText" dxfId="0" priority="64" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="87" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="63">
+    <cfRule type="containsBlanks" dxfId="1" priority="86">
       <formula>LEN(TRIM(DI8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK8">
-    <cfRule type="containsText" dxfId="0" priority="62" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="85" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="61">
+    <cfRule type="containsBlanks" dxfId="1" priority="84">
       <formula>LEN(TRIM(DK8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ8">
-    <cfRule type="containsText" dxfId="0" priority="14" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="37" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="13">
+    <cfRule type="containsBlanks" dxfId="1" priority="36">
       <formula>LEN(TRIM(DQ8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DS8">
-    <cfRule type="containsText" dxfId="0" priority="26" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="49" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DS8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="25">
+    <cfRule type="containsBlanks" dxfId="1" priority="48">
       <formula>LEN(TRIM(DS8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DU8">
-    <cfRule type="containsText" dxfId="0" priority="30" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="53" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DU8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="29">
+    <cfRule type="containsBlanks" dxfId="1" priority="52">
       <formula>LEN(TRIM(DU8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DW8">
-    <cfRule type="containsText" dxfId="0" priority="50" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="73" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DW8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="49">
+    <cfRule type="containsBlanks" dxfId="1" priority="72">
       <formula>LEN(TRIM(DW8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DY8">
-    <cfRule type="containsText" dxfId="0" priority="8" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="31" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DY8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="7">
+    <cfRule type="containsBlanks" dxfId="1" priority="30">
       <formula>LEN(TRIM(DY8))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="EE8">
+    <cfRule type="containsText" dxfId="0" priority="20" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EE8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="19">
+      <formula>LEN(TRIM(EE8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EG8">
+    <cfRule type="containsText" dxfId="0" priority="12" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EG8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="11">
+      <formula>LEN(TRIM(EG8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="DE10">
-    <cfRule type="containsText" dxfId="0" priority="94" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="117" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="93">
+    <cfRule type="containsBlanks" dxfId="1" priority="116">
       <formula>LEN(TRIM(DE10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI10">
-    <cfRule type="containsText" dxfId="0" priority="66" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="89" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="65">
+    <cfRule type="containsBlanks" dxfId="1" priority="88">
       <formula>LEN(TRIM(DI10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK10">
-    <cfRule type="containsText" dxfId="0" priority="60" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="83" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="59">
+    <cfRule type="containsBlanks" dxfId="1" priority="82">
       <formula>LEN(TRIM(DK10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ10">
-    <cfRule type="containsText" dxfId="0" priority="16" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="39" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="15">
+    <cfRule type="containsBlanks" dxfId="1" priority="38">
       <formula>LEN(TRIM(DQ10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DS10">
-    <cfRule type="containsText" dxfId="0" priority="24" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="47" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DS10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="23">
+    <cfRule type="containsBlanks" dxfId="1" priority="46">
       <formula>LEN(TRIM(DS10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DW10">
-    <cfRule type="containsText" dxfId="0" priority="48" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="71" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DW10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="47">
+    <cfRule type="containsBlanks" dxfId="1" priority="70">
       <formula>LEN(TRIM(DW10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DY10">
-    <cfRule type="containsText" dxfId="0" priority="6" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="29" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DY10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="5">
+    <cfRule type="containsBlanks" dxfId="1" priority="28">
       <formula>LEN(TRIM(DY10))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="EG10">
+    <cfRule type="containsText" dxfId="0" priority="10" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EG10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="9">
+      <formula>LEN(TRIM(EG10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="CR11">
-    <cfRule type="containsText" dxfId="0" priority="118" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="141" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",CR11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CT11">
-    <cfRule type="containsText" dxfId="0" priority="117" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="140" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",CT11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DX11">
-    <cfRule type="containsText" dxfId="0" priority="9" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="32" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DX11)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="EF11">
+    <cfRule type="containsText" dxfId="0" priority="21" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EF11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="DC12">
-    <cfRule type="containsText" dxfId="0" priority="108" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="131" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DC12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="107">
+    <cfRule type="containsBlanks" dxfId="1" priority="130">
       <formula>LEN(TRIM(DC12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DE12">
-    <cfRule type="containsText" dxfId="0" priority="96" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="119" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="95">
+    <cfRule type="containsBlanks" dxfId="1" priority="118">
       <formula>LEN(TRIM(DE12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG12">
-    <cfRule type="containsText" dxfId="0" priority="84" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="107" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="83">
+    <cfRule type="containsBlanks" dxfId="1" priority="106">
       <formula>LEN(TRIM(DG12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI12">
-    <cfRule type="containsText" dxfId="0" priority="68" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="91" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="67">
+    <cfRule type="containsBlanks" dxfId="1" priority="90">
       <formula>LEN(TRIM(DI12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ12">
-    <cfRule type="containsText" dxfId="0" priority="20" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="43" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="19">
+    <cfRule type="containsBlanks" dxfId="1" priority="42">
       <formula>LEN(TRIM(DQ12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DS12">
-    <cfRule type="containsText" dxfId="0" priority="22" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="45" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DS12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="21">
+    <cfRule type="containsBlanks" dxfId="1" priority="44">
       <formula>LEN(TRIM(DS12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DU12">
-    <cfRule type="containsText" dxfId="0" priority="32" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="55" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DU12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="31">
+    <cfRule type="containsBlanks" dxfId="1" priority="54">
       <formula>LEN(TRIM(DU12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DW12">
-    <cfRule type="containsText" dxfId="0" priority="46" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="69" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DW12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="45">
+    <cfRule type="containsBlanks" dxfId="1" priority="68">
       <formula>LEN(TRIM(DW12))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="EE12">
+    <cfRule type="containsText" dxfId="0" priority="18" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EE12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="17">
+      <formula>LEN(TRIM(EE12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EG12">
+    <cfRule type="containsText" dxfId="0" priority="8" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EG12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="7">
+      <formula>LEN(TRIM(EG12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="DC14">
-    <cfRule type="containsText" dxfId="0" priority="106" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="129" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DC14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="105">
+    <cfRule type="containsBlanks" dxfId="1" priority="128">
       <formula>LEN(TRIM(DC14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DE14">
-    <cfRule type="containsText" dxfId="0" priority="98" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="121" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="97">
+    <cfRule type="containsBlanks" dxfId="1" priority="120">
       <formula>LEN(TRIM(DE14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI14">
-    <cfRule type="containsText" dxfId="0" priority="70" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="93" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="69">
+    <cfRule type="containsBlanks" dxfId="1" priority="92">
       <formula>LEN(TRIM(DI14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK14">
-    <cfRule type="containsText" dxfId="0" priority="58" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="81" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="57">
+    <cfRule type="containsBlanks" dxfId="1" priority="80">
       <formula>LEN(TRIM(DK14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ14">
-    <cfRule type="containsText" dxfId="0" priority="18" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="41" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="17">
+    <cfRule type="containsBlanks" dxfId="1" priority="40">
       <formula>LEN(TRIM(DQ14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DS14">
-    <cfRule type="containsText" dxfId="0" priority="34" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="57" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DS14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="33">
+    <cfRule type="containsBlanks" dxfId="1" priority="56">
       <formula>LEN(TRIM(DS14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DW14">
-    <cfRule type="containsText" dxfId="0" priority="44" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="67" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DW14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="43">
+    <cfRule type="containsBlanks" dxfId="1" priority="66">
       <formula>LEN(TRIM(DW14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DY14">
-    <cfRule type="containsText" dxfId="0" priority="4" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="27" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DY14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="3">
+    <cfRule type="containsBlanks" dxfId="1" priority="26">
       <formula>LEN(TRIM(DY14))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="EE14">
+    <cfRule type="containsText" dxfId="0" priority="16" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EE14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="15">
+      <formula>LEN(TRIM(EE14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EG14">
+    <cfRule type="containsText" dxfId="0" priority="6" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EG14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="5">
+      <formula>LEN(TRIM(EG14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="DE16">
-    <cfRule type="containsText" dxfId="0" priority="100" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="123" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="99">
+    <cfRule type="containsBlanks" dxfId="1" priority="122">
       <formula>LEN(TRIM(DE16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG16">
-    <cfRule type="containsText" dxfId="0" priority="82" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="105" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="81">
+    <cfRule type="containsBlanks" dxfId="1" priority="104">
       <formula>LEN(TRIM(DG16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI16">
-    <cfRule type="containsText" dxfId="0" priority="72" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="95" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="71">
+    <cfRule type="containsBlanks" dxfId="1" priority="94">
       <formula>LEN(TRIM(DI16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK16">
-    <cfRule type="containsText" dxfId="0" priority="56" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="79" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="55">
+    <cfRule type="containsBlanks" dxfId="1" priority="78">
       <formula>LEN(TRIM(DK16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DS16">
-    <cfRule type="containsText" dxfId="0" priority="36" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="59" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DS16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="35">
+    <cfRule type="containsBlanks" dxfId="1" priority="58">
       <formula>LEN(TRIM(DS16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DU16">
-    <cfRule type="containsText" dxfId="0" priority="40" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="63" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DU16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="39">
+    <cfRule type="containsBlanks" dxfId="1" priority="62">
       <formula>LEN(TRIM(DU16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DW16">
-    <cfRule type="containsText" dxfId="0" priority="42" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="65" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DW16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="41">
+    <cfRule type="containsBlanks" dxfId="1" priority="64">
       <formula>LEN(TRIM(DW16))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="EG16">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EG16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="3">
+      <formula>LEN(TRIM(EG16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="DE18">
-    <cfRule type="containsText" dxfId="0" priority="102" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="125" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="101">
+    <cfRule type="containsBlanks" dxfId="1" priority="124">
       <formula>LEN(TRIM(DE18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG18">
-    <cfRule type="containsText" dxfId="0" priority="80" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="103" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="79">
+    <cfRule type="containsBlanks" dxfId="1" priority="102">
       <formula>LEN(TRIM(DG18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI18">
-    <cfRule type="containsText" dxfId="0" priority="74" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="97" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="73">
+    <cfRule type="containsBlanks" dxfId="1" priority="96">
       <formula>LEN(TRIM(DI18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK18">
-    <cfRule type="containsText" dxfId="0" priority="54" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="77" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="53">
+    <cfRule type="containsBlanks" dxfId="1" priority="76">
       <formula>LEN(TRIM(DK18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ18">
-    <cfRule type="containsText" dxfId="0" priority="12" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="35" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="11">
+    <cfRule type="containsBlanks" dxfId="1" priority="34">
       <formula>LEN(TRIM(DQ18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DY18">
-    <cfRule type="containsText" dxfId="0" priority="2" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="25" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DY18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="1">
+    <cfRule type="containsBlanks" dxfId="1" priority="24">
       <formula>LEN(TRIM(DY18))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="EG18">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EG18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="1">
+      <formula>LEN(TRIM(EG18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="DC20">
-    <cfRule type="containsText" dxfId="0" priority="104" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="127" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DC20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="103">
+    <cfRule type="containsBlanks" dxfId="1" priority="126">
       <formula>LEN(TRIM(DC20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG20">
-    <cfRule type="containsText" dxfId="0" priority="78" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="101" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="77">
+    <cfRule type="containsBlanks" dxfId="1" priority="100">
       <formula>LEN(TRIM(DG20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI20">
-    <cfRule type="containsText" dxfId="0" priority="76" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="99" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="75">
+    <cfRule type="containsBlanks" dxfId="1" priority="98">
       <formula>LEN(TRIM(DI20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK20">
-    <cfRule type="containsText" dxfId="0" priority="52" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="75" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="51">
+    <cfRule type="containsBlanks" dxfId="1" priority="74">
       <formula>LEN(TRIM(DK20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DU20">
-    <cfRule type="containsText" dxfId="0" priority="38" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="61" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DU20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="37">
+    <cfRule type="containsBlanks" dxfId="1" priority="60">
       <formula>LEN(TRIM(DU20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DX3:DX20">
-    <cfRule type="containsText" dxfId="2" priority="10" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="33" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",DX3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B3:B21 D3:D21 KV3:KV21 LH3:LH21 KT3:KT21 KR3:KR21 F3:F21 KP3:KP21 KN3:KN21 KL3:KL21 H3:H21 KJ3:KJ21 KH3:KH21 KF3:KF21 J3:J21 KD3:KD21 KB3:KB21 JZ3:JZ21 L3:L21 JX3:JX21 JV3:JV21 JT3:JT21 N3:N21 JR3:JR21 P3:P21 JP3:JP21 R3:R21 JN3:JN21 T3:T21 JL3:JL21 V3:V21 JJ3:JJ21 X3:X21 JH3:JH21 JF3:JF21 Z3:Z21 JD3:JD21 JB3:JB21 AB3:AB21 IZ3:IZ21 IX3:IX21 AD3:AD21 IV3:IV21 IT3:IT21 AF3:AF21 IR3:IR21 IP3:IP21 AH3:AH21 IN3:IN21 IL3:IL21 AJ3:AJ21 IJ3:IJ21 IH3:IH21 AL3:AL21 IF3:IF21 ID3:ID21 AN3:AN21 IB3:IB21 HZ3:HZ21 AP3:AP21 HX3:HX21 HV3:HV21 AR3:AR21 HT3:HT21 HR3:HR21 AT3:AT21 HP3:HP21 HN3:HN21 AV3:AV21 HL3:HL21 HJ3:HJ21 AX3:AX21 HH3:HH21 HF3:HF21 AZ3:AZ21 HD3:HD21 HB3:HB21 BB3:BB21 GZ3:GZ21 GX3:GX21 BD3:BD21 GV3:GV21 GT3:GT21 BF3:BF21 GR3:GR21 GP3:GP21 BH3:BH21 GN3:GN21 GL3:GL21 BJ3:BJ21 GJ3:GJ21 GH3:GH21 BL3:BL21 GF3:GF21 GD3:GD21 BN3:BN21 GB3:GB21 FZ3:FZ21 BP3:BP21 FX3:FX21 FV3:FV21 BR3:BR21 FT3:FT21 FR3:FR21 BT3:BT21 FP3:FP21 FN3:FN21 BV3:BV21 FL3:FL21 FJ3:FJ21 BX3:BX21 FH3:FH21 FF3:FF21 BZ3:BZ21 FD3:FD21 FB3:FB21 CB3:CB21 EZ3:EZ21 EX3:EX21 CD3:CD21 EV3:EV21 ET3:ET21 CF3:CF21 ER3:ER21 EP3:EP21 CH3:CH21 EN3:EN21 EL3:EL21 CJ3:CJ21 EJ3:EJ21 EH3:EH21 CL3:CL21 EF3:EF21 ED3:ED21 CN3:CN21 EB3:EB21 DZ3:DZ21 CP3:CP21 DX21 DV21 CR3:CR21 DT21 DR21 CT3:CT21 DP21 DN3:DN21 CV3:CV21 DL3:DL21 DJ21 CX3:CX21 DH21 DF21 CZ3:CZ21 DD21 DB21 LI11 KU11 KS11 KW11:LG11 KQ11 KO11 KM11 LF12:LF21 KK11 KI11 KG11 LD12:LD21 KE11 KC11 KA11 LB12:LB21 JY11 JW11 JU11 KZ12:KZ21 JS11 JQ11 JO11 JM11 JK11 JI11 JG11 W11 JE11 JC11 Y11 JA11 IY11 AA11 IW11 IU11 AC11 IS11 IQ11 AE11 IO11 IM11 AG11 IK11 II11 AI11 IG11 IE11 AK11 IC11 IA11 AM11 HY11 HW11 AO11 HU11 HS11 AQ11 HQ11 HO11 AS11 HM11 HK11 AU11 HI11 HG11 AW11 HE11 HC11 AY11 HA11 GY11 BA11 GW11 GU11 BC11 GS11 GQ11 BE11 GO11 GM11 BG11 GK11 GI11 BI11 GG11 GE11 BK11 GC11 GA11 BM11 FY11 FW11 BO11 FU11 FS11 BQ11 FQ11 FO11 BS11 FM11 FK11 BU11 FI11 FG11 BW11 FE11 FC11 BY11 FA11 EY11 CA11 EW11 EU11 CC11 ES11 EQ11 CE11 EO11 EM11 CG11 EK11 EI11 CI11 EG11 EE11 CK11 EC11 EA11 CM11 DY11 CO11 CQ11 DO11 CS11 DM11 CU11 CW11 CY11 DA11 KX3:KX10 KX12:KX21 KZ3:KZ10 LB3:LB10 LD3:LD10 LF3:LF10">
-    <cfRule type="containsText" dxfId="2" priority="123" operator="between" text="占">
+  <conditionalFormatting sqref="ED3:ED20">
+    <cfRule type="containsText" dxfId="2" priority="23" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",ED3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EF3:EF20">
+    <cfRule type="containsText" dxfId="2" priority="22" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",EF3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3:B21 D3:D21 KV3:KV21 LH3:LH21 KT3:KT21 KR3:KR21 F3:F21 KP3:KP21 KN3:KN21 KL3:KL21 H3:H21 KJ3:KJ21 KH3:KH21 KF3:KF21 J3:J21 KD3:KD21 KB3:KB21 JZ3:JZ21 L3:L21 JX3:JX21 JV3:JV21 JT3:JT21 N3:N21 JR3:JR21 P3:P21 JP3:JP21 R3:R21 JN3:JN21 T3:T21 JL3:JL21 V3:V21 JJ3:JJ21 X3:X21 JH3:JH21 JF3:JF21 Z3:Z21 JD3:JD21 JB3:JB21 AB3:AB21 IZ3:IZ21 IX3:IX21 AD3:AD21 IV3:IV21 IT3:IT21 AF3:AF21 IR3:IR21 IP3:IP21 AH3:AH21 IN3:IN21 IL3:IL21 AJ3:AJ21 IJ3:IJ21 IH3:IH21 AL3:AL21 IF3:IF21 ID3:ID21 AN3:AN21 IB3:IB21 HZ3:HZ21 AP3:AP21 HX3:HX21 HV3:HV21 AR3:AR21 HT3:HT21 HR3:HR21 AT3:AT21 HP3:HP21 HN3:HN21 AV3:AV21 HL3:HL21 HJ3:HJ21 AX3:AX21 HH3:HH21 HF3:HF21 AZ3:AZ21 HD3:HD21 HB3:HB21 BB3:BB21 GZ3:GZ21 GX3:GX21 BD3:BD21 GV3:GV21 GT3:GT21 BF3:BF21 GR3:GR21 GP3:GP21 BH3:BH21 GN3:GN21 GL3:GL21 BJ3:BJ21 GJ3:GJ21 GH3:GH21 BL3:BL21 GF3:GF21 GD3:GD21 BN3:BN21 GB3:GB21 FZ3:FZ21 BP3:BP21 FX3:FX21 FV3:FV21 BR3:BR21 FT3:FT21 FR3:FR21 BT3:BT21 FP3:FP21 FN3:FN21 BV3:BV21 FL3:FL21 FJ3:FJ21 BX3:BX21 FH3:FH21 FF3:FF21 BZ3:BZ21 FD3:FD21 FB3:FB21 CB3:CB21 EZ3:EZ21 EX3:EX21 CD3:CD21 EV3:EV21 ET3:ET21 CF3:CF21 ER3:ER21 EP3:EP21 CH3:CH21 EN3:EN21 EL3:EL21 CJ3:CJ21 EJ3:EJ21 EH3:EH21 CL3:CL21 EF21 ED21 CN3:CN21 EB3:EB21 DZ3:DZ21 CP3:CP21 DX21 DV21 CR3:CR21 DT21 DR21 CT3:CT21 DP21 DN3:DN21 CV3:CV21 DL3:DL21 DJ21 CX3:CX21 DH21 DF21 CZ3:CZ21 DD21 DB21 LI11 KU11 KS11 KW11:LG11 KQ11 KO11 KM11 LF12:LF21 KK11 KI11 KG11 LD12:LD21 KE11 KC11 KA11 LB12:LB21 JY11 JW11 JU11 KZ12:KZ21 JS11 JQ11 JO11 JM11 JK11 JI11 JG11 W11 JE11 JC11 Y11 JA11 IY11 AA11 IW11 IU11 AC11 IS11 IQ11 AE11 IO11 IM11 AG11 IK11 II11 AI11 IG11 IE11 AK11 IC11 IA11 AM11 HY11 HW11 AO11 HU11 HS11 AQ11 HQ11 HO11 AS11 HM11 HK11 AU11 HI11 HG11 AW11 HE11 HC11 AY11 HA11 GY11 BA11 GW11 GU11 BC11 GS11 GQ11 BE11 GO11 GM11 BG11 GK11 GI11 BI11 GG11 GE11 BK11 GC11 GA11 BM11 FY11 FW11 BO11 FU11 FS11 BQ11 FQ11 FO11 BS11 FM11 FK11 BU11 FI11 FG11 BW11 FE11 FC11 BY11 FA11 EY11 CA11 EW11 EU11 CC11 ES11 EQ11 CE11 EO11 EM11 CG11 EK11 EI11 CI11 EG11 EE11 CK11 EC11 EA11 CM11 DY11 CO11 CQ11 DO11 CS11 DM11 CU11 CW11 CY11 DA11 KX3:KX10 KX12:KX21 KZ3:KZ10 LB3:LB10 LD3:LD10 LF3:LF10">
+    <cfRule type="containsText" dxfId="2" priority="146" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",B3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3 C5 G5 E5 G3 E3 I3 I5 K3 M3 K5 M5 LI5 LG5 LE5 LC5 LA5 KY5 KW5 KU5 KS5 KQ5 O3 Q3 S3 U3 W3 Y3 AA3 AC3 AE3 AG3 AI3 AK3 AM3 AO3 AQ3 AS3 AU3 AW3 AY3 BA3 BC3 BE3 BG3 BI3 BK3 BM3 BO3 BQ3 BS3 BU3 BW3 BY3 CA3 CC3 CE3 CG3 CI3 CK3 CM3 CO3 CQ3 CS3 CU3 CW3 CY3 DA3 DM3 DO3 DY3 EA3 EC3 EE3 EG3 EI3 EK3 EM3 EO3 EQ3 ES3 EU3 EW3 EY3 FA3 FC3 FE3 FG3 FI3 FK3 FM3 FO3 FQ3 FS3 FU3 FW3 FY3 GA3 GC3 GE3 GG3 GI3 GK3 GM3 GO3 GQ3 GS3 GU3 GW3 GY3 HA3 HC3 HE3 HG3 HI3 HK3 HM3 HO3 HQ3 HS3 HU3 HW3 HY3 IA3 IC3 IE3 IG3 II3 IK3 IM3 IO3 IQ3 IS3 IU3 IW3 IY3 JA3 JC3 JE3 JG3 JI3 JK3 JM3 JO3 JQ3 JS3 JU3 JW3 JY3 KA3 KC3 KE3 KG3 KI3 KK3 KM3 KO3 KQ3 KS3 KU3 KW3 KY3 LA3 LC3 LE3 LG3 LI3 KO5 KM5 KK5 KI5 O5 Q5 S5 U5 W5 Y5 AA5 AC5 AE5 AG5 AI5 AK5 AM5 AO5 AQ5 AS5 AU5 AW5 AY5 BA5 BC5 BE5 BG5 BI5 BK5 BM5 BO5 BQ5 BS5 BU5 BW5 BY5 CA5 CC5 CE5 CG5 CI5 CK5 CM5 CO5 CQ5 CS5 CU5 CW5 CY5 DA5 DM5 DO5 DY5 EA5 EC5 EE5 EG5 EI5 EK5 EM5 EO5 EQ5 ES5 EU5 EW5 EY5 FA5 FC5 FE5 FG5 FI5 FK5 FM5 FO5 FQ5 FS5 FU5 FW5 FY5 GA5 GC5 GE5 GG5 GI5 GK5 GM5 GO5 GQ5 GS5 GU5 GW5 GY5 HA5 HC5 HE5 HG5 HI5 HK5 HM5 HO5 HQ5 HS5 HU5 HW5 HY5 IA5 IC5 IE5 IG5 II5 IK5 IM5 IO5 IQ5 IS5 IU5 IW5 IY5 JA5 JC5 JE5 JG5 JI5 JK5 JM5 JO5 JQ5 JS5 JU5 JW5 JY5 KA5 KC5 KE5 KG5 C8 G10 E10 G8 E8 G20 E20 G18 E18 G16 E16 G14 E14 G12 E12 C10 C12 C14 C16 C18 C20 I12 I14 I16 I18 I20 I8 I10 LI20 LG20 LE20 LC20 K8 M8 K10 M10 K12 M12 K14 M14 K16 M16 K18 M18 K20 M20 HW20 HU20 HS20 HQ20 HO20 HM20 HK20 HI20 HG20 HE20 HC20 HA20 GY20 GW20 GU20 GS20 GQ20 GO20 GM20 GK20 GI20 GG20 GE20 GC20 GA20 FY20 FW20 FU20 FS20 FQ20 FO20 FM20 FK20 FI20 FG20 FE20 FC20 FA20 EY20 EW20 EU20 ES20 EQ20 EO20 EM20 EK20 EI20 EG20 EE20 EC20 EA20 DY20 DO20 DM20 DA20 CY20 CW20 CU20 CS20 CQ20 CO20 CM20 CK20 CI20 CG20 CE20 CC20 CA20 BY20 BW20 BU20 BS20 BQ20 BO20 BM20 BK20 BI20 BG20 BE20 BC20 BA20 AY20 AW20 AU20 AS20 AQ20 AO20 AM20 AK20 AI20 AG20 AE20 AC20 AA20 Y20 W20 U20 S20 Q20 O20 HY20 IA20 JI20 JK20 LI18 LG18 LE18 LC18 LA18 KY18 KW18 KU18 KS18 KQ18 KO18 KM18 KK18 KI18 KG18 KE18 KC18 KA18 JY18 JW18 JU18 JS18 JQ18 JO18 JM18 JK18 JI18 JG18 JE18 JC18 JA18 IY18 IW18 IU18 IS18 IQ18 IO18 IM18 IK18 II18 IG18 IE18 IC18 IA18 HY18 HW18 HU18 HS18 HQ18 HO18 HM18 HK18 HI18 HG18 HE18 HC18 HA18 GY18 GW18 GU18 GS18 GQ18 GO18 GM18 GK18 GI18 GG18 GE18 GC18 GA18 FY18 FW18 FU18 FS18 FQ18 FO18 FM18 FK18 FI18 FG18 FE18 FC18 FA18 EY18 EW18 EU18 ES18 EQ18 EO18 EM18 EK18 EI18 EG18 EE18 EC18 EA18 DO18 DM18 DA18 CY18 CW18 CU18 CS18 CQ18 CO18 CM18 CK18 CI18 CG18 CE18 CC18 CA18 BY18 BW18 BU18 BS18 BQ18 BO18 BM18 BK18 BI18 BG18 BE18 BC18 BA18 AY18 AW18 AU18 AS18 AQ18 AO18 AM18 AK18 AI18 AG18 AE18 AC18 AA18 Y18 W18 U18 S18 Q18 O18 IC20 IE20 JM20 JO20 LI16 LG16 LE16 LC16 LA16 KY16 KW16 KU16 KS16 KQ16 KO16 KM16 KK16 KI16 KG16 KE16 KC16 KA16 JY16 JW16 JU16 JS16 JQ16 JO16 JM16 JK16 JI16 JG16 JE16 JC16 JA16 IY16 IW16 IU16 IS16 IQ16 IO16 IM16 IK16 II16 IG16 IE16 IC16 IA16 HY16 HW16 HU16 HS16 HQ16 HO16 HM16 HK16 HI16 HG16 HE16 HC16 HA16 GY16 GW16 GU16 GS16 GQ16 GO16 GM16 GK16 GI16 GG16 GE16 GC16 GA16 FY16 FW16 FU16 FS16 FQ16 FO16 FM16 FK16 FI16 FG16 FE16 FC16 FA16 EY16 EW16 EU16 ES16 EQ16 EO16 EM16 EK16 EI16 EG16 EE16 EC16 EA16 DY16 DO16 DM16 DA16 CY16 CW16 CU16 CS16 CQ16 CO16 CM16 CK16 CI16 CG16 CE16 CC16 CA16 BY16 BW16 BU16 BS16 BQ16 BO16 BM16 BK16 BI16 BG16 BE16 BC16 BA16 AY16 AW16 AU16 AS16 AQ16 AO16 AM16 AK16 AI16 AG16 AE16 AC16 AA16 Y16 W16 U16 S16 Q16 O16 IG20 II20 JQ20 JS20 LI14 LG14 LE14 LC14 LA14 KY14 KW14 KU14 KS14 KQ14 KO14 KM14 KK14 KI14 KG14 KE14 KC14 KA14 JY14 JW14 JU14 JS14 JQ14 JO14 JM14 JK14 JI14 JG14 JE14 JC14 JA14 IY14 IW14 IU14 IS14 IQ14 IO14 IM14 IK14 II14 IG14 IE14 IC14 IA14 HY14 HW14 HU14 HS14 HQ14 HO14 HM14 HK14 HI14 HG14 HE14 HC14 HA14 GY14 GW14 GU14 GS14 GQ14 GO14 GM14 GK14 GI14 GG14 GE14 GC14 GA14 FY14 FW14 FU14 FS14 FQ14 FO14 FM14 FK14 FI14 FG14 FE14 FC14 FA14 EY14 EW14 EU14 ES14 EQ14 EO14 EM14 EK14 EI14 EG14 EE14 EC14 EA14 DO14 DM14 DA14 CY14 CW14 CU14 CS14 CQ14 CO14 CM14 CK14 CI14 CG14 CE14 CC14 CA14 BY14 BW14 BU14 BS14 BQ14 BO14 BM14 BK14 BI14 BG14 BE14 BC14 BA14 AY14 AW14 AU14 AS14 AQ14 AO14 AM14 AK14 AI14 AG14 AE14 AC14 AA14 Y14 W14 U14 S14 Q14 O14 IK20 IM20 JU20 JW20 LI12 LG12 LE12 LC12 LA12 KY12 KW12 KU12 KS12 KQ12 KO12 KM12 KK12 KI12 KG12 KE12 KC12 KA12 JY12 JW12 JU12 JS12 JQ12 JO12 JM12 JK12 JI12 JG12 JE12 JC12 JA12 IY12 IW12 IU12 IS12 IQ12 IO12 IM12 IK12 II12 IG12 IE12 IC12 IA12 HY12 HW12 HU12 HS12 HQ12 HO12 HM12 HK12 HI12 HG12 HE12 HC12 HA12 GY12 GW12 GU12 GS12 GQ12 GO12 GM12 GK12 GI12 GG12 GE12 GC12 GA12 FY12 FW12 FU12 FS12 FQ12 FO12 FM12 FK12 FI12 FG12 FE12 FC12 FA12 EY12 EW12 EU12 ES12 EQ12 EO12 EM12 EK12 EI12 EG12 EE12 EC12 EA12 DY12 DO12 DM12 DA12 CY12 CW12 CU12 CS12 CQ12 CO12 CM12 CK12 CI12 CG12 CE12 CC12 CA12 BY12 BW12 BU12 BS12 BQ12 BO12 BM12 BK12 BI12 BG12 BE12 BC12 BA12 AY12 AW12 AU12 AS12 AQ12 AO12 AM12 AK12 AI12 AG12 AE12 AC12 AA12 Y12 W12 U12 S12 Q12 O12 IO20 IQ20 JY20 KA20 LI10 LG10 LE10 LC10 LA10 KY10 KW10 KU10 KS10 KQ10 KO10 KM10 KK10 KI10 KG10 KE10 KC10 KA10 JY10 JW10 JU10 JS10 JQ10 JO10 JM10 JK10 JI10 JG10 JE10 JC10 JA10 IY10 IW10 IU10 IS10 IQ10 IO10 IM10 IK10 II10 IG10 IE10 IC10 IA10 HY10 HW10 HU10 HS10 HQ10 HO10 HM10 HK10 HI10 HG10 HE10 HC10 HA10 GY10 GW10 GU10 GS10 GQ10 GO10 GM10 GK10 GI10 GG10 GE10 GC10 GA10 FY10 FW10 FU10 FS10 FQ10 FO10 FM10 FK10 FI10 FG10 FE10 FC10 FA10 EY10 EW10 EU10 ES10 EQ10 EO10 EM10 EK10 EI10 EG10 EE10 EC10 EA10 DO10 DM10 DA10 CY10 CW10 CU10 CS10 CQ10 CO10 CM10 CK10 CI10 CG10 CE10 CC10 CA10 BY10 BW10 BU10 BS10 BQ10 BO10 BM10 BK10 BI10 BG10 BE10 BC10 BA10 AY10 AW10 AU10 AS10 AQ10 AO10 AM10 AK10 AI10 AG10 AE10 AC10 AA10 Y10 W10 U10 S10 Q10 O10 IS20 IU20 KC20 KE20 LI8 LG8 LE8 LC8 LA8 KY8 KW8 KU8 KS8 KQ8 KO8 KM8 KK8 KI8 KG8 KE8 KC8 KA8 JY8 JW8 JU8 JS8 JQ8 JO8 JM8 JK8 JI8 JG8 JE8 JC8 JA8 IY8 IW8 IU8 IS8 IQ8 IO8 IM8 IK8 II8 IG8 IE8 IC8 IA8 HY8 HW8 HU8 HS8 HQ8 HO8 HM8 HK8 HI8 HG8 HE8 HC8 HA8 GY8 GW8 GU8 GS8 GQ8 GO8 GM8 GK8 GI8 GG8 GE8 GC8 GA8 FY8 FW8 FU8 FS8 FQ8 FO8 FM8 FK8 FI8 FG8 FE8 FC8 FA8 EY8 EW8 EU8 ES8 EQ8 EO8 EM8 EK8 EI8 EG8 EE8 EC8 EA8 DO8 DM8 DA8 CY8 CW8 CU8 CS8 CQ8 CO8 CM8 CK8 CI8 CG8 CE8 CC8 CA8 BY8 BW8 BU8 BS8 BQ8 BO8 BM8 BK8 BI8 BG8 BE8 BC8 BA8 AY8 AW8 AU8 AS8 AQ8 AO8 AM8 AK8 AI8 AG8 AE8 AC8 AA8 Y8 W8 U8 S8 Q8 O8 IW20 IY20 KG20 KI20 LA20 KY20 KW20 KU20 KS20 KQ20 KO20 JG20 JE20 KM20 KK20 JC20 JA20">
-    <cfRule type="containsBlanks" dxfId="1" priority="121">
+  <conditionalFormatting sqref="C3 C5 G5 E5 G3 E3 I3 I5 K3 M3 K5 M5 LI5 LG5 LE5 LC5 LA5 KY5 KW5 KU5 KS5 KQ5 O3 Q3 S3 U3 W3 Y3 AA3 AC3 AE3 AG3 AI3 AK3 AM3 AO3 AQ3 AS3 AU3 AW3 AY3 BA3 BC3 BE3 BG3 BI3 BK3 BM3 BO3 BQ3 BS3 BU3 BW3 BY3 CA3 CC3 CE3 CG3 CI3 CK3 CM3 CO3 CQ3 CS3 CU3 CW3 CY3 DA3 DM3 DO3 DY3 EA3 EC3 EE3 EG3 EI3 EK3 EM3 EO3 EQ3 ES3 EU3 EW3 EY3 FA3 FC3 FE3 FG3 FI3 FK3 FM3 FO3 FQ3 FS3 FU3 FW3 FY3 GA3 GC3 GE3 GG3 GI3 GK3 GM3 GO3 GQ3 GS3 GU3 GW3 GY3 HA3 HC3 HE3 HG3 HI3 HK3 HM3 HO3 HQ3 HS3 HU3 HW3 HY3 IA3 IC3 IE3 IG3 II3 IK3 IM3 IO3 IQ3 IS3 IU3 IW3 IY3 JA3 JC3 JE3 JG3 JI3 JK3 JM3 JO3 JQ3 JS3 JU3 JW3 JY3 KA3 KC3 KE3 KG3 KI3 KK3 KM3 KO3 KQ3 KS3 KU3 KW3 KY3 LA3 LC3 LE3 LG3 LI3 KO5 KM5 KK5 KI5 O5 Q5 S5 U5 W5 Y5 AA5 AC5 AE5 AG5 AI5 AK5 AM5 AO5 AQ5 AS5 AU5 AW5 AY5 BA5 BC5 BE5 BG5 BI5 BK5 BM5 BO5 BQ5 BS5 BU5 BW5 BY5 CA5 CC5 CE5 CG5 CI5 CK5 CM5 CO5 CQ5 CS5 CU5 CW5 CY5 DA5 DM5 DO5 DY5 EA5 EC5 EE5 EI5 EK5 EM5 EO5 EQ5 ES5 EU5 EW5 EY5 FA5 FC5 FE5 FG5 FI5 FK5 FM5 FO5 FQ5 FS5 FU5 FW5 FY5 GA5 GC5 GE5 GG5 GI5 GK5 GM5 GO5 GQ5 GS5 GU5 GW5 GY5 HA5 HC5 HE5 HG5 HI5 HK5 HM5 HO5 HQ5 HS5 HU5 HW5 HY5 IA5 IC5 IE5 IG5 II5 IK5 IM5 IO5 IQ5 IS5 IU5 IW5 IY5 JA5 JC5 JE5 JG5 JI5 JK5 JM5 JO5 JQ5 JS5 JU5 JW5 JY5 KA5 KC5 KE5 KG5 C8 G10 E10 G8 E8 G20 E20 G18 E18 G16 E16 G14 E14 G12 E12 C10 C12 C14 C16 C18 C20 I12 I14 I16 I18 I20 I8 I10 LI20 LG20 LE20 LC20 K8 M8 K10 M10 K12 M12 K14 M14 K16 M16 K18 M18 K20 M20 HW20 HU20 HS20 HQ20 HO20 HM20 HK20 HI20 HG20 HE20 HC20 HA20 GY20 GW20 GU20 GS20 GQ20 GO20 GM20 GK20 GI20 GG20 GE20 GC20 GA20 FY20 FW20 FU20 FS20 FQ20 FO20 FM20 FK20 FI20 FG20 FE20 FC20 FA20 EY20 EW20 EU20 ES20 EQ20 EO20 EM20 EK20 EI20 EG20 EE20 EC20 EA20 DY20 DO20 DM20 DA20 CY20 CW20 CU20 CS20 CQ20 CO20 CM20 CK20 CI20 CG20 CE20 CC20 CA20 BY20 BW20 BU20 BS20 BQ20 BO20 BM20 BK20 BI20 BG20 BE20 BC20 BA20 AY20 AW20 AU20 AS20 AQ20 AO20 AM20 AK20 AI20 AG20 AE20 AC20 AA20 Y20 W20 U20 S20 Q20 O20 HY20 IA20 JI20 JK20 LI18 LG18 LE18 LC18 LA18 KY18 KW18 KU18 KS18 KQ18 KO18 KM18 KK18 KI18 KG18 KE18 KC18 KA18 JY18 JW18 JU18 JS18 JQ18 JO18 JM18 JK18 JI18 JG18 JE18 JC18 JA18 IY18 IW18 IU18 IS18 IQ18 IO18 IM18 IK18 II18 IG18 IE18 IC18 IA18 HY18 HW18 HU18 HS18 HQ18 HO18 HM18 HK18 HI18 HG18 HE18 HC18 HA18 GY18 GW18 GU18 GS18 GQ18 GO18 GM18 GK18 GI18 GG18 GE18 GC18 GA18 FY18 FW18 FU18 FS18 FQ18 FO18 FM18 FK18 FI18 FG18 FE18 FC18 FA18 EY18 EW18 EU18 ES18 EQ18 EO18 EM18 EK18 EI18 EE18 EC18 EA18 DO18 DM18 DA18 CY18 CW18 CU18 CS18 CQ18 CO18 CM18 CK18 CI18 CG18 CE18 CC18 CA18 BY18 BW18 BU18 BS18 BQ18 BO18 BM18 BK18 BI18 BG18 BE18 BC18 BA18 AY18 AW18 AU18 AS18 AQ18 AO18 AM18 AK18 AI18 AG18 AE18 AC18 AA18 Y18 W18 U18 S18 Q18 O18 IC20 IE20 JM20 JO20 LI16 LG16 LE16 LC16 LA16 KY16 KW16 KU16 KS16 KQ16 KO16 KM16 KK16 KI16 KG16 KE16 KC16 KA16 JY16 JW16 JU16 JS16 JQ16 JO16 JM16 JK16 JI16 JG16 JE16 JC16 JA16 IY16 IW16 IU16 IS16 IQ16 IO16 IM16 IK16 II16 IG16 IE16 IC16 IA16 HY16 HW16 HU16 HS16 HQ16 HO16 HM16 HK16 HI16 HG16 HE16 HC16 HA16 GY16 GW16 GU16 GS16 GQ16 GO16 GM16 GK16 GI16 GG16 GE16 GC16 GA16 FY16 FW16 FU16 FS16 FQ16 FO16 FM16 FK16 FI16 FG16 FE16 FC16 FA16 EY16 EW16 EU16 ES16 EQ16 EO16 EM16 EK16 EI16 EE16 EC16 EA16 DY16 DO16 DM16 DA16 CY16 CW16 CU16 CS16 CQ16 CO16 CM16 CK16 CI16 CG16 CE16 CC16 CA16 BY16 BW16 BU16 BS16 BQ16 BO16 BM16 BK16 BI16 BG16 BE16 BC16 BA16 AY16 AW16 AU16 AS16 AQ16 AO16 AM16 AK16 AI16 AG16 AE16 AC16 AA16 Y16 W16 U16 S16 Q16 O16 IG20 II20 JQ20 JS20 LI14 LG14 LE14 LC14 LA14 KY14 KW14 KU14 KS14 KQ14 KO14 KM14 KK14 KI14 KG14 KE14 KC14 KA14 JY14 JW14 JU14 JS14 JQ14 JO14 JM14 JK14 JI14 JG14 JE14 JC14 JA14 IY14 IW14 IU14 IS14 IQ14 IO14 IM14 IK14 II14 IG14 IE14 IC14 IA14 HY14 HW14 HU14 HS14 HQ14 HO14 HM14 HK14 HI14 HG14 HE14 HC14 HA14 GY14 GW14 GU14 GS14 GQ14 GO14 GM14 GK14 GI14 GG14 GE14 GC14 GA14 FY14 FW14 FU14 FS14 FQ14 FO14 FM14 FK14 FI14 FG14 FE14 FC14 FA14 EY14 EW14 EU14 ES14 EQ14 EO14 EM14 EK14 EI14 EC14 EA14 DO14 DM14 DA14 CY14 CW14 CU14 CS14 CQ14 CO14 CM14 CK14 CI14 CG14 CE14 CC14 CA14 BY14 BW14 BU14 BS14 BQ14 BO14 BM14 BK14 BI14 BG14 BE14 BC14 BA14 AY14 AW14 AU14 AS14 AQ14 AO14 AM14 AK14 AI14 AG14 AE14 AC14 AA14 Y14 W14 U14 S14 Q14 O14 IK20 IM20 JU20 JW20 LI12 LG12 LE12 LC12 LA12 KY12 KW12 KU12 KS12 KQ12 KO12 KM12 KK12 KI12 KG12 KE12 KC12 KA12 JY12 JW12 JU12 JS12 JQ12 JO12 JM12 JK12 JI12 JG12 JE12 JC12 JA12 IY12 IW12 IU12 IS12 IQ12 IO12 IM12 IK12 II12 IG12 IE12 IC12 IA12 HY12 HW12 HU12 HS12 HQ12 HO12 HM12 HK12 HI12 HG12 HE12 HC12 HA12 GY12 GW12 GU12 GS12 GQ12 GO12 GM12 GK12 GI12 GG12 GE12 GC12 GA12 FY12 FW12 FU12 FS12 FQ12 FO12 FM12 FK12 FI12 FG12 FE12 FC12 FA12 EY12 EW12 EU12 ES12 EQ12 EO12 EM12 EK12 EI12 EC12 EA12 DY12 DO12 DM12 DA12 CY12 CW12 CU12 CS12 CQ12 CO12 CM12 CK12 CI12 CG12 CE12 CC12 CA12 BY12 BW12 BU12 BS12 BQ12 BO12 BM12 BK12 BI12 BG12 BE12 BC12 BA12 AY12 AW12 AU12 AS12 AQ12 AO12 AM12 AK12 AI12 AG12 AE12 AC12 AA12 Y12 W12 U12 S12 Q12 O12 IO20 IQ20 JY20 KA20 LI10 LG10 LE10 LC10 LA10 KY10 KW10 KU10 KS10 KQ10 KO10 KM10 KK10 KI10 KG10 KE10 KC10 KA10 JY10 JW10 JU10 JS10 JQ10 JO10 JM10 JK10 JI10 JG10 JE10 JC10 JA10 IY10 IW10 IU10 IS10 IQ10 IO10 IM10 IK10 II10 IG10 IE10 IC10 IA10 HY10 HW10 HU10 HS10 HQ10 HO10 HM10 HK10 HI10 HG10 HE10 HC10 HA10 GY10 GW10 GU10 GS10 GQ10 GO10 GM10 GK10 GI10 GG10 GE10 GC10 GA10 FY10 FW10 FU10 FS10 FQ10 FO10 FM10 FK10 FI10 FG10 FE10 FC10 FA10 EY10 EW10 EU10 ES10 EQ10 EO10 EM10 EK10 EI10 EE10 EC10 EA10 DO10 DM10 DA10 CY10 CW10 CU10 CS10 CQ10 CO10 CM10 CK10 CI10 CG10 CE10 CC10 CA10 BY10 BW10 BU10 BS10 BQ10 BO10 BM10 BK10 BI10 BG10 BE10 BC10 BA10 AY10 AW10 AU10 AS10 AQ10 AO10 AM10 AK10 AI10 AG10 AE10 AC10 AA10 Y10 W10 U10 S10 Q10 O10 IS20 IU20 KC20 KE20 LI8 LG8 LE8 LC8 LA8 KY8 KW8 KU8 KS8 KQ8 KO8 KM8 KK8 KI8 KG8 KE8 KC8 KA8 JY8 JW8 JU8 JS8 JQ8 JO8 JM8 JK8 JI8 JG8 JE8 JC8 JA8 IY8 IW8 IU8 IS8 IQ8 IO8 IM8 IK8 II8 IG8 IE8 IC8 IA8 HY8 HW8 HU8 HS8 HQ8 HO8 HM8 HK8 HI8 HG8 HE8 HC8 HA8 GY8 GW8 GU8 GS8 GQ8 GO8 GM8 GK8 GI8 GG8 GE8 GC8 GA8 FY8 FW8 FU8 FS8 FQ8 FO8 FM8 FK8 FI8 FG8 FE8 FC8 FA8 EY8 EW8 EU8 ES8 EQ8 EO8 EM8 EK8 EI8 EC8 EA8 DO8 DM8 DA8 CY8 CW8 CU8 CS8 CQ8 CO8 CM8 CK8 CI8 CG8 CE8 CC8 CA8 BY8 BW8 BU8 BS8 BQ8 BO8 BM8 BK8 BI8 BG8 BE8 BC8 BA8 AY8 AW8 AU8 AS8 AQ8 AO8 AM8 AK8 AI8 AG8 AE8 AC8 AA8 Y8 W8 U8 S8 Q8 O8 IW20 IY20 KG20 KI20 LA20 KY20 KW20 KU20 KS20 KQ20 KO20 JG20 JE20 KM20 KK20 JC20 JA20">
+    <cfRule type="containsBlanks" dxfId="1" priority="144">
       <formula>LEN(TRIM(C3))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C21 E3:E21 KW3:KW21 LI3:LI21 KU3:KU21 KS3:KS21 G3:G21 KQ3:KQ21 KO3:KO21 KM3:KM21 I3:I21 KK3:KK21 KI3:KI21 KG3:KG21 K3:K21 KE3:KE21 KC3:KC21 KA3:KA21 M3:M21 JY3:JY21 JW3:JW21 JU3:JU21 O3:O21 JS3:JS21 Q3:Q21 JQ3:JQ21 S3:S21 JO3:JO21 U3:U21 JM3:JM21 W3:W21 JK3:JK21 Y3:Y21 JI3:JI21 JG3:JG21 AA3:AA21 JE3:JE21 JC3:JC21 AC3:AC21 JA3:JA21 IY3:IY21 AE3:AE21 IW3:IW21 IU3:IU21 AG3:AG21 IS3:IS21 IQ3:IQ21 AI3:AI21 IO3:IO21 IM3:IM21 AK3:AK21 IK3:IK21 II3:II21 AM3:AM21 IG3:IG21 IE3:IE21 AO3:AO21 IC3:IC21 IA3:IA21 AQ3:AQ21 HY3:HY21 HW3:HW21 AS3:AS21 HU3:HU21 HS3:HS21 AU3:AU21 HQ3:HQ21 HO3:HO21 AW3:AW21 HM3:HM21 HK3:HK21 AY3:AY21 HI3:HI21 HG3:HG21 BA3:BA21 HE3:HE21 HC3:HC21 BC3:BC21 HA3:HA21 GY3:GY21 BE3:BE21 GW3:GW21 GU3:GU21 BG3:BG21 GS3:GS21 GQ3:GQ21 BI3:BI21 GO3:GO21 GM3:GM21 BK3:BK21 GK3:GK21 GI3:GI21 BM3:BM21 GG3:GG21 GE3:GE21 BO3:BO21 GC3:GC21 GA3:GA21 BQ3:BQ21 FY3:FY21 FW3:FW21 BS3:BS21 FU3:FU21 FS3:FS21 BU3:BU21 FQ3:FQ21 FO3:FO21 BW3:BW21 FM3:FM21 FK3:FK21 BY3:BY21 FI3:FI21 FG3:FG21 CA3:CA21 FE3:FE21 FC3:FC21 CC3:CC21 FA3:FA21 EY3:EY21 CE3:CE21 EW3:EW21 EU3:EU21 CG3:CG21 ES3:ES21 EQ3:EQ21 CI3:CI21 EO3:EO21 EM3:EM21 CK3:CK21 EK3:EK21 EI3:EI21 CM3:CM21 EG3:EG21 EE3:EE21 CO3:CO21 EC3:EC21 EA3:EA21 CQ3:CQ21 DY3:DY7 DY9 DY11:DY13 DY15:DY17 DY19:DY21 DW21 CS3:CS21 DU21 DS21 CU3:CU21 DQ21 DO3:DO21 CW3:CW21 DM3:DM21 DK21 CY3:CY21 DI21 DG21 DA3:DA21 DE21 DC21 KV11 KT11 KX11:LH11 KR11 KP11 KN11 LG12:LG21 KL11 KJ11 KH11 LE12:LE21 KF11 KD11 KB11 LC12:LC21 JZ11 JX11 JV11 LA12:LA21 JT11 JR11 JP11 JN11 JL11 JJ11 JH11 X11 JF11 JD11 Z11 JB11 IZ11 AB11 IX11 IV11 AD11 IT11 IR11 AF11 IP11 IN11 AH11 IL11 IJ11 AJ11 IH11 IF11 AL11 ID11 IB11 AN11 HZ11 HX11 AP11 HV11 HT11 AR11 HR11 HP11 AT11 HN11 HL11 AV11 HJ11 HH11 AX11 HF11 HD11 AZ11 HB11 GZ11 BB11 GX11 GV11 BD11 GT11 GR11 BF11 GP11 GN11 BH11 GL11 GJ11 BJ11 GH11 GF11 BL11 GD11 GB11 BN11 FZ11 FX11 BP11 FV11 FT11 BR11 FR11 FP11 BT11 FN11 FL11 BV11 FJ11 FH11 BX11 FF11 FD11 BZ11 FB11 EZ11 CB11 EX11 EV11 CD11 ET11 ER11 CF11 EP11 EN11 CH11 EL11 EJ11 CJ11 EH11 EF11 CL11 ED11 EB11 CN11 DZ11 DN11 DL11 CV11 CX11 CZ11 KY3:KY10 KY12:KY21 LA3:LA10 LC3:LC10 LE3:LE10 LG3:LG10">
-    <cfRule type="containsText" dxfId="0" priority="122" operator="between" text="—">
+  <conditionalFormatting sqref="C3:C21 E3:E21 KW3:KW21 LI3:LI21 KU3:KU21 KS3:KS21 G3:G21 KQ3:KQ21 KO3:KO21 KM3:KM21 I3:I21 KK3:KK21 KI3:KI21 KG3:KG21 K3:K21 KE3:KE21 KC3:KC21 KA3:KA21 M3:M21 JY3:JY21 JW3:JW21 JU3:JU21 O3:O21 JS3:JS21 Q3:Q21 JQ3:JQ21 S3:S21 JO3:JO21 U3:U21 JM3:JM21 W3:W21 JK3:JK21 Y3:Y21 JI3:JI21 JG3:JG21 AA3:AA21 JE3:JE21 JC3:JC21 AC3:AC21 JA3:JA21 IY3:IY21 AE3:AE21 IW3:IW21 IU3:IU21 AG3:AG21 IS3:IS21 IQ3:IQ21 AI3:AI21 IO3:IO21 IM3:IM21 AK3:AK21 IK3:IK21 II3:II21 AM3:AM21 IG3:IG21 IE3:IE21 AO3:AO21 IC3:IC21 IA3:IA21 AQ3:AQ21 HY3:HY21 HW3:HW21 AS3:AS21 HU3:HU21 HS3:HS21 AU3:AU21 HQ3:HQ21 HO3:HO21 AW3:AW21 HM3:HM21 HK3:HK21 AY3:AY21 HI3:HI21 HG3:HG21 BA3:BA21 HE3:HE21 HC3:HC21 BC3:BC21 HA3:HA21 GY3:GY21 BE3:BE21 GW3:GW21 GU3:GU21 BG3:BG21 GS3:GS21 GQ3:GQ21 BI3:BI21 GO3:GO21 GM3:GM21 BK3:BK21 GK3:GK21 GI3:GI21 BM3:BM21 GG3:GG21 GE3:GE21 BO3:BO21 GC3:GC21 GA3:GA21 BQ3:BQ21 FY3:FY21 FW3:FW21 BS3:BS21 FU3:FU21 FS3:FS21 BU3:BU21 FQ3:FQ21 FO3:FO21 BW3:BW21 FM3:FM21 FK3:FK21 BY3:BY21 FI3:FI21 FG3:FG21 CA3:CA21 FE3:FE21 FC3:FC21 CC3:CC21 FA3:FA21 EY3:EY21 CE3:CE21 EW3:EW21 EU3:EU21 CG3:CG21 ES3:ES21 EQ3:EQ21 CI3:CI21 EO3:EO21 EM3:EM21 CK3:CK21 EK3:EK21 EI3:EI21 CM3:CM21 EG3:EG4 EG6:EG7 EG9 EG11:EH11 EG13 EG15 EG17 EG19:EG21 EE3:EE7 EE9:EE11 EE13 EE15:EE21 CO3:CO21 EC3:EC21 EA3:EA21 CQ3:CQ21 DY3:DY7 DY9 DY11:DY13 DY15:DY17 DY19:DY21 DW21 CS3:CS21 DU21 DS21 CU3:CU21 DQ21 DO3:DO21 CW3:CW21 DM3:DM21 DK21 CY3:CY21 DI21 DG21 DA3:DA21 DE21 DC21 KV11 KT11 KX11:LH11 KR11 KP11 KN11 LG12:LG21 KL11 KJ11 KH11 LE12:LE21 KF11 KD11 KB11 LC12:LC21 JZ11 JX11 JV11 LA12:LA21 JT11 JR11 JP11 JN11 JL11 JJ11 JH11 X11 JF11 JD11 Z11 JB11 IZ11 AB11 IX11 IV11 AD11 IT11 IR11 AF11 IP11 IN11 AH11 IL11 IJ11 AJ11 IH11 IF11 AL11 ID11 IB11 AN11 HZ11 HX11 AP11 HV11 HT11 AR11 HR11 HP11 AT11 HN11 HL11 AV11 HJ11 HH11 AX11 HF11 HD11 AZ11 HB11 GZ11 BB11 GX11 GV11 BD11 GT11 GR11 BF11 GP11 GN11 BH11 GL11 GJ11 BJ11 GH11 GF11 BL11 GD11 GB11 BN11 FZ11 FX11 BP11 FV11 FT11 BR11 FR11 FP11 BT11 FN11 FL11 BV11 FJ11 FH11 BX11 FF11 FD11 BZ11 FB11 EZ11 CB11 EX11 EV11 CD11 ET11 ER11 CF11 EP11 EN11 CH11 EL11 EJ11 CJ11 CL11 EB11 CN11 DZ11 DN11 DL11 CV11 CX11 CZ11 KY3:KY10 KY12:KY21 LA3:LA10 LC3:LC10 LE3:LE10 LG3:LG10">
+    <cfRule type="containsText" dxfId="0" priority="145" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",C3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DB3:DB20 DD3:DD20 DF3:DF20 DH3:DH20 DJ3:DJ20 DC11 DE11 DG11 DI11 DK11">
-    <cfRule type="containsText" dxfId="2" priority="116" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="139" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",DB3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC3:DC7 DC9:DC11 DC13 DC15:DC19 DE3:DE4 DE6:DE7 DE9 DD11:DF11 DE13 DE15 DE17 DE19:DE20 DG3:DG4 DG6:DG7 DG9:DG11 DG13:DG15 DG17 DG19 DI3:DI7 DI9 DH11:DJ11 DI13 DI15 DI17 DI19 DK3:DK7 DK9 DK11:DK13 DK15 DK17 DK19">
-    <cfRule type="containsText" dxfId="0" priority="115" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="138" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DC3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC3 DE3 DG3 DI3 DK3 DC5 DI5 DK5 DE20 DC18 DC16 DG14 DK12 DG10 DC10">
-    <cfRule type="containsBlanks" dxfId="1" priority="114">
+    <cfRule type="containsBlanks" dxfId="1" priority="137">
       <formula>LEN(TRIM(DC3))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DP3:DP20 DR3:DR20 DT3:DT20 DV3:DV20 DQ11 DS11 DU11 DW11">
-    <cfRule type="containsText" dxfId="2" priority="113" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="136" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",DP3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ3 DS3 DU3 DW3 DQ5 DS5 DW5 DW20 DS20 DQ20 DW18 DU18 DS18 DQ16 DU14 DU10">
-    <cfRule type="containsBlanks" dxfId="1" priority="111">
+    <cfRule type="containsBlanks" dxfId="1" priority="134">
       <formula>LEN(TRIM(DQ3))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ3:DQ7 DQ9 DQ11:DT11 DQ13 DQ15:DQ17 DQ19:DQ20 DS3:DS7 DS9 DS13 DS15 DS17:DS20 DU3:DU4 DU6:DU7 DU9:DU11 DU13:DU15 DU17:DU19 DW3:DW7 DW9 DV11:DW11 DW13 DW15 DW17:DW20">
-    <cfRule type="containsText" dxfId="0" priority="112" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="135" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22 JO22 JM22 JK22 JI22 JG22 JE22 JC22 JA22 IY22 IW22 IU22 IS22 IQ22 IO22 IM22 IK22 II22 IG22 IE22 IC22 IA22 HY22 HW22 HU22 HS22 HQ22 HO22 HM22 HK22 HI22 HG22 HE22 HC22 HA22 GY22 GW22 GU22 GS22 GQ22 GO22 GM22 GK22 GI22 GG22 GE22 GC22 GA22 FY22 FW22 FU22 FS22 FQ22 FO22 FM22 FK22 FI22 FG22 FE22 FC22 FA22 EY22 EW22 EU22 ES22 EQ22 EO22 EM22 EK22 EI22 EG22 EE22 EC22 EA22 DY22 DW22 DU22 DS22 DQ22 DO22 DM22 DK22 DI22 DG22 DE22 DC22 DA22 CY22 CW22 CU22 CS22 CQ22 CO22 CM22 CK22 CI22 CG22 CE22 CC22 CA22 BY22 BW22 BU22 BS22 BQ22 BO22 BM22 BK22 BI22 BG22 BE22 BC22 BA22 AY22 AW22 AU22 AS22 AQ22 AO22 AM22 AK22 AI22 AG22 AE22 AC22 AA22 Y22 W22 U22 S22 Q22 O22 M22 K22 I22 G22 E22">
-    <cfRule type="containsBlanks" dxfId="3" priority="119">
+    <cfRule type="containsBlanks" dxfId="3" priority="142">
       <formula>LEN(TRIM(C22))=0</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="120" operator="between" text="—">
+    <cfRule type="containsText" dxfId="2" priority="143" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",C22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DY8 DY9 DY10 DY14 DY18 C3:C21 E3:E21 G3:G21 I3:I21 K3:K21 M3:M21 O3:O21 Q3:Q21 S3:S21 U3:U21 W3:W21 Y3:Y21 AA3:AA21 AC3:AC21 AE3:AE21 AG3:AG21 AI3:AI21 AK3:AK21 AM3:AM21 AO3:AO21 AQ3:AQ21 AS3:AS21 AU3:AU21 AW3:AW21 AY3:AY21 BA3:BA21 BC3:BC21 BE3:BE21 BG3:BG21 BI3:BI21 BK3:BK21 BM3:BM21 BO3:BO21 BQ3:BQ21 BS3:BS21 BU3:BU21 BW3:BW21 BY3:BY21 CA3:CA21 CC3:CC21 CE3:CE21 CG3:CG21 CI3:CI21 CK3:CK21 CM3:CM21 CO3:CO21 CQ3:CQ21 CS3:CS21 CU3:CU21 CW3:CW21 CY3:CY21 DA3:DA21 DC3:DC21 DE3:DE21 DG3:DG21 DI3:DI21 DK3:DK21 DM3:DM21 DO3:DO21 DQ3:DQ21 DS3:DS21 DU3:DU21 DW3:DW21 DY3:DY7 DY11:DY13 DY15:DY17 DY19:DY21 EA3:EA21 EC3:EC21 EE3:EE21 EG3:EG21 EI3:EI21 EK3:EK21 EM3:EM21 EO3:EO21 EQ3:EQ21 ES3:ES21 EU3:EU21 EW3:EW21 EY3:EY21 FA3:FA21 FC3:FC21 FE3:FE21 FG3:FG21 FI3:FI21 FK3:FK21 FM3:FM21 FO3:FO21 FQ3:FQ21 FS3:FS21 FU3:FU21 FW3:FW21 FY3:FY21 GA3:GA21 GC3:GC21 GE3:GE21 GG3:GG21 GI3:GI21 GK3:GK21 GM3:GM21 GO3:GO21 GQ3:GQ21 GS3:GS21 GU3:GU21 GW3:GW21 GY3:GY21 HA3:HA21 HC3:HC21 HE3:HE21 HG3:HG21 HI3:HI21 HK3:HK21 HM3:HM21 HO3:HO21 HQ3:HQ21 HS3:HS21 HU3:HU21 HW3:HW21 HY3:HY21 IA3:IA21 IC3:IC21 IE3:IE21 IG3:IG21 II3:II21 IK3:IK21 IM3:IM21 IO3:IO21 IQ3:IQ21 IS3:IS21 IU3:IU21 IW3:IW21 IY3:IY21 JA3:JA21 JC3:JC21 JE3:JE21 JG3:JG21 JI3:JI21 JK3:JK21 JM3:JM21 JO3:JO21">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EG5 EE8 EG8 EG9 EG10 EG11 EE12 EG12 EE13 EG13 EE14 EG14 EG15 EG16 EG17 EG18 C3:C21 E3:E21 G3:G21 I3:I21 K3:K21 M3:M21 O3:O21 Q3:Q21 S3:S21 U3:U21 W3:W21 Y3:Y21 AA3:AA21 AC3:AC21 AE3:AE21 AG3:AG21 AI3:AI21 AK3:AK21 AM3:AM21 AO3:AO21 AQ3:AQ21 AS3:AS21 AU3:AU21 AW3:AW21 AY3:AY21 BA3:BA21 BC3:BC21 BE3:BE21 BG3:BG21 BI3:BI21 BK3:BK21 BM3:BM21 BO3:BO21 BQ3:BQ21 BS3:BS21 BU3:BU21 BW3:BW21 BY3:BY21 CA3:CA21 CC3:CC21 CE3:CE21 CG3:CG21 CI3:CI21 CK3:CK21 CM3:CM21 CO3:CO21 CQ3:CQ21 CS3:CS21 CU3:CU21 CW3:CW21 CY3:CY21 DA3:DA21 DC3:DC21 DE3:DE21 DG3:DG21 DI3:DI21 DK3:DK21 DM3:DM21 DO3:DO21 DQ3:DQ21 DS3:DS21 DU3:DU21 DW3:DW21 DY3:DY21 EA3:EA21 EC3:EC21 EE3:EE7 EE9:EE11 EE15:EE21 EG3:EG4 EG6:EG7 EG19:EG21 EI3:EI21 EK3:EK21 EM3:EM21 EO3:EO21 EQ3:EQ21 ES3:ES21 EU3:EU21 EW3:EW21 EY3:EY21 FA3:FA21 FC3:FC21 FE3:FE21 FG3:FG21 FI3:FI21 FK3:FK21 FM3:FM21 FO3:FO21 FQ3:FQ21 FS3:FS21 FU3:FU21 FW3:FW21 FY3:FY21 GA3:GA21 GC3:GC21 GE3:GE21 GG3:GG21 GI3:GI21 GK3:GK21 GM3:GM21 GO3:GO21 GQ3:GQ21 GS3:GS21 GU3:GU21 GW3:GW21 GY3:GY21 HA3:HA21 HC3:HC21 HE3:HE21 HG3:HG21 HI3:HI21 HK3:HK21 HM3:HM21 HO3:HO21 HQ3:HQ21 HS3:HS21 HU3:HU21 HW3:HW21 HY3:HY21 IA3:IA21 IC3:IC21 IE3:IE21 IG3:IG21 II3:II21 IK3:IK21 IM3:IM21 IO3:IO21 IQ3:IQ21 IS3:IS21 IU3:IU21 IW3:IW21 IY3:IY21 JA3:JA21 JC3:JC21 JE3:JE21 JG3:JG21 JI3:JI21 JK3:JK21 JM3:JM21 JO3:JO21">
       <formula1>数据!$B$1:$B$62</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DX21 B3:B21 D3:D21 F3:F21 H3:H21 J3:J21 L3:L21 N3:N21 P3:P21 R3:R21 T3:T21 V3:V21 X3:X21 Z3:Z21 AB3:AB21 AD3:AD21 AF3:AF21 AH3:AH21 AJ3:AJ21 AL3:AL21 AN3:AN21 AP3:AP21 AR3:AR21 AT3:AT21 AV3:AV21 AX3:AX21 AZ3:AZ21 BB3:BB21 BD3:BD21 BF3:BF21 BH3:BH21 BJ3:BJ21 BL3:BL21 BN3:BN21 BP3:BP21 BR3:BR21 BT3:BT21 BV3:BV21 BX3:BX21 BZ3:BZ21 CB3:CB21 CD3:CD21 CF3:CF21 CH3:CH21 CJ3:CJ21 CL3:CL21 CN3:CN21 CP3:CP21 CR3:CR21 CT3:CT21 CV3:CV21 CX3:CX21 CZ3:CZ21 DB3:DB21 DD3:DD21 DF3:DF21 DH3:DH21 DJ3:DJ21 DL3:DL21 DN3:DN21 DP3:DP21 DR3:DR21 DT3:DT21 DV3:DV21 DX3:DX20 DZ3:DZ21 EB3:EB21 ED3:ED21 EF3:EF21 EH3:EH21 EJ3:EJ21 EL3:EL21 EN3:EN21 EP3:EP21 ER3:ER21 ET3:ET21 EV3:EV21 EX3:EX21 EZ3:EZ21 FB3:FB21 FD3:FD21 FF3:FF21 FH3:FH21 FJ3:FJ21 FL3:FL21 FN3:FN21 FP3:FP21 FR3:FR21 FT3:FT21 FV3:FV21 FX3:FX21 FZ3:FZ21 GB3:GB21 GD3:GD21 GF3:GF21 GH3:GH21 GJ3:GJ21 GL3:GL21 GN3:GN21 GP3:GP21 GR3:GR21 GT3:GT21 GV3:GV21 GX3:GX21 GZ3:GZ21 HB3:HB21 HD3:HD21 HF3:HF21 HH3:HH21 HJ3:HJ21 HL3:HL21 HN3:HN21 HP3:HP21 HR3:HR21 HT3:HT21 HV3:HV21 HX3:HX21 HZ3:HZ21 IB3:IB21 ID3:ID21 IF3:IF21 IH3:IH21 IJ3:IJ21 IL3:IL21 IN3:IN21 IP3:IP21 IR3:IR21 IT3:IT21 IV3:IV21 IX3:IX21 IZ3:IZ21 JB3:JB21 JD3:JD21 JF3:JF21 JH3:JH21 JJ3:JJ21 JL3:JL21 JN3:JN21">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="ED21 EF21 B3:B21 D3:D21 F3:F21 H3:H21 J3:J21 L3:L21 N3:N21 P3:P21 R3:R21 T3:T21 V3:V21 X3:X21 Z3:Z21 AB3:AB21 AD3:AD21 AF3:AF21 AH3:AH21 AJ3:AJ21 AL3:AL21 AN3:AN21 AP3:AP21 AR3:AR21 AT3:AT21 AV3:AV21 AX3:AX21 AZ3:AZ21 BB3:BB21 BD3:BD21 BF3:BF21 BH3:BH21 BJ3:BJ21 BL3:BL21 BN3:BN21 BP3:BP21 BR3:BR21 BT3:BT21 BV3:BV21 BX3:BX21 BZ3:BZ21 CB3:CB21 CD3:CD21 CF3:CF21 CH3:CH21 CJ3:CJ21 CL3:CL21 CN3:CN21 CP3:CP21 CR3:CR21 CT3:CT21 CV3:CV21 CX3:CX21 CZ3:CZ21 DB3:DB21 DD3:DD21 DF3:DF21 DH3:DH21 DJ3:DJ21 DL3:DL21 DN3:DN21 DP3:DP21 DR3:DR21 DT3:DT21 DV3:DV21 DX3:DX21 DZ3:DZ21 EB3:EB21 ED3:ED20 EF3:EF20 EH3:EH21 EJ3:EJ21 EL3:EL21 EN3:EN21 EP3:EP21 ER3:ER21 ET3:ET21 EV3:EV21 EX3:EX21 EZ3:EZ21 FB3:FB21 FD3:FD21 FF3:FF21 FH3:FH21 FJ3:FJ21 FL3:FL21 FN3:FN21 FP3:FP21 FR3:FR21 FT3:FT21 FV3:FV21 FX3:FX21 FZ3:FZ21 GB3:GB21 GD3:GD21 GF3:GF21 GH3:GH21 GJ3:GJ21 GL3:GL21 GN3:GN21 GP3:GP21 GR3:GR21 GT3:GT21 GV3:GV21 GX3:GX21 GZ3:GZ21 HB3:HB21 HD3:HD21 HF3:HF21 HH3:HH21 HJ3:HJ21 HL3:HL21 HN3:HN21 HP3:HP21 HR3:HR21 HT3:HT21 HV3:HV21 HX3:HX21 HZ3:HZ21 IB3:IB21 ID3:ID21 IF3:IF21 IH3:IH21 IJ3:IJ21 IL3:IL21 IN3:IN21 IP3:IP21 IR3:IR21 IT3:IT21 IV3:IV21 IX3:IX21 IZ3:IZ21 JB3:JB21 JD3:JD21 JF3:JF21 JH3:JH21 JJ3:JJ21 JL3:JL21 JN3:JN21">
       <formula1>数据!$A$1:$A$88</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C22 E22 G22 I22 K22 M22 O22 Q22 S22 U22 W22 Y22 AA22 AC22 AE22 AG22 AI22 AK22 AM22 AO22 AQ22 AS22 AU22 AW22 AY22 BA22 BC22 BE22 BG22 BI22 BK22 BM22 BO22 BQ22 BS22 BU22 BW22 BY22 CA22 CC22 CE22 CG22 CI22 CK22 CM22 CO22 CQ22 CS22 CU22 CW22 CY22 DA22 DC22 DE22 DG22 DI22 DK22 DM22 DO22 DQ22 DS22 DU22 DW22 DY22 EA22 EC22 EE22 EG22 EI22 EK22 EM22 EO22 EQ22 ES22 EU22 EW22 EY22 FA22 FC22 FE22 FG22 FI22 FK22 FM22 FO22 FQ22 FS22 FU22 FW22 FY22 GA22 GC22 GE22 GG22 GI22 GK22 GM22 GO22 GQ22 GS22 GU22 GW22 GY22 HA22 HC22 HE22 HG22 HI22 HK22 HM22 HO22 HQ22 HS22 HU22 HW22 HY22 IA22 IC22 IE22 IG22 II22 IK22 IM22 IO22 IQ22 IS22 IU22 IW22 IY22 JA22 JC22 JE22 JG22 JI22 JK22 JM22 JO22">
@@ -15721,7 +15914,7 @@
   <sheetData>
     <row r="1" s="2" customFormat="1" customHeight="1" spans="1:16">
       <c r="A1" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -15760,15 +15953,15 @@
     </row>
     <row r="3" customHeight="1" spans="1:9">
       <c r="A3" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="13"/>
       <c r="D3" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F3" s="15"/>
       <c r="G3" s="15"/>
@@ -15778,163 +15971,163 @@
     <row r="4" customHeight="1" spans="1:9">
       <c r="A4" s="17"/>
       <c r="B4" s="18" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:9">
       <c r="A5" s="17"/>
       <c r="B5" s="18" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:9">
       <c r="A6" s="17"/>
       <c r="B6" s="18" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:9">
       <c r="A7" s="17"/>
       <c r="B7" s="18" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:9">
       <c r="A8" s="17"/>
       <c r="B8" s="18" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:9">
       <c r="A9" s="17"/>
       <c r="B9" s="18" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:9">
@@ -15942,7 +16135,7 @@
       <c r="B10" s="20"/>
       <c r="C10" s="21"/>
       <c r="D10" s="22" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="24"/>
@@ -15952,15 +16145,15 @@
     </row>
     <row r="11" customHeight="1" spans="1:9">
       <c r="A11" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="13"/>
       <c r="D11" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
@@ -15970,163 +16163,163 @@
     <row r="12" customHeight="1" spans="1:9">
       <c r="A12" s="17"/>
       <c r="B12" s="18" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:9">
       <c r="A13" s="17"/>
       <c r="B13" s="18" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D13" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>338</v>
       </c>
-      <c r="E13" s="14" t="s">
-        <v>337</v>
-      </c>
       <c r="F13" s="15" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:9">
       <c r="A14" s="17"/>
       <c r="B14" s="18" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:9">
       <c r="A15" s="17"/>
       <c r="B15" s="18" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F15" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="G15" s="15" t="s">
         <v>356</v>
       </c>
-      <c r="G15" s="15" t="s">
-        <v>355</v>
-      </c>
       <c r="H15" s="16" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:9">
       <c r="A16" s="17"/>
       <c r="B16" s="18" t="s">
+        <v>369</v>
+      </c>
+      <c r="C16" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="C16" s="18" t="s">
-        <v>367</v>
-      </c>
       <c r="D16" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I16" s="30" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:9">
       <c r="A17" s="17"/>
       <c r="B17" s="18" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:9">
@@ -16134,7 +16327,7 @@
       <c r="B18" s="20"/>
       <c r="C18" s="21"/>
       <c r="D18" s="22" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E18" s="23"/>
       <c r="F18" s="24"/>
@@ -16144,16 +16337,16 @@
     </row>
     <row r="19" customHeight="1" spans="1:9">
       <c r="A19" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B19" s="12"/>
       <c r="C19" s="13"/>
       <c r="D19" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E19" s="14"/>
       <c r="F19" s="25" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G19" s="25"/>
       <c r="H19" s="26"/>
@@ -16162,163 +16355,163 @@
     <row r="20" customHeight="1" spans="1:9">
       <c r="A20" s="17"/>
       <c r="B20" s="27" t="s">
+        <v>391</v>
+      </c>
+      <c r="C20" s="28" t="s">
         <v>390</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="D20" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>341</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="H20" s="16" t="s">
         <v>389</v>
       </c>
-      <c r="D20" s="14" t="s">
-        <v>345</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>340</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>385</v>
-      </c>
-      <c r="G20" s="15" t="s">
-        <v>386</v>
-      </c>
-      <c r="H20" s="16" t="s">
+      <c r="I20" s="16" t="s">
         <v>388</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:9">
       <c r="A21" s="17"/>
       <c r="B21" s="18" t="s">
+        <v>340</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>393</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>396</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="I21" s="16" t="s">
         <v>339</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>337</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>391</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>392</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="G21" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H21" s="16" t="s">
-        <v>393</v>
-      </c>
-      <c r="I21" s="16" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:9">
       <c r="A22" s="17"/>
       <c r="B22" s="18" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:9">
       <c r="A23" s="17"/>
       <c r="B23" s="18" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C23" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="E23" s="14" t="s">
         <v>402</v>
       </c>
-      <c r="D23" s="14" t="s">
-        <v>398</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>401</v>
-      </c>
       <c r="F23" s="15" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I23" s="16" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:9">
       <c r="A24" s="17"/>
       <c r="B24" s="18" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I24" s="30" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:9">
       <c r="A25" s="17"/>
       <c r="B25" s="18" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E25" s="14" t="s">
+        <v>377</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>361</v>
+      </c>
+      <c r="G25" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="H25" s="16" t="s">
         <v>376</v>
       </c>
-      <c r="F25" s="15" t="s">
-        <v>360</v>
-      </c>
-      <c r="G25" s="15" t="s">
-        <v>403</v>
-      </c>
-      <c r="H25" s="16" t="s">
-        <v>375</v>
-      </c>
       <c r="I25" s="16" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:9">
@@ -16326,7 +16519,7 @@
       <c r="B26" s="20"/>
       <c r="C26" s="21"/>
       <c r="D26" s="22" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E26" s="23"/>
       <c r="F26" s="24"/>
@@ -16422,7 +16615,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <v>1.25</v>
@@ -16499,7 +16692,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -16510,7 +16703,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>3.25</v>
@@ -16521,7 +16714,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B15">
         <v>3.5</v>
@@ -16532,7 +16725,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B16">
         <v>3.75</v>
@@ -16543,7 +16736,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B17">
         <v>4</v>
@@ -16554,7 +16747,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B18">
         <v>4.25</v>
@@ -16565,7 +16758,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B19">
         <v>4.5</v>
@@ -16576,7 +16769,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B20">
         <v>4.75</v>
@@ -16587,7 +16780,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B21">
         <v>5</v>
@@ -16598,7 +16791,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B22">
         <v>5.25</v>
@@ -16609,7 +16802,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B23">
         <v>5.5</v>
@@ -16620,7 +16813,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B24">
         <v>5.75</v>
@@ -16631,7 +16824,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B25">
         <v>6</v>
@@ -16666,7 +16859,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>423</v>
+        <v>20</v>
       </c>
       <c r="B29">
         <v>7</v>
@@ -17053,7 +17246,7 @@
     </row>
     <row r="86" spans="1:1">
       <c r="A86" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87" spans="1:1">
@@ -17100,24 +17293,24 @@
     <row r="1" ht="16.5" spans="1:9">
       <c r="A1" s="120"/>
       <c r="B1" s="121" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C1" s="121"/>
       <c r="D1" s="121" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" s="121"/>
       <c r="F1" s="121" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G1" s="121" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H1" s="121" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I1" s="121" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:9">
@@ -17125,14 +17318,14 @@
         <v>4</v>
       </c>
       <c r="B2" s="122" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" s="123" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" s="124"/>
       <c r="E2" s="122" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F2" s="120"/>
       <c r="G2" s="120"/>
@@ -17144,7 +17337,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="125" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C3" s="125"/>
       <c r="D3" s="125"/>
@@ -17159,7 +17352,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="126" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C4" s="126"/>
       <c r="D4" s="126"/>
@@ -17197,10 +17390,10 @@
     </row>
     <row r="7" ht="16.5" spans="1:9">
       <c r="A7" s="121" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7" s="130" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" s="130"/>
       <c r="D7" s="130"/>
@@ -17228,7 +17421,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="122" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9" s="122"/>
       <c r="D9" s="122"/>
@@ -17279,10 +17472,10 @@
     </row>
     <row r="13" ht="16.5" spans="1:9">
       <c r="A13" s="121" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13" s="134" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" s="134"/>
       <c r="D13" s="134"/>
@@ -17291,10 +17484,10 @@
     </row>
     <row r="14" ht="16.5" spans="1:9">
       <c r="A14" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="135" t="s">
         <v>41</v>
-      </c>
-      <c r="B14" s="135" t="s">
-        <v>40</v>
       </c>
       <c r="C14" s="135"/>
       <c r="D14" s="135"/>
@@ -17363,341 +17556,341 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="116" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B1" s="117" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C1" s="118" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="119" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" s="114" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="115" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="119"/>
       <c r="B3" s="114" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C3" s="115" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="119"/>
       <c r="B4" s="114" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C4" s="115" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="119"/>
       <c r="B5" s="114" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" s="115" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="119"/>
       <c r="B6" s="114" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6" s="115" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="119"/>
       <c r="B7" s="114" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C7" s="115" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="119"/>
       <c r="B8" s="114" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" s="115" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="119"/>
       <c r="B9" s="114" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C9" s="115" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="119"/>
       <c r="B10" s="114" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C10" s="115" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="119"/>
       <c r="B11" s="114" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C11" s="115" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="119"/>
       <c r="B12" s="114" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C12" s="115" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="119"/>
       <c r="B13" s="114" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C13" s="115" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="119"/>
       <c r="B14" s="114" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C14" s="115" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="119"/>
       <c r="B15" s="114" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C15" s="115" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="119"/>
       <c r="B16" s="114" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C16" s="115" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="119"/>
       <c r="B17" s="114" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C17" s="115" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="119"/>
       <c r="B18" s="114" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C18" s="115" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="119"/>
       <c r="B19" s="114" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C19" s="115" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="119"/>
       <c r="B20" s="114" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C20" s="115" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="119"/>
       <c r="B21" s="114" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C21" s="115" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="119"/>
       <c r="B22" s="114" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C22" s="115" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="119"/>
       <c r="B23" s="114" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C23" s="115" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="119"/>
       <c r="B24" s="114" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C24" s="115" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="119"/>
       <c r="B25" s="114" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C25" s="115" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="119"/>
       <c r="B26" s="114" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C26" s="115" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="119"/>
       <c r="B27" s="114" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C27" s="115" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="119"/>
       <c r="B28" s="114" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C28" s="115" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="119"/>
       <c r="B29" s="114" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C29" s="115" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="119"/>
       <c r="B30" s="114" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C30" s="115" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="119"/>
       <c r="B31" s="114" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C31" s="115" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="119"/>
       <c r="B32" s="114" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C32" s="115" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="116" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B33" s="114" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C33" s="115" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="116"/>
       <c r="B34" s="114" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C34" s="115" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="116"/>
       <c r="B35" s="114" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C35" s="115" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="116"/>
       <c r="B36" s="114" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C36" s="115" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="116"/>
       <c r="B37" s="114" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C37" s="115" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -17781,16 +17974,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="104" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B1" s="105" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C1" s="106" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D1" s="107" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -17798,13 +17991,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="109" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C2" s="110">
         <v>20111216</v>
       </c>
       <c r="D2" s="103" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -17812,13 +18005,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="109" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C3" s="111">
         <v>20111227</v>
       </c>
       <c r="D3" s="103" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -17826,13 +18019,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="109" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C4" s="111">
         <v>20120518</v>
       </c>
       <c r="D4" s="103" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -17840,7 +18033,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="109" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C5" s="111">
         <v>20120714</v>
@@ -17851,13 +18044,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="109" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C6" s="111">
         <v>20120504</v>
       </c>
       <c r="D6" s="103" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -17865,13 +18058,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="109" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C7" s="111">
         <v>20120809</v>
       </c>
       <c r="D7" s="103" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -17879,7 +18072,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="109" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C8" s="111">
         <v>20120227</v>
@@ -17890,13 +18083,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="109" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C9" s="111">
         <v>20120127</v>
       </c>
       <c r="D9" s="103" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -17904,13 +18097,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="109" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C10" s="111">
         <v>20111202</v>
       </c>
       <c r="D10" s="103" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -17918,7 +18111,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="109" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C11" s="111">
         <v>20120623</v>
@@ -17929,13 +18122,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="109" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C12" s="111">
         <v>20111024</v>
       </c>
       <c r="D12" s="103" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -17943,13 +18136,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="109" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C13" s="111">
         <v>20110908</v>
       </c>
       <c r="D13" s="103" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -17957,13 +18150,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="109" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C14" s="111">
         <v>20120228</v>
       </c>
       <c r="D14" s="103" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -17971,7 +18164,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="109" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C15" s="111">
         <v>20110904</v>
@@ -17982,7 +18175,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="109" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C16" s="110">
         <v>20111201</v>
@@ -17993,7 +18186,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="109" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C17" s="111">
         <v>20120722</v>
@@ -18004,7 +18197,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="109" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C18" s="111">
         <v>20111215</v>
@@ -18015,7 +18208,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="109" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C19" s="111">
         <v>20120509</v>
@@ -18026,7 +18219,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="109" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C20" s="111">
         <v>20120530</v>
@@ -18037,13 +18230,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="109" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C21" s="111">
         <v>20120827</v>
       </c>
       <c r="D21" s="103" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -18051,7 +18244,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="109" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C22" s="111">
         <v>20120816</v>
@@ -18062,7 +18255,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="109" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C23" s="111">
         <v>20120518</v>
@@ -18073,13 +18266,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="109" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C24" s="111">
         <v>20120413</v>
       </c>
       <c r="D24" s="103" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -18087,13 +18280,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="109" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C25" s="111">
         <v>20120629</v>
       </c>
       <c r="D25" s="103" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -18101,13 +18294,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="109" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C26" s="111">
         <v>20111105</v>
       </c>
       <c r="D26" s="103" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -18115,13 +18308,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="109" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C27" s="111">
         <v>20120112</v>
       </c>
       <c r="D27" s="103" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -18129,13 +18322,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="109" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C28" s="111">
         <v>20111119</v>
       </c>
       <c r="D28" s="103" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -18143,7 +18336,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="109" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C29" s="111">
         <v>20120110</v>
@@ -18154,13 +18347,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="109" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C30" s="111">
         <v>20120331</v>
       </c>
       <c r="D30" s="103" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -18168,13 +18361,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="109" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C31" s="111">
         <v>20111109</v>
       </c>
       <c r="D31" s="103" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -18182,13 +18375,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="109" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C32" s="111">
         <v>20120824</v>
       </c>
       <c r="D32" s="103" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -18196,7 +18389,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="109" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C33" s="111">
         <v>20120425</v>
@@ -18207,13 +18400,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="109" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C34" s="111">
         <v>20120624</v>
       </c>
       <c r="D34" s="103" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -18221,7 +18414,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="109" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C35" s="111">
         <v>20120507</v>
@@ -18232,13 +18425,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="109" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C36" s="111">
         <v>20120603</v>
       </c>
       <c r="D36" s="103" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -18246,13 +18439,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="109" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C37" s="110">
         <v>20120326</v>
       </c>
       <c r="D37" s="103" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -18260,13 +18453,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="109" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C38" s="111">
         <v>20111106</v>
       </c>
       <c r="D38" s="103" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -18274,13 +18467,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="109" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C39" s="111">
         <v>20120811</v>
       </c>
       <c r="D39" s="112" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -18288,13 +18481,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="109" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C40" s="111">
         <v>20111217</v>
       </c>
       <c r="D40" s="112" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -18302,13 +18495,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="109" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C41" s="111">
         <v>20111013</v>
       </c>
       <c r="D41" s="103" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -18316,7 +18509,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="109" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C42" s="111">
         <v>20111027</v>
@@ -18327,13 +18520,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="109" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C43" s="111">
         <v>20120207</v>
       </c>
       <c r="D43" s="103" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -18341,7 +18534,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="109" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C44" s="110">
         <v>20120508</v>
@@ -18352,13 +18545,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="109" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C45" s="111">
         <v>20110929</v>
       </c>
       <c r="D45" s="103" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -18366,7 +18559,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="109" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C46" s="111">
         <v>20111205</v>
@@ -18377,13 +18570,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="109" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C47" s="111">
         <v>20120108</v>
       </c>
       <c r="D47" s="103" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -18391,13 +18584,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="109" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C48" s="111">
         <v>20120311</v>
       </c>
       <c r="D48" s="103" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -18405,7 +18598,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="109" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C49" s="111">
         <v>20110902</v>
@@ -18416,13 +18609,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="109" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C50" s="111">
         <v>20120723</v>
       </c>
       <c r="D50" s="103" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -18430,7 +18623,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="109" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C51" s="111">
         <v>20120101</v>
@@ -18441,13 +18634,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="109" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C52" s="111">
         <v>20111220</v>
       </c>
       <c r="D52" s="103" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -18477,70 +18670,70 @@
   <sheetData>
     <row r="1" ht="14" spans="1:5">
       <c r="A1" s="94" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B1" s="95" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C1" s="96" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D1" s="97" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E1" s="98" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" ht="217" spans="1:5">
       <c r="A2" s="62" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B2" s="64" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C2" s="63" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D2" s="42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E2" s="99" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" ht="356.5" spans="1:5">
       <c r="A3" s="62" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" s="64" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C3" s="63" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D3" s="42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3" s="99" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" ht="108.5" spans="1:5">
       <c r="A4" s="62" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4" s="99" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -18576,17 +18769,17 @@
   <sheetData>
     <row r="1" s="66" customFormat="1" spans="1:5">
       <c r="A1" s="73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B1" s="74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C1" s="75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D1" s="76"/>
       <c r="E1" s="77" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" ht="409" customHeight="1" spans="1:5">
@@ -18594,16 +18787,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="79" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" s="80" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D2" s="70" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E2" s="71" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" ht="56" spans="1:5">
@@ -18611,10 +18804,10 @@
       <c r="B3" s="82"/>
       <c r="C3" s="83"/>
       <c r="D3" s="70" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E3" s="71" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -18622,10 +18815,10 @@
       <c r="B4" s="82"/>
       <c r="C4" s="83"/>
       <c r="D4" s="70" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E4" s="71" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" ht="56" spans="1:5">
@@ -18633,10 +18826,10 @@
       <c r="B5" s="82"/>
       <c r="C5" s="83"/>
       <c r="D5" s="70" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E5" s="71" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" ht="238" spans="1:5">
@@ -18644,23 +18837,23 @@
       <c r="B6" s="82"/>
       <c r="C6" s="83"/>
       <c r="D6" s="70" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E6" s="71" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" ht="210" spans="1:5">
       <c r="A7" s="81"/>
       <c r="B7" s="82"/>
       <c r="C7" s="80" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D7" s="70" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E7" s="71" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" ht="56" spans="1:5">
@@ -18668,10 +18861,10 @@
       <c r="B8" s="82"/>
       <c r="C8" s="83"/>
       <c r="D8" s="70" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E8" s="71" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="9" ht="84" spans="1:5">
@@ -18679,10 +18872,10 @@
       <c r="B9" s="82"/>
       <c r="C9" s="83"/>
       <c r="D9" s="70" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E9" s="71" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" ht="28" spans="1:5">
@@ -18690,10 +18883,10 @@
       <c r="B10" s="82"/>
       <c r="C10" s="83"/>
       <c r="D10" s="70" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E10" s="71" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -18701,10 +18894,10 @@
       <c r="B11" s="82"/>
       <c r="C11" s="84"/>
       <c r="D11" s="70" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E11" s="71" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12" ht="154" spans="1:5">
@@ -18712,50 +18905,50 @@
       <c r="B12" s="82"/>
       <c r="C12" s="69"/>
       <c r="D12" s="70" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E12" s="71" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="13" ht="56" spans="1:5">
       <c r="A13" s="81"/>
       <c r="B13" s="82"/>
       <c r="C13" s="85" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D13" s="76"/>
       <c r="E13" s="71" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="14" ht="84" spans="1:5">
       <c r="A14" s="81"/>
       <c r="B14" s="82"/>
       <c r="C14" s="85" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D14" s="76"/>
       <c r="E14" s="71" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15" ht="28" spans="1:5">
       <c r="A15" s="81"/>
       <c r="B15" s="82"/>
       <c r="C15" s="85" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D15" s="76"/>
       <c r="E15" s="71" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="81"/>
       <c r="B16" s="82"/>
       <c r="C16" s="85" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D16" s="76"/>
     </row>
@@ -18763,7 +18956,7 @@
       <c r="A17" s="81"/>
       <c r="B17" s="82"/>
       <c r="C17" s="85" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D17" s="76"/>
     </row>
@@ -18771,10 +18964,10 @@
       <c r="A18" s="81"/>
       <c r="B18" s="82"/>
       <c r="C18" s="80" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D18" s="70" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -18782,14 +18975,14 @@
       <c r="B19" s="82"/>
       <c r="C19" s="84"/>
       <c r="D19" s="70" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="81"/>
       <c r="B20" s="82"/>
       <c r="C20" s="85" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D20" s="76"/>
     </row>
@@ -18797,7 +18990,7 @@
       <c r="A21" s="86"/>
       <c r="B21" s="87"/>
       <c r="C21" s="85" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D21" s="76"/>
     </row>
@@ -18805,11 +18998,11 @@
       <c r="A22" s="81"/>
       <c r="B22" s="82"/>
       <c r="C22" s="69" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D22" s="69"/>
       <c r="E22" s="71" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="23" ht="28" spans="1:5">
@@ -18817,16 +19010,16 @@
         <v>1</v>
       </c>
       <c r="B23" s="79" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C23" s="83" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D23" s="88" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E23" s="71" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -18834,10 +19027,10 @@
       <c r="B24" s="82"/>
       <c r="C24" s="83"/>
       <c r="D24" s="70" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E24" s="71" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="25" ht="28" spans="1:5">
@@ -18845,10 +19038,10 @@
       <c r="B25" s="82"/>
       <c r="C25" s="83"/>
       <c r="D25" s="70" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E25" s="71" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="26" ht="42" spans="1:5">
@@ -18856,16 +19049,16 @@
         <v>4</v>
       </c>
       <c r="B26" s="79" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C26" s="80" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D26" s="70" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E26" s="71" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27" ht="70" spans="1:5">
@@ -18873,10 +19066,10 @@
       <c r="B27" s="82"/>
       <c r="C27" s="83"/>
       <c r="D27" s="70" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E27" s="71" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -18884,10 +19077,10 @@
       <c r="B28" s="82"/>
       <c r="C28" s="83"/>
       <c r="D28" s="70" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E28" s="71" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="29" ht="28" spans="1:5">
@@ -18895,30 +19088,30 @@
       <c r="B29" s="82"/>
       <c r="C29" s="84"/>
       <c r="D29" s="70" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E29" s="71" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="30" ht="42" spans="1:5">
       <c r="A30" s="81"/>
       <c r="B30" s="87"/>
       <c r="C30" s="85" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D30" s="89"/>
       <c r="E30" s="71" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="81"/>
       <c r="B31" s="79" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C31" s="85" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D31" s="89"/>
     </row>
@@ -18926,7 +19119,7 @@
       <c r="A32" s="86"/>
       <c r="B32" s="87"/>
       <c r="C32" s="85" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D32" s="89"/>
     </row>
@@ -18935,7 +19128,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="90" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C33" s="91"/>
       <c r="D33" s="92"/>
@@ -18943,7 +19136,7 @@
     <row r="34" spans="1:4">
       <c r="A34" s="86"/>
       <c r="B34" s="90" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C34" s="91"/>
       <c r="D34" s="92"/>
@@ -18953,23 +19146,23 @@
         <v>6</v>
       </c>
       <c r="B35" s="90" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C35" s="91"/>
       <c r="D35" s="92"/>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="78" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B36" s="79" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C36" s="80" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D36" s="70" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -18977,14 +19170,14 @@
       <c r="B37" s="82"/>
       <c r="C37" s="84"/>
       <c r="D37" s="70" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="81"/>
       <c r="B38" s="82"/>
       <c r="C38" s="85" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D38" s="89"/>
     </row>
@@ -18992,7 +19185,7 @@
       <c r="A39" s="86"/>
       <c r="B39" s="87"/>
       <c r="C39" s="85" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D39" s="89"/>
     </row>
@@ -19001,10 +19194,10 @@
         <v>17</v>
       </c>
       <c r="B40" s="79" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C40" s="85" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D40" s="89"/>
     </row>
@@ -19012,10 +19205,10 @@
       <c r="A41" s="81"/>
       <c r="B41" s="82"/>
       <c r="C41" s="80" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D41" s="70" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -19023,13 +19216,13 @@
       <c r="B42" s="87"/>
       <c r="C42" s="84"/>
       <c r="D42" s="70" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="86"/>
       <c r="B43" s="90" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C43" s="91"/>
       <c r="D43" s="92"/>
@@ -19039,13 +19232,13 @@
         <v>11</v>
       </c>
       <c r="B44" s="79" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C44" s="80" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D44" s="70" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -19053,7 +19246,7 @@
       <c r="B45" s="82"/>
       <c r="C45" s="83"/>
       <c r="D45" s="70" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -19061,7 +19254,7 @@
       <c r="B46" s="87"/>
       <c r="C46" s="84"/>
       <c r="D46" s="70" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -19069,7 +19262,7 @@
         <v>9</v>
       </c>
       <c r="B47" s="90" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C47" s="91"/>
       <c r="D47" s="92"/>
@@ -19079,7 +19272,7 @@
         <v>18</v>
       </c>
       <c r="B48" s="90" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C48" s="91"/>
       <c r="D48" s="92"/>
@@ -19087,7 +19280,7 @@
     <row r="49" spans="1:4">
       <c r="A49" s="86"/>
       <c r="B49" s="90" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C49" s="91"/>
       <c r="D49" s="92"/>
@@ -19097,7 +19290,7 @@
         <v>12</v>
       </c>
       <c r="B50" s="90" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C50" s="91"/>
       <c r="D50" s="92"/>
@@ -19107,7 +19300,7 @@
         <v>10</v>
       </c>
       <c r="B51" s="90" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C51" s="91"/>
       <c r="D51" s="92"/>
@@ -19185,352 +19378,352 @@
   <sheetData>
     <row r="1" s="50" customFormat="1" spans="1:7">
       <c r="A1" s="59" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B1" s="42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C1" s="60" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D1" s="61" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E1" s="62" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F1" s="63" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G1" s="64" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" ht="70" spans="1:2">
       <c r="A2" s="59" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="59" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="59" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="59" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="59" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="59" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="59" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="59" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" ht="42" spans="1:2">
       <c r="A10" s="59" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B10" s="52" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="59" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="59" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="59" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" ht="42" spans="1:2">
       <c r="A14" s="59" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B14" s="52" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="59" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="59" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" ht="28" spans="1:3">
       <c r="A17" s="59" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C17" s="53" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="59" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="59" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" ht="70" spans="1:2">
       <c r="A20" s="59" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B20" s="52" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="21" ht="280" spans="1:3">
       <c r="A21" s="59" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B21" s="52" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="59" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" ht="112" spans="1:2">
       <c r="A23" s="59" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B23" s="52" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="24" ht="112" spans="1:3">
       <c r="A24" s="59" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B24" s="52" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C24" s="53" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="59" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="59" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" ht="112" spans="1:3">
       <c r="A27" s="59" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B27" s="52" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C27" s="53" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="28" ht="409" customHeight="1" spans="1:3">
       <c r="A28" s="59" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B28" s="52" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C28" s="53" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="59" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" ht="42" spans="1:3">
       <c r="A30" s="59" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C30" s="53" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="59" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="59" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="59" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="59" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="59" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="36" ht="56" spans="1:2">
       <c r="A36" s="59" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B36" s="52" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="37" ht="28" spans="1:3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="37" ht="56" spans="1:3">
       <c r="A37" s="59" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C37" s="53" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="59" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="39" ht="28" spans="1:3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="39" ht="70" spans="1:3">
       <c r="A39" s="59" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C39" s="53" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40" ht="28" spans="1:2">
       <c r="A40" s="59" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B40" s="52" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41" ht="112" spans="1:3">
       <c r="A41" s="59" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C41" s="53" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="59" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="43" ht="28" spans="1:2">
       <c r="A43" s="59" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B43" s="52" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="59" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" ht="387" spans="1:2">
       <c r="A45" s="59" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B45" s="52" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="59" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="59" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="59" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="59" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="50" ht="252" spans="1:3">
       <c r="A50" s="59" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C50" s="53" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="59" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="52" ht="224" spans="1:2">
       <c r="A52" s="59" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B52" s="52" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -19558,47 +19751,47 @@
   <sheetData>
     <row r="1" s="31" customFormat="1" spans="1:8">
       <c r="A1" s="35" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B1" s="36"/>
       <c r="C1" s="31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1" s="31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" s="31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F1" s="31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G1" s="31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H1" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" s="32" customFormat="1" spans="1:4">
       <c r="A2" s="37" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C2" s="39" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D2" s="40"/>
     </row>
     <row r="3" s="32" customFormat="1" spans="1:4">
       <c r="A3" s="41"/>
       <c r="B3" s="38" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C3" s="39" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D3" s="40"/>
     </row>
@@ -19606,93 +19799,93 @@
       <c r="A4" s="41"/>
       <c r="B4" s="38"/>
       <c r="C4" s="39" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D4" s="40"/>
     </row>
     <row r="5" s="32" customFormat="1" spans="1:4">
       <c r="A5" s="41"/>
       <c r="B5" s="38" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D5" s="40"/>
     </row>
     <row r="6" s="32" customFormat="1" spans="1:4">
       <c r="A6" s="41"/>
       <c r="B6" s="38" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" s="32" customFormat="1" spans="1:4">
       <c r="A7" s="41"/>
       <c r="B7" s="38"/>
       <c r="C7" s="42" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" s="32" customFormat="1" spans="1:4">
       <c r="A8" s="41"/>
       <c r="B8" s="38" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C8" s="42" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" s="32" customFormat="1" spans="1:4">
       <c r="A9" s="41"/>
       <c r="B9" s="38" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D9" s="40"/>
     </row>
     <row r="10" s="32" customFormat="1" spans="1:4">
       <c r="A10" s="41"/>
       <c r="B10" s="38" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D10" s="40"/>
     </row>
     <row r="11" s="32" customFormat="1" spans="1:4">
       <c r="A11" s="43"/>
       <c r="B11" s="38" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D11" s="40"/>
     </row>
     <row r="12" s="33" customFormat="1" spans="1:4">
       <c r="A12" s="44" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C12" s="46" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D12" s="47"/>
     </row>
@@ -19700,27 +19893,27 @@
       <c r="A13" s="48"/>
       <c r="B13" s="45"/>
       <c r="C13" s="46" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D13" s="47"/>
     </row>
     <row r="14" s="33" customFormat="1" spans="1:4">
       <c r="A14" s="48"/>
       <c r="B14" s="45" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C14" s="46" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D14" s="47"/>
     </row>
     <row r="15" s="33" customFormat="1" spans="1:4">
       <c r="A15" s="48"/>
       <c r="B15" s="45" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C15" s="46" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D15" s="47"/>
     </row>
@@ -19728,47 +19921,47 @@
       <c r="A16" s="48"/>
       <c r="B16" s="45"/>
       <c r="C16" s="46" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D16" s="47"/>
     </row>
     <row r="17" s="33" customFormat="1" spans="1:4">
       <c r="A17" s="48"/>
       <c r="B17" s="45" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C17" s="46" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D17" s="47"/>
     </row>
     <row r="18" s="33" customFormat="1" spans="1:4">
       <c r="A18" s="48"/>
       <c r="B18" s="45" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C18" s="46" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D18" s="47"/>
     </row>
     <row r="19" s="33" customFormat="1" spans="1:4">
       <c r="A19" s="48"/>
       <c r="B19" s="45" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C19" s="46" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D19" s="47"/>
     </row>
     <row r="20" s="33" customFormat="1" spans="1:4">
       <c r="A20" s="49"/>
       <c r="B20" s="45" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C20" s="46" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D20" s="47"/>
     </row>

--- a/c/9班资料.xlsx
+++ b/c/9班资料.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480" activeTab="7"/>
+    <workbookView windowWidth="20750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="七下拖课" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="481">
   <si>
     <t>拖课统计表</t>
   </si>
@@ -1705,6 +1705,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">海参
 </t>
     </r>
@@ -1737,6 +1742,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">嘴甜
 </t>
     </r>
@@ -4304,9 +4314,20 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="宋体"/>
+      <color rgb="FF000033"/>
+      <name val="等线"/>
       <charset val="134"/>
-      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF4F81BD"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4322,20 +4343,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000033"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF4F81BD"/>
-      <name val="黑体"/>
-      <charset val="134"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="61">
@@ -7526,10 +7536,18 @@
       <c r="EM3" s="154"/>
       <c r="EN3" s="153"/>
       <c r="EO3" s="154"/>
-      <c r="EP3" s="153"/>
-      <c r="EQ3" s="154"/>
-      <c r="ER3" s="153"/>
-      <c r="ES3" s="154"/>
+      <c r="EP3" s="153" t="s">
+        <v>4</v>
+      </c>
+      <c r="EQ3" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="ER3" s="153" t="s">
+        <v>4</v>
+      </c>
+      <c r="ES3" s="154" t="s">
+        <v>3</v>
+      </c>
       <c r="ET3" s="153"/>
       <c r="EU3" s="154"/>
       <c r="EV3" s="153"/>
@@ -8270,10 +8288,18 @@
       <c r="EM5" s="160"/>
       <c r="EN5" s="159"/>
       <c r="EO5" s="160"/>
-      <c r="EP5" s="159"/>
-      <c r="EQ5" s="160"/>
-      <c r="ER5" s="159"/>
-      <c r="ES5" s="160"/>
+      <c r="EP5" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="EQ5" s="160">
+        <v>5</v>
+      </c>
+      <c r="ER5" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="ES5" s="160" t="s">
+        <v>3</v>
+      </c>
       <c r="ET5" s="159"/>
       <c r="EU5" s="160"/>
       <c r="EV5" s="159"/>
@@ -8549,8 +8575,12 @@
       <c r="EO6" s="157"/>
       <c r="EP6" s="156"/>
       <c r="EQ6" s="157"/>
-      <c r="ER6" s="156"/>
-      <c r="ES6" s="157"/>
+      <c r="ER6" s="156" t="s">
+        <v>2</v>
+      </c>
+      <c r="ES6" s="157">
+        <v>5</v>
+      </c>
       <c r="ET6" s="156"/>
       <c r="EU6" s="157"/>
       <c r="EV6" s="156"/>
@@ -9297,10 +9327,18 @@
       <c r="EM8" s="160"/>
       <c r="EN8" s="164"/>
       <c r="EO8" s="160"/>
-      <c r="EP8" s="164"/>
-      <c r="EQ8" s="160"/>
-      <c r="ER8" s="164"/>
-      <c r="ES8" s="160"/>
+      <c r="EP8" s="164" t="s">
+        <v>9</v>
+      </c>
+      <c r="EQ8" s="160" t="s">
+        <v>3</v>
+      </c>
+      <c r="ER8" s="164" t="s">
+        <v>9</v>
+      </c>
+      <c r="ES8" s="160" t="s">
+        <v>3</v>
+      </c>
       <c r="ET8" s="164"/>
       <c r="EU8" s="160"/>
       <c r="EV8" s="164"/>
@@ -10045,10 +10083,18 @@
       <c r="EM10" s="160"/>
       <c r="EN10" s="159"/>
       <c r="EO10" s="160"/>
-      <c r="EP10" s="159"/>
-      <c r="EQ10" s="160"/>
-      <c r="ER10" s="159"/>
-      <c r="ES10" s="160"/>
+      <c r="EP10" s="159" t="s">
+        <v>1</v>
+      </c>
+      <c r="EQ10" s="160" t="s">
+        <v>3</v>
+      </c>
+      <c r="ER10" s="159" t="s">
+        <v>14</v>
+      </c>
+      <c r="ES10" s="160" t="s">
+        <v>3</v>
+      </c>
       <c r="ET10" s="159"/>
       <c r="EU10" s="160"/>
       <c r="EV10" s="159"/>
@@ -10789,10 +10835,18 @@
       <c r="EM12" s="160"/>
       <c r="EN12" s="159"/>
       <c r="EO12" s="160"/>
-      <c r="EP12" s="159"/>
-      <c r="EQ12" s="160"/>
-      <c r="ER12" s="159"/>
-      <c r="ES12" s="160"/>
+      <c r="EP12" s="159" t="s">
+        <v>17</v>
+      </c>
+      <c r="EQ12" s="160" t="s">
+        <v>3</v>
+      </c>
+      <c r="ER12" s="159" t="s">
+        <v>17</v>
+      </c>
+      <c r="ES12" s="160" t="s">
+        <v>3</v>
+      </c>
       <c r="ET12" s="159"/>
       <c r="EU12" s="160"/>
       <c r="EV12" s="159"/>
@@ -11527,14 +11581,26 @@
       <c r="EI14" s="160"/>
       <c r="EJ14" s="159"/>
       <c r="EK14" s="160"/>
-      <c r="EL14" s="159"/>
-      <c r="EM14" s="160"/>
+      <c r="EL14" s="159" t="s">
+        <v>14</v>
+      </c>
+      <c r="EM14" s="160" t="s">
+        <v>3</v>
+      </c>
       <c r="EN14" s="159"/>
       <c r="EO14" s="160"/>
-      <c r="EP14" s="159"/>
-      <c r="EQ14" s="160"/>
-      <c r="ER14" s="159"/>
-      <c r="ES14" s="160"/>
+      <c r="EP14" s="159" t="s">
+        <v>14</v>
+      </c>
+      <c r="EQ14" s="160" t="s">
+        <v>3</v>
+      </c>
+      <c r="ER14" s="159" t="s">
+        <v>1</v>
+      </c>
+      <c r="ES14" s="160" t="s">
+        <v>3</v>
+      </c>
       <c r="ET14" s="159"/>
       <c r="EU14" s="160"/>
       <c r="EV14" s="159"/>
@@ -12271,14 +12337,26 @@
       <c r="EI16" s="160"/>
       <c r="EJ16" s="159"/>
       <c r="EK16" s="160"/>
-      <c r="EL16" s="159"/>
-      <c r="EM16" s="160"/>
+      <c r="EL16" s="159" t="s">
+        <v>21</v>
+      </c>
+      <c r="EM16" s="160" t="s">
+        <v>3</v>
+      </c>
       <c r="EN16" s="159"/>
       <c r="EO16" s="160"/>
-      <c r="EP16" s="159"/>
-      <c r="EQ16" s="160"/>
-      <c r="ER16" s="159"/>
-      <c r="ES16" s="160"/>
+      <c r="EP16" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="EQ16" s="160" t="s">
+        <v>3</v>
+      </c>
+      <c r="ER16" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="ES16" s="160" t="s">
+        <v>3</v>
+      </c>
       <c r="ET16" s="159"/>
       <c r="EU16" s="160"/>
       <c r="EV16" s="159"/>
@@ -13007,14 +13085,26 @@
       <c r="EI18" s="160"/>
       <c r="EJ18" s="159"/>
       <c r="EK18" s="160"/>
-      <c r="EL18" s="159"/>
-      <c r="EM18" s="160"/>
+      <c r="EL18" s="159" t="s">
+        <v>4</v>
+      </c>
+      <c r="EM18" s="160" t="s">
+        <v>3</v>
+      </c>
       <c r="EN18" s="159"/>
       <c r="EO18" s="160"/>
-      <c r="EP18" s="159"/>
-      <c r="EQ18" s="160"/>
-      <c r="ER18" s="159"/>
-      <c r="ES18" s="160"/>
+      <c r="EP18" s="159" t="s">
+        <v>17</v>
+      </c>
+      <c r="EQ18" s="160" t="s">
+        <v>3</v>
+      </c>
+      <c r="ER18" s="159" t="s">
+        <v>17</v>
+      </c>
+      <c r="ES18" s="160" t="s">
+        <v>3</v>
+      </c>
       <c r="ET18" s="159"/>
       <c r="EU18" s="160"/>
       <c r="EV18" s="159"/>
@@ -13715,14 +13805,26 @@
       <c r="EI20" s="160"/>
       <c r="EJ20" s="159"/>
       <c r="EK20" s="160"/>
-      <c r="EL20" s="159"/>
-      <c r="EM20" s="160"/>
+      <c r="EL20" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="EM20" s="160">
+        <v>5</v>
+      </c>
       <c r="EN20" s="159"/>
       <c r="EO20" s="160"/>
-      <c r="EP20" s="159"/>
-      <c r="EQ20" s="160"/>
-      <c r="ER20" s="159"/>
-      <c r="ES20" s="160"/>
+      <c r="EP20" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="EQ20" s="160">
+        <v>7.25</v>
+      </c>
+      <c r="ER20" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="ES20" s="160">
+        <v>13</v>
+      </c>
       <c r="ET20" s="159"/>
       <c r="EU20" s="160"/>
       <c r="EV20" s="159"/>
@@ -15286,610 +15388,748 @@
     <mergeCell ref="JN23:JO23"/>
   </mergeCells>
   <conditionalFormatting sqref="DE5">
-    <cfRule type="containsText" dxfId="0" priority="113" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="147" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="112">
+    <cfRule type="containsBlanks" dxfId="1" priority="146">
       <formula>LEN(TRIM(DE5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG5">
-    <cfRule type="containsText" dxfId="0" priority="111" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="145" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="110">
+    <cfRule type="containsBlanks" dxfId="1" priority="144">
       <formula>LEN(TRIM(DG5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DU5">
-    <cfRule type="containsText" dxfId="0" priority="51" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="85" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DU5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="50">
+    <cfRule type="containsBlanks" dxfId="1" priority="84">
       <formula>LEN(TRIM(DU5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG5">
-    <cfRule type="containsText" dxfId="0" priority="14" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="48" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="13">
+    <cfRule type="containsBlanks" dxfId="1" priority="47">
       <formula>LEN(TRIM(EG5))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="ES5">
+    <cfRule type="containsText" dxfId="0" priority="16" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",ES5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="15">
+      <formula>LEN(TRIM(ES5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="DC8">
-    <cfRule type="containsText" dxfId="0" priority="133" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="167" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DC8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="132">
+    <cfRule type="containsBlanks" dxfId="1" priority="166">
       <formula>LEN(TRIM(DC8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DE8">
-    <cfRule type="containsText" dxfId="0" priority="115" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="149" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="114">
+    <cfRule type="containsBlanks" dxfId="1" priority="148">
       <formula>LEN(TRIM(DE8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG8">
-    <cfRule type="containsText" dxfId="0" priority="109" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="143" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="108">
+    <cfRule type="containsBlanks" dxfId="1" priority="142">
       <formula>LEN(TRIM(DG8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI8">
-    <cfRule type="containsText" dxfId="0" priority="87" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="121" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="86">
+    <cfRule type="containsBlanks" dxfId="1" priority="120">
       <formula>LEN(TRIM(DI8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK8">
-    <cfRule type="containsText" dxfId="0" priority="85" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="119" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="84">
+    <cfRule type="containsBlanks" dxfId="1" priority="118">
       <formula>LEN(TRIM(DK8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ8">
-    <cfRule type="containsText" dxfId="0" priority="37" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="71" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="36">
+    <cfRule type="containsBlanks" dxfId="1" priority="70">
       <formula>LEN(TRIM(DQ8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DS8">
-    <cfRule type="containsText" dxfId="0" priority="49" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="83" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DS8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="48">
+    <cfRule type="containsBlanks" dxfId="1" priority="82">
       <formula>LEN(TRIM(DS8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DU8">
-    <cfRule type="containsText" dxfId="0" priority="53" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="87" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DU8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="52">
+    <cfRule type="containsBlanks" dxfId="1" priority="86">
       <formula>LEN(TRIM(DU8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DW8">
-    <cfRule type="containsText" dxfId="0" priority="73" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="107" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DW8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="72">
+    <cfRule type="containsBlanks" dxfId="1" priority="106">
       <formula>LEN(TRIM(DW8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DY8">
-    <cfRule type="containsText" dxfId="0" priority="31" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="65" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DY8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="30">
+    <cfRule type="containsBlanks" dxfId="1" priority="64">
       <formula>LEN(TRIM(DY8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EE8">
-    <cfRule type="containsText" dxfId="0" priority="20" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="54" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EE8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="19">
+    <cfRule type="containsBlanks" dxfId="1" priority="53">
       <formula>LEN(TRIM(EE8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG8">
-    <cfRule type="containsText" dxfId="0" priority="12" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="46" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="11">
+    <cfRule type="containsBlanks" dxfId="1" priority="45">
       <formula>LEN(TRIM(EG8))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="EQ8">
+    <cfRule type="containsText" dxfId="0" priority="28" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EQ8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="27">
+      <formula>LEN(TRIM(EQ8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="ES8">
+    <cfRule type="containsText" dxfId="0" priority="14" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",ES8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="13">
+      <formula>LEN(TRIM(ES8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="DE10">
-    <cfRule type="containsText" dxfId="0" priority="117" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="151" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="116">
+    <cfRule type="containsBlanks" dxfId="1" priority="150">
       <formula>LEN(TRIM(DE10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI10">
-    <cfRule type="containsText" dxfId="0" priority="89" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="123" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="88">
+    <cfRule type="containsBlanks" dxfId="1" priority="122">
       <formula>LEN(TRIM(DI10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK10">
-    <cfRule type="containsText" dxfId="0" priority="83" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="117" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="82">
+    <cfRule type="containsBlanks" dxfId="1" priority="116">
       <formula>LEN(TRIM(DK10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ10">
-    <cfRule type="containsText" dxfId="0" priority="39" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="73" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="38">
+    <cfRule type="containsBlanks" dxfId="1" priority="72">
       <formula>LEN(TRIM(DQ10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DS10">
-    <cfRule type="containsText" dxfId="0" priority="47" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="81" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DS10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="46">
+    <cfRule type="containsBlanks" dxfId="1" priority="80">
       <formula>LEN(TRIM(DS10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DW10">
-    <cfRule type="containsText" dxfId="0" priority="71" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="105" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DW10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="70">
+    <cfRule type="containsBlanks" dxfId="1" priority="104">
       <formula>LEN(TRIM(DW10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DY10">
-    <cfRule type="containsText" dxfId="0" priority="29" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="63" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DY10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="28">
+    <cfRule type="containsBlanks" dxfId="1" priority="62">
       <formula>LEN(TRIM(DY10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG10">
-    <cfRule type="containsText" dxfId="0" priority="10" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="44" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="9">
+    <cfRule type="containsBlanks" dxfId="1" priority="43">
       <formula>LEN(TRIM(EG10))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="EQ10">
+    <cfRule type="containsText" dxfId="0" priority="26" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EQ10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="25">
+      <formula>LEN(TRIM(EQ10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="ES10">
+    <cfRule type="containsText" dxfId="0" priority="12" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",ES10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="11">
+      <formula>LEN(TRIM(ES10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="CR11">
-    <cfRule type="containsText" dxfId="0" priority="141" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="175" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",CR11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CT11">
-    <cfRule type="containsText" dxfId="0" priority="140" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="174" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",CT11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DX11">
-    <cfRule type="containsText" dxfId="0" priority="32" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="66" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DX11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EF11">
-    <cfRule type="containsText" dxfId="0" priority="21" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="55" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EF11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC12">
-    <cfRule type="containsText" dxfId="0" priority="131" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="165" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DC12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="130">
+    <cfRule type="containsBlanks" dxfId="1" priority="164">
       <formula>LEN(TRIM(DC12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DE12">
-    <cfRule type="containsText" dxfId="0" priority="119" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="153" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="118">
+    <cfRule type="containsBlanks" dxfId="1" priority="152">
       <formula>LEN(TRIM(DE12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG12">
-    <cfRule type="containsText" dxfId="0" priority="107" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="141" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="106">
+    <cfRule type="containsBlanks" dxfId="1" priority="140">
       <formula>LEN(TRIM(DG12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI12">
-    <cfRule type="containsText" dxfId="0" priority="91" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="125" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="90">
+    <cfRule type="containsBlanks" dxfId="1" priority="124">
       <formula>LEN(TRIM(DI12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ12">
-    <cfRule type="containsText" dxfId="0" priority="43" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="77" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="42">
+    <cfRule type="containsBlanks" dxfId="1" priority="76">
       <formula>LEN(TRIM(DQ12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DS12">
-    <cfRule type="containsText" dxfId="0" priority="45" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="79" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DS12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="44">
+    <cfRule type="containsBlanks" dxfId="1" priority="78">
       <formula>LEN(TRIM(DS12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DU12">
-    <cfRule type="containsText" dxfId="0" priority="55" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="89" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DU12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="54">
+    <cfRule type="containsBlanks" dxfId="1" priority="88">
       <formula>LEN(TRIM(DU12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DW12">
-    <cfRule type="containsText" dxfId="0" priority="69" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="103" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DW12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="68">
+    <cfRule type="containsBlanks" dxfId="1" priority="102">
       <formula>LEN(TRIM(DW12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EE12">
-    <cfRule type="containsText" dxfId="0" priority="18" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="52" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EE12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="17">
+    <cfRule type="containsBlanks" dxfId="1" priority="51">
       <formula>LEN(TRIM(EE12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG12">
-    <cfRule type="containsText" dxfId="0" priority="8" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="42" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="7">
+    <cfRule type="containsBlanks" dxfId="1" priority="41">
       <formula>LEN(TRIM(EG12))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="EQ12">
+    <cfRule type="containsText" dxfId="0" priority="24" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EQ12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="23">
+      <formula>LEN(TRIM(EQ12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="ES12">
+    <cfRule type="containsText" dxfId="0" priority="10" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",ES12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="9">
+      <formula>LEN(TRIM(ES12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="DC14">
-    <cfRule type="containsText" dxfId="0" priority="129" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="163" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DC14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="128">
+    <cfRule type="containsBlanks" dxfId="1" priority="162">
       <formula>LEN(TRIM(DC14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DE14">
-    <cfRule type="containsText" dxfId="0" priority="121" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="155" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="120">
+    <cfRule type="containsBlanks" dxfId="1" priority="154">
       <formula>LEN(TRIM(DE14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI14">
-    <cfRule type="containsText" dxfId="0" priority="93" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="127" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="92">
+    <cfRule type="containsBlanks" dxfId="1" priority="126">
       <formula>LEN(TRIM(DI14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK14">
-    <cfRule type="containsText" dxfId="0" priority="81" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="115" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="80">
+    <cfRule type="containsBlanks" dxfId="1" priority="114">
       <formula>LEN(TRIM(DK14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ14">
-    <cfRule type="containsText" dxfId="0" priority="41" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="75" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="40">
+    <cfRule type="containsBlanks" dxfId="1" priority="74">
       <formula>LEN(TRIM(DQ14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DS14">
-    <cfRule type="containsText" dxfId="0" priority="57" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="91" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DS14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="56">
+    <cfRule type="containsBlanks" dxfId="1" priority="90">
       <formula>LEN(TRIM(DS14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DW14">
-    <cfRule type="containsText" dxfId="0" priority="67" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="101" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DW14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="66">
+    <cfRule type="containsBlanks" dxfId="1" priority="100">
       <formula>LEN(TRIM(DW14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DY14">
-    <cfRule type="containsText" dxfId="0" priority="27" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="61" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DY14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="26">
+    <cfRule type="containsBlanks" dxfId="1" priority="60">
       <formula>LEN(TRIM(DY14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EE14">
-    <cfRule type="containsText" dxfId="0" priority="16" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="50" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EE14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="15">
+    <cfRule type="containsBlanks" dxfId="1" priority="49">
       <formula>LEN(TRIM(EE14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG14">
-    <cfRule type="containsText" dxfId="0" priority="6" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="40" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="5">
+    <cfRule type="containsBlanks" dxfId="1" priority="39">
       <formula>LEN(TRIM(EG14))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="EM14">
+    <cfRule type="containsText" dxfId="0" priority="34" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EM14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="33">
+      <formula>LEN(TRIM(EM14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EQ14">
+    <cfRule type="containsText" dxfId="0" priority="22" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EQ14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="21">
+      <formula>LEN(TRIM(EQ14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="ES14">
+    <cfRule type="containsText" dxfId="0" priority="8" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",ES14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="7">
+      <formula>LEN(TRIM(ES14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="DE16">
-    <cfRule type="containsText" dxfId="0" priority="123" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="157" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="122">
+    <cfRule type="containsBlanks" dxfId="1" priority="156">
       <formula>LEN(TRIM(DE16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG16">
-    <cfRule type="containsText" dxfId="0" priority="105" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="139" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="104">
+    <cfRule type="containsBlanks" dxfId="1" priority="138">
       <formula>LEN(TRIM(DG16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI16">
-    <cfRule type="containsText" dxfId="0" priority="95" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="129" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="94">
+    <cfRule type="containsBlanks" dxfId="1" priority="128">
       <formula>LEN(TRIM(DI16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK16">
-    <cfRule type="containsText" dxfId="0" priority="79" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="113" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="78">
+    <cfRule type="containsBlanks" dxfId="1" priority="112">
       <formula>LEN(TRIM(DK16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DS16">
-    <cfRule type="containsText" dxfId="0" priority="59" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="93" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DS16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="58">
+    <cfRule type="containsBlanks" dxfId="1" priority="92">
       <formula>LEN(TRIM(DS16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DU16">
-    <cfRule type="containsText" dxfId="0" priority="63" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="97" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DU16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="62">
+    <cfRule type="containsBlanks" dxfId="1" priority="96">
       <formula>LEN(TRIM(DU16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DW16">
-    <cfRule type="containsText" dxfId="0" priority="65" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="99" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DW16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="64">
+    <cfRule type="containsBlanks" dxfId="1" priority="98">
       <formula>LEN(TRIM(DW16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG16">
-    <cfRule type="containsText" dxfId="0" priority="4" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="38" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="3">
+    <cfRule type="containsBlanks" dxfId="1" priority="37">
       <formula>LEN(TRIM(EG16))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="EM16">
+    <cfRule type="containsText" dxfId="0" priority="32" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EM16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="31">
+      <formula>LEN(TRIM(EM16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EQ16">
+    <cfRule type="containsText" dxfId="0" priority="20" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EQ16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="19">
+      <formula>LEN(TRIM(EQ16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="ES16">
+    <cfRule type="containsText" dxfId="0" priority="6" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",ES16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="5">
+      <formula>LEN(TRIM(ES16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="DE18">
-    <cfRule type="containsText" dxfId="0" priority="125" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="159" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="124">
+    <cfRule type="containsBlanks" dxfId="1" priority="158">
       <formula>LEN(TRIM(DE18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG18">
-    <cfRule type="containsText" dxfId="0" priority="103" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="137" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="102">
+    <cfRule type="containsBlanks" dxfId="1" priority="136">
       <formula>LEN(TRIM(DG18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI18">
-    <cfRule type="containsText" dxfId="0" priority="97" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="131" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="96">
+    <cfRule type="containsBlanks" dxfId="1" priority="130">
       <formula>LEN(TRIM(DI18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK18">
-    <cfRule type="containsText" dxfId="0" priority="77" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="111" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="76">
+    <cfRule type="containsBlanks" dxfId="1" priority="110">
       <formula>LEN(TRIM(DK18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ18">
-    <cfRule type="containsText" dxfId="0" priority="35" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="69" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="34">
+    <cfRule type="containsBlanks" dxfId="1" priority="68">
       <formula>LEN(TRIM(DQ18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DY18">
-    <cfRule type="containsText" dxfId="0" priority="25" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="59" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DY18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="24">
+    <cfRule type="containsBlanks" dxfId="1" priority="58">
       <formula>LEN(TRIM(DY18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG18">
-    <cfRule type="containsText" dxfId="0" priority="2" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="36" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="1">
+    <cfRule type="containsBlanks" dxfId="1" priority="35">
       <formula>LEN(TRIM(EG18))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="EM18">
+    <cfRule type="containsText" dxfId="0" priority="30" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EM18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="29">
+      <formula>LEN(TRIM(EM18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EQ18">
+    <cfRule type="containsText" dxfId="0" priority="18" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EQ18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="17">
+      <formula>LEN(TRIM(EQ18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="ES18">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",ES18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="3">
+      <formula>LEN(TRIM(ES18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="DC20">
-    <cfRule type="containsText" dxfId="0" priority="127" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="161" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DC20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="126">
+    <cfRule type="containsBlanks" dxfId="1" priority="160">
       <formula>LEN(TRIM(DC20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG20">
-    <cfRule type="containsText" dxfId="0" priority="101" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="135" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="100">
+    <cfRule type="containsBlanks" dxfId="1" priority="134">
       <formula>LEN(TRIM(DG20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI20">
-    <cfRule type="containsText" dxfId="0" priority="99" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="133" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="98">
+    <cfRule type="containsBlanks" dxfId="1" priority="132">
       <formula>LEN(TRIM(DI20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK20">
-    <cfRule type="containsText" dxfId="0" priority="75" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="109" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="74">
+    <cfRule type="containsBlanks" dxfId="1" priority="108">
       <formula>LEN(TRIM(DK20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DU20">
-    <cfRule type="containsText" dxfId="0" priority="61" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="95" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DU20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="60">
+    <cfRule type="containsBlanks" dxfId="1" priority="94">
       <formula>LEN(TRIM(DU20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DX3:DX20">
-    <cfRule type="containsText" dxfId="2" priority="33" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="67" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",DX3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ED3:ED20">
-    <cfRule type="containsText" dxfId="2" priority="23" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="57" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",ED3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EF3:EF20">
-    <cfRule type="containsText" dxfId="2" priority="22" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="56" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",EF3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B3:B21 D3:D21 KV3:KV21 LH3:LH21 KT3:KT21 KR3:KR21 F3:F21 KP3:KP21 KN3:KN21 KL3:KL21 H3:H21 KJ3:KJ21 KH3:KH21 KF3:KF21 J3:J21 KD3:KD21 KB3:KB21 JZ3:JZ21 L3:L21 JX3:JX21 JV3:JV21 JT3:JT21 N3:N21 JR3:JR21 P3:P21 JP3:JP21 R3:R21 JN3:JN21 T3:T21 JL3:JL21 V3:V21 JJ3:JJ21 X3:X21 JH3:JH21 JF3:JF21 Z3:Z21 JD3:JD21 JB3:JB21 AB3:AB21 IZ3:IZ21 IX3:IX21 AD3:AD21 IV3:IV21 IT3:IT21 AF3:AF21 IR3:IR21 IP3:IP21 AH3:AH21 IN3:IN21 IL3:IL21 AJ3:AJ21 IJ3:IJ21 IH3:IH21 AL3:AL21 IF3:IF21 ID3:ID21 AN3:AN21 IB3:IB21 HZ3:HZ21 AP3:AP21 HX3:HX21 HV3:HV21 AR3:AR21 HT3:HT21 HR3:HR21 AT3:AT21 HP3:HP21 HN3:HN21 AV3:AV21 HL3:HL21 HJ3:HJ21 AX3:AX21 HH3:HH21 HF3:HF21 AZ3:AZ21 HD3:HD21 HB3:HB21 BB3:BB21 GZ3:GZ21 GX3:GX21 BD3:BD21 GV3:GV21 GT3:GT21 BF3:BF21 GR3:GR21 GP3:GP21 BH3:BH21 GN3:GN21 GL3:GL21 BJ3:BJ21 GJ3:GJ21 GH3:GH21 BL3:BL21 GF3:GF21 GD3:GD21 BN3:BN21 GB3:GB21 FZ3:FZ21 BP3:BP21 FX3:FX21 FV3:FV21 BR3:BR21 FT3:FT21 FR3:FR21 BT3:BT21 FP3:FP21 FN3:FN21 BV3:BV21 FL3:FL21 FJ3:FJ21 BX3:BX21 FH3:FH21 FF3:FF21 BZ3:BZ21 FD3:FD21 FB3:FB21 CB3:CB21 EZ3:EZ21 EX3:EX21 CD3:CD21 EV3:EV21 ET3:ET21 CF3:CF21 ER3:ER21 EP3:EP21 CH3:CH21 EN3:EN21 EL3:EL21 CJ3:CJ21 EJ3:EJ21 EH3:EH21 CL3:CL21 EF21 ED21 CN3:CN21 EB3:EB21 DZ3:DZ21 CP3:CP21 DX21 DV21 CR3:CR21 DT21 DR21 CT3:CT21 DP21 DN3:DN21 CV3:CV21 DL3:DL21 DJ21 CX3:CX21 DH21 DF21 CZ3:CZ21 DD21 DB21 LI11 KU11 KS11 KW11:LG11 KQ11 KO11 KM11 LF12:LF21 KK11 KI11 KG11 LD12:LD21 KE11 KC11 KA11 LB12:LB21 JY11 JW11 JU11 KZ12:KZ21 JS11 JQ11 JO11 JM11 JK11 JI11 JG11 W11 JE11 JC11 Y11 JA11 IY11 AA11 IW11 IU11 AC11 IS11 IQ11 AE11 IO11 IM11 AG11 IK11 II11 AI11 IG11 IE11 AK11 IC11 IA11 AM11 HY11 HW11 AO11 HU11 HS11 AQ11 HQ11 HO11 AS11 HM11 HK11 AU11 HI11 HG11 AW11 HE11 HC11 AY11 HA11 GY11 BA11 GW11 GU11 BC11 GS11 GQ11 BE11 GO11 GM11 BG11 GK11 GI11 BI11 GG11 GE11 BK11 GC11 GA11 BM11 FY11 FW11 BO11 FU11 FS11 BQ11 FQ11 FO11 BS11 FM11 FK11 BU11 FI11 FG11 BW11 FE11 FC11 BY11 FA11 EY11 CA11 EW11 EU11 CC11 ES11 EQ11 CE11 EO11 EM11 CG11 EK11 EI11 CI11 EG11 EE11 CK11 EC11 EA11 CM11 DY11 CO11 CQ11 DO11 CS11 DM11 CU11 CW11 CY11 DA11 KX3:KX10 KX12:KX21 KZ3:KZ10 LB3:LB10 LD3:LD10 LF3:LF10">
-    <cfRule type="containsText" dxfId="2" priority="146" operator="between" text="占">
+  <conditionalFormatting sqref="EP3:EP20">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",EP3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="ER3:ER20">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",ER3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3:B21 D3:D21 KV3:KV21 LH3:LH21 KT3:KT21 KR3:KR21 F3:F21 KP3:KP21 KN3:KN21 KL3:KL21 H3:H21 KJ3:KJ21 KH3:KH21 KF3:KF21 J3:J21 KD3:KD21 KB3:KB21 JZ3:JZ21 L3:L21 JX3:JX21 JV3:JV21 JT3:JT21 N3:N21 JR3:JR21 P3:P21 JP3:JP21 R3:R21 JN3:JN21 T3:T21 JL3:JL21 V3:V21 JJ3:JJ21 X3:X21 JH3:JH21 JF3:JF21 Z3:Z21 JD3:JD21 JB3:JB21 AB3:AB21 IZ3:IZ21 IX3:IX21 AD3:AD21 IV3:IV21 IT3:IT21 AF3:AF21 IR3:IR21 IP3:IP21 AH3:AH21 IN3:IN21 IL3:IL21 AJ3:AJ21 IJ3:IJ21 IH3:IH21 AL3:AL21 IF3:IF21 ID3:ID21 AN3:AN21 IB3:IB21 HZ3:HZ21 AP3:AP21 HX3:HX21 HV3:HV21 AR3:AR21 HT3:HT21 HR3:HR21 AT3:AT21 HP3:HP21 HN3:HN21 AV3:AV21 HL3:HL21 HJ3:HJ21 AX3:AX21 HH3:HH21 HF3:HF21 AZ3:AZ21 HD3:HD21 HB3:HB21 BB3:BB21 GZ3:GZ21 GX3:GX21 BD3:BD21 GV3:GV21 GT3:GT21 BF3:BF21 GR3:GR21 GP3:GP21 BH3:BH21 GN3:GN21 GL3:GL21 BJ3:BJ21 GJ3:GJ21 GH3:GH21 BL3:BL21 GF3:GF21 GD3:GD21 BN3:BN21 GB3:GB21 FZ3:FZ21 BP3:BP21 FX3:FX21 FV3:FV21 BR3:BR21 FT3:FT21 FR3:FR21 BT3:BT21 FP3:FP21 FN3:FN21 BV3:BV21 FL3:FL21 FJ3:FJ21 BX3:BX21 FH3:FH21 FF3:FF21 BZ3:BZ21 FD3:FD21 FB3:FB21 CB3:CB21 EZ3:EZ21 EX3:EX21 CD3:CD21 EV3:EV21 ET3:ET21 CF3:CF21 ER21 EP21 CH3:CH21 EN3:EN21 EL3:EL21 CJ3:CJ21 EJ3:EJ21 EH3:EH21 CL3:CL21 EF21 ED21 CN3:CN21 EB3:EB21 DZ3:DZ21 CP3:CP21 DX21 DV21 CR3:CR21 DT21 DR21 CT3:CT21 DP21 DN3:DN21 CV3:CV21 DL3:DL21 DJ21 CX3:CX21 DH21 DF21 CZ3:CZ21 DD21 DB21 LI11 KU11 KS11 KW11:LG11 KQ11 KO11 KM11 LF12:LF21 KK11 KI11 KG11 LD12:LD21 KE11 KC11 KA11 LB12:LB21 JY11 JW11 JU11 KZ12:KZ21 JS11 JQ11 JO11 JM11 JK11 JI11 JG11 W11 JE11 JC11 Y11 JA11 IY11 AA11 IW11 IU11 AC11 IS11 IQ11 AE11 IO11 IM11 AG11 IK11 II11 AI11 IG11 IE11 AK11 IC11 IA11 AM11 HY11 HW11 AO11 HU11 HS11 AQ11 HQ11 HO11 AS11 HM11 HK11 AU11 HI11 HG11 AW11 HE11 HC11 AY11 HA11 GY11 BA11 GW11 GU11 BC11 GS11 GQ11 BE11 GO11 GM11 BG11 GK11 GI11 BI11 GG11 GE11 BK11 GC11 GA11 BM11 FY11 FW11 BO11 FU11 FS11 BQ11 FQ11 FO11 BS11 FM11 FK11 BU11 FI11 FG11 BW11 FE11 FC11 BY11 FA11 EY11 CA11 EW11 EU11 CC11 ES11 EQ11 CE11 EO11 EM11 CG11 EK11 EI11 CI11 EG11 EE11 CK11 EC11 EA11 CM11 DY11 CO11 CQ11 DO11 CS11 DM11 CU11 CW11 CY11 DA11 KX3:KX10 KX12:KX21 KZ3:KZ10 LB3:LB10 LD3:LD10 LF3:LF10">
+    <cfRule type="containsText" dxfId="2" priority="180" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",B3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3 C5 G5 E5 G3 E3 I3 I5 K3 M3 K5 M5 LI5 LG5 LE5 LC5 LA5 KY5 KW5 KU5 KS5 KQ5 O3 Q3 S3 U3 W3 Y3 AA3 AC3 AE3 AG3 AI3 AK3 AM3 AO3 AQ3 AS3 AU3 AW3 AY3 BA3 BC3 BE3 BG3 BI3 BK3 BM3 BO3 BQ3 BS3 BU3 BW3 BY3 CA3 CC3 CE3 CG3 CI3 CK3 CM3 CO3 CQ3 CS3 CU3 CW3 CY3 DA3 DM3 DO3 DY3 EA3 EC3 EE3 EG3 EI3 EK3 EM3 EO3 EQ3 ES3 EU3 EW3 EY3 FA3 FC3 FE3 FG3 FI3 FK3 FM3 FO3 FQ3 FS3 FU3 FW3 FY3 GA3 GC3 GE3 GG3 GI3 GK3 GM3 GO3 GQ3 GS3 GU3 GW3 GY3 HA3 HC3 HE3 HG3 HI3 HK3 HM3 HO3 HQ3 HS3 HU3 HW3 HY3 IA3 IC3 IE3 IG3 II3 IK3 IM3 IO3 IQ3 IS3 IU3 IW3 IY3 JA3 JC3 JE3 JG3 JI3 JK3 JM3 JO3 JQ3 JS3 JU3 JW3 JY3 KA3 KC3 KE3 KG3 KI3 KK3 KM3 KO3 KQ3 KS3 KU3 KW3 KY3 LA3 LC3 LE3 LG3 LI3 KO5 KM5 KK5 KI5 O5 Q5 S5 U5 W5 Y5 AA5 AC5 AE5 AG5 AI5 AK5 AM5 AO5 AQ5 AS5 AU5 AW5 AY5 BA5 BC5 BE5 BG5 BI5 BK5 BM5 BO5 BQ5 BS5 BU5 BW5 BY5 CA5 CC5 CE5 CG5 CI5 CK5 CM5 CO5 CQ5 CS5 CU5 CW5 CY5 DA5 DM5 DO5 DY5 EA5 EC5 EE5 EI5 EK5 EM5 EO5 EQ5 ES5 EU5 EW5 EY5 FA5 FC5 FE5 FG5 FI5 FK5 FM5 FO5 FQ5 FS5 FU5 FW5 FY5 GA5 GC5 GE5 GG5 GI5 GK5 GM5 GO5 GQ5 GS5 GU5 GW5 GY5 HA5 HC5 HE5 HG5 HI5 HK5 HM5 HO5 HQ5 HS5 HU5 HW5 HY5 IA5 IC5 IE5 IG5 II5 IK5 IM5 IO5 IQ5 IS5 IU5 IW5 IY5 JA5 JC5 JE5 JG5 JI5 JK5 JM5 JO5 JQ5 JS5 JU5 JW5 JY5 KA5 KC5 KE5 KG5 C8 G10 E10 G8 E8 G20 E20 G18 E18 G16 E16 G14 E14 G12 E12 C10 C12 C14 C16 C18 C20 I12 I14 I16 I18 I20 I8 I10 LI20 LG20 LE20 LC20 K8 M8 K10 M10 K12 M12 K14 M14 K16 M16 K18 M18 K20 M20 HW20 HU20 HS20 HQ20 HO20 HM20 HK20 HI20 HG20 HE20 HC20 HA20 GY20 GW20 GU20 GS20 GQ20 GO20 GM20 GK20 GI20 GG20 GE20 GC20 GA20 FY20 FW20 FU20 FS20 FQ20 FO20 FM20 FK20 FI20 FG20 FE20 FC20 FA20 EY20 EW20 EU20 ES20 EQ20 EO20 EM20 EK20 EI20 EG20 EE20 EC20 EA20 DY20 DO20 DM20 DA20 CY20 CW20 CU20 CS20 CQ20 CO20 CM20 CK20 CI20 CG20 CE20 CC20 CA20 BY20 BW20 BU20 BS20 BQ20 BO20 BM20 BK20 BI20 BG20 BE20 BC20 BA20 AY20 AW20 AU20 AS20 AQ20 AO20 AM20 AK20 AI20 AG20 AE20 AC20 AA20 Y20 W20 U20 S20 Q20 O20 HY20 IA20 JI20 JK20 LI18 LG18 LE18 LC18 LA18 KY18 KW18 KU18 KS18 KQ18 KO18 KM18 KK18 KI18 KG18 KE18 KC18 KA18 JY18 JW18 JU18 JS18 JQ18 JO18 JM18 JK18 JI18 JG18 JE18 JC18 JA18 IY18 IW18 IU18 IS18 IQ18 IO18 IM18 IK18 II18 IG18 IE18 IC18 IA18 HY18 HW18 HU18 HS18 HQ18 HO18 HM18 HK18 HI18 HG18 HE18 HC18 HA18 GY18 GW18 GU18 GS18 GQ18 GO18 GM18 GK18 GI18 GG18 GE18 GC18 GA18 FY18 FW18 FU18 FS18 FQ18 FO18 FM18 FK18 FI18 FG18 FE18 FC18 FA18 EY18 EW18 EU18 ES18 EQ18 EO18 EM18 EK18 EI18 EE18 EC18 EA18 DO18 DM18 DA18 CY18 CW18 CU18 CS18 CQ18 CO18 CM18 CK18 CI18 CG18 CE18 CC18 CA18 BY18 BW18 BU18 BS18 BQ18 BO18 BM18 BK18 BI18 BG18 BE18 BC18 BA18 AY18 AW18 AU18 AS18 AQ18 AO18 AM18 AK18 AI18 AG18 AE18 AC18 AA18 Y18 W18 U18 S18 Q18 O18 IC20 IE20 JM20 JO20 LI16 LG16 LE16 LC16 LA16 KY16 KW16 KU16 KS16 KQ16 KO16 KM16 KK16 KI16 KG16 KE16 KC16 KA16 JY16 JW16 JU16 JS16 JQ16 JO16 JM16 JK16 JI16 JG16 JE16 JC16 JA16 IY16 IW16 IU16 IS16 IQ16 IO16 IM16 IK16 II16 IG16 IE16 IC16 IA16 HY16 HW16 HU16 HS16 HQ16 HO16 HM16 HK16 HI16 HG16 HE16 HC16 HA16 GY16 GW16 GU16 GS16 GQ16 GO16 GM16 GK16 GI16 GG16 GE16 GC16 GA16 FY16 FW16 FU16 FS16 FQ16 FO16 FM16 FK16 FI16 FG16 FE16 FC16 FA16 EY16 EW16 EU16 ES16 EQ16 EO16 EM16 EK16 EI16 EE16 EC16 EA16 DY16 DO16 DM16 DA16 CY16 CW16 CU16 CS16 CQ16 CO16 CM16 CK16 CI16 CG16 CE16 CC16 CA16 BY16 BW16 BU16 BS16 BQ16 BO16 BM16 BK16 BI16 BG16 BE16 BC16 BA16 AY16 AW16 AU16 AS16 AQ16 AO16 AM16 AK16 AI16 AG16 AE16 AC16 AA16 Y16 W16 U16 S16 Q16 O16 IG20 II20 JQ20 JS20 LI14 LG14 LE14 LC14 LA14 KY14 KW14 KU14 KS14 KQ14 KO14 KM14 KK14 KI14 KG14 KE14 KC14 KA14 JY14 JW14 JU14 JS14 JQ14 JO14 JM14 JK14 JI14 JG14 JE14 JC14 JA14 IY14 IW14 IU14 IS14 IQ14 IO14 IM14 IK14 II14 IG14 IE14 IC14 IA14 HY14 HW14 HU14 HS14 HQ14 HO14 HM14 HK14 HI14 HG14 HE14 HC14 HA14 GY14 GW14 GU14 GS14 GQ14 GO14 GM14 GK14 GI14 GG14 GE14 GC14 GA14 FY14 FW14 FU14 FS14 FQ14 FO14 FM14 FK14 FI14 FG14 FE14 FC14 FA14 EY14 EW14 EU14 ES14 EQ14 EO14 EM14 EK14 EI14 EC14 EA14 DO14 DM14 DA14 CY14 CW14 CU14 CS14 CQ14 CO14 CM14 CK14 CI14 CG14 CE14 CC14 CA14 BY14 BW14 BU14 BS14 BQ14 BO14 BM14 BK14 BI14 BG14 BE14 BC14 BA14 AY14 AW14 AU14 AS14 AQ14 AO14 AM14 AK14 AI14 AG14 AE14 AC14 AA14 Y14 W14 U14 S14 Q14 O14 IK20 IM20 JU20 JW20 LI12 LG12 LE12 LC12 LA12 KY12 KW12 KU12 KS12 KQ12 KO12 KM12 KK12 KI12 KG12 KE12 KC12 KA12 JY12 JW12 JU12 JS12 JQ12 JO12 JM12 JK12 JI12 JG12 JE12 JC12 JA12 IY12 IW12 IU12 IS12 IQ12 IO12 IM12 IK12 II12 IG12 IE12 IC12 IA12 HY12 HW12 HU12 HS12 HQ12 HO12 HM12 HK12 HI12 HG12 HE12 HC12 HA12 GY12 GW12 GU12 GS12 GQ12 GO12 GM12 GK12 GI12 GG12 GE12 GC12 GA12 FY12 FW12 FU12 FS12 FQ12 FO12 FM12 FK12 FI12 FG12 FE12 FC12 FA12 EY12 EW12 EU12 ES12 EQ12 EO12 EM12 EK12 EI12 EC12 EA12 DY12 DO12 DM12 DA12 CY12 CW12 CU12 CS12 CQ12 CO12 CM12 CK12 CI12 CG12 CE12 CC12 CA12 BY12 BW12 BU12 BS12 BQ12 BO12 BM12 BK12 BI12 BG12 BE12 BC12 BA12 AY12 AW12 AU12 AS12 AQ12 AO12 AM12 AK12 AI12 AG12 AE12 AC12 AA12 Y12 W12 U12 S12 Q12 O12 IO20 IQ20 JY20 KA20 LI10 LG10 LE10 LC10 LA10 KY10 KW10 KU10 KS10 KQ10 KO10 KM10 KK10 KI10 KG10 KE10 KC10 KA10 JY10 JW10 JU10 JS10 JQ10 JO10 JM10 JK10 JI10 JG10 JE10 JC10 JA10 IY10 IW10 IU10 IS10 IQ10 IO10 IM10 IK10 II10 IG10 IE10 IC10 IA10 HY10 HW10 HU10 HS10 HQ10 HO10 HM10 HK10 HI10 HG10 HE10 HC10 HA10 GY10 GW10 GU10 GS10 GQ10 GO10 GM10 GK10 GI10 GG10 GE10 GC10 GA10 FY10 FW10 FU10 FS10 FQ10 FO10 FM10 FK10 FI10 FG10 FE10 FC10 FA10 EY10 EW10 EU10 ES10 EQ10 EO10 EM10 EK10 EI10 EE10 EC10 EA10 DO10 DM10 DA10 CY10 CW10 CU10 CS10 CQ10 CO10 CM10 CK10 CI10 CG10 CE10 CC10 CA10 BY10 BW10 BU10 BS10 BQ10 BO10 BM10 BK10 BI10 BG10 BE10 BC10 BA10 AY10 AW10 AU10 AS10 AQ10 AO10 AM10 AK10 AI10 AG10 AE10 AC10 AA10 Y10 W10 U10 S10 Q10 O10 IS20 IU20 KC20 KE20 LI8 LG8 LE8 LC8 LA8 KY8 KW8 KU8 KS8 KQ8 KO8 KM8 KK8 KI8 KG8 KE8 KC8 KA8 JY8 JW8 JU8 JS8 JQ8 JO8 JM8 JK8 JI8 JG8 JE8 JC8 JA8 IY8 IW8 IU8 IS8 IQ8 IO8 IM8 IK8 II8 IG8 IE8 IC8 IA8 HY8 HW8 HU8 HS8 HQ8 HO8 HM8 HK8 HI8 HG8 HE8 HC8 HA8 GY8 GW8 GU8 GS8 GQ8 GO8 GM8 GK8 GI8 GG8 GE8 GC8 GA8 FY8 FW8 FU8 FS8 FQ8 FO8 FM8 FK8 FI8 FG8 FE8 FC8 FA8 EY8 EW8 EU8 ES8 EQ8 EO8 EM8 EK8 EI8 EC8 EA8 DO8 DM8 DA8 CY8 CW8 CU8 CS8 CQ8 CO8 CM8 CK8 CI8 CG8 CE8 CC8 CA8 BY8 BW8 BU8 BS8 BQ8 BO8 BM8 BK8 BI8 BG8 BE8 BC8 BA8 AY8 AW8 AU8 AS8 AQ8 AO8 AM8 AK8 AI8 AG8 AE8 AC8 AA8 Y8 W8 U8 S8 Q8 O8 IW20 IY20 KG20 KI20 LA20 KY20 KW20 KU20 KS20 KQ20 KO20 JG20 JE20 KM20 KK20 JC20 JA20">
-    <cfRule type="containsBlanks" dxfId="1" priority="144">
+  <conditionalFormatting sqref="C3 C5 G5 E5 G3 E3 I3 I5 K3 M3 K5 M5 LI5 LG5 LE5 LC5 LA5 KY5 KW5 KU5 KS5 KQ5 O3 Q3 S3 U3 W3 Y3 AA3 AC3 AE3 AG3 AI3 AK3 AM3 AO3 AQ3 AS3 AU3 AW3 AY3 BA3 BC3 BE3 BG3 BI3 BK3 BM3 BO3 BQ3 BS3 BU3 BW3 BY3 CA3 CC3 CE3 CG3 CI3 CK3 CM3 CO3 CQ3 CS3 CU3 CW3 CY3 DA3 DM3 DO3 DY3 EA3 EC3 EE3 EG3 EI3 EK3 EM3 EO3 EQ3 ES3 EU3 EW3 EY3 FA3 FC3 FE3 FG3 FI3 FK3 FM3 FO3 FQ3 FS3 FU3 FW3 FY3 GA3 GC3 GE3 GG3 GI3 GK3 GM3 GO3 GQ3 GS3 GU3 GW3 GY3 HA3 HC3 HE3 HG3 HI3 HK3 HM3 HO3 HQ3 HS3 HU3 HW3 HY3 IA3 IC3 IE3 IG3 II3 IK3 IM3 IO3 IQ3 IS3 IU3 IW3 IY3 JA3 JC3 JE3 JG3 JI3 JK3 JM3 JO3 JQ3 JS3 JU3 JW3 JY3 KA3 KC3 KE3 KG3 KI3 KK3 KM3 KO3 KQ3 KS3 KU3 KW3 KY3 LA3 LC3 LE3 LG3 LI3 KO5 KM5 KK5 KI5 O5 Q5 S5 U5 W5 Y5 AA5 AC5 AE5 AG5 AI5 AK5 AM5 AO5 AQ5 AS5 AU5 AW5 AY5 BA5 BC5 BE5 BG5 BI5 BK5 BM5 BO5 BQ5 BS5 BU5 BW5 BY5 CA5 CC5 CE5 CG5 CI5 CK5 CM5 CO5 CQ5 CS5 CU5 CW5 CY5 DA5 DM5 DO5 DY5 EA5 EC5 EE5 EI5 EK5 EM5 EO5 EQ5 EU5 EW5 EY5 FA5 FC5 FE5 FG5 FI5 FK5 FM5 FO5 FQ5 FS5 FU5 FW5 FY5 GA5 GC5 GE5 GG5 GI5 GK5 GM5 GO5 GQ5 GS5 GU5 GW5 GY5 HA5 HC5 HE5 HG5 HI5 HK5 HM5 HO5 HQ5 HS5 HU5 HW5 HY5 IA5 IC5 IE5 IG5 II5 IK5 IM5 IO5 IQ5 IS5 IU5 IW5 IY5 JA5 JC5 JE5 JG5 JI5 JK5 JM5 JO5 JQ5 JS5 JU5 JW5 JY5 KA5 KC5 KE5 KG5 C8 G10 E10 G8 E8 G20 E20 G18 E18 G16 E16 G14 E14 G12 E12 C10 C12 C14 C16 C18 C20 I12 I14 I16 I18 I20 I8 I10 LI20 LG20 LE20 LC20 K8 M8 K10 M10 K12 M12 K14 M14 K16 M16 K18 M18 K20 M20 HW20 HU20 HS20 HQ20 HO20 HM20 HK20 HI20 HG20 HE20 HC20 HA20 GY20 GW20 GU20 GS20 GQ20 GO20 GM20 GK20 GI20 GG20 GE20 GC20 GA20 FY20 FW20 FU20 FS20 FQ20 FO20 FM20 FK20 FI20 FG20 FE20 FC20 FA20 EY20 EW20 EU20 ES20 EQ20 EO20 EM20 EK20 EI20 EG20 EE20 EC20 EA20 DY20 DO20 DM20 DA20 CY20 CW20 CU20 CS20 CQ20 CO20 CM20 CK20 CI20 CG20 CE20 CC20 CA20 BY20 BW20 BU20 BS20 BQ20 BO20 BM20 BK20 BI20 BG20 BE20 BC20 BA20 AY20 AW20 AU20 AS20 AQ20 AO20 AM20 AK20 AI20 AG20 AE20 AC20 AA20 Y20 W20 U20 S20 Q20 O20 HY20 IA20 JI20 JK20 LI18 LG18 LE18 LC18 LA18 KY18 KW18 KU18 KS18 KQ18 KO18 KM18 KK18 KI18 KG18 KE18 KC18 KA18 JY18 JW18 JU18 JS18 JQ18 JO18 JM18 JK18 JI18 JG18 JE18 JC18 JA18 IY18 IW18 IU18 IS18 IQ18 IO18 IM18 IK18 II18 IG18 IE18 IC18 IA18 HY18 HW18 HU18 HS18 HQ18 HO18 HM18 HK18 HI18 HG18 HE18 HC18 HA18 GY18 GW18 GU18 GS18 GQ18 GO18 GM18 GK18 GI18 GG18 GE18 GC18 GA18 FY18 FW18 FU18 FS18 FQ18 FO18 FM18 FK18 FI18 FG18 FE18 FC18 FA18 EY18 EW18 EU18 EO18 EK18 EI18 EE18 EC18 EA18 DO18 DM18 DA18 CY18 CW18 CU18 CS18 CQ18 CO18 CM18 CK18 CI18 CG18 CE18 CC18 CA18 BY18 BW18 BU18 BS18 BQ18 BO18 BM18 BK18 BI18 BG18 BE18 BC18 BA18 AY18 AW18 AU18 AS18 AQ18 AO18 AM18 AK18 AI18 AG18 AE18 AC18 AA18 Y18 W18 U18 S18 Q18 O18 IC20 IE20 JM20 JO20 LI16 LG16 LE16 LC16 LA16 KY16 KW16 KU16 KS16 KQ16 KO16 KM16 KK16 KI16 KG16 KE16 KC16 KA16 JY16 JW16 JU16 JS16 JQ16 JO16 JM16 JK16 JI16 JG16 JE16 JC16 JA16 IY16 IW16 IU16 IS16 IQ16 IO16 IM16 IK16 II16 IG16 IE16 IC16 IA16 HY16 HW16 HU16 HS16 HQ16 HO16 HM16 HK16 HI16 HG16 HE16 HC16 HA16 GY16 GW16 GU16 GS16 GQ16 GO16 GM16 GK16 GI16 GG16 GE16 GC16 GA16 FY16 FW16 FU16 FS16 FQ16 FO16 FM16 FK16 FI16 FG16 FE16 FC16 FA16 EY16 EW16 EU16 EO16 EK16 EI16 EE16 EC16 EA16 DY16 DO16 DM16 DA16 CY16 CW16 CU16 CS16 CQ16 CO16 CM16 CK16 CI16 CG16 CE16 CC16 CA16 BY16 BW16 BU16 BS16 BQ16 BO16 BM16 BK16 BI16 BG16 BE16 BC16 BA16 AY16 AW16 AU16 AS16 AQ16 AO16 AM16 AK16 AI16 AG16 AE16 AC16 AA16 Y16 W16 U16 S16 Q16 O16 IG20 II20 JQ20 JS20 LI14 LG14 LE14 LC14 LA14 KY14 KW14 KU14 KS14 KQ14 KO14 KM14 KK14 KI14 KG14 KE14 KC14 KA14 JY14 JW14 JU14 JS14 JQ14 JO14 JM14 JK14 JI14 JG14 JE14 JC14 JA14 IY14 IW14 IU14 IS14 IQ14 IO14 IM14 IK14 II14 IG14 IE14 IC14 IA14 HY14 HW14 HU14 HS14 HQ14 HO14 HM14 HK14 HI14 HG14 HE14 HC14 HA14 GY14 GW14 GU14 GS14 GQ14 GO14 GM14 GK14 GI14 GG14 GE14 GC14 GA14 FY14 FW14 FU14 FS14 FQ14 FO14 FM14 FK14 FI14 FG14 FE14 FC14 FA14 EY14 EW14 EU14 EO14 EK14 EI14 EC14 EA14 DO14 DM14 DA14 CY14 CW14 CU14 CS14 CQ14 CO14 CM14 CK14 CI14 CG14 CE14 CC14 CA14 BY14 BW14 BU14 BS14 BQ14 BO14 BM14 BK14 BI14 BG14 BE14 BC14 BA14 AY14 AW14 AU14 AS14 AQ14 AO14 AM14 AK14 AI14 AG14 AE14 AC14 AA14 Y14 W14 U14 S14 Q14 O14 IK20 IM20 JU20 JW20 LI12 LG12 LE12 LC12 LA12 KY12 KW12 KU12 KS12 KQ12 KO12 KM12 KK12 KI12 KG12 KE12 KC12 KA12 JY12 JW12 JU12 JS12 JQ12 JO12 JM12 JK12 JI12 JG12 JE12 JC12 JA12 IY12 IW12 IU12 IS12 IQ12 IO12 IM12 IK12 II12 IG12 IE12 IC12 IA12 HY12 HW12 HU12 HS12 HQ12 HO12 HM12 HK12 HI12 HG12 HE12 HC12 HA12 GY12 GW12 GU12 GS12 GQ12 GO12 GM12 GK12 GI12 GG12 GE12 GC12 GA12 FY12 FW12 FU12 FS12 FQ12 FO12 FM12 FK12 FI12 FG12 FE12 FC12 FA12 EY12 EW12 EU12 EO12 EM12 EK12 EI12 EC12 EA12 DY12 DO12 DM12 DA12 CY12 CW12 CU12 CS12 CQ12 CO12 CM12 CK12 CI12 CG12 CE12 CC12 CA12 BY12 BW12 BU12 BS12 BQ12 BO12 BM12 BK12 BI12 BG12 BE12 BC12 BA12 AY12 AW12 AU12 AS12 AQ12 AO12 AM12 AK12 AI12 AG12 AE12 AC12 AA12 Y12 W12 U12 S12 Q12 O12 IO20 IQ20 JY20 KA20 LI10 LG10 LE10 LC10 LA10 KY10 KW10 KU10 KS10 KQ10 KO10 KM10 KK10 KI10 KG10 KE10 KC10 KA10 JY10 JW10 JU10 JS10 JQ10 JO10 JM10 JK10 JI10 JG10 JE10 JC10 JA10 IY10 IW10 IU10 IS10 IQ10 IO10 IM10 IK10 II10 IG10 IE10 IC10 IA10 HY10 HW10 HU10 HS10 HQ10 HO10 HM10 HK10 HI10 HG10 HE10 HC10 HA10 GY10 GW10 GU10 GS10 GQ10 GO10 GM10 GK10 GI10 GG10 GE10 GC10 GA10 FY10 FW10 FU10 FS10 FQ10 FO10 FM10 FK10 FI10 FG10 FE10 FC10 FA10 EY10 EW10 EU10 EO10 EM10 EK10 EI10 EE10 EC10 EA10 DO10 DM10 DA10 CY10 CW10 CU10 CS10 CQ10 CO10 CM10 CK10 CI10 CG10 CE10 CC10 CA10 BY10 BW10 BU10 BS10 BQ10 BO10 BM10 BK10 BI10 BG10 BE10 BC10 BA10 AY10 AW10 AU10 AS10 AQ10 AO10 AM10 AK10 AI10 AG10 AE10 AC10 AA10 Y10 W10 U10 S10 Q10 O10 IS20 IU20 KC20 KE20 LI8 LG8 LE8 LC8 LA8 KY8 KW8 KU8 KS8 KQ8 KO8 KM8 KK8 KI8 KG8 KE8 KC8 KA8 JY8 JW8 JU8 JS8 JQ8 JO8 JM8 JK8 JI8 JG8 JE8 JC8 JA8 IY8 IW8 IU8 IS8 IQ8 IO8 IM8 IK8 II8 IG8 IE8 IC8 IA8 HY8 HW8 HU8 HS8 HQ8 HO8 HM8 HK8 HI8 HG8 HE8 HC8 HA8 GY8 GW8 GU8 GS8 GQ8 GO8 GM8 GK8 GI8 GG8 GE8 GC8 GA8 FY8 FW8 FU8 FS8 FQ8 FO8 FM8 FK8 FI8 FG8 FE8 FC8 FA8 EY8 EW8 EU8 EO8 EM8 EK8 EI8 EC8 EA8 DO8 DM8 DA8 CY8 CW8 CU8 CS8 CQ8 CO8 CM8 CK8 CI8 CG8 CE8 CC8 CA8 BY8 BW8 BU8 BS8 BQ8 BO8 BM8 BK8 BI8 BG8 BE8 BC8 BA8 AY8 AW8 AU8 AS8 AQ8 AO8 AM8 AK8 AI8 AG8 AE8 AC8 AA8 Y8 W8 U8 S8 Q8 O8 IW20 IY20 KG20 KI20 LA20 KY20 KW20 KU20 KS20 KQ20 KO20 JG20 JE20 KM20 KK20 JC20 JA20">
+    <cfRule type="containsBlanks" dxfId="1" priority="178">
       <formula>LEN(TRIM(C3))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C21 E3:E21 KW3:KW21 LI3:LI21 KU3:KU21 KS3:KS21 G3:G21 KQ3:KQ21 KO3:KO21 KM3:KM21 I3:I21 KK3:KK21 KI3:KI21 KG3:KG21 K3:K21 KE3:KE21 KC3:KC21 KA3:KA21 M3:M21 JY3:JY21 JW3:JW21 JU3:JU21 O3:O21 JS3:JS21 Q3:Q21 JQ3:JQ21 S3:S21 JO3:JO21 U3:U21 JM3:JM21 W3:W21 JK3:JK21 Y3:Y21 JI3:JI21 JG3:JG21 AA3:AA21 JE3:JE21 JC3:JC21 AC3:AC21 JA3:JA21 IY3:IY21 AE3:AE21 IW3:IW21 IU3:IU21 AG3:AG21 IS3:IS21 IQ3:IQ21 AI3:AI21 IO3:IO21 IM3:IM21 AK3:AK21 IK3:IK21 II3:II21 AM3:AM21 IG3:IG21 IE3:IE21 AO3:AO21 IC3:IC21 IA3:IA21 AQ3:AQ21 HY3:HY21 HW3:HW21 AS3:AS21 HU3:HU21 HS3:HS21 AU3:AU21 HQ3:HQ21 HO3:HO21 AW3:AW21 HM3:HM21 HK3:HK21 AY3:AY21 HI3:HI21 HG3:HG21 BA3:BA21 HE3:HE21 HC3:HC21 BC3:BC21 HA3:HA21 GY3:GY21 BE3:BE21 GW3:GW21 GU3:GU21 BG3:BG21 GS3:GS21 GQ3:GQ21 BI3:BI21 GO3:GO21 GM3:GM21 BK3:BK21 GK3:GK21 GI3:GI21 BM3:BM21 GG3:GG21 GE3:GE21 BO3:BO21 GC3:GC21 GA3:GA21 BQ3:BQ21 FY3:FY21 FW3:FW21 BS3:BS21 FU3:FU21 FS3:FS21 BU3:BU21 FQ3:FQ21 FO3:FO21 BW3:BW21 FM3:FM21 FK3:FK21 BY3:BY21 FI3:FI21 FG3:FG21 CA3:CA21 FE3:FE21 FC3:FC21 CC3:CC21 FA3:FA21 EY3:EY21 CE3:CE21 EW3:EW21 EU3:EU21 CG3:CG21 ES3:ES21 EQ3:EQ21 CI3:CI21 EO3:EO21 EM3:EM21 CK3:CK21 EK3:EK21 EI3:EI21 CM3:CM21 EG3:EG4 EG6:EG7 EG9 EG11:EH11 EG13 EG15 EG17 EG19:EG21 EE3:EE7 EE9:EE11 EE13 EE15:EE21 CO3:CO21 EC3:EC21 EA3:EA21 CQ3:CQ21 DY3:DY7 DY9 DY11:DY13 DY15:DY17 DY19:DY21 DW21 CS3:CS21 DU21 DS21 CU3:CU21 DQ21 DO3:DO21 CW3:CW21 DM3:DM21 DK21 CY3:CY21 DI21 DG21 DA3:DA21 DE21 DC21 KV11 KT11 KX11:LH11 KR11 KP11 KN11 LG12:LG21 KL11 KJ11 KH11 LE12:LE21 KF11 KD11 KB11 LC12:LC21 JZ11 JX11 JV11 LA12:LA21 JT11 JR11 JP11 JN11 JL11 JJ11 JH11 X11 JF11 JD11 Z11 JB11 IZ11 AB11 IX11 IV11 AD11 IT11 IR11 AF11 IP11 IN11 AH11 IL11 IJ11 AJ11 IH11 IF11 AL11 ID11 IB11 AN11 HZ11 HX11 AP11 HV11 HT11 AR11 HR11 HP11 AT11 HN11 HL11 AV11 HJ11 HH11 AX11 HF11 HD11 AZ11 HB11 GZ11 BB11 GX11 GV11 BD11 GT11 GR11 BF11 GP11 GN11 BH11 GL11 GJ11 BJ11 GH11 GF11 BL11 GD11 GB11 BN11 FZ11 FX11 BP11 FV11 FT11 BR11 FR11 FP11 BT11 FN11 FL11 BV11 FJ11 FH11 BX11 FF11 FD11 BZ11 FB11 EZ11 CB11 EX11 EV11 CD11 ET11 ER11 CF11 EP11 EN11 CH11 EL11 EJ11 CJ11 CL11 EB11 CN11 DZ11 DN11 DL11 CV11 CX11 CZ11 KY3:KY10 KY12:KY21 LA3:LA10 LC3:LC10 LE3:LE10 LG3:LG10">
-    <cfRule type="containsText" dxfId="0" priority="145" operator="between" text="—">
+  <conditionalFormatting sqref="C3:C21 E3:E21 KW3:KW21 LI3:LI21 KU3:KU21 KS3:KS21 G3:G21 KQ3:KQ21 KO3:KO21 KM3:KM21 I3:I21 KK3:KK21 KI3:KI21 KG3:KG21 K3:K21 KE3:KE21 KC3:KC21 KA3:KA21 M3:M21 JY3:JY21 JW3:JW21 JU3:JU21 O3:O21 JS3:JS21 Q3:Q21 JQ3:JQ21 S3:S21 JO3:JO21 U3:U21 JM3:JM21 W3:W21 JK3:JK21 Y3:Y21 JI3:JI21 JG3:JG21 AA3:AA21 JE3:JE21 JC3:JC21 AC3:AC21 JA3:JA21 IY3:IY21 AE3:AE21 IW3:IW21 IU3:IU21 AG3:AG21 IS3:IS21 IQ3:IQ21 AI3:AI21 IO3:IO21 IM3:IM21 AK3:AK21 IK3:IK21 II3:II21 AM3:AM21 IG3:IG21 IE3:IE21 AO3:AO21 IC3:IC21 IA3:IA21 AQ3:AQ21 HY3:HY21 HW3:HW21 AS3:AS21 HU3:HU21 HS3:HS21 AU3:AU21 HQ3:HQ21 HO3:HO21 AW3:AW21 HM3:HM21 HK3:HK21 AY3:AY21 HI3:HI21 HG3:HG21 BA3:BA21 HE3:HE21 HC3:HC21 BC3:BC21 HA3:HA21 GY3:GY21 BE3:BE21 GW3:GW21 GU3:GU21 BG3:BG21 GS3:GS21 GQ3:GQ21 BI3:BI21 GO3:GO21 GM3:GM21 BK3:BK21 GK3:GK21 GI3:GI21 BM3:BM21 GG3:GG21 GE3:GE21 BO3:BO21 GC3:GC21 GA3:GA21 BQ3:BQ21 FY3:FY21 FW3:FW21 BS3:BS21 FU3:FU21 FS3:FS21 BU3:BU21 FQ3:FQ21 FO3:FO21 BW3:BW21 FM3:FM21 FK3:FK21 BY3:BY21 FI3:FI21 FG3:FG21 CA3:CA21 FE3:FE21 FC3:FC21 CC3:CC21 FA3:FA21 EY3:EY21 CE3:CE21 EW3:EW21 EU3:EU21 CG3:CG21 ES3:ES4 ES6:ES7 ES9 EQ11 ES11:ET11 ES13 ES15 ES17 ES19:ES21 EQ3:EQ7 EQ9 EQ13 EQ15 EQ17 EQ19:EQ21 CI3:CI21 EO3:EO21 EM3:EM13 EM15 EM17 EM19:EM21 CK3:CK21 EK3:EK21 EI3:EI21 CM3:CM21 EG3:EG4 EG6:EG7 EG9 EG11:EH11 EG13 EG15 EG17 EG19:EG21 EE3:EE7 EE9:EE11 EE13 EE15:EE21 CO3:CO21 EC3:EC21 EA3:EA21 CQ3:CQ21 DY3:DY7 DY9 DY11:DY13 DY15:DY17 DY19:DY21 DW21 CS3:CS21 DU21 DS21 CU3:CU21 DQ21 DO3:DO21 CW3:CW21 DM3:DM21 DK21 CY3:CY21 DI21 DG21 DA3:DA21 DE21 DC21 KV11 KT11 KX11:LH11 KR11 KP11 KN11 LG12:LG21 KL11 KJ11 KH11 LE12:LE21 KF11 KD11 KB11 LC12:LC21 JZ11 JX11 JV11 LA12:LA21 JT11 JR11 JP11 JN11 JL11 JJ11 JH11 X11 JF11 JD11 Z11 JB11 IZ11 AB11 IX11 IV11 AD11 IT11 IR11 AF11 IP11 IN11 AH11 IL11 IJ11 AJ11 IH11 IF11 AL11 ID11 IB11 AN11 HZ11 HX11 AP11 HV11 HT11 AR11 HR11 HP11 AT11 HN11 HL11 AV11 HJ11 HH11 AX11 HF11 HD11 AZ11 HB11 GZ11 BB11 GX11 GV11 BD11 GT11 GR11 BF11 GP11 GN11 BH11 GL11 GJ11 BJ11 GH11 GF11 BL11 GD11 GB11 BN11 FZ11 FX11 BP11 FV11 FT11 BR11 FR11 FP11 BT11 FN11 FL11 BV11 FJ11 FH11 BX11 FF11 FD11 BZ11 FB11 EZ11 CB11 EX11 EV11 CD11 CF11 EN11 CH11 EL11 EJ11 CJ11 CL11 EB11 CN11 DZ11 DN11 DL11 CV11 CX11 CZ11 KY3:KY10 KY12:KY21 LA3:LA10 LC3:LC10 LE3:LE10 LG3:LG10">
+    <cfRule type="containsText" dxfId="0" priority="179" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",C3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DB3:DB20 DD3:DD20 DF3:DF20 DH3:DH20 DJ3:DJ20 DC11 DE11 DG11 DI11 DK11">
-    <cfRule type="containsText" dxfId="2" priority="139" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="173" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",DB3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC3:DC7 DC9:DC11 DC13 DC15:DC19 DE3:DE4 DE6:DE7 DE9 DD11:DF11 DE13 DE15 DE17 DE19:DE20 DG3:DG4 DG6:DG7 DG9:DG11 DG13:DG15 DG17 DG19 DI3:DI7 DI9 DH11:DJ11 DI13 DI15 DI17 DI19 DK3:DK7 DK9 DK11:DK13 DK15 DK17 DK19">
-    <cfRule type="containsText" dxfId="0" priority="138" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="172" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DC3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC3 DE3 DG3 DI3 DK3 DC5 DI5 DK5 DE20 DC18 DC16 DG14 DK12 DG10 DC10">
-    <cfRule type="containsBlanks" dxfId="1" priority="137">
+    <cfRule type="containsBlanks" dxfId="1" priority="171">
       <formula>LEN(TRIM(DC3))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DP3:DP20 DR3:DR20 DT3:DT20 DV3:DV20 DQ11 DS11 DU11 DW11">
-    <cfRule type="containsText" dxfId="2" priority="136" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="170" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",DP3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ3 DS3 DU3 DW3 DQ5 DS5 DW5 DW20 DS20 DQ20 DW18 DU18 DS18 DQ16 DU14 DU10">
-    <cfRule type="containsBlanks" dxfId="1" priority="134">
+    <cfRule type="containsBlanks" dxfId="1" priority="168">
       <formula>LEN(TRIM(DQ3))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ3:DQ7 DQ9 DQ11:DT11 DQ13 DQ15:DQ17 DQ19:DQ20 DS3:DS7 DS9 DS13 DS15 DS17:DS20 DU3:DU4 DU6:DU7 DU9:DU11 DU13:DU15 DU17:DU19 DW3:DW7 DW9 DV11:DW11 DW13 DW15 DW17:DW20">
-    <cfRule type="containsText" dxfId="0" priority="135" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="169" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22 JO22 JM22 JK22 JI22 JG22 JE22 JC22 JA22 IY22 IW22 IU22 IS22 IQ22 IO22 IM22 IK22 II22 IG22 IE22 IC22 IA22 HY22 HW22 HU22 HS22 HQ22 HO22 HM22 HK22 HI22 HG22 HE22 HC22 HA22 GY22 GW22 GU22 GS22 GQ22 GO22 GM22 GK22 GI22 GG22 GE22 GC22 GA22 FY22 FW22 FU22 FS22 FQ22 FO22 FM22 FK22 FI22 FG22 FE22 FC22 FA22 EY22 EW22 EU22 ES22 EQ22 EO22 EM22 EK22 EI22 EG22 EE22 EC22 EA22 DY22 DW22 DU22 DS22 DQ22 DO22 DM22 DK22 DI22 DG22 DE22 DC22 DA22 CY22 CW22 CU22 CS22 CQ22 CO22 CM22 CK22 CI22 CG22 CE22 CC22 CA22 BY22 BW22 BU22 BS22 BQ22 BO22 BM22 BK22 BI22 BG22 BE22 BC22 BA22 AY22 AW22 AU22 AS22 AQ22 AO22 AM22 AK22 AI22 AG22 AE22 AC22 AA22 Y22 W22 U22 S22 Q22 O22 M22 K22 I22 G22 E22">
-    <cfRule type="containsBlanks" dxfId="3" priority="142">
+    <cfRule type="containsBlanks" dxfId="3" priority="176">
       <formula>LEN(TRIM(C22))=0</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="143" operator="between" text="—">
+    <cfRule type="containsText" dxfId="2" priority="177" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",C22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EG5 EE8 EG8 EG9 EG10 EG11 EE12 EG12 EE13 EG13 EE14 EG14 EG15 EG16 EG17 EG18 C3:C21 E3:E21 G3:G21 I3:I21 K3:K21 M3:M21 O3:O21 Q3:Q21 S3:S21 U3:U21 W3:W21 Y3:Y21 AA3:AA21 AC3:AC21 AE3:AE21 AG3:AG21 AI3:AI21 AK3:AK21 AM3:AM21 AO3:AO21 AQ3:AQ21 AS3:AS21 AU3:AU21 AW3:AW21 AY3:AY21 BA3:BA21 BC3:BC21 BE3:BE21 BG3:BG21 BI3:BI21 BK3:BK21 BM3:BM21 BO3:BO21 BQ3:BQ21 BS3:BS21 BU3:BU21 BW3:BW21 BY3:BY21 CA3:CA21 CC3:CC21 CE3:CE21 CG3:CG21 CI3:CI21 CK3:CK21 CM3:CM21 CO3:CO21 CQ3:CQ21 CS3:CS21 CU3:CU21 CW3:CW21 CY3:CY21 DA3:DA21 DC3:DC21 DE3:DE21 DG3:DG21 DI3:DI21 DK3:DK21 DM3:DM21 DO3:DO21 DQ3:DQ21 DS3:DS21 DU3:DU21 DW3:DW21 DY3:DY21 EA3:EA21 EC3:EC21 EE3:EE7 EE9:EE11 EE15:EE21 EG3:EG4 EG6:EG7 EG19:EG21 EI3:EI21 EK3:EK21 EM3:EM21 EO3:EO21 EQ3:EQ21 ES3:ES21 EU3:EU21 EW3:EW21 EY3:EY21 FA3:FA21 FC3:FC21 FE3:FE21 FG3:FG21 FI3:FI21 FK3:FK21 FM3:FM21 FO3:FO21 FQ3:FQ21 FS3:FS21 FU3:FU21 FW3:FW21 FY3:FY21 GA3:GA21 GC3:GC21 GE3:GE21 GG3:GG21 GI3:GI21 GK3:GK21 GM3:GM21 GO3:GO21 GQ3:GQ21 GS3:GS21 GU3:GU21 GW3:GW21 GY3:GY21 HA3:HA21 HC3:HC21 HE3:HE21 HG3:HG21 HI3:HI21 HK3:HK21 HM3:HM21 HO3:HO21 HQ3:HQ21 HS3:HS21 HU3:HU21 HW3:HW21 HY3:HY21 IA3:IA21 IC3:IC21 IE3:IE21 IG3:IG21 II3:II21 IK3:IK21 IM3:IM21 IO3:IO21 IQ3:IQ21 IS3:IS21 IU3:IU21 IW3:IW21 IY3:IY21 JA3:JA21 JC3:JC21 JE3:JE21 JG3:JG21 JI3:JI21 JK3:JK21 JM3:JM21 JO3:JO21">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="ES5 EQ8 ES8 EQ9 ES9 EQ10 ES10 EQ11 ES11 EQ12 ES12 EQ13 ES13 EM14 EQ14 ES14 EM15 EQ15 ES15 EM16 EQ16 ES16 EM17 EQ17 ES17 EM18 EQ18 ES18 C3:C21 E3:E21 G3:G21 I3:I21 K3:K21 M3:M21 O3:O21 Q3:Q21 S3:S21 U3:U21 W3:W21 Y3:Y21 AA3:AA21 AC3:AC21 AE3:AE21 AG3:AG21 AI3:AI21 AK3:AK21 AM3:AM21 AO3:AO21 AQ3:AQ21 AS3:AS21 AU3:AU21 AW3:AW21 AY3:AY21 BA3:BA21 BC3:BC21 BE3:BE21 BG3:BG21 BI3:BI21 BK3:BK21 BM3:BM21 BO3:BO21 BQ3:BQ21 BS3:BS21 BU3:BU21 BW3:BW21 BY3:BY21 CA3:CA21 CC3:CC21 CE3:CE21 CG3:CG21 CI3:CI21 CK3:CK21 CM3:CM21 CO3:CO21 CQ3:CQ21 CS3:CS21 CU3:CU21 CW3:CW21 CY3:CY21 DA3:DA21 DC3:DC21 DE3:DE21 DG3:DG21 DI3:DI21 DK3:DK21 DM3:DM21 DO3:DO21 DQ3:DQ21 DS3:DS21 DU3:DU21 DW3:DW21 DY3:DY21 EA3:EA21 EC3:EC21 EE3:EE21 EG3:EG21 EI3:EI21 EK3:EK21 EM3:EM13 EM19:EM21 EO3:EO21 EQ3:EQ7 EQ19:EQ21 ES3:ES4 ES6:ES7 ES19:ES21 EU3:EU21 EW3:EW21 EY3:EY21 FA3:FA21 FC3:FC21 FE3:FE21 FG3:FG21 FI3:FI21 FK3:FK21 FM3:FM21 FO3:FO21 FQ3:FQ21 FS3:FS21 FU3:FU21 FW3:FW21 FY3:FY21 GA3:GA21 GC3:GC21 GE3:GE21 GG3:GG21 GI3:GI21 GK3:GK21 GM3:GM21 GO3:GO21 GQ3:GQ21 GS3:GS21 GU3:GU21 GW3:GW21 GY3:GY21 HA3:HA21 HC3:HC21 HE3:HE21 HG3:HG21 HI3:HI21 HK3:HK21 HM3:HM21 HO3:HO21 HQ3:HQ21 HS3:HS21 HU3:HU21 HW3:HW21 HY3:HY21 IA3:IA21 IC3:IC21 IE3:IE21 IG3:IG21 II3:II21 IK3:IK21 IM3:IM21 IO3:IO21 IQ3:IQ21 IS3:IS21 IU3:IU21 IW3:IW21 IY3:IY21 JA3:JA21 JC3:JC21 JE3:JE21 JG3:JG21 JI3:JI21 JK3:JK21 JM3:JM21 JO3:JO21">
       <formula1>数据!$B$1:$B$62</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="ED21 EF21 B3:B21 D3:D21 F3:F21 H3:H21 J3:J21 L3:L21 N3:N21 P3:P21 R3:R21 T3:T21 V3:V21 X3:X21 Z3:Z21 AB3:AB21 AD3:AD21 AF3:AF21 AH3:AH21 AJ3:AJ21 AL3:AL21 AN3:AN21 AP3:AP21 AR3:AR21 AT3:AT21 AV3:AV21 AX3:AX21 AZ3:AZ21 BB3:BB21 BD3:BD21 BF3:BF21 BH3:BH21 BJ3:BJ21 BL3:BL21 BN3:BN21 BP3:BP21 BR3:BR21 BT3:BT21 BV3:BV21 BX3:BX21 BZ3:BZ21 CB3:CB21 CD3:CD21 CF3:CF21 CH3:CH21 CJ3:CJ21 CL3:CL21 CN3:CN21 CP3:CP21 CR3:CR21 CT3:CT21 CV3:CV21 CX3:CX21 CZ3:CZ21 DB3:DB21 DD3:DD21 DF3:DF21 DH3:DH21 DJ3:DJ21 DL3:DL21 DN3:DN21 DP3:DP21 DR3:DR21 DT3:DT21 DV3:DV21 DX3:DX21 DZ3:DZ21 EB3:EB21 ED3:ED20 EF3:EF20 EH3:EH21 EJ3:EJ21 EL3:EL21 EN3:EN21 EP3:EP21 ER3:ER21 ET3:ET21 EV3:EV21 EX3:EX21 EZ3:EZ21 FB3:FB21 FD3:FD21 FF3:FF21 FH3:FH21 FJ3:FJ21 FL3:FL21 FN3:FN21 FP3:FP21 FR3:FR21 FT3:FT21 FV3:FV21 FX3:FX21 FZ3:FZ21 GB3:GB21 GD3:GD21 GF3:GF21 GH3:GH21 GJ3:GJ21 GL3:GL21 GN3:GN21 GP3:GP21 GR3:GR21 GT3:GT21 GV3:GV21 GX3:GX21 GZ3:GZ21 HB3:HB21 HD3:HD21 HF3:HF21 HH3:HH21 HJ3:HJ21 HL3:HL21 HN3:HN21 HP3:HP21 HR3:HR21 HT3:HT21 HV3:HV21 HX3:HX21 HZ3:HZ21 IB3:IB21 ID3:ID21 IF3:IF21 IH3:IH21 IJ3:IJ21 IL3:IL21 IN3:IN21 IP3:IP21 IR3:IR21 IT3:IT21 IV3:IV21 IX3:IX21 IZ3:IZ21 JB3:JB21 JD3:JD21 JF3:JF21 JH3:JH21 JJ3:JJ21 JL3:JL21 JN3:JN21">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EP21 ER21 B3:B21 D3:D21 F3:F21 H3:H21 J3:J21 L3:L21 N3:N21 P3:P21 R3:R21 T3:T21 V3:V21 X3:X21 Z3:Z21 AB3:AB21 AD3:AD21 AF3:AF21 AH3:AH21 AJ3:AJ21 AL3:AL21 AN3:AN21 AP3:AP21 AR3:AR21 AT3:AT21 AV3:AV21 AX3:AX21 AZ3:AZ21 BB3:BB21 BD3:BD21 BF3:BF21 BH3:BH21 BJ3:BJ21 BL3:BL21 BN3:BN21 BP3:BP21 BR3:BR21 BT3:BT21 BV3:BV21 BX3:BX21 BZ3:BZ21 CB3:CB21 CD3:CD21 CF3:CF21 CH3:CH21 CJ3:CJ21 CL3:CL21 CN3:CN21 CP3:CP21 CR3:CR21 CT3:CT21 CV3:CV21 CX3:CX21 CZ3:CZ21 DB3:DB21 DD3:DD21 DF3:DF21 DH3:DH21 DJ3:DJ21 DL3:DL21 DN3:DN21 DP3:DP21 DR3:DR21 DT3:DT21 DV3:DV21 DX3:DX21 DZ3:DZ21 EB3:EB21 ED3:ED21 EF3:EF21 EH3:EH21 EJ3:EJ21 EL3:EL21 EN3:EN21 EP3:EP20 ER3:ER20 ET3:ET21 EV3:EV21 EX3:EX21 EZ3:EZ21 FB3:FB21 FD3:FD21 FF3:FF21 FH3:FH21 FJ3:FJ21 FL3:FL21 FN3:FN21 FP3:FP21 FR3:FR21 FT3:FT21 FV3:FV21 FX3:FX21 FZ3:FZ21 GB3:GB21 GD3:GD21 GF3:GF21 GH3:GH21 GJ3:GJ21 GL3:GL21 GN3:GN21 GP3:GP21 GR3:GR21 GT3:GT21 GV3:GV21 GX3:GX21 GZ3:GZ21 HB3:HB21 HD3:HD21 HF3:HF21 HH3:HH21 HJ3:HJ21 HL3:HL21 HN3:HN21 HP3:HP21 HR3:HR21 HT3:HT21 HV3:HV21 HX3:HX21 HZ3:HZ21 IB3:IB21 ID3:ID21 IF3:IF21 IH3:IH21 IJ3:IJ21 IL3:IL21 IN3:IN21 IP3:IP21 IR3:IR21 IT3:IT21 IV3:IV21 IX3:IX21 IZ3:IZ21 JB3:JB21 JD3:JD21 JF3:JF21 JH3:JH21 JJ3:JJ21 JL3:JL21 JN3:JN21">
       <formula1>数据!$A$1:$A$88</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C22 E22 G22 I22 K22 M22 O22 Q22 S22 U22 W22 Y22 AA22 AC22 AE22 AG22 AI22 AK22 AM22 AO22 AQ22 AS22 AU22 AW22 AY22 BA22 BC22 BE22 BG22 BI22 BK22 BM22 BO22 BQ22 BS22 BU22 BW22 BY22 CA22 CC22 CE22 CG22 CI22 CK22 CM22 CO22 CQ22 CS22 CU22 CW22 CY22 DA22 DC22 DE22 DG22 DI22 DK22 DM22 DO22 DQ22 DS22 DU22 DW22 DY22 EA22 EC22 EE22 EG22 EI22 EK22 EM22 EO22 EQ22 ES22 EU22 EW22 EY22 FA22 FC22 FE22 FG22 FI22 FK22 FM22 FO22 FQ22 FS22 FU22 FW22 FY22 GA22 GC22 GE22 GG22 GI22 GK22 GM22 GO22 GQ22 GS22 GU22 GW22 GY22 HA22 HC22 HE22 HG22 HI22 HK22 HM22 HO22 HQ22 HS22 HU22 HW22 HY22 IA22 IC22 IE22 IG22 II22 IK22 IM22 IO22 IQ22 IS22 IU22 IW22 IY22 JA22 JC22 JE22 JG22 JI22 JK22 JM22 JO22">

--- a/c/9班资料.xlsx
+++ b/c/9班资料.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1572" uniqueCount="481">
   <si>
     <t>拖课统计表</t>
   </si>
@@ -1662,6 +1662,24 @@
         <charset val="134"/>
       </rPr>
       <t>黄恩亚喜欢带北师大版的数学书，下课/体育课自由活动时经常随身携带。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+磨鞋
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>黄恩亚有时上课会磨鞋，发出噪音。</t>
     </r>
   </si>
   <si>
@@ -4314,6 +4332,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000033"/>
       <name val="等线"/>
       <charset val="134"/>
@@ -4340,12 +4364,6 @@
       <color rgb="FFC0504D"/>
       <name val="黑体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="61">
@@ -7548,8 +7566,12 @@
       <c r="ES3" s="154" t="s">
         <v>3</v>
       </c>
-      <c r="ET3" s="153"/>
-      <c r="EU3" s="154"/>
+      <c r="ET3" s="153" t="s">
+        <v>4</v>
+      </c>
+      <c r="EU3" s="154" t="s">
+        <v>3</v>
+      </c>
       <c r="EV3" s="153"/>
       <c r="EW3" s="154"/>
       <c r="EX3" s="153"/>
@@ -8300,8 +8322,12 @@
       <c r="ES5" s="160" t="s">
         <v>3</v>
       </c>
-      <c r="ET5" s="159"/>
-      <c r="EU5" s="160"/>
+      <c r="ET5" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="EU5" s="160" t="s">
+        <v>3</v>
+      </c>
       <c r="EV5" s="159"/>
       <c r="EW5" s="160"/>
       <c r="EX5" s="159"/>
@@ -9339,8 +9365,12 @@
       <c r="ES8" s="160" t="s">
         <v>3</v>
       </c>
-      <c r="ET8" s="164"/>
-      <c r="EU8" s="160"/>
+      <c r="ET8" s="164" t="s">
+        <v>1</v>
+      </c>
+      <c r="EU8" s="160" t="s">
+        <v>3</v>
+      </c>
       <c r="EV8" s="164"/>
       <c r="EW8" s="160"/>
       <c r="EX8" s="164"/>
@@ -10095,8 +10125,12 @@
       <c r="ES10" s="160" t="s">
         <v>3</v>
       </c>
-      <c r="ET10" s="159"/>
-      <c r="EU10" s="160"/>
+      <c r="ET10" s="159" t="s">
+        <v>9</v>
+      </c>
+      <c r="EU10" s="160" t="s">
+        <v>3</v>
+      </c>
       <c r="EV10" s="159"/>
       <c r="EW10" s="160"/>
       <c r="EX10" s="159"/>
@@ -10847,8 +10881,12 @@
       <c r="ES12" s="160" t="s">
         <v>3</v>
       </c>
-      <c r="ET12" s="159"/>
-      <c r="EU12" s="160"/>
+      <c r="ET12" s="159" t="s">
+        <v>1</v>
+      </c>
+      <c r="EU12" s="160" t="s">
+        <v>3</v>
+      </c>
       <c r="EV12" s="159"/>
       <c r="EW12" s="160"/>
       <c r="EX12" s="159"/>
@@ -11601,8 +11639,12 @@
       <c r="ES14" s="160" t="s">
         <v>3</v>
       </c>
-      <c r="ET14" s="159"/>
-      <c r="EU14" s="160"/>
+      <c r="ET14" s="159" t="s">
+        <v>18</v>
+      </c>
+      <c r="EU14" s="160" t="s">
+        <v>3</v>
+      </c>
       <c r="EV14" s="159"/>
       <c r="EW14" s="160"/>
       <c r="EX14" s="159"/>
@@ -12357,8 +12399,12 @@
       <c r="ES16" s="160" t="s">
         <v>3</v>
       </c>
-      <c r="ET16" s="159"/>
-      <c r="EU16" s="160"/>
+      <c r="ET16" s="159" t="s">
+        <v>6</v>
+      </c>
+      <c r="EU16" s="160" t="s">
+        <v>3</v>
+      </c>
       <c r="EV16" s="159"/>
       <c r="EW16" s="160"/>
       <c r="EX16" s="159"/>
@@ -13105,8 +13151,12 @@
       <c r="ES18" s="160" t="s">
         <v>3</v>
       </c>
-      <c r="ET18" s="159"/>
-      <c r="EU18" s="160"/>
+      <c r="ET18" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="EU18" s="160">
+        <v>7</v>
+      </c>
       <c r="EV18" s="159"/>
       <c r="EW18" s="160"/>
       <c r="EX18" s="159"/>
@@ -13825,8 +13875,12 @@
       <c r="ES20" s="160">
         <v>13</v>
       </c>
-      <c r="ET20" s="159"/>
-      <c r="EU20" s="160"/>
+      <c r="ET20" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="EU20" s="160">
+        <v>6.25</v>
+      </c>
       <c r="EV20" s="159"/>
       <c r="EW20" s="160"/>
       <c r="EX20" s="159"/>
@@ -14566,7 +14620,9 @@
       <c r="ET22" s="169" t="s">
         <v>25</v>
       </c>
-      <c r="EU22" s="170"/>
+      <c r="EU22" s="170">
+        <v>6</v>
+      </c>
       <c r="EV22" s="169" t="s">
         <v>25</v>
       </c>
@@ -15388,748 +15444,806 @@
     <mergeCell ref="JN23:JO23"/>
   </mergeCells>
   <conditionalFormatting sqref="DE5">
-    <cfRule type="containsText" dxfId="0" priority="147" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="161" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="146">
+    <cfRule type="containsBlanks" dxfId="1" priority="160">
       <formula>LEN(TRIM(DE5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG5">
-    <cfRule type="containsText" dxfId="0" priority="145" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="159" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="144">
+    <cfRule type="containsBlanks" dxfId="1" priority="158">
       <formula>LEN(TRIM(DG5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DU5">
-    <cfRule type="containsText" dxfId="0" priority="85" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="99" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DU5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="84">
+    <cfRule type="containsBlanks" dxfId="1" priority="98">
       <formula>LEN(TRIM(DU5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG5">
-    <cfRule type="containsText" dxfId="0" priority="48" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="62" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="47">
+    <cfRule type="containsBlanks" dxfId="1" priority="61">
       <formula>LEN(TRIM(EG5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ES5">
-    <cfRule type="containsText" dxfId="0" priority="16" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="30" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",ES5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="15">
+    <cfRule type="containsBlanks" dxfId="1" priority="29">
       <formula>LEN(TRIM(ES5))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="EU5">
+    <cfRule type="containsText" dxfId="0" priority="12" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EU5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="11">
+      <formula>LEN(TRIM(EU5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="DC8">
-    <cfRule type="containsText" dxfId="0" priority="167" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="181" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DC8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="166">
+    <cfRule type="containsBlanks" dxfId="1" priority="180">
       <formula>LEN(TRIM(DC8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DE8">
-    <cfRule type="containsText" dxfId="0" priority="149" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="163" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="148">
+    <cfRule type="containsBlanks" dxfId="1" priority="162">
       <formula>LEN(TRIM(DE8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG8">
-    <cfRule type="containsText" dxfId="0" priority="143" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="157" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="142">
+    <cfRule type="containsBlanks" dxfId="1" priority="156">
       <formula>LEN(TRIM(DG8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI8">
-    <cfRule type="containsText" dxfId="0" priority="121" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="135" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="120">
+    <cfRule type="containsBlanks" dxfId="1" priority="134">
       <formula>LEN(TRIM(DI8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK8">
-    <cfRule type="containsText" dxfId="0" priority="119" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="133" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="118">
+    <cfRule type="containsBlanks" dxfId="1" priority="132">
       <formula>LEN(TRIM(DK8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ8">
-    <cfRule type="containsText" dxfId="0" priority="71" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="85" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="70">
+    <cfRule type="containsBlanks" dxfId="1" priority="84">
       <formula>LEN(TRIM(DQ8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DS8">
-    <cfRule type="containsText" dxfId="0" priority="83" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="97" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DS8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="82">
+    <cfRule type="containsBlanks" dxfId="1" priority="96">
       <formula>LEN(TRIM(DS8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DU8">
-    <cfRule type="containsText" dxfId="0" priority="87" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="101" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DU8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="86">
+    <cfRule type="containsBlanks" dxfId="1" priority="100">
       <formula>LEN(TRIM(DU8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DW8">
-    <cfRule type="containsText" dxfId="0" priority="107" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="121" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DW8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="106">
+    <cfRule type="containsBlanks" dxfId="1" priority="120">
       <formula>LEN(TRIM(DW8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DY8">
-    <cfRule type="containsText" dxfId="0" priority="65" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="79" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DY8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="64">
+    <cfRule type="containsBlanks" dxfId="1" priority="78">
       <formula>LEN(TRIM(DY8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EE8">
-    <cfRule type="containsText" dxfId="0" priority="54" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="68" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EE8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="53">
+    <cfRule type="containsBlanks" dxfId="1" priority="67">
       <formula>LEN(TRIM(EE8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG8">
-    <cfRule type="containsText" dxfId="0" priority="46" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="60" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="45">
+    <cfRule type="containsBlanks" dxfId="1" priority="59">
       <formula>LEN(TRIM(EG8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EQ8">
-    <cfRule type="containsText" dxfId="0" priority="28" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="42" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EQ8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="27">
+    <cfRule type="containsBlanks" dxfId="1" priority="41">
       <formula>LEN(TRIM(EQ8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ES8">
-    <cfRule type="containsText" dxfId="0" priority="14" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="28" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",ES8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="13">
+    <cfRule type="containsBlanks" dxfId="1" priority="27">
       <formula>LEN(TRIM(ES8))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="EU8">
+    <cfRule type="containsText" dxfId="0" priority="10" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EU8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="9">
+      <formula>LEN(TRIM(EU8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="DE10">
-    <cfRule type="containsText" dxfId="0" priority="151" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="165" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="150">
+    <cfRule type="containsBlanks" dxfId="1" priority="164">
       <formula>LEN(TRIM(DE10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI10">
-    <cfRule type="containsText" dxfId="0" priority="123" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="137" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="122">
+    <cfRule type="containsBlanks" dxfId="1" priority="136">
       <formula>LEN(TRIM(DI10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK10">
-    <cfRule type="containsText" dxfId="0" priority="117" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="131" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="116">
+    <cfRule type="containsBlanks" dxfId="1" priority="130">
       <formula>LEN(TRIM(DK10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ10">
-    <cfRule type="containsText" dxfId="0" priority="73" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="87" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="72">
+    <cfRule type="containsBlanks" dxfId="1" priority="86">
       <formula>LEN(TRIM(DQ10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DS10">
-    <cfRule type="containsText" dxfId="0" priority="81" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="95" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DS10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="80">
+    <cfRule type="containsBlanks" dxfId="1" priority="94">
       <formula>LEN(TRIM(DS10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DW10">
-    <cfRule type="containsText" dxfId="0" priority="105" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="119" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DW10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="104">
+    <cfRule type="containsBlanks" dxfId="1" priority="118">
       <formula>LEN(TRIM(DW10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DY10">
-    <cfRule type="containsText" dxfId="0" priority="63" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="77" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DY10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="62">
+    <cfRule type="containsBlanks" dxfId="1" priority="76">
       <formula>LEN(TRIM(DY10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG10">
-    <cfRule type="containsText" dxfId="0" priority="44" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="58" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="43">
+    <cfRule type="containsBlanks" dxfId="1" priority="57">
       <formula>LEN(TRIM(EG10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EQ10">
-    <cfRule type="containsText" dxfId="0" priority="26" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="40" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EQ10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="25">
+    <cfRule type="containsBlanks" dxfId="1" priority="39">
       <formula>LEN(TRIM(EQ10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ES10">
-    <cfRule type="containsText" dxfId="0" priority="12" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="26" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",ES10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="11">
+    <cfRule type="containsBlanks" dxfId="1" priority="25">
       <formula>LEN(TRIM(ES10))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="EU10">
+    <cfRule type="containsText" dxfId="0" priority="8" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EU10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="7">
+      <formula>LEN(TRIM(EU10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="CR11">
-    <cfRule type="containsText" dxfId="0" priority="175" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="189" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",CR11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CT11">
-    <cfRule type="containsText" dxfId="0" priority="174" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="188" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",CT11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DX11">
-    <cfRule type="containsText" dxfId="0" priority="66" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="80" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DX11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EF11">
-    <cfRule type="containsText" dxfId="0" priority="55" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="69" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EF11)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="ET11">
+    <cfRule type="containsText" dxfId="0" priority="13" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",ET11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="DC12">
-    <cfRule type="containsText" dxfId="0" priority="165" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="179" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DC12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="164">
+    <cfRule type="containsBlanks" dxfId="1" priority="178">
       <formula>LEN(TRIM(DC12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DE12">
-    <cfRule type="containsText" dxfId="0" priority="153" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="167" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="152">
+    <cfRule type="containsBlanks" dxfId="1" priority="166">
       <formula>LEN(TRIM(DE12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG12">
-    <cfRule type="containsText" dxfId="0" priority="141" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="155" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="140">
+    <cfRule type="containsBlanks" dxfId="1" priority="154">
       <formula>LEN(TRIM(DG12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI12">
-    <cfRule type="containsText" dxfId="0" priority="125" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="139" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="124">
+    <cfRule type="containsBlanks" dxfId="1" priority="138">
       <formula>LEN(TRIM(DI12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ12">
-    <cfRule type="containsText" dxfId="0" priority="77" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="91" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="76">
+    <cfRule type="containsBlanks" dxfId="1" priority="90">
       <formula>LEN(TRIM(DQ12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DS12">
-    <cfRule type="containsText" dxfId="0" priority="79" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="93" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DS12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="78">
+    <cfRule type="containsBlanks" dxfId="1" priority="92">
       <formula>LEN(TRIM(DS12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DU12">
-    <cfRule type="containsText" dxfId="0" priority="89" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="103" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DU12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="88">
+    <cfRule type="containsBlanks" dxfId="1" priority="102">
       <formula>LEN(TRIM(DU12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DW12">
-    <cfRule type="containsText" dxfId="0" priority="103" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="117" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DW12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="102">
+    <cfRule type="containsBlanks" dxfId="1" priority="116">
       <formula>LEN(TRIM(DW12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EE12">
-    <cfRule type="containsText" dxfId="0" priority="52" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="66" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EE12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="51">
+    <cfRule type="containsBlanks" dxfId="1" priority="65">
       <formula>LEN(TRIM(EE12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG12">
-    <cfRule type="containsText" dxfId="0" priority="42" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="56" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="41">
+    <cfRule type="containsBlanks" dxfId="1" priority="55">
       <formula>LEN(TRIM(EG12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EQ12">
-    <cfRule type="containsText" dxfId="0" priority="24" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="38" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EQ12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="23">
+    <cfRule type="containsBlanks" dxfId="1" priority="37">
       <formula>LEN(TRIM(EQ12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ES12">
-    <cfRule type="containsText" dxfId="0" priority="10" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="24" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",ES12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="9">
+    <cfRule type="containsBlanks" dxfId="1" priority="23">
       <formula>LEN(TRIM(ES12))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="EU12">
+    <cfRule type="containsText" dxfId="0" priority="6" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EU12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="5">
+      <formula>LEN(TRIM(EU12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="DC14">
-    <cfRule type="containsText" dxfId="0" priority="163" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="177" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DC14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="162">
+    <cfRule type="containsBlanks" dxfId="1" priority="176">
       <formula>LEN(TRIM(DC14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DE14">
-    <cfRule type="containsText" dxfId="0" priority="155" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="169" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="154">
+    <cfRule type="containsBlanks" dxfId="1" priority="168">
       <formula>LEN(TRIM(DE14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI14">
-    <cfRule type="containsText" dxfId="0" priority="127" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="141" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="126">
+    <cfRule type="containsBlanks" dxfId="1" priority="140">
       <formula>LEN(TRIM(DI14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK14">
-    <cfRule type="containsText" dxfId="0" priority="115" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="129" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="114">
+    <cfRule type="containsBlanks" dxfId="1" priority="128">
       <formula>LEN(TRIM(DK14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ14">
-    <cfRule type="containsText" dxfId="0" priority="75" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="89" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="74">
+    <cfRule type="containsBlanks" dxfId="1" priority="88">
       <formula>LEN(TRIM(DQ14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DS14">
-    <cfRule type="containsText" dxfId="0" priority="91" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="105" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DS14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="90">
+    <cfRule type="containsBlanks" dxfId="1" priority="104">
       <formula>LEN(TRIM(DS14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DW14">
-    <cfRule type="containsText" dxfId="0" priority="101" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="115" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DW14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="100">
+    <cfRule type="containsBlanks" dxfId="1" priority="114">
       <formula>LEN(TRIM(DW14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DY14">
-    <cfRule type="containsText" dxfId="0" priority="61" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="75" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DY14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="60">
+    <cfRule type="containsBlanks" dxfId="1" priority="74">
       <formula>LEN(TRIM(DY14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EE14">
-    <cfRule type="containsText" dxfId="0" priority="50" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="64" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EE14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="49">
+    <cfRule type="containsBlanks" dxfId="1" priority="63">
       <formula>LEN(TRIM(EE14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG14">
-    <cfRule type="containsText" dxfId="0" priority="40" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="54" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="39">
+    <cfRule type="containsBlanks" dxfId="1" priority="53">
       <formula>LEN(TRIM(EG14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EM14">
-    <cfRule type="containsText" dxfId="0" priority="34" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="48" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EM14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="33">
+    <cfRule type="containsBlanks" dxfId="1" priority="47">
       <formula>LEN(TRIM(EM14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EQ14">
-    <cfRule type="containsText" dxfId="0" priority="22" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="36" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EQ14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="21">
+    <cfRule type="containsBlanks" dxfId="1" priority="35">
       <formula>LEN(TRIM(EQ14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ES14">
-    <cfRule type="containsText" dxfId="0" priority="8" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="22" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",ES14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="7">
+    <cfRule type="containsBlanks" dxfId="1" priority="21">
       <formula>LEN(TRIM(ES14))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="EU14">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EU14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="3">
+      <formula>LEN(TRIM(EU14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="DE16">
-    <cfRule type="containsText" dxfId="0" priority="157" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="171" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="156">
+    <cfRule type="containsBlanks" dxfId="1" priority="170">
       <formula>LEN(TRIM(DE16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG16">
-    <cfRule type="containsText" dxfId="0" priority="139" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="153" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="138">
+    <cfRule type="containsBlanks" dxfId="1" priority="152">
       <formula>LEN(TRIM(DG16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI16">
-    <cfRule type="containsText" dxfId="0" priority="129" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="143" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="128">
+    <cfRule type="containsBlanks" dxfId="1" priority="142">
       <formula>LEN(TRIM(DI16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK16">
-    <cfRule type="containsText" dxfId="0" priority="113" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="127" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="112">
+    <cfRule type="containsBlanks" dxfId="1" priority="126">
       <formula>LEN(TRIM(DK16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DS16">
-    <cfRule type="containsText" dxfId="0" priority="93" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="107" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DS16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="92">
+    <cfRule type="containsBlanks" dxfId="1" priority="106">
       <formula>LEN(TRIM(DS16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DU16">
-    <cfRule type="containsText" dxfId="0" priority="97" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="111" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DU16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="96">
+    <cfRule type="containsBlanks" dxfId="1" priority="110">
       <formula>LEN(TRIM(DU16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DW16">
-    <cfRule type="containsText" dxfId="0" priority="99" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="113" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DW16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="98">
+    <cfRule type="containsBlanks" dxfId="1" priority="112">
       <formula>LEN(TRIM(DW16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG16">
-    <cfRule type="containsText" dxfId="0" priority="38" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="52" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="37">
+    <cfRule type="containsBlanks" dxfId="1" priority="51">
       <formula>LEN(TRIM(EG16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EM16">
-    <cfRule type="containsText" dxfId="0" priority="32" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="46" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EM16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="31">
+    <cfRule type="containsBlanks" dxfId="1" priority="45">
       <formula>LEN(TRIM(EM16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EQ16">
-    <cfRule type="containsText" dxfId="0" priority="20" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="34" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EQ16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="19">
+    <cfRule type="containsBlanks" dxfId="1" priority="33">
       <formula>LEN(TRIM(EQ16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ES16">
-    <cfRule type="containsText" dxfId="0" priority="6" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="20" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",ES16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="5">
+    <cfRule type="containsBlanks" dxfId="1" priority="19">
       <formula>LEN(TRIM(ES16))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="EU16">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EU16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="1">
+      <formula>LEN(TRIM(EU16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="DE18">
-    <cfRule type="containsText" dxfId="0" priority="159" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="173" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="158">
+    <cfRule type="containsBlanks" dxfId="1" priority="172">
       <formula>LEN(TRIM(DE18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG18">
-    <cfRule type="containsText" dxfId="0" priority="137" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="151" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="136">
+    <cfRule type="containsBlanks" dxfId="1" priority="150">
       <formula>LEN(TRIM(DG18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI18">
-    <cfRule type="containsText" dxfId="0" priority="131" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="145" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="130">
+    <cfRule type="containsBlanks" dxfId="1" priority="144">
       <formula>LEN(TRIM(DI18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK18">
-    <cfRule type="containsText" dxfId="0" priority="111" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="125" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="110">
+    <cfRule type="containsBlanks" dxfId="1" priority="124">
       <formula>LEN(TRIM(DK18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ18">
-    <cfRule type="containsText" dxfId="0" priority="69" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="83" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="68">
+    <cfRule type="containsBlanks" dxfId="1" priority="82">
       <formula>LEN(TRIM(DQ18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DY18">
-    <cfRule type="containsText" dxfId="0" priority="59" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="73" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DY18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="58">
+    <cfRule type="containsBlanks" dxfId="1" priority="72">
       <formula>LEN(TRIM(DY18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG18">
-    <cfRule type="containsText" dxfId="0" priority="36" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="50" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="35">
+    <cfRule type="containsBlanks" dxfId="1" priority="49">
       <formula>LEN(TRIM(EG18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EM18">
-    <cfRule type="containsText" dxfId="0" priority="30" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="44" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EM18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="29">
+    <cfRule type="containsBlanks" dxfId="1" priority="43">
       <formula>LEN(TRIM(EM18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EQ18">
-    <cfRule type="containsText" dxfId="0" priority="18" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="32" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EQ18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="17">
+    <cfRule type="containsBlanks" dxfId="1" priority="31">
       <formula>LEN(TRIM(EQ18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ES18">
-    <cfRule type="containsText" dxfId="0" priority="4" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="18" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",ES18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="3">
+    <cfRule type="containsBlanks" dxfId="1" priority="17">
       <formula>LEN(TRIM(ES18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC20">
-    <cfRule type="containsText" dxfId="0" priority="161" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="175" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DC20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="160">
+    <cfRule type="containsBlanks" dxfId="1" priority="174">
       <formula>LEN(TRIM(DC20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG20">
-    <cfRule type="containsText" dxfId="0" priority="135" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="149" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="134">
+    <cfRule type="containsBlanks" dxfId="1" priority="148">
       <formula>LEN(TRIM(DG20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI20">
-    <cfRule type="containsText" dxfId="0" priority="133" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="147" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="132">
+    <cfRule type="containsBlanks" dxfId="1" priority="146">
       <formula>LEN(TRIM(DI20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK20">
-    <cfRule type="containsText" dxfId="0" priority="109" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="123" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="108">
+    <cfRule type="containsBlanks" dxfId="1" priority="122">
       <formula>LEN(TRIM(DK20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DU20">
-    <cfRule type="containsText" dxfId="0" priority="95" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="109" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DU20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="94">
+    <cfRule type="containsBlanks" dxfId="1" priority="108">
       <formula>LEN(TRIM(DU20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DX3:DX20">
-    <cfRule type="containsText" dxfId="2" priority="67" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="81" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",DX3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ED3:ED20">
-    <cfRule type="containsText" dxfId="2" priority="57" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="71" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",ED3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EF3:EF20">
-    <cfRule type="containsText" dxfId="2" priority="56" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="70" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",EF3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EP3:EP20">
-    <cfRule type="containsText" dxfId="2" priority="2" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="16" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",EP3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ER3:ER20">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="15" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",ER3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B3:B21 D3:D21 KV3:KV21 LH3:LH21 KT3:KT21 KR3:KR21 F3:F21 KP3:KP21 KN3:KN21 KL3:KL21 H3:H21 KJ3:KJ21 KH3:KH21 KF3:KF21 J3:J21 KD3:KD21 KB3:KB21 JZ3:JZ21 L3:L21 JX3:JX21 JV3:JV21 JT3:JT21 N3:N21 JR3:JR21 P3:P21 JP3:JP21 R3:R21 JN3:JN21 T3:T21 JL3:JL21 V3:V21 JJ3:JJ21 X3:X21 JH3:JH21 JF3:JF21 Z3:Z21 JD3:JD21 JB3:JB21 AB3:AB21 IZ3:IZ21 IX3:IX21 AD3:AD21 IV3:IV21 IT3:IT21 AF3:AF21 IR3:IR21 IP3:IP21 AH3:AH21 IN3:IN21 IL3:IL21 AJ3:AJ21 IJ3:IJ21 IH3:IH21 AL3:AL21 IF3:IF21 ID3:ID21 AN3:AN21 IB3:IB21 HZ3:HZ21 AP3:AP21 HX3:HX21 HV3:HV21 AR3:AR21 HT3:HT21 HR3:HR21 AT3:AT21 HP3:HP21 HN3:HN21 AV3:AV21 HL3:HL21 HJ3:HJ21 AX3:AX21 HH3:HH21 HF3:HF21 AZ3:AZ21 HD3:HD21 HB3:HB21 BB3:BB21 GZ3:GZ21 GX3:GX21 BD3:BD21 GV3:GV21 GT3:GT21 BF3:BF21 GR3:GR21 GP3:GP21 BH3:BH21 GN3:GN21 GL3:GL21 BJ3:BJ21 GJ3:GJ21 GH3:GH21 BL3:BL21 GF3:GF21 GD3:GD21 BN3:BN21 GB3:GB21 FZ3:FZ21 BP3:BP21 FX3:FX21 FV3:FV21 BR3:BR21 FT3:FT21 FR3:FR21 BT3:BT21 FP3:FP21 FN3:FN21 BV3:BV21 FL3:FL21 FJ3:FJ21 BX3:BX21 FH3:FH21 FF3:FF21 BZ3:BZ21 FD3:FD21 FB3:FB21 CB3:CB21 EZ3:EZ21 EX3:EX21 CD3:CD21 EV3:EV21 ET3:ET21 CF3:CF21 ER21 EP21 CH3:CH21 EN3:EN21 EL3:EL21 CJ3:CJ21 EJ3:EJ21 EH3:EH21 CL3:CL21 EF21 ED21 CN3:CN21 EB3:EB21 DZ3:DZ21 CP3:CP21 DX21 DV21 CR3:CR21 DT21 DR21 CT3:CT21 DP21 DN3:DN21 CV3:CV21 DL3:DL21 DJ21 CX3:CX21 DH21 DF21 CZ3:CZ21 DD21 DB21 LI11 KU11 KS11 KW11:LG11 KQ11 KO11 KM11 LF12:LF21 KK11 KI11 KG11 LD12:LD21 KE11 KC11 KA11 LB12:LB21 JY11 JW11 JU11 KZ12:KZ21 JS11 JQ11 JO11 JM11 JK11 JI11 JG11 W11 JE11 JC11 Y11 JA11 IY11 AA11 IW11 IU11 AC11 IS11 IQ11 AE11 IO11 IM11 AG11 IK11 II11 AI11 IG11 IE11 AK11 IC11 IA11 AM11 HY11 HW11 AO11 HU11 HS11 AQ11 HQ11 HO11 AS11 HM11 HK11 AU11 HI11 HG11 AW11 HE11 HC11 AY11 HA11 GY11 BA11 GW11 GU11 BC11 GS11 GQ11 BE11 GO11 GM11 BG11 GK11 GI11 BI11 GG11 GE11 BK11 GC11 GA11 BM11 FY11 FW11 BO11 FU11 FS11 BQ11 FQ11 FO11 BS11 FM11 FK11 BU11 FI11 FG11 BW11 FE11 FC11 BY11 FA11 EY11 CA11 EW11 EU11 CC11 ES11 EQ11 CE11 EO11 EM11 CG11 EK11 EI11 CI11 EG11 EE11 CK11 EC11 EA11 CM11 DY11 CO11 CQ11 DO11 CS11 DM11 CU11 CW11 CY11 DA11 KX3:KX10 KX12:KX21 KZ3:KZ10 LB3:LB10 LD3:LD10 LF3:LF10">
-    <cfRule type="containsText" dxfId="2" priority="180" operator="between" text="占">
+  <conditionalFormatting sqref="ET3:ET20">
+    <cfRule type="containsText" dxfId="2" priority="14" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",ET3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3:B21 D3:D21 KV3:KV21 LH3:LH21 KT3:KT21 KR3:KR21 F3:F21 KP3:KP21 KN3:KN21 KL3:KL21 H3:H21 KJ3:KJ21 KH3:KH21 KF3:KF21 J3:J21 KD3:KD21 KB3:KB21 JZ3:JZ21 L3:L21 JX3:JX21 JV3:JV21 JT3:JT21 N3:N21 JR3:JR21 P3:P21 JP3:JP21 R3:R21 JN3:JN21 T3:T21 JL3:JL21 V3:V21 JJ3:JJ21 X3:X21 JH3:JH21 JF3:JF21 Z3:Z21 JD3:JD21 JB3:JB21 AB3:AB21 IZ3:IZ21 IX3:IX21 AD3:AD21 IV3:IV21 IT3:IT21 AF3:AF21 IR3:IR21 IP3:IP21 AH3:AH21 IN3:IN21 IL3:IL21 AJ3:AJ21 IJ3:IJ21 IH3:IH21 AL3:AL21 IF3:IF21 ID3:ID21 AN3:AN21 IB3:IB21 HZ3:HZ21 AP3:AP21 HX3:HX21 HV3:HV21 AR3:AR21 HT3:HT21 HR3:HR21 AT3:AT21 HP3:HP21 HN3:HN21 AV3:AV21 HL3:HL21 HJ3:HJ21 AX3:AX21 HH3:HH21 HF3:HF21 AZ3:AZ21 HD3:HD21 HB3:HB21 BB3:BB21 GZ3:GZ21 GX3:GX21 BD3:BD21 GV3:GV21 GT3:GT21 BF3:BF21 GR3:GR21 GP3:GP21 BH3:BH21 GN3:GN21 GL3:GL21 BJ3:BJ21 GJ3:GJ21 GH3:GH21 BL3:BL21 GF3:GF21 GD3:GD21 BN3:BN21 GB3:GB21 FZ3:FZ21 BP3:BP21 FX3:FX21 FV3:FV21 BR3:BR21 FT3:FT21 FR3:FR21 BT3:BT21 FP3:FP21 FN3:FN21 BV3:BV21 FL3:FL21 FJ3:FJ21 BX3:BX21 FH3:FH21 FF3:FF21 BZ3:BZ21 FD3:FD21 FB3:FB21 CB3:CB21 EZ3:EZ21 EX3:EX21 CD3:CD21 EV3:EV21 ET21 CF3:CF21 ER21 EP21 CH3:CH21 EN3:EN21 EL3:EL21 CJ3:CJ21 EJ3:EJ21 EH3:EH21 CL3:CL21 EF21 ED21 CN3:CN21 EB3:EB21 DZ3:DZ21 CP3:CP21 DX21 DV21 CR3:CR21 DT21 DR21 CT3:CT21 DP21 DN3:DN21 CV3:CV21 DL3:DL21 DJ21 CX3:CX21 DH21 DF21 CZ3:CZ21 DD21 DB21 LI11 KU11 KS11 KW11:LG11 KQ11 KO11 KM11 LF12:LF21 KK11 KI11 KG11 LD12:LD21 KE11 KC11 KA11 LB12:LB21 JY11 JW11 JU11 KZ12:KZ21 JS11 JQ11 JO11 JM11 JK11 JI11 JG11 W11 JE11 JC11 Y11 JA11 IY11 AA11 IW11 IU11 AC11 IS11 IQ11 AE11 IO11 IM11 AG11 IK11 II11 AI11 IG11 IE11 AK11 IC11 IA11 AM11 HY11 HW11 AO11 HU11 HS11 AQ11 HQ11 HO11 AS11 HM11 HK11 AU11 HI11 HG11 AW11 HE11 HC11 AY11 HA11 GY11 BA11 GW11 GU11 BC11 GS11 GQ11 BE11 GO11 GM11 BG11 GK11 GI11 BI11 GG11 GE11 BK11 GC11 GA11 BM11 FY11 FW11 BO11 FU11 FS11 BQ11 FQ11 FO11 BS11 FM11 FK11 BU11 FI11 FG11 BW11 FE11 FC11 BY11 FA11 EY11 CA11 EW11 EU11 CC11 ES11 EQ11 CE11 EO11 EM11 CG11 EK11 EI11 CI11 EG11 EE11 CK11 EC11 EA11 CM11 DY11 CO11 CQ11 DO11 CS11 DM11 CU11 CW11 CY11 DA11 KX3:KX10 KX12:KX21 KZ3:KZ10 LB3:LB10 LD3:LD10 LF3:LF10">
+    <cfRule type="containsText" dxfId="2" priority="194" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",B3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3 C5 G5 E5 G3 E3 I3 I5 K3 M3 K5 M5 LI5 LG5 LE5 LC5 LA5 KY5 KW5 KU5 KS5 KQ5 O3 Q3 S3 U3 W3 Y3 AA3 AC3 AE3 AG3 AI3 AK3 AM3 AO3 AQ3 AS3 AU3 AW3 AY3 BA3 BC3 BE3 BG3 BI3 BK3 BM3 BO3 BQ3 BS3 BU3 BW3 BY3 CA3 CC3 CE3 CG3 CI3 CK3 CM3 CO3 CQ3 CS3 CU3 CW3 CY3 DA3 DM3 DO3 DY3 EA3 EC3 EE3 EG3 EI3 EK3 EM3 EO3 EQ3 ES3 EU3 EW3 EY3 FA3 FC3 FE3 FG3 FI3 FK3 FM3 FO3 FQ3 FS3 FU3 FW3 FY3 GA3 GC3 GE3 GG3 GI3 GK3 GM3 GO3 GQ3 GS3 GU3 GW3 GY3 HA3 HC3 HE3 HG3 HI3 HK3 HM3 HO3 HQ3 HS3 HU3 HW3 HY3 IA3 IC3 IE3 IG3 II3 IK3 IM3 IO3 IQ3 IS3 IU3 IW3 IY3 JA3 JC3 JE3 JG3 JI3 JK3 JM3 JO3 JQ3 JS3 JU3 JW3 JY3 KA3 KC3 KE3 KG3 KI3 KK3 KM3 KO3 KQ3 KS3 KU3 KW3 KY3 LA3 LC3 LE3 LG3 LI3 KO5 KM5 KK5 KI5 O5 Q5 S5 U5 W5 Y5 AA5 AC5 AE5 AG5 AI5 AK5 AM5 AO5 AQ5 AS5 AU5 AW5 AY5 BA5 BC5 BE5 BG5 BI5 BK5 BM5 BO5 BQ5 BS5 BU5 BW5 BY5 CA5 CC5 CE5 CG5 CI5 CK5 CM5 CO5 CQ5 CS5 CU5 CW5 CY5 DA5 DM5 DO5 DY5 EA5 EC5 EE5 EI5 EK5 EM5 EO5 EQ5 EU5 EW5 EY5 FA5 FC5 FE5 FG5 FI5 FK5 FM5 FO5 FQ5 FS5 FU5 FW5 FY5 GA5 GC5 GE5 GG5 GI5 GK5 GM5 GO5 GQ5 GS5 GU5 GW5 GY5 HA5 HC5 HE5 HG5 HI5 HK5 HM5 HO5 HQ5 HS5 HU5 HW5 HY5 IA5 IC5 IE5 IG5 II5 IK5 IM5 IO5 IQ5 IS5 IU5 IW5 IY5 JA5 JC5 JE5 JG5 JI5 JK5 JM5 JO5 JQ5 JS5 JU5 JW5 JY5 KA5 KC5 KE5 KG5 C8 G10 E10 G8 E8 G20 E20 G18 E18 G16 E16 G14 E14 G12 E12 C10 C12 C14 C16 C18 C20 I12 I14 I16 I18 I20 I8 I10 LI20 LG20 LE20 LC20 K8 M8 K10 M10 K12 M12 K14 M14 K16 M16 K18 M18 K20 M20 HW20 HU20 HS20 HQ20 HO20 HM20 HK20 HI20 HG20 HE20 HC20 HA20 GY20 GW20 GU20 GS20 GQ20 GO20 GM20 GK20 GI20 GG20 GE20 GC20 GA20 FY20 FW20 FU20 FS20 FQ20 FO20 FM20 FK20 FI20 FG20 FE20 FC20 FA20 EY20 EW20 EU20 ES20 EQ20 EO20 EM20 EK20 EI20 EG20 EE20 EC20 EA20 DY20 DO20 DM20 DA20 CY20 CW20 CU20 CS20 CQ20 CO20 CM20 CK20 CI20 CG20 CE20 CC20 CA20 BY20 BW20 BU20 BS20 BQ20 BO20 BM20 BK20 BI20 BG20 BE20 BC20 BA20 AY20 AW20 AU20 AS20 AQ20 AO20 AM20 AK20 AI20 AG20 AE20 AC20 AA20 Y20 W20 U20 S20 Q20 O20 HY20 IA20 JI20 JK20 LI18 LG18 LE18 LC18 LA18 KY18 KW18 KU18 KS18 KQ18 KO18 KM18 KK18 KI18 KG18 KE18 KC18 KA18 JY18 JW18 JU18 JS18 JQ18 JO18 JM18 JK18 JI18 JG18 JE18 JC18 JA18 IY18 IW18 IU18 IS18 IQ18 IO18 IM18 IK18 II18 IG18 IE18 IC18 IA18 HY18 HW18 HU18 HS18 HQ18 HO18 HM18 HK18 HI18 HG18 HE18 HC18 HA18 GY18 GW18 GU18 GS18 GQ18 GO18 GM18 GK18 GI18 GG18 GE18 GC18 GA18 FY18 FW18 FU18 FS18 FQ18 FO18 FM18 FK18 FI18 FG18 FE18 FC18 FA18 EY18 EW18 EU18 EO18 EK18 EI18 EE18 EC18 EA18 DO18 DM18 DA18 CY18 CW18 CU18 CS18 CQ18 CO18 CM18 CK18 CI18 CG18 CE18 CC18 CA18 BY18 BW18 BU18 BS18 BQ18 BO18 BM18 BK18 BI18 BG18 BE18 BC18 BA18 AY18 AW18 AU18 AS18 AQ18 AO18 AM18 AK18 AI18 AG18 AE18 AC18 AA18 Y18 W18 U18 S18 Q18 O18 IC20 IE20 JM20 JO20 LI16 LG16 LE16 LC16 LA16 KY16 KW16 KU16 KS16 KQ16 KO16 KM16 KK16 KI16 KG16 KE16 KC16 KA16 JY16 JW16 JU16 JS16 JQ16 JO16 JM16 JK16 JI16 JG16 JE16 JC16 JA16 IY16 IW16 IU16 IS16 IQ16 IO16 IM16 IK16 II16 IG16 IE16 IC16 IA16 HY16 HW16 HU16 HS16 HQ16 HO16 HM16 HK16 HI16 HG16 HE16 HC16 HA16 GY16 GW16 GU16 GS16 GQ16 GO16 GM16 GK16 GI16 GG16 GE16 GC16 GA16 FY16 FW16 FU16 FS16 FQ16 FO16 FM16 FK16 FI16 FG16 FE16 FC16 FA16 EY16 EW16 EU16 EO16 EK16 EI16 EE16 EC16 EA16 DY16 DO16 DM16 DA16 CY16 CW16 CU16 CS16 CQ16 CO16 CM16 CK16 CI16 CG16 CE16 CC16 CA16 BY16 BW16 BU16 BS16 BQ16 BO16 BM16 BK16 BI16 BG16 BE16 BC16 BA16 AY16 AW16 AU16 AS16 AQ16 AO16 AM16 AK16 AI16 AG16 AE16 AC16 AA16 Y16 W16 U16 S16 Q16 O16 IG20 II20 JQ20 JS20 LI14 LG14 LE14 LC14 LA14 KY14 KW14 KU14 KS14 KQ14 KO14 KM14 KK14 KI14 KG14 KE14 KC14 KA14 JY14 JW14 JU14 JS14 JQ14 JO14 JM14 JK14 JI14 JG14 JE14 JC14 JA14 IY14 IW14 IU14 IS14 IQ14 IO14 IM14 IK14 II14 IG14 IE14 IC14 IA14 HY14 HW14 HU14 HS14 HQ14 HO14 HM14 HK14 HI14 HG14 HE14 HC14 HA14 GY14 GW14 GU14 GS14 GQ14 GO14 GM14 GK14 GI14 GG14 GE14 GC14 GA14 FY14 FW14 FU14 FS14 FQ14 FO14 FM14 FK14 FI14 FG14 FE14 FC14 FA14 EY14 EW14 EU14 EO14 EK14 EI14 EC14 EA14 DO14 DM14 DA14 CY14 CW14 CU14 CS14 CQ14 CO14 CM14 CK14 CI14 CG14 CE14 CC14 CA14 BY14 BW14 BU14 BS14 BQ14 BO14 BM14 BK14 BI14 BG14 BE14 BC14 BA14 AY14 AW14 AU14 AS14 AQ14 AO14 AM14 AK14 AI14 AG14 AE14 AC14 AA14 Y14 W14 U14 S14 Q14 O14 IK20 IM20 JU20 JW20 LI12 LG12 LE12 LC12 LA12 KY12 KW12 KU12 KS12 KQ12 KO12 KM12 KK12 KI12 KG12 KE12 KC12 KA12 JY12 JW12 JU12 JS12 JQ12 JO12 JM12 JK12 JI12 JG12 JE12 JC12 JA12 IY12 IW12 IU12 IS12 IQ12 IO12 IM12 IK12 II12 IG12 IE12 IC12 IA12 HY12 HW12 HU12 HS12 HQ12 HO12 HM12 HK12 HI12 HG12 HE12 HC12 HA12 GY12 GW12 GU12 GS12 GQ12 GO12 GM12 GK12 GI12 GG12 GE12 GC12 GA12 FY12 FW12 FU12 FS12 FQ12 FO12 FM12 FK12 FI12 FG12 FE12 FC12 FA12 EY12 EW12 EU12 EO12 EM12 EK12 EI12 EC12 EA12 DY12 DO12 DM12 DA12 CY12 CW12 CU12 CS12 CQ12 CO12 CM12 CK12 CI12 CG12 CE12 CC12 CA12 BY12 BW12 BU12 BS12 BQ12 BO12 BM12 BK12 BI12 BG12 BE12 BC12 BA12 AY12 AW12 AU12 AS12 AQ12 AO12 AM12 AK12 AI12 AG12 AE12 AC12 AA12 Y12 W12 U12 S12 Q12 O12 IO20 IQ20 JY20 KA20 LI10 LG10 LE10 LC10 LA10 KY10 KW10 KU10 KS10 KQ10 KO10 KM10 KK10 KI10 KG10 KE10 KC10 KA10 JY10 JW10 JU10 JS10 JQ10 JO10 JM10 JK10 JI10 JG10 JE10 JC10 JA10 IY10 IW10 IU10 IS10 IQ10 IO10 IM10 IK10 II10 IG10 IE10 IC10 IA10 HY10 HW10 HU10 HS10 HQ10 HO10 HM10 HK10 HI10 HG10 HE10 HC10 HA10 GY10 GW10 GU10 GS10 GQ10 GO10 GM10 GK10 GI10 GG10 GE10 GC10 GA10 FY10 FW10 FU10 FS10 FQ10 FO10 FM10 FK10 FI10 FG10 FE10 FC10 FA10 EY10 EW10 EU10 EO10 EM10 EK10 EI10 EE10 EC10 EA10 DO10 DM10 DA10 CY10 CW10 CU10 CS10 CQ10 CO10 CM10 CK10 CI10 CG10 CE10 CC10 CA10 BY10 BW10 BU10 BS10 BQ10 BO10 BM10 BK10 BI10 BG10 BE10 BC10 BA10 AY10 AW10 AU10 AS10 AQ10 AO10 AM10 AK10 AI10 AG10 AE10 AC10 AA10 Y10 W10 U10 S10 Q10 O10 IS20 IU20 KC20 KE20 LI8 LG8 LE8 LC8 LA8 KY8 KW8 KU8 KS8 KQ8 KO8 KM8 KK8 KI8 KG8 KE8 KC8 KA8 JY8 JW8 JU8 JS8 JQ8 JO8 JM8 JK8 JI8 JG8 JE8 JC8 JA8 IY8 IW8 IU8 IS8 IQ8 IO8 IM8 IK8 II8 IG8 IE8 IC8 IA8 HY8 HW8 HU8 HS8 HQ8 HO8 HM8 HK8 HI8 HG8 HE8 HC8 HA8 GY8 GW8 GU8 GS8 GQ8 GO8 GM8 GK8 GI8 GG8 GE8 GC8 GA8 FY8 FW8 FU8 FS8 FQ8 FO8 FM8 FK8 FI8 FG8 FE8 FC8 FA8 EY8 EW8 EU8 EO8 EM8 EK8 EI8 EC8 EA8 DO8 DM8 DA8 CY8 CW8 CU8 CS8 CQ8 CO8 CM8 CK8 CI8 CG8 CE8 CC8 CA8 BY8 BW8 BU8 BS8 BQ8 BO8 BM8 BK8 BI8 BG8 BE8 BC8 BA8 AY8 AW8 AU8 AS8 AQ8 AO8 AM8 AK8 AI8 AG8 AE8 AC8 AA8 Y8 W8 U8 S8 Q8 O8 IW20 IY20 KG20 KI20 LA20 KY20 KW20 KU20 KS20 KQ20 KO20 JG20 JE20 KM20 KK20 JC20 JA20">
-    <cfRule type="containsBlanks" dxfId="1" priority="178">
+  <conditionalFormatting sqref="C3 C5 G5 E5 G3 E3 I3 I5 K3 M3 K5 M5 LI5 LG5 LE5 LC5 LA5 KY5 KW5 KU5 KS5 KQ5 O3 Q3 S3 U3 W3 Y3 AA3 AC3 AE3 AG3 AI3 AK3 AM3 AO3 AQ3 AS3 AU3 AW3 AY3 BA3 BC3 BE3 BG3 BI3 BK3 BM3 BO3 BQ3 BS3 BU3 BW3 BY3 CA3 CC3 CE3 CG3 CI3 CK3 CM3 CO3 CQ3 CS3 CU3 CW3 CY3 DA3 DM3 DO3 DY3 EA3 EC3 EE3 EG3 EI3 EK3 EM3 EO3 EQ3 ES3 EU3 EW3 EY3 FA3 FC3 FE3 FG3 FI3 FK3 FM3 FO3 FQ3 FS3 FU3 FW3 FY3 GA3 GC3 GE3 GG3 GI3 GK3 GM3 GO3 GQ3 GS3 GU3 GW3 GY3 HA3 HC3 HE3 HG3 HI3 HK3 HM3 HO3 HQ3 HS3 HU3 HW3 HY3 IA3 IC3 IE3 IG3 II3 IK3 IM3 IO3 IQ3 IS3 IU3 IW3 IY3 JA3 JC3 JE3 JG3 JI3 JK3 JM3 JO3 JQ3 JS3 JU3 JW3 JY3 KA3 KC3 KE3 KG3 KI3 KK3 KM3 KO3 KQ3 KS3 KU3 KW3 KY3 LA3 LC3 LE3 LG3 LI3 KO5 KM5 KK5 KI5 O5 Q5 S5 U5 W5 Y5 AA5 AC5 AE5 AG5 AI5 AK5 AM5 AO5 AQ5 AS5 AU5 AW5 AY5 BA5 BC5 BE5 BG5 BI5 BK5 BM5 BO5 BQ5 BS5 BU5 BW5 BY5 CA5 CC5 CE5 CG5 CI5 CK5 CM5 CO5 CQ5 CS5 CU5 CW5 CY5 DA5 DM5 DO5 DY5 EA5 EC5 EE5 EI5 EK5 EM5 EO5 EQ5 EW5 EY5 FA5 FC5 FE5 FG5 FI5 FK5 FM5 FO5 FQ5 FS5 FU5 FW5 FY5 GA5 GC5 GE5 GG5 GI5 GK5 GM5 GO5 GQ5 GS5 GU5 GW5 GY5 HA5 HC5 HE5 HG5 HI5 HK5 HM5 HO5 HQ5 HS5 HU5 HW5 HY5 IA5 IC5 IE5 IG5 II5 IK5 IM5 IO5 IQ5 IS5 IU5 IW5 IY5 JA5 JC5 JE5 JG5 JI5 JK5 JM5 JO5 JQ5 JS5 JU5 JW5 JY5 KA5 KC5 KE5 KG5 C8 G10 E10 G8 E8 G20 E20 G18 E18 G16 E16 G14 E14 G12 E12 C10 C12 C14 C16 C18 C20 I12 I14 I16 I18 I20 I8 I10 LI20 LG20 LE20 LC20 K8 M8 K10 M10 K12 M12 K14 M14 K16 M16 K18 M18 K20 M20 HW20 HU20 HS20 HQ20 HO20 HM20 HK20 HI20 HG20 HE20 HC20 HA20 GY20 GW20 GU20 GS20 GQ20 GO20 GM20 GK20 GI20 GG20 GE20 GC20 GA20 FY20 FW20 FU20 FS20 FQ20 FO20 FM20 FK20 FI20 FG20 FE20 FC20 FA20 EY20 EW20 EU20 ES20 EQ20 EO20 EM20 EK20 EI20 EG20 EE20 EC20 EA20 DY20 DO20 DM20 DA20 CY20 CW20 CU20 CS20 CQ20 CO20 CM20 CK20 CI20 CG20 CE20 CC20 CA20 BY20 BW20 BU20 BS20 BQ20 BO20 BM20 BK20 BI20 BG20 BE20 BC20 BA20 AY20 AW20 AU20 AS20 AQ20 AO20 AM20 AK20 AI20 AG20 AE20 AC20 AA20 Y20 W20 U20 S20 Q20 O20 HY20 IA20 JI20 JK20 LI18 LG18 LE18 LC18 LA18 KY18 KW18 KU18 KS18 KQ18 KO18 KM18 KK18 KI18 KG18 KE18 KC18 KA18 JY18 JW18 JU18 JS18 JQ18 JO18 JM18 JK18 JI18 JG18 JE18 JC18 JA18 IY18 IW18 IU18 IS18 IQ18 IO18 IM18 IK18 II18 IG18 IE18 IC18 IA18 HY18 HW18 HU18 HS18 HQ18 HO18 HM18 HK18 HI18 HG18 HE18 HC18 HA18 GY18 GW18 GU18 GS18 GQ18 GO18 GM18 GK18 GI18 GG18 GE18 GC18 GA18 FY18 FW18 FU18 FS18 FQ18 FO18 FM18 FK18 FI18 FG18 FE18 FC18 FA18 EY18 EW18 EU18 EO18 EK18 EI18 EE18 EC18 EA18 DO18 DM18 DA18 CY18 CW18 CU18 CS18 CQ18 CO18 CM18 CK18 CI18 CG18 CE18 CC18 CA18 BY18 BW18 BU18 BS18 BQ18 BO18 BM18 BK18 BI18 BG18 BE18 BC18 BA18 AY18 AW18 AU18 AS18 AQ18 AO18 AM18 AK18 AI18 AG18 AE18 AC18 AA18 Y18 W18 U18 S18 Q18 O18 IC20 IE20 JM20 JO20 LI16 LG16 LE16 LC16 LA16 KY16 KW16 KU16 KS16 KQ16 KO16 KM16 KK16 KI16 KG16 KE16 KC16 KA16 JY16 JW16 JU16 JS16 JQ16 JO16 JM16 JK16 JI16 JG16 JE16 JC16 JA16 IY16 IW16 IU16 IS16 IQ16 IO16 IM16 IK16 II16 IG16 IE16 IC16 IA16 HY16 HW16 HU16 HS16 HQ16 HO16 HM16 HK16 HI16 HG16 HE16 HC16 HA16 GY16 GW16 GU16 GS16 GQ16 GO16 GM16 GK16 GI16 GG16 GE16 GC16 GA16 FY16 FW16 FU16 FS16 FQ16 FO16 FM16 FK16 FI16 FG16 FE16 FC16 FA16 EY16 EW16 EO16 EK16 EI16 EE16 EC16 EA16 DY16 DO16 DM16 DA16 CY16 CW16 CU16 CS16 CQ16 CO16 CM16 CK16 CI16 CG16 CE16 CC16 CA16 BY16 BW16 BU16 BS16 BQ16 BO16 BM16 BK16 BI16 BG16 BE16 BC16 BA16 AY16 AW16 AU16 AS16 AQ16 AO16 AM16 AK16 AI16 AG16 AE16 AC16 AA16 Y16 W16 U16 S16 Q16 O16 IG20 II20 JQ20 JS20 LI14 LG14 LE14 LC14 LA14 KY14 KW14 KU14 KS14 KQ14 KO14 KM14 KK14 KI14 KG14 KE14 KC14 KA14 JY14 JW14 JU14 JS14 JQ14 JO14 JM14 JK14 JI14 JG14 JE14 JC14 JA14 IY14 IW14 IU14 IS14 IQ14 IO14 IM14 IK14 II14 IG14 IE14 IC14 IA14 HY14 HW14 HU14 HS14 HQ14 HO14 HM14 HK14 HI14 HG14 HE14 HC14 HA14 GY14 GW14 GU14 GS14 GQ14 GO14 GM14 GK14 GI14 GG14 GE14 GC14 GA14 FY14 FW14 FU14 FS14 FQ14 FO14 FM14 FK14 FI14 FG14 FE14 FC14 FA14 EY14 EW14 EO14 EK14 EI14 EC14 EA14 DO14 DM14 DA14 CY14 CW14 CU14 CS14 CQ14 CO14 CM14 CK14 CI14 CG14 CE14 CC14 CA14 BY14 BW14 BU14 BS14 BQ14 BO14 BM14 BK14 BI14 BG14 BE14 BC14 BA14 AY14 AW14 AU14 AS14 AQ14 AO14 AM14 AK14 AI14 AG14 AE14 AC14 AA14 Y14 W14 U14 S14 Q14 O14 IK20 IM20 JU20 JW20 LI12 LG12 LE12 LC12 LA12 KY12 KW12 KU12 KS12 KQ12 KO12 KM12 KK12 KI12 KG12 KE12 KC12 KA12 JY12 JW12 JU12 JS12 JQ12 JO12 JM12 JK12 JI12 JG12 JE12 JC12 JA12 IY12 IW12 IU12 IS12 IQ12 IO12 IM12 IK12 II12 IG12 IE12 IC12 IA12 HY12 HW12 HU12 HS12 HQ12 HO12 HM12 HK12 HI12 HG12 HE12 HC12 HA12 GY12 GW12 GU12 GS12 GQ12 GO12 GM12 GK12 GI12 GG12 GE12 GC12 GA12 FY12 FW12 FU12 FS12 FQ12 FO12 FM12 FK12 FI12 FG12 FE12 FC12 FA12 EY12 EW12 EO12 EM12 EK12 EI12 EC12 EA12 DY12 DO12 DM12 DA12 CY12 CW12 CU12 CS12 CQ12 CO12 CM12 CK12 CI12 CG12 CE12 CC12 CA12 BY12 BW12 BU12 BS12 BQ12 BO12 BM12 BK12 BI12 BG12 BE12 BC12 BA12 AY12 AW12 AU12 AS12 AQ12 AO12 AM12 AK12 AI12 AG12 AE12 AC12 AA12 Y12 W12 U12 S12 Q12 O12 IO20 IQ20 JY20 KA20 LI10 LG10 LE10 LC10 LA10 KY10 KW10 KU10 KS10 KQ10 KO10 KM10 KK10 KI10 KG10 KE10 KC10 KA10 JY10 JW10 JU10 JS10 JQ10 JO10 JM10 JK10 JI10 JG10 JE10 JC10 JA10 IY10 IW10 IU10 IS10 IQ10 IO10 IM10 IK10 II10 IG10 IE10 IC10 IA10 HY10 HW10 HU10 HS10 HQ10 HO10 HM10 HK10 HI10 HG10 HE10 HC10 HA10 GY10 GW10 GU10 GS10 GQ10 GO10 GM10 GK10 GI10 GG10 GE10 GC10 GA10 FY10 FW10 FU10 FS10 FQ10 FO10 FM10 FK10 FI10 FG10 FE10 FC10 FA10 EY10 EW10 EO10 EM10 EK10 EI10 EE10 EC10 EA10 DO10 DM10 DA10 CY10 CW10 CU10 CS10 CQ10 CO10 CM10 CK10 CI10 CG10 CE10 CC10 CA10 BY10 BW10 BU10 BS10 BQ10 BO10 BM10 BK10 BI10 BG10 BE10 BC10 BA10 AY10 AW10 AU10 AS10 AQ10 AO10 AM10 AK10 AI10 AG10 AE10 AC10 AA10 Y10 W10 U10 S10 Q10 O10 IS20 IU20 KC20 KE20 LI8 LG8 LE8 LC8 LA8 KY8 KW8 KU8 KS8 KQ8 KO8 KM8 KK8 KI8 KG8 KE8 KC8 KA8 JY8 JW8 JU8 JS8 JQ8 JO8 JM8 JK8 JI8 JG8 JE8 JC8 JA8 IY8 IW8 IU8 IS8 IQ8 IO8 IM8 IK8 II8 IG8 IE8 IC8 IA8 HY8 HW8 HU8 HS8 HQ8 HO8 HM8 HK8 HI8 HG8 HE8 HC8 HA8 GY8 GW8 GU8 GS8 GQ8 GO8 GM8 GK8 GI8 GG8 GE8 GC8 GA8 FY8 FW8 FU8 FS8 FQ8 FO8 FM8 FK8 FI8 FG8 FE8 FC8 FA8 EY8 EW8 EO8 EM8 EK8 EI8 EC8 EA8 DO8 DM8 DA8 CY8 CW8 CU8 CS8 CQ8 CO8 CM8 CK8 CI8 CG8 CE8 CC8 CA8 BY8 BW8 BU8 BS8 BQ8 BO8 BM8 BK8 BI8 BG8 BE8 BC8 BA8 AY8 AW8 AU8 AS8 AQ8 AO8 AM8 AK8 AI8 AG8 AE8 AC8 AA8 Y8 W8 U8 S8 Q8 O8 IW20 IY20 KG20 KI20 LA20 KY20 KW20 KU20 KS20 KQ20 KO20 JG20 JE20 KM20 KK20 JC20 JA20">
+    <cfRule type="containsBlanks" dxfId="1" priority="192">
       <formula>LEN(TRIM(C3))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C21 E3:E21 KW3:KW21 LI3:LI21 KU3:KU21 KS3:KS21 G3:G21 KQ3:KQ21 KO3:KO21 KM3:KM21 I3:I21 KK3:KK21 KI3:KI21 KG3:KG21 K3:K21 KE3:KE21 KC3:KC21 KA3:KA21 M3:M21 JY3:JY21 JW3:JW21 JU3:JU21 O3:O21 JS3:JS21 Q3:Q21 JQ3:JQ21 S3:S21 JO3:JO21 U3:U21 JM3:JM21 W3:W21 JK3:JK21 Y3:Y21 JI3:JI21 JG3:JG21 AA3:AA21 JE3:JE21 JC3:JC21 AC3:AC21 JA3:JA21 IY3:IY21 AE3:AE21 IW3:IW21 IU3:IU21 AG3:AG21 IS3:IS21 IQ3:IQ21 AI3:AI21 IO3:IO21 IM3:IM21 AK3:AK21 IK3:IK21 II3:II21 AM3:AM21 IG3:IG21 IE3:IE21 AO3:AO21 IC3:IC21 IA3:IA21 AQ3:AQ21 HY3:HY21 HW3:HW21 AS3:AS21 HU3:HU21 HS3:HS21 AU3:AU21 HQ3:HQ21 HO3:HO21 AW3:AW21 HM3:HM21 HK3:HK21 AY3:AY21 HI3:HI21 HG3:HG21 BA3:BA21 HE3:HE21 HC3:HC21 BC3:BC21 HA3:HA21 GY3:GY21 BE3:BE21 GW3:GW21 GU3:GU21 BG3:BG21 GS3:GS21 GQ3:GQ21 BI3:BI21 GO3:GO21 GM3:GM21 BK3:BK21 GK3:GK21 GI3:GI21 BM3:BM21 GG3:GG21 GE3:GE21 BO3:BO21 GC3:GC21 GA3:GA21 BQ3:BQ21 FY3:FY21 FW3:FW21 BS3:BS21 FU3:FU21 FS3:FS21 BU3:BU21 FQ3:FQ21 FO3:FO21 BW3:BW21 FM3:FM21 FK3:FK21 BY3:BY21 FI3:FI21 FG3:FG21 CA3:CA21 FE3:FE21 FC3:FC21 CC3:CC21 FA3:FA21 EY3:EY21 CE3:CE21 EW3:EW21 EU3:EU21 CG3:CG21 ES3:ES4 ES6:ES7 ES9 EQ11 ES11:ET11 ES13 ES15 ES17 ES19:ES21 EQ3:EQ7 EQ9 EQ13 EQ15 EQ17 EQ19:EQ21 CI3:CI21 EO3:EO21 EM3:EM13 EM15 EM17 EM19:EM21 CK3:CK21 EK3:EK21 EI3:EI21 CM3:CM21 EG3:EG4 EG6:EG7 EG9 EG11:EH11 EG13 EG15 EG17 EG19:EG21 EE3:EE7 EE9:EE11 EE13 EE15:EE21 CO3:CO21 EC3:EC21 EA3:EA21 CQ3:CQ21 DY3:DY7 DY9 DY11:DY13 DY15:DY17 DY19:DY21 DW21 CS3:CS21 DU21 DS21 CU3:CU21 DQ21 DO3:DO21 CW3:CW21 DM3:DM21 DK21 CY3:CY21 DI21 DG21 DA3:DA21 DE21 DC21 KV11 KT11 KX11:LH11 KR11 KP11 KN11 LG12:LG21 KL11 KJ11 KH11 LE12:LE21 KF11 KD11 KB11 LC12:LC21 JZ11 JX11 JV11 LA12:LA21 JT11 JR11 JP11 JN11 JL11 JJ11 JH11 X11 JF11 JD11 Z11 JB11 IZ11 AB11 IX11 IV11 AD11 IT11 IR11 AF11 IP11 IN11 AH11 IL11 IJ11 AJ11 IH11 IF11 AL11 ID11 IB11 AN11 HZ11 HX11 AP11 HV11 HT11 AR11 HR11 HP11 AT11 HN11 HL11 AV11 HJ11 HH11 AX11 HF11 HD11 AZ11 HB11 GZ11 BB11 GX11 GV11 BD11 GT11 GR11 BF11 GP11 GN11 BH11 GL11 GJ11 BJ11 GH11 GF11 BL11 GD11 GB11 BN11 FZ11 FX11 BP11 FV11 FT11 BR11 FR11 FP11 BT11 FN11 FL11 BV11 FJ11 FH11 BX11 FF11 FD11 BZ11 FB11 EZ11 CB11 EX11 EV11 CD11 CF11 EN11 CH11 EL11 EJ11 CJ11 CL11 EB11 CN11 DZ11 DN11 DL11 CV11 CX11 CZ11 KY3:KY10 KY12:KY21 LA3:LA10 LC3:LC10 LE3:LE10 LG3:LG10">
-    <cfRule type="containsText" dxfId="0" priority="179" operator="between" text="—">
+  <conditionalFormatting sqref="C3:C21 E3:E21 KW3:KW21 LI3:LI21 KU3:KU21 KS3:KS21 G3:G21 KQ3:KQ21 KO3:KO21 KM3:KM21 I3:I21 KK3:KK21 KI3:KI21 KG3:KG21 K3:K21 KE3:KE21 KC3:KC21 KA3:KA21 M3:M21 JY3:JY21 JW3:JW21 JU3:JU21 O3:O21 JS3:JS21 Q3:Q21 JQ3:JQ21 S3:S21 JO3:JO21 U3:U21 JM3:JM21 W3:W21 JK3:JK21 Y3:Y21 JI3:JI21 JG3:JG21 AA3:AA21 JE3:JE21 JC3:JC21 AC3:AC21 JA3:JA21 IY3:IY21 AE3:AE21 IW3:IW21 IU3:IU21 AG3:AG21 IS3:IS21 IQ3:IQ21 AI3:AI21 IO3:IO21 IM3:IM21 AK3:AK21 IK3:IK21 II3:II21 AM3:AM21 IG3:IG21 IE3:IE21 AO3:AO21 IC3:IC21 IA3:IA21 AQ3:AQ21 HY3:HY21 HW3:HW21 AS3:AS21 HU3:HU21 HS3:HS21 AU3:AU21 HQ3:HQ21 HO3:HO21 AW3:AW21 HM3:HM21 HK3:HK21 AY3:AY21 HI3:HI21 HG3:HG21 BA3:BA21 HE3:HE21 HC3:HC21 BC3:BC21 HA3:HA21 GY3:GY21 BE3:BE21 GW3:GW21 GU3:GU21 BG3:BG21 GS3:GS21 GQ3:GQ21 BI3:BI21 GO3:GO21 GM3:GM21 BK3:BK21 GK3:GK21 GI3:GI21 BM3:BM21 GG3:GG21 GE3:GE21 BO3:BO21 GC3:GC21 GA3:GA21 BQ3:BQ21 FY3:FY21 FW3:FW21 BS3:BS21 FU3:FU21 FS3:FS21 BU3:BU21 FQ3:FQ21 FO3:FO21 BW3:BW21 FM3:FM21 FK3:FK21 BY3:BY21 FI3:FI21 FG3:FG21 CA3:CA21 FE3:FE21 FC3:FC21 CC3:CC21 FA3:FA21 EY3:EY21 CE3:CE21 EW3:EW21 EU3:EU4 EU6:EU7 EU9 EU11:EV11 EU13 EU15 EU17:EU21 CG3:CG21 ES3:ES4 ES6:ES7 ES9 EQ11 ES11 ES13 ES15 ES17 ES19:ES21 EQ3:EQ7 EQ9 EQ13 EQ15 EQ17 EQ19:EQ21 CI3:CI21 EO3:EO21 EM3:EM13 EM15 EM17 EM19:EM21 CK3:CK21 EK3:EK21 EI3:EI21 CM3:CM21 EG3:EG4 EG6:EG7 EG9 EG11:EH11 EG13 EG15 EG17 EG19:EG21 EE3:EE7 EE9:EE11 EE13 EE15:EE21 CO3:CO21 EC3:EC21 EA3:EA21 CQ3:CQ21 DY3:DY7 DY9 DY11:DY13 DY15:DY17 DY19:DY21 DW21 CS3:CS21 DU21 DS21 CU3:CU21 DQ21 DO3:DO21 CW3:CW21 DM3:DM21 DK21 CY3:CY21 DI21 DG21 DA3:DA21 DE21 DC21 KV11 KT11 KX11:LH11 KR11 KP11 KN11 LG12:LG21 KL11 KJ11 KH11 LE12:LE21 KF11 KD11 KB11 LC12:LC21 JZ11 JX11 JV11 LA12:LA21 JT11 JR11 JP11 JN11 JL11 JJ11 JH11 X11 JF11 JD11 Z11 JB11 IZ11 AB11 IX11 IV11 AD11 IT11 IR11 AF11 IP11 IN11 AH11 IL11 IJ11 AJ11 IH11 IF11 AL11 ID11 IB11 AN11 HZ11 HX11 AP11 HV11 HT11 AR11 HR11 HP11 AT11 HN11 HL11 AV11 HJ11 HH11 AX11 HF11 HD11 AZ11 HB11 GZ11 BB11 GX11 GV11 BD11 GT11 GR11 BF11 GP11 GN11 BH11 GL11 GJ11 BJ11 GH11 GF11 BL11 GD11 GB11 BN11 FZ11 FX11 BP11 FV11 FT11 BR11 FR11 FP11 BT11 FN11 FL11 BV11 FJ11 FH11 BX11 FF11 FD11 BZ11 FB11 EZ11 CB11 EX11 CD11 CF11 EN11 CH11 EL11 EJ11 CJ11 CL11 EB11 CN11 DZ11 DN11 DL11 CV11 CX11 CZ11 KY3:KY10 KY12:KY21 LA3:LA10 LC3:LC10 LE3:LE10 LG3:LG10">
+    <cfRule type="containsText" dxfId="0" priority="193" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",C3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DB3:DB20 DD3:DD20 DF3:DF20 DH3:DH20 DJ3:DJ20 DC11 DE11 DG11 DI11 DK11">
-    <cfRule type="containsText" dxfId="2" priority="173" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="187" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",DB3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC3:DC7 DC9:DC11 DC13 DC15:DC19 DE3:DE4 DE6:DE7 DE9 DD11:DF11 DE13 DE15 DE17 DE19:DE20 DG3:DG4 DG6:DG7 DG9:DG11 DG13:DG15 DG17 DG19 DI3:DI7 DI9 DH11:DJ11 DI13 DI15 DI17 DI19 DK3:DK7 DK9 DK11:DK13 DK15 DK17 DK19">
-    <cfRule type="containsText" dxfId="0" priority="172" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="186" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DC3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC3 DE3 DG3 DI3 DK3 DC5 DI5 DK5 DE20 DC18 DC16 DG14 DK12 DG10 DC10">
-    <cfRule type="containsBlanks" dxfId="1" priority="171">
+    <cfRule type="containsBlanks" dxfId="1" priority="185">
       <formula>LEN(TRIM(DC3))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DP3:DP20 DR3:DR20 DT3:DT20 DV3:DV20 DQ11 DS11 DU11 DW11">
-    <cfRule type="containsText" dxfId="2" priority="170" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="184" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",DP3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ3 DS3 DU3 DW3 DQ5 DS5 DW5 DW20 DS20 DQ20 DW18 DU18 DS18 DQ16 DU14 DU10">
-    <cfRule type="containsBlanks" dxfId="1" priority="168">
+    <cfRule type="containsBlanks" dxfId="1" priority="182">
       <formula>LEN(TRIM(DQ3))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ3:DQ7 DQ9 DQ11:DT11 DQ13 DQ15:DQ17 DQ19:DQ20 DS3:DS7 DS9 DS13 DS15 DS17:DS20 DU3:DU4 DU6:DU7 DU9:DU11 DU13:DU15 DU17:DU19 DW3:DW7 DW9 DV11:DW11 DW13 DW15 DW17:DW20">
-    <cfRule type="containsText" dxfId="0" priority="169" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="183" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22 JO22 JM22 JK22 JI22 JG22 JE22 JC22 JA22 IY22 IW22 IU22 IS22 IQ22 IO22 IM22 IK22 II22 IG22 IE22 IC22 IA22 HY22 HW22 HU22 HS22 HQ22 HO22 HM22 HK22 HI22 HG22 HE22 HC22 HA22 GY22 GW22 GU22 GS22 GQ22 GO22 GM22 GK22 GI22 GG22 GE22 GC22 GA22 FY22 FW22 FU22 FS22 FQ22 FO22 FM22 FK22 FI22 FG22 FE22 FC22 FA22 EY22 EW22 EU22 ES22 EQ22 EO22 EM22 EK22 EI22 EG22 EE22 EC22 EA22 DY22 DW22 DU22 DS22 DQ22 DO22 DM22 DK22 DI22 DG22 DE22 DC22 DA22 CY22 CW22 CU22 CS22 CQ22 CO22 CM22 CK22 CI22 CG22 CE22 CC22 CA22 BY22 BW22 BU22 BS22 BQ22 BO22 BM22 BK22 BI22 BG22 BE22 BC22 BA22 AY22 AW22 AU22 AS22 AQ22 AO22 AM22 AK22 AI22 AG22 AE22 AC22 AA22 Y22 W22 U22 S22 Q22 O22 M22 K22 I22 G22 E22">
-    <cfRule type="containsBlanks" dxfId="3" priority="176">
+    <cfRule type="containsBlanks" dxfId="3" priority="190">
       <formula>LEN(TRIM(C22))=0</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="177" operator="between" text="—">
+    <cfRule type="containsText" dxfId="2" priority="191" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",C22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="ES5 EQ8 ES8 EQ9 ES9 EQ10 ES10 EQ11 ES11 EQ12 ES12 EQ13 ES13 EM14 EQ14 ES14 EM15 EQ15 ES15 EM16 EQ16 ES16 EM17 EQ17 ES17 EM18 EQ18 ES18 C3:C21 E3:E21 G3:G21 I3:I21 K3:K21 M3:M21 O3:O21 Q3:Q21 S3:S21 U3:U21 W3:W21 Y3:Y21 AA3:AA21 AC3:AC21 AE3:AE21 AG3:AG21 AI3:AI21 AK3:AK21 AM3:AM21 AO3:AO21 AQ3:AQ21 AS3:AS21 AU3:AU21 AW3:AW21 AY3:AY21 BA3:BA21 BC3:BC21 BE3:BE21 BG3:BG21 BI3:BI21 BK3:BK21 BM3:BM21 BO3:BO21 BQ3:BQ21 BS3:BS21 BU3:BU21 BW3:BW21 BY3:BY21 CA3:CA21 CC3:CC21 CE3:CE21 CG3:CG21 CI3:CI21 CK3:CK21 CM3:CM21 CO3:CO21 CQ3:CQ21 CS3:CS21 CU3:CU21 CW3:CW21 CY3:CY21 DA3:DA21 DC3:DC21 DE3:DE21 DG3:DG21 DI3:DI21 DK3:DK21 DM3:DM21 DO3:DO21 DQ3:DQ21 DS3:DS21 DU3:DU21 DW3:DW21 DY3:DY21 EA3:EA21 EC3:EC21 EE3:EE21 EG3:EG21 EI3:EI21 EK3:EK21 EM3:EM13 EM19:EM21 EO3:EO21 EQ3:EQ7 EQ19:EQ21 ES3:ES4 ES6:ES7 ES19:ES21 EU3:EU21 EW3:EW21 EY3:EY21 FA3:FA21 FC3:FC21 FE3:FE21 FG3:FG21 FI3:FI21 FK3:FK21 FM3:FM21 FO3:FO21 FQ3:FQ21 FS3:FS21 FU3:FU21 FW3:FW21 FY3:FY21 GA3:GA21 GC3:GC21 GE3:GE21 GG3:GG21 GI3:GI21 GK3:GK21 GM3:GM21 GO3:GO21 GQ3:GQ21 GS3:GS21 GU3:GU21 GW3:GW21 GY3:GY21 HA3:HA21 HC3:HC21 HE3:HE21 HG3:HG21 HI3:HI21 HK3:HK21 HM3:HM21 HO3:HO21 HQ3:HQ21 HS3:HS21 HU3:HU21 HW3:HW21 HY3:HY21 IA3:IA21 IC3:IC21 IE3:IE21 IG3:IG21 II3:II21 IK3:IK21 IM3:IM21 IO3:IO21 IQ3:IQ21 IS3:IS21 IU3:IU21 IW3:IW21 IY3:IY21 JA3:JA21 JC3:JC21 JE3:JE21 JG3:JG21 JI3:JI21 JK3:JK21 JM3:JM21 JO3:JO21">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EU5 EU8 EU9 EU10 EU11 EU12 EU13 EU14 EU15 EU16 C3:C21 E3:E21 G3:G21 I3:I21 K3:K21 M3:M21 O3:O21 Q3:Q21 S3:S21 U3:U21 W3:W21 Y3:Y21 AA3:AA21 AC3:AC21 AE3:AE21 AG3:AG21 AI3:AI21 AK3:AK21 AM3:AM21 AO3:AO21 AQ3:AQ21 AS3:AS21 AU3:AU21 AW3:AW21 AY3:AY21 BA3:BA21 BC3:BC21 BE3:BE21 BG3:BG21 BI3:BI21 BK3:BK21 BM3:BM21 BO3:BO21 BQ3:BQ21 BS3:BS21 BU3:BU21 BW3:BW21 BY3:BY21 CA3:CA21 CC3:CC21 CE3:CE21 CG3:CG21 CI3:CI21 CK3:CK21 CM3:CM21 CO3:CO21 CQ3:CQ21 CS3:CS21 CU3:CU21 CW3:CW21 CY3:CY21 DA3:DA21 DC3:DC21 DE3:DE21 DG3:DG21 DI3:DI21 DK3:DK21 DM3:DM21 DO3:DO21 DQ3:DQ21 DS3:DS21 DU3:DU21 DW3:DW21 DY3:DY21 EA3:EA21 EC3:EC21 EE3:EE21 EG3:EG21 EI3:EI21 EK3:EK21 EM3:EM21 EO3:EO21 EQ3:EQ21 ES3:ES21 EU3:EU4 EU6:EU7 EU17:EU21 EW3:EW21 EY3:EY21 FA3:FA21 FC3:FC21 FE3:FE21 FG3:FG21 FI3:FI21 FK3:FK21 FM3:FM21 FO3:FO21 FQ3:FQ21 FS3:FS21 FU3:FU21 FW3:FW21 FY3:FY21 GA3:GA21 GC3:GC21 GE3:GE21 GG3:GG21 GI3:GI21 GK3:GK21 GM3:GM21 GO3:GO21 GQ3:GQ21 GS3:GS21 GU3:GU21 GW3:GW21 GY3:GY21 HA3:HA21 HC3:HC21 HE3:HE21 HG3:HG21 HI3:HI21 HK3:HK21 HM3:HM21 HO3:HO21 HQ3:HQ21 HS3:HS21 HU3:HU21 HW3:HW21 HY3:HY21 IA3:IA21 IC3:IC21 IE3:IE21 IG3:IG21 II3:II21 IK3:IK21 IM3:IM21 IO3:IO21 IQ3:IQ21 IS3:IS21 IU3:IU21 IW3:IW21 IY3:IY21 JA3:JA21 JC3:JC21 JE3:JE21 JG3:JG21 JI3:JI21 JK3:JK21 JM3:JM21 JO3:JO21">
       <formula1>数据!$B$1:$B$62</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EP21 ER21 B3:B21 D3:D21 F3:F21 H3:H21 J3:J21 L3:L21 N3:N21 P3:P21 R3:R21 T3:T21 V3:V21 X3:X21 Z3:Z21 AB3:AB21 AD3:AD21 AF3:AF21 AH3:AH21 AJ3:AJ21 AL3:AL21 AN3:AN21 AP3:AP21 AR3:AR21 AT3:AT21 AV3:AV21 AX3:AX21 AZ3:AZ21 BB3:BB21 BD3:BD21 BF3:BF21 BH3:BH21 BJ3:BJ21 BL3:BL21 BN3:BN21 BP3:BP21 BR3:BR21 BT3:BT21 BV3:BV21 BX3:BX21 BZ3:BZ21 CB3:CB21 CD3:CD21 CF3:CF21 CH3:CH21 CJ3:CJ21 CL3:CL21 CN3:CN21 CP3:CP21 CR3:CR21 CT3:CT21 CV3:CV21 CX3:CX21 CZ3:CZ21 DB3:DB21 DD3:DD21 DF3:DF21 DH3:DH21 DJ3:DJ21 DL3:DL21 DN3:DN21 DP3:DP21 DR3:DR21 DT3:DT21 DV3:DV21 DX3:DX21 DZ3:DZ21 EB3:EB21 ED3:ED21 EF3:EF21 EH3:EH21 EJ3:EJ21 EL3:EL21 EN3:EN21 EP3:EP20 ER3:ER20 ET3:ET21 EV3:EV21 EX3:EX21 EZ3:EZ21 FB3:FB21 FD3:FD21 FF3:FF21 FH3:FH21 FJ3:FJ21 FL3:FL21 FN3:FN21 FP3:FP21 FR3:FR21 FT3:FT21 FV3:FV21 FX3:FX21 FZ3:FZ21 GB3:GB21 GD3:GD21 GF3:GF21 GH3:GH21 GJ3:GJ21 GL3:GL21 GN3:GN21 GP3:GP21 GR3:GR21 GT3:GT21 GV3:GV21 GX3:GX21 GZ3:GZ21 HB3:HB21 HD3:HD21 HF3:HF21 HH3:HH21 HJ3:HJ21 HL3:HL21 HN3:HN21 HP3:HP21 HR3:HR21 HT3:HT21 HV3:HV21 HX3:HX21 HZ3:HZ21 IB3:IB21 ID3:ID21 IF3:IF21 IH3:IH21 IJ3:IJ21 IL3:IL21 IN3:IN21 IP3:IP21 IR3:IR21 IT3:IT21 IV3:IV21 IX3:IX21 IZ3:IZ21 JB3:JB21 JD3:JD21 JF3:JF21 JH3:JH21 JJ3:JJ21 JL3:JL21 JN3:JN21">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="ET21 B3:B21 D3:D21 F3:F21 H3:H21 J3:J21 L3:L21 N3:N21 P3:P21 R3:R21 T3:T21 V3:V21 X3:X21 Z3:Z21 AB3:AB21 AD3:AD21 AF3:AF21 AH3:AH21 AJ3:AJ21 AL3:AL21 AN3:AN21 AP3:AP21 AR3:AR21 AT3:AT21 AV3:AV21 AX3:AX21 AZ3:AZ21 BB3:BB21 BD3:BD21 BF3:BF21 BH3:BH21 BJ3:BJ21 BL3:BL21 BN3:BN21 BP3:BP21 BR3:BR21 BT3:BT21 BV3:BV21 BX3:BX21 BZ3:BZ21 CB3:CB21 CD3:CD21 CF3:CF21 CH3:CH21 CJ3:CJ21 CL3:CL21 CN3:CN21 CP3:CP21 CR3:CR21 CT3:CT21 CV3:CV21 CX3:CX21 CZ3:CZ21 DB3:DB21 DD3:DD21 DF3:DF21 DH3:DH21 DJ3:DJ21 DL3:DL21 DN3:DN21 DP3:DP21 DR3:DR21 DT3:DT21 DV3:DV21 DX3:DX21 DZ3:DZ21 EB3:EB21 ED3:ED21 EF3:EF21 EH3:EH21 EJ3:EJ21 EL3:EL21 EN3:EN21 EP3:EP21 ER3:ER21 ET3:ET20 EV3:EV21 EX3:EX21 EZ3:EZ21 FB3:FB21 FD3:FD21 FF3:FF21 FH3:FH21 FJ3:FJ21 FL3:FL21 FN3:FN21 FP3:FP21 FR3:FR21 FT3:FT21 FV3:FV21 FX3:FX21 FZ3:FZ21 GB3:GB21 GD3:GD21 GF3:GF21 GH3:GH21 GJ3:GJ21 GL3:GL21 GN3:GN21 GP3:GP21 GR3:GR21 GT3:GT21 GV3:GV21 GX3:GX21 GZ3:GZ21 HB3:HB21 HD3:HD21 HF3:HF21 HH3:HH21 HJ3:HJ21 HL3:HL21 HN3:HN21 HP3:HP21 HR3:HR21 HT3:HT21 HV3:HV21 HX3:HX21 HZ3:HZ21 IB3:IB21 ID3:ID21 IF3:IF21 IH3:IH21 IJ3:IJ21 IL3:IL21 IN3:IN21 IP3:IP21 IR3:IR21 IT3:IT21 IV3:IV21 IX3:IX21 IZ3:IZ21 JB3:JB21 JD3:JD21 JF3:JF21 JH3:JH21 JJ3:JJ21 JL3:JL21 JN3:JN21">
       <formula1>数据!$A$1:$A$88</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C22 E22 G22 I22 K22 M22 O22 Q22 S22 U22 W22 Y22 AA22 AC22 AE22 AG22 AI22 AK22 AM22 AO22 AQ22 AS22 AU22 AW22 AY22 BA22 BC22 BE22 BG22 BI22 BK22 BM22 BO22 BQ22 BS22 BU22 BW22 BY22 CA22 CC22 CE22 CG22 CI22 CK22 CM22 CO22 CQ22 CS22 CU22 CW22 CY22 DA22 DC22 DE22 DG22 DI22 DK22 DM22 DO22 DQ22 DS22 DU22 DW22 DY22 EA22 EC22 EE22 EG22 EI22 EK22 EM22 EO22 EQ22 ES22 EU22 EW22 EY22 FA22 FC22 FE22 FG22 FI22 FK22 FM22 FO22 FQ22 FS22 FU22 FW22 FY22 GA22 GC22 GE22 GG22 GI22 GK22 GM22 GO22 GQ22 GS22 GU22 GW22 GY22 HA22 HC22 HE22 HG22 HI22 HK22 HM22 HO22 HQ22 HS22 HU22 HW22 HY22 IA22 IC22 IE22 IG22 II22 IK22 IM22 IO22 IQ22 IS22 IU22 IW22 IY22 JA22 JC22 JE22 JG22 JI22 JK22 JM22 JO22">

--- a/c/9班资料.xlsx
+++ b/c/9班资料.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480" activeTab="3"/>
+    <workbookView windowWidth="20750" windowHeight="10480" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="七下拖课" sheetId="1" r:id="rId1"/>
@@ -1548,6 +1548,7 @@
         <charset val="134"/>
       </rPr>
       <t>陈睿卓被称“林俊卓”，唱歌时会摇头摆手，表情狰狞，动作经典。
+陈睿卓说自己家里有两辆车。
 陈睿卓爱“装”，如对答案时：“完蛋我选了C！（正确答案是C）”</t>
     </r>
   </si>
@@ -1752,6 +1753,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
       <t>七上时，唐家祺说：“梦妍比较狡猾。”是有根据的。重测时，她可能会用“雕版印刷术”，即准备两张英语作业纸，在上面那一张上写出小测答案，重测时即可通过产生的压痕来投机取巧。抄词时，会用黑笔抄一些、红笔抄一些，装作是订正。
 同时，她喜欢和一些女生抢别人东西（笔盒/袋子/书包）。
 据她所述，六年级时她都不写数学丛书，每天都在早读课上抄。
@@ -4066,15 +4072,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF4F81BD"/>
-      <name val="黑体"/>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -4090,12 +4089,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
+      <sz val="12"/>
+      <color rgb="FF4F81BD"/>
+      <name val="黑体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
-  <fills count="62">
+  <fills count="61">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4219,12 +4225,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.05"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4785,7 +4785,7 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4809,16 +4809,16 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="33" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="32" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="26" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="25" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="26" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="34" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="33" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -4827,85 +4827,85 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0">
@@ -5256,13 +5256,13 @@
     <xf numFmtId="0" fontId="12" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5298,10 +5298,10 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -5349,19 +5349,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5370,31 +5370,31 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="4" fillId="25" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="58" fontId="4" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5403,16 +5403,16 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5421,10 +5421,10 @@
     <xf numFmtId="0" fontId="26" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5436,10 +5436,10 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -16449,14 +16449,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FL21 FN21 B3:B21 D3:D21 F3:F21 H3:H21 J3:J21 L3:L21 N3:N21 P3:P21 R3:R21 T3:T21 V3:V21 X3:X21 Z3:Z21 AB3:AB21 AD3:AD21 AF3:AF21 AH3:AH21 AJ3:AJ21 AL3:AL21 AN3:AN21 AP3:AP21 AR3:AR21 AT3:AT21 AV3:AV21 AX3:AX21 AZ3:AZ21 BB3:BB21 BD3:BD21 BF3:BF21 BH3:BH21 BJ3:BJ21 BL3:BL21 BN3:BN21 BP3:BP21 BR3:BR21 BT3:BT21 BV3:BV21 BX3:BX21 BZ3:BZ21 CB3:CB21 CD3:CD21 CF3:CF21 CH3:CH21 CJ3:CJ21 CL3:CL21 CN3:CN21 CP3:CP21 CR3:CR21 CT3:CT21 CV3:CV21 CX3:CX21 CZ3:CZ21 DB3:DB21 DD3:DD21 DF3:DF21 DH3:DH21 DJ3:DJ21 DL3:DL21 DN3:DN21 DP3:DP21 DR3:DR21 DT3:DT21 DV3:DV21 DX3:DX21 DZ3:DZ21 EB3:EB21 ED3:ED21 EF3:EF21 EH3:EH21 EJ3:EJ21 EL3:EL21 EN3:EN21 EP3:EP21 ER3:ER21 ET3:ET21 EV3:EV21 EX3:EX21 EZ3:EZ21 FB3:FB21 FD3:FD21 FF3:FF21 FH3:FH21 FJ3:FJ21 FL3:FL20 FN3:FN20 FP3:FP21 FR3:FR21 FT3:FT21 FV3:FV21 FX3:FX21 FZ3:FZ21 GB3:GB21 GD3:GD21 GF3:GF21 GH3:GH21 GJ3:GJ21 GL3:GL21 GN3:GN21 GP3:GP21 GR3:GR21 GT3:GT21 GV3:GV21 GX3:GX21 GZ3:GZ21 HB3:HB21 HD3:HD21 HF3:HF21 HH3:HH21 HJ3:HJ21 HL3:HL21 HN3:HN21 HP3:HP21 HR3:HR21 HT3:HT21 HV3:HV21 HX3:HX21 HZ3:HZ21 IB3:IB21 ID3:ID21 IF3:IF21 IH3:IH21 IJ3:IJ21 IL3:IL21 IN3:IN21 IP3:IP21 IR3:IR21 IT3:IT21 IV3:IV21 IX3:IX21 IZ3:IZ21 JB3:JB21 JD3:JD21 JF3:JF21 JH3:JH21 JJ3:JJ21 JL3:JL21 JN3:JN21">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C22 E22 G22 I22 K22 M22 O22 Q22 S22 U22 W22 Y22 AA22 AC22 AE22 AG22 AI22 AK22 AM22 AO22 AQ22 AS22 AU22 AW22 AY22 BA22 BC22 BE22 BG22 BI22 BK22 BM22 BO22 BQ22 BS22 BU22 BW22 BY22 CA22 CC22 CE22 CG22 CI22 CK22 CM22 CO22 CQ22 CS22 CU22 CW22 CY22 DA22 DC22 DE22 DG22 DI22 DK22 DM22 DO22 DQ22 DS22 DU22 DW22 DY22 EA22 EC22 EE22 EG22 EI22 EK22 EM22 EO22 EQ22 ES22 EU22 EW22 EY22 FA22 FC22 FE22 FG22 FI22 FK22 FM22 FO22 FQ22 FS22 FU22 FW22 FY22 GA22 GC22 GE22 GG22 GI22 GK22 GM22 GO22 GQ22 GS22 GU22 GW22 GY22 HA22 HC22 HE22 HG22 HI22 HK22 HM22 HO22 HQ22 HS22 HU22 HW22 HY22 IA22 IC22 IE22 IG22 II22 IK22 IM22 IO22 IQ22 IS22 IU22 IW22 IY22 JA22 JC22 JE22 JG22 JI22 JK22 JM22 JO22">
+      <formula1>数据!$C$1:$C$25</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B21 D3:D21 F3:F21 H3:H21 J3:J21 L3:L21 N3:N21 P3:P21 R3:R21 T3:T21 V3:V21 X3:X21 Z3:Z21 AB3:AB21 AD3:AD21 AF3:AF21 AH3:AH21 AJ3:AJ21 AL3:AL21 AN3:AN21 AP3:AP21 AR3:AR21 AT3:AT21 AV3:AV21 AX3:AX21 AZ3:AZ21 BB3:BB21 BD3:BD21 BF3:BF21 BH3:BH21 BJ3:BJ21 BL3:BL21 BN3:BN21 BP3:BP21 BR3:BR21 BT3:BT21 BV3:BV21 BX3:BX21 BZ3:BZ21 CB3:CB21 CD3:CD21 CF3:CF21 CH3:CH21 CJ3:CJ21 CL3:CL21 CN3:CN21 CP3:CP21 CR3:CR21 CT3:CT21 CV3:CV21 CX3:CX21 CZ3:CZ21 DB3:DB21 DD3:DD21 DF3:DF21 DH3:DH21 DJ3:DJ21 DL3:DL21 DN3:DN21 DP3:DP21 DR3:DR21 DT3:DT21 DV3:DV21 DX3:DX21 DZ3:DZ21 EB3:EB21 ED3:ED21 EF3:EF21 EH3:EH21 EJ3:EJ21 EL3:EL21 EN3:EN21 EP3:EP21 ER3:ER21 ET3:ET21 EV3:EV21 EX3:EX21 EZ3:EZ21 FB3:FB21 FD3:FD21 FF3:FF21 FH3:FH21 FJ3:FJ21 FL3:FL21 FN3:FN21 FP3:FP21 FR3:FR21 FT3:FT21 FV3:FV21 FX3:FX21 FZ3:FZ21 GB3:GB21 GD3:GD21 GF3:GF21 GH3:GH21 GJ3:GJ21 GL3:GL21 GN3:GN21 GP3:GP21 GR3:GR21 GT3:GT21 GV3:GV21 GX3:GX21 GZ3:GZ21 HB3:HB21 HD3:HD21 HF3:HF21 HH3:HH21 HJ3:HJ21 HL3:HL21 HN3:HN21 HP3:HP21 HR3:HR21 HT3:HT21 HV3:HV21 HX3:HX21 HZ3:HZ21 IB3:IB21 ID3:ID21 IF3:IF21 IH3:IH21 IJ3:IJ21 IL3:IL21 IN3:IN21 IP3:IP21 IR3:IR21 IT3:IT21 IV3:IV21 IX3:IX21 IZ3:IZ21 JB3:JB21 JD3:JD21 JF3:JF21 JH3:JH21 JJ3:JJ21 JL3:JL21 JN3:JN21">
       <formula1>数据!$A$1:$A$88</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FM21 FO21 C3:C21 E3:E21 G3:G21 I3:I21 K3:K21 M3:M21 O3:O21 Q3:Q21 S3:S21 U3:U21 W3:W21 Y3:Y21 AA3:AA21 AC3:AC21 AE3:AE21 AG3:AG21 AI3:AI21 AK3:AK21 AM3:AM21 AO3:AO21 AQ3:AQ21 AS3:AS21 AU3:AU21 AW3:AW21 AY3:AY21 BA3:BA21 BC3:BC21 BE3:BE21 BG3:BG21 BI3:BI21 BK3:BK21 BM3:BM21 BO3:BO21 BQ3:BQ21 BS3:BS21 BU3:BU21 BW3:BW21 BY3:BY21 CA3:CA21 CC3:CC21 CE3:CE21 CG3:CG21 CI3:CI21 CK3:CK21 CM3:CM21 CO3:CO21 CQ3:CQ21 CS3:CS21 CU3:CU21 CW3:CW21 CY3:CY21 DA3:DA21 DC3:DC21 DE3:DE21 DG3:DG21 DI3:DI21 DK3:DK21 DM3:DM21 DO3:DO21 DQ3:DQ21 DS3:DS21 DU3:DU21 DW3:DW21 DY3:DY21 EA3:EA21 EC3:EC21 EE3:EE21 EG3:EG21 EI3:EI21 EK3:EK21 EM3:EM21 EO3:EO21 EQ3:EQ21 ES3:ES21 EU3:EU21 EW3:EW21 EY3:EY21 FA3:FA21 FC3:FC21 FE3:FE21 FG3:FG21 FI3:FI21 FK3:FK21 FM3:FM20 FO3:FO20 FQ3:FQ21 FS3:FS21 FU3:FU21 FW3:FW21 FY3:FY21 GA3:GA21 GC3:GC21 GE3:GE21 GG3:GG21 GI3:GI21 GK3:GK21 GM3:GM21 GO3:GO21 GQ3:GQ21 GS3:GS21 GU3:GU21 GW3:GW21 GY3:GY21 HA3:HA21 HC3:HC21 HE3:HE21 HG3:HG21 HI3:HI21 HK3:HK21 HM3:HM21 HO3:HO21 HQ3:HQ21 HS3:HS21 HU3:HU21 HW3:HW21 HY3:HY21 IA3:IA21 IC3:IC21 IE3:IE21 IG3:IG21 II3:II21 IK3:IK21 IM3:IM21 IO3:IO21 IQ3:IQ21 IS3:IS21 IU3:IU21 IW3:IW21 IY3:IY21 JA3:JA21 JC3:JC21 JE3:JE21 JG3:JG21 JI3:JI21 JK3:JK21 JM3:JM21 JO3:JO21">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C21 E3:E21 G3:G21 I3:I21 K3:K21 M3:M21 O3:O21 Q3:Q21 S3:S21 U3:U21 W3:W21 Y3:Y21 AA3:AA21 AC3:AC21 AE3:AE21 AG3:AG21 AI3:AI21 AK3:AK21 AM3:AM21 AO3:AO21 AQ3:AQ21 AS3:AS21 AU3:AU21 AW3:AW21 AY3:AY21 BA3:BA21 BC3:BC21 BE3:BE21 BG3:BG21 BI3:BI21 BK3:BK21 BM3:BM21 BO3:BO21 BQ3:BQ21 BS3:BS21 BU3:BU21 BW3:BW21 BY3:BY21 CA3:CA21 CC3:CC21 CE3:CE21 CG3:CG21 CI3:CI21 CK3:CK21 CM3:CM21 CO3:CO21 CQ3:CQ21 CS3:CS21 CU3:CU21 CW3:CW21 CY3:CY21 DA3:DA21 DC3:DC21 DE3:DE21 DG3:DG21 DI3:DI21 DK3:DK21 DM3:DM21 DO3:DO21 DQ3:DQ21 DS3:DS21 DU3:DU21 DW3:DW21 DY3:DY21 EA3:EA21 EC3:EC21 EE3:EE21 EG3:EG21 EI3:EI21 EK3:EK21 EM3:EM21 EO3:EO21 EQ3:EQ21 ES3:ES21 EU3:EU21 EW3:EW21 EY3:EY21 FA3:FA21 FC3:FC21 FE3:FE21 FG3:FG21 FI3:FI21 FK3:FK21 FM3:FM21 FO3:FO21 FQ3:FQ21 FS3:FS21 FU3:FU21 FW3:FW21 FY3:FY21 GA3:GA21 GC3:GC21 GE3:GE21 GG3:GG21 GI3:GI21 GK3:GK21 GM3:GM21 GO3:GO21 GQ3:GQ21 GS3:GS21 GU3:GU21 GW3:GW21 GY3:GY21 HA3:HA21 HC3:HC21 HE3:HE21 HG3:HG21 HI3:HI21 HK3:HK21 HM3:HM21 HO3:HO21 HQ3:HQ21 HS3:HS21 HU3:HU21 HW3:HW21 HY3:HY21 IA3:IA21 IC3:IC21 IE3:IE21 IG3:IG21 II3:II21 IK3:IK21 IM3:IM21 IO3:IO21 IQ3:IQ21 IS3:IS21 IU3:IU21 IW3:IW21 IY3:IY21 JA3:JA21 JC3:JC21 JE3:JE21 JG3:JG21 JI3:JI21 JK3:JK21 JM3:JM21 JO3:JO21">
       <formula1>数据!$B$1:$B$62</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C22 E22 G22 I22 K22 M22 O22 Q22 S22 U22 W22 Y22 AA22 AC22 AE22 AG22 AI22 AK22 AM22 AO22 AQ22 AS22 AU22 AW22 AY22 BA22 BC22 BE22 BG22 BI22 BK22 BM22 BO22 BQ22 BS22 BU22 BW22 BY22 CA22 CC22 CE22 CG22 CI22 CK22 CM22 CO22 CQ22 CS22 CU22 CW22 CY22 DA22 DC22 DE22 DG22 DI22 DK22 DM22 DO22 DQ22 DS22 DU22 DW22 DY22 EA22 EC22 EE22 EG22 EI22 EK22 EM22 EO22 EQ22 ES22 EU22 EW22 EY22 FA22 FC22 FE22 FG22 FI22 FK22 FM22 FO22 FQ22 FS22 FU22 FW22 FY22 GA22 GC22 GE22 GG22 GI22 GK22 GM22 GO22 GQ22 GS22 GU22 GW22 GY22 HA22 HC22 HE22 HG22 HI22 HK22 HM22 HO22 HQ22 HS22 HU22 HW22 HY22 IA22 IC22 IE22 IG22 II22 IK22 IM22 IO22 IQ22 IS22 IU22 IW22 IY22 JA22 JC22 JE22 JG22 JI22 JK22 JM22 JO22">
-      <formula1>数据!$C$1:$C$25</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20229,7 +20229,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="37" ht="42" spans="1:3">
+    <row r="37" ht="56" spans="1:3">
       <c r="A37" s="59" t="s">
         <v>175</v>
       </c>

--- a/c/9班资料.xlsx
+++ b/c/9班资料.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1681" uniqueCount="485">
   <si>
     <t>拖课统计表</t>
   </si>
@@ -570,29 +570,24 @@
     <t>陈睿卓</t>
   </si>
   <si>
+    <r>
+      <t>装备哥、睿zhuo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>̄</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="黑体"/>
         <charset val="134"/>
       </rPr>
-      <t>装备哥、睿zhuo</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>̄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、睿猪</t>
+      <t>、睿猪、陶喆、文班亚马</t>
     </r>
   </si>
   <si>
@@ -971,7 +966,8 @@
     <t>其他</t>
   </si>
   <si>
-    <t>数学老师如果觉得纪律不好，就会直接说：“今天纪律差！”</t>
+    <t>数学老师如果觉得纪律不好，就会直接说：“今天纪律差！”
+数学老师仅允许数学120分以上的人在课上写数学作业。</t>
   </si>
   <si>
     <t>方翔曾发明“防伪标志”，但目前仅用过1次。
@@ -1011,6 +1007,9 @@
   </si>
   <si>
     <t>×××</t>
+  </si>
+  <si>
+    <t>请大家在课文当中画一下。</t>
   </si>
   <si>
     <t>张××</t>
@@ -1530,7 +1529,7 @@
   </si>
   <si>
     <r>
-      <t>有人说，陈睿卓每天吃得都很补，整天中午吃海参。</t>
+      <t>有人说，陈睿卓每天吃得都很补，整天中午吃海参、小米粥。</t>
     </r>
     <r>
       <rPr>
@@ -1547,9 +1546,12 @@
         <rFont val="等线"/>
         <charset val="134"/>
       </rPr>
-      <t>陈睿卓被称“林俊卓”，唱歌时会摇头摆手，表情狰狞，动作经典。
+      <t>陈睿卓被称“林俊卓”、“陶喆”，唱歌时会摇头、皱眉、抖手、抬头、后仰、双腿开叉。
 陈睿卓说自己家里有两辆车。
-陈睿卓爱“装”，如对答案时：“完蛋我选了C！（正确答案是C）”</t>
+陈睿卓爱“装”，如对答案时：“完蛋我选了C！（正确答案是C）”
+陈睿卓经典歌曲：感谢你曾来过、再给我两分钟。
+陈睿卓戴眼镜时：“我戴眼镜帅还是不戴帅？”
+陈睿卓在自己建的群里发：“好的宝宝，明天下午。”然后说发错了。“</t>
     </r>
   </si>
   <si>
@@ -1584,20 +1586,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">早读
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
       <t>一段时间内，洪鑫洋很喜欢读《孙权劝学》和《木兰诗》，于是大家读的时候就开始把人物替换成“鑫洋”，如：</t>
     </r>
     <r>
@@ -1621,6 +1609,15 @@
 小弟闻姊来，磨刀霍霍向鑫洋。
 同行十二年，不知鑫洋是女郎。
 双兔傍地走，安能辨我是鑫洋。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+洪鑫洋曾说：“反正生物期中考只有30分。”</t>
     </r>
   </si>
   <si>
@@ -4072,14 +4069,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
+      <sz val="12"/>
+      <color rgb="FF4F81BD"/>
+      <name val="黑体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FFC0504D"/>
-      <name val="黑体"/>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -4090,7 +4087,7 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF4F81BD"/>
+      <color rgb="FFC0504D"/>
       <name val="黑体"/>
       <charset val="134"/>
     </font>
@@ -7368,10 +7365,18 @@
       <c r="FQ3" s="159"/>
       <c r="FR3" s="158"/>
       <c r="FS3" s="159"/>
-      <c r="FT3" s="158"/>
-      <c r="FU3" s="159"/>
-      <c r="FV3" s="158"/>
-      <c r="FW3" s="159"/>
+      <c r="FT3" s="158" t="s">
+        <v>4</v>
+      </c>
+      <c r="FU3" s="159" t="s">
+        <v>3</v>
+      </c>
+      <c r="FV3" s="158" t="s">
+        <v>4</v>
+      </c>
+      <c r="FW3" s="159">
+        <v>2.25</v>
+      </c>
       <c r="FX3" s="158"/>
       <c r="FY3" s="159"/>
       <c r="FZ3" s="158"/>
@@ -8144,10 +8149,18 @@
       <c r="FQ5" s="165"/>
       <c r="FR5" s="164"/>
       <c r="FS5" s="165"/>
-      <c r="FT5" s="164"/>
-      <c r="FU5" s="165"/>
-      <c r="FV5" s="164"/>
-      <c r="FW5" s="165"/>
+      <c r="FT5" s="164" t="s">
+        <v>2</v>
+      </c>
+      <c r="FU5" s="165">
+        <v>4</v>
+      </c>
+      <c r="FV5" s="164" t="s">
+        <v>2</v>
+      </c>
+      <c r="FW5" s="165" t="s">
+        <v>3</v>
+      </c>
       <c r="FX5" s="164"/>
       <c r="FY5" s="165"/>
       <c r="FZ5" s="164"/>
@@ -9211,10 +9224,18 @@
       <c r="FQ8" s="165"/>
       <c r="FR8" s="169"/>
       <c r="FS8" s="165"/>
-      <c r="FT8" s="169"/>
-      <c r="FU8" s="165"/>
-      <c r="FV8" s="169"/>
-      <c r="FW8" s="165"/>
+      <c r="FT8" s="169" t="s">
+        <v>9</v>
+      </c>
+      <c r="FU8" s="165" t="s">
+        <v>3</v>
+      </c>
+      <c r="FV8" s="169" t="s">
+        <v>1</v>
+      </c>
+      <c r="FW8" s="165" t="s">
+        <v>3</v>
+      </c>
       <c r="FX8" s="169"/>
       <c r="FY8" s="165"/>
       <c r="FZ8" s="169"/>
@@ -9991,10 +10012,18 @@
       <c r="FQ10" s="165"/>
       <c r="FR10" s="164"/>
       <c r="FS10" s="165"/>
-      <c r="FT10" s="164"/>
-      <c r="FU10" s="165"/>
-      <c r="FV10" s="164"/>
-      <c r="FW10" s="165"/>
+      <c r="FT10" s="164" t="s">
+        <v>1</v>
+      </c>
+      <c r="FU10" s="165" t="s">
+        <v>3</v>
+      </c>
+      <c r="FV10" s="164" t="s">
+        <v>9</v>
+      </c>
+      <c r="FW10" s="165" t="s">
+        <v>3</v>
+      </c>
       <c r="FX10" s="164"/>
       <c r="FY10" s="165"/>
       <c r="FZ10" s="164"/>
@@ -10767,10 +10796,18 @@
       <c r="FQ12" s="165"/>
       <c r="FR12" s="164"/>
       <c r="FS12" s="165"/>
-      <c r="FT12" s="164"/>
-      <c r="FU12" s="165"/>
-      <c r="FV12" s="164"/>
-      <c r="FW12" s="165"/>
+      <c r="FT12" s="164" t="s">
+        <v>17</v>
+      </c>
+      <c r="FU12" s="165" t="s">
+        <v>3</v>
+      </c>
+      <c r="FV12" s="164" t="s">
+        <v>1</v>
+      </c>
+      <c r="FW12" s="165" t="s">
+        <v>3</v>
+      </c>
       <c r="FX12" s="164"/>
       <c r="FY12" s="165"/>
       <c r="FZ12" s="164"/>
@@ -11545,10 +11582,18 @@
       <c r="FQ14" s="165"/>
       <c r="FR14" s="164"/>
       <c r="FS14" s="165"/>
-      <c r="FT14" s="164"/>
-      <c r="FU14" s="165"/>
-      <c r="FV14" s="164"/>
-      <c r="FW14" s="165"/>
+      <c r="FT14" s="164" t="s">
+        <v>14</v>
+      </c>
+      <c r="FU14" s="165" t="s">
+        <v>3</v>
+      </c>
+      <c r="FV14" s="164" t="s">
+        <v>18</v>
+      </c>
+      <c r="FW14" s="165" t="s">
+        <v>3</v>
+      </c>
       <c r="FX14" s="164"/>
       <c r="FY14" s="165"/>
       <c r="FZ14" s="164"/>
@@ -12325,10 +12370,18 @@
       <c r="FQ16" s="165"/>
       <c r="FR16" s="164"/>
       <c r="FS16" s="165"/>
-      <c r="FT16" s="164"/>
-      <c r="FU16" s="165"/>
-      <c r="FV16" s="164"/>
-      <c r="FW16" s="165"/>
+      <c r="FT16" s="164" t="s">
+        <v>2</v>
+      </c>
+      <c r="FU16" s="165" t="s">
+        <v>3</v>
+      </c>
+      <c r="FV16" s="164" t="s">
+        <v>6</v>
+      </c>
+      <c r="FW16" s="165" t="s">
+        <v>3</v>
+      </c>
       <c r="FX16" s="164"/>
       <c r="FY16" s="165"/>
       <c r="FZ16" s="164"/>
@@ -13097,10 +13150,18 @@
       <c r="FQ18" s="165"/>
       <c r="FR18" s="164"/>
       <c r="FS18" s="165"/>
-      <c r="FT18" s="164"/>
-      <c r="FU18" s="165"/>
-      <c r="FV18" s="164"/>
-      <c r="FW18" s="165"/>
+      <c r="FT18" s="164" t="s">
+        <v>17</v>
+      </c>
+      <c r="FU18" s="165" t="s">
+        <v>3</v>
+      </c>
+      <c r="FV18" s="164" t="s">
+        <v>2</v>
+      </c>
+      <c r="FW18" s="165">
+        <v>7</v>
+      </c>
       <c r="FX18" s="164"/>
       <c r="FY18" s="165"/>
       <c r="FZ18" s="164"/>
@@ -13835,10 +13896,18 @@
       <c r="FQ20" s="165"/>
       <c r="FR20" s="164"/>
       <c r="FS20" s="165"/>
-      <c r="FT20" s="164"/>
-      <c r="FU20" s="165"/>
-      <c r="FV20" s="164"/>
-      <c r="FW20" s="165"/>
+      <c r="FT20" s="164" t="s">
+        <v>2</v>
+      </c>
+      <c r="FU20" s="165">
+        <v>4</v>
+      </c>
+      <c r="FV20" s="164" t="s">
+        <v>2</v>
+      </c>
+      <c r="FW20" s="165">
+        <v>3.25</v>
+      </c>
       <c r="FX20" s="164"/>
       <c r="FY20" s="165"/>
       <c r="FZ20" s="164"/>
@@ -14614,7 +14683,9 @@
       <c r="FV22" s="174" t="s">
         <v>25</v>
       </c>
-      <c r="FW22" s="175"/>
+      <c r="FW22" s="175">
+        <v>8</v>
+      </c>
       <c r="FX22" s="174" t="s">
         <v>25</v>
       </c>
@@ -15368,1095 +15439,1206 @@
     <mergeCell ref="JN23:JO23"/>
   </mergeCells>
   <conditionalFormatting sqref="DE5">
-    <cfRule type="containsText" dxfId="0" priority="241" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="268" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="240">
+    <cfRule type="containsBlanks" dxfId="1" priority="267">
       <formula>LEN(TRIM(DE5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG5">
-    <cfRule type="containsText" dxfId="0" priority="239" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="266" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="238">
+    <cfRule type="containsBlanks" dxfId="1" priority="265">
       <formula>LEN(TRIM(DG5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DU5">
-    <cfRule type="containsText" dxfId="0" priority="179" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="206" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DU5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="178">
+    <cfRule type="containsBlanks" dxfId="1" priority="205">
       <formula>LEN(TRIM(DU5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG5">
-    <cfRule type="containsText" dxfId="0" priority="142" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="169" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="141">
+    <cfRule type="containsBlanks" dxfId="1" priority="168">
       <formula>LEN(TRIM(EG5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ES5">
-    <cfRule type="containsText" dxfId="0" priority="110" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="137" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",ES5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="109">
+    <cfRule type="containsBlanks" dxfId="1" priority="136">
       <formula>LEN(TRIM(ES5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EU5">
-    <cfRule type="containsText" dxfId="0" priority="92" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="119" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EU5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="91">
+    <cfRule type="containsBlanks" dxfId="1" priority="118">
       <formula>LEN(TRIM(EU5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EW5">
-    <cfRule type="containsText" dxfId="0" priority="79" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="106" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EW5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="78">
+    <cfRule type="containsBlanks" dxfId="1" priority="105">
       <formula>LEN(TRIM(EW5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FI5">
-    <cfRule type="containsText" dxfId="0" priority="53" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="80" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FI5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="52">
+    <cfRule type="containsBlanks" dxfId="1" priority="79">
       <formula>LEN(TRIM(FI5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FW5">
+    <cfRule type="containsText" dxfId="0" priority="25" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FW5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="24">
+      <formula>LEN(TRIM(FW5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC8">
-    <cfRule type="containsText" dxfId="0" priority="261" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="288" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DC8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="260">
+    <cfRule type="containsBlanks" dxfId="1" priority="287">
       <formula>LEN(TRIM(DC8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DE8">
-    <cfRule type="containsText" dxfId="0" priority="243" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="270" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="242">
+    <cfRule type="containsBlanks" dxfId="1" priority="269">
       <formula>LEN(TRIM(DE8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG8">
-    <cfRule type="containsText" dxfId="0" priority="237" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="264" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="236">
+    <cfRule type="containsBlanks" dxfId="1" priority="263">
       <formula>LEN(TRIM(DG8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI8">
-    <cfRule type="containsText" dxfId="0" priority="215" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="242" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="214">
+    <cfRule type="containsBlanks" dxfId="1" priority="241">
       <formula>LEN(TRIM(DI8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK8">
-    <cfRule type="containsText" dxfId="0" priority="213" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="240" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="212">
+    <cfRule type="containsBlanks" dxfId="1" priority="239">
       <formula>LEN(TRIM(DK8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ8">
-    <cfRule type="containsText" dxfId="0" priority="165" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="192" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="164">
+    <cfRule type="containsBlanks" dxfId="1" priority="191">
       <formula>LEN(TRIM(DQ8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DS8">
-    <cfRule type="containsText" dxfId="0" priority="177" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="204" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DS8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="176">
+    <cfRule type="containsBlanks" dxfId="1" priority="203">
       <formula>LEN(TRIM(DS8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DU8">
-    <cfRule type="containsText" dxfId="0" priority="181" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="208" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DU8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="180">
+    <cfRule type="containsBlanks" dxfId="1" priority="207">
       <formula>LEN(TRIM(DU8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DW8">
-    <cfRule type="containsText" dxfId="0" priority="201" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="228" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DW8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="200">
+    <cfRule type="containsBlanks" dxfId="1" priority="227">
       <formula>LEN(TRIM(DW8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DY8">
-    <cfRule type="containsText" dxfId="0" priority="159" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="186" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DY8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="158">
+    <cfRule type="containsBlanks" dxfId="1" priority="185">
       <formula>LEN(TRIM(DY8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EE8">
-    <cfRule type="containsText" dxfId="0" priority="148" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="175" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EE8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="147">
+    <cfRule type="containsBlanks" dxfId="1" priority="174">
       <formula>LEN(TRIM(EE8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG8">
-    <cfRule type="containsText" dxfId="0" priority="140" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="167" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="139">
+    <cfRule type="containsBlanks" dxfId="1" priority="166">
       <formula>LEN(TRIM(EG8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EQ8">
-    <cfRule type="containsText" dxfId="0" priority="122" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="149" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EQ8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="121">
+    <cfRule type="containsBlanks" dxfId="1" priority="148">
       <formula>LEN(TRIM(EQ8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ES8">
-    <cfRule type="containsText" dxfId="0" priority="108" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="135" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",ES8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="107">
+    <cfRule type="containsBlanks" dxfId="1" priority="134">
       <formula>LEN(TRIM(ES8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EU8">
-    <cfRule type="containsText" dxfId="0" priority="90" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="117" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EU8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="89">
+    <cfRule type="containsBlanks" dxfId="1" priority="116">
       <formula>LEN(TRIM(EU8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EW8">
-    <cfRule type="containsText" dxfId="0" priority="77" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="104" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EW8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="76">
+    <cfRule type="containsBlanks" dxfId="1" priority="103">
       <formula>LEN(TRIM(EW8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FI8">
-    <cfRule type="containsText" dxfId="0" priority="51" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="78" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FI8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="50">
+    <cfRule type="containsBlanks" dxfId="1" priority="77">
       <formula>LEN(TRIM(FI8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FK8">
-    <cfRule type="containsText" dxfId="0" priority="31" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="58" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FK8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="30">
+    <cfRule type="containsBlanks" dxfId="1" priority="57">
       <formula>LEN(TRIM(FK8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FM8">
-    <cfRule type="containsText" dxfId="0" priority="14" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="41" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FM8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="13">
+    <cfRule type="containsBlanks" dxfId="1" priority="40">
       <formula>LEN(TRIM(FM8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FO8">
-    <cfRule type="containsText" dxfId="0" priority="12" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="39" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FO8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="11">
+    <cfRule type="containsBlanks" dxfId="1" priority="38">
       <formula>LEN(TRIM(FO8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FU8">
+    <cfRule type="containsText" dxfId="0" priority="27" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FU8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="26">
+      <formula>LEN(TRIM(FU8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FW8">
+    <cfRule type="containsText" dxfId="0" priority="23" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FW8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="22">
+      <formula>LEN(TRIM(FW8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DE10">
-    <cfRule type="containsText" dxfId="0" priority="245" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="272" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="244">
+    <cfRule type="containsBlanks" dxfId="1" priority="271">
       <formula>LEN(TRIM(DE10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI10">
-    <cfRule type="containsText" dxfId="0" priority="217" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="244" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="216">
+    <cfRule type="containsBlanks" dxfId="1" priority="243">
       <formula>LEN(TRIM(DI10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK10">
-    <cfRule type="containsText" dxfId="0" priority="211" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="238" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="210">
+    <cfRule type="containsBlanks" dxfId="1" priority="237">
       <formula>LEN(TRIM(DK10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ10">
-    <cfRule type="containsText" dxfId="0" priority="167" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="194" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="166">
+    <cfRule type="containsBlanks" dxfId="1" priority="193">
       <formula>LEN(TRIM(DQ10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DS10">
-    <cfRule type="containsText" dxfId="0" priority="175" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="202" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DS10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="174">
+    <cfRule type="containsBlanks" dxfId="1" priority="201">
       <formula>LEN(TRIM(DS10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DW10">
-    <cfRule type="containsText" dxfId="0" priority="199" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="226" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DW10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="198">
+    <cfRule type="containsBlanks" dxfId="1" priority="225">
       <formula>LEN(TRIM(DW10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DY10">
-    <cfRule type="containsText" dxfId="0" priority="157" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="184" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DY10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="156">
+    <cfRule type="containsBlanks" dxfId="1" priority="183">
       <formula>LEN(TRIM(DY10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG10">
-    <cfRule type="containsText" dxfId="0" priority="138" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="165" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="137">
+    <cfRule type="containsBlanks" dxfId="1" priority="164">
       <formula>LEN(TRIM(EG10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EQ10">
-    <cfRule type="containsText" dxfId="0" priority="120" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="147" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EQ10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="119">
+    <cfRule type="containsBlanks" dxfId="1" priority="146">
       <formula>LEN(TRIM(EQ10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ES10">
-    <cfRule type="containsText" dxfId="0" priority="106" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="133" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",ES10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="105">
+    <cfRule type="containsBlanks" dxfId="1" priority="132">
       <formula>LEN(TRIM(ES10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EU10">
-    <cfRule type="containsText" dxfId="0" priority="88" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="115" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EU10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="87">
+    <cfRule type="containsBlanks" dxfId="1" priority="114">
       <formula>LEN(TRIM(EU10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FI10">
-    <cfRule type="containsText" dxfId="0" priority="49" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="76" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FI10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="48">
+    <cfRule type="containsBlanks" dxfId="1" priority="75">
       <formula>LEN(TRIM(FI10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FK10">
-    <cfRule type="containsText" dxfId="0" priority="33" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="60" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FK10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="32">
+    <cfRule type="containsBlanks" dxfId="1" priority="59">
       <formula>LEN(TRIM(FK10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FM10">
-    <cfRule type="containsText" dxfId="0" priority="16" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="43" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FM10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="15">
+    <cfRule type="containsBlanks" dxfId="1" priority="42">
       <formula>LEN(TRIM(FM10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FO10">
-    <cfRule type="containsText" dxfId="0" priority="10" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="37" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FO10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="9">
+    <cfRule type="containsBlanks" dxfId="1" priority="36">
       <formula>LEN(TRIM(FO10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FU10">
+    <cfRule type="containsText" dxfId="0" priority="13" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FU10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="12">
+      <formula>LEN(TRIM(FU10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FW10">
+    <cfRule type="containsText" dxfId="0" priority="21" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FW10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="20">
+      <formula>LEN(TRIM(FW10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CR11">
-    <cfRule type="containsText" dxfId="0" priority="269" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="296" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",CR11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CT11">
-    <cfRule type="containsText" dxfId="0" priority="268" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="295" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",CT11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DX11">
-    <cfRule type="containsText" dxfId="0" priority="160" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="187" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DX11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EF11">
-    <cfRule type="containsText" dxfId="0" priority="149" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="176" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EF11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ET11">
-    <cfRule type="containsText" dxfId="0" priority="93" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="120" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",ET11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EV11">
-    <cfRule type="containsText" dxfId="0" priority="80" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="107" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EV11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FI11">
-    <cfRule type="containsText" dxfId="2" priority="56" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="83" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",FI11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FV11">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FV11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC12">
-    <cfRule type="containsText" dxfId="0" priority="259" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="286" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DC12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="258">
+    <cfRule type="containsBlanks" dxfId="1" priority="285">
       <formula>LEN(TRIM(DC12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DE12">
-    <cfRule type="containsText" dxfId="0" priority="247" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="274" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="246">
+    <cfRule type="containsBlanks" dxfId="1" priority="273">
       <formula>LEN(TRIM(DE12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG12">
-    <cfRule type="containsText" dxfId="0" priority="235" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="262" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="234">
+    <cfRule type="containsBlanks" dxfId="1" priority="261">
       <formula>LEN(TRIM(DG12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI12">
-    <cfRule type="containsText" dxfId="0" priority="219" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="246" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="218">
+    <cfRule type="containsBlanks" dxfId="1" priority="245">
       <formula>LEN(TRIM(DI12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ12">
-    <cfRule type="containsText" dxfId="0" priority="171" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="198" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="170">
+    <cfRule type="containsBlanks" dxfId="1" priority="197">
       <formula>LEN(TRIM(DQ12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DS12">
-    <cfRule type="containsText" dxfId="0" priority="173" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="200" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DS12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="172">
+    <cfRule type="containsBlanks" dxfId="1" priority="199">
       <formula>LEN(TRIM(DS12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DU12">
-    <cfRule type="containsText" dxfId="0" priority="183" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="210" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DU12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="182">
+    <cfRule type="containsBlanks" dxfId="1" priority="209">
       <formula>LEN(TRIM(DU12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DW12">
-    <cfRule type="containsText" dxfId="0" priority="197" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="224" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DW12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="196">
+    <cfRule type="containsBlanks" dxfId="1" priority="223">
       <formula>LEN(TRIM(DW12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EE12">
-    <cfRule type="containsText" dxfId="0" priority="146" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="173" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EE12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="145">
+    <cfRule type="containsBlanks" dxfId="1" priority="172">
       <formula>LEN(TRIM(EE12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG12">
-    <cfRule type="containsText" dxfId="0" priority="136" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="163" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="135">
+    <cfRule type="containsBlanks" dxfId="1" priority="162">
       <formula>LEN(TRIM(EG12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EQ12">
-    <cfRule type="containsText" dxfId="0" priority="118" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="145" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EQ12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="117">
+    <cfRule type="containsBlanks" dxfId="1" priority="144">
       <formula>LEN(TRIM(EQ12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ES12">
-    <cfRule type="containsText" dxfId="0" priority="104" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="131" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",ES12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="103">
+    <cfRule type="containsBlanks" dxfId="1" priority="130">
       <formula>LEN(TRIM(ES12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EU12">
-    <cfRule type="containsText" dxfId="0" priority="86" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="113" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EU12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="85">
+    <cfRule type="containsBlanks" dxfId="1" priority="112">
       <formula>LEN(TRIM(EU12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EW12">
-    <cfRule type="containsText" dxfId="0" priority="75" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="102" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EW12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="74">
+    <cfRule type="containsBlanks" dxfId="1" priority="101">
       <formula>LEN(TRIM(EW12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FI12">
-    <cfRule type="containsText" dxfId="0" priority="47" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="74" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FI12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="46">
+    <cfRule type="containsBlanks" dxfId="1" priority="73">
       <formula>LEN(TRIM(FI12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FK12">
-    <cfRule type="containsText" dxfId="0" priority="35" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="62" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FK12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="34">
+    <cfRule type="containsBlanks" dxfId="1" priority="61">
       <formula>LEN(TRIM(FK12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FM12">
-    <cfRule type="containsText" dxfId="0" priority="18" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="45" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FM12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="17">
+    <cfRule type="containsBlanks" dxfId="1" priority="44">
       <formula>LEN(TRIM(FM12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FU12">
+    <cfRule type="containsText" dxfId="0" priority="11" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FU12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="10">
+      <formula>LEN(TRIM(FU12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FW12">
+    <cfRule type="containsText" dxfId="0" priority="19" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FW12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="18">
+      <formula>LEN(TRIM(FW12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC14">
-    <cfRule type="containsText" dxfId="0" priority="257" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="284" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DC14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="256">
+    <cfRule type="containsBlanks" dxfId="1" priority="283">
       <formula>LEN(TRIM(DC14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DE14">
-    <cfRule type="containsText" dxfId="0" priority="249" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="276" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="248">
+    <cfRule type="containsBlanks" dxfId="1" priority="275">
       <formula>LEN(TRIM(DE14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI14">
-    <cfRule type="containsText" dxfId="0" priority="221" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="248" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="220">
+    <cfRule type="containsBlanks" dxfId="1" priority="247">
       <formula>LEN(TRIM(DI14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK14">
-    <cfRule type="containsText" dxfId="0" priority="209" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="236" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="208">
+    <cfRule type="containsBlanks" dxfId="1" priority="235">
       <formula>LEN(TRIM(DK14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ14">
-    <cfRule type="containsText" dxfId="0" priority="169" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="196" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="168">
+    <cfRule type="containsBlanks" dxfId="1" priority="195">
       <formula>LEN(TRIM(DQ14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DS14">
-    <cfRule type="containsText" dxfId="0" priority="185" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="212" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DS14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="184">
+    <cfRule type="containsBlanks" dxfId="1" priority="211">
       <formula>LEN(TRIM(DS14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DW14">
-    <cfRule type="containsText" dxfId="0" priority="195" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="222" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DW14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="194">
+    <cfRule type="containsBlanks" dxfId="1" priority="221">
       <formula>LEN(TRIM(DW14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DY14">
-    <cfRule type="containsText" dxfId="0" priority="155" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="182" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DY14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="154">
+    <cfRule type="containsBlanks" dxfId="1" priority="181">
       <formula>LEN(TRIM(DY14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EE14">
-    <cfRule type="containsText" dxfId="0" priority="144" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="171" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EE14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="143">
+    <cfRule type="containsBlanks" dxfId="1" priority="170">
       <formula>LEN(TRIM(EE14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG14">
-    <cfRule type="containsText" dxfId="0" priority="134" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="161" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="133">
+    <cfRule type="containsBlanks" dxfId="1" priority="160">
       <formula>LEN(TRIM(EG14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EM14">
-    <cfRule type="containsText" dxfId="0" priority="128" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="155" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EM14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="127">
+    <cfRule type="containsBlanks" dxfId="1" priority="154">
       <formula>LEN(TRIM(EM14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EQ14">
-    <cfRule type="containsText" dxfId="0" priority="116" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="143" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EQ14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="115">
+    <cfRule type="containsBlanks" dxfId="1" priority="142">
       <formula>LEN(TRIM(EQ14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ES14">
-    <cfRule type="containsText" dxfId="0" priority="102" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="129" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",ES14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="101">
+    <cfRule type="containsBlanks" dxfId="1" priority="128">
       <formula>LEN(TRIM(ES14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EU14">
-    <cfRule type="containsText" dxfId="0" priority="84" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="111" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EU14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="83">
+    <cfRule type="containsBlanks" dxfId="1" priority="110">
       <formula>LEN(TRIM(EU14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FI14">
-    <cfRule type="containsText" dxfId="0" priority="45" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="72" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FI14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="44">
+    <cfRule type="containsBlanks" dxfId="1" priority="71">
       <formula>LEN(TRIM(FI14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FK14">
-    <cfRule type="containsText" dxfId="0" priority="37" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="64" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FK14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="36">
+    <cfRule type="containsBlanks" dxfId="1" priority="63">
       <formula>LEN(TRIM(FK14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FM14">
-    <cfRule type="containsText" dxfId="0" priority="20" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="47" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FM14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="19">
+    <cfRule type="containsBlanks" dxfId="1" priority="46">
       <formula>LEN(TRIM(FM14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FO14">
-    <cfRule type="containsText" dxfId="0" priority="8" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="35" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FO14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="7">
+    <cfRule type="containsBlanks" dxfId="1" priority="34">
       <formula>LEN(TRIM(FO14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FU14">
+    <cfRule type="containsText" dxfId="0" priority="9" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FU14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="8">
+      <formula>LEN(TRIM(FU14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FW14">
+    <cfRule type="containsText" dxfId="0" priority="17" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FW14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="16">
+      <formula>LEN(TRIM(FW14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DE16">
-    <cfRule type="containsText" dxfId="0" priority="251" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="278" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="250">
+    <cfRule type="containsBlanks" dxfId="1" priority="277">
       <formula>LEN(TRIM(DE16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG16">
-    <cfRule type="containsText" dxfId="0" priority="233" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="260" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="232">
+    <cfRule type="containsBlanks" dxfId="1" priority="259">
       <formula>LEN(TRIM(DG16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI16">
-    <cfRule type="containsText" dxfId="0" priority="223" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="250" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="222">
+    <cfRule type="containsBlanks" dxfId="1" priority="249">
       <formula>LEN(TRIM(DI16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK16">
-    <cfRule type="containsText" dxfId="0" priority="207" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="234" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="206">
+    <cfRule type="containsBlanks" dxfId="1" priority="233">
       <formula>LEN(TRIM(DK16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DS16">
-    <cfRule type="containsText" dxfId="0" priority="187" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="214" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DS16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="186">
+    <cfRule type="containsBlanks" dxfId="1" priority="213">
       <formula>LEN(TRIM(DS16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DU16">
-    <cfRule type="containsText" dxfId="0" priority="191" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="218" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DU16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="190">
+    <cfRule type="containsBlanks" dxfId="1" priority="217">
       <formula>LEN(TRIM(DU16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DW16">
-    <cfRule type="containsText" dxfId="0" priority="193" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="220" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DW16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="192">
+    <cfRule type="containsBlanks" dxfId="1" priority="219">
       <formula>LEN(TRIM(DW16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG16">
-    <cfRule type="containsText" dxfId="0" priority="132" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="159" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="131">
+    <cfRule type="containsBlanks" dxfId="1" priority="158">
       <formula>LEN(TRIM(EG16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EM16">
-    <cfRule type="containsText" dxfId="0" priority="126" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="153" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EM16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="125">
+    <cfRule type="containsBlanks" dxfId="1" priority="152">
       <formula>LEN(TRIM(EM16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EQ16">
-    <cfRule type="containsText" dxfId="0" priority="114" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="141" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EQ16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="113">
+    <cfRule type="containsBlanks" dxfId="1" priority="140">
       <formula>LEN(TRIM(EQ16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ES16">
-    <cfRule type="containsText" dxfId="0" priority="100" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="127" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",ES16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="99">
+    <cfRule type="containsBlanks" dxfId="1" priority="126">
       <formula>LEN(TRIM(ES16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EU16">
-    <cfRule type="containsText" dxfId="0" priority="82" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="109" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EU16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="81">
+    <cfRule type="containsBlanks" dxfId="1" priority="108">
       <formula>LEN(TRIM(EU16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FI16">
-    <cfRule type="containsText" dxfId="0" priority="43" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="70" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FI16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="42">
+    <cfRule type="containsBlanks" dxfId="1" priority="69">
       <formula>LEN(TRIM(FI16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FM16">
-    <cfRule type="containsText" dxfId="0" priority="22" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="49" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FM16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="21">
+    <cfRule type="containsBlanks" dxfId="1" priority="48">
       <formula>LEN(TRIM(FM16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FO16">
-    <cfRule type="containsText" dxfId="0" priority="6" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="33" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FO16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="5">
+    <cfRule type="containsBlanks" dxfId="1" priority="32">
       <formula>LEN(TRIM(FO16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FU16">
+    <cfRule type="containsText" dxfId="0" priority="7" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FU16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="6">
+      <formula>LEN(TRIM(FU16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FW16">
+    <cfRule type="containsText" dxfId="0" priority="15" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FW16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="14">
+      <formula>LEN(TRIM(FW16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DE18">
-    <cfRule type="containsText" dxfId="0" priority="253" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="280" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="252">
+    <cfRule type="containsBlanks" dxfId="1" priority="279">
       <formula>LEN(TRIM(DE18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG18">
-    <cfRule type="containsText" dxfId="0" priority="231" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="258" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="230">
+    <cfRule type="containsBlanks" dxfId="1" priority="257">
       <formula>LEN(TRIM(DG18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI18">
-    <cfRule type="containsText" dxfId="0" priority="225" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="252" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="224">
+    <cfRule type="containsBlanks" dxfId="1" priority="251">
       <formula>LEN(TRIM(DI18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK18">
-    <cfRule type="containsText" dxfId="0" priority="205" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="232" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="204">
+    <cfRule type="containsBlanks" dxfId="1" priority="231">
       <formula>LEN(TRIM(DK18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ18">
-    <cfRule type="containsText" dxfId="0" priority="163" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="190" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="162">
+    <cfRule type="containsBlanks" dxfId="1" priority="189">
       <formula>LEN(TRIM(DQ18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DY18">
-    <cfRule type="containsText" dxfId="0" priority="153" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="180" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DY18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="152">
+    <cfRule type="containsBlanks" dxfId="1" priority="179">
       <formula>LEN(TRIM(DY18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG18">
-    <cfRule type="containsText" dxfId="0" priority="130" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="157" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="129">
+    <cfRule type="containsBlanks" dxfId="1" priority="156">
       <formula>LEN(TRIM(EG18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EM18">
-    <cfRule type="containsText" dxfId="0" priority="124" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="151" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EM18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="123">
+    <cfRule type="containsBlanks" dxfId="1" priority="150">
       <formula>LEN(TRIM(EM18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EQ18">
-    <cfRule type="containsText" dxfId="0" priority="112" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="139" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EQ18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="111">
+    <cfRule type="containsBlanks" dxfId="1" priority="138">
       <formula>LEN(TRIM(EQ18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ES18">
-    <cfRule type="containsText" dxfId="0" priority="98" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="125" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",ES18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="97">
+    <cfRule type="containsBlanks" dxfId="1" priority="124">
       <formula>LEN(TRIM(ES18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EW18">
-    <cfRule type="containsText" dxfId="0" priority="73" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="100" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EW18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="72">
+    <cfRule type="containsBlanks" dxfId="1" priority="99">
       <formula>LEN(TRIM(EW18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FK18">
-    <cfRule type="containsText" dxfId="0" priority="41" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="68" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FK18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="40">
+    <cfRule type="containsBlanks" dxfId="1" priority="67">
       <formula>LEN(TRIM(FK18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FM18">
-    <cfRule type="containsText" dxfId="0" priority="24" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="51" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FM18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="23">
+    <cfRule type="containsBlanks" dxfId="1" priority="50">
       <formula>LEN(TRIM(FM18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FO18">
-    <cfRule type="containsText" dxfId="0" priority="4" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="31" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FO18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="3">
+    <cfRule type="containsBlanks" dxfId="1" priority="30">
       <formula>LEN(TRIM(FO18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FU18">
+    <cfRule type="containsText" dxfId="0" priority="5" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FU18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="1" priority="4">
+      <formula>LEN(TRIM(FU18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC20">
-    <cfRule type="containsText" dxfId="0" priority="255" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="282" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DC20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="254">
+    <cfRule type="containsBlanks" dxfId="1" priority="281">
       <formula>LEN(TRIM(DC20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG20">
-    <cfRule type="containsText" dxfId="0" priority="229" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="256" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="228">
+    <cfRule type="containsBlanks" dxfId="1" priority="255">
       <formula>LEN(TRIM(DG20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI20">
-    <cfRule type="containsText" dxfId="0" priority="227" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="254" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="226">
+    <cfRule type="containsBlanks" dxfId="1" priority="253">
       <formula>LEN(TRIM(DI20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK20">
-    <cfRule type="containsText" dxfId="0" priority="203" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="230" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="202">
+    <cfRule type="containsBlanks" dxfId="1" priority="229">
       <formula>LEN(TRIM(DK20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DU20">
-    <cfRule type="containsText" dxfId="0" priority="189" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="216" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DU20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="188">
+    <cfRule type="containsBlanks" dxfId="1" priority="215">
       <formula>LEN(TRIM(DU20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EW20">
-    <cfRule type="containsText" dxfId="0" priority="71" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="98" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EW20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="70">
+    <cfRule type="containsBlanks" dxfId="1" priority="97">
       <formula>LEN(TRIM(EW20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FK20">
-    <cfRule type="containsText" dxfId="0" priority="39" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="66" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FK20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="38">
+    <cfRule type="containsBlanks" dxfId="1" priority="65">
       <formula>LEN(TRIM(FK20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FM20">
-    <cfRule type="containsText" dxfId="0" priority="26" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="53" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FM20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="25">
+    <cfRule type="containsBlanks" dxfId="1" priority="52">
       <formula>LEN(TRIM(FM20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FO20">
-    <cfRule type="containsText" dxfId="0" priority="2" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="29" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FO20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="1">
+    <cfRule type="containsBlanks" dxfId="1" priority="28">
       <formula>LEN(TRIM(FO20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DX3:DX20">
-    <cfRule type="containsText" dxfId="2" priority="161" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="188" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",DX3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ED3:ED20">
-    <cfRule type="containsText" dxfId="2" priority="151" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="178" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",ED3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EF3:EF20">
-    <cfRule type="containsText" dxfId="2" priority="150" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="177" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",EF3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EP3:EP20">
-    <cfRule type="containsText" dxfId="2" priority="96" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="123" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",EP3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ER3:ER20">
-    <cfRule type="containsText" dxfId="2" priority="95" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="122" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",ER3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ET3:ET20">
-    <cfRule type="containsText" dxfId="2" priority="94" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="121" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",ET3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B3:B21 D3:D21 KV3:KV21 LH3:LH21 KT3:KT21 KR3:KR21 F3:F21 KP3:KP21 KN3:KN21 KL3:KL21 H3:H21 KJ3:KJ21 KH3:KH21 KF3:KF21 J3:J21 KD3:KD21 KB3:KB21 JZ3:JZ21 L3:L21 JX3:JX21 JV3:JV21 JT3:JT21 N3:N21 JR3:JR21 P3:P21 JP3:JP21 R3:R21 JN3:JN21 T3:T21 JL3:JL21 V3:V21 JJ3:JJ21 X3:X21 JH3:JH21 JF3:JF21 Z3:Z21 JD3:JD21 JB3:JB21 AB3:AB21 IZ3:IZ21 IX3:IX21 AD3:AD21 IV3:IV21 IT3:IT21 AF3:AF21 IR3:IR21 IP3:IP21 AH3:AH21 IN3:IN21 IL3:IL21 AJ3:AJ21 IJ3:IJ21 IH3:IH21 AL3:AL21 IF3:IF21 ID3:ID21 AN3:AN21 IB3:IB21 HZ3:HZ21 AP3:AP21 HX3:HX21 HV3:HV21 AR3:AR21 HT3:HT21 HR3:HR21 AT3:AT21 HP3:HP21 HN3:HN21 AV3:AV21 HL3:HL21 HJ3:HJ21 AX3:AX21 HH3:HH21 HF3:HF21 AZ3:AZ21 HD3:HD21 HB3:HB21 BB3:BB21 GZ3:GZ21 GX3:GX21 BD3:BD21 GV3:GV21 GT3:GT21 BF3:BF21 GR3:GR21 GP3:GP21 BH3:BH21 GN3:GN21 GL3:GL21 BJ3:BJ21 GJ3:GJ21 GH3:GH21 BL3:BL21 GF3:GF21 GD3:GD21 BN3:BN21 GB3:GB21 FZ3:FZ21 BP3:BP21 FX3:FX21 FV3:FV21 BR3:BR21 FT3:FT21 FR3:FR21 BT3:BT21 FP3:FP21 FN21 BV3:BV21 FL21 FJ21 BX3:BX21 FH21 FF3:FF21 BZ3:BZ21 FD3:FD21 FB3:FB21 CB3:CB21 EZ3:EZ21 EX3:EX21 CD3:CD21 EV3:EV21 ET21 CF3:CF21 ER21 EP21 CH3:CH21 EN3:EN21 EL3:EL21 CJ3:CJ21 EJ3:EJ21 EH3:EH21 CL3:CL21 EF21 ED21 CN3:CN21 EB3:EB21 DZ3:DZ21 CP3:CP21 DX21 DV21 CR3:CR21 DT21 DR21 CT3:CT21 DP21 DN3:DN21 CV3:CV21 DL3:DL21 DJ21 CX3:CX21 DH21 DF21 CZ3:CZ21 DD21 DB21 LI11 KU11 KS11 KW11:LG11 KQ11 KO11 KM11 LF12:LF21 KK11 KI11 KG11 LD12:LD21 KE11 KC11 KA11 LB12:LB21 JY11 JW11 JU11 KZ12:KZ21 JS11 JQ11 JO11 JM11 JK11 JI11 JG11 W11 JE11 JC11 Y11 JA11 IY11 AA11 IW11 IU11 AC11 IS11 IQ11 AE11 IO11 IM11 AG11 IK11 II11 AI11 IG11 IE11 AK11 IC11 IA11 AM11 HY11 HW11 AO11 HU11 HS11 AQ11 HQ11 HO11 AS11 HM11 HK11 AU11 HI11 HG11 AW11 HE11 HC11 AY11 HA11 GY11 BA11 GW11 GU11 BC11 GS11 GQ11 BE11 GO11 GM11 BG11 GK11 GI11 BI11 GG11 GE11 BK11 GC11 GA11 BM11 FY11 FW11 BO11 FU11 FS11 BQ11 FQ11 BS11 FK11 BU11 FG11 BW11 FE11 FC11 BY11 FA11 EY11 CA11 EW11 EU11 CC11 ES11 EQ11 CE11 EO11 EM11 CG11 EK11 EI11 CI11 EG11 EE11 CK11 EC11 EA11 CM11 DY11 CO11 CQ11 DO11 CS11 DM11 CU11 CW11 CY11 DA11 KX3:KX10 KX12:KX21 KZ3:KZ10 LB3:LB10 LD3:LD10 LF3:LF10">
-    <cfRule type="containsText" dxfId="2" priority="274" operator="between" text="占">
+  <conditionalFormatting sqref="FT3:FT20">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",FT3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FV3:FV20">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",FV3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3:B21 D3:D21 KV3:KV21 LH3:LH21 KT3:KT21 KR3:KR21 F3:F21 KP3:KP21 KN3:KN21 KL3:KL21 H3:H21 KJ3:KJ21 KH3:KH21 KF3:KF21 J3:J21 KD3:KD21 KB3:KB21 JZ3:JZ21 L3:L21 JX3:JX21 JV3:JV21 JT3:JT21 N3:N21 JR3:JR21 P3:P21 JP3:JP21 R3:R21 JN3:JN21 T3:T21 JL3:JL21 V3:V21 JJ3:JJ21 X3:X21 JH3:JH21 JF3:JF21 Z3:Z21 JD3:JD21 JB3:JB21 AB3:AB21 IZ3:IZ21 IX3:IX21 AD3:AD21 IV3:IV21 IT3:IT21 AF3:AF21 IR3:IR21 IP3:IP21 AH3:AH21 IN3:IN21 IL3:IL21 AJ3:AJ21 IJ3:IJ21 IH3:IH21 AL3:AL21 IF3:IF21 ID3:ID21 AN3:AN21 IB3:IB21 HZ3:HZ21 AP3:AP21 HX3:HX21 HV3:HV21 AR3:AR21 HT3:HT21 HR3:HR21 AT3:AT21 HP3:HP21 HN3:HN21 AV3:AV21 HL3:HL21 HJ3:HJ21 AX3:AX21 HH3:HH21 HF3:HF21 AZ3:AZ21 HD3:HD21 HB3:HB21 BB3:BB21 GZ3:GZ21 GX3:GX21 BD3:BD21 GV3:GV21 GT3:GT21 BF3:BF21 GR3:GR21 GP3:GP21 BH3:BH21 GN3:GN21 GL3:GL21 BJ3:BJ21 GJ3:GJ21 GH3:GH21 BL3:BL21 GF3:GF21 GD3:GD21 BN3:BN21 GB3:GB21 FZ3:FZ21 BP3:BP21 FX3:FX21 FV21 BR3:BR21 FT21 FR3:FR21 BT3:BT21 FP3:FP21 FN21 BV3:BV21 FL21 FJ21 BX3:BX21 FH21 FF3:FF21 BZ3:BZ21 FD3:FD21 FB3:FB21 CB3:CB21 EZ3:EZ21 EX3:EX21 CD3:CD21 EV3:EV21 ET21 CF3:CF21 ER21 EP21 CH3:CH21 EN3:EN21 EL3:EL21 CJ3:CJ21 EJ3:EJ21 EH3:EH21 CL3:CL21 EF21 ED21 CN3:CN21 EB3:EB21 DZ3:DZ21 CP3:CP21 DX21 DV21 CR3:CR21 DT21 DR21 CT3:CT21 DP21 DN3:DN21 CV3:CV21 DL3:DL21 DJ21 CX3:CX21 DH21 DF21 CZ3:CZ21 DD21 DB21 LI11 KU11 KS11 KW11:LG11 KQ11 KO11 KM11 LF12:LF21 KK11 KI11 KG11 LD12:LD21 KE11 KC11 KA11 LB12:LB21 JY11 JW11 JU11 KZ12:KZ21 JS11 JQ11 JO11 JM11 JK11 JI11 JG11 W11 JE11 JC11 Y11 JA11 IY11 AA11 IW11 IU11 AC11 IS11 IQ11 AE11 IO11 IM11 AG11 IK11 II11 AI11 IG11 IE11 AK11 IC11 IA11 AM11 HY11 HW11 AO11 HU11 HS11 AQ11 HQ11 HO11 AS11 HM11 HK11 AU11 HI11 HG11 AW11 HE11 HC11 AY11 HA11 GY11 BA11 GW11 GU11 BC11 GS11 GQ11 BE11 GO11 GM11 BG11 GK11 GI11 BI11 GG11 GE11 BK11 GC11 GA11 BM11 FY11 FW11 BO11 FU11 FS11 BQ11 FQ11 BS11 FK11 BU11 FG11 BW11 FE11 FC11 BY11 FA11 EY11 CA11 EW11 EU11 CC11 ES11 EQ11 CE11 EO11 EM11 CG11 EK11 EI11 CI11 EG11 EE11 CK11 EC11 EA11 CM11 DY11 CO11 CQ11 DO11 CS11 DM11 CU11 CW11 CY11 DA11 KX3:KX10 KX12:KX21 KZ3:KZ10 LB3:LB10 LD3:LD10 LF3:LF10">
+    <cfRule type="containsText" dxfId="2" priority="301" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",B3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C21 E3:E21 KW3:KW21 LI3:LI21 KU3:KU21 KS3:KS21 G3:G21 KQ3:KQ21 KO3:KO21 KM3:KM21 I3:I21 KK3:KK21 KI3:KI21 KG3:KG21 K3:K21 KE3:KE21 KC3:KC21 KA3:KA21 M3:M21 JY3:JY21 JW3:JW21 JU3:JU21 O3:O21 JS3:JS21 Q3:Q21 JQ3:JQ21 S3:S21 JO3:JO21 U3:U21 JM3:JM21 W3:W21 JK3:JK21 Y3:Y21 JI3:JI21 JG3:JG21 AA3:AA21 JE3:JE21 JC3:JC21 AC3:AC21 JA3:JA21 IY3:IY21 AE3:AE21 IW3:IW21 IU3:IU21 AG3:AG21 IS3:IS21 IQ3:IQ21 AI3:AI21 IO3:IO21 IM3:IM21 AK3:AK21 IK3:IK21 II3:II21 AM3:AM21 IG3:IG21 IE3:IE21 AO3:AO21 IC3:IC21 IA3:IA21 AQ3:AQ21 HY3:HY21 HW3:HW21 AS3:AS21 HU3:HU21 HS3:HS21 AU3:AU21 HQ3:HQ21 HO3:HO21 AW3:AW21 HM3:HM21 HK3:HK21 AY3:AY21 HI3:HI21 HG3:HG21 BA3:BA21 HE3:HE21 HC3:HC21 BC3:BC21 HA3:HA21 GY3:GY21 BE3:BE21 GW3:GW21 GU3:GU21 BG3:BG21 GS3:GS21 GQ3:GQ21 BI3:BI21 GO3:GO21 GM3:GM21 BK3:BK21 GK3:GK21 GI3:GI21 BM3:BM21 GG3:GG21 GE3:GE21 BO3:BO21 GC3:GC21 GA3:GA21 BQ3:BQ21 FY3:FY21 FW3:FW21 BS3:BS21 FU3:FU21 FS3:FS21 BU3:BU21 FQ3:FQ21 FO21 BW3:BW21 FM21 FK3:FK7 FK9 FK11 FK13 FK15:FK17 FK19 FK21 BY3:BY21 FI21 FG3:FG21 CA3:CA21 FE3:FE21 FC3:FC21 CC3:CC21 FA3:FA21 EY3:EY21 CE3:CE21 EW3:EW4 EW6:EW7 EW9:EW11 EW13:EW17 EW19 EW21 EU3:EU4 EU6:EU7 EU9 EU11 EU13 EU15 EU17:EU21 CG3:CG21 ES3:ES4 ES6:ES7 ES9 EQ11 ES11 ES13 ES15 ES17 ES19:ES21 EQ3:EQ7 EQ9 EQ13 EQ15 EQ17 EQ19:EQ21 CI3:CI21 EO3:EO21 EM3:EM13 EM15 EM17 EM19:EM21 CK3:CK21 EK3:EK21 EI3:EI21 CM3:CM21 EG3:EG4 EG6:EG7 EG9 EG11:EH11 EG13 EG15 EG17 EG19:EG21 EE3:EE7 EE9:EE11 EE13 EE15:EE21 CO3:CO21 EC3:EC21 EA3:EA21 CQ3:CQ21 DY3:DY7 DY9 DY11:DY13 DY15:DY17 DY19:DY21 DW21 CS3:CS21 DU21 DS21 CU3:CU21 DQ21 DO3:DO21 CW3:CW21 DM3:DM21 DK21 CY3:CY21 DI21 DG21 DA3:DA21 DE21 DC21 KV11 KT11 KX11:LH11 KR11 KP11 KN11 LG12:LG21 KL11 KJ11 KH11 LE12:LE21 KF11 KD11 KB11 LC12:LC21 JZ11 JX11 JV11 LA12:LA21 JT11 JR11 JP11 JN11 JL11 JJ11 JH11 X11 JF11 JD11 Z11 JB11 IZ11 AB11 IX11 IV11 AD11 IT11 IR11 AF11 IP11 IN11 AH11 IL11 IJ11 AJ11 IH11 IF11 AL11 ID11 IB11 AN11 HZ11 HX11 AP11 HV11 HT11 AR11 HR11 HP11 AT11 HN11 HL11 AV11 HJ11 HH11 AX11 HF11 HD11 AZ11 HB11 GZ11 BB11 GX11 GV11 BD11 GT11 GR11 BF11 GP11 GN11 BH11 GL11 GJ11 BJ11 GH11 GF11 BL11 GD11 GB11 BN11 FZ11 FX11 BP11 FV11 FT11 BR11 FR11 FP11 BT11 BV11 BX11 FF11 FD11 BZ11 FB11 EZ11 CB11 EX11 CD11 CF11 EN11 CH11 EL11 EJ11 CJ11 CL11 EB11 CN11 DZ11 DN11 DL11 CV11 CX11 CZ11 KY3:KY10 KY12:KY21 LA3:LA10 LC3:LC10 LE3:LE10 LG3:LG10">
-    <cfRule type="containsText" dxfId="0" priority="273" operator="between" text="—">
+  <conditionalFormatting sqref="C3 C5 G5 E5 G3 E3 I3 I5 K3 M3 K5 M5 LI5 LG5 LE5 LC5 LA5 KY5 KW5 KU5 KS5 KQ5 O3 Q3 S3 U3 W3 Y3 AA3 AC3 AE3 AG3 AI3 AK3 AM3 AO3 AQ3 AS3 AU3 AW3 AY3 BA3 BC3 BE3 BG3 BI3 BK3 BM3 BO3 BQ3 BS3 BU3 BW3 BY3 CA3 CC3 CE3 CG3 CI3 CK3 CM3 CO3 CQ3 CS3 CU3 CW3 CY3 DA3 DM3 DO3 DY3 EA3 EC3 EE3 EG3 EI3 EK3 EM3 EO3 EQ3 ES3 EU3 EW3 EY3 FA3 FC3 FE3 FG3 FK3 FQ3 FS3 FU3 FW3 FY3 GA3 GC3 GE3 GG3 GI3 GK3 GM3 GO3 GQ3 GS3 GU3 GW3 GY3 HA3 HC3 HE3 HG3 HI3 HK3 HM3 HO3 HQ3 HS3 HU3 HW3 HY3 IA3 IC3 IE3 IG3 II3 IK3 IM3 IO3 IQ3 IS3 IU3 IW3 IY3 JA3 JC3 JE3 JG3 JI3 JK3 JM3 JO3 JQ3 JS3 JU3 JW3 JY3 KA3 KC3 KE3 KG3 KI3 KK3 KM3 KO3 KQ3 KS3 KU3 KW3 KY3 LA3 LC3 LE3 LG3 LI3 KO5 KM5 KK5 KI5 O5 Q5 S5 U5 W5 Y5 AA5 AC5 AE5 AG5 AI5 AK5 AM5 AO5 AQ5 AS5 AU5 AW5 AY5 BA5 BC5 BE5 BG5 BI5 BK5 BM5 BO5 BQ5 BS5 BU5 BW5 BY5 CA5 CC5 CE5 CG5 CI5 CK5 CM5 CO5 CQ5 CS5 CU5 CW5 CY5 DA5 DM5 DO5 DY5 EA5 EC5 EE5 EI5 EK5 EM5 EO5 EQ5 EY5 FA5 FC5 FE5 FG5 FK5 FQ5 FS5 FU5 FY5 GA5 GC5 GE5 GG5 GI5 GK5 GM5 GO5 GQ5 GS5 GU5 GW5 GY5 HA5 HC5 HE5 HG5 HI5 HK5 HM5 HO5 HQ5 HS5 HU5 HW5 HY5 IA5 IC5 IE5 IG5 II5 IK5 IM5 IO5 IQ5 IS5 IU5 IW5 IY5 JA5 JC5 JE5 JG5 JI5 JK5 JM5 JO5 JQ5 JS5 JU5 JW5 JY5 KA5 KC5 KE5 KG5 C8 G10 E10 G8 E8 G20 E20 G18 E18 G16 E16 G14 E14 G12 E12 C10 C12 C14 C16 C18 C20 I12 I14 I16 I18 I20 I8 I10 LI20 LG20 LE20 LC20 K8 M8 K10 M10 K12 M12 K14 M14 K16 M16 K18 M18 K20 M20 HW20 HU20 HS20 HQ20 HO20 HM20 HK20 HI20 HG20 HE20 HC20 HA20 GY20 GW20 GU20 GS20 GQ20 GO20 GM20 GK20 GI20 GG20 GE20 GC20 GA20 FY20 FW20 FU20 FS20 FQ20 FG20 FE20 FC20 FA20 EY20 EU20 ES20 EQ20 EO20 EM20 EK20 EI20 EG20 EE20 EC20 EA20 DY20 DO20 DM20 DA20 CY20 CW20 CU20 CS20 CQ20 CO20 CM20 CK20 CI20 CG20 CE20 CC20 CA20 BY20 BW20 BU20 BS20 BQ20 BO20 BM20 BK20 BI20 BG20 BE20 BC20 BA20 AY20 AW20 AU20 AS20 AQ20 AO20 AM20 AK20 AI20 AG20 AE20 AC20 AA20 Y20 W20 U20 S20 Q20 O20 HY20 IA20 JI20 JK20 LI18 LG18 LE18 LC18 LA18 KY18 KW18 KU18 KS18 KQ18 KO18 KM18 KK18 KI18 KG18 KE18 KC18 KA18 JY18 JW18 JU18 JS18 JQ18 JO18 JM18 JK18 JI18 JG18 JE18 JC18 JA18 IY18 IW18 IU18 IS18 IQ18 IO18 IM18 IK18 II18 IG18 IE18 IC18 IA18 HY18 HW18 HU18 HS18 HQ18 HO18 HM18 HK18 HI18 HG18 HE18 HC18 HA18 GY18 GW18 GU18 GS18 GQ18 GO18 GM18 GK18 GI18 GG18 GE18 GC18 GA18 FY18 FW18 FS18 FQ18 FG18 FE18 FC18 FA18 EY18 EU18 EO18 EK18 EI18 EE18 EC18 EA18 DO18 DM18 DA18 CY18 CW18 CU18 CS18 CQ18 CO18 CM18 CK18 CI18 CG18 CE18 CC18 CA18 BY18 BW18 BU18 BS18 BQ18 BO18 BM18 BK18 BI18 BG18 BE18 BC18 BA18 AY18 AW18 AU18 AS18 AQ18 AO18 AM18 AK18 AI18 AG18 AE18 AC18 AA18 Y18 W18 U18 S18 Q18 O18 IC20 IE20 JM20 JO20 LI16 LG16 LE16 LC16 LA16 KY16 KW16 KU16 KS16 KQ16 KO16 KM16 KK16 KI16 KG16 KE16 KC16 KA16 JY16 JW16 JU16 JS16 JQ16 JO16 JM16 JK16 JI16 JG16 JE16 JC16 JA16 IY16 IW16 IU16 IS16 IQ16 IO16 IM16 IK16 II16 IG16 IE16 IC16 IA16 HY16 HW16 HU16 HS16 HQ16 HO16 HM16 HK16 HI16 HG16 HE16 HC16 HA16 GY16 GW16 GU16 GS16 GQ16 GO16 GM16 GK16 GI16 GG16 GE16 GC16 GA16 FY16 FS16 FQ16 FK16 FG16 FE16 FC16 FA16 EY16 EW16 EO16 EK16 EI16 EE16 EC16 EA16 DY16 DO16 DM16 DA16 CY16 CW16 CU16 CS16 CQ16 CO16 CM16 CK16 CI16 CG16 CE16 CC16 CA16 BY16 BW16 BU16 BS16 BQ16 BO16 BM16 BK16 BI16 BG16 BE16 BC16 BA16 AY16 AW16 AU16 AS16 AQ16 AO16 AM16 AK16 AI16 AG16 AE16 AC16 AA16 Y16 W16 U16 S16 Q16 O16 IG20 II20 JQ20 JS20 LI14 LG14 LE14 LC14 LA14 KY14 KW14 KU14 KS14 KQ14 KO14 KM14 KK14 KI14 KG14 KE14 KC14 KA14 JY14 JW14 JU14 JS14 JQ14 JO14 JM14 JK14 JI14 JG14 JE14 JC14 JA14 IY14 IW14 IU14 IS14 IQ14 IO14 IM14 IK14 II14 IG14 IE14 IC14 IA14 HY14 HW14 HU14 HS14 HQ14 HO14 HM14 HK14 HI14 HG14 HE14 HC14 HA14 GY14 GW14 GU14 GS14 GQ14 GO14 GM14 GK14 GI14 GG14 GE14 GC14 GA14 FY14 FS14 FQ14 FG14 FE14 FC14 FA14 EY14 EW14 EO14 EK14 EI14 EC14 EA14 DO14 DM14 DA14 CY14 CW14 CU14 CS14 CQ14 CO14 CM14 CK14 CI14 CG14 CE14 CC14 CA14 BY14 BW14 BU14 BS14 BQ14 BO14 BM14 BK14 BI14 BG14 BE14 BC14 BA14 AY14 AW14 AU14 AS14 AQ14 AO14 AM14 AK14 AI14 AG14 AE14 AC14 AA14 Y14 W14 U14 S14 Q14 O14 IK20 IM20 JU20 JW20 LI12 LG12 LE12 LC12 LA12 KY12 KW12 KU12 KS12 KQ12 KO12 KM12 KK12 KI12 KG12 KE12 KC12 KA12 JY12 JW12 JU12 JS12 JQ12 JO12 JM12 JK12 JI12 JG12 JE12 JC12 JA12 IY12 IW12 IU12 IS12 IQ12 IO12 IM12 IK12 II12 IG12 IE12 IC12 IA12 HY12 HW12 HU12 HS12 HQ12 HO12 HM12 HK12 HI12 HG12 HE12 HC12 HA12 GY12 GW12 GU12 GS12 GQ12 GO12 GM12 GK12 GI12 GG12 GE12 GC12 GA12 FY12 FS12 FQ12 FG12 FE12 FC12 FA12 EY12 EO12 EM12 EK12 EI12 EC12 EA12 DY12 DO12 DM12 DA12 CY12 CW12 CU12 CS12 CQ12 CO12 CM12 CK12 CI12 CG12 CE12 CC12 CA12 BY12 BW12 BU12 BS12 BQ12 BO12 BM12 BK12 BI12 BG12 BE12 BC12 BA12 AY12 AW12 AU12 AS12 AQ12 AO12 AM12 AK12 AI12 AG12 AE12 AC12 AA12 Y12 W12 U12 S12 Q12 O12 IO20 IQ20 JY20 KA20 LI10 LG10 LE10 LC10 LA10 KY10 KW10 KU10 KS10 KQ10 KO10 KM10 KK10 KI10 KG10 KE10 KC10 KA10 JY10 JW10 JU10 JS10 JQ10 JO10 JM10 JK10 JI10 JG10 JE10 JC10 JA10 IY10 IW10 IU10 IS10 IQ10 IO10 IM10 IK10 II10 IG10 IE10 IC10 IA10 HY10 HW10 HU10 HS10 HQ10 HO10 HM10 HK10 HI10 HG10 HE10 HC10 HA10 GY10 GW10 GU10 GS10 GQ10 GO10 GM10 GK10 GI10 GG10 GE10 GC10 GA10 FY10 FS10 FQ10 FG10 FE10 FC10 FA10 EY10 EW10 EO10 EM10 EK10 EI10 EE10 EC10 EA10 DO10 DM10 DA10 CY10 CW10 CU10 CS10 CQ10 CO10 CM10 CK10 CI10 CG10 CE10 CC10 CA10 BY10 BW10 BU10 BS10 BQ10 BO10 BM10 BK10 BI10 BG10 BE10 BC10 BA10 AY10 AW10 AU10 AS10 AQ10 AO10 AM10 AK10 AI10 AG10 AE10 AC10 AA10 Y10 W10 U10 S10 Q10 O10 IS20 IU20 KC20 KE20 LI8 LG8 LE8 LC8 LA8 KY8 KW8 KU8 KS8 KQ8 KO8 KM8 KK8 KI8 KG8 KE8 KC8 KA8 JY8 JW8 JU8 JS8 JQ8 JO8 JM8 JK8 JI8 JG8 JE8 JC8 JA8 IY8 IW8 IU8 IS8 IQ8 IO8 IM8 IK8 II8 IG8 IE8 IC8 IA8 HY8 HW8 HU8 HS8 HQ8 HO8 HM8 HK8 HI8 HG8 HE8 HC8 HA8 GY8 GW8 GU8 GS8 GQ8 GO8 GM8 GK8 GI8 GG8 GE8 GC8 GA8 FY8 FS8 FQ8 FG8 FE8 FC8 FA8 EY8 EO8 EM8 EK8 EI8 EC8 EA8 DO8 DM8 DA8 CY8 CW8 CU8 CS8 CQ8 CO8 CM8 CK8 CI8 CG8 CE8 CC8 CA8 BY8 BW8 BU8 BS8 BQ8 BO8 BM8 BK8 BI8 BG8 BE8 BC8 BA8 AY8 AW8 AU8 AS8 AQ8 AO8 AM8 AK8 AI8 AG8 AE8 AC8 AA8 Y8 W8 U8 S8 Q8 O8 IW20 IY20 KG20 KI20 LA20 KY20 KW20 KU20 KS20 KQ20 KO20 JG20 JE20 KM20 KK20 JC20 JA20">
+    <cfRule type="containsBlanks" dxfId="1" priority="299">
+      <formula>LEN(TRIM(C3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3:C21 E3:E21 KW3:KW21 LI3:LI21 KU3:KU21 KS3:KS21 G3:G21 KQ3:KQ21 KO3:KO21 KM3:KM21 I3:I21 KK3:KK21 KI3:KI21 KG3:KG21 K3:K21 KE3:KE21 KC3:KC21 KA3:KA21 M3:M21 JY3:JY21 JW3:JW21 JU3:JU21 O3:O21 JS3:JS21 Q3:Q21 JQ3:JQ21 S3:S21 JO3:JO21 U3:U21 JM3:JM21 W3:W21 JK3:JK21 Y3:Y21 JI3:JI21 JG3:JG21 AA3:AA21 JE3:JE21 JC3:JC21 AC3:AC21 JA3:JA21 IY3:IY21 AE3:AE21 IW3:IW21 IU3:IU21 AG3:AG21 IS3:IS21 IQ3:IQ21 AI3:AI21 IO3:IO21 IM3:IM21 AK3:AK21 IK3:IK21 II3:II21 AM3:AM21 IG3:IG21 IE3:IE21 AO3:AO21 IC3:IC21 IA3:IA21 AQ3:AQ21 HY3:HY21 HW3:HW21 AS3:AS21 HU3:HU21 HS3:HS21 AU3:AU21 HQ3:HQ21 HO3:HO21 AW3:AW21 HM3:HM21 HK3:HK21 AY3:AY21 HI3:HI21 HG3:HG21 BA3:BA21 HE3:HE21 HC3:HC21 BC3:BC21 HA3:HA21 GY3:GY21 BE3:BE21 GW3:GW21 GU3:GU21 BG3:BG21 GS3:GS21 GQ3:GQ21 BI3:BI21 GO3:GO21 GM3:GM21 BK3:BK21 GK3:GK21 GI3:GI21 BM3:BM21 GG3:GG21 GE3:GE21 BO3:BO21 GC3:GC21 GA3:GA21 BQ3:BQ21 FY3:FY21 FW3:FW4 FW6:FW7 FW9 FU11 FW11:FX11 FW13 FW15 FW17:FW21 BS3:BS21 FU3:FU7 FU9 FU13 FU15 FU17 FU19:FU21 FS3:FS21 BU3:BU21 FQ3:FQ21 FO21 BW3:BW21 FM21 FK3:FK7 FK9 FK11 FK13 FK15:FK17 FK19 FK21 BY3:BY21 FI21 FG3:FG21 CA3:CA21 FE3:FE21 FC3:FC21 CC3:CC21 FA3:FA21 EY3:EY21 CE3:CE21 EW3:EW4 EW6:EW7 EW9:EW11 EW13:EW17 EW19 EW21 EU3:EU4 EU6:EU7 EU9 EU11 EU13 EU15 EU17:EU21 CG3:CG21 ES3:ES4 ES6:ES7 ES9 EQ11 ES11 ES13 ES15 ES17 ES19:ES21 EQ3:EQ7 EQ9 EQ13 EQ15 EQ17 EQ19:EQ21 CI3:CI21 EO3:EO21 EM3:EM13 EM15 EM17 EM19:EM21 CK3:CK21 EK3:EK21 EI3:EI21 CM3:CM21 EG3:EG4 EG6:EG7 EG9 EG11:EH11 EG13 EG15 EG17 EG19:EG21 EE3:EE7 EE9:EE11 EE13 EE15:EE21 CO3:CO21 EC3:EC21 EA3:EA21 CQ3:CQ21 DY3:DY7 DY9 DY11:DY13 DY15:DY17 DY19:DY21 DW21 CS3:CS21 DU21 DS21 CU3:CU21 DQ21 DO3:DO21 CW3:CW21 DM3:DM21 DK21 CY3:CY21 DI21 DG21 DA3:DA21 DE21 DC21 KV11 KT11 KX11:LH11 KR11 KP11 KN11 LG12:LG21 KL11 KJ11 KH11 LE12:LE21 KF11 KD11 KB11 LC12:LC21 JZ11 JX11 JV11 LA12:LA21 JT11 JR11 JP11 JN11 JL11 JJ11 JH11 X11 JF11 JD11 Z11 JB11 IZ11 AB11 IX11 IV11 AD11 IT11 IR11 AF11 IP11 IN11 AH11 IL11 IJ11 AJ11 IH11 IF11 AL11 ID11 IB11 AN11 HZ11 HX11 AP11 HV11 HT11 AR11 HR11 HP11 AT11 HN11 HL11 AV11 HJ11 HH11 AX11 HF11 HD11 AZ11 HB11 GZ11 BB11 GX11 GV11 BD11 GT11 GR11 BF11 GP11 GN11 BH11 GL11 GJ11 BJ11 GH11 GF11 BL11 GD11 GB11 BN11 FZ11 BP11 BR11 FR11 FP11 BT11 BV11 BX11 FF11 FD11 BZ11 FB11 EZ11 CB11 EX11 CD11 CF11 EN11 CH11 EL11 EJ11 CJ11 CL11 EB11 CN11 DZ11 DN11 DL11 CV11 CX11 CZ11 KY3:KY10 KY12:KY21 LA3:LA10 LC3:LC10 LE3:LE10 LG3:LG10">
+    <cfRule type="containsText" dxfId="0" priority="300" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",C3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C3 C5 G5 E5 G3 E3 I3 I5 K3 M3 K5 M5 LI5 LG5 LE5 LC5 LA5 KY5 KW5 KU5 KS5 KQ5 O3 Q3 S3 U3 W3 Y3 AA3 AC3 AE3 AG3 AI3 AK3 AM3 AO3 AQ3 AS3 AU3 AW3 AY3 BA3 BC3 BE3 BG3 BI3 BK3 BM3 BO3 BQ3 BS3 BU3 BW3 BY3 CA3 CC3 CE3 CG3 CI3 CK3 CM3 CO3 CQ3 CS3 CU3 CW3 CY3 DA3 DM3 DO3 DY3 EA3 EC3 EE3 EG3 EI3 EK3 EM3 EO3 EQ3 ES3 EU3 EW3 EY3 FA3 FC3 FE3 FG3 FK3 FQ3 FS3 FU3 FW3 FY3 GA3 GC3 GE3 GG3 GI3 GK3 GM3 GO3 GQ3 GS3 GU3 GW3 GY3 HA3 HC3 HE3 HG3 HI3 HK3 HM3 HO3 HQ3 HS3 HU3 HW3 HY3 IA3 IC3 IE3 IG3 II3 IK3 IM3 IO3 IQ3 IS3 IU3 IW3 IY3 JA3 JC3 JE3 JG3 JI3 JK3 JM3 JO3 JQ3 JS3 JU3 JW3 JY3 KA3 KC3 KE3 KG3 KI3 KK3 KM3 KO3 KQ3 KS3 KU3 KW3 KY3 LA3 LC3 LE3 LG3 LI3 KO5 KM5 KK5 KI5 O5 Q5 S5 U5 W5 Y5 AA5 AC5 AE5 AG5 AI5 AK5 AM5 AO5 AQ5 AS5 AU5 AW5 AY5 BA5 BC5 BE5 BG5 BI5 BK5 BM5 BO5 BQ5 BS5 BU5 BW5 BY5 CA5 CC5 CE5 CG5 CI5 CK5 CM5 CO5 CQ5 CS5 CU5 CW5 CY5 DA5 DM5 DO5 DY5 EA5 EC5 EE5 EI5 EK5 EM5 EO5 EQ5 EY5 FA5 FC5 FE5 FG5 FK5 FQ5 FS5 FU5 FW5 FY5 GA5 GC5 GE5 GG5 GI5 GK5 GM5 GO5 GQ5 GS5 GU5 GW5 GY5 HA5 HC5 HE5 HG5 HI5 HK5 HM5 HO5 HQ5 HS5 HU5 HW5 HY5 IA5 IC5 IE5 IG5 II5 IK5 IM5 IO5 IQ5 IS5 IU5 IW5 IY5 JA5 JC5 JE5 JG5 JI5 JK5 JM5 JO5 JQ5 JS5 JU5 JW5 JY5 KA5 KC5 KE5 KG5 C8 G10 E10 G8 E8 G20 E20 G18 E18 G16 E16 G14 E14 G12 E12 C10 C12 C14 C16 C18 C20 I12 I14 I16 I18 I20 I8 I10 LI20 LG20 LE20 LC20 K8 M8 K10 M10 K12 M12 K14 M14 K16 M16 K18 M18 K20 M20 HW20 HU20 HS20 HQ20 HO20 HM20 HK20 HI20 HG20 HE20 HC20 HA20 GY20 GW20 GU20 GS20 GQ20 GO20 GM20 GK20 GI20 GG20 GE20 GC20 GA20 FY20 FW20 FU20 FS20 FQ20 FG20 FE20 FC20 FA20 EY20 EU20 ES20 EQ20 EO20 EM20 EK20 EI20 EG20 EE20 EC20 EA20 DY20 DO20 DM20 DA20 CY20 CW20 CU20 CS20 CQ20 CO20 CM20 CK20 CI20 CG20 CE20 CC20 CA20 BY20 BW20 BU20 BS20 BQ20 BO20 BM20 BK20 BI20 BG20 BE20 BC20 BA20 AY20 AW20 AU20 AS20 AQ20 AO20 AM20 AK20 AI20 AG20 AE20 AC20 AA20 Y20 W20 U20 S20 Q20 O20 HY20 IA20 JI20 JK20 LI18 LG18 LE18 LC18 LA18 KY18 KW18 KU18 KS18 KQ18 KO18 KM18 KK18 KI18 KG18 KE18 KC18 KA18 JY18 JW18 JU18 JS18 JQ18 JO18 JM18 JK18 JI18 JG18 JE18 JC18 JA18 IY18 IW18 IU18 IS18 IQ18 IO18 IM18 IK18 II18 IG18 IE18 IC18 IA18 HY18 HW18 HU18 HS18 HQ18 HO18 HM18 HK18 HI18 HG18 HE18 HC18 HA18 GY18 GW18 GU18 GS18 GQ18 GO18 GM18 GK18 GI18 GG18 GE18 GC18 GA18 FY18 FW18 FU18 FS18 FQ18 FG18 FE18 FC18 FA18 EY18 EU18 EO18 EK18 EI18 EE18 EC18 EA18 DO18 DM18 DA18 CY18 CW18 CU18 CS18 CQ18 CO18 CM18 CK18 CI18 CG18 CE18 CC18 CA18 BY18 BW18 BU18 BS18 BQ18 BO18 BM18 BK18 BI18 BG18 BE18 BC18 BA18 AY18 AW18 AU18 AS18 AQ18 AO18 AM18 AK18 AI18 AG18 AE18 AC18 AA18 Y18 W18 U18 S18 Q18 O18 IC20 IE20 JM20 JO20 LI16 LG16 LE16 LC16 LA16 KY16 KW16 KU16 KS16 KQ16 KO16 KM16 KK16 KI16 KG16 KE16 KC16 KA16 JY16 JW16 JU16 JS16 JQ16 JO16 JM16 JK16 JI16 JG16 JE16 JC16 JA16 IY16 IW16 IU16 IS16 IQ16 IO16 IM16 IK16 II16 IG16 IE16 IC16 IA16 HY16 HW16 HU16 HS16 HQ16 HO16 HM16 HK16 HI16 HG16 HE16 HC16 HA16 GY16 GW16 GU16 GS16 GQ16 GO16 GM16 GK16 GI16 GG16 GE16 GC16 GA16 FY16 FW16 FU16 FS16 FQ16 FK16 FG16 FE16 FC16 FA16 EY16 EW16 EO16 EK16 EI16 EE16 EC16 EA16 DY16 DO16 DM16 DA16 CY16 CW16 CU16 CS16 CQ16 CO16 CM16 CK16 CI16 CG16 CE16 CC16 CA16 BY16 BW16 BU16 BS16 BQ16 BO16 BM16 BK16 BI16 BG16 BE16 BC16 BA16 AY16 AW16 AU16 AS16 AQ16 AO16 AM16 AK16 AI16 AG16 AE16 AC16 AA16 Y16 W16 U16 S16 Q16 O16 IG20 II20 JQ20 JS20 LI14 LG14 LE14 LC14 LA14 KY14 KW14 KU14 KS14 KQ14 KO14 KM14 KK14 KI14 KG14 KE14 KC14 KA14 JY14 JW14 JU14 JS14 JQ14 JO14 JM14 JK14 JI14 JG14 JE14 JC14 JA14 IY14 IW14 IU14 IS14 IQ14 IO14 IM14 IK14 II14 IG14 IE14 IC14 IA14 HY14 HW14 HU14 HS14 HQ14 HO14 HM14 HK14 HI14 HG14 HE14 HC14 HA14 GY14 GW14 GU14 GS14 GQ14 GO14 GM14 GK14 GI14 GG14 GE14 GC14 GA14 FY14 FW14 FU14 FS14 FQ14 FG14 FE14 FC14 FA14 EY14 EW14 EO14 EK14 EI14 EC14 EA14 DO14 DM14 DA14 CY14 CW14 CU14 CS14 CQ14 CO14 CM14 CK14 CI14 CG14 CE14 CC14 CA14 BY14 BW14 BU14 BS14 BQ14 BO14 BM14 BK14 BI14 BG14 BE14 BC14 BA14 AY14 AW14 AU14 AS14 AQ14 AO14 AM14 AK14 AI14 AG14 AE14 AC14 AA14 Y14 W14 U14 S14 Q14 O14 IK20 IM20 JU20 JW20 LI12 LG12 LE12 LC12 LA12 KY12 KW12 KU12 KS12 KQ12 KO12 KM12 KK12 KI12 KG12 KE12 KC12 KA12 JY12 JW12 JU12 JS12 JQ12 JO12 JM12 JK12 JI12 JG12 JE12 JC12 JA12 IY12 IW12 IU12 IS12 IQ12 IO12 IM12 IK12 II12 IG12 IE12 IC12 IA12 HY12 HW12 HU12 HS12 HQ12 HO12 HM12 HK12 HI12 HG12 HE12 HC12 HA12 GY12 GW12 GU12 GS12 GQ12 GO12 GM12 GK12 GI12 GG12 GE12 GC12 GA12 FY12 FW12 FU12 FS12 FQ12 FG12 FE12 FC12 FA12 EY12 EO12 EM12 EK12 EI12 EC12 EA12 DY12 DO12 DM12 DA12 CY12 CW12 CU12 CS12 CQ12 CO12 CM12 CK12 CI12 CG12 CE12 CC12 CA12 BY12 BW12 BU12 BS12 BQ12 BO12 BM12 BK12 BI12 BG12 BE12 BC12 BA12 AY12 AW12 AU12 AS12 AQ12 AO12 AM12 AK12 AI12 AG12 AE12 AC12 AA12 Y12 W12 U12 S12 Q12 O12 IO20 IQ20 JY20 KA20 LI10 LG10 LE10 LC10 LA10 KY10 KW10 KU10 KS10 KQ10 KO10 KM10 KK10 KI10 KG10 KE10 KC10 KA10 JY10 JW10 JU10 JS10 JQ10 JO10 JM10 JK10 JI10 JG10 JE10 JC10 JA10 IY10 IW10 IU10 IS10 IQ10 IO10 IM10 IK10 II10 IG10 IE10 IC10 IA10 HY10 HW10 HU10 HS10 HQ10 HO10 HM10 HK10 HI10 HG10 HE10 HC10 HA10 GY10 GW10 GU10 GS10 GQ10 GO10 GM10 GK10 GI10 GG10 GE10 GC10 GA10 FY10 FW10 FU10 FS10 FQ10 FG10 FE10 FC10 FA10 EY10 EW10 EO10 EM10 EK10 EI10 EE10 EC10 EA10 DO10 DM10 DA10 CY10 CW10 CU10 CS10 CQ10 CO10 CM10 CK10 CI10 CG10 CE10 CC10 CA10 BY10 BW10 BU10 BS10 BQ10 BO10 BM10 BK10 BI10 BG10 BE10 BC10 BA10 AY10 AW10 AU10 AS10 AQ10 AO10 AM10 AK10 AI10 AG10 AE10 AC10 AA10 Y10 W10 U10 S10 Q10 O10 IS20 IU20 KC20 KE20 LI8 LG8 LE8 LC8 LA8 KY8 KW8 KU8 KS8 KQ8 KO8 KM8 KK8 KI8 KG8 KE8 KC8 KA8 JY8 JW8 JU8 JS8 JQ8 JO8 JM8 JK8 JI8 JG8 JE8 JC8 JA8 IY8 IW8 IU8 IS8 IQ8 IO8 IM8 IK8 II8 IG8 IE8 IC8 IA8 HY8 HW8 HU8 HS8 HQ8 HO8 HM8 HK8 HI8 HG8 HE8 HC8 HA8 GY8 GW8 GU8 GS8 GQ8 GO8 GM8 GK8 GI8 GG8 GE8 GC8 GA8 FY8 FW8 FU8 FS8 FQ8 FG8 FE8 FC8 FA8 EY8 EO8 EM8 EK8 EI8 EC8 EA8 DO8 DM8 DA8 CY8 CW8 CU8 CS8 CQ8 CO8 CM8 CK8 CI8 CG8 CE8 CC8 CA8 BY8 BW8 BU8 BS8 BQ8 BO8 BM8 BK8 BI8 BG8 BE8 BC8 BA8 AY8 AW8 AU8 AS8 AQ8 AO8 AM8 AK8 AI8 AG8 AE8 AC8 AA8 Y8 W8 U8 S8 Q8 O8 IW20 IY20 KG20 KI20 LA20 KY20 KW20 KU20 KS20 KQ20 KO20 JG20 JE20 KM20 KK20 JC20 JA20">
-    <cfRule type="containsBlanks" dxfId="1" priority="272">
-      <formula>LEN(TRIM(C3))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DB3:DB20 DD3:DD20 DF3:DF20 DH3:DH20 DJ3:DJ20 DC11 DE11 DG11 DI11 DK11">
-    <cfRule type="containsText" dxfId="2" priority="267" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="294" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",DB3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC3:DC7 DC9:DC11 DC13 DC15:DC19 DE3:DE4 DE6:DE7 DE9 DD11:DF11 DE13 DE15 DE17 DE19:DE20 DG3:DG4 DG6:DG7 DG9:DG11 DG13:DG15 DG17 DG19 DI3:DI7 DI9 DH11:DJ11 DI13 DI15 DI17 DI19 DK3:DK7 DK9 DK11:DK13 DK15 DK17 DK19">
-    <cfRule type="containsText" dxfId="0" priority="266" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="293" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DC3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC3 DE3 DG3 DI3 DK3 DC5 DI5 DK5 DE20 DC18 DC16 DG14 DK12 DG10 DC10">
-    <cfRule type="containsBlanks" dxfId="1" priority="265">
+    <cfRule type="containsBlanks" dxfId="1" priority="292">
       <formula>LEN(TRIM(DC3))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DP3:DP20 DR3:DR20 DT3:DT20 DV3:DV20 DQ11 DS11 DU11 DW11">
-    <cfRule type="containsText" dxfId="2" priority="264" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="291" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",DP3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ3 DS3 DU3 DW3 DQ5 DS5 DW5 DW20 DS20 DQ20 DW18 DU18 DS18 DQ16 DU14 DU10">
-    <cfRule type="containsBlanks" dxfId="1" priority="262">
+    <cfRule type="containsBlanks" dxfId="1" priority="289">
       <formula>LEN(TRIM(DQ3))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ3:DQ7 DQ9 DQ11:DT11 DQ13 DQ15:DQ17 DQ19:DQ20 DS3:DS7 DS9 DS13 DS15 DS17:DS20 DU3:DU4 DU6:DU7 DU9:DU11 DU13:DU15 DU17:DU19 DW3:DW7 DW9 DV11:DW11 DW13 DW15 DW17:DW20">
-    <cfRule type="containsText" dxfId="0" priority="263" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="290" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FH3:FH20 FJ3:FJ20">
-    <cfRule type="containsText" dxfId="2" priority="69" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="96" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",FH3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FI3:FI4 FI6:FI7 FI9 FI11 FI13 FI15 FI17:FI20">
-    <cfRule type="containsText" dxfId="0" priority="55" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="82" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FI3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FI3 FI20 FI18">
-    <cfRule type="containsBlanks" dxfId="1" priority="54">
+    <cfRule type="containsBlanks" dxfId="1" priority="81">
       <formula>LEN(TRIM(FI3))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FL3:FL20 FN3:FN20 FM11 FO11">
-    <cfRule type="containsText" dxfId="2" priority="29" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="56" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",FL3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FM3:FM7 FM9 FL11:FN11 FM13 FM15 FM17 FM19 FO3:FO7 FO9 FO11:FO13 FO15 FO17 FO19">
-    <cfRule type="containsText" dxfId="0" priority="28" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="55" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FL3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FM3 FO3 FM5 FO5 FO12">
-    <cfRule type="containsBlanks" dxfId="1" priority="27">
+    <cfRule type="containsBlanks" dxfId="1" priority="54">
       <formula>LEN(TRIM(FM3))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FH11 FJ11">
-    <cfRule type="containsText" dxfId="0" priority="68" operator="between" text="—">
+    <cfRule type="containsText" dxfId="0" priority="95" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FH11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22 JO22 JM22 JK22 JI22 JG22 JE22 JC22 JA22 IY22 IW22 IU22 IS22 IQ22 IO22 IM22 IK22 II22 IG22 IE22 IC22 IA22 HY22 HW22 HU22 HS22 HQ22 HO22 HM22 HK22 HI22 HG22 HE22 HC22 HA22 GY22 GW22 GU22 GS22 GQ22 GO22 GM22 GK22 GI22 GG22 GE22 GC22 GA22 FY22 FW22 FU22 FS22 FQ22 FO22 FM22 FK22 FI22 FG22 FE22 FC22 FA22 EY22 EW22 EU22 ES22 EQ22 EO22 EM22 EK22 EI22 EG22 EE22 EC22 EA22 DY22 DW22 DU22 DS22 DQ22 DO22 DM22 DK22 DI22 DG22 DE22 DC22 DA22 CY22 CW22 CU22 CS22 CQ22 CO22 CM22 CK22 CI22 CG22 CE22 CC22 CA22 BY22 BW22 BU22 BS22 BQ22 BO22 BM22 BK22 BI22 BG22 BE22 BC22 BA22 AY22 AW22 AU22 AS22 AQ22 AO22 AM22 AK22 AI22 AG22 AE22 AC22 AA22 Y22 W22 U22 S22 Q22 O22 M22 K22 I22 G22 E22">
-    <cfRule type="containsBlanks" dxfId="3" priority="270">
+    <cfRule type="containsBlanks" dxfId="3" priority="297">
       <formula>LEN(TRIM(C22))=0</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="271" operator="between" text="—">
+    <cfRule type="containsText" dxfId="2" priority="298" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",C22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FW5 FU8 FW8 FU9 FW9 FU10 FW10 FU11 FW11 FU12 FW12 FU13 FW13 FU14 FW14 FU15 FW15 FU16 FW16 FU17 FU18 C3:C21 E3:E21 G3:G21 I3:I21 K3:K21 M3:M21 O3:O21 Q3:Q21 S3:S21 U3:U21 W3:W21 Y3:Y21 AA3:AA21 AC3:AC21 AE3:AE21 AG3:AG21 AI3:AI21 AK3:AK21 AM3:AM21 AO3:AO21 AQ3:AQ21 AS3:AS21 AU3:AU21 AW3:AW21 AY3:AY21 BA3:BA21 BC3:BC21 BE3:BE21 BG3:BG21 BI3:BI21 BK3:BK21 BM3:BM21 BO3:BO21 BQ3:BQ21 BS3:BS21 BU3:BU21 BW3:BW21 BY3:BY21 CA3:CA21 CC3:CC21 CE3:CE21 CG3:CG21 CI3:CI21 CK3:CK21 CM3:CM21 CO3:CO21 CQ3:CQ21 CS3:CS21 CU3:CU21 CW3:CW21 CY3:CY21 DA3:DA21 DC3:DC21 DE3:DE21 DG3:DG21 DI3:DI21 DK3:DK21 DM3:DM21 DO3:DO21 DQ3:DQ21 DS3:DS21 DU3:DU21 DW3:DW21 DY3:DY21 EA3:EA21 EC3:EC21 EE3:EE21 EG3:EG21 EI3:EI21 EK3:EK21 EM3:EM21 EO3:EO21 EQ3:EQ21 ES3:ES21 EU3:EU21 EW3:EW21 EY3:EY21 FA3:FA21 FC3:FC21 FE3:FE21 FG3:FG21 FI3:FI21 FK3:FK21 FM3:FM21 FO3:FO21 FQ3:FQ21 FS3:FS21 FU3:FU7 FU19:FU21 FW3:FW4 FW6:FW7 FW17:FW21 FY3:FY21 GA3:GA21 GC3:GC21 GE3:GE21 GG3:GG21 GI3:GI21 GK3:GK21 GM3:GM21 GO3:GO21 GQ3:GQ21 GS3:GS21 GU3:GU21 GW3:GW21 GY3:GY21 HA3:HA21 HC3:HC21 HE3:HE21 HG3:HG21 HI3:HI21 HK3:HK21 HM3:HM21 HO3:HO21 HQ3:HQ21 HS3:HS21 HU3:HU21 HW3:HW21 HY3:HY21 IA3:IA21 IC3:IC21 IE3:IE21 IG3:IG21 II3:II21 IK3:IK21 IM3:IM21 IO3:IO21 IQ3:IQ21 IS3:IS21 IU3:IU21 IW3:IW21 IY3:IY21 JA3:JA21 JC3:JC21 JE3:JE21 JG3:JG21 JI3:JI21 JK3:JK21 JM3:JM21 JO3:JO21">
+      <formula1>数据!$B$1:$B$62</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FT21 FV21 B3:B21 D3:D21 F3:F21 H3:H21 J3:J21 L3:L21 N3:N21 P3:P21 R3:R21 T3:T21 V3:V21 X3:X21 Z3:Z21 AB3:AB21 AD3:AD21 AF3:AF21 AH3:AH21 AJ3:AJ21 AL3:AL21 AN3:AN21 AP3:AP21 AR3:AR21 AT3:AT21 AV3:AV21 AX3:AX21 AZ3:AZ21 BB3:BB21 BD3:BD21 BF3:BF21 BH3:BH21 BJ3:BJ21 BL3:BL21 BN3:BN21 BP3:BP21 BR3:BR21 BT3:BT21 BV3:BV21 BX3:BX21 BZ3:BZ21 CB3:CB21 CD3:CD21 CF3:CF21 CH3:CH21 CJ3:CJ21 CL3:CL21 CN3:CN21 CP3:CP21 CR3:CR21 CT3:CT21 CV3:CV21 CX3:CX21 CZ3:CZ21 DB3:DB21 DD3:DD21 DF3:DF21 DH3:DH21 DJ3:DJ21 DL3:DL21 DN3:DN21 DP3:DP21 DR3:DR21 DT3:DT21 DV3:DV21 DX3:DX21 DZ3:DZ21 EB3:EB21 ED3:ED21 EF3:EF21 EH3:EH21 EJ3:EJ21 EL3:EL21 EN3:EN21 EP3:EP21 ER3:ER21 ET3:ET21 EV3:EV21 EX3:EX21 EZ3:EZ21 FB3:FB21 FD3:FD21 FF3:FF21 FH3:FH21 FJ3:FJ21 FL3:FL21 FN3:FN21 FP3:FP21 FR3:FR21 FT3:FT20 FV3:FV20 FX3:FX21 FZ3:FZ21 GB3:GB21 GD3:GD21 GF3:GF21 GH3:GH21 GJ3:GJ21 GL3:GL21 GN3:GN21 GP3:GP21 GR3:GR21 GT3:GT21 GV3:GV21 GX3:GX21 GZ3:GZ21 HB3:HB21 HD3:HD21 HF3:HF21 HH3:HH21 HJ3:HJ21 HL3:HL21 HN3:HN21 HP3:HP21 HR3:HR21 HT3:HT21 HV3:HV21 HX3:HX21 HZ3:HZ21 IB3:IB21 ID3:ID21 IF3:IF21 IH3:IH21 IJ3:IJ21 IL3:IL21 IN3:IN21 IP3:IP21 IR3:IR21 IT3:IT21 IV3:IV21 IX3:IX21 IZ3:IZ21 JB3:JB21 JD3:JD21 JF3:JF21 JH3:JH21 JJ3:JJ21 JL3:JL21 JN3:JN21">
+      <formula1>数据!$A$1:$A$88</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C22 E22 G22 I22 K22 M22 O22 Q22 S22 U22 W22 Y22 AA22 AC22 AE22 AG22 AI22 AK22 AM22 AO22 AQ22 AS22 AU22 AW22 AY22 BA22 BC22 BE22 BG22 BI22 BK22 BM22 BO22 BQ22 BS22 BU22 BW22 BY22 CA22 CC22 CE22 CG22 CI22 CK22 CM22 CO22 CQ22 CS22 CU22 CW22 CY22 DA22 DC22 DE22 DG22 DI22 DK22 DM22 DO22 DQ22 DS22 DU22 DW22 DY22 EA22 EC22 EE22 EG22 EI22 EK22 EM22 EO22 EQ22 ES22 EU22 EW22 EY22 FA22 FC22 FE22 FG22 FI22 FK22 FM22 FO22 FQ22 FS22 FU22 FW22 FY22 GA22 GC22 GE22 GG22 GI22 GK22 GM22 GO22 GQ22 GS22 GU22 GW22 GY22 HA22 HC22 HE22 HG22 HI22 HK22 HM22 HO22 HQ22 HS22 HU22 HW22 HY22 IA22 IC22 IE22 IG22 II22 IK22 IM22 IO22 IQ22 IS22 IU22 IW22 IY22 JA22 JC22 JE22 JG22 JI22 JK22 JM22 JO22">
       <formula1>数据!$C$1:$C$25</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B21 D3:D21 F3:F21 H3:H21 J3:J21 L3:L21 N3:N21 P3:P21 R3:R21 T3:T21 V3:V21 X3:X21 Z3:Z21 AB3:AB21 AD3:AD21 AF3:AF21 AH3:AH21 AJ3:AJ21 AL3:AL21 AN3:AN21 AP3:AP21 AR3:AR21 AT3:AT21 AV3:AV21 AX3:AX21 AZ3:AZ21 BB3:BB21 BD3:BD21 BF3:BF21 BH3:BH21 BJ3:BJ21 BL3:BL21 BN3:BN21 BP3:BP21 BR3:BR21 BT3:BT21 BV3:BV21 BX3:BX21 BZ3:BZ21 CB3:CB21 CD3:CD21 CF3:CF21 CH3:CH21 CJ3:CJ21 CL3:CL21 CN3:CN21 CP3:CP21 CR3:CR21 CT3:CT21 CV3:CV21 CX3:CX21 CZ3:CZ21 DB3:DB21 DD3:DD21 DF3:DF21 DH3:DH21 DJ3:DJ21 DL3:DL21 DN3:DN21 DP3:DP21 DR3:DR21 DT3:DT21 DV3:DV21 DX3:DX21 DZ3:DZ21 EB3:EB21 ED3:ED21 EF3:EF21 EH3:EH21 EJ3:EJ21 EL3:EL21 EN3:EN21 EP3:EP21 ER3:ER21 ET3:ET21 EV3:EV21 EX3:EX21 EZ3:EZ21 FB3:FB21 FD3:FD21 FF3:FF21 FH3:FH21 FJ3:FJ21 FL3:FL21 FN3:FN21 FP3:FP21 FR3:FR21 FT3:FT21 FV3:FV21 FX3:FX21 FZ3:FZ21 GB3:GB21 GD3:GD21 GF3:GF21 GH3:GH21 GJ3:GJ21 GL3:GL21 GN3:GN21 GP3:GP21 GR3:GR21 GT3:GT21 GV3:GV21 GX3:GX21 GZ3:GZ21 HB3:HB21 HD3:HD21 HF3:HF21 HH3:HH21 HJ3:HJ21 HL3:HL21 HN3:HN21 HP3:HP21 HR3:HR21 HT3:HT21 HV3:HV21 HX3:HX21 HZ3:HZ21 IB3:IB21 ID3:ID21 IF3:IF21 IH3:IH21 IJ3:IJ21 IL3:IL21 IN3:IN21 IP3:IP21 IR3:IR21 IT3:IT21 IV3:IV21 IX3:IX21 IZ3:IZ21 JB3:JB21 JD3:JD21 JF3:JF21 JH3:JH21 JJ3:JJ21 JL3:JL21 JN3:JN21">
-      <formula1>数据!$A$1:$A$88</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C21 E3:E21 G3:G21 I3:I21 K3:K21 M3:M21 O3:O21 Q3:Q21 S3:S21 U3:U21 W3:W21 Y3:Y21 AA3:AA21 AC3:AC21 AE3:AE21 AG3:AG21 AI3:AI21 AK3:AK21 AM3:AM21 AO3:AO21 AQ3:AQ21 AS3:AS21 AU3:AU21 AW3:AW21 AY3:AY21 BA3:BA21 BC3:BC21 BE3:BE21 BG3:BG21 BI3:BI21 BK3:BK21 BM3:BM21 BO3:BO21 BQ3:BQ21 BS3:BS21 BU3:BU21 BW3:BW21 BY3:BY21 CA3:CA21 CC3:CC21 CE3:CE21 CG3:CG21 CI3:CI21 CK3:CK21 CM3:CM21 CO3:CO21 CQ3:CQ21 CS3:CS21 CU3:CU21 CW3:CW21 CY3:CY21 DA3:DA21 DC3:DC21 DE3:DE21 DG3:DG21 DI3:DI21 DK3:DK21 DM3:DM21 DO3:DO21 DQ3:DQ21 DS3:DS21 DU3:DU21 DW3:DW21 DY3:DY21 EA3:EA21 EC3:EC21 EE3:EE21 EG3:EG21 EI3:EI21 EK3:EK21 EM3:EM21 EO3:EO21 EQ3:EQ21 ES3:ES21 EU3:EU21 EW3:EW21 EY3:EY21 FA3:FA21 FC3:FC21 FE3:FE21 FG3:FG21 FI3:FI21 FK3:FK21 FM3:FM21 FO3:FO21 FQ3:FQ21 FS3:FS21 FU3:FU21 FW3:FW21 FY3:FY21 GA3:GA21 GC3:GC21 GE3:GE21 GG3:GG21 GI3:GI21 GK3:GK21 GM3:GM21 GO3:GO21 GQ3:GQ21 GS3:GS21 GU3:GU21 GW3:GW21 GY3:GY21 HA3:HA21 HC3:HC21 HE3:HE21 HG3:HG21 HI3:HI21 HK3:HK21 HM3:HM21 HO3:HO21 HQ3:HQ21 HS3:HS21 HU3:HU21 HW3:HW21 HY3:HY21 IA3:IA21 IC3:IC21 IE3:IE21 IG3:IG21 II3:II21 IK3:IK21 IM3:IM21 IO3:IO21 IQ3:IQ21 IS3:IS21 IU3:IU21 IW3:IW21 IY3:IY21 JA3:JA21 JC3:JC21 JE3:JE21 JG3:JG21 JI3:JI21 JK3:JK21 JM3:JM21 JO3:JO21">
-      <formula1>数据!$B$1:$B$62</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16479,7 +16661,7 @@
   <sheetData>
     <row r="1" s="2" customFormat="1" customHeight="1" spans="1:16">
       <c r="A1" s="5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -16518,15 +16700,15 @@
     </row>
     <row r="3" customHeight="1" spans="1:9">
       <c r="A3" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="13"/>
       <c r="D3" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F3" s="15"/>
       <c r="G3" s="15"/>
@@ -16536,163 +16718,163 @@
     <row r="4" customHeight="1" spans="1:9">
       <c r="A4" s="17"/>
       <c r="B4" s="18" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:9">
       <c r="A5" s="17"/>
       <c r="B5" s="18" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:9">
       <c r="A6" s="17"/>
       <c r="B6" s="18" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:9">
       <c r="A7" s="17"/>
       <c r="B7" s="18" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:9">
       <c r="A8" s="17"/>
       <c r="B8" s="18" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:9">
       <c r="A9" s="17"/>
       <c r="B9" s="18" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:9">
@@ -16700,7 +16882,7 @@
       <c r="B10" s="20"/>
       <c r="C10" s="21"/>
       <c r="D10" s="22" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="24"/>
@@ -16710,15 +16892,15 @@
     </row>
     <row r="11" customHeight="1" spans="1:9">
       <c r="A11" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="13"/>
       <c r="D11" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
@@ -16728,163 +16910,163 @@
     <row r="12" customHeight="1" spans="1:9">
       <c r="A12" s="17"/>
       <c r="B12" s="18" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:9">
       <c r="A13" s="17"/>
       <c r="B13" s="18" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D13" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>342</v>
       </c>
-      <c r="E13" s="14" t="s">
-        <v>341</v>
-      </c>
       <c r="F13" s="15" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:9">
       <c r="A14" s="17"/>
       <c r="B14" s="18" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:9">
       <c r="A15" s="17"/>
       <c r="B15" s="18" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F15" s="15" t="s">
+        <v>361</v>
+      </c>
+      <c r="G15" s="15" t="s">
         <v>360</v>
       </c>
-      <c r="G15" s="15" t="s">
-        <v>359</v>
-      </c>
       <c r="H15" s="16" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:9">
       <c r="A16" s="17"/>
       <c r="B16" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="C16" s="18" t="s">
         <v>372</v>
       </c>
-      <c r="C16" s="18" t="s">
-        <v>371</v>
-      </c>
       <c r="D16" s="14" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="I16" s="30" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:9">
       <c r="A17" s="17"/>
       <c r="B17" s="18" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:9">
@@ -16892,7 +17074,7 @@
       <c r="B18" s="20"/>
       <c r="C18" s="21"/>
       <c r="D18" s="22" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E18" s="23"/>
       <c r="F18" s="24"/>
@@ -16902,16 +17084,16 @@
     </row>
     <row r="19" customHeight="1" spans="1:9">
       <c r="A19" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B19" s="12"/>
       <c r="C19" s="13"/>
       <c r="D19" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E19" s="14"/>
       <c r="F19" s="25" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G19" s="25"/>
       <c r="H19" s="26"/>
@@ -16920,163 +17102,163 @@
     <row r="20" customHeight="1" spans="1:9">
       <c r="A20" s="17"/>
       <c r="B20" s="27" t="s">
+        <v>395</v>
+      </c>
+      <c r="C20" s="28" t="s">
         <v>394</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="D20" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>345</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>390</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>391</v>
+      </c>
+      <c r="H20" s="16" t="s">
         <v>393</v>
       </c>
-      <c r="D20" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>389</v>
-      </c>
-      <c r="G20" s="15" t="s">
-        <v>390</v>
-      </c>
-      <c r="H20" s="16" t="s">
+      <c r="I20" s="16" t="s">
         <v>392</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:9">
       <c r="A21" s="17"/>
       <c r="B21" s="18" t="s">
+        <v>344</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>342</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>400</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>398</v>
+      </c>
+      <c r="I21" s="16" t="s">
         <v>343</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>341</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>395</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>396</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>398</v>
-      </c>
-      <c r="G21" s="15" t="s">
-        <v>399</v>
-      </c>
-      <c r="H21" s="16" t="s">
-        <v>397</v>
-      </c>
-      <c r="I21" s="16" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:9">
       <c r="A22" s="17"/>
       <c r="B22" s="18" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:9">
       <c r="A23" s="17"/>
       <c r="B23" s="18" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C23" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="E23" s="14" t="s">
         <v>406</v>
       </c>
-      <c r="D23" s="14" t="s">
-        <v>402</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>405</v>
-      </c>
       <c r="F23" s="15" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="I23" s="16" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:9">
       <c r="A24" s="17"/>
       <c r="B24" s="18" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="I24" s="30" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:9">
       <c r="A25" s="17"/>
       <c r="B25" s="18" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E25" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>365</v>
+      </c>
+      <c r="G25" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="H25" s="16" t="s">
         <v>380</v>
       </c>
-      <c r="F25" s="15" t="s">
-        <v>364</v>
-      </c>
-      <c r="G25" s="15" t="s">
-        <v>407</v>
-      </c>
-      <c r="H25" s="16" t="s">
-        <v>379</v>
-      </c>
       <c r="I25" s="16" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:9">
@@ -17084,7 +17266,7 @@
       <c r="B26" s="20"/>
       <c r="C26" s="21"/>
       <c r="D26" s="22" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E26" s="23"/>
       <c r="F26" s="24"/>
@@ -17292,7 +17474,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B16">
         <v>3.75</v>
@@ -17303,7 +17485,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B17">
         <v>4</v>
@@ -17314,7 +17496,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B18">
         <v>4.25</v>
@@ -17325,7 +17507,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B19">
         <v>4.5</v>
@@ -17336,7 +17518,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B20">
         <v>4.75</v>
@@ -17347,7 +17529,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B21">
         <v>5</v>
@@ -17358,7 +17540,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B22">
         <v>5.25</v>
@@ -17369,7 +17551,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B23">
         <v>5.5</v>
@@ -17380,7 +17562,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B24">
         <v>5.75</v>
@@ -17391,7 +17573,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B25">
         <v>6</v>
@@ -17434,7 +17616,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B30">
         <v>7.25</v>
@@ -17442,7 +17624,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B31">
         <v>7.5</v>
@@ -17450,7 +17632,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B32">
         <v>7.75</v>
@@ -17458,7 +17640,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B33">
         <v>8</v>
@@ -17466,7 +17648,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B34">
         <v>8.25</v>
@@ -17474,7 +17656,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B35">
         <v>8.5</v>
@@ -17482,7 +17664,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B36">
         <v>8.75</v>
@@ -17490,7 +17672,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B37">
         <v>9</v>
@@ -17498,7 +17680,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B38">
         <v>9.25</v>
@@ -17506,7 +17688,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B39">
         <v>9.5</v>
@@ -17514,7 +17696,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B40">
         <v>9.75</v>
@@ -17522,7 +17704,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B41">
         <v>10</v>
@@ -17530,7 +17712,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B42">
         <v>11</v>
@@ -17538,7 +17720,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B43">
         <v>12</v>
@@ -17546,7 +17728,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B44">
         <v>13</v>
@@ -17554,7 +17736,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B45">
         <v>14</v>
@@ -17562,7 +17744,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B46">
         <v>15</v>
@@ -17570,7 +17752,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B47">
         <v>16</v>
@@ -17578,7 +17760,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B48">
         <v>17</v>
@@ -17586,7 +17768,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B49">
         <v>18</v>
@@ -17594,7 +17776,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B50">
         <v>19</v>
@@ -17602,7 +17784,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B51">
         <v>20</v>
@@ -17610,7 +17792,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B52">
         <v>21</v>
@@ -17618,7 +17800,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B53">
         <v>22</v>
@@ -17626,7 +17808,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B54">
         <v>23</v>
@@ -17634,7 +17816,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B55">
         <v>24</v>
@@ -17642,7 +17824,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B56">
         <v>25</v>
@@ -17650,7 +17832,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B57">
         <v>26</v>
@@ -17658,7 +17840,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B58">
         <v>27</v>
@@ -17666,7 +17848,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B59">
         <v>28</v>
@@ -17674,7 +17856,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B60">
         <v>29</v>
@@ -17682,7 +17864,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B61">
         <v>30</v>
@@ -17690,7 +17872,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B62" t="s">
         <v>5</v>
@@ -17698,117 +17880,117 @@
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="86" spans="1:1">
@@ -17818,7 +18000,7 @@
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -19634,7 +19816,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" ht="28" spans="1:5">
       <c r="A27" s="83"/>
       <c r="B27" s="84"/>
       <c r="C27" s="85"/>
@@ -19742,7 +19924,7 @@
       <c r="C36" s="93"/>
       <c r="D36" s="94"/>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:5">
       <c r="A37" s="69" t="s">
         <v>6</v>
       </c>
@@ -19751,19 +19933,22 @@
       </c>
       <c r="C37" s="93"/>
       <c r="D37" s="94"/>
+      <c r="E37" s="73" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="80" t="s">
         <v>21</v>
       </c>
       <c r="B38" s="81" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C38" s="82" t="s">
         <v>221</v>
       </c>
       <c r="D38" s="72" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -19771,14 +19956,14 @@
       <c r="B39" s="84"/>
       <c r="C39" s="86"/>
       <c r="D39" s="72" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="83"/>
       <c r="B40" s="84"/>
       <c r="C40" s="87" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D40" s="88"/>
     </row>
@@ -19798,7 +19983,7 @@
         <v>280</v>
       </c>
       <c r="C42" s="87" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D42" s="88"/>
     </row>
@@ -19809,7 +19994,7 @@
         <v>221</v>
       </c>
       <c r="D43" s="72" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -19823,7 +20008,7 @@
     <row r="45" spans="1:4">
       <c r="A45" s="91"/>
       <c r="B45" s="92" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C45" s="93"/>
       <c r="D45" s="94"/>
@@ -19833,13 +20018,13 @@
         <v>11</v>
       </c>
       <c r="B46" s="81" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C46" s="82" t="s">
         <v>221</v>
       </c>
       <c r="D46" s="72" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -19847,7 +20032,7 @@
       <c r="B47" s="84"/>
       <c r="C47" s="85"/>
       <c r="D47" s="72" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -20008,7 +20193,7 @@
         <v>120</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -20031,7 +20216,7 @@
         <v>127</v>
       </c>
       <c r="C6" s="66" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -20054,7 +20239,7 @@
         <v>133</v>
       </c>
       <c r="B10" s="67" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -20077,7 +20262,7 @@
         <v>140</v>
       </c>
       <c r="B14" s="67" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="15" spans="1:1">
@@ -20095,7 +20280,7 @@
         <v>144</v>
       </c>
       <c r="C17" s="66" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -20113,7 +20298,7 @@
         <v>147</v>
       </c>
       <c r="B20" s="67" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="21" ht="280" spans="1:3">
@@ -20121,10 +20306,10 @@
         <v>148</v>
       </c>
       <c r="B21" s="52" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -20137,7 +20322,7 @@
         <v>151</v>
       </c>
       <c r="B23" s="67" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="24" ht="70" spans="1:3">
@@ -20145,10 +20330,10 @@
         <v>152</v>
       </c>
       <c r="B24" s="67" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C24" s="66" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="25" spans="1:1">
@@ -20166,10 +20351,10 @@
         <v>158</v>
       </c>
       <c r="B27" s="52" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C27" s="66" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="28" ht="409" customHeight="1" spans="1:3">
@@ -20177,10 +20362,10 @@
         <v>160</v>
       </c>
       <c r="B28" s="52" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C28" s="66" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="29" spans="1:1">
@@ -20193,7 +20378,7 @@
         <v>163</v>
       </c>
       <c r="C30" s="66" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="31" spans="1:1">
@@ -20226,15 +20411,15 @@
         <v>173</v>
       </c>
       <c r="B36" s="67" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="37" ht="56" spans="1:3">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="37" ht="112" spans="1:3">
       <c r="A37" s="59" t="s">
         <v>175</v>
       </c>
       <c r="C37" s="66" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -20247,7 +20432,7 @@
         <v>179</v>
       </c>
       <c r="C39" s="66" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -20255,15 +20440,15 @@
         <v>181</v>
       </c>
       <c r="B40" s="67" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="41" ht="112" spans="1:3">
       <c r="A41" s="59" t="s">
         <v>183</v>
       </c>
-      <c r="C41" s="53" t="s">
-        <v>311</v>
+      <c r="C41" s="66" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -20276,7 +20461,7 @@
         <v>186</v>
       </c>
       <c r="B43" s="67" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="44" spans="1:1">
@@ -20289,7 +20474,7 @@
         <v>189</v>
       </c>
       <c r="B45" s="52" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="46" spans="1:1">
@@ -20317,7 +20502,7 @@
         <v>197</v>
       </c>
       <c r="C50" s="66" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -20330,7 +20515,7 @@
         <v>200</v>
       </c>
       <c r="B52" s="52" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -20360,7 +20545,7 @@
   <sheetData>
     <row r="1" s="31" customFormat="1" spans="1:8">
       <c r="A1" s="35" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B1" s="36"/>
       <c r="C1" s="31" t="s">
@@ -20384,10 +20569,10 @@
     </row>
     <row r="2" s="32" customFormat="1" spans="1:4">
       <c r="A2" s="37" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C2" s="39" t="s">
         <v>120</v>
@@ -20397,7 +20582,7 @@
     <row r="3" s="32" customFormat="1" spans="1:4">
       <c r="A3" s="41"/>
       <c r="B3" s="38" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C3" s="39" t="s">
         <v>136</v>
@@ -20415,7 +20600,7 @@
     <row r="5" s="32" customFormat="1" spans="1:4">
       <c r="A5" s="41"/>
       <c r="B5" s="38" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C5" s="39" t="s">
         <v>140</v>
@@ -20425,7 +20610,7 @@
     <row r="6" s="32" customFormat="1" spans="1:4">
       <c r="A6" s="41"/>
       <c r="B6" s="38" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C6" s="42" t="s">
         <v>128</v>
@@ -20447,7 +20632,7 @@
     <row r="8" s="32" customFormat="1" spans="1:4">
       <c r="A8" s="41"/>
       <c r="B8" s="38" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C8" s="42" t="s">
         <v>126</v>
@@ -20459,7 +20644,7 @@
     <row r="9" s="32" customFormat="1" spans="1:4">
       <c r="A9" s="41"/>
       <c r="B9" s="38" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C9" s="39" t="s">
         <v>131</v>
@@ -20469,7 +20654,7 @@
     <row r="10" s="32" customFormat="1" spans="1:4">
       <c r="A10" s="41"/>
       <c r="B10" s="38" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C10" s="39" t="s">
         <v>143</v>
@@ -20479,7 +20664,7 @@
     <row r="11" s="32" customFormat="1" spans="1:4">
       <c r="A11" s="43"/>
       <c r="B11" s="38" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C11" s="39" t="s">
         <v>165</v>
@@ -20488,10 +20673,10 @@
     </row>
     <row r="12" s="33" customFormat="1" spans="1:4">
       <c r="A12" s="44" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C12" s="46" t="s">
         <v>183</v>
@@ -20509,17 +20694,17 @@
     <row r="14" s="33" customFormat="1" spans="1:4">
       <c r="A14" s="48"/>
       <c r="B14" s="45" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C14" s="46" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D14" s="47"/>
     </row>
     <row r="15" s="33" customFormat="1" spans="1:4">
       <c r="A15" s="48"/>
       <c r="B15" s="45" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C15" s="46" t="s">
         <v>122</v>
@@ -20537,7 +20722,7 @@
     <row r="17" s="33" customFormat="1" spans="1:4">
       <c r="A17" s="48"/>
       <c r="B17" s="45" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C17" s="46" t="s">
         <v>135</v>
@@ -20547,7 +20732,7 @@
     <row r="18" s="33" customFormat="1" spans="1:4">
       <c r="A18" s="48"/>
       <c r="B18" s="45" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C18" s="46" t="s">
         <v>147</v>
@@ -20557,7 +20742,7 @@
     <row r="19" s="33" customFormat="1" spans="1:4">
       <c r="A19" s="48"/>
       <c r="B19" s="45" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C19" s="46" t="s">
         <v>179</v>
@@ -20567,7 +20752,7 @@
     <row r="20" s="33" customFormat="1" spans="1:4">
       <c r="A20" s="49"/>
       <c r="B20" s="45" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C20" s="46" t="s">
         <v>181</v>

--- a/c/9班资料.xlsx
+++ b/c/9班资料.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480" activeTab="7"/>
+    <workbookView windowWidth="20750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="七下拖课" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1681" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1731" uniqueCount="485">
   <si>
     <t>拖课统计表</t>
   </si>
@@ -571,6 +571,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
       <t>装备哥、睿zhuo</t>
     </r>
     <r>
@@ -1529,6 +1534,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
       <t>有人说，陈睿卓每天吃得都很补，整天中午吃海参、小米粥。</t>
     </r>
     <r>
@@ -1586,6 +1596,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
       <t>一段时间内，洪鑫洋很喜欢读《孙权劝学》和《木兰诗》，于是大家读的时候就开始把人物替换成“鑫洋”，如：</t>
     </r>
     <r>
@@ -4069,10 +4084,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF4F81BD"/>
+      <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -4080,14 +4095,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
-      <color rgb="FFC0504D"/>
+      <color rgb="FF4F81BD"/>
       <name val="黑体"/>
       <charset val="134"/>
     </font>
@@ -4096,6 +4105,12 @@
       <name val="黑体"/>
       <charset val="134"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFC0504D"/>
+      <name val="黑体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="61">
@@ -5502,14 +5517,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFE3F2D9"/>
+          <bgColor rgb="FFF2F2F2"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFF2F2F2"/>
+          <bgColor rgb="FFE3F2D9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7372,17 +7387,29 @@
         <v>3</v>
       </c>
       <c r="FV3" s="158" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="FW3" s="159">
         <v>2.25</v>
       </c>
-      <c r="FX3" s="158"/>
-      <c r="FY3" s="159"/>
-      <c r="FZ3" s="158"/>
-      <c r="GA3" s="159"/>
-      <c r="GB3" s="158"/>
-      <c r="GC3" s="159"/>
+      <c r="FX3" s="158" t="s">
+        <v>1</v>
+      </c>
+      <c r="FY3" s="159">
+        <v>7</v>
+      </c>
+      <c r="FZ3" s="158" t="s">
+        <v>2</v>
+      </c>
+      <c r="GA3" s="159" t="s">
+        <v>3</v>
+      </c>
+      <c r="GB3" s="158" t="s">
+        <v>1</v>
+      </c>
+      <c r="GC3" s="159" t="s">
+        <v>3</v>
+      </c>
       <c r="GD3" s="158"/>
       <c r="GE3" s="159"/>
       <c r="GF3" s="158"/>
@@ -8161,12 +8188,24 @@
       <c r="FW5" s="165" t="s">
         <v>3</v>
       </c>
-      <c r="FX5" s="164"/>
-      <c r="FY5" s="165"/>
-      <c r="FZ5" s="164"/>
-      <c r="GA5" s="165"/>
-      <c r="GB5" s="164"/>
-      <c r="GC5" s="165"/>
+      <c r="FX5" s="164" t="s">
+        <v>2</v>
+      </c>
+      <c r="FY5" s="165" t="s">
+        <v>3</v>
+      </c>
+      <c r="FZ5" s="164" t="s">
+        <v>1</v>
+      </c>
+      <c r="GA5" s="165" t="s">
+        <v>3</v>
+      </c>
+      <c r="GB5" s="164" t="s">
+        <v>2</v>
+      </c>
+      <c r="GC5" s="165">
+        <v>3</v>
+      </c>
       <c r="GD5" s="164"/>
       <c r="GE5" s="165"/>
       <c r="GF5" s="164"/>
@@ -8729,10 +8768,18 @@
       <c r="FU7" s="168"/>
       <c r="FV7" s="167"/>
       <c r="FW7" s="168"/>
-      <c r="FX7" s="167"/>
-      <c r="FY7" s="168"/>
-      <c r="FZ7" s="167"/>
-      <c r="GA7" s="168"/>
+      <c r="FX7" s="167" t="s">
+        <v>2</v>
+      </c>
+      <c r="FY7" s="168">
+        <v>1.25</v>
+      </c>
+      <c r="FZ7" s="167" t="s">
+        <v>2</v>
+      </c>
+      <c r="GA7" s="168">
+        <v>1.5</v>
+      </c>
       <c r="GB7" s="167"/>
       <c r="GC7" s="168"/>
       <c r="GD7" s="167"/>
@@ -9236,12 +9283,24 @@
       <c r="FW8" s="165" t="s">
         <v>3</v>
       </c>
-      <c r="FX8" s="169"/>
-      <c r="FY8" s="165"/>
-      <c r="FZ8" s="169"/>
-      <c r="GA8" s="165"/>
-      <c r="GB8" s="169"/>
-      <c r="GC8" s="165"/>
+      <c r="FX8" s="169" t="s">
+        <v>10</v>
+      </c>
+      <c r="FY8" s="165" t="s">
+        <v>3</v>
+      </c>
+      <c r="FZ8" s="169" t="s">
+        <v>11</v>
+      </c>
+      <c r="GA8" s="165" t="s">
+        <v>3</v>
+      </c>
+      <c r="GB8" s="169" t="s">
+        <v>12</v>
+      </c>
+      <c r="GC8" s="165" t="s">
+        <v>3</v>
+      </c>
       <c r="GD8" s="169"/>
       <c r="GE8" s="165"/>
       <c r="GF8" s="169"/>
@@ -10024,12 +10083,24 @@
       <c r="FW10" s="165" t="s">
         <v>3</v>
       </c>
-      <c r="FX10" s="164"/>
-      <c r="FY10" s="165"/>
-      <c r="FZ10" s="164"/>
-      <c r="GA10" s="165"/>
-      <c r="GB10" s="164"/>
-      <c r="GC10" s="165"/>
+      <c r="FX10" s="164" t="s">
+        <v>4</v>
+      </c>
+      <c r="FY10" s="165">
+        <v>3</v>
+      </c>
+      <c r="FZ10" s="164" t="s">
+        <v>9</v>
+      </c>
+      <c r="GA10" s="165" t="s">
+        <v>3</v>
+      </c>
+      <c r="GB10" s="164" t="s">
+        <v>6</v>
+      </c>
+      <c r="GC10" s="165" t="s">
+        <v>3</v>
+      </c>
       <c r="GD10" s="164"/>
       <c r="GE10" s="165"/>
       <c r="GF10" s="164"/>
@@ -10808,12 +10879,24 @@
       <c r="FW12" s="165" t="s">
         <v>3</v>
       </c>
-      <c r="FX12" s="164"/>
-      <c r="FY12" s="165"/>
-      <c r="FZ12" s="164"/>
-      <c r="GA12" s="165"/>
-      <c r="GB12" s="164"/>
-      <c r="GC12" s="165"/>
+      <c r="FX12" s="164" t="s">
+        <v>9</v>
+      </c>
+      <c r="FY12" s="165" t="s">
+        <v>3</v>
+      </c>
+      <c r="FZ12" s="164" t="s">
+        <v>2</v>
+      </c>
+      <c r="GA12" s="165" t="s">
+        <v>3</v>
+      </c>
+      <c r="GB12" s="164" t="s">
+        <v>2</v>
+      </c>
+      <c r="GC12" s="165">
+        <v>14</v>
+      </c>
       <c r="GD12" s="164"/>
       <c r="GE12" s="165"/>
       <c r="GF12" s="164"/>
@@ -11594,12 +11677,24 @@
       <c r="FW14" s="165" t="s">
         <v>3</v>
       </c>
-      <c r="FX14" s="164"/>
-      <c r="FY14" s="165"/>
-      <c r="FZ14" s="164"/>
-      <c r="GA14" s="165"/>
-      <c r="GB14" s="164"/>
-      <c r="GC14" s="165"/>
+      <c r="FX14" s="164" t="s">
+        <v>1</v>
+      </c>
+      <c r="FY14" s="165" t="s">
+        <v>3</v>
+      </c>
+      <c r="FZ14" s="164" t="s">
+        <v>4</v>
+      </c>
+      <c r="GA14" s="165" t="s">
+        <v>3</v>
+      </c>
+      <c r="GB14" s="164" t="s">
+        <v>14</v>
+      </c>
+      <c r="GC14" s="165" t="s">
+        <v>3</v>
+      </c>
       <c r="GD14" s="164"/>
       <c r="GE14" s="165"/>
       <c r="GF14" s="164"/>
@@ -11875,8 +11970,12 @@
       <c r="FU15" s="162"/>
       <c r="FV15" s="161"/>
       <c r="FW15" s="162"/>
-      <c r="FX15" s="161"/>
-      <c r="FY15" s="162"/>
+      <c r="FX15" s="161" t="s">
+        <v>2</v>
+      </c>
+      <c r="FY15" s="162">
+        <v>4.75</v>
+      </c>
       <c r="FZ15" s="161"/>
       <c r="GA15" s="162"/>
       <c r="GB15" s="161"/>
@@ -12382,12 +12481,24 @@
       <c r="FW16" s="165" t="s">
         <v>3</v>
       </c>
-      <c r="FX16" s="164"/>
-      <c r="FY16" s="165"/>
-      <c r="FZ16" s="164"/>
-      <c r="GA16" s="165"/>
-      <c r="GB16" s="164"/>
-      <c r="GC16" s="165"/>
+      <c r="FX16" s="164" t="s">
+        <v>21</v>
+      </c>
+      <c r="FY16" s="165">
+        <v>4</v>
+      </c>
+      <c r="FZ16" s="164" t="s">
+        <v>4</v>
+      </c>
+      <c r="GA16" s="165" t="s">
+        <v>3</v>
+      </c>
+      <c r="GB16" s="164" t="s">
+        <v>21</v>
+      </c>
+      <c r="GC16" s="165">
+        <v>4.75</v>
+      </c>
       <c r="GD16" s="164"/>
       <c r="GE16" s="165"/>
       <c r="GF16" s="164"/>
@@ -13162,12 +13273,24 @@
       <c r="FW18" s="165">
         <v>7</v>
       </c>
-      <c r="FX18" s="164"/>
-      <c r="FY18" s="165"/>
-      <c r="FZ18" s="164"/>
-      <c r="GA18" s="165"/>
-      <c r="GB18" s="164"/>
-      <c r="GC18" s="165"/>
+      <c r="FX18" s="164" t="s">
+        <v>1</v>
+      </c>
+      <c r="FY18" s="165">
+        <v>1</v>
+      </c>
+      <c r="FZ18" s="164" t="s">
+        <v>17</v>
+      </c>
+      <c r="GA18" s="165" t="s">
+        <v>3</v>
+      </c>
+      <c r="GB18" s="164" t="s">
+        <v>4</v>
+      </c>
+      <c r="GC18" s="165" t="s">
+        <v>3</v>
+      </c>
       <c r="GD18" s="164"/>
       <c r="GE18" s="165"/>
       <c r="GF18" s="164"/>
@@ -13908,12 +14031,24 @@
       <c r="FW20" s="165">
         <v>3.25</v>
       </c>
-      <c r="FX20" s="164"/>
-      <c r="FY20" s="165"/>
-      <c r="FZ20" s="164"/>
-      <c r="GA20" s="165"/>
-      <c r="GB20" s="164"/>
-      <c r="GC20" s="165"/>
+      <c r="FX20" s="164" t="s">
+        <v>4</v>
+      </c>
+      <c r="FY20" s="165" t="s">
+        <v>3</v>
+      </c>
+      <c r="FZ20" s="164" t="s">
+        <v>23</v>
+      </c>
+      <c r="GA20" s="165" t="s">
+        <v>3</v>
+      </c>
+      <c r="GB20" s="164" t="s">
+        <v>2</v>
+      </c>
+      <c r="GC20" s="165">
+        <v>18</v>
+      </c>
       <c r="GD20" s="164"/>
       <c r="GE20" s="165"/>
       <c r="GF20" s="164"/>
@@ -14199,8 +14334,12 @@
       <c r="FW21" s="172"/>
       <c r="FX21" s="171"/>
       <c r="FY21" s="172"/>
-      <c r="FZ21" s="171"/>
-      <c r="GA21" s="172"/>
+      <c r="FZ21" s="171" t="s">
+        <v>2</v>
+      </c>
+      <c r="GA21" s="172">
+        <v>25</v>
+      </c>
       <c r="GB21" s="171"/>
       <c r="GC21" s="172"/>
       <c r="GD21" s="171"/>
@@ -14689,15 +14828,21 @@
       <c r="FX22" s="174" t="s">
         <v>25</v>
       </c>
-      <c r="FY22" s="175"/>
+      <c r="FY22" s="175">
+        <v>7</v>
+      </c>
       <c r="FZ22" s="174" t="s">
         <v>25</v>
       </c>
-      <c r="GA22" s="175"/>
+      <c r="GA22" s="175">
+        <v>8</v>
+      </c>
       <c r="GB22" s="174" t="s">
         <v>25</v>
       </c>
-      <c r="GC22" s="175"/>
+      <c r="GC22" s="175">
+        <v>8</v>
+      </c>
       <c r="GD22" s="174" t="s">
         <v>25</v>
       </c>
@@ -15438,1203 +15583,1395 @@
     <mergeCell ref="JL23:JM23"/>
     <mergeCell ref="JN23:JO23"/>
   </mergeCells>
+  <conditionalFormatting sqref="GA3">
+    <cfRule type="containsBlanks" dxfId="0" priority="49">
+      <formula>LEN(TRIM(GA3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="DE5">
-    <cfRule type="containsText" dxfId="0" priority="268" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="336" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="267">
+    <cfRule type="containsBlanks" dxfId="0" priority="335">
       <formula>LEN(TRIM(DE5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG5">
-    <cfRule type="containsText" dxfId="0" priority="266" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="334" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="265">
+    <cfRule type="containsBlanks" dxfId="0" priority="333">
       <formula>LEN(TRIM(DG5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DU5">
-    <cfRule type="containsText" dxfId="0" priority="206" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="274" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DU5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="205">
+    <cfRule type="containsBlanks" dxfId="0" priority="273">
       <formula>LEN(TRIM(DU5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG5">
-    <cfRule type="containsText" dxfId="0" priority="169" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="237" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="168">
+    <cfRule type="containsBlanks" dxfId="0" priority="236">
       <formula>LEN(TRIM(EG5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ES5">
-    <cfRule type="containsText" dxfId="0" priority="137" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="205" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",ES5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="136">
+    <cfRule type="containsBlanks" dxfId="0" priority="204">
       <formula>LEN(TRIM(ES5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EU5">
-    <cfRule type="containsText" dxfId="0" priority="119" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="187" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EU5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="118">
+    <cfRule type="containsBlanks" dxfId="0" priority="186">
       <formula>LEN(TRIM(EU5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EW5">
-    <cfRule type="containsText" dxfId="0" priority="106" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="174" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EW5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="105">
+    <cfRule type="containsBlanks" dxfId="0" priority="173">
       <formula>LEN(TRIM(EW5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FI5">
-    <cfRule type="containsText" dxfId="0" priority="80" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="148" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FI5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="79">
+    <cfRule type="containsBlanks" dxfId="0" priority="147">
       <formula>LEN(TRIM(FI5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FW5">
-    <cfRule type="containsText" dxfId="0" priority="25" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="93" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FW5)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="24">
+    <cfRule type="containsBlanks" dxfId="0" priority="92">
       <formula>LEN(TRIM(FW5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FY5">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FY5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(FY5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GA5">
+    <cfRule type="containsText" dxfId="1" priority="32" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GA5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="31">
+      <formula>LEN(TRIM(GA5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC8">
-    <cfRule type="containsText" dxfId="0" priority="288" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="356" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DC8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="287">
+    <cfRule type="containsBlanks" dxfId="0" priority="355">
       <formula>LEN(TRIM(DC8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DE8">
-    <cfRule type="containsText" dxfId="0" priority="270" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="338" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="269">
+    <cfRule type="containsBlanks" dxfId="0" priority="337">
       <formula>LEN(TRIM(DE8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG8">
-    <cfRule type="containsText" dxfId="0" priority="264" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="332" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="263">
+    <cfRule type="containsBlanks" dxfId="0" priority="331">
       <formula>LEN(TRIM(DG8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI8">
-    <cfRule type="containsText" dxfId="0" priority="242" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="310" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="241">
+    <cfRule type="containsBlanks" dxfId="0" priority="309">
       <formula>LEN(TRIM(DI8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK8">
-    <cfRule type="containsText" dxfId="0" priority="240" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="308" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="239">
+    <cfRule type="containsBlanks" dxfId="0" priority="307">
       <formula>LEN(TRIM(DK8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ8">
-    <cfRule type="containsText" dxfId="0" priority="192" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="260" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="191">
+    <cfRule type="containsBlanks" dxfId="0" priority="259">
       <formula>LEN(TRIM(DQ8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DS8">
-    <cfRule type="containsText" dxfId="0" priority="204" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="272" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DS8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="203">
+    <cfRule type="containsBlanks" dxfId="0" priority="271">
       <formula>LEN(TRIM(DS8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DU8">
-    <cfRule type="containsText" dxfId="0" priority="208" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="276" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DU8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="207">
+    <cfRule type="containsBlanks" dxfId="0" priority="275">
       <formula>LEN(TRIM(DU8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DW8">
-    <cfRule type="containsText" dxfId="0" priority="228" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="296" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DW8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="227">
+    <cfRule type="containsBlanks" dxfId="0" priority="295">
       <formula>LEN(TRIM(DW8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DY8">
-    <cfRule type="containsText" dxfId="0" priority="186" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="254" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DY8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="185">
+    <cfRule type="containsBlanks" dxfId="0" priority="253">
       <formula>LEN(TRIM(DY8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EE8">
-    <cfRule type="containsText" dxfId="0" priority="175" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="243" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EE8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="174">
+    <cfRule type="containsBlanks" dxfId="0" priority="242">
       <formula>LEN(TRIM(EE8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG8">
-    <cfRule type="containsText" dxfId="0" priority="167" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="235" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="166">
+    <cfRule type="containsBlanks" dxfId="0" priority="234">
       <formula>LEN(TRIM(EG8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EQ8">
-    <cfRule type="containsText" dxfId="0" priority="149" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="217" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EQ8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="148">
+    <cfRule type="containsBlanks" dxfId="0" priority="216">
       <formula>LEN(TRIM(EQ8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ES8">
-    <cfRule type="containsText" dxfId="0" priority="135" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="203" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",ES8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="134">
+    <cfRule type="containsBlanks" dxfId="0" priority="202">
       <formula>LEN(TRIM(ES8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EU8">
-    <cfRule type="containsText" dxfId="0" priority="117" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="185" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EU8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="116">
+    <cfRule type="containsBlanks" dxfId="0" priority="184">
       <formula>LEN(TRIM(EU8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EW8">
-    <cfRule type="containsText" dxfId="0" priority="104" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="172" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EW8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="103">
+    <cfRule type="containsBlanks" dxfId="0" priority="171">
       <formula>LEN(TRIM(EW8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FI8">
-    <cfRule type="containsText" dxfId="0" priority="78" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="146" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FI8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="77">
+    <cfRule type="containsBlanks" dxfId="0" priority="145">
       <formula>LEN(TRIM(FI8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FK8">
-    <cfRule type="containsText" dxfId="0" priority="58" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="126" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FK8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="57">
+    <cfRule type="containsBlanks" dxfId="0" priority="125">
       <formula>LEN(TRIM(FK8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FM8">
-    <cfRule type="containsText" dxfId="0" priority="41" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="109" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FM8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="40">
+    <cfRule type="containsBlanks" dxfId="0" priority="108">
       <formula>LEN(TRIM(FM8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FO8">
-    <cfRule type="containsText" dxfId="0" priority="39" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="107" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FO8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="38">
+    <cfRule type="containsBlanks" dxfId="0" priority="106">
       <formula>LEN(TRIM(FO8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FU8">
-    <cfRule type="containsText" dxfId="0" priority="27" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="95" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FU8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="26">
+    <cfRule type="containsBlanks" dxfId="0" priority="94">
       <formula>LEN(TRIM(FU8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FW8">
-    <cfRule type="containsText" dxfId="0" priority="23" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="91" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FW8)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="22">
+    <cfRule type="containsBlanks" dxfId="0" priority="90">
       <formula>LEN(TRIM(FW8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FY8">
+    <cfRule type="containsText" dxfId="1" priority="4" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FY8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="3">
+      <formula>LEN(TRIM(FY8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GA8">
+    <cfRule type="containsText" dxfId="1" priority="34" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GA8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="33">
+      <formula>LEN(TRIM(GA8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GC8">
+    <cfRule type="containsText" dxfId="1" priority="30" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GC8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="29">
+      <formula>LEN(TRIM(GC8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DE10">
-    <cfRule type="containsText" dxfId="0" priority="272" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="340" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="271">
+    <cfRule type="containsBlanks" dxfId="0" priority="339">
       <formula>LEN(TRIM(DE10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI10">
-    <cfRule type="containsText" dxfId="0" priority="244" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="312" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="243">
+    <cfRule type="containsBlanks" dxfId="0" priority="311">
       <formula>LEN(TRIM(DI10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK10">
-    <cfRule type="containsText" dxfId="0" priority="238" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="306" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="237">
+    <cfRule type="containsBlanks" dxfId="0" priority="305">
       <formula>LEN(TRIM(DK10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ10">
-    <cfRule type="containsText" dxfId="0" priority="194" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="262" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="193">
+    <cfRule type="containsBlanks" dxfId="0" priority="261">
       <formula>LEN(TRIM(DQ10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DS10">
-    <cfRule type="containsText" dxfId="0" priority="202" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="270" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DS10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="201">
+    <cfRule type="containsBlanks" dxfId="0" priority="269">
       <formula>LEN(TRIM(DS10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DW10">
-    <cfRule type="containsText" dxfId="0" priority="226" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="294" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DW10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="225">
+    <cfRule type="containsBlanks" dxfId="0" priority="293">
       <formula>LEN(TRIM(DW10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DY10">
-    <cfRule type="containsText" dxfId="0" priority="184" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="252" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DY10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="183">
+    <cfRule type="containsBlanks" dxfId="0" priority="251">
       <formula>LEN(TRIM(DY10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG10">
-    <cfRule type="containsText" dxfId="0" priority="165" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="233" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="164">
+    <cfRule type="containsBlanks" dxfId="0" priority="232">
       <formula>LEN(TRIM(EG10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EQ10">
-    <cfRule type="containsText" dxfId="0" priority="147" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="215" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EQ10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="146">
+    <cfRule type="containsBlanks" dxfId="0" priority="214">
       <formula>LEN(TRIM(EQ10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ES10">
-    <cfRule type="containsText" dxfId="0" priority="133" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="201" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",ES10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="132">
+    <cfRule type="containsBlanks" dxfId="0" priority="200">
       <formula>LEN(TRIM(ES10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EU10">
-    <cfRule type="containsText" dxfId="0" priority="115" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="183" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EU10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="114">
+    <cfRule type="containsBlanks" dxfId="0" priority="182">
       <formula>LEN(TRIM(EU10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FI10">
-    <cfRule type="containsText" dxfId="0" priority="76" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="144" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FI10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="75">
+    <cfRule type="containsBlanks" dxfId="0" priority="143">
       <formula>LEN(TRIM(FI10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FK10">
-    <cfRule type="containsText" dxfId="0" priority="60" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="128" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FK10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="59">
+    <cfRule type="containsBlanks" dxfId="0" priority="127">
       <formula>LEN(TRIM(FK10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FM10">
-    <cfRule type="containsText" dxfId="0" priority="43" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="111" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FM10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="42">
+    <cfRule type="containsBlanks" dxfId="0" priority="110">
       <formula>LEN(TRIM(FM10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FO10">
-    <cfRule type="containsText" dxfId="0" priority="37" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="105" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FO10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="36">
+    <cfRule type="containsBlanks" dxfId="0" priority="104">
       <formula>LEN(TRIM(FO10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FU10">
-    <cfRule type="containsText" dxfId="0" priority="13" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="81" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FU10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="12">
+    <cfRule type="containsBlanks" dxfId="0" priority="80">
       <formula>LEN(TRIM(FU10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FW10">
-    <cfRule type="containsText" dxfId="0" priority="21" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="89" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FW10)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="20">
+    <cfRule type="containsBlanks" dxfId="0" priority="88">
       <formula>LEN(TRIM(FW10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FY10">
+    <cfRule type="containsText" dxfId="1" priority="55" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FY10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="54">
+      <formula>LEN(TRIM(FY10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GA10">
+    <cfRule type="containsText" dxfId="1" priority="14" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GA10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="13">
+      <formula>LEN(TRIM(GA10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GC10">
+    <cfRule type="containsText" dxfId="1" priority="28" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GC10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="27">
+      <formula>LEN(TRIM(GC10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CR11">
-    <cfRule type="containsText" dxfId="0" priority="296" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="364" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",CR11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CT11">
-    <cfRule type="containsText" dxfId="0" priority="295" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="363" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",CT11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DX11">
-    <cfRule type="containsText" dxfId="0" priority="187" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="255" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DX11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EF11">
-    <cfRule type="containsText" dxfId="0" priority="176" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="244" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EF11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ET11">
-    <cfRule type="containsText" dxfId="0" priority="120" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="188" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",ET11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EV11">
-    <cfRule type="containsText" dxfId="0" priority="107" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="175" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EV11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FI11">
-    <cfRule type="containsText" dxfId="2" priority="83" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="151" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",FI11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FV11">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="69" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FV11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FX11">
+    <cfRule type="containsText" dxfId="1" priority="64" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FX11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FY11">
+    <cfRule type="containsText" dxfId="2" priority="68" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",FY11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC12">
-    <cfRule type="containsText" dxfId="0" priority="286" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="354" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DC12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="285">
+    <cfRule type="containsBlanks" dxfId="0" priority="353">
       <formula>LEN(TRIM(DC12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DE12">
-    <cfRule type="containsText" dxfId="0" priority="274" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="342" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="273">
+    <cfRule type="containsBlanks" dxfId="0" priority="341">
       <formula>LEN(TRIM(DE12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG12">
-    <cfRule type="containsText" dxfId="0" priority="262" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="330" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="261">
+    <cfRule type="containsBlanks" dxfId="0" priority="329">
       <formula>LEN(TRIM(DG12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI12">
-    <cfRule type="containsText" dxfId="0" priority="246" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="314" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="245">
+    <cfRule type="containsBlanks" dxfId="0" priority="313">
       <formula>LEN(TRIM(DI12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ12">
-    <cfRule type="containsText" dxfId="0" priority="198" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="266" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="197">
+    <cfRule type="containsBlanks" dxfId="0" priority="265">
       <formula>LEN(TRIM(DQ12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DS12">
-    <cfRule type="containsText" dxfId="0" priority="200" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="268" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DS12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="199">
+    <cfRule type="containsBlanks" dxfId="0" priority="267">
       <formula>LEN(TRIM(DS12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DU12">
-    <cfRule type="containsText" dxfId="0" priority="210" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="278" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DU12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="209">
+    <cfRule type="containsBlanks" dxfId="0" priority="277">
       <formula>LEN(TRIM(DU12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DW12">
-    <cfRule type="containsText" dxfId="0" priority="224" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="292" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DW12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="223">
+    <cfRule type="containsBlanks" dxfId="0" priority="291">
       <formula>LEN(TRIM(DW12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EE12">
-    <cfRule type="containsText" dxfId="0" priority="173" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="241" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EE12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="172">
+    <cfRule type="containsBlanks" dxfId="0" priority="240">
       <formula>LEN(TRIM(EE12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG12">
-    <cfRule type="containsText" dxfId="0" priority="163" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="231" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="162">
+    <cfRule type="containsBlanks" dxfId="0" priority="230">
       <formula>LEN(TRIM(EG12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EQ12">
-    <cfRule type="containsText" dxfId="0" priority="145" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="213" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EQ12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="144">
+    <cfRule type="containsBlanks" dxfId="0" priority="212">
       <formula>LEN(TRIM(EQ12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ES12">
-    <cfRule type="containsText" dxfId="0" priority="131" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="199" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",ES12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="130">
+    <cfRule type="containsBlanks" dxfId="0" priority="198">
       <formula>LEN(TRIM(ES12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EU12">
-    <cfRule type="containsText" dxfId="0" priority="113" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="181" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EU12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="112">
+    <cfRule type="containsBlanks" dxfId="0" priority="180">
       <formula>LEN(TRIM(EU12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EW12">
-    <cfRule type="containsText" dxfId="0" priority="102" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="170" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EW12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="101">
+    <cfRule type="containsBlanks" dxfId="0" priority="169">
       <formula>LEN(TRIM(EW12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FI12">
-    <cfRule type="containsText" dxfId="0" priority="74" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="142" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FI12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="73">
+    <cfRule type="containsBlanks" dxfId="0" priority="141">
       <formula>LEN(TRIM(FI12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FK12">
-    <cfRule type="containsText" dxfId="0" priority="62" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="130" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FK12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="61">
+    <cfRule type="containsBlanks" dxfId="0" priority="129">
       <formula>LEN(TRIM(FK12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FM12">
-    <cfRule type="containsText" dxfId="0" priority="45" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="113" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FM12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="44">
+    <cfRule type="containsBlanks" dxfId="0" priority="112">
       <formula>LEN(TRIM(FM12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FU12">
-    <cfRule type="containsText" dxfId="0" priority="11" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="79" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FU12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="10">
+    <cfRule type="containsBlanks" dxfId="0" priority="78">
       <formula>LEN(TRIM(FU12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FW12">
-    <cfRule type="containsText" dxfId="0" priority="19" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="87" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FW12)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="18">
+    <cfRule type="containsBlanks" dxfId="0" priority="86">
       <formula>LEN(TRIM(FW12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FY12">
+    <cfRule type="containsText" dxfId="1" priority="10" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FY12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="9">
+      <formula>LEN(TRIM(FY12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GA12">
+    <cfRule type="containsText" dxfId="1" priority="12" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GA12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="11">
+      <formula>LEN(TRIM(GA12))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC14">
-    <cfRule type="containsText" dxfId="0" priority="284" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="352" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DC14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="283">
+    <cfRule type="containsBlanks" dxfId="0" priority="351">
       <formula>LEN(TRIM(DC14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DE14">
-    <cfRule type="containsText" dxfId="0" priority="276" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="344" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="275">
+    <cfRule type="containsBlanks" dxfId="0" priority="343">
       <formula>LEN(TRIM(DE14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI14">
-    <cfRule type="containsText" dxfId="0" priority="248" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="316" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="247">
+    <cfRule type="containsBlanks" dxfId="0" priority="315">
       <formula>LEN(TRIM(DI14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK14">
-    <cfRule type="containsText" dxfId="0" priority="236" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="304" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="235">
+    <cfRule type="containsBlanks" dxfId="0" priority="303">
       <formula>LEN(TRIM(DK14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ14">
-    <cfRule type="containsText" dxfId="0" priority="196" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="264" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="195">
+    <cfRule type="containsBlanks" dxfId="0" priority="263">
       <formula>LEN(TRIM(DQ14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DS14">
-    <cfRule type="containsText" dxfId="0" priority="212" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="280" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DS14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="211">
+    <cfRule type="containsBlanks" dxfId="0" priority="279">
       <formula>LEN(TRIM(DS14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DW14">
-    <cfRule type="containsText" dxfId="0" priority="222" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="290" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DW14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="221">
+    <cfRule type="containsBlanks" dxfId="0" priority="289">
       <formula>LEN(TRIM(DW14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DY14">
-    <cfRule type="containsText" dxfId="0" priority="182" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="250" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DY14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="181">
+    <cfRule type="containsBlanks" dxfId="0" priority="249">
       <formula>LEN(TRIM(DY14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EE14">
-    <cfRule type="containsText" dxfId="0" priority="171" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="239" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EE14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="170">
+    <cfRule type="containsBlanks" dxfId="0" priority="238">
       <formula>LEN(TRIM(EE14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG14">
-    <cfRule type="containsText" dxfId="0" priority="161" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="229" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="160">
+    <cfRule type="containsBlanks" dxfId="0" priority="228">
       <formula>LEN(TRIM(EG14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EM14">
-    <cfRule type="containsText" dxfId="0" priority="155" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="223" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EM14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="154">
+    <cfRule type="containsBlanks" dxfId="0" priority="222">
       <formula>LEN(TRIM(EM14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EQ14">
-    <cfRule type="containsText" dxfId="0" priority="143" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="211" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EQ14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="142">
+    <cfRule type="containsBlanks" dxfId="0" priority="210">
       <formula>LEN(TRIM(EQ14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ES14">
-    <cfRule type="containsText" dxfId="0" priority="129" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="197" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",ES14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="128">
+    <cfRule type="containsBlanks" dxfId="0" priority="196">
       <formula>LEN(TRIM(ES14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EU14">
-    <cfRule type="containsText" dxfId="0" priority="111" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="179" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EU14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="110">
+    <cfRule type="containsBlanks" dxfId="0" priority="178">
       <formula>LEN(TRIM(EU14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FI14">
-    <cfRule type="containsText" dxfId="0" priority="72" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="140" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FI14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="71">
+    <cfRule type="containsBlanks" dxfId="0" priority="139">
       <formula>LEN(TRIM(FI14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FK14">
-    <cfRule type="containsText" dxfId="0" priority="64" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="132" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FK14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="63">
+    <cfRule type="containsBlanks" dxfId="0" priority="131">
       <formula>LEN(TRIM(FK14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FM14">
-    <cfRule type="containsText" dxfId="0" priority="47" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="115" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FM14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="46">
+    <cfRule type="containsBlanks" dxfId="0" priority="114">
       <formula>LEN(TRIM(FM14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FO14">
-    <cfRule type="containsText" dxfId="0" priority="35" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="103" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FO14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="34">
+    <cfRule type="containsBlanks" dxfId="0" priority="102">
       <formula>LEN(TRIM(FO14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FU14">
-    <cfRule type="containsText" dxfId="0" priority="9" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="77" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FU14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="8">
+    <cfRule type="containsBlanks" dxfId="0" priority="76">
       <formula>LEN(TRIM(FU14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FW14">
-    <cfRule type="containsText" dxfId="0" priority="17" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="85" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FW14)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="16">
+    <cfRule type="containsBlanks" dxfId="0" priority="84">
       <formula>LEN(TRIM(FW14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FY14">
+    <cfRule type="containsText" dxfId="1" priority="8" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FY14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="7">
+      <formula>LEN(TRIM(FY14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GA14">
+    <cfRule type="containsText" dxfId="1" priority="16" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GA14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="15">
+      <formula>LEN(TRIM(GA14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GC14">
+    <cfRule type="containsText" dxfId="1" priority="26" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GC14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="25">
+      <formula>LEN(TRIM(GC14))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DE16">
-    <cfRule type="containsText" dxfId="0" priority="278" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="346" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="277">
+    <cfRule type="containsBlanks" dxfId="0" priority="345">
       <formula>LEN(TRIM(DE16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG16">
-    <cfRule type="containsText" dxfId="0" priority="260" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="328" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="259">
+    <cfRule type="containsBlanks" dxfId="0" priority="327">
       <formula>LEN(TRIM(DG16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI16">
-    <cfRule type="containsText" dxfId="0" priority="250" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="318" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="249">
+    <cfRule type="containsBlanks" dxfId="0" priority="317">
       <formula>LEN(TRIM(DI16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK16">
-    <cfRule type="containsText" dxfId="0" priority="234" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="302" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="233">
+    <cfRule type="containsBlanks" dxfId="0" priority="301">
       <formula>LEN(TRIM(DK16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DS16">
-    <cfRule type="containsText" dxfId="0" priority="214" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="282" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DS16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="213">
+    <cfRule type="containsBlanks" dxfId="0" priority="281">
       <formula>LEN(TRIM(DS16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DU16">
-    <cfRule type="containsText" dxfId="0" priority="218" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="286" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DU16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="217">
+    <cfRule type="containsBlanks" dxfId="0" priority="285">
       <formula>LEN(TRIM(DU16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DW16">
-    <cfRule type="containsText" dxfId="0" priority="220" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="288" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DW16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="219">
+    <cfRule type="containsBlanks" dxfId="0" priority="287">
       <formula>LEN(TRIM(DW16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG16">
-    <cfRule type="containsText" dxfId="0" priority="159" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="227" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="158">
+    <cfRule type="containsBlanks" dxfId="0" priority="226">
       <formula>LEN(TRIM(EG16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EM16">
-    <cfRule type="containsText" dxfId="0" priority="153" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="221" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EM16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="152">
+    <cfRule type="containsBlanks" dxfId="0" priority="220">
       <formula>LEN(TRIM(EM16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EQ16">
-    <cfRule type="containsText" dxfId="0" priority="141" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="209" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EQ16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="140">
+    <cfRule type="containsBlanks" dxfId="0" priority="208">
       <formula>LEN(TRIM(EQ16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ES16">
-    <cfRule type="containsText" dxfId="0" priority="127" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="195" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",ES16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="126">
+    <cfRule type="containsBlanks" dxfId="0" priority="194">
       <formula>LEN(TRIM(ES16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EU16">
-    <cfRule type="containsText" dxfId="0" priority="109" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="177" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EU16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="108">
+    <cfRule type="containsBlanks" dxfId="0" priority="176">
       <formula>LEN(TRIM(EU16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FI16">
-    <cfRule type="containsText" dxfId="0" priority="70" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="138" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FI16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="69">
+    <cfRule type="containsBlanks" dxfId="0" priority="137">
       <formula>LEN(TRIM(FI16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FM16">
-    <cfRule type="containsText" dxfId="0" priority="49" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="117" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FM16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="48">
+    <cfRule type="containsBlanks" dxfId="0" priority="116">
       <formula>LEN(TRIM(FM16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FO16">
-    <cfRule type="containsText" dxfId="0" priority="33" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="101" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FO16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="32">
+    <cfRule type="containsBlanks" dxfId="0" priority="100">
       <formula>LEN(TRIM(FO16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FU16">
-    <cfRule type="containsText" dxfId="0" priority="7" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="75" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FU16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="6">
+    <cfRule type="containsBlanks" dxfId="0" priority="74">
       <formula>LEN(TRIM(FU16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FW16">
-    <cfRule type="containsText" dxfId="0" priority="15" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="83" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FW16)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="14">
+    <cfRule type="containsBlanks" dxfId="0" priority="82">
       <formula>LEN(TRIM(FW16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GA16">
+    <cfRule type="containsText" dxfId="1" priority="20" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GA16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="19">
+      <formula>LEN(TRIM(GA16))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DE18">
-    <cfRule type="containsText" dxfId="0" priority="280" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="348" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DE18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="279">
+    <cfRule type="containsBlanks" dxfId="0" priority="347">
       <formula>LEN(TRIM(DE18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG18">
-    <cfRule type="containsText" dxfId="0" priority="258" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="326" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="257">
+    <cfRule type="containsBlanks" dxfId="0" priority="325">
       <formula>LEN(TRIM(DG18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI18">
-    <cfRule type="containsText" dxfId="0" priority="252" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="320" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="251">
+    <cfRule type="containsBlanks" dxfId="0" priority="319">
       <formula>LEN(TRIM(DI18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK18">
-    <cfRule type="containsText" dxfId="0" priority="232" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="300" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="231">
+    <cfRule type="containsBlanks" dxfId="0" priority="299">
       <formula>LEN(TRIM(DK18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ18">
-    <cfRule type="containsText" dxfId="0" priority="190" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="258" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="189">
+    <cfRule type="containsBlanks" dxfId="0" priority="257">
       <formula>LEN(TRIM(DQ18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DY18">
-    <cfRule type="containsText" dxfId="0" priority="180" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="248" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DY18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="179">
+    <cfRule type="containsBlanks" dxfId="0" priority="247">
       <formula>LEN(TRIM(DY18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG18">
-    <cfRule type="containsText" dxfId="0" priority="157" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="225" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EG18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="156">
+    <cfRule type="containsBlanks" dxfId="0" priority="224">
       <formula>LEN(TRIM(EG18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EM18">
-    <cfRule type="containsText" dxfId="0" priority="151" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="219" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EM18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="150">
+    <cfRule type="containsBlanks" dxfId="0" priority="218">
       <formula>LEN(TRIM(EM18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EQ18">
-    <cfRule type="containsText" dxfId="0" priority="139" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="207" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EQ18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="138">
+    <cfRule type="containsBlanks" dxfId="0" priority="206">
       <formula>LEN(TRIM(EQ18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ES18">
-    <cfRule type="containsText" dxfId="0" priority="125" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="193" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",ES18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="124">
+    <cfRule type="containsBlanks" dxfId="0" priority="192">
       <formula>LEN(TRIM(ES18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EW18">
-    <cfRule type="containsText" dxfId="0" priority="100" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="168" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EW18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="99">
+    <cfRule type="containsBlanks" dxfId="0" priority="167">
       <formula>LEN(TRIM(EW18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FK18">
-    <cfRule type="containsText" dxfId="0" priority="68" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="136" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FK18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="67">
+    <cfRule type="containsBlanks" dxfId="0" priority="135">
       <formula>LEN(TRIM(FK18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FM18">
-    <cfRule type="containsText" dxfId="0" priority="51" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="119" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FM18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="50">
+    <cfRule type="containsBlanks" dxfId="0" priority="118">
       <formula>LEN(TRIM(FM18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FO18">
-    <cfRule type="containsText" dxfId="0" priority="31" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="99" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FO18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="30">
+    <cfRule type="containsBlanks" dxfId="0" priority="98">
       <formula>LEN(TRIM(FO18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FU18">
-    <cfRule type="containsText" dxfId="0" priority="5" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="73" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FU18)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="4">
+    <cfRule type="containsBlanks" dxfId="0" priority="72">
       <formula>LEN(TRIM(FU18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FY18">
+    <cfRule type="containsText" dxfId="1" priority="63" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FY18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="62">
+      <formula>LEN(TRIM(FY18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GA18">
+    <cfRule type="containsText" dxfId="1" priority="22" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GA18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="21">
+      <formula>LEN(TRIM(GA18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GC18">
+    <cfRule type="containsText" dxfId="1" priority="24" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GC18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="23">
+      <formula>LEN(TRIM(GC18))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC20">
-    <cfRule type="containsText" dxfId="0" priority="282" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="350" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DC20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="281">
+    <cfRule type="containsBlanks" dxfId="0" priority="349">
       <formula>LEN(TRIM(DC20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG20">
-    <cfRule type="containsText" dxfId="0" priority="256" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="324" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DG20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="255">
+    <cfRule type="containsBlanks" dxfId="0" priority="323">
       <formula>LEN(TRIM(DG20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI20">
-    <cfRule type="containsText" dxfId="0" priority="254" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="322" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DI20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="253">
+    <cfRule type="containsBlanks" dxfId="0" priority="321">
       <formula>LEN(TRIM(DI20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DK20">
-    <cfRule type="containsText" dxfId="0" priority="230" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="298" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DK20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="229">
+    <cfRule type="containsBlanks" dxfId="0" priority="297">
       <formula>LEN(TRIM(DK20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DU20">
-    <cfRule type="containsText" dxfId="0" priority="216" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="284" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DU20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="215">
+    <cfRule type="containsBlanks" dxfId="0" priority="283">
       <formula>LEN(TRIM(DU20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EW20">
-    <cfRule type="containsText" dxfId="0" priority="98" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="166" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",EW20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="97">
+    <cfRule type="containsBlanks" dxfId="0" priority="165">
       <formula>LEN(TRIM(EW20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FK20">
-    <cfRule type="containsText" dxfId="0" priority="66" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="134" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FK20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="65">
+    <cfRule type="containsBlanks" dxfId="0" priority="133">
       <formula>LEN(TRIM(FK20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FM20">
-    <cfRule type="containsText" dxfId="0" priority="53" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="121" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FM20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="52">
+    <cfRule type="containsBlanks" dxfId="0" priority="120">
       <formula>LEN(TRIM(FM20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FO20">
-    <cfRule type="containsText" dxfId="0" priority="29" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="97" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FO20)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="1" priority="28">
+    <cfRule type="containsBlanks" dxfId="0" priority="96">
       <formula>LEN(TRIM(FO20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FY20">
+    <cfRule type="containsText" dxfId="1" priority="6" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FY20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="5">
+      <formula>LEN(TRIM(FY20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GA20">
+    <cfRule type="containsText" dxfId="1" priority="18" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GA20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="17">
+      <formula>LEN(TRIM(GA20))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DX3:DX20">
-    <cfRule type="containsText" dxfId="2" priority="188" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="256" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",DX3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ED3:ED20">
-    <cfRule type="containsText" dxfId="2" priority="178" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="246" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",ED3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EF3:EF20">
-    <cfRule type="containsText" dxfId="2" priority="177" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="245" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",EF3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EP3:EP20">
-    <cfRule type="containsText" dxfId="2" priority="123" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="191" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",EP3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ER3:ER20">
-    <cfRule type="containsText" dxfId="2" priority="122" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="190" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",ER3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ET3:ET20">
-    <cfRule type="containsText" dxfId="2" priority="121" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="189" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",ET3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FT3:FT20">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="71" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",FT3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FV3:FV20">
-    <cfRule type="containsText" dxfId="2" priority="2" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="70" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",FV3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B3:B21 D3:D21 KV3:KV21 LH3:LH21 KT3:KT21 KR3:KR21 F3:F21 KP3:KP21 KN3:KN21 KL3:KL21 H3:H21 KJ3:KJ21 KH3:KH21 KF3:KF21 J3:J21 KD3:KD21 KB3:KB21 JZ3:JZ21 L3:L21 JX3:JX21 JV3:JV21 JT3:JT21 N3:N21 JR3:JR21 P3:P21 JP3:JP21 R3:R21 JN3:JN21 T3:T21 JL3:JL21 V3:V21 JJ3:JJ21 X3:X21 JH3:JH21 JF3:JF21 Z3:Z21 JD3:JD21 JB3:JB21 AB3:AB21 IZ3:IZ21 IX3:IX21 AD3:AD21 IV3:IV21 IT3:IT21 AF3:AF21 IR3:IR21 IP3:IP21 AH3:AH21 IN3:IN21 IL3:IL21 AJ3:AJ21 IJ3:IJ21 IH3:IH21 AL3:AL21 IF3:IF21 ID3:ID21 AN3:AN21 IB3:IB21 HZ3:HZ21 AP3:AP21 HX3:HX21 HV3:HV21 AR3:AR21 HT3:HT21 HR3:HR21 AT3:AT21 HP3:HP21 HN3:HN21 AV3:AV21 HL3:HL21 HJ3:HJ21 AX3:AX21 HH3:HH21 HF3:HF21 AZ3:AZ21 HD3:HD21 HB3:HB21 BB3:BB21 GZ3:GZ21 GX3:GX21 BD3:BD21 GV3:GV21 GT3:GT21 BF3:BF21 GR3:GR21 GP3:GP21 BH3:BH21 GN3:GN21 GL3:GL21 BJ3:BJ21 GJ3:GJ21 GH3:GH21 BL3:BL21 GF3:GF21 GD3:GD21 BN3:BN21 GB3:GB21 FZ3:FZ21 BP3:BP21 FX3:FX21 FV21 BR3:BR21 FT21 FR3:FR21 BT3:BT21 FP3:FP21 FN21 BV3:BV21 FL21 FJ21 BX3:BX21 FH21 FF3:FF21 BZ3:BZ21 FD3:FD21 FB3:FB21 CB3:CB21 EZ3:EZ21 EX3:EX21 CD3:CD21 EV3:EV21 ET21 CF3:CF21 ER21 EP21 CH3:CH21 EN3:EN21 EL3:EL21 CJ3:CJ21 EJ3:EJ21 EH3:EH21 CL3:CL21 EF21 ED21 CN3:CN21 EB3:EB21 DZ3:DZ21 CP3:CP21 DX21 DV21 CR3:CR21 DT21 DR21 CT3:CT21 DP21 DN3:DN21 CV3:CV21 DL3:DL21 DJ21 CX3:CX21 DH21 DF21 CZ3:CZ21 DD21 DB21 LI11 KU11 KS11 KW11:LG11 KQ11 KO11 KM11 LF12:LF21 KK11 KI11 KG11 LD12:LD21 KE11 KC11 KA11 LB12:LB21 JY11 JW11 JU11 KZ12:KZ21 JS11 JQ11 JO11 JM11 JK11 JI11 JG11 W11 JE11 JC11 Y11 JA11 IY11 AA11 IW11 IU11 AC11 IS11 IQ11 AE11 IO11 IM11 AG11 IK11 II11 AI11 IG11 IE11 AK11 IC11 IA11 AM11 HY11 HW11 AO11 HU11 HS11 AQ11 HQ11 HO11 AS11 HM11 HK11 AU11 HI11 HG11 AW11 HE11 HC11 AY11 HA11 GY11 BA11 GW11 GU11 BC11 GS11 GQ11 BE11 GO11 GM11 BG11 GK11 GI11 BI11 GG11 GE11 BK11 GC11 GA11 BM11 FY11 FW11 BO11 FU11 FS11 BQ11 FQ11 BS11 FK11 BU11 FG11 BW11 FE11 FC11 BY11 FA11 EY11 CA11 EW11 EU11 CC11 ES11 EQ11 CE11 EO11 EM11 CG11 EK11 EI11 CI11 EG11 EE11 CK11 EC11 EA11 CM11 DY11 CO11 CQ11 DO11 CS11 DM11 CU11 CW11 CY11 DA11 KX3:KX10 KX12:KX21 KZ3:KZ10 LB3:LB10 LD3:LD10 LF3:LF10">
-    <cfRule type="containsText" dxfId="2" priority="301" operator="between" text="占">
+  <conditionalFormatting sqref="FX3:FX20">
+    <cfRule type="containsText" dxfId="2" priority="65" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",FX3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3:B21 D3:D21 KV3:KV21 LH3:LH21 KT3:KT21 KR3:KR21 F3:F21 KP3:KP21 KN3:KN21 KL3:KL21 H3:H21 KJ3:KJ21 KH3:KH21 KF3:KF21 J3:J21 KD3:KD21 KB3:KB21 JZ3:JZ21 L3:L21 JX3:JX21 JV3:JV21 JT3:JT21 N3:N21 JR3:JR21 P3:P21 JP3:JP21 R3:R21 JN3:JN21 T3:T21 JL3:JL21 V3:V21 JJ3:JJ21 X3:X21 JH3:JH21 JF3:JF21 Z3:Z21 JD3:JD21 JB3:JB21 AB3:AB21 IZ3:IZ21 IX3:IX21 AD3:AD21 IV3:IV21 IT3:IT21 AF3:AF21 IR3:IR21 IP3:IP21 AH3:AH21 IN3:IN21 IL3:IL21 AJ3:AJ21 IJ3:IJ21 IH3:IH21 AL3:AL21 IF3:IF21 ID3:ID21 AN3:AN21 IB3:IB21 HZ3:HZ21 AP3:AP21 HX3:HX21 HV3:HV21 AR3:AR21 HT3:HT21 HR3:HR21 AT3:AT21 HP3:HP21 HN3:HN21 AV3:AV21 HL3:HL21 HJ3:HJ21 AX3:AX21 HH3:HH21 HF3:HF21 AZ3:AZ21 HD3:HD21 HB3:HB21 BB3:BB21 GZ3:GZ21 GX3:GX21 BD3:BD21 GV3:GV21 GT3:GT21 BF3:BF21 GR3:GR21 GP3:GP21 BH3:BH21 GN3:GN21 GL3:GL21 BJ3:BJ21 GJ3:GJ21 GH3:GH21 BL3:BL21 GF3:GF21 GD3:GD21 BN3:BN21 GB21 FZ21 BP3:BP21 FX21 FV21 BR3:BR21 FT21 FR3:FR21 BT3:BT21 FP3:FP21 FN21 BV3:BV21 FL21 FJ21 BX3:BX21 FH21 FF3:FF21 BZ3:BZ21 FD3:FD21 FB3:FB21 CB3:CB21 EZ3:EZ21 EX3:EX21 CD3:CD21 EV3:EV21 ET21 CF3:CF21 ER21 EP21 CH3:CH21 EN3:EN21 EL3:EL21 CJ3:CJ21 EJ3:EJ21 EH3:EH21 CL3:CL21 EF21 ED21 CN3:CN21 EB3:EB21 DZ3:DZ21 CP3:CP21 DX21 DV21 CR3:CR21 DT21 DR21 CT3:CT21 DP21 DN3:DN21 CV3:CV21 DL3:DL21 DJ21 CX3:CX21 DH21 DF21 CZ3:CZ21 DD21 DB21 LI11 KU11 KS11 KW11:LG11 KQ11 KO11 KM11 LF12:LF21 KK11 KI11 KG11 LD12:LD21 KE11 KC11 KA11 LB12:LB21 JY11 JW11 JU11 KZ12:KZ21 JS11 JQ11 JO11 JM11 JK11 JI11 JG11 W11 JE11 JC11 Y11 JA11 IY11 AA11 IW11 IU11 AC11 IS11 IQ11 AE11 IO11 IM11 AG11 IK11 II11 AI11 IG11 IE11 AK11 IC11 IA11 AM11 HY11 HW11 AO11 HU11 HS11 AQ11 HQ11 HO11 AS11 HM11 HK11 AU11 HI11 HG11 AW11 HE11 HC11 AY11 HA11 GY11 BA11 GW11 GU11 BC11 GS11 GQ11 BE11 GO11 GM11 BG11 GK11 GI11 BI11 GG11 GE11 BK11 GC11 BM11 FW11 BO11 FU11 FS11 BQ11 FQ11 BS11 FK11 BU11 FG11 BW11 FE11 FC11 BY11 FA11 EY11 CA11 EW11 EU11 CC11 ES11 EQ11 CE11 EO11 EM11 CG11 EK11 EI11 CI11 EG11 EE11 CK11 EC11 EA11 CM11 DY11 CO11 CQ11 DO11 CS11 DM11 CU11 CW11 CY11 DA11 KX3:KX10 KX12:KX21 KZ3:KZ10 LB3:LB10 LD3:LD10 LF3:LF10">
+    <cfRule type="containsText" dxfId="2" priority="369" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",B3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3 C5 G5 E5 G3 E3 I3 I5 K3 M3 K5 M5 LI5 LG5 LE5 LC5 LA5 KY5 KW5 KU5 KS5 KQ5 O3 Q3 S3 U3 W3 Y3 AA3 AC3 AE3 AG3 AI3 AK3 AM3 AO3 AQ3 AS3 AU3 AW3 AY3 BA3 BC3 BE3 BG3 BI3 BK3 BM3 BO3 BQ3 BS3 BU3 BW3 BY3 CA3 CC3 CE3 CG3 CI3 CK3 CM3 CO3 CQ3 CS3 CU3 CW3 CY3 DA3 DM3 DO3 DY3 EA3 EC3 EE3 EG3 EI3 EK3 EM3 EO3 EQ3 ES3 EU3 EW3 EY3 FA3 FC3 FE3 FG3 FK3 FQ3 FS3 FU3 FW3 FY3 GA3 GC3 GE3 GG3 GI3 GK3 GM3 GO3 GQ3 GS3 GU3 GW3 GY3 HA3 HC3 HE3 HG3 HI3 HK3 HM3 HO3 HQ3 HS3 HU3 HW3 HY3 IA3 IC3 IE3 IG3 II3 IK3 IM3 IO3 IQ3 IS3 IU3 IW3 IY3 JA3 JC3 JE3 JG3 JI3 JK3 JM3 JO3 JQ3 JS3 JU3 JW3 JY3 KA3 KC3 KE3 KG3 KI3 KK3 KM3 KO3 KQ3 KS3 KU3 KW3 KY3 LA3 LC3 LE3 LG3 LI3 KO5 KM5 KK5 KI5 O5 Q5 S5 U5 W5 Y5 AA5 AC5 AE5 AG5 AI5 AK5 AM5 AO5 AQ5 AS5 AU5 AW5 AY5 BA5 BC5 BE5 BG5 BI5 BK5 BM5 BO5 BQ5 BS5 BU5 BW5 BY5 CA5 CC5 CE5 CG5 CI5 CK5 CM5 CO5 CQ5 CS5 CU5 CW5 CY5 DA5 DM5 DO5 DY5 EA5 EC5 EE5 EI5 EK5 EM5 EO5 EQ5 EY5 FA5 FC5 FE5 FG5 FK5 FQ5 FS5 FU5 FY5 GA5 GC5 GE5 GG5 GI5 GK5 GM5 GO5 GQ5 GS5 GU5 GW5 GY5 HA5 HC5 HE5 HG5 HI5 HK5 HM5 HO5 HQ5 HS5 HU5 HW5 HY5 IA5 IC5 IE5 IG5 II5 IK5 IM5 IO5 IQ5 IS5 IU5 IW5 IY5 JA5 JC5 JE5 JG5 JI5 JK5 JM5 JO5 JQ5 JS5 JU5 JW5 JY5 KA5 KC5 KE5 KG5 C8 G10 E10 G8 E8 G20 E20 G18 E18 G16 E16 G14 E14 G12 E12 C10 C12 C14 C16 C18 C20 I12 I14 I16 I18 I20 I8 I10 LI20 LG20 LE20 LC20 K8 M8 K10 M10 K12 M12 K14 M14 K16 M16 K18 M18 K20 M20 HW20 HU20 HS20 HQ20 HO20 HM20 HK20 HI20 HG20 HE20 HC20 HA20 GY20 GW20 GU20 GS20 GQ20 GO20 GM20 GK20 GI20 GG20 GE20 GC20 GA20 FY20 FW20 FU20 FS20 FQ20 FG20 FE20 FC20 FA20 EY20 EU20 ES20 EQ20 EO20 EM20 EK20 EI20 EG20 EE20 EC20 EA20 DY20 DO20 DM20 DA20 CY20 CW20 CU20 CS20 CQ20 CO20 CM20 CK20 CI20 CG20 CE20 CC20 CA20 BY20 BW20 BU20 BS20 BQ20 BO20 BM20 BK20 BI20 BG20 BE20 BC20 BA20 AY20 AW20 AU20 AS20 AQ20 AO20 AM20 AK20 AI20 AG20 AE20 AC20 AA20 Y20 W20 U20 S20 Q20 O20 HY20 IA20 JI20 JK20 LI18 LG18 LE18 LC18 LA18 KY18 KW18 KU18 KS18 KQ18 KO18 KM18 KK18 KI18 KG18 KE18 KC18 KA18 JY18 JW18 JU18 JS18 JQ18 JO18 JM18 JK18 JI18 JG18 JE18 JC18 JA18 IY18 IW18 IU18 IS18 IQ18 IO18 IM18 IK18 II18 IG18 IE18 IC18 IA18 HY18 HW18 HU18 HS18 HQ18 HO18 HM18 HK18 HI18 HG18 HE18 HC18 HA18 GY18 GW18 GU18 GS18 GQ18 GO18 GM18 GK18 GI18 GG18 GE18 GC18 GA18 FY18 FW18 FS18 FQ18 FG18 FE18 FC18 FA18 EY18 EU18 EO18 EK18 EI18 EE18 EC18 EA18 DO18 DM18 DA18 CY18 CW18 CU18 CS18 CQ18 CO18 CM18 CK18 CI18 CG18 CE18 CC18 CA18 BY18 BW18 BU18 BS18 BQ18 BO18 BM18 BK18 BI18 BG18 BE18 BC18 BA18 AY18 AW18 AU18 AS18 AQ18 AO18 AM18 AK18 AI18 AG18 AE18 AC18 AA18 Y18 W18 U18 S18 Q18 O18 IC20 IE20 JM20 JO20 LI16 LG16 LE16 LC16 LA16 KY16 KW16 KU16 KS16 KQ16 KO16 KM16 KK16 KI16 KG16 KE16 KC16 KA16 JY16 JW16 JU16 JS16 JQ16 JO16 JM16 JK16 JI16 JG16 JE16 JC16 JA16 IY16 IW16 IU16 IS16 IQ16 IO16 IM16 IK16 II16 IG16 IE16 IC16 IA16 HY16 HW16 HU16 HS16 HQ16 HO16 HM16 HK16 HI16 HG16 HE16 HC16 HA16 GY16 GW16 GU16 GS16 GQ16 GO16 GM16 GK16 GI16 GG16 GE16 GC16 GA16 FY16 FS16 FQ16 FK16 FG16 FE16 FC16 FA16 EY16 EW16 EO16 EK16 EI16 EE16 EC16 EA16 DY16 DO16 DM16 DA16 CY16 CW16 CU16 CS16 CQ16 CO16 CM16 CK16 CI16 CG16 CE16 CC16 CA16 BY16 BW16 BU16 BS16 BQ16 BO16 BM16 BK16 BI16 BG16 BE16 BC16 BA16 AY16 AW16 AU16 AS16 AQ16 AO16 AM16 AK16 AI16 AG16 AE16 AC16 AA16 Y16 W16 U16 S16 Q16 O16 IG20 II20 JQ20 JS20 LI14 LG14 LE14 LC14 LA14 KY14 KW14 KU14 KS14 KQ14 KO14 KM14 KK14 KI14 KG14 KE14 KC14 KA14 JY14 JW14 JU14 JS14 JQ14 JO14 JM14 JK14 JI14 JG14 JE14 JC14 JA14 IY14 IW14 IU14 IS14 IQ14 IO14 IM14 IK14 II14 IG14 IE14 IC14 IA14 HY14 HW14 HU14 HS14 HQ14 HO14 HM14 HK14 HI14 HG14 HE14 HC14 HA14 GY14 GW14 GU14 GS14 GQ14 GO14 GM14 GK14 GI14 GG14 GE14 GC14 GA14 FY14 FS14 FQ14 FG14 FE14 FC14 FA14 EY14 EW14 EO14 EK14 EI14 EC14 EA14 DO14 DM14 DA14 CY14 CW14 CU14 CS14 CQ14 CO14 CM14 CK14 CI14 CG14 CE14 CC14 CA14 BY14 BW14 BU14 BS14 BQ14 BO14 BM14 BK14 BI14 BG14 BE14 BC14 BA14 AY14 AW14 AU14 AS14 AQ14 AO14 AM14 AK14 AI14 AG14 AE14 AC14 AA14 Y14 W14 U14 S14 Q14 O14 IK20 IM20 JU20 JW20 LI12 LG12 LE12 LC12 LA12 KY12 KW12 KU12 KS12 KQ12 KO12 KM12 KK12 KI12 KG12 KE12 KC12 KA12 JY12 JW12 JU12 JS12 JQ12 JO12 JM12 JK12 JI12 JG12 JE12 JC12 JA12 IY12 IW12 IU12 IS12 IQ12 IO12 IM12 IK12 II12 IG12 IE12 IC12 IA12 HY12 HW12 HU12 HS12 HQ12 HO12 HM12 HK12 HI12 HG12 HE12 HC12 HA12 GY12 GW12 GU12 GS12 GQ12 GO12 GM12 GK12 GI12 GG12 GE12 GC12 GA12 FY12 FS12 FQ12 FG12 FE12 FC12 FA12 EY12 EO12 EM12 EK12 EI12 EC12 EA12 DY12 DO12 DM12 DA12 CY12 CW12 CU12 CS12 CQ12 CO12 CM12 CK12 CI12 CG12 CE12 CC12 CA12 BY12 BW12 BU12 BS12 BQ12 BO12 BM12 BK12 BI12 BG12 BE12 BC12 BA12 AY12 AW12 AU12 AS12 AQ12 AO12 AM12 AK12 AI12 AG12 AE12 AC12 AA12 Y12 W12 U12 S12 Q12 O12 IO20 IQ20 JY20 KA20 LI10 LG10 LE10 LC10 LA10 KY10 KW10 KU10 KS10 KQ10 KO10 KM10 KK10 KI10 KG10 KE10 KC10 KA10 JY10 JW10 JU10 JS10 JQ10 JO10 JM10 JK10 JI10 JG10 JE10 JC10 JA10 IY10 IW10 IU10 IS10 IQ10 IO10 IM10 IK10 II10 IG10 IE10 IC10 IA10 HY10 HW10 HU10 HS10 HQ10 HO10 HM10 HK10 HI10 HG10 HE10 HC10 HA10 GY10 GW10 GU10 GS10 GQ10 GO10 GM10 GK10 GI10 GG10 GE10 GC10 GA10 FY10 FS10 FQ10 FG10 FE10 FC10 FA10 EY10 EW10 EO10 EM10 EK10 EI10 EE10 EC10 EA10 DO10 DM10 DA10 CY10 CW10 CU10 CS10 CQ10 CO10 CM10 CK10 CI10 CG10 CE10 CC10 CA10 BY10 BW10 BU10 BS10 BQ10 BO10 BM10 BK10 BI10 BG10 BE10 BC10 BA10 AY10 AW10 AU10 AS10 AQ10 AO10 AM10 AK10 AI10 AG10 AE10 AC10 AA10 Y10 W10 U10 S10 Q10 O10 IS20 IU20 KC20 KE20 LI8 LG8 LE8 LC8 LA8 KY8 KW8 KU8 KS8 KQ8 KO8 KM8 KK8 KI8 KG8 KE8 KC8 KA8 JY8 JW8 JU8 JS8 JQ8 JO8 JM8 JK8 JI8 JG8 JE8 JC8 JA8 IY8 IW8 IU8 IS8 IQ8 IO8 IM8 IK8 II8 IG8 IE8 IC8 IA8 HY8 HW8 HU8 HS8 HQ8 HO8 HM8 HK8 HI8 HG8 HE8 HC8 HA8 GY8 GW8 GU8 GS8 GQ8 GO8 GM8 GK8 GI8 GG8 GE8 GC8 GA8 FY8 FS8 FQ8 FG8 FE8 FC8 FA8 EY8 EO8 EM8 EK8 EI8 EC8 EA8 DO8 DM8 DA8 CY8 CW8 CU8 CS8 CQ8 CO8 CM8 CK8 CI8 CG8 CE8 CC8 CA8 BY8 BW8 BU8 BS8 BQ8 BO8 BM8 BK8 BI8 BG8 BE8 BC8 BA8 AY8 AW8 AU8 AS8 AQ8 AO8 AM8 AK8 AI8 AG8 AE8 AC8 AA8 Y8 W8 U8 S8 Q8 O8 IW20 IY20 KG20 KI20 LA20 KY20 KW20 KU20 KS20 KQ20 KO20 JG20 JE20 KM20 KK20 JC20 JA20">
-    <cfRule type="containsBlanks" dxfId="1" priority="299">
+  <conditionalFormatting sqref="C3:C21 E3:E21 KW3:KW21 LI3:LI21 KU3:KU21 KS3:KS21 G3:G21 KQ3:KQ21 KO3:KO21 KM3:KM21 I3:I21 KK3:KK21 KI3:KI21 KG3:KG21 K3:K21 KE3:KE21 KC3:KC21 KA3:KA21 M3:M21 JY3:JY21 JW3:JW21 JU3:JU21 O3:O21 JS3:JS21 Q3:Q21 JQ3:JQ21 S3:S21 JO3:JO21 U3:U21 JM3:JM21 W3:W21 JK3:JK21 Y3:Y21 JI3:JI21 JG3:JG21 AA3:AA21 JE3:JE21 JC3:JC21 AC3:AC21 JA3:JA21 IY3:IY21 AE3:AE21 IW3:IW21 IU3:IU21 AG3:AG21 IS3:IS21 IQ3:IQ21 AI3:AI21 IO3:IO21 IM3:IM21 AK3:AK21 IK3:IK21 II3:II21 AM3:AM21 IG3:IG21 IE3:IE21 AO3:AO21 IC3:IC21 IA3:IA21 AQ3:AQ21 HY3:HY21 HW3:HW21 AS3:AS21 HU3:HU21 HS3:HS21 AU3:AU21 HQ3:HQ21 HO3:HO21 AW3:AW21 HM3:HM21 HK3:HK21 AY3:AY21 HI3:HI21 HG3:HG21 BA3:BA21 HE3:HE21 HC3:HC21 BC3:BC21 HA3:HA21 GY3:GY21 BE3:BE21 GW3:GW21 GU3:GU21 BG3:BG21 GS3:GS21 GQ3:GQ21 BI3:BI21 GO3:GO21 GM3:GM21 BK3:BK21 GK3:GK21 GI3:GI21 BM3:BM21 GG3:GG21 GE3:GE21 BO3:BO21 GC3:GC7 GC9 GC11:GC13 GC15:GC17 GC19:GC21 GA21 BQ3:BQ21 FY21 FW3:FW4 FW6:FW7 FW9 FU11 FW11 FW13 FW15 FW17:FW21 BS3:BS21 FU3:FU7 FU9 FU13 FU15 FU17 FU19:FU21 FS3:FS21 BU3:BU21 FQ3:FQ21 FO21 BW3:BW21 FM21 FK3:FK7 FK9 FK11 FK13 FK15:FK17 FK19 FK21 BY3:BY21 FI21 FG3:FG21 CA3:CA21 FE3:FE21 FC3:FC21 CC3:CC21 FA3:FA21 EY3:EY21 CE3:CE21 EW3:EW4 EW6:EW7 EW9:EW11 EW13:EW17 EW19 EW21 EU3:EU4 EU6:EU7 EU9 EU11 EU13 EU15 EU17:EU21 CG3:CG21 ES3:ES4 ES6:ES7 ES9 EQ11 ES11 ES13 ES15 ES17 ES19:ES21 EQ3:EQ7 EQ9 EQ13 EQ15 EQ17 EQ19:EQ21 CI3:CI21 EO3:EO21 EM3:EM13 EM15 EM17 EM19:EM21 CK3:CK21 EK3:EK21 EI3:EI21 CM3:CM21 EG3:EG4 EG6:EG7 EG9 EG11:EH11 EG13 EG15 EG17 EG19:EG21 EE3:EE7 EE9:EE11 EE13 EE15:EE21 CO3:CO21 EC3:EC21 EA3:EA21 CQ3:CQ21 DY3:DY7 DY9 DY11:DY13 DY15:DY17 DY19:DY21 DW21 CS3:CS21 DU21 DS21 CU3:CU21 DQ21 DO3:DO21 CW3:CW21 DM3:DM21 DK21 CY3:CY21 DI21 DG21 DA3:DA21 DE21 DC21 KV11 KT11 KX11:LH11 KR11 KP11 KN11 LG12:LG21 KL11 KJ11 KH11 LE12:LE21 KF11 KD11 KB11 LC12:LC21 JZ11 JX11 JV11 LA12:LA21 JT11 JR11 JP11 JN11 JL11 JJ11 JH11 X11 JF11 JD11 Z11 JB11 IZ11 AB11 IX11 IV11 AD11 IT11 IR11 AF11 IP11 IN11 AH11 IL11 IJ11 AJ11 IH11 IF11 AL11 ID11 IB11 AN11 HZ11 HX11 AP11 HV11 HT11 AR11 HR11 HP11 AT11 HN11 HL11 AV11 HJ11 HH11 AX11 HF11 HD11 AZ11 HB11 GZ11 BB11 GX11 GV11 BD11 GT11 GR11 BF11 GP11 GN11 BH11 GL11 GJ11 BJ11 GH11 GF11 BL11 GD11 BN11 BP11 BR11 FR11 FP11 BT11 BV11 BX11 FF11 FD11 BZ11 FB11 EZ11 CB11 EX11 CD11 CF11 EN11 CH11 EL11 EJ11 CJ11 CL11 EB11 CN11 DZ11 DN11 DL11 CV11 CX11 CZ11 KY3:KY10 KY12:KY21 LA3:LA10 LC3:LC10 LE3:LE10 LG3:LG10">
+    <cfRule type="containsText" dxfId="1" priority="368" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",C3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3 C5 G5 E5 G3 E3 I3 I5 K3 M3 K5 M5 LI5 LG5 LE5 LC5 LA5 KY5 KW5 KU5 KS5 KQ5 O3 Q3 S3 U3 W3 Y3 AA3 AC3 AE3 AG3 AI3 AK3 AM3 AO3 AQ3 AS3 AU3 AW3 AY3 BA3 BC3 BE3 BG3 BI3 BK3 BM3 BO3 BQ3 BS3 BU3 BW3 BY3 CA3 CC3 CE3 CG3 CI3 CK3 CM3 CO3 CQ3 CS3 CU3 CW3 CY3 DA3 DM3 DO3 DY3 EA3 EC3 EE3 EG3 EI3 EK3 EM3 EO3 EQ3 ES3 EU3 EW3 EY3 FA3 FC3 FE3 FG3 FK3 FQ3 FS3 FU3 FW3 GC3 GE3 GG3 GI3 GK3 GM3 GO3 GQ3 GS3 GU3 GW3 GY3 HA3 HC3 HE3 HG3 HI3 HK3 HM3 HO3 HQ3 HS3 HU3 HW3 HY3 IA3 IC3 IE3 IG3 II3 IK3 IM3 IO3 IQ3 IS3 IU3 IW3 IY3 JA3 JC3 JE3 JG3 JI3 JK3 JM3 JO3 JQ3 JS3 JU3 JW3 JY3 KA3 KC3 KE3 KG3 KI3 KK3 KM3 KO3 KQ3 KS3 KU3 KW3 KY3 LA3 LC3 LE3 LG3 LI3 KO5 KM5 KK5 KI5 O5 Q5 S5 U5 W5 Y5 AA5 AC5 AE5 AG5 AI5 AK5 AM5 AO5 AQ5 AS5 AU5 AW5 AY5 BA5 BC5 BE5 BG5 BI5 BK5 BM5 BO5 BQ5 BS5 BU5 BW5 BY5 CA5 CC5 CE5 CG5 CI5 CK5 CM5 CO5 CQ5 CS5 CU5 CW5 CY5 DA5 DM5 DO5 DY5 EA5 EC5 EE5 EI5 EK5 EM5 EO5 EQ5 EY5 FA5 FC5 FE5 FG5 FK5 FQ5 FS5 FU5 GC5 GE5 GG5 GI5 GK5 GM5 GO5 GQ5 GS5 GU5 GW5 GY5 HA5 HC5 HE5 HG5 HI5 HK5 HM5 HO5 HQ5 HS5 HU5 HW5 HY5 IA5 IC5 IE5 IG5 II5 IK5 IM5 IO5 IQ5 IS5 IU5 IW5 IY5 JA5 JC5 JE5 JG5 JI5 JK5 JM5 JO5 JQ5 JS5 JU5 JW5 JY5 KA5 KC5 KE5 KG5 C8 G10 E10 G8 E8 G20 E20 G18 E18 G16 E16 G14 E14 G12 E12 C10 C12 C14 C16 C18 C20 I12 I14 I16 I18 I20 I8 I10 LI20 LG20 LE20 LC20 K8 M8 K10 M10 K12 M12 K14 M14 K16 M16 K18 M18 K20 M20 HW20 HU20 HS20 HQ20 HO20 HM20 HK20 HI20 HG20 HE20 HC20 HA20 GY20 GW20 GU20 GS20 GQ20 GO20 GM20 GK20 GI20 GG20 GE20 GC20 FW20 FU20 FS20 FQ20 FG20 FE20 FC20 FA20 EY20 EU20 ES20 EQ20 EO20 EM20 EK20 EI20 EG20 EE20 EC20 EA20 DY20 DO20 DM20 DA20 CY20 CW20 CU20 CS20 CQ20 CO20 CM20 CK20 CI20 CG20 CE20 CC20 CA20 BY20 BW20 BU20 BS20 BQ20 BO20 BM20 BK20 BI20 BG20 BE20 BC20 BA20 AY20 AW20 AU20 AS20 AQ20 AO20 AM20 AK20 AI20 AG20 AE20 AC20 AA20 Y20 W20 U20 S20 Q20 O20 HY20 IA20 JI20 JK20 LI18 LG18 LE18 LC18 LA18 KY18 KW18 KU18 KS18 KQ18 KO18 KM18 KK18 KI18 KG18 KE18 KC18 KA18 JY18 JW18 JU18 JS18 JQ18 JO18 JM18 JK18 JI18 JG18 JE18 JC18 JA18 IY18 IW18 IU18 IS18 IQ18 IO18 IM18 IK18 II18 IG18 IE18 IC18 IA18 HY18 HW18 HU18 HS18 HQ18 HO18 HM18 HK18 HI18 HG18 HE18 HC18 HA18 GY18 GW18 GU18 GS18 GQ18 GO18 GM18 GK18 GI18 GG18 GE18 FW18 FS18 FQ18 FG18 FE18 FC18 FA18 EY18 EU18 EO18 EK18 EI18 EE18 EC18 EA18 DO18 DM18 DA18 CY18 CW18 CU18 CS18 CQ18 CO18 CM18 CK18 CI18 CG18 CE18 CC18 CA18 BY18 BW18 BU18 BS18 BQ18 BO18 BM18 BK18 BI18 BG18 BE18 BC18 BA18 AY18 AW18 AU18 AS18 AQ18 AO18 AM18 AK18 AI18 AG18 AE18 AC18 AA18 Y18 W18 U18 S18 Q18 O18 IC20 IE20 JM20 JO20 LI16 LG16 LE16 LC16 LA16 KY16 KW16 KU16 KS16 KQ16 KO16 KM16 KK16 KI16 KG16 KE16 KC16 KA16 JY16 JW16 JU16 JS16 JQ16 JO16 JM16 JK16 JI16 JG16 JE16 JC16 JA16 IY16 IW16 IU16 IS16 IQ16 IO16 IM16 IK16 II16 IG16 IE16 IC16 IA16 HY16 HW16 HU16 HS16 HQ16 HO16 HM16 HK16 HI16 HG16 HE16 HC16 HA16 GY16 GW16 GU16 GS16 GQ16 GO16 GM16 GK16 GI16 GG16 GE16 GC16 FS16 FQ16 FK16 FG16 FE16 FC16 FA16 EY16 EW16 EO16 EK16 EI16 EE16 EC16 EA16 DY16 DO16 DM16 DA16 CY16 CW16 CU16 CS16 CQ16 CO16 CM16 CK16 CI16 CG16 CE16 CC16 CA16 BY16 BW16 BU16 BS16 BQ16 BO16 BM16 BK16 BI16 BG16 BE16 BC16 BA16 AY16 AW16 AU16 AS16 AQ16 AO16 AM16 AK16 AI16 AG16 AE16 AC16 AA16 Y16 W16 U16 S16 Q16 O16 IG20 II20 JQ20 JS20 LI14 LG14 LE14 LC14 LA14 KY14 KW14 KU14 KS14 KQ14 KO14 KM14 KK14 KI14 KG14 KE14 KC14 KA14 JY14 JW14 JU14 JS14 JQ14 JO14 JM14 JK14 JI14 JG14 JE14 JC14 JA14 IY14 IW14 IU14 IS14 IQ14 IO14 IM14 IK14 II14 IG14 IE14 IC14 IA14 HY14 HW14 HU14 HS14 HQ14 HO14 HM14 HK14 HI14 HG14 HE14 HC14 HA14 GY14 GW14 GU14 GS14 GQ14 GO14 GM14 GK14 GI14 GG14 GE14 FS14 FQ14 FG14 FE14 FC14 FA14 EY14 EW14 EO14 EK14 EI14 EC14 EA14 DO14 DM14 DA14 CY14 CW14 CU14 CS14 CQ14 CO14 CM14 CK14 CI14 CG14 CE14 CC14 CA14 BY14 BW14 BU14 BS14 BQ14 BO14 BM14 BK14 BI14 BG14 BE14 BC14 BA14 AY14 AW14 AU14 AS14 AQ14 AO14 AM14 AK14 AI14 AG14 AE14 AC14 AA14 Y14 W14 U14 S14 Q14 O14 IK20 IM20 JU20 JW20 LI12 LG12 LE12 LC12 LA12 KY12 KW12 KU12 KS12 KQ12 KO12 KM12 KK12 KI12 KG12 KE12 KC12 KA12 JY12 JW12 JU12 JS12 JQ12 JO12 JM12 JK12 JI12 JG12 JE12 JC12 JA12 IY12 IW12 IU12 IS12 IQ12 IO12 IM12 IK12 II12 IG12 IE12 IC12 IA12 HY12 HW12 HU12 HS12 HQ12 HO12 HM12 HK12 HI12 HG12 HE12 HC12 HA12 GY12 GW12 GU12 GS12 GQ12 GO12 GM12 GK12 GI12 GG12 GE12 GC12 FS12 FQ12 FG12 FE12 FC12 FA12 EY12 EO12 EM12 EK12 EI12 EC12 EA12 DY12 DO12 DM12 DA12 CY12 CW12 CU12 CS12 CQ12 CO12 CM12 CK12 CI12 CG12 CE12 CC12 CA12 BY12 BW12 BU12 BS12 BQ12 BO12 BM12 BK12 BI12 BG12 BE12 BC12 BA12 AY12 AW12 AU12 AS12 AQ12 AO12 AM12 AK12 AI12 AG12 AE12 AC12 AA12 Y12 W12 U12 S12 Q12 O12 IO20 IQ20 JY20 KA20 LI10 LG10 LE10 LC10 LA10 KY10 KW10 KU10 KS10 KQ10 KO10 KM10 KK10 KI10 KG10 KE10 KC10 KA10 JY10 JW10 JU10 JS10 JQ10 JO10 JM10 JK10 JI10 JG10 JE10 JC10 JA10 IY10 IW10 IU10 IS10 IQ10 IO10 IM10 IK10 II10 IG10 IE10 IC10 IA10 HY10 HW10 HU10 HS10 HQ10 HO10 HM10 HK10 HI10 HG10 HE10 HC10 HA10 GY10 GW10 GU10 GS10 GQ10 GO10 GM10 GK10 GI10 GG10 GE10 FS10 FQ10 FG10 FE10 FC10 FA10 EY10 EW10 EO10 EM10 EK10 EI10 EE10 EC10 EA10 DO10 DM10 DA10 CY10 CW10 CU10 CS10 CQ10 CO10 CM10 CK10 CI10 CG10 CE10 CC10 CA10 BY10 BW10 BU10 BS10 BQ10 BO10 BM10 BK10 BI10 BG10 BE10 BC10 BA10 AY10 AW10 AU10 AS10 AQ10 AO10 AM10 AK10 AI10 AG10 AE10 AC10 AA10 Y10 W10 U10 S10 Q10 O10 IS20 IU20 KC20 KE20 LI8 LG8 LE8 LC8 LA8 KY8 KW8 KU8 KS8 KQ8 KO8 KM8 KK8 KI8 KG8 KE8 KC8 KA8 JY8 JW8 JU8 JS8 JQ8 JO8 JM8 JK8 JI8 JG8 JE8 JC8 JA8 IY8 IW8 IU8 IS8 IQ8 IO8 IM8 IK8 II8 IG8 IE8 IC8 IA8 HY8 HW8 HU8 HS8 HQ8 HO8 HM8 HK8 HI8 HG8 HE8 HC8 HA8 GY8 GW8 GU8 GS8 GQ8 GO8 GM8 GK8 GI8 GG8 GE8 FS8 FQ8 FG8 FE8 FC8 FA8 EY8 EO8 EM8 EK8 EI8 EC8 EA8 DO8 DM8 DA8 CY8 CW8 CU8 CS8 CQ8 CO8 CM8 CK8 CI8 CG8 CE8 CC8 CA8 BY8 BW8 BU8 BS8 BQ8 BO8 BM8 BK8 BI8 BG8 BE8 BC8 BA8 AY8 AW8 AU8 AS8 AQ8 AO8 AM8 AK8 AI8 AG8 AE8 AC8 AA8 Y8 W8 U8 S8 Q8 O8 IW20 IY20 KG20 KI20 LA20 KY20 KW20 KU20 KS20 KQ20 KO20 JG20 JE20 KM20 KK20 JC20 JA20">
+    <cfRule type="containsBlanks" dxfId="0" priority="367">
       <formula>LEN(TRIM(C3))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C21 E3:E21 KW3:KW21 LI3:LI21 KU3:KU21 KS3:KS21 G3:G21 KQ3:KQ21 KO3:KO21 KM3:KM21 I3:I21 KK3:KK21 KI3:KI21 KG3:KG21 K3:K21 KE3:KE21 KC3:KC21 KA3:KA21 M3:M21 JY3:JY21 JW3:JW21 JU3:JU21 O3:O21 JS3:JS21 Q3:Q21 JQ3:JQ21 S3:S21 JO3:JO21 U3:U21 JM3:JM21 W3:W21 JK3:JK21 Y3:Y21 JI3:JI21 JG3:JG21 AA3:AA21 JE3:JE21 JC3:JC21 AC3:AC21 JA3:JA21 IY3:IY21 AE3:AE21 IW3:IW21 IU3:IU21 AG3:AG21 IS3:IS21 IQ3:IQ21 AI3:AI21 IO3:IO21 IM3:IM21 AK3:AK21 IK3:IK21 II3:II21 AM3:AM21 IG3:IG21 IE3:IE21 AO3:AO21 IC3:IC21 IA3:IA21 AQ3:AQ21 HY3:HY21 HW3:HW21 AS3:AS21 HU3:HU21 HS3:HS21 AU3:AU21 HQ3:HQ21 HO3:HO21 AW3:AW21 HM3:HM21 HK3:HK21 AY3:AY21 HI3:HI21 HG3:HG21 BA3:BA21 HE3:HE21 HC3:HC21 BC3:BC21 HA3:HA21 GY3:GY21 BE3:BE21 GW3:GW21 GU3:GU21 BG3:BG21 GS3:GS21 GQ3:GQ21 BI3:BI21 GO3:GO21 GM3:GM21 BK3:BK21 GK3:GK21 GI3:GI21 BM3:BM21 GG3:GG21 GE3:GE21 BO3:BO21 GC3:GC21 GA3:GA21 BQ3:BQ21 FY3:FY21 FW3:FW4 FW6:FW7 FW9 FU11 FW11:FX11 FW13 FW15 FW17:FW21 BS3:BS21 FU3:FU7 FU9 FU13 FU15 FU17 FU19:FU21 FS3:FS21 BU3:BU21 FQ3:FQ21 FO21 BW3:BW21 FM21 FK3:FK7 FK9 FK11 FK13 FK15:FK17 FK19 FK21 BY3:BY21 FI21 FG3:FG21 CA3:CA21 FE3:FE21 FC3:FC21 CC3:CC21 FA3:FA21 EY3:EY21 CE3:CE21 EW3:EW4 EW6:EW7 EW9:EW11 EW13:EW17 EW19 EW21 EU3:EU4 EU6:EU7 EU9 EU11 EU13 EU15 EU17:EU21 CG3:CG21 ES3:ES4 ES6:ES7 ES9 EQ11 ES11 ES13 ES15 ES17 ES19:ES21 EQ3:EQ7 EQ9 EQ13 EQ15 EQ17 EQ19:EQ21 CI3:CI21 EO3:EO21 EM3:EM13 EM15 EM17 EM19:EM21 CK3:CK21 EK3:EK21 EI3:EI21 CM3:CM21 EG3:EG4 EG6:EG7 EG9 EG11:EH11 EG13 EG15 EG17 EG19:EG21 EE3:EE7 EE9:EE11 EE13 EE15:EE21 CO3:CO21 EC3:EC21 EA3:EA21 CQ3:CQ21 DY3:DY7 DY9 DY11:DY13 DY15:DY17 DY19:DY21 DW21 CS3:CS21 DU21 DS21 CU3:CU21 DQ21 DO3:DO21 CW3:CW21 DM3:DM21 DK21 CY3:CY21 DI21 DG21 DA3:DA21 DE21 DC21 KV11 KT11 KX11:LH11 KR11 KP11 KN11 LG12:LG21 KL11 KJ11 KH11 LE12:LE21 KF11 KD11 KB11 LC12:LC21 JZ11 JX11 JV11 LA12:LA21 JT11 JR11 JP11 JN11 JL11 JJ11 JH11 X11 JF11 JD11 Z11 JB11 IZ11 AB11 IX11 IV11 AD11 IT11 IR11 AF11 IP11 IN11 AH11 IL11 IJ11 AJ11 IH11 IF11 AL11 ID11 IB11 AN11 HZ11 HX11 AP11 HV11 HT11 AR11 HR11 HP11 AT11 HN11 HL11 AV11 HJ11 HH11 AX11 HF11 HD11 AZ11 HB11 GZ11 BB11 GX11 GV11 BD11 GT11 GR11 BF11 GP11 GN11 BH11 GL11 GJ11 BJ11 GH11 GF11 BL11 GD11 GB11 BN11 FZ11 BP11 BR11 FR11 FP11 BT11 BV11 BX11 FF11 FD11 BZ11 FB11 EZ11 CB11 EX11 CD11 CF11 EN11 CH11 EL11 EJ11 CJ11 CL11 EB11 CN11 DZ11 DN11 DL11 CV11 CX11 CZ11 KY3:KY10 KY12:KY21 LA3:LA10 LC3:LC10 LE3:LE10 LG3:LG10">
-    <cfRule type="containsText" dxfId="0" priority="300" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",C3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DB3:DB20 DD3:DD20 DF3:DF20 DH3:DH20 DJ3:DJ20 DC11 DE11 DG11 DI11 DK11">
-    <cfRule type="containsText" dxfId="2" priority="294" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="362" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",DB3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC3:DC7 DC9:DC11 DC13 DC15:DC19 DE3:DE4 DE6:DE7 DE9 DD11:DF11 DE13 DE15 DE17 DE19:DE20 DG3:DG4 DG6:DG7 DG9:DG11 DG13:DG15 DG17 DG19 DI3:DI7 DI9 DH11:DJ11 DI13 DI15 DI17 DI19 DK3:DK7 DK9 DK11:DK13 DK15 DK17 DK19">
-    <cfRule type="containsText" dxfId="0" priority="293" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="361" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DC3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC3 DE3 DG3 DI3 DK3 DC5 DI5 DK5 DE20 DC18 DC16 DG14 DK12 DG10 DC10">
-    <cfRule type="containsBlanks" dxfId="1" priority="292">
+    <cfRule type="containsBlanks" dxfId="0" priority="360">
       <formula>LEN(TRIM(DC3))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DP3:DP20 DR3:DR20 DT3:DT20 DV3:DV20 DQ11 DS11 DU11 DW11">
-    <cfRule type="containsText" dxfId="2" priority="291" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="359" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",DP3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ3 DS3 DU3 DW3 DQ5 DS5 DW5 DW20 DS20 DQ20 DW18 DU18 DS18 DQ16 DU14 DU10">
-    <cfRule type="containsBlanks" dxfId="1" priority="289">
+    <cfRule type="containsBlanks" dxfId="0" priority="357">
       <formula>LEN(TRIM(DQ3))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ3:DQ7 DQ9 DQ11:DT11 DQ13 DQ15:DQ17 DQ19:DQ20 DS3:DS7 DS9 DS13 DS15 DS17:DS20 DU3:DU4 DU6:DU7 DU9:DU11 DU13:DU15 DU17:DU19 DW3:DW7 DW9 DV11:DW11 DW13 DW15 DW17:DW20">
-    <cfRule type="containsText" dxfId="0" priority="290" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="358" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",DQ3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FH3:FH20 FJ3:FJ20">
-    <cfRule type="containsText" dxfId="2" priority="96" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="164" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",FH3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FI3:FI4 FI6:FI7 FI9 FI11 FI13 FI15 FI17:FI20">
-    <cfRule type="containsText" dxfId="0" priority="82" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="150" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FI3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FI3 FI20 FI18">
-    <cfRule type="containsBlanks" dxfId="1" priority="81">
+    <cfRule type="containsBlanks" dxfId="0" priority="149">
       <formula>LEN(TRIM(FI3))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FL3:FL20 FN3:FN20 FM11 FO11">
-    <cfRule type="containsText" dxfId="2" priority="56" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="124" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",FL3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FM3:FM7 FM9 FL11:FN11 FM13 FM15 FM17 FM19 FO3:FO7 FO9 FO11:FO13 FO15 FO17 FO19">
-    <cfRule type="containsText" dxfId="0" priority="55" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="123" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FL3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FM3 FO3 FM5 FO5 FO12">
-    <cfRule type="containsBlanks" dxfId="1" priority="54">
+    <cfRule type="containsBlanks" dxfId="0" priority="122">
       <formula>LEN(TRIM(FM3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FY3 FY16">
+    <cfRule type="containsBlanks" dxfId="0" priority="66">
+      <formula>LEN(TRIM(FY3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FY3:FY4 FY6:FY7 FY9 FY11 FY13 FY15:FY17 FY19">
+    <cfRule type="containsText" dxfId="1" priority="67" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FY3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FZ3:FZ20 GB3:GB20 GA11">
+    <cfRule type="containsText" dxfId="2" priority="51" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",FZ3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GA3:GA4 GA6:GA7 GA9 FZ11:GB11 GA13 GA15 GA17 GA19">
+    <cfRule type="containsText" dxfId="1" priority="50" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FZ3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FH11 FJ11">
-    <cfRule type="containsText" dxfId="0" priority="95" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="163" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FH11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22 JO22 JM22 JK22 JI22 JG22 JE22 JC22 JA22 IY22 IW22 IU22 IS22 IQ22 IO22 IM22 IK22 II22 IG22 IE22 IC22 IA22 HY22 HW22 HU22 HS22 HQ22 HO22 HM22 HK22 HI22 HG22 HE22 HC22 HA22 GY22 GW22 GU22 GS22 GQ22 GO22 GM22 GK22 GI22 GG22 GE22 GC22 GA22 FY22 FW22 FU22 FS22 FQ22 FO22 FM22 FK22 FI22 FG22 FE22 FC22 FA22 EY22 EW22 EU22 ES22 EQ22 EO22 EM22 EK22 EI22 EG22 EE22 EC22 EA22 DY22 DW22 DU22 DS22 DQ22 DO22 DM22 DK22 DI22 DG22 DE22 DC22 DA22 CY22 CW22 CU22 CS22 CQ22 CO22 CM22 CK22 CI22 CG22 CE22 CC22 CA22 BY22 BW22 BU22 BS22 BQ22 BO22 BM22 BK22 BI22 BG22 BE22 BC22 BA22 AY22 AW22 AU22 AS22 AQ22 AO22 AM22 AK22 AI22 AG22 AE22 AC22 AA22 Y22 W22 U22 S22 Q22 O22 M22 K22 I22 G22 E22">
-    <cfRule type="containsBlanks" dxfId="3" priority="297">
+    <cfRule type="containsBlanks" dxfId="3" priority="365">
       <formula>LEN(TRIM(C22))=0</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="298" operator="between" text="—">
+    <cfRule type="containsText" dxfId="2" priority="366" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",C22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FW5 FU8 FW8 FU9 FW9 FU10 FW10 FU11 FW11 FU12 FW12 FU13 FW13 FU14 FW14 FU15 FW15 FU16 FW16 FU17 FU18 C3:C21 E3:E21 G3:G21 I3:I21 K3:K21 M3:M21 O3:O21 Q3:Q21 S3:S21 U3:U21 W3:W21 Y3:Y21 AA3:AA21 AC3:AC21 AE3:AE21 AG3:AG21 AI3:AI21 AK3:AK21 AM3:AM21 AO3:AO21 AQ3:AQ21 AS3:AS21 AU3:AU21 AW3:AW21 AY3:AY21 BA3:BA21 BC3:BC21 BE3:BE21 BG3:BG21 BI3:BI21 BK3:BK21 BM3:BM21 BO3:BO21 BQ3:BQ21 BS3:BS21 BU3:BU21 BW3:BW21 BY3:BY21 CA3:CA21 CC3:CC21 CE3:CE21 CG3:CG21 CI3:CI21 CK3:CK21 CM3:CM21 CO3:CO21 CQ3:CQ21 CS3:CS21 CU3:CU21 CW3:CW21 CY3:CY21 DA3:DA21 DC3:DC21 DE3:DE21 DG3:DG21 DI3:DI21 DK3:DK21 DM3:DM21 DO3:DO21 DQ3:DQ21 DS3:DS21 DU3:DU21 DW3:DW21 DY3:DY21 EA3:EA21 EC3:EC21 EE3:EE21 EG3:EG21 EI3:EI21 EK3:EK21 EM3:EM21 EO3:EO21 EQ3:EQ21 ES3:ES21 EU3:EU21 EW3:EW21 EY3:EY21 FA3:FA21 FC3:FC21 FE3:FE21 FG3:FG21 FI3:FI21 FK3:FK21 FM3:FM21 FO3:FO21 FQ3:FQ21 FS3:FS21 FU3:FU7 FU19:FU21 FW3:FW4 FW6:FW7 FW17:FW21 FY3:FY21 GA3:GA21 GC3:GC21 GE3:GE21 GG3:GG21 GI3:GI21 GK3:GK21 GM3:GM21 GO3:GO21 GQ3:GQ21 GS3:GS21 GU3:GU21 GW3:GW21 GY3:GY21 HA3:HA21 HC3:HC21 HE3:HE21 HG3:HG21 HI3:HI21 HK3:HK21 HM3:HM21 HO3:HO21 HQ3:HQ21 HS3:HS21 HU3:HU21 HW3:HW21 HY3:HY21 IA3:IA21 IC3:IC21 IE3:IE21 IG3:IG21 II3:II21 IK3:IK21 IM3:IM21 IO3:IO21 IQ3:IQ21 IS3:IS21 IU3:IU21 IW3:IW21 IY3:IY21 JA3:JA21 JC3:JC21 JE3:JE21 JG3:JG21 JI3:JI21 JK3:JK21 JM3:JM21 JO3:JO21">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FY5 GA5 FY8 GA8 GC8 GA9 GC9 GA10 GC10 GA11 FY12 GA12 FY13 GA13 FY14 GA14 GC14 GA15 GA16 GA17 GA18 GC18 GA19 FY20 GA20 FY21 GA21 C3:C21 E3:E21 G3:G21 I3:I21 K3:K21 M3:M21 O3:O21 Q3:Q21 S3:S21 U3:U21 W3:W21 Y3:Y21 AA3:AA21 AC3:AC21 AE3:AE21 AG3:AG21 AI3:AI21 AK3:AK21 AM3:AM21 AO3:AO21 AQ3:AQ21 AS3:AS21 AU3:AU21 AW3:AW21 AY3:AY21 BA3:BA21 BC3:BC21 BE3:BE21 BG3:BG21 BI3:BI21 BK3:BK21 BM3:BM21 BO3:BO21 BQ3:BQ21 BS3:BS21 BU3:BU21 BW3:BW21 BY3:BY21 CA3:CA21 CC3:CC21 CE3:CE21 CG3:CG21 CI3:CI21 CK3:CK21 CM3:CM21 CO3:CO21 CQ3:CQ21 CS3:CS21 CU3:CU21 CW3:CW21 CY3:CY21 DA3:DA21 DC3:DC21 DE3:DE21 DG3:DG21 DI3:DI21 DK3:DK21 DM3:DM21 DO3:DO21 DQ3:DQ21 DS3:DS21 DU3:DU21 DW3:DW21 DY3:DY21 EA3:EA21 EC3:EC21 EE3:EE21 EG3:EG21 EI3:EI21 EK3:EK21 EM3:EM21 EO3:EO21 EQ3:EQ21 ES3:ES21 EU3:EU21 EW3:EW21 EY3:EY21 FA3:FA21 FC3:FC21 FE3:FE21 FG3:FG21 FI3:FI21 FK3:FK21 FM3:FM21 FO3:FO21 FQ3:FQ21 FS3:FS21 FU3:FU21 FW3:FW21 FY3:FY4 FY6:FY7 FY9:FY11 FY15:FY19 GA3:GA4 GA6:GA7 GC3:GC7 GC11:GC13 GC15:GC17 GC19:GC21 GE3:GE21 GG3:GG21 GI3:GI21 GK3:GK21 GM3:GM21 GO3:GO21 GQ3:GQ21 GS3:GS21 GU3:GU21 GW3:GW21 GY3:GY21 HA3:HA21 HC3:HC21 HE3:HE21 HG3:HG21 HI3:HI21 HK3:HK21 HM3:HM21 HO3:HO21 HQ3:HQ21 HS3:HS21 HU3:HU21 HW3:HW21 HY3:HY21 IA3:IA21 IC3:IC21 IE3:IE21 IG3:IG21 II3:II21 IK3:IK21 IM3:IM21 IO3:IO21 IQ3:IQ21 IS3:IS21 IU3:IU21 IW3:IW21 IY3:IY21 JA3:JA21 JC3:JC21 JE3:JE21 JG3:JG21 JI3:JI21 JK3:JK21 JM3:JM21 JO3:JO21">
       <formula1>数据!$B$1:$B$62</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FT21 FV21 B3:B21 D3:D21 F3:F21 H3:H21 J3:J21 L3:L21 N3:N21 P3:P21 R3:R21 T3:T21 V3:V21 X3:X21 Z3:Z21 AB3:AB21 AD3:AD21 AF3:AF21 AH3:AH21 AJ3:AJ21 AL3:AL21 AN3:AN21 AP3:AP21 AR3:AR21 AT3:AT21 AV3:AV21 AX3:AX21 AZ3:AZ21 BB3:BB21 BD3:BD21 BF3:BF21 BH3:BH21 BJ3:BJ21 BL3:BL21 BN3:BN21 BP3:BP21 BR3:BR21 BT3:BT21 BV3:BV21 BX3:BX21 BZ3:BZ21 CB3:CB21 CD3:CD21 CF3:CF21 CH3:CH21 CJ3:CJ21 CL3:CL21 CN3:CN21 CP3:CP21 CR3:CR21 CT3:CT21 CV3:CV21 CX3:CX21 CZ3:CZ21 DB3:DB21 DD3:DD21 DF3:DF21 DH3:DH21 DJ3:DJ21 DL3:DL21 DN3:DN21 DP3:DP21 DR3:DR21 DT3:DT21 DV3:DV21 DX3:DX21 DZ3:DZ21 EB3:EB21 ED3:ED21 EF3:EF21 EH3:EH21 EJ3:EJ21 EL3:EL21 EN3:EN21 EP3:EP21 ER3:ER21 ET3:ET21 EV3:EV21 EX3:EX21 EZ3:EZ21 FB3:FB21 FD3:FD21 FF3:FF21 FH3:FH21 FJ3:FJ21 FL3:FL21 FN3:FN21 FP3:FP21 FR3:FR21 FT3:FT20 FV3:FV20 FX3:FX21 FZ3:FZ21 GB3:GB21 GD3:GD21 GF3:GF21 GH3:GH21 GJ3:GJ21 GL3:GL21 GN3:GN21 GP3:GP21 GR3:GR21 GT3:GT21 GV3:GV21 GX3:GX21 GZ3:GZ21 HB3:HB21 HD3:HD21 HF3:HF21 HH3:HH21 HJ3:HJ21 HL3:HL21 HN3:HN21 HP3:HP21 HR3:HR21 HT3:HT21 HV3:HV21 HX3:HX21 HZ3:HZ21 IB3:IB21 ID3:ID21 IF3:IF21 IH3:IH21 IJ3:IJ21 IL3:IL21 IN3:IN21 IP3:IP21 IR3:IR21 IT3:IT21 IV3:IV21 IX3:IX21 IZ3:IZ21 JB3:JB21 JD3:JD21 JF3:JF21 JH3:JH21 JJ3:JJ21 JL3:JL21 JN3:JN21">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FX21 FZ21 GB21 B3:B21 D3:D21 F3:F21 H3:H21 J3:J21 L3:L21 N3:N21 P3:P21 R3:R21 T3:T21 V3:V21 X3:X21 Z3:Z21 AB3:AB21 AD3:AD21 AF3:AF21 AH3:AH21 AJ3:AJ21 AL3:AL21 AN3:AN21 AP3:AP21 AR3:AR21 AT3:AT21 AV3:AV21 AX3:AX21 AZ3:AZ21 BB3:BB21 BD3:BD21 BF3:BF21 BH3:BH21 BJ3:BJ21 BL3:BL21 BN3:BN21 BP3:BP21 BR3:BR21 BT3:BT21 BV3:BV21 BX3:BX21 BZ3:BZ21 CB3:CB21 CD3:CD21 CF3:CF21 CH3:CH21 CJ3:CJ21 CL3:CL21 CN3:CN21 CP3:CP21 CR3:CR21 CT3:CT21 CV3:CV21 CX3:CX21 CZ3:CZ21 DB3:DB21 DD3:DD21 DF3:DF21 DH3:DH21 DJ3:DJ21 DL3:DL21 DN3:DN21 DP3:DP21 DR3:DR21 DT3:DT21 DV3:DV21 DX3:DX21 DZ3:DZ21 EB3:EB21 ED3:ED21 EF3:EF21 EH3:EH21 EJ3:EJ21 EL3:EL21 EN3:EN21 EP3:EP21 ER3:ER21 ET3:ET21 EV3:EV21 EX3:EX21 EZ3:EZ21 FB3:FB21 FD3:FD21 FF3:FF21 FH3:FH21 FJ3:FJ21 FL3:FL21 FN3:FN21 FP3:FP21 FR3:FR21 FT3:FT21 FV3:FV21 FX3:FX20 FZ3:FZ20 GB3:GB20 GD3:GD21 GF3:GF21 GH3:GH21 GJ3:GJ21 GL3:GL21 GN3:GN21 GP3:GP21 GR3:GR21 GT3:GT21 GV3:GV21 GX3:GX21 GZ3:GZ21 HB3:HB21 HD3:HD21 HF3:HF21 HH3:HH21 HJ3:HJ21 HL3:HL21 HN3:HN21 HP3:HP21 HR3:HR21 HT3:HT21 HV3:HV21 HX3:HX21 HZ3:HZ21 IB3:IB21 ID3:ID21 IF3:IF21 IH3:IH21 IJ3:IJ21 IL3:IL21 IN3:IN21 IP3:IP21 IR3:IR21 IT3:IT21 IV3:IV21 IX3:IX21 IZ3:IZ21 JB3:JB21 JD3:JD21 JF3:JF21 JH3:JH21 JJ3:JJ21 JL3:JL21 JN3:JN21">
       <formula1>数据!$A$1:$A$88</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C22 E22 G22 I22 K22 M22 O22 Q22 S22 U22 W22 Y22 AA22 AC22 AE22 AG22 AI22 AK22 AM22 AO22 AQ22 AS22 AU22 AW22 AY22 BA22 BC22 BE22 BG22 BI22 BK22 BM22 BO22 BQ22 BS22 BU22 BW22 BY22 CA22 CC22 CE22 CG22 CI22 CK22 CM22 CO22 CQ22 CS22 CU22 CW22 CY22 DA22 DC22 DE22 DG22 DI22 DK22 DM22 DO22 DQ22 DS22 DU22 DW22 DY22 EA22 EC22 EE22 EG22 EI22 EK22 EM22 EO22 EQ22 ES22 EU22 EW22 EY22 FA22 FC22 FE22 FG22 FI22 FK22 FM22 FO22 FQ22 FS22 FU22 FW22 FY22 GA22 GC22 GE22 GG22 GI22 GK22 GM22 GO22 GQ22 GS22 GU22 GW22 GY22 HA22 HC22 HE22 HG22 HI22 HK22 HM22 HO22 HQ22 HS22 HU22 HW22 HY22 IA22 IC22 IE22 IG22 II22 IK22 IM22 IO22 IQ22 IS22 IU22 IW22 IY22 JA22 JC22 JE22 JG22 JI22 JK22 JM22 JO22">

--- a/c/9班资料.xlsx
+++ b/c/9班资料.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480" firstSheet="1" activeTab="3"/>
+    <workbookView windowWidth="20750" windowHeight="10480" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="七下拖课" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2047" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2050" uniqueCount="453">
   <si>
     <t>拖课统计表</t>
   </si>
@@ -1090,7 +1090,8 @@
   </si>
   <si>
     <t>课件半自制，最后一节课还在讲评校本。
-名言：我没马，我骑小电驴；漂亮的我生气地打丑陋的你；……</t>
+名言：我没马，我骑小电驴；漂亮的我生气地打丑陋的你；……
+抽西游记</t>
   </si>
   <si>
     <t>魏××</t>
@@ -1174,7 +1175,16 @@
     <t>王淮之前整纪律时说过：“声音声音！”结果这句话成为了班上热梗。下课、课前甚至上课时都能听到此起彼伏的“声音声音！”，还有人当着王淮的面说“声音声音！”后又出现“睡觉睡觉”这一句话，不过并未引起太大轰动。</t>
   </si>
   <si>
+    <t>猴。
+关心郑致辰。</t>
+  </si>
+  <si>
     <t>江雨晴喜欢写小说（如“恩芽”）。</t>
+  </si>
+  <si>
+    <t>语文老师：“祥懿，又是你~”
+下午课件吃午饭。
+爱吃番茄酱。</t>
   </si>
   <si>
     <r>
@@ -1236,6 +1246,9 @@
       </rPr>
       <t>英语课上，刘必艳发现他经常是记笔记最快的一个，可走近一看，字迹非常潦草，于是总让他放慢速度。</t>
     </r>
+  </si>
+  <si>
+    <t>廖成羲背诵内容潦草，抽背时先一笔一划认真写，然后干脆摆烂。写道最后一个字时一竖下来，用力一点。</t>
   </si>
   <si>
     <r>
@@ -2646,9 +2659,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
+      <sz val="11"/>
+      <name val="黑体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2657,10 +2671,9 @@
       <scheme val="major"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="黑体"/>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="62">
@@ -17534,14 +17547,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="HX21 HZ21 IB21 ID21 IF21 B3:B21 D3:D21 F3:F21 H3:H21 J3:J21 L3:L21 N3:N21 P3:P21 R3:R21 T3:T21 V3:V21 X3:X21 Z3:Z21 AB3:AB21 AD3:AD21 AF3:AF21 AH3:AH21 AJ3:AJ21 AL3:AL21 AN3:AN21 AP3:AP21 AR3:AR21 AT3:AT21 AV3:AV21 AX3:AX21 AZ3:AZ21 BB3:BB21 BD3:BD21 BF3:BF21 BH3:BH21 BJ3:BJ21 BL3:BL21 BN3:BN21 BP3:BP21 BR3:BR21 BT3:BT21 BV3:BV21 BX3:BX21 BZ3:BZ21 CB3:CB21 CD3:CD21 CF3:CF21 CH3:CH21 CJ3:CJ21 CL3:CL21 CN3:CN21 CP3:CP21 CR3:CR21 CT3:CT21 CV3:CV21 CX3:CX21 CZ3:CZ21 DB3:DB21 DD3:DD21 DF3:DF21 DH3:DH21 DJ3:DJ21 DL3:DL21 DN3:DN21 DP3:DP21 DR3:DR21 DT3:DT21 DV3:DV21 DX3:DX21 DZ3:DZ21 EB3:EB21 ED3:ED21 EF3:EF21 EH3:EH21 EJ3:EJ21 EL3:EL21 EN3:EN21 EP3:EP21 ER3:ER21 ET3:ET21 EV3:EV21 EX3:EX21 EZ3:EZ21 FB3:FB21 FD3:FD21 FF3:FF21 FH3:FH21 FJ3:FJ21 FL3:FL21 FN3:FN21 FP3:FP21 FR3:FR21 FT3:FT21 FV3:FV21 FX3:FX21 FZ3:FZ21 GB3:GB21 GD3:GD21 GF3:GF21 GH3:GH21 GJ3:GJ21 GL3:GL21 GN3:GN21 GP3:GP21 GR3:GR21 GT3:GT21 GV3:GV21 GX3:GX21 GZ3:GZ21 HB3:HB21 HD3:HD21 HF3:HF21 HH3:HH21 HJ3:HJ21 HL3:HL21 HN3:HN21 HP3:HP21 HR3:HR21 HT3:HT21 HV3:HV21 HX3:HX20 HZ3:HZ20 IB3:IB20 ID3:ID20 IF3:IF20 IH3:IH21 IJ3:IJ21 IL3:IL21 IN3:IN21 IP3:IP21 IR3:IR21 IT3:IT21 IV3:IV21 IX3:IX21 IZ3:IZ21 JB3:JB21 JD3:JD21 JF3:JF21 JH3:JH21 JJ3:JJ21 JL3:JL21 JN3:JN21">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C22 E22 G22 I22 K22 M22 O22 Q22 S22 U22 W22 Y22 AA22 AC22 AE22 AG22 AI22 AK22 AM22 AO22 AQ22 AS22 AU22 AW22 AY22 BA22 BC22 BE22 BG22 BI22 BK22 BM22 BO22 BQ22 BS22 BU22 BW22 BY22 CA22 CC22 CE22 CG22 CI22 CK22 CM22 CO22 CQ22 CS22 CU22 CW22 CY22 DA22 DC22 DE22 DG22 DI22 DK22 DM22 DO22 DQ22 DS22 DU22 DW22 DY22 EA22 EC22 EE22 EG22 EI22 EK22 EM22 EO22 EQ22 ES22 EU22 EW22 EY22 FA22 FC22 FE22 FG22 FI22 FK22 FM22 FO22 FQ22 FS22 FU22 FW22 FY22 GA22 GC22 GE22 GG22 GI22 GK22 GM22 GO22 GQ22 GS22 GU22 GW22 GY22 HA22 HC22 HE22 HG22 HI22 HK22 HM22 HO22 HQ22 HS22 HU22 HW22 HY22 IA22 IC22 IE22 IG22 II22 IK22 IM22 IO22 IQ22 IS22 IU22 IW22 IY22 JA22 JC22 JE22 JG22 JI22 JK22 JM22 JO22">
+      <formula1>数据!$C$1:$C$25</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B21 D3:D21 F3:F21 H3:H21 J3:J21 L3:L21 N3:N21 P3:P21 R3:R21 T3:T21 V3:V21 X3:X21 Z3:Z21 AB3:AB21 AD3:AD21 AF3:AF21 AH3:AH21 AJ3:AJ21 AL3:AL21 AN3:AN21 AP3:AP21 AR3:AR21 AT3:AT21 AV3:AV21 AX3:AX21 AZ3:AZ21 BB3:BB21 BD3:BD21 BF3:BF21 BH3:BH21 BJ3:BJ21 BL3:BL21 BN3:BN21 BP3:BP21 BR3:BR21 BT3:BT21 BV3:BV21 BX3:BX21 BZ3:BZ21 CB3:CB21 CD3:CD21 CF3:CF21 CH3:CH21 CJ3:CJ21 CL3:CL21 CN3:CN21 CP3:CP21 CR3:CR21 CT3:CT21 CV3:CV21 CX3:CX21 CZ3:CZ21 DB3:DB21 DD3:DD21 DF3:DF21 DH3:DH21 DJ3:DJ21 DL3:DL21 DN3:DN21 DP3:DP21 DR3:DR21 DT3:DT21 DV3:DV21 DX3:DX21 DZ3:DZ21 EB3:EB21 ED3:ED21 EF3:EF21 EH3:EH21 EJ3:EJ21 EL3:EL21 EN3:EN21 EP3:EP21 ER3:ER21 ET3:ET21 EV3:EV21 EX3:EX21 EZ3:EZ21 FB3:FB21 FD3:FD21 FF3:FF21 FH3:FH21 FJ3:FJ21 FL3:FL21 FN3:FN21 FP3:FP21 FR3:FR21 FT3:FT21 FV3:FV21 FX3:FX21 FZ3:FZ21 GB3:GB21 GD3:GD21 GF3:GF21 GH3:GH21 GJ3:GJ21 GL3:GL21 GN3:GN21 GP3:GP21 GR3:GR21 GT3:GT21 GV3:GV21 GX3:GX21 GZ3:GZ21 HB3:HB21 HD3:HD21 HF3:HF21 HH3:HH21 HJ3:HJ21 HL3:HL21 HN3:HN21 HP3:HP21 HR3:HR21 HT3:HT21 HV3:HV21 HX3:HX21 HZ3:HZ21 IB3:IB21 ID3:ID21 IF3:IF21 IH3:IH21 IJ3:IJ21 IL3:IL21 IN3:IN21 IP3:IP21 IR3:IR21 IT3:IT21 IV3:IV21 IX3:IX21 IZ3:IZ21 JB3:JB21 JD3:JD21 JF3:JF21 JH3:JH21 JJ3:JJ21 JL3:JL21 JN3:JN21">
       <formula1>数据!$A$1:$A$88</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="HY21 IA21 IC21 IE21 C3:C21 E3:E21 G3:G21 I3:I21 K3:K21 M3:M21 O3:O21 Q3:Q21 S3:S21 U3:U21 W3:W21 Y3:Y21 AA3:AA21 AC3:AC21 AE3:AE21 AG3:AG21 AI3:AI21 AK3:AK21 AM3:AM21 AO3:AO21 AQ3:AQ21 AS3:AS21 AU3:AU21 AW3:AW21 AY3:AY21 BA3:BA21 BC3:BC21 BE3:BE21 BG3:BG21 BI3:BI21 BK3:BK21 BM3:BM21 BO3:BO21 BQ3:BQ21 BS3:BS21 BU3:BU21 BW3:BW21 BY3:BY21 CA3:CA21 CC3:CC21 CE3:CE21 CG3:CG21 CI3:CI21 CK3:CK21 CM3:CM21 CO3:CO21 CQ3:CQ21 CS3:CS21 CU3:CU21 CW3:CW21 CY3:CY21 DA3:DA21 DC3:DC21 DE3:DE21 DG3:DG21 DI3:DI21 DK3:DK21 DM3:DM21 DO3:DO21 DQ3:DQ21 DS3:DS21 DU3:DU21 DW3:DW21 DY3:DY21 EA3:EA21 EC3:EC21 EE3:EE21 EG3:EG21 EI3:EI21 EK3:EK21 EM3:EM21 EO3:EO21 EQ3:EQ21 ES3:ES21 EU3:EU21 EW3:EW21 EY3:EY21 FA3:FA21 FC3:FC21 FE3:FE21 FG3:FG21 FI3:FI21 FK3:FK21 FM3:FM21 FO3:FO21 FQ3:FQ21 FS3:FS21 FU3:FU21 FW3:FW21 FY3:FY21 GA3:GA21 GC3:GC21 GE3:GE21 GG3:GG21 GI3:GI21 GK3:GK21 GM3:GM21 GO3:GO21 GQ3:GQ21 GS3:GS21 GU3:GU21 GW3:GW21 GY3:GY21 HA3:HA21 HC3:HC21 HE3:HE21 HG3:HG21 HI3:HI21 HK3:HK21 HM3:HM21 HO3:HO21 HQ3:HQ21 HS3:HS21 HU3:HU21 HW3:HW21 HY3:HY20 IA3:IA20 IC3:IC20 IE3:IE20 IG3:IG21 II3:II21 IK3:IK21 IM3:IM21 IO3:IO21 IQ3:IQ21 IS3:IS21 IU3:IU21 IW3:IW21 IY3:IY21 JA3:JA21 JC3:JC21 JE3:JE21 JG3:JG21 JI3:JI21 JK3:JK21 JM3:JM21 JO3:JO21">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C21 E3:E21 G3:G21 I3:I21 K3:K21 M3:M21 O3:O21 Q3:Q21 S3:S21 U3:U21 W3:W21 Y3:Y21 AA3:AA21 AC3:AC21 AE3:AE21 AG3:AG21 AI3:AI21 AK3:AK21 AM3:AM21 AO3:AO21 AQ3:AQ21 AS3:AS21 AU3:AU21 AW3:AW21 AY3:AY21 BA3:BA21 BC3:BC21 BE3:BE21 BG3:BG21 BI3:BI21 BK3:BK21 BM3:BM21 BO3:BO21 BQ3:BQ21 BS3:BS21 BU3:BU21 BW3:BW21 BY3:BY21 CA3:CA21 CC3:CC21 CE3:CE21 CG3:CG21 CI3:CI21 CK3:CK21 CM3:CM21 CO3:CO21 CQ3:CQ21 CS3:CS21 CU3:CU21 CW3:CW21 CY3:CY21 DA3:DA21 DC3:DC21 DE3:DE21 DG3:DG21 DI3:DI21 DK3:DK21 DM3:DM21 DO3:DO21 DQ3:DQ21 DS3:DS21 DU3:DU21 DW3:DW21 DY3:DY21 EA3:EA21 EC3:EC21 EE3:EE21 EG3:EG21 EI3:EI21 EK3:EK21 EM3:EM21 EO3:EO21 EQ3:EQ21 ES3:ES21 EU3:EU21 EW3:EW21 EY3:EY21 FA3:FA21 FC3:FC21 FE3:FE21 FG3:FG21 FI3:FI21 FK3:FK21 FM3:FM21 FO3:FO21 FQ3:FQ21 FS3:FS21 FU3:FU21 FW3:FW21 FY3:FY21 GA3:GA21 GC3:GC21 GE3:GE21 GG3:GG21 GI3:GI21 GK3:GK21 GM3:GM21 GO3:GO21 GQ3:GQ21 GS3:GS21 GU3:GU21 GW3:GW21 GY3:GY21 HA3:HA21 HC3:HC21 HE3:HE21 HG3:HG21 HI3:HI21 HK3:HK21 HM3:HM21 HO3:HO21 HQ3:HQ21 HS3:HS21 HU3:HU21 HW3:HW21 HY3:HY21 IA3:IA21 IC3:IC21 IE3:IE21 IG3:IG21 II3:II21 IK3:IK21 IM3:IM21 IO3:IO21 IQ3:IQ21 IS3:IS21 IU3:IU21 IW3:IW21 IY3:IY21 JA3:JA21 JC3:JC21 JE3:JE21 JG3:JG21 JI3:JI21 JK3:JK21 JM3:JM21 JO3:JO21">
       <formula1>数据!$B$1:$B$62</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C22 E22 G22 I22 K22 M22 O22 Q22 S22 U22 W22 Y22 AA22 AC22 AE22 AG22 AI22 AK22 AM22 AO22 AQ22 AS22 AU22 AW22 AY22 BA22 BC22 BE22 BG22 BI22 BK22 BM22 BO22 BQ22 BS22 BU22 BW22 BY22 CA22 CC22 CE22 CG22 CI22 CK22 CM22 CO22 CQ22 CS22 CU22 CW22 CY22 DA22 DC22 DE22 DG22 DI22 DK22 DM22 DO22 DQ22 DS22 DU22 DW22 DY22 EA22 EC22 EE22 EG22 EI22 EK22 EM22 EO22 EQ22 ES22 EU22 EW22 EY22 FA22 FC22 FE22 FG22 FI22 FK22 FM22 FO22 FQ22 FS22 FU22 FW22 FY22 GA22 GC22 GE22 GG22 GI22 GK22 GM22 GO22 GQ22 GS22 GU22 GW22 GY22 HA22 HC22 HE22 HG22 HI22 HK22 HM22 HO22 HQ22 HS22 HU22 HW22 HY22 IA22 IC22 IE22 IG22 II22 IK22 IM22 IO22 IQ22 IS22 IU22 IW22 IY22 JA22 JC22 JE22 JG22 JI22 JK22 JM22 JO22">
-      <formula1>数据!$C$1:$C$25</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17564,7 +17577,7 @@
   <sheetData>
     <row r="1" s="2" customFormat="1" customHeight="1" spans="1:16">
       <c r="A1" s="5" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -17595,7 +17608,7 @@
     </row>
     <row r="3" customHeight="1" spans="1:9">
       <c r="A3" s="11" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="13"/>
@@ -17787,7 +17800,7 @@
     </row>
     <row r="11" customHeight="1" spans="1:9">
       <c r="A11" s="11" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="13"/>
@@ -17979,7 +17992,7 @@
     </row>
     <row r="19" customHeight="1" spans="1:9">
       <c r="A19" s="11" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B19" s="12"/>
       <c r="C19" s="13"/>
@@ -18369,7 +18382,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B16">
         <v>3.75</v>
@@ -18391,7 +18404,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B18">
         <v>4.25</v>
@@ -18402,7 +18415,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B19">
         <v>4.5</v>
@@ -18413,7 +18426,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B20">
         <v>4.75</v>
@@ -18424,7 +18437,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B21">
         <v>5</v>
@@ -18435,7 +18448,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B22">
         <v>5.25</v>
@@ -18446,7 +18459,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B23">
         <v>5.5</v>
@@ -18457,7 +18470,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B24">
         <v>5.75</v>
@@ -18468,7 +18481,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B25">
         <v>6</v>
@@ -18511,7 +18524,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B30">
         <v>7.25</v>
@@ -18519,7 +18532,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B31">
         <v>7.5</v>
@@ -18527,7 +18540,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B32">
         <v>7.75</v>
@@ -18535,7 +18548,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B33">
         <v>8</v>
@@ -18543,7 +18556,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B34">
         <v>8.25</v>
@@ -18551,7 +18564,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B35">
         <v>8.5</v>
@@ -18559,7 +18572,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B36">
         <v>8.75</v>
@@ -18567,7 +18580,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B37">
         <v>9</v>
@@ -18575,7 +18588,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B38">
         <v>9.25</v>
@@ -18583,7 +18596,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B39">
         <v>9.5</v>
@@ -18591,7 +18604,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B40">
         <v>9.75</v>
@@ -18599,7 +18612,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B41">
         <v>10</v>
@@ -18607,7 +18620,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B42">
         <v>11</v>
@@ -18615,7 +18628,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B43">
         <v>12</v>
@@ -18623,7 +18636,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B44">
         <v>13</v>
@@ -18631,7 +18644,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B45">
         <v>14</v>
@@ -18639,7 +18652,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B46">
         <v>15</v>
@@ -18647,7 +18660,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B47">
         <v>16</v>
@@ -18655,7 +18668,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B48">
         <v>17</v>
@@ -18663,7 +18676,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B49">
         <v>18</v>
@@ -18671,7 +18684,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B50">
         <v>19</v>
@@ -18679,7 +18692,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B51">
         <v>20</v>
@@ -18687,7 +18700,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B52">
         <v>21</v>
@@ -18695,7 +18708,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B53">
         <v>22</v>
@@ -18703,7 +18716,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B54">
         <v>23</v>
@@ -18711,7 +18724,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B55">
         <v>24</v>
@@ -18719,7 +18732,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B56">
         <v>25</v>
@@ -18727,7 +18740,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B57">
         <v>26</v>
@@ -18735,7 +18748,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B58">
         <v>27</v>
@@ -18743,7 +18756,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B59">
         <v>28</v>
@@ -18751,7 +18764,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B60">
         <v>29</v>
@@ -18759,7 +18772,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B61">
         <v>30</v>
@@ -18767,7 +18780,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B62" t="s">
         <v>5</v>
@@ -18775,117 +18788,117 @@
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="1" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="1" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="86" spans="1:1">
@@ -18895,7 +18908,7 @@
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -20903,7 +20916,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="35" ht="28" spans="1:5">
+    <row r="35" ht="42" spans="1:5">
       <c r="A35" s="94"/>
       <c r="B35" s="95"/>
       <c r="C35" s="77" t="s">
@@ -21242,9 +21255,12 @@
         <v>332</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" ht="28" spans="1:3">
       <c r="A3" s="56" t="s">
         <v>143</v>
+      </c>
+      <c r="C3" s="50" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -21262,12 +21278,15 @@
         <v>148</v>
       </c>
       <c r="C6" s="63" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="7" ht="42" spans="1:3">
       <c r="A7" s="56" t="s">
         <v>149</v>
+      </c>
+      <c r="C7" s="50" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="8" spans="1:1">
@@ -21285,7 +21304,7 @@
         <v>154</v>
       </c>
       <c r="B10" s="64" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -21308,7 +21327,7 @@
         <v>161</v>
       </c>
       <c r="B14" s="64" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="15" spans="1:1">
@@ -21326,7 +21345,7 @@
         <v>165</v>
       </c>
       <c r="C17" s="63" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -21339,12 +21358,15 @@
         <v>167</v>
       </c>
     </row>
-    <row r="20" ht="42" spans="1:2">
+    <row r="20" ht="42" spans="1:3">
       <c r="A20" s="56" t="s">
         <v>168</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>337</v>
+        <v>339</v>
+      </c>
+      <c r="C20" s="50" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="21" ht="280" spans="1:3">
@@ -21352,10 +21374,10 @@
         <v>169</v>
       </c>
       <c r="B21" s="49" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C21" s="50" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -21368,7 +21390,7 @@
         <v>172</v>
       </c>
       <c r="B23" s="64" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="24" ht="70" spans="1:3">
@@ -21376,10 +21398,10 @@
         <v>173</v>
       </c>
       <c r="B24" s="64" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C24" s="63" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="25" spans="1:1">
@@ -21397,10 +21419,10 @@
         <v>179</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C27" s="63" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="28" ht="409" customHeight="1" spans="1:3">
@@ -21408,10 +21430,10 @@
         <v>181</v>
       </c>
       <c r="B28" s="49" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C28" s="63" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="29" spans="1:1">
@@ -21424,7 +21446,7 @@
         <v>184</v>
       </c>
       <c r="C30" s="63" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="31" spans="1:1">
@@ -21457,7 +21479,7 @@
         <v>194</v>
       </c>
       <c r="B36" s="64" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="37" ht="126" spans="1:3">
@@ -21465,7 +21487,7 @@
         <v>196</v>
       </c>
       <c r="C37" s="63" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="38" ht="28" spans="1:7">
@@ -21473,7 +21495,7 @@
         <v>198</v>
       </c>
       <c r="B38" s="65" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C38" s="66"/>
       <c r="D38" s="67"/>
@@ -21486,7 +21508,7 @@
         <v>201</v>
       </c>
       <c r="C39" s="63" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -21494,10 +21516,10 @@
         <v>203</v>
       </c>
       <c r="B40" s="64" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C40" s="63" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="41" ht="112" spans="1:3">
@@ -21505,7 +21527,7 @@
         <v>205</v>
       </c>
       <c r="C41" s="63" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -21518,7 +21540,7 @@
         <v>208</v>
       </c>
       <c r="B43" s="64" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="44" spans="1:1">
@@ -21531,7 +21553,7 @@
         <v>211</v>
       </c>
       <c r="B45" s="49" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="46" spans="1:1">
@@ -21549,7 +21571,7 @@
         <v>216</v>
       </c>
       <c r="C48" s="63" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -21562,7 +21584,7 @@
         <v>219</v>
       </c>
       <c r="C50" s="63" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -21575,10 +21597,10 @@
         <v>222</v>
       </c>
       <c r="B52" s="49" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C52" s="63" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -21608,7 +21630,7 @@
   <sheetData>
     <row r="1" s="28" customFormat="1" spans="1:8">
       <c r="A1" s="32" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="28" t="s">
@@ -21632,10 +21654,10 @@
     </row>
     <row r="2" s="29" customFormat="1" spans="1:4">
       <c r="A2" s="34" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C2" s="36" t="s">
         <v>141</v>
@@ -21645,7 +21667,7 @@
     <row r="3" s="29" customFormat="1" spans="1:4">
       <c r="A3" s="38"/>
       <c r="B3" s="35" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C3" s="36" t="s">
         <v>157</v>
@@ -21663,7 +21685,7 @@
     <row r="5" s="29" customFormat="1" spans="1:4">
       <c r="A5" s="38"/>
       <c r="B5" s="35" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C5" s="36" t="s">
         <v>161</v>
@@ -21673,7 +21695,7 @@
     <row r="6" s="29" customFormat="1" spans="1:4">
       <c r="A6" s="38"/>
       <c r="B6" s="35" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C6" s="39" t="s">
         <v>149</v>
@@ -21695,7 +21717,7 @@
     <row r="8" s="29" customFormat="1" spans="1:4">
       <c r="A8" s="38"/>
       <c r="B8" s="35" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C8" s="39" t="s">
         <v>147</v>
@@ -21707,7 +21729,7 @@
     <row r="9" s="29" customFormat="1" spans="1:4">
       <c r="A9" s="38"/>
       <c r="B9" s="35" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C9" s="36" t="s">
         <v>152</v>
@@ -21717,7 +21739,7 @@
     <row r="10" s="29" customFormat="1" spans="1:4">
       <c r="A10" s="38"/>
       <c r="B10" s="35" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C10" s="36" t="s">
         <v>164</v>
@@ -21727,7 +21749,7 @@
     <row r="11" s="29" customFormat="1" spans="1:4">
       <c r="A11" s="40"/>
       <c r="B11" s="35" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C11" s="36" t="s">
         <v>186</v>
@@ -21736,10 +21758,10 @@
     </row>
     <row r="12" s="30" customFormat="1" spans="1:4">
       <c r="A12" s="41" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B12" s="42" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C12" s="43" t="s">
         <v>205</v>
@@ -21757,17 +21779,17 @@
     <row r="14" s="30" customFormat="1" spans="1:4">
       <c r="A14" s="45"/>
       <c r="B14" s="42" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C14" s="43" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D14" s="44"/>
     </row>
     <row r="15" s="30" customFormat="1" spans="1:4">
       <c r="A15" s="45"/>
       <c r="B15" s="42" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C15" s="43" t="s">
         <v>143</v>
@@ -21785,7 +21807,7 @@
     <row r="17" s="30" customFormat="1" spans="1:4">
       <c r="A17" s="45"/>
       <c r="B17" s="42" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C17" s="43" t="s">
         <v>156</v>
@@ -21795,7 +21817,7 @@
     <row r="18" s="30" customFormat="1" spans="1:4">
       <c r="A18" s="45"/>
       <c r="B18" s="42" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C18" s="43" t="s">
         <v>168</v>
@@ -21805,7 +21827,7 @@
     <row r="19" s="30" customFormat="1" spans="1:4">
       <c r="A19" s="45"/>
       <c r="B19" s="42" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C19" s="43" t="s">
         <v>201</v>
@@ -21815,7 +21837,7 @@
     <row r="20" s="30" customFormat="1" spans="1:4">
       <c r="A20" s="46"/>
       <c r="B20" s="42" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C20" s="43" t="s">
         <v>203</v>

--- a/c/9班资料.xlsx
+++ b/c/9班资料.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480" firstSheet="1" activeTab="6"/>
+    <workbookView windowWidth="20750" windowHeight="10480" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="七下拖课" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2050" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2212" uniqueCount="454">
   <si>
     <t>拖课统计表</t>
   </si>
@@ -1186,7 +1186,7 @@
   </si>
   <si>
     <t>语文老师：“祥懿，又是你~”
-下午课件吃午饭。
+下午课间吃午饭。
 爱吃番茄酱。</t>
   </si>
   <si>
@@ -1221,7 +1221,8 @@
     <t>郑致辰曾数次吃过“牛奶拌饭”，甚至还吃过一次“酸奶拌饭”，后又疑似出现石榴拌饭。</t>
   </si>
   <si>
-    <t>徐嘉明曾在数学课上用放大镜试图点燃纸巾，被称“物理学家”。</t>
+    <t>徐嘉明曾在数学课上用放大镜试图点燃纸巾，被称“物理学家”。
+徐嘉明创造“修正带陀螺”等，被称“发明家”。</t>
   </si>
   <si>
     <r>
@@ -1745,6 +1746,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
       <t>一段时间内，洪鑫洋很喜欢读《孙权劝学》和《木兰诗》，于是大家读的时候就开始把人物替换成“鑫洋”，如：</t>
     </r>
     <r>
@@ -2661,18 +2667,18 @@
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="黑体"/>
+      <charset val="134"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="62">
@@ -6158,29 +6164,65 @@
       <c r="II3" s="171"/>
       <c r="IJ3" s="170"/>
       <c r="IK3" s="171"/>
-      <c r="IL3" s="170"/>
-      <c r="IM3" s="171"/>
-      <c r="IN3" s="170"/>
-      <c r="IO3" s="171"/>
-      <c r="IP3" s="170"/>
-      <c r="IQ3" s="171"/>
-      <c r="IR3" s="170"/>
-      <c r="IS3" s="171"/>
-      <c r="IT3" s="170"/>
+      <c r="IL3" s="170" t="s">
+        <v>4</v>
+      </c>
+      <c r="IM3" s="171" t="s">
+        <v>3</v>
+      </c>
+      <c r="IN3" s="170" t="s">
+        <v>2</v>
+      </c>
+      <c r="IO3" s="171" t="s">
+        <v>3</v>
+      </c>
+      <c r="IP3" s="170" t="s">
+        <v>1</v>
+      </c>
+      <c r="IQ3" s="171" t="s">
+        <v>3</v>
+      </c>
+      <c r="IR3" s="170" t="s">
+        <v>2</v>
+      </c>
+      <c r="IS3" s="171" t="s">
+        <v>3</v>
+      </c>
+      <c r="IT3" s="170" t="s">
+        <v>1</v>
+      </c>
       <c r="IU3" s="171"/>
       <c r="IV3" s="170"/>
       <c r="IW3" s="171"/>
       <c r="IX3" s="170"/>
       <c r="IY3" s="171"/>
-      <c r="IZ3" s="170"/>
-      <c r="JA3" s="171"/>
-      <c r="JB3" s="170"/>
-      <c r="JC3" s="171"/>
-      <c r="JD3" s="170"/>
-      <c r="JE3" s="171"/>
-      <c r="JF3" s="170"/>
-      <c r="JG3" s="171"/>
-      <c r="JH3" s="170"/>
+      <c r="IZ3" s="170" t="s">
+        <v>4</v>
+      </c>
+      <c r="JA3" s="171" t="s">
+        <v>3</v>
+      </c>
+      <c r="JB3" s="170" t="s">
+        <v>2</v>
+      </c>
+      <c r="JC3" s="171" t="s">
+        <v>3</v>
+      </c>
+      <c r="JD3" s="170" t="s">
+        <v>1</v>
+      </c>
+      <c r="JE3" s="171" t="s">
+        <v>3</v>
+      </c>
+      <c r="JF3" s="170" t="s">
+        <v>2</v>
+      </c>
+      <c r="JG3" s="171" t="s">
+        <v>3</v>
+      </c>
+      <c r="JH3" s="170" t="s">
+        <v>1</v>
+      </c>
       <c r="JI3" s="171"/>
       <c r="JJ3" s="170"/>
       <c r="JK3" s="171"/>
@@ -7022,29 +7064,65 @@
       <c r="II5" s="177"/>
       <c r="IJ5" s="176"/>
       <c r="IK5" s="177"/>
-      <c r="IL5" s="176"/>
-      <c r="IM5" s="177"/>
-      <c r="IN5" s="176"/>
-      <c r="IO5" s="177"/>
-      <c r="IP5" s="176"/>
-      <c r="IQ5" s="177"/>
-      <c r="IR5" s="176"/>
-      <c r="IS5" s="177"/>
-      <c r="IT5" s="176"/>
+      <c r="IL5" s="176" t="s">
+        <v>2</v>
+      </c>
+      <c r="IM5" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IN5" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="IO5" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IP5" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="IQ5" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IR5" s="176" t="s">
+        <v>1</v>
+      </c>
+      <c r="IS5" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IT5" s="176" t="s">
+        <v>2</v>
+      </c>
       <c r="IU5" s="177"/>
       <c r="IV5" s="176"/>
       <c r="IW5" s="177"/>
       <c r="IX5" s="176"/>
       <c r="IY5" s="177"/>
-      <c r="IZ5" s="176"/>
-      <c r="JA5" s="177"/>
-      <c r="JB5" s="176"/>
-      <c r="JC5" s="177"/>
-      <c r="JD5" s="176"/>
-      <c r="JE5" s="177"/>
-      <c r="JF5" s="176"/>
-      <c r="JG5" s="177"/>
-      <c r="JH5" s="176"/>
+      <c r="IZ5" s="176" t="s">
+        <v>2</v>
+      </c>
+      <c r="JA5" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JB5" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="JC5" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JD5" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="JE5" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JF5" s="176" t="s">
+        <v>1</v>
+      </c>
+      <c r="JG5" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JH5" s="176" t="s">
+        <v>2</v>
+      </c>
       <c r="JI5" s="177"/>
       <c r="JJ5" s="176"/>
       <c r="JK5" s="177"/>
@@ -8181,29 +8259,65 @@
       <c r="II8" s="177"/>
       <c r="IJ8" s="181"/>
       <c r="IK8" s="177"/>
-      <c r="IL8" s="181"/>
-      <c r="IM8" s="177"/>
-      <c r="IN8" s="181"/>
-      <c r="IO8" s="177"/>
-      <c r="IP8" s="181"/>
-      <c r="IQ8" s="177"/>
-      <c r="IR8" s="181"/>
-      <c r="IS8" s="177"/>
-      <c r="IT8" s="181"/>
+      <c r="IL8" s="181" t="s">
+        <v>9</v>
+      </c>
+      <c r="IM8" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IN8" s="181" t="s">
+        <v>1</v>
+      </c>
+      <c r="IO8" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IP8" s="181" t="s">
+        <v>10</v>
+      </c>
+      <c r="IQ8" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IR8" s="181" t="s">
+        <v>11</v>
+      </c>
+      <c r="IS8" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IT8" s="181" t="s">
+        <v>12</v>
+      </c>
       <c r="IU8" s="177"/>
       <c r="IV8" s="181"/>
       <c r="IW8" s="177"/>
       <c r="IX8" s="181"/>
       <c r="IY8" s="177"/>
-      <c r="IZ8" s="181"/>
-      <c r="JA8" s="177"/>
-      <c r="JB8" s="181"/>
-      <c r="JC8" s="177"/>
-      <c r="JD8" s="181"/>
-      <c r="JE8" s="177"/>
-      <c r="JF8" s="181"/>
-      <c r="JG8" s="177"/>
-      <c r="JH8" s="181"/>
+      <c r="IZ8" s="181" t="s">
+        <v>9</v>
+      </c>
+      <c r="JA8" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JB8" s="181" t="s">
+        <v>1</v>
+      </c>
+      <c r="JC8" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JD8" s="181" t="s">
+        <v>10</v>
+      </c>
+      <c r="JE8" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JF8" s="181" t="s">
+        <v>11</v>
+      </c>
+      <c r="JG8" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JH8" s="181" t="s">
+        <v>12</v>
+      </c>
       <c r="JI8" s="177"/>
       <c r="JJ8" s="181"/>
       <c r="JK8" s="177"/>
@@ -9043,29 +9157,65 @@
       <c r="II10" s="177"/>
       <c r="IJ10" s="176"/>
       <c r="IK10" s="177"/>
-      <c r="IL10" s="176"/>
-      <c r="IM10" s="177"/>
-      <c r="IN10" s="176"/>
-      <c r="IO10" s="177"/>
-      <c r="IP10" s="176"/>
-      <c r="IQ10" s="177"/>
-      <c r="IR10" s="176"/>
-      <c r="IS10" s="177"/>
-      <c r="IT10" s="176"/>
+      <c r="IL10" s="176" t="s">
+        <v>1</v>
+      </c>
+      <c r="IM10" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IN10" s="176" t="s">
+        <v>9</v>
+      </c>
+      <c r="IO10" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IP10" s="176" t="s">
+        <v>2</v>
+      </c>
+      <c r="IQ10" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IR10" s="176" t="s">
+        <v>9</v>
+      </c>
+      <c r="IS10" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IT10" s="176" t="s">
+        <v>6</v>
+      </c>
       <c r="IU10" s="177"/>
       <c r="IV10" s="176"/>
       <c r="IW10" s="177"/>
       <c r="IX10" s="176"/>
       <c r="IY10" s="177"/>
-      <c r="IZ10" s="176"/>
-      <c r="JA10" s="177"/>
-      <c r="JB10" s="176"/>
-      <c r="JC10" s="177"/>
-      <c r="JD10" s="176"/>
-      <c r="JE10" s="177"/>
-      <c r="JF10" s="176"/>
-      <c r="JG10" s="177"/>
-      <c r="JH10" s="176"/>
+      <c r="IZ10" s="176" t="s">
+        <v>1</v>
+      </c>
+      <c r="JA10" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JB10" s="176" t="s">
+        <v>9</v>
+      </c>
+      <c r="JC10" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JD10" s="176" t="s">
+        <v>2</v>
+      </c>
+      <c r="JE10" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JF10" s="176" t="s">
+        <v>9</v>
+      </c>
+      <c r="JG10" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JH10" s="176" t="s">
+        <v>6</v>
+      </c>
       <c r="JI10" s="177"/>
       <c r="JJ10" s="176"/>
       <c r="JK10" s="177"/>
@@ -9903,29 +10053,65 @@
       <c r="II12" s="177"/>
       <c r="IJ12" s="176"/>
       <c r="IK12" s="177"/>
-      <c r="IL12" s="176"/>
-      <c r="IM12" s="177"/>
-      <c r="IN12" s="176"/>
-      <c r="IO12" s="177"/>
-      <c r="IP12" s="176"/>
-      <c r="IQ12" s="177"/>
-      <c r="IR12" s="176"/>
-      <c r="IS12" s="177"/>
-      <c r="IT12" s="176"/>
+      <c r="IL12" s="176" t="s">
+        <v>18</v>
+      </c>
+      <c r="IM12" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IN12" s="176" t="s">
+        <v>1</v>
+      </c>
+      <c r="IO12" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IP12" s="176" t="s">
+        <v>9</v>
+      </c>
+      <c r="IQ12" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IR12" s="176" t="s">
+        <v>2</v>
+      </c>
+      <c r="IS12" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IT12" s="176" t="s">
+        <v>2</v>
+      </c>
       <c r="IU12" s="177"/>
       <c r="IV12" s="176"/>
       <c r="IW12" s="177"/>
       <c r="IX12" s="176"/>
       <c r="IY12" s="177"/>
-      <c r="IZ12" s="176"/>
-      <c r="JA12" s="177"/>
-      <c r="JB12" s="176"/>
-      <c r="JC12" s="177"/>
-      <c r="JD12" s="176"/>
-      <c r="JE12" s="177"/>
-      <c r="JF12" s="176"/>
-      <c r="JG12" s="177"/>
-      <c r="JH12" s="176"/>
+      <c r="IZ12" s="176" t="s">
+        <v>18</v>
+      </c>
+      <c r="JA12" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JB12" s="176" t="s">
+        <v>1</v>
+      </c>
+      <c r="JC12" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JD12" s="176" t="s">
+        <v>9</v>
+      </c>
+      <c r="JE12" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JF12" s="176" t="s">
+        <v>2</v>
+      </c>
+      <c r="JG12" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JH12" s="176" t="s">
+        <v>2</v>
+      </c>
       <c r="JI12" s="177"/>
       <c r="JJ12" s="176"/>
       <c r="JK12" s="177"/>
@@ -10767,29 +10953,65 @@
       <c r="II14" s="177"/>
       <c r="IJ14" s="176"/>
       <c r="IK14" s="177"/>
-      <c r="IL14" s="176"/>
-      <c r="IM14" s="177"/>
-      <c r="IN14" s="176"/>
-      <c r="IO14" s="177"/>
-      <c r="IP14" s="176"/>
-      <c r="IQ14" s="177"/>
-      <c r="IR14" s="176"/>
-      <c r="IS14" s="177"/>
-      <c r="IT14" s="176"/>
+      <c r="IL14" s="176" t="s">
+        <v>14</v>
+      </c>
+      <c r="IM14" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IN14" s="176" t="s">
+        <v>19</v>
+      </c>
+      <c r="IO14" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IP14" s="176" t="s">
+        <v>1</v>
+      </c>
+      <c r="IQ14" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IR14" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="IS14" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IT14" s="176" t="s">
+        <v>14</v>
+      </c>
       <c r="IU14" s="177"/>
       <c r="IV14" s="176"/>
       <c r="IW14" s="177"/>
       <c r="IX14" s="176"/>
       <c r="IY14" s="177"/>
-      <c r="IZ14" s="176"/>
-      <c r="JA14" s="177"/>
-      <c r="JB14" s="176"/>
-      <c r="JC14" s="177"/>
-      <c r="JD14" s="176"/>
-      <c r="JE14" s="177"/>
-      <c r="JF14" s="176"/>
-      <c r="JG14" s="177"/>
-      <c r="JH14" s="176"/>
+      <c r="IZ14" s="176" t="s">
+        <v>14</v>
+      </c>
+      <c r="JA14" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JB14" s="176" t="s">
+        <v>19</v>
+      </c>
+      <c r="JC14" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JD14" s="176" t="s">
+        <v>1</v>
+      </c>
+      <c r="JE14" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JF14" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="JG14" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JH14" s="176" t="s">
+        <v>14</v>
+      </c>
       <c r="JI14" s="177"/>
       <c r="JJ14" s="176"/>
       <c r="JK14" s="177"/>
@@ -11637,29 +11859,65 @@
       <c r="II16" s="177"/>
       <c r="IJ16" s="176"/>
       <c r="IK16" s="177"/>
-      <c r="IL16" s="176"/>
-      <c r="IM16" s="177"/>
-      <c r="IN16" s="176"/>
-      <c r="IO16" s="177"/>
-      <c r="IP16" s="176"/>
-      <c r="IQ16" s="177"/>
-      <c r="IR16" s="176"/>
-      <c r="IS16" s="177"/>
-      <c r="IT16" s="176"/>
+      <c r="IL16" s="176" t="s">
+        <v>2</v>
+      </c>
+      <c r="IM16" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IN16" s="176" t="s">
+        <v>6</v>
+      </c>
+      <c r="IO16" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IP16" s="176" t="s">
+        <v>22</v>
+      </c>
+      <c r="IQ16" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IR16" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="IS16" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IT16" s="176" t="s">
+        <v>22</v>
+      </c>
       <c r="IU16" s="177"/>
       <c r="IV16" s="176"/>
       <c r="IW16" s="177"/>
       <c r="IX16" s="176"/>
       <c r="IY16" s="177"/>
-      <c r="IZ16" s="176"/>
-      <c r="JA16" s="177"/>
-      <c r="JB16" s="176"/>
-      <c r="JC16" s="177"/>
-      <c r="JD16" s="176"/>
-      <c r="JE16" s="177"/>
-      <c r="JF16" s="176"/>
-      <c r="JG16" s="177"/>
-      <c r="JH16" s="176"/>
+      <c r="IZ16" s="176" t="s">
+        <v>2</v>
+      </c>
+      <c r="JA16" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JB16" s="176" t="s">
+        <v>6</v>
+      </c>
+      <c r="JC16" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JD16" s="176" t="s">
+        <v>22</v>
+      </c>
+      <c r="JE16" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JF16" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="JG16" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JH16" s="176" t="s">
+        <v>22</v>
+      </c>
       <c r="JI16" s="177"/>
       <c r="JJ16" s="176"/>
       <c r="JK16" s="177"/>
@@ -12495,29 +12753,65 @@
       <c r="II18" s="177"/>
       <c r="IJ18" s="176"/>
       <c r="IK18" s="177"/>
-      <c r="IL18" s="176"/>
-      <c r="IM18" s="177"/>
-      <c r="IN18" s="176"/>
-      <c r="IO18" s="177"/>
-      <c r="IP18" s="176"/>
-      <c r="IQ18" s="177"/>
-      <c r="IR18" s="176"/>
-      <c r="IS18" s="177"/>
-      <c r="IT18" s="176"/>
+      <c r="IL18" s="176" t="s">
+        <v>18</v>
+      </c>
+      <c r="IM18" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IN18" s="176" t="s">
+        <v>2</v>
+      </c>
+      <c r="IO18" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IP18" s="176" t="s">
+        <v>1</v>
+      </c>
+      <c r="IQ18" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IR18" s="176" t="s">
+        <v>18</v>
+      </c>
+      <c r="IS18" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IT18" s="176" t="s">
+        <v>4</v>
+      </c>
       <c r="IU18" s="177"/>
       <c r="IV18" s="176"/>
       <c r="IW18" s="177"/>
       <c r="IX18" s="176"/>
       <c r="IY18" s="177"/>
-      <c r="IZ18" s="176"/>
-      <c r="JA18" s="177"/>
-      <c r="JB18" s="176"/>
-      <c r="JC18" s="177"/>
-      <c r="JD18" s="176"/>
-      <c r="JE18" s="177"/>
-      <c r="JF18" s="176"/>
-      <c r="JG18" s="177"/>
-      <c r="JH18" s="176"/>
+      <c r="IZ18" s="176" t="s">
+        <v>18</v>
+      </c>
+      <c r="JA18" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JB18" s="176" t="s">
+        <v>2</v>
+      </c>
+      <c r="JC18" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JD18" s="176" t="s">
+        <v>1</v>
+      </c>
+      <c r="JE18" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JF18" s="176" t="s">
+        <v>18</v>
+      </c>
+      <c r="JG18" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JH18" s="176" t="s">
+        <v>4</v>
+      </c>
       <c r="JI18" s="177"/>
       <c r="JJ18" s="176"/>
       <c r="JK18" s="177"/>
@@ -13325,29 +13619,65 @@
       <c r="II20" s="177"/>
       <c r="IJ20" s="176"/>
       <c r="IK20" s="177"/>
-      <c r="IL20" s="176"/>
-      <c r="IM20" s="177"/>
-      <c r="IN20" s="176"/>
-      <c r="IO20" s="177"/>
-      <c r="IP20" s="176"/>
-      <c r="IQ20" s="177"/>
-      <c r="IR20" s="176"/>
-      <c r="IS20" s="177"/>
-      <c r="IT20" s="176"/>
+      <c r="IL20" s="176" t="s">
+        <v>2</v>
+      </c>
+      <c r="IM20" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IN20" s="176" t="s">
+        <v>2</v>
+      </c>
+      <c r="IO20" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IP20" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="IQ20" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IR20" s="176" t="s">
+        <v>24</v>
+      </c>
+      <c r="IS20" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="IT20" s="176" t="s">
+        <v>2</v>
+      </c>
       <c r="IU20" s="177"/>
       <c r="IV20" s="176"/>
       <c r="IW20" s="177"/>
       <c r="IX20" s="176"/>
       <c r="IY20" s="177"/>
-      <c r="IZ20" s="176"/>
-      <c r="JA20" s="177"/>
-      <c r="JB20" s="176"/>
-      <c r="JC20" s="177"/>
-      <c r="JD20" s="176"/>
-      <c r="JE20" s="177"/>
-      <c r="JF20" s="176"/>
-      <c r="JG20" s="177"/>
-      <c r="JH20" s="176"/>
+      <c r="IZ20" s="176" t="s">
+        <v>2</v>
+      </c>
+      <c r="JA20" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JB20" s="176" t="s">
+        <v>2</v>
+      </c>
+      <c r="JC20" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JD20" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="JE20" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JF20" s="176" t="s">
+        <v>24</v>
+      </c>
+      <c r="JG20" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="JH20" s="176" t="s">
+        <v>2</v>
+      </c>
       <c r="JI20" s="177"/>
       <c r="JJ20" s="176"/>
       <c r="JK20" s="177"/>
@@ -14806,2758 +15136,3452 @@
     <mergeCell ref="JN23:JO23"/>
   </mergeCells>
   <conditionalFormatting sqref="GA3">
+    <cfRule type="containsBlanks" dxfId="0" priority="648">
+      <formula>LEN(TRIM(GA3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GI3">
+    <cfRule type="containsText" dxfId="1" priority="463" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GI3)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="462">
+      <formula>LEN(TRIM(GI3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GM3">
+    <cfRule type="containsText" dxfId="1" priority="461" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GM3)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="460">
+      <formula>LEN(TRIM(GM3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GO3">
+    <cfRule type="containsBlanks" dxfId="0" priority="558">
+      <formula>LEN(TRIM(GO3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GQ3">
+    <cfRule type="containsText" dxfId="1" priority="459" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GQ3)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="458">
+      <formula>LEN(TRIM(GQ3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HC3">
+    <cfRule type="containsBlanks" dxfId="0" priority="490">
+      <formula>LEN(TRIM(HC3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HM3">
+    <cfRule type="containsText" dxfId="1" priority="332" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HM3)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="331">
+      <formula>LEN(TRIM(HM3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HO3">
+    <cfRule type="containsText" dxfId="1" priority="330" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HO3)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="329">
+      <formula>LEN(TRIM(HO3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HQ3">
+    <cfRule type="containsText" dxfId="1" priority="328" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HQ3)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="327">
+      <formula>LEN(TRIM(HQ3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HS3">
+    <cfRule type="containsText" dxfId="1" priority="326" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HS3)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="325">
+      <formula>LEN(TRIM(HS3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IA3">
+    <cfRule type="containsText" dxfId="1" priority="234" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IA3)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="233">
+      <formula>LEN(TRIM(IA3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IC3">
+    <cfRule type="containsText" dxfId="1" priority="232" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IC3)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="231">
+      <formula>LEN(TRIM(IC3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IE3">
+    <cfRule type="containsText" dxfId="1" priority="230" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IE3)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="229">
+      <formula>LEN(TRIM(IE3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IO3">
+    <cfRule type="containsText" dxfId="1" priority="151" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IO3)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="150">
+      <formula>LEN(TRIM(IO3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IQ3">
+    <cfRule type="containsText" dxfId="1" priority="149" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IQ3)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="148">
+      <formula>LEN(TRIM(IQ3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IS3">
+    <cfRule type="containsText" dxfId="1" priority="147" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IS3)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="146">
+      <formula>LEN(TRIM(IS3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JC3">
+    <cfRule type="containsText" dxfId="1" priority="68" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JC3)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="67">
+      <formula>LEN(TRIM(JC3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JE3">
+    <cfRule type="containsText" dxfId="1" priority="66" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JE3)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="65">
+      <formula>LEN(TRIM(JE3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JG3">
+    <cfRule type="containsText" dxfId="1" priority="64" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JG3)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="63">
+      <formula>LEN(TRIM(JG3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DE5">
+    <cfRule type="containsText" dxfId="1" priority="935" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DE5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="934">
+      <formula>LEN(TRIM(DE5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DG5">
+    <cfRule type="containsText" dxfId="1" priority="933" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DG5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="932">
+      <formula>LEN(TRIM(DG5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DU5">
+    <cfRule type="containsText" dxfId="1" priority="873" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DU5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="872">
+      <formula>LEN(TRIM(DU5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EG5">
+    <cfRule type="containsText" dxfId="1" priority="836" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EG5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="835">
+      <formula>LEN(TRIM(EG5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="ES5">
+    <cfRule type="containsText" dxfId="1" priority="804" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",ES5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="803">
+      <formula>LEN(TRIM(ES5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EU5">
+    <cfRule type="containsText" dxfId="1" priority="786" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EU5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="785">
+      <formula>LEN(TRIM(EU5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EW5">
+    <cfRule type="containsText" dxfId="1" priority="773" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EW5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="772">
+      <formula>LEN(TRIM(EW5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FI5">
+    <cfRule type="containsText" dxfId="1" priority="747" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FI5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="746">
+      <formula>LEN(TRIM(FI5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FW5">
+    <cfRule type="containsText" dxfId="1" priority="692" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FW5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="691">
+      <formula>LEN(TRIM(FW5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FY5">
+    <cfRule type="containsText" dxfId="1" priority="601" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FY5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="600">
+      <formula>LEN(TRIM(FY5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GA5">
+    <cfRule type="containsText" dxfId="1" priority="631" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GA5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="630">
+      <formula>LEN(TRIM(GA5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GI5">
+    <cfRule type="containsText" dxfId="1" priority="457" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GI5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="456">
+      <formula>LEN(TRIM(GI5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GK5">
+    <cfRule type="containsText" dxfId="1" priority="435" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GK5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="434">
+      <formula>LEN(TRIM(GK5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GM5">
+    <cfRule type="containsText" dxfId="1" priority="433" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GM5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="432">
+      <formula>LEN(TRIM(GM5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GO5">
+    <cfRule type="containsText" dxfId="1" priority="555" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GO5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="554">
+      <formula>LEN(TRIM(GO5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GY5">
+    <cfRule type="containsText" dxfId="1" priority="526" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GY5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="525">
+      <formula>LEN(TRIM(GY5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HA5">
+    <cfRule type="containsText" dxfId="1" priority="465" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HA5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="464">
+      <formula>LEN(TRIM(HA5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HC5">
+    <cfRule type="containsText" dxfId="1" priority="487" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HC5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="486">
+      <formula>LEN(TRIM(HC5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HM5">
+    <cfRule type="containsText" dxfId="1" priority="268" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HM5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="267">
+      <formula>LEN(TRIM(HM5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HO5">
+    <cfRule type="containsText" dxfId="1" priority="270" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HO5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="269">
+      <formula>LEN(TRIM(HO5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HQ5">
+    <cfRule type="containsText" dxfId="1" priority="272" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HQ5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="271">
+      <formula>LEN(TRIM(HQ5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HS5">
+    <cfRule type="containsText" dxfId="1" priority="286" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HS5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="285">
+      <formula>LEN(TRIM(HS5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IA5">
+    <cfRule type="containsText" dxfId="1" priority="188" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IA5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="187">
+      <formula>LEN(TRIM(IA5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IC5">
+    <cfRule type="containsText" dxfId="1" priority="190" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IC5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="189">
+      <formula>LEN(TRIM(IC5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IE5">
+    <cfRule type="containsText" dxfId="1" priority="192" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IE5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="191">
+      <formula>LEN(TRIM(IE5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IO5">
+    <cfRule type="containsText" dxfId="1" priority="105" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IO5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="104">
+      <formula>LEN(TRIM(IO5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IQ5">
+    <cfRule type="containsText" dxfId="1" priority="107" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IQ5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="106">
+      <formula>LEN(TRIM(IQ5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IS5">
+    <cfRule type="containsText" dxfId="1" priority="109" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IS5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="108">
+      <formula>LEN(TRIM(IS5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JC5">
+    <cfRule type="containsText" dxfId="1" priority="22" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JC5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="21">
+      <formula>LEN(TRIM(JC5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JE5">
+    <cfRule type="containsText" dxfId="1" priority="24" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JE5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="23">
+      <formula>LEN(TRIM(JE5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JG5">
+    <cfRule type="containsText" dxfId="1" priority="26" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JG5)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="25">
+      <formula>LEN(TRIM(JG5))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DC8">
+    <cfRule type="containsText" dxfId="1" priority="955" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DC8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="954">
+      <formula>LEN(TRIM(DC8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DE8">
+    <cfRule type="containsText" dxfId="1" priority="937" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DE8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="936">
+      <formula>LEN(TRIM(DE8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DG8">
+    <cfRule type="containsText" dxfId="1" priority="931" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DG8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="930">
+      <formula>LEN(TRIM(DG8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DI8">
+    <cfRule type="containsText" dxfId="1" priority="909" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DI8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="908">
+      <formula>LEN(TRIM(DI8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DK8">
+    <cfRule type="containsText" dxfId="1" priority="907" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DK8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="906">
+      <formula>LEN(TRIM(DK8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DQ8">
+    <cfRule type="containsText" dxfId="1" priority="859" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DQ8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="858">
+      <formula>LEN(TRIM(DQ8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DS8">
+    <cfRule type="containsText" dxfId="1" priority="871" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DS8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="870">
+      <formula>LEN(TRIM(DS8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DU8">
+    <cfRule type="containsText" dxfId="1" priority="875" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DU8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="874">
+      <formula>LEN(TRIM(DU8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DW8">
+    <cfRule type="containsText" dxfId="1" priority="895" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DW8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="894">
+      <formula>LEN(TRIM(DW8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DY8">
+    <cfRule type="containsText" dxfId="1" priority="853" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DY8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="852">
+      <formula>LEN(TRIM(DY8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EE8">
+    <cfRule type="containsText" dxfId="1" priority="842" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EE8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="841">
+      <formula>LEN(TRIM(EE8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EG8">
+    <cfRule type="containsText" dxfId="1" priority="834" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EG8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="833">
+      <formula>LEN(TRIM(EG8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EQ8">
+    <cfRule type="containsText" dxfId="1" priority="816" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EQ8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="815">
+      <formula>LEN(TRIM(EQ8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="ES8">
+    <cfRule type="containsText" dxfId="1" priority="802" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",ES8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="801">
+      <formula>LEN(TRIM(ES8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EU8">
+    <cfRule type="containsText" dxfId="1" priority="784" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EU8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="783">
+      <formula>LEN(TRIM(EU8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EW8">
+    <cfRule type="containsText" dxfId="1" priority="771" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EW8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="770">
+      <formula>LEN(TRIM(EW8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FI8">
+    <cfRule type="containsText" dxfId="1" priority="745" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FI8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="744">
+      <formula>LEN(TRIM(FI8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FK8">
+    <cfRule type="containsText" dxfId="1" priority="725" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FK8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="724">
+      <formula>LEN(TRIM(FK8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FM8">
+    <cfRule type="containsText" dxfId="1" priority="708" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FM8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="707">
+      <formula>LEN(TRIM(FM8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FO8">
+    <cfRule type="containsText" dxfId="1" priority="706" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FO8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="705">
+      <formula>LEN(TRIM(FO8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FU8">
+    <cfRule type="containsText" dxfId="1" priority="694" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FU8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="693">
+      <formula>LEN(TRIM(FU8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FW8">
+    <cfRule type="containsText" dxfId="1" priority="690" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FW8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="689">
+      <formula>LEN(TRIM(FW8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FY8">
+    <cfRule type="containsText" dxfId="1" priority="603" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FY8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="602">
+      <formula>LEN(TRIM(FY8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GA8">
+    <cfRule type="containsText" dxfId="1" priority="633" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GA8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="632">
+      <formula>LEN(TRIM(GA8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GC8">
+    <cfRule type="containsText" dxfId="1" priority="629" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GC8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="628">
+      <formula>LEN(TRIM(GC8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GI8">
+    <cfRule type="containsText" dxfId="1" priority="455" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GI8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="454">
+      <formula>LEN(TRIM(GI8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GK8">
+    <cfRule type="containsText" dxfId="1" priority="592" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GK8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="591">
+      <formula>LEN(TRIM(GK8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GM8">
+    <cfRule type="containsText" dxfId="1" priority="431" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GM8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="430">
+      <formula>LEN(TRIM(GM8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GO8">
+    <cfRule type="containsText" dxfId="1" priority="557" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GO8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="556">
+      <formula>LEN(TRIM(GO8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GW8">
+    <cfRule type="containsText" dxfId="1" priority="528" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GW8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="527">
+      <formula>LEN(TRIM(GW8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GY8">
+    <cfRule type="containsText" dxfId="1" priority="524" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GY8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="523">
+      <formula>LEN(TRIM(GY8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HA8">
+    <cfRule type="containsText" dxfId="1" priority="467" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HA8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="466">
+      <formula>LEN(TRIM(HA8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HC8">
+    <cfRule type="containsText" dxfId="1" priority="489" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HC8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="488">
+      <formula>LEN(TRIM(HC8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HK8">
+    <cfRule type="containsText" dxfId="1" priority="324" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HK8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="323">
+      <formula>LEN(TRIM(HK8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HM8">
+    <cfRule type="containsText" dxfId="1" priority="266" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HM8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="265">
+      <formula>LEN(TRIM(HM8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HO8">
+    <cfRule type="containsText" dxfId="1" priority="264" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HO8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="263">
+      <formula>LEN(TRIM(HO8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HQ8">
+    <cfRule type="containsText" dxfId="1" priority="290" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HQ8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="289">
+      <formula>LEN(TRIM(HQ8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HS8">
+    <cfRule type="containsText" dxfId="1" priority="288" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HS8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="287">
+      <formula>LEN(TRIM(HS8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HY8">
+    <cfRule type="containsText" dxfId="1" priority="228" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HY8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="227">
+      <formula>LEN(TRIM(HY8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IA8">
+    <cfRule type="containsText" dxfId="1" priority="186" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IA8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="185">
+      <formula>LEN(TRIM(IA8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IC8">
+    <cfRule type="containsText" dxfId="1" priority="184" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IC8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="183">
+      <formula>LEN(TRIM(IC8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IE8">
+    <cfRule type="containsText" dxfId="1" priority="194" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IE8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="193">
+      <formula>LEN(TRIM(IE8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IM8">
+    <cfRule type="containsText" dxfId="1" priority="145" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IM8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="144">
+      <formula>LEN(TRIM(IM8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IO8">
+    <cfRule type="containsText" dxfId="1" priority="103" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IO8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="102">
+      <formula>LEN(TRIM(IO8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IQ8">
+    <cfRule type="containsText" dxfId="1" priority="101" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IQ8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="100">
+      <formula>LEN(TRIM(IQ8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IS8">
+    <cfRule type="containsText" dxfId="1" priority="111" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IS8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="110">
+      <formula>LEN(TRIM(IS8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JA8">
+    <cfRule type="containsText" dxfId="1" priority="62" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JA8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="61">
+      <formula>LEN(TRIM(JA8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JC8">
+    <cfRule type="containsText" dxfId="1" priority="20" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JC8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="19">
+      <formula>LEN(TRIM(JC8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JE8">
+    <cfRule type="containsText" dxfId="1" priority="18" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JE8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="17">
+      <formula>LEN(TRIM(JE8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JG8">
+    <cfRule type="containsText" dxfId="1" priority="28" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JG8)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="27">
+      <formula>LEN(TRIM(JG8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DE10">
+    <cfRule type="containsText" dxfId="1" priority="939" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DE10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="938">
+      <formula>LEN(TRIM(DE10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DI10">
+    <cfRule type="containsText" dxfId="1" priority="911" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DI10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="910">
+      <formula>LEN(TRIM(DI10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DK10">
+    <cfRule type="containsText" dxfId="1" priority="905" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DK10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="904">
+      <formula>LEN(TRIM(DK10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DQ10">
+    <cfRule type="containsText" dxfId="1" priority="861" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DQ10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="860">
+      <formula>LEN(TRIM(DQ10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DS10">
+    <cfRule type="containsText" dxfId="1" priority="869" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DS10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="868">
+      <formula>LEN(TRIM(DS10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DW10">
+    <cfRule type="containsText" dxfId="1" priority="893" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DW10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="892">
+      <formula>LEN(TRIM(DW10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DY10">
+    <cfRule type="containsText" dxfId="1" priority="851" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DY10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="850">
+      <formula>LEN(TRIM(DY10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EG10">
+    <cfRule type="containsText" dxfId="1" priority="832" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EG10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="831">
+      <formula>LEN(TRIM(EG10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EQ10">
+    <cfRule type="containsText" dxfId="1" priority="814" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EQ10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="813">
+      <formula>LEN(TRIM(EQ10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="ES10">
+    <cfRule type="containsText" dxfId="1" priority="800" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",ES10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="799">
+      <formula>LEN(TRIM(ES10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EU10">
+    <cfRule type="containsText" dxfId="1" priority="782" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EU10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="781">
+      <formula>LEN(TRIM(EU10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FI10">
+    <cfRule type="containsText" dxfId="1" priority="743" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FI10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="742">
+      <formula>LEN(TRIM(FI10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FK10">
+    <cfRule type="containsText" dxfId="1" priority="727" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FK10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="726">
+      <formula>LEN(TRIM(FK10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FM10">
+    <cfRule type="containsText" dxfId="1" priority="710" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FM10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="709">
+      <formula>LEN(TRIM(FM10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FO10">
+    <cfRule type="containsText" dxfId="1" priority="704" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FO10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="703">
+      <formula>LEN(TRIM(FO10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FU10">
+    <cfRule type="containsText" dxfId="1" priority="680" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FU10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="679">
+      <formula>LEN(TRIM(FU10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FW10">
+    <cfRule type="containsText" dxfId="1" priority="688" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FW10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="687">
+      <formula>LEN(TRIM(FW10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FY10">
+    <cfRule type="containsText" dxfId="1" priority="654" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FY10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="653">
+      <formula>LEN(TRIM(FY10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GA10">
+    <cfRule type="containsText" dxfId="1" priority="613" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GA10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="612">
+      <formula>LEN(TRIM(GA10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GC10">
+    <cfRule type="containsText" dxfId="1" priority="627" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GC10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="626">
+      <formula>LEN(TRIM(GC10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GI10">
+    <cfRule type="containsText" dxfId="1" priority="453" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GI10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="452">
+      <formula>LEN(TRIM(GI10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GK10">
+    <cfRule type="containsText" dxfId="1" priority="437" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GK10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="436">
+      <formula>LEN(TRIM(GK10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GM10">
+    <cfRule type="containsText" dxfId="1" priority="429" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GM10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="428">
+      <formula>LEN(TRIM(GM10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GO10">
+    <cfRule type="containsText" dxfId="1" priority="403" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GO10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="402">
+      <formula>LEN(TRIM(GO10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GW10">
+    <cfRule type="containsText" dxfId="1" priority="514" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GW10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="513">
+      <formula>LEN(TRIM(GW10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GY10">
+    <cfRule type="containsText" dxfId="1" priority="522" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GY10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="521">
+      <formula>LEN(TRIM(GY10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HA10">
+    <cfRule type="containsText" dxfId="1" priority="494" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HA10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="493">
+      <formula>LEN(TRIM(HA10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HC10">
+    <cfRule type="containsText" dxfId="1" priority="477" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HC10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="476">
+      <formula>LEN(TRIM(HC10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HK10">
+    <cfRule type="containsText" dxfId="1" priority="322" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HK10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="321">
+      <formula>LEN(TRIM(HK10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HM10">
+    <cfRule type="containsText" dxfId="1" priority="248" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HM10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="247">
+      <formula>LEN(TRIM(HM10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HO10">
+    <cfRule type="containsText" dxfId="1" priority="262" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HO10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="261">
+      <formula>LEN(TRIM(HO10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HQ10">
+    <cfRule type="containsText" dxfId="1" priority="292" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HQ10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="291">
+      <formula>LEN(TRIM(HQ10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HS10">
+    <cfRule type="containsText" dxfId="1" priority="284" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HS10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="283">
+      <formula>LEN(TRIM(HS10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HY10">
+    <cfRule type="containsText" dxfId="1" priority="226" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HY10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="225">
+      <formula>LEN(TRIM(HY10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IA10">
+    <cfRule type="containsText" dxfId="1" priority="168" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IA10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="167">
+      <formula>LEN(TRIM(IA10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IC10">
+    <cfRule type="containsText" dxfId="1" priority="182" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IC10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="181">
+      <formula>LEN(TRIM(IC10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IE10">
+    <cfRule type="containsText" dxfId="1" priority="196" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IE10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="195">
+      <formula>LEN(TRIM(IE10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IM10">
+    <cfRule type="containsText" dxfId="1" priority="143" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IM10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="142">
+      <formula>LEN(TRIM(IM10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IO10">
+    <cfRule type="containsText" dxfId="1" priority="85" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IO10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="84">
+      <formula>LEN(TRIM(IO10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IQ10">
+    <cfRule type="containsText" dxfId="1" priority="99" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IQ10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="98">
+      <formula>LEN(TRIM(IQ10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IS10">
+    <cfRule type="containsText" dxfId="1" priority="113" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IS10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="112">
+      <formula>LEN(TRIM(IS10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JA10">
+    <cfRule type="containsText" dxfId="1" priority="60" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JA10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="59">
+      <formula>LEN(TRIM(JA10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JC10">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JC10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(JC10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JE10">
+    <cfRule type="containsText" dxfId="1" priority="16" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JE10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="15">
+      <formula>LEN(TRIM(JE10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JG10">
+    <cfRule type="containsText" dxfId="1" priority="30" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JG10)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="29">
+      <formula>LEN(TRIM(JG10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CR11">
+    <cfRule type="containsText" dxfId="1" priority="963" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",CR11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CT11">
+    <cfRule type="containsText" dxfId="1" priority="962" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",CT11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DX11">
+    <cfRule type="containsText" dxfId="1" priority="854" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DX11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EF11">
+    <cfRule type="containsText" dxfId="1" priority="843" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EF11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="ET11">
+    <cfRule type="containsText" dxfId="1" priority="787" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",ET11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EV11">
+    <cfRule type="containsText" dxfId="1" priority="774" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EV11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FI11">
+    <cfRule type="containsText" dxfId="2" priority="750" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",FI11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FV11">
+    <cfRule type="containsText" dxfId="1" priority="668" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FV11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FX11">
+    <cfRule type="containsText" dxfId="1" priority="663" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FX11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FY11">
+    <cfRule type="containsText" dxfId="2" priority="667" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",FY11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GJ11">
+    <cfRule type="containsText" dxfId="1" priority="570" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GJ11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GL11">
+    <cfRule type="containsText" dxfId="1" priority="565" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GL11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GM11">
+    <cfRule type="containsText" dxfId="2" priority="569" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",GM11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GX11">
+    <cfRule type="containsText" dxfId="1" priority="502" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GX11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GZ11">
+    <cfRule type="containsText" dxfId="1" priority="497" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GZ11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HA11">
+    <cfRule type="containsText" dxfId="2" priority="501" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",HA11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HL11">
+    <cfRule type="containsText" dxfId="1" priority="372" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HL11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HN11">
+    <cfRule type="containsText" dxfId="1" priority="367" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HN11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HO11">
+    <cfRule type="containsText" dxfId="2" priority="371" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",HO11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HZ11">
+    <cfRule type="containsText" dxfId="1" priority="242" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HZ11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IB11">
+    <cfRule type="containsText" dxfId="1" priority="238" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IB11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IC11">
+    <cfRule type="containsText" dxfId="2" priority="241" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",IC11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IN11">
+    <cfRule type="containsText" dxfId="1" priority="159" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IN11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IP11">
+    <cfRule type="containsText" dxfId="1" priority="155" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IP11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IQ11">
+    <cfRule type="containsText" dxfId="2" priority="158" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",IQ11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IU11">
+    <cfRule type="containsText" dxfId="2" priority="166" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",IU11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JB11">
+    <cfRule type="containsText" dxfId="1" priority="76" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JB11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JD11">
+    <cfRule type="containsText" dxfId="1" priority="72" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JD11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JE11">
+    <cfRule type="containsText" dxfId="2" priority="75" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",JE11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JI11">
+    <cfRule type="containsText" dxfId="2" priority="83" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",JI11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DC12">
+    <cfRule type="containsText" dxfId="1" priority="953" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DC12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="952">
+      <formula>LEN(TRIM(DC12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DE12">
+    <cfRule type="containsText" dxfId="1" priority="941" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DE12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="940">
+      <formula>LEN(TRIM(DE12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DG12">
+    <cfRule type="containsText" dxfId="1" priority="929" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DG12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="928">
+      <formula>LEN(TRIM(DG12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DI12">
+    <cfRule type="containsText" dxfId="1" priority="913" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DI12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="912">
+      <formula>LEN(TRIM(DI12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DQ12">
+    <cfRule type="containsText" dxfId="1" priority="865" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DQ12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="864">
+      <formula>LEN(TRIM(DQ12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DS12">
+    <cfRule type="containsText" dxfId="1" priority="867" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DS12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="866">
+      <formula>LEN(TRIM(DS12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DU12">
+    <cfRule type="containsText" dxfId="1" priority="877" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DU12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="876">
+      <formula>LEN(TRIM(DU12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DW12">
+    <cfRule type="containsText" dxfId="1" priority="891" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DW12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="890">
+      <formula>LEN(TRIM(DW12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EE12">
+    <cfRule type="containsText" dxfId="1" priority="840" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EE12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="839">
+      <formula>LEN(TRIM(EE12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EG12">
+    <cfRule type="containsText" dxfId="1" priority="830" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EG12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="829">
+      <formula>LEN(TRIM(EG12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EQ12">
+    <cfRule type="containsText" dxfId="1" priority="812" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EQ12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="811">
+      <formula>LEN(TRIM(EQ12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="ES12">
+    <cfRule type="containsText" dxfId="1" priority="798" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",ES12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="797">
+      <formula>LEN(TRIM(ES12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EU12">
+    <cfRule type="containsText" dxfId="1" priority="780" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EU12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="779">
+      <formula>LEN(TRIM(EU12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EW12">
+    <cfRule type="containsText" dxfId="1" priority="769" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EW12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="768">
+      <formula>LEN(TRIM(EW12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FI12">
+    <cfRule type="containsText" dxfId="1" priority="741" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FI12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="740">
+      <formula>LEN(TRIM(FI12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FK12">
+    <cfRule type="containsText" dxfId="1" priority="729" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FK12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="728">
+      <formula>LEN(TRIM(FK12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FM12">
+    <cfRule type="containsText" dxfId="1" priority="712" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FM12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="711">
+      <formula>LEN(TRIM(FM12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FU12">
+    <cfRule type="containsText" dxfId="1" priority="678" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FU12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="677">
+      <formula>LEN(TRIM(FU12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FW12">
+    <cfRule type="containsText" dxfId="1" priority="686" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FW12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="685">
+      <formula>LEN(TRIM(FW12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FY12">
+    <cfRule type="containsText" dxfId="1" priority="609" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FY12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="608">
+      <formula>LEN(TRIM(FY12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GA12">
+    <cfRule type="containsText" dxfId="1" priority="611" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GA12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="610">
+      <formula>LEN(TRIM(GA12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GI12">
+    <cfRule type="containsText" dxfId="1" priority="451" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GI12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="450">
+      <formula>LEN(TRIM(GI12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GK12">
+    <cfRule type="containsText" dxfId="1" priority="439" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GK12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="438">
+      <formula>LEN(TRIM(GK12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GM12">
+    <cfRule type="containsText" dxfId="1" priority="427" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GM12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="426">
+      <formula>LEN(TRIM(GM12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GO12">
+    <cfRule type="containsText" dxfId="1" priority="405" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GO12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="404">
+      <formula>LEN(TRIM(GO12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GQ12">
+    <cfRule type="containsText" dxfId="1" priority="411" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GQ12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="410">
+      <formula>LEN(TRIM(GQ12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GW12">
+    <cfRule type="containsText" dxfId="1" priority="512" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GW12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="511">
+      <formula>LEN(TRIM(GW12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GY12">
+    <cfRule type="containsText" dxfId="1" priority="520" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GY12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="519">
+      <formula>LEN(TRIM(GY12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HA12">
+    <cfRule type="containsText" dxfId="1" priority="473" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HA12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="472">
+      <formula>LEN(TRIM(HA12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HC12">
+    <cfRule type="containsText" dxfId="1" priority="475" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HC12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="474">
+      <formula>LEN(TRIM(HC12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HK12">
+    <cfRule type="containsText" dxfId="1" priority="320" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HK12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="319">
+      <formula>LEN(TRIM(HK12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HM12">
+    <cfRule type="containsText" dxfId="1" priority="250" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HM12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="249">
+      <formula>LEN(TRIM(HM12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HO12">
+    <cfRule type="containsText" dxfId="1" priority="260" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HO12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="259">
+      <formula>LEN(TRIM(HO12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HQ12">
+    <cfRule type="containsText" dxfId="1" priority="294" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HQ12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="293">
+      <formula>LEN(TRIM(HQ12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HS12">
+    <cfRule type="containsText" dxfId="1" priority="282" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HS12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="281">
+      <formula>LEN(TRIM(HS12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HY12">
+    <cfRule type="containsText" dxfId="1" priority="224" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HY12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="223">
+      <formula>LEN(TRIM(HY12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IA12">
+    <cfRule type="containsText" dxfId="1" priority="170" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IA12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="169">
+      <formula>LEN(TRIM(IA12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IC12">
+    <cfRule type="containsText" dxfId="1" priority="180" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IC12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="179">
+      <formula>LEN(TRIM(IC12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IE12">
+    <cfRule type="containsText" dxfId="1" priority="198" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IE12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="197">
+      <formula>LEN(TRIM(IE12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IM12">
+    <cfRule type="containsText" dxfId="1" priority="141" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IM12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="140">
+      <formula>LEN(TRIM(IM12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IO12">
+    <cfRule type="containsText" dxfId="1" priority="87" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IO12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="86">
+      <formula>LEN(TRIM(IO12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IQ12">
+    <cfRule type="containsText" dxfId="1" priority="97" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IQ12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="96">
+      <formula>LEN(TRIM(IQ12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IS12">
+    <cfRule type="containsText" dxfId="1" priority="115" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IS12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="114">
+      <formula>LEN(TRIM(IS12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JA12">
+    <cfRule type="containsText" dxfId="1" priority="58" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JA12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="57">
+      <formula>LEN(TRIM(JA12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JC12">
+    <cfRule type="containsText" dxfId="1" priority="4" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JC12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="3">
+      <formula>LEN(TRIM(JC12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JE12">
+    <cfRule type="containsText" dxfId="1" priority="14" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JE12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="13">
+      <formula>LEN(TRIM(JE12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JG12">
+    <cfRule type="containsText" dxfId="1" priority="32" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JG12)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="31">
+      <formula>LEN(TRIM(JG12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DC14">
+    <cfRule type="containsText" dxfId="1" priority="951" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DC14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="950">
+      <formula>LEN(TRIM(DC14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DE14">
+    <cfRule type="containsText" dxfId="1" priority="943" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DE14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="942">
+      <formula>LEN(TRIM(DE14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DI14">
+    <cfRule type="containsText" dxfId="1" priority="915" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DI14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="914">
+      <formula>LEN(TRIM(DI14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DK14">
+    <cfRule type="containsText" dxfId="1" priority="903" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DK14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="902">
+      <formula>LEN(TRIM(DK14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DQ14">
+    <cfRule type="containsText" dxfId="1" priority="863" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DQ14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="862">
+      <formula>LEN(TRIM(DQ14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DS14">
+    <cfRule type="containsText" dxfId="1" priority="879" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DS14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="878">
+      <formula>LEN(TRIM(DS14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DW14">
+    <cfRule type="containsText" dxfId="1" priority="889" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DW14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="888">
+      <formula>LEN(TRIM(DW14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DY14">
+    <cfRule type="containsText" dxfId="1" priority="849" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DY14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="848">
+      <formula>LEN(TRIM(DY14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EE14">
+    <cfRule type="containsText" dxfId="1" priority="838" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EE14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="837">
+      <formula>LEN(TRIM(EE14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EG14">
+    <cfRule type="containsText" dxfId="1" priority="828" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EG14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="827">
+      <formula>LEN(TRIM(EG14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EM14">
+    <cfRule type="containsText" dxfId="1" priority="822" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EM14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="821">
+      <formula>LEN(TRIM(EM14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EQ14">
+    <cfRule type="containsText" dxfId="1" priority="810" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EQ14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="809">
+      <formula>LEN(TRIM(EQ14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="ES14">
+    <cfRule type="containsText" dxfId="1" priority="796" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",ES14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="795">
+      <formula>LEN(TRIM(ES14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EU14">
+    <cfRule type="containsText" dxfId="1" priority="778" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EU14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="777">
+      <formula>LEN(TRIM(EU14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FI14">
+    <cfRule type="containsText" dxfId="1" priority="739" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FI14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="738">
+      <formula>LEN(TRIM(FI14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FK14">
+    <cfRule type="containsText" dxfId="1" priority="731" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FK14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="730">
+      <formula>LEN(TRIM(FK14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FM14">
+    <cfRule type="containsText" dxfId="1" priority="714" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FM14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="713">
+      <formula>LEN(TRIM(FM14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FO14">
+    <cfRule type="containsText" dxfId="1" priority="702" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FO14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="701">
+      <formula>LEN(TRIM(FO14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FU14">
+    <cfRule type="containsText" dxfId="1" priority="676" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FU14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="675">
+      <formula>LEN(TRIM(FU14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FW14">
+    <cfRule type="containsText" dxfId="1" priority="684" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FW14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="683">
+      <formula>LEN(TRIM(FW14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FY14">
+    <cfRule type="containsText" dxfId="1" priority="607" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FY14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="606">
+      <formula>LEN(TRIM(FY14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GA14">
+    <cfRule type="containsText" dxfId="1" priority="615" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GA14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="614">
+      <formula>LEN(TRIM(GA14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GC14">
+    <cfRule type="containsText" dxfId="1" priority="625" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GC14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="624">
+      <formula>LEN(TRIM(GC14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GI14">
+    <cfRule type="containsText" dxfId="1" priority="449" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GI14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="448">
+      <formula>LEN(TRIM(GI14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GK14">
+    <cfRule type="containsText" dxfId="1" priority="441" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GK14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="440">
+      <formula>LEN(TRIM(GK14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GM14">
+    <cfRule type="containsText" dxfId="1" priority="425" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GM14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="424">
+      <formula>LEN(TRIM(GM14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GO14">
+    <cfRule type="containsText" dxfId="1" priority="407" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GO14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="406">
+      <formula>LEN(TRIM(GO14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GQ14">
+    <cfRule type="containsText" dxfId="1" priority="413" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GQ14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="412">
+      <formula>LEN(TRIM(GQ14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GW14">
+    <cfRule type="containsText" dxfId="1" priority="510" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GW14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="509">
+      <formula>LEN(TRIM(GW14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GY14">
+    <cfRule type="containsText" dxfId="1" priority="518" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GY14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="517">
+      <formula>LEN(TRIM(GY14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HA14">
+    <cfRule type="containsText" dxfId="1" priority="471" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HA14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="470">
+      <formula>LEN(TRIM(HA14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HC14">
+    <cfRule type="containsText" dxfId="1" priority="479" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HC14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="478">
+      <formula>LEN(TRIM(HC14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HK14">
+    <cfRule type="containsText" dxfId="1" priority="318" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HK14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="317">
+      <formula>LEN(TRIM(HK14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HM14">
+    <cfRule type="containsText" dxfId="1" priority="252" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HM14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="251">
+      <formula>LEN(TRIM(HM14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HO14">
+    <cfRule type="containsText" dxfId="1" priority="258" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HO14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="257">
+      <formula>LEN(TRIM(HO14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HQ14">
+    <cfRule type="containsText" dxfId="1" priority="296" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HQ14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="295">
+      <formula>LEN(TRIM(HQ14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HS14">
+    <cfRule type="containsText" dxfId="1" priority="280" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HS14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="279">
+      <formula>LEN(TRIM(HS14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HY14">
+    <cfRule type="containsText" dxfId="1" priority="222" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HY14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="221">
+      <formula>LEN(TRIM(HY14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IA14">
+    <cfRule type="containsText" dxfId="1" priority="172" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IA14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="171">
+      <formula>LEN(TRIM(IA14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IC14">
+    <cfRule type="containsText" dxfId="1" priority="178" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IC14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="177">
+      <formula>LEN(TRIM(IC14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IE14">
+    <cfRule type="containsText" dxfId="1" priority="200" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IE14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="199">
+      <formula>LEN(TRIM(IE14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IM14">
+    <cfRule type="containsText" dxfId="1" priority="139" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IM14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="138">
+      <formula>LEN(TRIM(IM14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IO14">
+    <cfRule type="containsText" dxfId="1" priority="89" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IO14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="88">
+      <formula>LEN(TRIM(IO14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IQ14">
+    <cfRule type="containsText" dxfId="1" priority="95" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IQ14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="94">
+      <formula>LEN(TRIM(IQ14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IS14">
+    <cfRule type="containsText" dxfId="1" priority="117" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IS14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="116">
+      <formula>LEN(TRIM(IS14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JA14">
+    <cfRule type="containsText" dxfId="1" priority="56" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JA14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="55">
+      <formula>LEN(TRIM(JA14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JC14">
+    <cfRule type="containsText" dxfId="1" priority="6" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JC14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="5">
+      <formula>LEN(TRIM(JC14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JE14">
+    <cfRule type="containsText" dxfId="1" priority="12" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JE14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="11">
+      <formula>LEN(TRIM(JE14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JG14">
+    <cfRule type="containsText" dxfId="1" priority="34" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JG14)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="33">
+      <formula>LEN(TRIM(JG14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DE16">
+    <cfRule type="containsText" dxfId="1" priority="945" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DE16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="944">
+      <formula>LEN(TRIM(DE16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DG16">
+    <cfRule type="containsText" dxfId="1" priority="927" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DG16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="926">
+      <formula>LEN(TRIM(DG16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DI16">
+    <cfRule type="containsText" dxfId="1" priority="917" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DI16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="916">
+      <formula>LEN(TRIM(DI16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DK16">
+    <cfRule type="containsText" dxfId="1" priority="901" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DK16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="900">
+      <formula>LEN(TRIM(DK16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DS16">
+    <cfRule type="containsText" dxfId="1" priority="881" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DS16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="880">
+      <formula>LEN(TRIM(DS16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DU16">
+    <cfRule type="containsText" dxfId="1" priority="885" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DU16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="884">
+      <formula>LEN(TRIM(DU16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DW16">
+    <cfRule type="containsText" dxfId="1" priority="887" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DW16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="886">
+      <formula>LEN(TRIM(DW16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EG16">
+    <cfRule type="containsText" dxfId="1" priority="826" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EG16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="825">
+      <formula>LEN(TRIM(EG16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EM16">
+    <cfRule type="containsText" dxfId="1" priority="820" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EM16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="819">
+      <formula>LEN(TRIM(EM16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EQ16">
+    <cfRule type="containsText" dxfId="1" priority="808" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EQ16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="807">
+      <formula>LEN(TRIM(EQ16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="ES16">
+    <cfRule type="containsText" dxfId="1" priority="794" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",ES16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="793">
+      <formula>LEN(TRIM(ES16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EU16">
+    <cfRule type="containsText" dxfId="1" priority="776" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EU16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="775">
+      <formula>LEN(TRIM(EU16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FI16">
+    <cfRule type="containsText" dxfId="1" priority="737" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FI16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="736">
+      <formula>LEN(TRIM(FI16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FM16">
+    <cfRule type="containsText" dxfId="1" priority="716" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FM16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="715">
+      <formula>LEN(TRIM(FM16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FO16">
+    <cfRule type="containsText" dxfId="1" priority="700" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FO16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="699">
+      <formula>LEN(TRIM(FO16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FU16">
+    <cfRule type="containsText" dxfId="1" priority="674" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FU16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="673">
+      <formula>LEN(TRIM(FU16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FW16">
+    <cfRule type="containsText" dxfId="1" priority="682" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FW16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="681">
+      <formula>LEN(TRIM(FW16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GA16">
+    <cfRule type="containsText" dxfId="1" priority="619" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GA16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="618">
+      <formula>LEN(TRIM(GA16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GI16">
+    <cfRule type="containsText" dxfId="1" priority="576" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GI16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="575">
+      <formula>LEN(TRIM(GI16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GK16">
+    <cfRule type="containsText" dxfId="1" priority="443" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GK16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="442">
+      <formula>LEN(TRIM(GK16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GM16">
+    <cfRule type="containsBlanks" dxfId="0" priority="567">
+      <formula>LEN(TRIM(GM16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GO16">
+    <cfRule type="containsText" dxfId="1" priority="409" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GO16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="408">
+      <formula>LEN(TRIM(GO16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GW16">
+    <cfRule type="containsText" dxfId="1" priority="508" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GW16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="507">
+      <formula>LEN(TRIM(GW16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GY16">
+    <cfRule type="containsText" dxfId="1" priority="516" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GY16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="515">
+      <formula>LEN(TRIM(GY16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HC16">
+    <cfRule type="containsText" dxfId="1" priority="483" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HC16)))</formula>
+    </cfRule>
     <cfRule type="containsBlanks" dxfId="0" priority="482">
-      <formula>LEN(TRIM(GA3))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GI3">
-    <cfRule type="containsText" dxfId="1" priority="297" operator="between" text="—">
+      <formula>LEN(TRIM(HC16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HK16">
+    <cfRule type="containsText" dxfId="1" priority="316" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HK16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="315">
+      <formula>LEN(TRIM(HK16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HM16">
+    <cfRule type="containsText" dxfId="1" priority="254" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HM16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="253">
+      <formula>LEN(TRIM(HM16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HO16">
+    <cfRule type="containsText" dxfId="1" priority="256" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HO16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="255">
+      <formula>LEN(TRIM(HO16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HQ16">
+    <cfRule type="containsText" dxfId="1" priority="298" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HQ16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="297">
+      <formula>LEN(TRIM(HQ16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HS16">
+    <cfRule type="containsText" dxfId="1" priority="278" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HS16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="277">
+      <formula>LEN(TRIM(HS16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HY16">
+    <cfRule type="containsText" dxfId="1" priority="220" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HY16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="219">
+      <formula>LEN(TRIM(HY16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IA16">
+    <cfRule type="containsText" dxfId="1" priority="174" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IA16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="173">
+      <formula>LEN(TRIM(IA16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IC16">
+    <cfRule type="containsText" dxfId="1" priority="176" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IC16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="175">
+      <formula>LEN(TRIM(IC16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IE16">
+    <cfRule type="containsText" dxfId="1" priority="202" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IE16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="201">
+      <formula>LEN(TRIM(IE16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IM16">
+    <cfRule type="containsText" dxfId="1" priority="137" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IM16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="136">
+      <formula>LEN(TRIM(IM16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IO16">
+    <cfRule type="containsText" dxfId="1" priority="91" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IO16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="90">
+      <formula>LEN(TRIM(IO16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IQ16">
+    <cfRule type="containsText" dxfId="1" priority="93" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IQ16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="92">
+      <formula>LEN(TRIM(IQ16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IS16">
+    <cfRule type="containsText" dxfId="1" priority="119" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IS16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="118">
+      <formula>LEN(TRIM(IS16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JA16">
+    <cfRule type="containsText" dxfId="1" priority="54" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JA16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="53">
+      <formula>LEN(TRIM(JA16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JC16">
+    <cfRule type="containsText" dxfId="1" priority="8" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JC16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="7">
+      <formula>LEN(TRIM(JC16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JE16">
+    <cfRule type="containsText" dxfId="1" priority="10" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JE16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="9">
+      <formula>LEN(TRIM(JE16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JG16">
+    <cfRule type="containsText" dxfId="1" priority="36" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JG16)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="35">
+      <formula>LEN(TRIM(JG16))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DE18">
+    <cfRule type="containsText" dxfId="1" priority="947" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DE18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="946">
+      <formula>LEN(TRIM(DE18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DG18">
+    <cfRule type="containsText" dxfId="1" priority="925" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DG18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="924">
+      <formula>LEN(TRIM(DG18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DI18">
+    <cfRule type="containsText" dxfId="1" priority="919" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DI18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="918">
+      <formula>LEN(TRIM(DI18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DK18">
+    <cfRule type="containsText" dxfId="1" priority="899" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DK18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="898">
+      <formula>LEN(TRIM(DK18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DQ18">
+    <cfRule type="containsText" dxfId="1" priority="857" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DQ18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="856">
+      <formula>LEN(TRIM(DQ18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DY18">
+    <cfRule type="containsText" dxfId="1" priority="847" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DY18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="846">
+      <formula>LEN(TRIM(DY18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EG18">
+    <cfRule type="containsText" dxfId="1" priority="824" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EG18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="823">
+      <formula>LEN(TRIM(EG18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EM18">
+    <cfRule type="containsText" dxfId="1" priority="818" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EM18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="817">
+      <formula>LEN(TRIM(EM18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EQ18">
+    <cfRule type="containsText" dxfId="1" priority="806" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EQ18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="805">
+      <formula>LEN(TRIM(EQ18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="ES18">
+    <cfRule type="containsText" dxfId="1" priority="792" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",ES18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="791">
+      <formula>LEN(TRIM(ES18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EW18">
+    <cfRule type="containsText" dxfId="1" priority="767" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EW18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="766">
+      <formula>LEN(TRIM(EW18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FK18">
+    <cfRule type="containsText" dxfId="1" priority="735" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FK18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="734">
+      <formula>LEN(TRIM(FK18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FM18">
+    <cfRule type="containsText" dxfId="1" priority="718" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FM18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="717">
+      <formula>LEN(TRIM(FM18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FO18">
+    <cfRule type="containsText" dxfId="1" priority="698" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FO18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="697">
+      <formula>LEN(TRIM(FO18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FU18">
+    <cfRule type="containsText" dxfId="1" priority="672" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FU18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="671">
+      <formula>LEN(TRIM(FU18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FY18">
+    <cfRule type="containsText" dxfId="1" priority="662" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FY18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="661">
+      <formula>LEN(TRIM(FY18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GA18">
+    <cfRule type="containsText" dxfId="1" priority="621" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GA18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="620">
+      <formula>LEN(TRIM(GA18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GC18">
+    <cfRule type="containsText" dxfId="1" priority="623" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GC18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="622">
+      <formula>LEN(TRIM(GC18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GI18">
+    <cfRule type="containsText" dxfId="1" priority="447" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GI18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="446">
+      <formula>LEN(TRIM(GI18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GM18">
+    <cfRule type="containsText" dxfId="1" priority="423" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GM18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="422">
+      <formula>LEN(TRIM(GM18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GO18">
+    <cfRule type="containsText" dxfId="1" priority="417" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GO18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="416">
+      <formula>LEN(TRIM(GO18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GQ18">
+    <cfRule type="containsText" dxfId="1" priority="415" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GQ18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="414">
+      <formula>LEN(TRIM(GQ18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GW18">
+    <cfRule type="containsText" dxfId="1" priority="506" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GW18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="505">
+      <formula>LEN(TRIM(GW18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HA18">
+    <cfRule type="containsText" dxfId="1" priority="496" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HA18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="495">
+      <formula>LEN(TRIM(HA18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HC18">
+    <cfRule type="containsText" dxfId="1" priority="485" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HC18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="484">
+      <formula>LEN(TRIM(HC18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HK18">
+    <cfRule type="containsText" dxfId="1" priority="312" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HK18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="311">
+      <formula>LEN(TRIM(HK18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HM18">
+    <cfRule type="containsText" dxfId="1" priority="308" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HM18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="307">
+      <formula>LEN(TRIM(HM18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HO18">
+    <cfRule type="containsText" dxfId="1" priority="304" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HO18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="303">
+      <formula>LEN(TRIM(HO18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HQ18">
+    <cfRule type="containsText" dxfId="1" priority="300" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HQ18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="299">
+      <formula>LEN(TRIM(HQ18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HS18">
+    <cfRule type="containsText" dxfId="1" priority="276" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HS18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="275">
+      <formula>LEN(TRIM(HS18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HY18">
+    <cfRule type="containsText" dxfId="1" priority="216" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HY18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="215">
+      <formula>LEN(TRIM(HY18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IA18">
+    <cfRule type="containsText" dxfId="1" priority="212" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IA18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="211">
+      <formula>LEN(TRIM(IA18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IC18">
+    <cfRule type="containsText" dxfId="1" priority="208" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IC18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="207">
+      <formula>LEN(TRIM(IC18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IE18">
+    <cfRule type="containsText" dxfId="1" priority="204" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IE18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="203">
+      <formula>LEN(TRIM(IE18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IM18">
+    <cfRule type="containsText" dxfId="1" priority="133" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IM18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="132">
+      <formula>LEN(TRIM(IM18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IO18">
+    <cfRule type="containsText" dxfId="1" priority="129" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IO18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="128">
+      <formula>LEN(TRIM(IO18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IQ18">
+    <cfRule type="containsText" dxfId="1" priority="125" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IQ18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="124">
+      <formula>LEN(TRIM(IQ18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IS18">
+    <cfRule type="containsText" dxfId="1" priority="121" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IS18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="120">
+      <formula>LEN(TRIM(IS18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JA18">
+    <cfRule type="containsText" dxfId="1" priority="50" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JA18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="49">
+      <formula>LEN(TRIM(JA18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JC18">
+    <cfRule type="containsText" dxfId="1" priority="46" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JC18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="45">
+      <formula>LEN(TRIM(JC18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JE18">
+    <cfRule type="containsText" dxfId="1" priority="42" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JE18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="41">
+      <formula>LEN(TRIM(JE18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JG18">
+    <cfRule type="containsText" dxfId="1" priority="38" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JG18)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="37">
+      <formula>LEN(TRIM(JG18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DC20">
+    <cfRule type="containsText" dxfId="1" priority="949" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DC20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="948">
+      <formula>LEN(TRIM(DC20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DG20">
+    <cfRule type="containsText" dxfId="1" priority="923" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DG20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="922">
+      <formula>LEN(TRIM(DG20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DI20">
+    <cfRule type="containsText" dxfId="1" priority="921" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DI20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="920">
+      <formula>LEN(TRIM(DI20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DK20">
+    <cfRule type="containsText" dxfId="1" priority="897" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DK20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="896">
+      <formula>LEN(TRIM(DK20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DU20">
+    <cfRule type="containsText" dxfId="1" priority="883" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DU20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="882">
+      <formula>LEN(TRIM(DU20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EW20">
+    <cfRule type="containsText" dxfId="1" priority="765" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",EW20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="764">
+      <formula>LEN(TRIM(EW20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FK20">
+    <cfRule type="containsText" dxfId="1" priority="733" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FK20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="732">
+      <formula>LEN(TRIM(FK20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FM20">
+    <cfRule type="containsText" dxfId="1" priority="720" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FM20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="719">
+      <formula>LEN(TRIM(FM20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FO20">
+    <cfRule type="containsText" dxfId="1" priority="696" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FO20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="695">
+      <formula>LEN(TRIM(FO20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FY20">
+    <cfRule type="containsText" dxfId="1" priority="605" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FY20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="604">
+      <formula>LEN(TRIM(FY20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GA20">
+    <cfRule type="containsText" dxfId="1" priority="617" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GA20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="616">
+      <formula>LEN(TRIM(GA20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GK20">
+    <cfRule type="containsText" dxfId="1" priority="445" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GK20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="444">
+      <formula>LEN(TRIM(GK20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GM20">
+    <cfRule type="containsText" dxfId="1" priority="421" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GM20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="420">
+      <formula>LEN(TRIM(GM20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GO20">
+    <cfRule type="containsText" dxfId="1" priority="419" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GO20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="418">
+      <formula>LEN(TRIM(GO20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HA20">
+    <cfRule type="containsText" dxfId="1" priority="469" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HA20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="468">
+      <formula>LEN(TRIM(HA20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HC20">
+    <cfRule type="containsText" dxfId="1" priority="481" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HC20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="480">
+      <formula>LEN(TRIM(HC20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HK20">
+    <cfRule type="containsText" dxfId="1" priority="314" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HK20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="313">
+      <formula>LEN(TRIM(HK20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HM20">
+    <cfRule type="containsText" dxfId="1" priority="310" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HM20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="309">
+      <formula>LEN(TRIM(HM20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HO20">
+    <cfRule type="containsText" dxfId="1" priority="306" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HO20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="305">
+      <formula>LEN(TRIM(HO20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HQ20">
+    <cfRule type="containsText" dxfId="1" priority="302" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HQ20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="301">
+      <formula>LEN(TRIM(HQ20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HS20">
+    <cfRule type="containsText" dxfId="1" priority="274" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HS20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="273">
+      <formula>LEN(TRIM(HS20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HY20">
+    <cfRule type="containsText" dxfId="1" priority="218" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HY20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="217">
+      <formula>LEN(TRIM(HY20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IA20">
+    <cfRule type="containsText" dxfId="1" priority="214" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IA20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="213">
+      <formula>LEN(TRIM(IA20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IC20">
+    <cfRule type="containsText" dxfId="1" priority="210" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IC20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="209">
+      <formula>LEN(TRIM(IC20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IE20">
+    <cfRule type="containsText" dxfId="1" priority="206" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IE20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="205">
+      <formula>LEN(TRIM(IE20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IM20">
+    <cfRule type="containsText" dxfId="1" priority="135" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IM20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="134">
+      <formula>LEN(TRIM(IM20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IO20">
+    <cfRule type="containsText" dxfId="1" priority="131" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IO20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="130">
+      <formula>LEN(TRIM(IO20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IQ20">
+    <cfRule type="containsText" dxfId="1" priority="127" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IQ20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="126">
+      <formula>LEN(TRIM(IQ20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IS20">
+    <cfRule type="containsText" dxfId="1" priority="123" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IS20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="122">
+      <formula>LEN(TRIM(IS20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JA20">
+    <cfRule type="containsText" dxfId="1" priority="52" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JA20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="51">
+      <formula>LEN(TRIM(JA20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JC20">
+    <cfRule type="containsText" dxfId="1" priority="48" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JC20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="47">
+      <formula>LEN(TRIM(JC20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JE20">
+    <cfRule type="containsText" dxfId="1" priority="44" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JE20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="43">
+      <formula>LEN(TRIM(JE20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JG20">
+    <cfRule type="containsText" dxfId="1" priority="40" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JG20)))</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="39">
+      <formula>LEN(TRIM(JG20))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DX3:DX20">
+    <cfRule type="containsText" dxfId="2" priority="855" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",DX3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="ED3:ED20">
+    <cfRule type="containsText" dxfId="2" priority="845" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",ED3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EF3:EF20">
+    <cfRule type="containsText" dxfId="2" priority="844" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",EF3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EP3:EP20">
+    <cfRule type="containsText" dxfId="2" priority="790" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",EP3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="ER3:ER20">
+    <cfRule type="containsText" dxfId="2" priority="789" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",ER3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="ET3:ET20">
+    <cfRule type="containsText" dxfId="2" priority="788" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",ET3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FT3:FT20">
+    <cfRule type="containsText" dxfId="2" priority="670" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",FT3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FV3:FV20">
+    <cfRule type="containsText" dxfId="2" priority="669" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",FV3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FX3:FX20">
+    <cfRule type="containsText" dxfId="2" priority="664" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",FX3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GH3:GH20">
+    <cfRule type="containsText" dxfId="2" priority="572" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",GH3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GJ3:GJ20">
+    <cfRule type="containsText" dxfId="2" priority="571" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",GJ3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GL3:GL20">
+    <cfRule type="containsText" dxfId="2" priority="566" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",GL3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GV3:GV20">
+    <cfRule type="containsText" dxfId="2" priority="504" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",GV3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GX3:GX20">
+    <cfRule type="containsText" dxfId="2" priority="503" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",GX3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GZ3:GZ20">
+    <cfRule type="containsText" dxfId="2" priority="498" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",GZ3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HJ3:HJ20">
+    <cfRule type="containsText" dxfId="2" priority="333" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",HJ3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HL3:HL20">
+    <cfRule type="containsText" dxfId="2" priority="373" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",HL3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HN3:HN20">
+    <cfRule type="containsText" dxfId="2" priority="368" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",HN3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HX3:HX20">
+    <cfRule type="containsText" dxfId="2" priority="235" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",HX3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HZ3:HZ20">
+    <cfRule type="containsText" dxfId="2" priority="243" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",HZ3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IB3:IB20">
+    <cfRule type="containsText" dxfId="2" priority="239" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",IB3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IL3:IL20">
+    <cfRule type="containsText" dxfId="2" priority="152" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",IL3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IN3:IN20">
+    <cfRule type="containsText" dxfId="2" priority="160" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",IN3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IP3:IP20">
+    <cfRule type="containsText" dxfId="2" priority="156" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",IP3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IU3:IU20">
+    <cfRule type="containsText" dxfId="1" priority="165" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IU3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IZ3:IZ20">
+    <cfRule type="containsText" dxfId="2" priority="69" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",IZ3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JB3:JB20">
+    <cfRule type="containsText" dxfId="2" priority="77" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",JB3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JD3:JD20">
+    <cfRule type="containsText" dxfId="2" priority="73" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",JD3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JI3:JI20">
+    <cfRule type="containsText" dxfId="1" priority="82" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JI3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3:B21 D3:D21 KV3:KV21 LH3:LH21 KT3:KT21 KR3:KR21 F3:F21 KP3:KP21 KN3:KN21 KL3:KL21 H3:H21 KJ3:KJ21 KH3:KH21 KF3:KF21 J3:J21 KD3:KD21 KB3:KB21 JZ3:JZ21 L3:L21 JX3:JX21 JV3:JV21 JT3:JT21 N3:N21 JR3:JR21 P3:P21 JP3:JP21 R3:R21 JN3:JN21 T3:T21 JL3:JL21 V3:V21 JJ3:JJ21 X3:X21 JH21 JF21 Z3:Z21 JD21 JB21 AB3:AB21 IZ21 IX3:IX21 AD3:AD21 IV3:IV21 IT21 AF3:AF21 IR21 IP21 AH3:AH21 IN21 IL21 AJ3:AJ21 IJ3:IJ21 IH3:IH21 AL3:AL21 IF21 ID21 AN3:AN21 IB21 HZ21 AP3:AP21 HX21 HV3:HV21 AR3:AR21 HT3:HT21 HR21 AT3:AT21 HP21 HN21 AV3:AV21 HL21 HJ21 AX3:AX21 HH3:HH21 HF3:HF21 AZ3:AZ21 HD21 HB21 BB3:BB21 GZ21 GX21 BD3:BD21 GV21 GT3:GT21 BF3:BF21 GR3:GR21 GP21 BH3:BH21 GN21 GL21 BJ3:BJ21 GJ21 GH21 BL3:BL21 GF3:GF21 GD3:GD21 BN3:BN21 GB21 FZ21 BP3:BP21 FX21 FV21 BR3:BR21 FT21 FR3:FR21 BT3:BT21 FP3:FP21 FN21 BV3:BV21 FL21 FJ21 BX3:BX21 FH21 FF3:FF21 BZ3:BZ21 FD3:FD21 FB3:FB21 CB3:CB21 EZ3:EZ21 EX3:EX21 CD3:CD21 EV3:EV21 ET21 CF3:CF21 ER21 EP21 CH3:CH21 EN3:EN21 EL3:EL21 CJ3:CJ21 EJ3:EJ21 EH3:EH21 CL3:CL21 EF21 ED21 CN3:CN21 EB3:EB21 DZ3:DZ21 CP3:CP21 DX21 DV21 CR3:CR21 DT21 DR21 CT3:CT21 DP21 DN3:DN21 CV3:CV21 DL3:DL21 DJ21 CX3:CX21 DH21 DF21 CZ3:CZ21 DD21 DB21 LI11 KU11 KS11 KW11:LG11 KQ11 KO11 KM11 LF12:LF21 KK11 KI11 KG11 LD12:LD21 KE11 KC11 KA11 LB12:LB21 JY11 JW11 JU11 KZ12:KZ21 JS11 JQ11 JO11 JM11 JK11 W11 Y11 IY11 AA11 IW11 AC11 AE11 AG11 IK11 II11 AI11 IG11 AK11 AM11 HW11 AO11 HU11 HS11 AQ11 AS11 AU11 HI11 HG11 AW11 HE11 AY11 BA11 GU11 BC11 GS11 GQ11 BE11 BG11 BI11 GG11 GE11 BK11 GC11 BM11 FW11 BO11 FU11 FS11 BQ11 FQ11 BS11 FK11 BU11 FG11 BW11 FE11 FC11 BY11 FA11 EY11 CA11 EW11 EU11 CC11 ES11 EQ11 CE11 EO11 EM11 CG11 EK11 EI11 CI11 EG11 EE11 CK11 EC11 EA11 CM11 DY11 CO11 CQ11 DO11 CS11 DM11 CU11 CW11 CY11 DA11 KX3:KX10 KX12:KX21 KZ3:KZ10 LB3:LB10 LD3:LD10 LF3:LF10">
+    <cfRule type="containsText" dxfId="2" priority="968" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",B3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3 C5 G5 E5 G3 E3 I3 I5 K3 M3 K5 M5 LI5 LG5 LE5 LC5 LA5 KY5 KW5 KU5 KS5 KQ5 O3 Q3 S3 U3 W3 Y3 AA3 AC3 AE3 AG3 AI3 AK3 AM3 AO3 AQ3 AS3 AU3 AW3 AY3 BA3 BC3 BE3 BG3 BI3 BK3 BM3 BO3 BQ3 BS3 BU3 BW3 BY3 CA3 CC3 CE3 CG3 CI3 CK3 CM3 CO3 CQ3 CS3 CU3 CW3 CY3 DA3 DM3 DO3 DY3 EA3 EC3 EE3 EG3 EI3 EK3 EM3 EO3 EQ3 ES3 EU3 EW3 EY3 FA3 FC3 FE3 FG3 FK3 FQ3 FS3 FU3 FW3 GC3 GE3 GG3 GS3 GU3 HE3 HG3 HI3 HU3 HW3 IG3 II3 IK3 IW3 IY3 JK3 JM3 JO3 JQ3 JS3 JU3 JW3 JY3 KA3 KC3 KE3 KG3 KI3 KK3 KM3 KO3 KQ3 KS3 KU3 KW3 KY3 LA3 LC3 LE3 LG3 LI3 KO5 KM5 KK5 KI5 O5 Q5 S5 U5 W5 Y5 AA5 AC5 AE5 AG5 AI5 AK5 AM5 AO5 AQ5 AS5 AU5 AW5 AY5 BA5 BC5 BE5 BG5 BI5 BK5 BM5 BO5 BQ5 BS5 BU5 BW5 BY5 CA5 CC5 CE5 CG5 CI5 CK5 CM5 CO5 CQ5 CS5 CU5 CW5 CY5 DA5 DM5 DO5 DY5 EA5 EC5 EE5 EI5 EK5 EM5 EO5 EQ5 EY5 FA5 FC5 FE5 FG5 FK5 FQ5 FS5 FU5 GC5 GE5 GG5 GQ5 GS5 GU5 HE5 HG5 HI5 HU5 HW5 IG5 II5 IK5 IW5 IY5 JK5 JM5 JO5 JQ5 JS5 JU5 JW5 JY5 KA5 KC5 KE5 KG5 C8 G10 E10 G8 E8 G20 E20 G18 E18 G16 E16 G14 E14 G12 E12 C10 C12 C14 C16 C18 C20 I12 I14 I16 I18 I20 I8 I10 LI20 LG20 LE20 LC20 K8 M8 K10 M10 K12 M12 K14 M14 K16 M16 K18 M18 K20 M20 HW20 HU20 HI20 HG20 HE20 GU20 GS20 GQ20 GG20 GE20 GC20 FW20 FU20 FS20 FQ20 FG20 FE20 FC20 FA20 EY20 EU20 ES20 EQ20 EO20 EM20 EK20 EI20 EG20 EE20 EC20 EA20 DY20 DO20 DM20 DA20 CY20 CW20 CU20 CS20 CQ20 CO20 CM20 CK20 CI20 CG20 CE20 CC20 CA20 BY20 BW20 BU20 BS20 BQ20 BO20 BM20 BK20 BI20 BG20 BE20 BC20 BA20 AY20 AW20 AU20 AS20 AQ20 AO20 AM20 AK20 AI20 AG20 AE20 AC20 AA20 Y20 W20 U20 S20 Q20 O20 JK20 LI18 LG18 LE18 LC18 LA18 KY18 KW18 KU18 KS18 KQ18 KO18 KM18 KK18 KI18 KG18 KE18 KC18 KA18 JY18 JW18 JU18 JS18 JQ18 JO18 JM18 JK18 IY18 IW18 IK18 II18 IG18 HW18 HU18 HI18 HG18 HE18 GU18 GS18 GG18 GE18 FW18 FS18 FQ18 FG18 FE18 FC18 FA18 EY18 EU18 EO18 EK18 EI18 EE18 EC18 EA18 DO18 DM18 DA18 CY18 CW18 CU18 CS18 CQ18 CO18 CM18 CK18 CI18 CG18 CE18 CC18 CA18 BY18 BW18 BU18 BS18 BQ18 BO18 BM18 BK18 BI18 BG18 BE18 BC18 BA18 AY18 AW18 AU18 AS18 AQ18 AO18 AM18 AK18 AI18 AG18 AE18 AC18 AA18 Y18 W18 U18 S18 Q18 O18 JM20 JO20 LI16 LG16 LE16 LC16 LA16 KY16 KW16 KU16 KS16 KQ16 KO16 KM16 KK16 KI16 KG16 KE16 KC16 KA16 JY16 JW16 JU16 JS16 JQ16 JO16 JM16 JK16 IY16 IW16 IK16 II16 IG16 HW16 HU16 HI16 HG16 HE16 GU16 GS16 GQ16 GG16 GE16 GC16 FS16 FQ16 FK16 FG16 FE16 FC16 FA16 EY16 EW16 EO16 EK16 EI16 EE16 EC16 EA16 DY16 DO16 DM16 DA16 CY16 CW16 CU16 CS16 CQ16 CO16 CM16 CK16 CI16 CG16 CE16 CC16 CA16 BY16 BW16 BU16 BS16 BQ16 BO16 BM16 BK16 BI16 BG16 BE16 BC16 BA16 AY16 AW16 AU16 AS16 AQ16 AO16 AM16 AK16 AI16 AG16 AE16 AC16 AA16 Y16 W16 U16 S16 Q16 O16 IG20 II20 JQ20 JS20 LI14 LG14 LE14 LC14 LA14 KY14 KW14 KU14 KS14 KQ14 KO14 KM14 KK14 KI14 KG14 KE14 KC14 KA14 JY14 JW14 JU14 JS14 JQ14 JO14 JM14 JK14 IY14 IW14 IK14 II14 IG14 HW14 HU14 HI14 HG14 HE14 GU14 GS14 GG14 GE14 FS14 FQ14 FG14 FE14 FC14 FA14 EY14 EW14 EO14 EK14 EI14 EC14 EA14 DO14 DM14 DA14 CY14 CW14 CU14 CS14 CQ14 CO14 CM14 CK14 CI14 CG14 CE14 CC14 CA14 BY14 BW14 BU14 BS14 BQ14 BO14 BM14 BK14 BI14 BG14 BE14 BC14 BA14 AY14 AW14 AU14 AS14 AQ14 AO14 AM14 AK14 AI14 AG14 AE14 AC14 AA14 Y14 W14 U14 S14 Q14 O14 IK20 JU20 JW20 LI12 LG12 LE12 LC12 LA12 KY12 KW12 KU12 KS12 KQ12 KO12 KM12 KK12 KI12 KG12 KE12 KC12 KA12 JY12 JW12 JU12 JS12 JQ12 JO12 JM12 JK12 IY12 IW12 IK12 II12 IG12 HW12 HU12 HI12 HG12 HE12 GU12 GS12 GG12 GE12 GC12 FS12 FQ12 FG12 FE12 FC12 FA12 EY12 EO12 EM12 EK12 EI12 EC12 EA12 DY12 DO12 DM12 DA12 CY12 CW12 CU12 CS12 CQ12 CO12 CM12 CK12 CI12 CG12 CE12 CC12 CA12 BY12 BW12 BU12 BS12 BQ12 BO12 BM12 BK12 BI12 BG12 BE12 BC12 BA12 AY12 AW12 AU12 AS12 AQ12 AO12 AM12 AK12 AI12 AG12 AE12 AC12 AA12 Y12 W12 U12 S12 Q12 O12 JY20 KA20 LI10 LG10 LE10 LC10 LA10 KY10 KW10 KU10 KS10 KQ10 KO10 KM10 KK10 KI10 KG10 KE10 KC10 KA10 JY10 JW10 JU10 JS10 JQ10 JO10 JM10 JK10 IY10 IW10 IK10 II10 IG10 HW10 HU10 HI10 HG10 HE10 GU10 GS10 GQ10 GG10 GE10 FS10 FQ10 FG10 FE10 FC10 FA10 EY10 EW10 EO10 EM10 EK10 EI10 EE10 EC10 EA10 DO10 DM10 DA10 CY10 CW10 CU10 CS10 CQ10 CO10 CM10 CK10 CI10 CG10 CE10 CC10 CA10 BY10 BW10 BU10 BS10 BQ10 BO10 BM10 BK10 BI10 BG10 BE10 BC10 BA10 AY10 AW10 AU10 AS10 AQ10 AO10 AM10 AK10 AI10 AG10 AE10 AC10 AA10 Y10 W10 U10 S10 Q10 O10 KC20 KE20 LI8 LG8 LE8 LC8 LA8 KY8 KW8 KU8 KS8 KQ8 KO8 KM8 KK8 KI8 KG8 KE8 KC8 KA8 JY8 JW8 JU8 JS8 JQ8 JO8 JM8 JK8 IY8 IW8 IK8 II8 IG8 HW8 HU8 HI8 HG8 HE8 GU8 GS8 GQ8 GG8 GE8 FS8 FQ8 FG8 FE8 FC8 FA8 EY8 EO8 EM8 EK8 EI8 EC8 EA8 DO8 DM8 DA8 CY8 CW8 CU8 CS8 CQ8 CO8 CM8 CK8 CI8 CG8 CE8 CC8 CA8 BY8 BW8 BU8 BS8 BQ8 BO8 BM8 BK8 BI8 BG8 BE8 BC8 BA8 AY8 AW8 AU8 AS8 AQ8 AO8 AM8 AK8 AI8 AG8 AE8 AC8 AA8 Y8 W8 U8 S8 Q8 O8 IW20 IY20 KG20 KI20 LA20 KY20 KW20 KU20 KS20 KQ20 KO20 KM20 KK20">
+    <cfRule type="containsBlanks" dxfId="0" priority="966">
+      <formula>LEN(TRIM(C3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3:C21 E3:E21 KW3:KW21 LI3:LI21 KU3:KU21 KS3:KS21 G3:G21 KQ3:KQ21 KO3:KO21 KM3:KM21 I3:I21 KK3:KK21 KI3:KI21 KG3:KG21 K3:K21 KE3:KE21 KC3:KC21 KA3:KA21 M3:M21 JY3:JY21 JW3:JW21 JU3:JU21 O3:O21 JS3:JS21 Q3:Q21 JQ3:JQ21 S3:S21 JO3:JO21 U3:U21 JM3:JM21 W3:W21 JK3:JK21 Y3:Y21 JI21 JG21 AA3:AA21 JE21 JC21 AC3:AC21 JA21 IY3:IY21 AE3:AE21 IW3:IW21 IU21 AG3:AG21 IS21 IQ21 AI3:AI21 IO21 IM21 AK3:AK21 IK3:IK21 II3:II21 AM3:AM21 IG3:IG21 IE21 AO3:AO21 IC21 IA21 AQ3:AQ21 HY21 HW3:HW21 AS3:AS21 HU3:HU21 HS4 HS6:HS7 HS9 HS11:HT11 HS13 HS15 HS17 HS19 HS21 AU3:AU21 HQ21 HO21 AW3:AW21 HM21 HK21 AY3:AY21 HI3:HI21 HG3:HG21 BA3:BA21 HE3:HE21 HC21 BC3:BC21 HA21 GY21 BE3:BE21 GW21 GU3:GU21 BG3:BG21 GS3:GS21 GQ4:GQ11 GQ13 GQ15:GQ17 GQ19:GQ21 BI3:BI21 GO21 GM21 BK3:BK21 GK21 GI21 BM3:BM21 GG3:GG21 GE3:GE21 BO3:BO21 GC3:GC7 GC9 GC11:GC13 GC15:GC17 GC19:GC21 GA21 BQ3:BQ21 FY21 FW3:FW4 FW6:FW7 FW9 FU11 FW11 FW13 FW15 FW17:FW21 BS3:BS21 FU3:FU7 FU9 FU13 FU15 FU17 FU19:FU21 FS3:FS21 BU3:BU21 FQ3:FQ21 FO21 BW3:BW21 FM21 FK3:FK7 FK9 FK11 FK13 FK15:FK17 FK19 FK21 BY3:BY21 FI21 FG3:FG21 CA3:CA21 FE3:FE21 FC3:FC21 CC3:CC21 FA3:FA21 EY3:EY21 CE3:CE21 EW3:EW4 EW6:EW7 EW9:EW11 EW13:EW17 EW19 EW21 EU3:EU4 EU6:EU7 EU9 EU11 EU13 EU15 EU17:EU21 CG3:CG21 ES3:ES4 ES6:ES7 ES9 EQ11 ES11 ES13 ES15 ES17 ES19:ES21 EQ3:EQ7 EQ9 EQ13 EQ15 EQ17 EQ19:EQ21 CI3:CI21 EO3:EO21 EM3:EM13 EM15 EM17 EM19:EM21 CK3:CK21 EK3:EK21 EI3:EI21 CM3:CM21 EG3:EG4 EG6:EG7 EG9 EG11:EH11 EG13 EG15 EG17 EG19:EG21 EE3:EE7 EE9:EE11 EE13 EE15:EE21 CO3:CO21 EC3:EC21 EA3:EA21 CQ3:CQ21 DY3:DY7 DY9 DY11:DY13 DY15:DY17 DY19:DY21 DW21 CS3:CS21 DU21 DS21 CU3:CU21 DQ21 DO3:DO21 CW3:CW21 DM3:DM21 DK21 CY3:CY21 DI21 DG21 DA3:DA21 DE21 DC21 KV11 KT11 KX11:LH11 KR11 KP11 KN11 LG12:LG21 KL11 KJ11 KH11 LE12:LE21 KF11 KD11 KB11 LC12:LC21 JZ11 JX11 JV11 LA12:LA21 JT11 JR11 JP11 JN11 JL11 JJ11 X11 Z11 AB11 IX11 IV11 AD11 AF11 AH11 IJ11 AJ11 IH11 AL11 AN11 AP11 HV11 AR11 AT11 AV11 HH11 AX11 HF11 AZ11 BB11 BD11 GT11 GR11 BF11 BH11 BJ11 GF11 BL11 GD11 BN11 BP11 BR11 FR11 FP11 BT11 BV11 BX11 FF11 FD11 BZ11 FB11 EZ11 CB11 EX11 CD11 CF11 EN11 CH11 EL11 EJ11 CJ11 CL11 EB11 CN11 DZ11 DN11 DL11 CV11 CX11 CZ11 KY3:KY10 KY12:KY21 LA3:LA10 LC3:LC10 LE3:LE10 LG3:LG10">
+    <cfRule type="containsText" dxfId="1" priority="967" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",C3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DB3:DB20 DD3:DD20 DF3:DF20 DH3:DH20 DJ3:DJ20 DC11 DE11 DG11 DI11 DK11">
+    <cfRule type="containsText" dxfId="2" priority="961" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",DB3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DC3:DC7 DC9:DC11 DC13 DC15:DC19 DE3:DE4 DE6:DE7 DE9 DD11:DF11 DE13 DE15 DE17 DE19:DE20 DG3:DG4 DG6:DG7 DG9:DG11 DG13:DG15 DG17 DG19 DI3:DI7 DI9 DH11:DJ11 DI13 DI15 DI17 DI19 DK3:DK7 DK9 DK11:DK13 DK15 DK17 DK19">
+    <cfRule type="containsText" dxfId="1" priority="960" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DC3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DC3 DE3 DG3 DI3 DK3 DC5 DI5 DK5 DE20 DC18 DC16 DG14 DK12 DG10 DC10">
+    <cfRule type="containsBlanks" dxfId="0" priority="959">
+      <formula>LEN(TRIM(DC3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DP3:DP20 DR3:DR20 DT3:DT20 DV3:DV20 DQ11 DS11 DU11 DW11">
+    <cfRule type="containsText" dxfId="2" priority="958" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",DP3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DQ3 DS3 DU3 DW3 DQ5 DS5 DW5 DW20 DS20 DQ20 DW18 DU18 DS18 DQ16 DU14 DU10">
+    <cfRule type="containsBlanks" dxfId="0" priority="956">
+      <formula>LEN(TRIM(DQ3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DQ3:DQ7 DQ9 DQ11:DT11 DQ13 DQ15:DQ17 DQ19:DQ20 DS3:DS7 DS9 DS13 DS15 DS17:DS20 DU3:DU4 DU6:DU7 DU9:DU11 DU13:DU15 DU17:DU19 DW3:DW7 DW9 DV11:DW11 DW13 DW15 DW17:DW20">
+    <cfRule type="containsText" dxfId="1" priority="957" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",DQ3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FH3:FH20 FJ3:FJ20">
+    <cfRule type="containsText" dxfId="2" priority="763" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",FH3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FI3:FI4 FI6:FI7 FI9 FI11 FI13 FI15 FI17:FI20">
+    <cfRule type="containsText" dxfId="1" priority="749" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FI3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FI3 FI20 FI18">
+    <cfRule type="containsBlanks" dxfId="0" priority="748">
+      <formula>LEN(TRIM(FI3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FL3:FL20 FN3:FN20 FM11 FO11">
+    <cfRule type="containsText" dxfId="2" priority="723" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",FL3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FM3:FM7 FM9 FL11:FN11 FM13 FM15 FM17 FM19 FO3:FO7 FO9 FO11:FO13 FO15 FO17 FO19">
+    <cfRule type="containsText" dxfId="1" priority="722" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FL3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FM3 FO3 FM5 FO5 FO12">
+    <cfRule type="containsBlanks" dxfId="0" priority="721">
+      <formula>LEN(TRIM(FM3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FY3 FY16">
+    <cfRule type="containsBlanks" dxfId="0" priority="665">
+      <formula>LEN(TRIM(FY3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FY3:FY4 FY6:FY7 FY9 FY11 FY13 FY15:FY17 FY19">
+    <cfRule type="containsText" dxfId="1" priority="666" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FY3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FZ3:FZ20 GB3:GB20 GA11">
+    <cfRule type="containsText" dxfId="2" priority="650" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",FZ3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GA3:GA4 GA6:GA7 GA9 FZ11:GB11 GA13 GA15 GA17 GA19">
+    <cfRule type="containsText" dxfId="1" priority="649" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",FZ3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GK3 GI20 GK18">
+    <cfRule type="containsBlanks" dxfId="0" priority="597">
+      <formula>LEN(TRIM(GI3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GK3:GK4 GK6:GK7 GK9 GI11 GK11 GK13 GK15 GK17:GK19 GI4 GI6:GI7 GI9 GI13 GI15 GI17 GI19:GI20">
+    <cfRule type="containsText" dxfId="1" priority="598" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",GI3)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="296">
-      <formula>LEN(TRIM(GI3))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GM3">
-    <cfRule type="containsText" dxfId="1" priority="295" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GM3)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="294">
-      <formula>LEN(TRIM(GM3))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GO3">
-    <cfRule type="containsBlanks" dxfId="0" priority="392">
-      <formula>LEN(TRIM(GO3))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GQ3">
-    <cfRule type="containsText" dxfId="1" priority="293" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GQ3)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="292">
-      <formula>LEN(TRIM(GQ3))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HC3">
-    <cfRule type="containsBlanks" dxfId="0" priority="324">
-      <formula>LEN(TRIM(HC3))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HM3">
-    <cfRule type="containsText" dxfId="1" priority="166" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HM3)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="165">
-      <formula>LEN(TRIM(HM3))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HO3">
-    <cfRule type="containsText" dxfId="1" priority="164" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HO3)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="163">
-      <formula>LEN(TRIM(HO3))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HQ3">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GN3:GN20 GP3:GP20 GO11">
+    <cfRule type="containsText" dxfId="2" priority="560" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",GN3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GO3:GO4 GO6:GO7 GO9 GN11:GP11 GO13 GO15 GO17 GO19">
+    <cfRule type="containsText" dxfId="1" priority="559" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GN3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GY3:GY4 GY6:GY7 GY9 GW11 GY11 GY13 GY15 GY17:GY20 GW3:GW7 GW9 GW13 GW15 GW17 GW19:GW20">
+    <cfRule type="containsText" dxfId="1" priority="530" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",GW3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GW3 GY3 GW5 GY20 GW20 GY18">
+    <cfRule type="containsBlanks" dxfId="0" priority="529">
+      <formula>LEN(TRIM(GW3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HA3:HA4 HA6:HA7 HA9 HA11 HA13 HA15:HA17 HA19">
+    <cfRule type="containsText" dxfId="1" priority="500" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HA3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HA3 HA16">
+    <cfRule type="containsBlanks" dxfId="0" priority="499">
+      <formula>LEN(TRIM(HA3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HB3:HB20 HD3:HD20 HC11">
+    <cfRule type="containsText" dxfId="2" priority="492" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",HB3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HC3:HC4 HC6:HC7 HC9 HB11:HD11 HC13 HC15 HC17 HC19">
+    <cfRule type="containsText" dxfId="1" priority="491" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HB3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HM4 HM6:HM7 HM9 HK11 HM11 HM13 HM15 HM17 HM19 HK3:HK7 HK9 HK13 HK15 HK17 HK19">
+    <cfRule type="containsText" dxfId="1" priority="400" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HK3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HK3 HK5">
+    <cfRule type="containsBlanks" dxfId="0" priority="399">
+      <formula>LEN(TRIM(HK3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HP3:HP20 HR3:HR20 HQ11">
+    <cfRule type="containsText" dxfId="2" priority="362" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",HP3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IA4 IA6:IA7 IA9 HY11 IA11 IA13 IA15 IA17 IA19 HY3:HY7 HY9 HY13 HY15 HY17 HY19">
+    <cfRule type="containsText" dxfId="1" priority="245" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",HY3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="HY3 HY5">
+    <cfRule type="containsBlanks" dxfId="0" priority="244">
+      <formula>LEN(TRIM(HY3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="ID3:ID20 IF3:IF20 IE11">
+    <cfRule type="containsText" dxfId="2" priority="237" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",ID3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IO4 IO6:IO7 IO9 IM11 IO11 IO13 IO15 IO17 IO19 IM3:IM7 IM9 IM13 IM15 IM17 IM19">
     <cfRule type="containsText" dxfId="1" priority="162" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HQ3)))</formula>
-    </cfRule>
+      <formula>NOT(ISERROR(SEARCH("—",IM3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IM3 IM5">
     <cfRule type="containsBlanks" dxfId="0" priority="161">
-      <formula>LEN(TRIM(HQ3))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HS3">
-    <cfRule type="containsText" dxfId="1" priority="160" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HS3)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="159">
-      <formula>LEN(TRIM(HS3))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IA3">
-    <cfRule type="containsText" dxfId="1" priority="68" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IA3)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="67">
-      <formula>LEN(TRIM(IA3))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IC3">
-    <cfRule type="containsText" dxfId="1" priority="66" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IC3)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="65">
-      <formula>LEN(TRIM(IC3))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IE3">
-    <cfRule type="containsText" dxfId="1" priority="64" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IE3)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="63">
-      <formula>LEN(TRIM(IE3))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DE5">
-    <cfRule type="containsText" dxfId="1" priority="769" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DE5)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="768">
-      <formula>LEN(TRIM(DE5))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DG5">
-    <cfRule type="containsText" dxfId="1" priority="767" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DG5)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="766">
-      <formula>LEN(TRIM(DG5))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DU5">
-    <cfRule type="containsText" dxfId="1" priority="707" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DU5)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="706">
-      <formula>LEN(TRIM(DU5))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EG5">
-    <cfRule type="containsText" dxfId="1" priority="670" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EG5)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="669">
-      <formula>LEN(TRIM(EG5))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="ES5">
-    <cfRule type="containsText" dxfId="1" priority="638" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",ES5)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="637">
-      <formula>LEN(TRIM(ES5))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EU5">
-    <cfRule type="containsText" dxfId="1" priority="620" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EU5)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="619">
-      <formula>LEN(TRIM(EU5))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EW5">
-    <cfRule type="containsText" dxfId="1" priority="607" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EW5)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="606">
-      <formula>LEN(TRIM(EW5))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FI5">
-    <cfRule type="containsText" dxfId="1" priority="581" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FI5)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="580">
-      <formula>LEN(TRIM(FI5))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FW5">
-    <cfRule type="containsText" dxfId="1" priority="526" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FW5)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="525">
-      <formula>LEN(TRIM(FW5))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FY5">
-    <cfRule type="containsText" dxfId="1" priority="435" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FY5)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="434">
-      <formula>LEN(TRIM(FY5))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GA5">
-    <cfRule type="containsText" dxfId="1" priority="465" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GA5)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="464">
-      <formula>LEN(TRIM(GA5))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GI5">
-    <cfRule type="containsText" dxfId="1" priority="291" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GI5)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="290">
-      <formula>LEN(TRIM(GI5))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GK5">
-    <cfRule type="containsText" dxfId="1" priority="269" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GK5)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="268">
-      <formula>LEN(TRIM(GK5))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GM5">
-    <cfRule type="containsText" dxfId="1" priority="267" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GM5)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="266">
-      <formula>LEN(TRIM(GM5))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GO5">
-    <cfRule type="containsText" dxfId="1" priority="389" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GO5)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="388">
-      <formula>LEN(TRIM(GO5))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GY5">
-    <cfRule type="containsText" dxfId="1" priority="360" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GY5)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="359">
-      <formula>LEN(TRIM(GY5))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HA5">
-    <cfRule type="containsText" dxfId="1" priority="299" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HA5)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="298">
-      <formula>LEN(TRIM(HA5))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HC5">
-    <cfRule type="containsText" dxfId="1" priority="321" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HC5)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="320">
-      <formula>LEN(TRIM(HC5))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HM5">
-    <cfRule type="containsText" dxfId="1" priority="102" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HM5)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="101">
-      <formula>LEN(TRIM(HM5))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HO5">
-    <cfRule type="containsText" dxfId="1" priority="104" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HO5)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="103">
-      <formula>LEN(TRIM(HO5))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HQ5">
-    <cfRule type="containsText" dxfId="1" priority="106" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HQ5)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="105">
-      <formula>LEN(TRIM(HQ5))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HS5">
-    <cfRule type="containsText" dxfId="1" priority="120" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HS5)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="119">
-      <formula>LEN(TRIM(HS5))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IA5">
-    <cfRule type="containsText" dxfId="1" priority="22" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IA5)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="21">
-      <formula>LEN(TRIM(IA5))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IC5">
-    <cfRule type="containsText" dxfId="1" priority="24" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IC5)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="23">
-      <formula>LEN(TRIM(IC5))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IE5">
-    <cfRule type="containsText" dxfId="1" priority="26" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IE5)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="25">
-      <formula>LEN(TRIM(IE5))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DC8">
-    <cfRule type="containsText" dxfId="1" priority="789" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DC8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="788">
-      <formula>LEN(TRIM(DC8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DE8">
-    <cfRule type="containsText" dxfId="1" priority="771" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DE8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="770">
-      <formula>LEN(TRIM(DE8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DG8">
-    <cfRule type="containsText" dxfId="1" priority="765" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DG8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="764">
-      <formula>LEN(TRIM(DG8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DI8">
-    <cfRule type="containsText" dxfId="1" priority="743" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DI8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="742">
-      <formula>LEN(TRIM(DI8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DK8">
-    <cfRule type="containsText" dxfId="1" priority="741" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DK8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="740">
-      <formula>LEN(TRIM(DK8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DQ8">
-    <cfRule type="containsText" dxfId="1" priority="693" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DQ8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="692">
-      <formula>LEN(TRIM(DQ8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DS8">
-    <cfRule type="containsText" dxfId="1" priority="705" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DS8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="704">
-      <formula>LEN(TRIM(DS8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DU8">
-    <cfRule type="containsText" dxfId="1" priority="709" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DU8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="708">
-      <formula>LEN(TRIM(DU8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DW8">
-    <cfRule type="containsText" dxfId="1" priority="729" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DW8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="728">
-      <formula>LEN(TRIM(DW8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DY8">
-    <cfRule type="containsText" dxfId="1" priority="687" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DY8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="686">
-      <formula>LEN(TRIM(DY8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EE8">
-    <cfRule type="containsText" dxfId="1" priority="676" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EE8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="675">
-      <formula>LEN(TRIM(EE8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EG8">
-    <cfRule type="containsText" dxfId="1" priority="668" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EG8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="667">
-      <formula>LEN(TRIM(EG8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EQ8">
-    <cfRule type="containsText" dxfId="1" priority="650" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EQ8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="649">
-      <formula>LEN(TRIM(EQ8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="ES8">
-    <cfRule type="containsText" dxfId="1" priority="636" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",ES8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="635">
-      <formula>LEN(TRIM(ES8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EU8">
-    <cfRule type="containsText" dxfId="1" priority="618" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EU8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="617">
-      <formula>LEN(TRIM(EU8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EW8">
-    <cfRule type="containsText" dxfId="1" priority="605" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EW8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="604">
-      <formula>LEN(TRIM(EW8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FI8">
-    <cfRule type="containsText" dxfId="1" priority="579" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FI8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="578">
-      <formula>LEN(TRIM(FI8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FK8">
-    <cfRule type="containsText" dxfId="1" priority="559" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FK8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="558">
-      <formula>LEN(TRIM(FK8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FM8">
-    <cfRule type="containsText" dxfId="1" priority="542" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FM8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="541">
-      <formula>LEN(TRIM(FM8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FO8">
-    <cfRule type="containsText" dxfId="1" priority="540" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FO8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="539">
-      <formula>LEN(TRIM(FO8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FU8">
-    <cfRule type="containsText" dxfId="1" priority="528" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FU8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="527">
-      <formula>LEN(TRIM(FU8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FW8">
-    <cfRule type="containsText" dxfId="1" priority="524" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FW8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="523">
-      <formula>LEN(TRIM(FW8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FY8">
-    <cfRule type="containsText" dxfId="1" priority="437" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FY8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="436">
-      <formula>LEN(TRIM(FY8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GA8">
-    <cfRule type="containsText" dxfId="1" priority="467" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GA8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="466">
-      <formula>LEN(TRIM(GA8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GC8">
-    <cfRule type="containsText" dxfId="1" priority="463" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GC8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="462">
-      <formula>LEN(TRIM(GC8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GI8">
-    <cfRule type="containsText" dxfId="1" priority="289" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GI8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="288">
-      <formula>LEN(TRIM(GI8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GK8">
-    <cfRule type="containsText" dxfId="1" priority="426" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GK8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="425">
-      <formula>LEN(TRIM(GK8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GM8">
-    <cfRule type="containsText" dxfId="1" priority="265" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GM8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="264">
-      <formula>LEN(TRIM(GM8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GO8">
-    <cfRule type="containsText" dxfId="1" priority="391" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GO8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="390">
-      <formula>LEN(TRIM(GO8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GW8">
-    <cfRule type="containsText" dxfId="1" priority="362" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GW8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="361">
-      <formula>LEN(TRIM(GW8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GY8">
-    <cfRule type="containsText" dxfId="1" priority="358" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GY8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="357">
-      <formula>LEN(TRIM(GY8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HA8">
-    <cfRule type="containsText" dxfId="1" priority="301" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HA8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="300">
-      <formula>LEN(TRIM(HA8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HC8">
-    <cfRule type="containsText" dxfId="1" priority="323" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HC8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="322">
-      <formula>LEN(TRIM(HC8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HK8">
-    <cfRule type="containsText" dxfId="1" priority="158" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HK8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="157">
-      <formula>LEN(TRIM(HK8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HM8">
-    <cfRule type="containsText" dxfId="1" priority="100" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HM8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="99">
-      <formula>LEN(TRIM(HM8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HO8">
-    <cfRule type="containsText" dxfId="1" priority="98" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HO8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="97">
-      <formula>LEN(TRIM(HO8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HQ8">
-    <cfRule type="containsText" dxfId="1" priority="124" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HQ8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="123">
-      <formula>LEN(TRIM(HQ8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HS8">
-    <cfRule type="containsText" dxfId="1" priority="122" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HS8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="121">
-      <formula>LEN(TRIM(HS8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HY8">
-    <cfRule type="containsText" dxfId="1" priority="62" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HY8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="61">
-      <formula>LEN(TRIM(HY8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IA8">
-    <cfRule type="containsText" dxfId="1" priority="20" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IA8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="19">
-      <formula>LEN(TRIM(IA8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IC8">
-    <cfRule type="containsText" dxfId="1" priority="18" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IC8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="17">
-      <formula>LEN(TRIM(IC8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IE8">
-    <cfRule type="containsText" dxfId="1" priority="28" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IE8)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="27">
-      <formula>LEN(TRIM(IE8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DE10">
-    <cfRule type="containsText" dxfId="1" priority="773" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DE10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="772">
-      <formula>LEN(TRIM(DE10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DI10">
-    <cfRule type="containsText" dxfId="1" priority="745" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DI10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="744">
-      <formula>LEN(TRIM(DI10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DK10">
-    <cfRule type="containsText" dxfId="1" priority="739" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DK10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="738">
-      <formula>LEN(TRIM(DK10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DQ10">
-    <cfRule type="containsText" dxfId="1" priority="695" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DQ10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="694">
-      <formula>LEN(TRIM(DQ10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DS10">
-    <cfRule type="containsText" dxfId="1" priority="703" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DS10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="702">
-      <formula>LEN(TRIM(DS10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DW10">
-    <cfRule type="containsText" dxfId="1" priority="727" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DW10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="726">
-      <formula>LEN(TRIM(DW10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DY10">
-    <cfRule type="containsText" dxfId="1" priority="685" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DY10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="684">
-      <formula>LEN(TRIM(DY10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EG10">
-    <cfRule type="containsText" dxfId="1" priority="666" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EG10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="665">
-      <formula>LEN(TRIM(EG10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EQ10">
-    <cfRule type="containsText" dxfId="1" priority="648" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EQ10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="647">
-      <formula>LEN(TRIM(EQ10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="ES10">
-    <cfRule type="containsText" dxfId="1" priority="634" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",ES10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="633">
-      <formula>LEN(TRIM(ES10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EU10">
-    <cfRule type="containsText" dxfId="1" priority="616" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EU10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="615">
-      <formula>LEN(TRIM(EU10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FI10">
-    <cfRule type="containsText" dxfId="1" priority="577" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FI10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="576">
-      <formula>LEN(TRIM(FI10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FK10">
-    <cfRule type="containsText" dxfId="1" priority="561" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FK10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="560">
-      <formula>LEN(TRIM(FK10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FM10">
-    <cfRule type="containsText" dxfId="1" priority="544" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FM10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="543">
-      <formula>LEN(TRIM(FM10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FO10">
-    <cfRule type="containsText" dxfId="1" priority="538" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FO10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="537">
-      <formula>LEN(TRIM(FO10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FU10">
-    <cfRule type="containsText" dxfId="1" priority="514" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FU10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="513">
-      <formula>LEN(TRIM(FU10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FW10">
-    <cfRule type="containsText" dxfId="1" priority="522" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FW10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="521">
-      <formula>LEN(TRIM(FW10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FY10">
-    <cfRule type="containsText" dxfId="1" priority="488" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FY10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="487">
-      <formula>LEN(TRIM(FY10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GA10">
-    <cfRule type="containsText" dxfId="1" priority="447" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GA10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="446">
-      <formula>LEN(TRIM(GA10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GC10">
-    <cfRule type="containsText" dxfId="1" priority="461" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GC10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="460">
-      <formula>LEN(TRIM(GC10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GI10">
-    <cfRule type="containsText" dxfId="1" priority="287" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GI10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="286">
-      <formula>LEN(TRIM(GI10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GK10">
-    <cfRule type="containsText" dxfId="1" priority="271" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GK10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="270">
-      <formula>LEN(TRIM(GK10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GM10">
-    <cfRule type="containsText" dxfId="1" priority="263" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GM10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="262">
-      <formula>LEN(TRIM(GM10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GO10">
-    <cfRule type="containsText" dxfId="1" priority="237" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GO10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="236">
-      <formula>LEN(TRIM(GO10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GW10">
-    <cfRule type="containsText" dxfId="1" priority="348" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GW10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="347">
-      <formula>LEN(TRIM(GW10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GY10">
-    <cfRule type="containsText" dxfId="1" priority="356" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GY10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="355">
-      <formula>LEN(TRIM(GY10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HA10">
-    <cfRule type="containsText" dxfId="1" priority="328" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HA10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="327">
-      <formula>LEN(TRIM(HA10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HC10">
-    <cfRule type="containsText" dxfId="1" priority="311" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HC10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="310">
-      <formula>LEN(TRIM(HC10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HK10">
-    <cfRule type="containsText" dxfId="1" priority="156" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HK10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="155">
-      <formula>LEN(TRIM(HK10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HM10">
-    <cfRule type="containsText" dxfId="1" priority="82" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HM10)))</formula>
-    </cfRule>
+      <formula>LEN(TRIM(IM3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IR3:IR20 IT3:IT20 IS11">
+    <cfRule type="containsText" dxfId="2" priority="154" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",IR3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IU3 IU5 IU18 IU16 IU20 IU14 IU12 IU10 IU8">
+    <cfRule type="containsBlanks" dxfId="0" priority="164">
+      <formula>LEN(TRIM(IU3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JC4 JC6:JC7 JC9 JA11 JC11 JC13 JC15 JC17 JC19 JA3:JA7 JA9 JA13 JA15 JA17 JA19">
+    <cfRule type="containsText" dxfId="1" priority="79" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",JA3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JA3 JA5">
+    <cfRule type="containsBlanks" dxfId="0" priority="78">
+      <formula>LEN(TRIM(JA3))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JF3:JF20 JH3:JH20 JG11">
+    <cfRule type="containsText" dxfId="2" priority="71" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",JF3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JI3 JI5 JI18 JI16 JI20 JI14 JI12 JI10 JI8">
     <cfRule type="containsBlanks" dxfId="0" priority="81">
-      <formula>LEN(TRIM(HM10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HO10">
-    <cfRule type="containsText" dxfId="1" priority="96" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HO10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="95">
-      <formula>LEN(TRIM(HO10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HQ10">
-    <cfRule type="containsText" dxfId="1" priority="126" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HQ10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="125">
-      <formula>LEN(TRIM(HQ10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HS10">
-    <cfRule type="containsText" dxfId="1" priority="118" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HS10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="117">
-      <formula>LEN(TRIM(HS10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HY10">
-    <cfRule type="containsText" dxfId="1" priority="60" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HY10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="59">
-      <formula>LEN(TRIM(HY10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IA10">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IA10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="1">
-      <formula>LEN(TRIM(IA10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IC10">
-    <cfRule type="containsText" dxfId="1" priority="16" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IC10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="15">
-      <formula>LEN(TRIM(IC10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IE10">
-    <cfRule type="containsText" dxfId="1" priority="30" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IE10)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="29">
-      <formula>LEN(TRIM(IE10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="CR11">
-    <cfRule type="containsText" dxfId="1" priority="797" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",CR11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="CT11">
-    <cfRule type="containsText" dxfId="1" priority="796" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",CT11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DX11">
-    <cfRule type="containsText" dxfId="1" priority="688" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DX11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EF11">
-    <cfRule type="containsText" dxfId="1" priority="677" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EF11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="ET11">
-    <cfRule type="containsText" dxfId="1" priority="621" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",ET11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EV11">
-    <cfRule type="containsText" dxfId="1" priority="608" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EV11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FI11">
-    <cfRule type="containsText" dxfId="2" priority="584" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",FI11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FV11">
-    <cfRule type="containsText" dxfId="1" priority="502" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FV11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FX11">
-    <cfRule type="containsText" dxfId="1" priority="497" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FX11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FY11">
-    <cfRule type="containsText" dxfId="2" priority="501" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",FY11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GJ11">
-    <cfRule type="containsText" dxfId="1" priority="404" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GJ11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GL11">
-    <cfRule type="containsText" dxfId="1" priority="399" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GL11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GM11">
-    <cfRule type="containsText" dxfId="2" priority="403" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",GM11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GX11">
-    <cfRule type="containsText" dxfId="1" priority="336" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GX11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GZ11">
-    <cfRule type="containsText" dxfId="1" priority="331" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GZ11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HA11">
-    <cfRule type="containsText" dxfId="2" priority="335" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",HA11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HL11">
-    <cfRule type="containsText" dxfId="1" priority="206" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HL11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HN11">
-    <cfRule type="containsText" dxfId="1" priority="201" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HN11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HO11">
-    <cfRule type="containsText" dxfId="2" priority="205" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",HO11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HZ11">
-    <cfRule type="containsText" dxfId="1" priority="76" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HZ11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IB11">
-    <cfRule type="containsText" dxfId="1" priority="72" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IB11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IC11">
-    <cfRule type="containsText" dxfId="2" priority="75" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",IC11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DC12">
-    <cfRule type="containsText" dxfId="1" priority="787" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DC12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="786">
-      <formula>LEN(TRIM(DC12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DE12">
-    <cfRule type="containsText" dxfId="1" priority="775" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DE12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="774">
-      <formula>LEN(TRIM(DE12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DG12">
-    <cfRule type="containsText" dxfId="1" priority="763" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DG12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="762">
-      <formula>LEN(TRIM(DG12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DI12">
-    <cfRule type="containsText" dxfId="1" priority="747" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DI12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="746">
-      <formula>LEN(TRIM(DI12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DQ12">
-    <cfRule type="containsText" dxfId="1" priority="699" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DQ12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="698">
-      <formula>LEN(TRIM(DQ12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DS12">
-    <cfRule type="containsText" dxfId="1" priority="701" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DS12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="700">
-      <formula>LEN(TRIM(DS12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DU12">
-    <cfRule type="containsText" dxfId="1" priority="711" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DU12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="710">
-      <formula>LEN(TRIM(DU12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DW12">
-    <cfRule type="containsText" dxfId="1" priority="725" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DW12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="724">
-      <formula>LEN(TRIM(DW12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EE12">
-    <cfRule type="containsText" dxfId="1" priority="674" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EE12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="673">
-      <formula>LEN(TRIM(EE12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EG12">
-    <cfRule type="containsText" dxfId="1" priority="664" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EG12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="663">
-      <formula>LEN(TRIM(EG12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EQ12">
-    <cfRule type="containsText" dxfId="1" priority="646" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EQ12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="645">
-      <formula>LEN(TRIM(EQ12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="ES12">
-    <cfRule type="containsText" dxfId="1" priority="632" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",ES12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="631">
-      <formula>LEN(TRIM(ES12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EU12">
-    <cfRule type="containsText" dxfId="1" priority="614" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EU12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="613">
-      <formula>LEN(TRIM(EU12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EW12">
-    <cfRule type="containsText" dxfId="1" priority="603" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EW12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="602">
-      <formula>LEN(TRIM(EW12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FI12">
-    <cfRule type="containsText" dxfId="1" priority="575" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FI12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="574">
-      <formula>LEN(TRIM(FI12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FK12">
-    <cfRule type="containsText" dxfId="1" priority="563" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FK12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="562">
-      <formula>LEN(TRIM(FK12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FM12">
-    <cfRule type="containsText" dxfId="1" priority="546" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FM12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="545">
-      <formula>LEN(TRIM(FM12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FU12">
-    <cfRule type="containsText" dxfId="1" priority="512" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FU12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="511">
-      <formula>LEN(TRIM(FU12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FW12">
-    <cfRule type="containsText" dxfId="1" priority="520" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FW12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="519">
-      <formula>LEN(TRIM(FW12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FY12">
-    <cfRule type="containsText" dxfId="1" priority="443" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FY12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="442">
-      <formula>LEN(TRIM(FY12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GA12">
-    <cfRule type="containsText" dxfId="1" priority="445" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GA12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="444">
-      <formula>LEN(TRIM(GA12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GI12">
-    <cfRule type="containsText" dxfId="1" priority="285" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GI12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="284">
-      <formula>LEN(TRIM(GI12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GK12">
-    <cfRule type="containsText" dxfId="1" priority="273" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GK12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="272">
-      <formula>LEN(TRIM(GK12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GM12">
-    <cfRule type="containsText" dxfId="1" priority="261" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GM12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="260">
-      <formula>LEN(TRIM(GM12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GO12">
-    <cfRule type="containsText" dxfId="1" priority="239" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GO12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="238">
-      <formula>LEN(TRIM(GO12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GQ12">
-    <cfRule type="containsText" dxfId="1" priority="245" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GQ12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="244">
-      <formula>LEN(TRIM(GQ12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GW12">
-    <cfRule type="containsText" dxfId="1" priority="346" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GW12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="345">
-      <formula>LEN(TRIM(GW12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GY12">
-    <cfRule type="containsText" dxfId="1" priority="354" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GY12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="353">
-      <formula>LEN(TRIM(GY12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HA12">
-    <cfRule type="containsText" dxfId="1" priority="307" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HA12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="306">
-      <formula>LEN(TRIM(HA12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HC12">
-    <cfRule type="containsText" dxfId="1" priority="309" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HC12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="308">
-      <formula>LEN(TRIM(HC12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HK12">
-    <cfRule type="containsText" dxfId="1" priority="154" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HK12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="153">
-      <formula>LEN(TRIM(HK12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HM12">
-    <cfRule type="containsText" dxfId="1" priority="84" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HM12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="83">
-      <formula>LEN(TRIM(HM12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HO12">
-    <cfRule type="containsText" dxfId="1" priority="94" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HO12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="93">
-      <formula>LEN(TRIM(HO12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HQ12">
-    <cfRule type="containsText" dxfId="1" priority="128" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HQ12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="127">
-      <formula>LEN(TRIM(HQ12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HS12">
-    <cfRule type="containsText" dxfId="1" priority="116" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HS12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="115">
-      <formula>LEN(TRIM(HS12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HY12">
-    <cfRule type="containsText" dxfId="1" priority="58" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HY12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="57">
-      <formula>LEN(TRIM(HY12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IA12">
-    <cfRule type="containsText" dxfId="1" priority="4" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IA12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="3">
-      <formula>LEN(TRIM(IA12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IC12">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IC12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="13">
-      <formula>LEN(TRIM(IC12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IE12">
-    <cfRule type="containsText" dxfId="1" priority="32" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IE12)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="31">
-      <formula>LEN(TRIM(IE12))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DC14">
-    <cfRule type="containsText" dxfId="1" priority="785" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DC14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="784">
-      <formula>LEN(TRIM(DC14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DE14">
-    <cfRule type="containsText" dxfId="1" priority="777" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DE14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="776">
-      <formula>LEN(TRIM(DE14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DI14">
-    <cfRule type="containsText" dxfId="1" priority="749" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DI14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="748">
-      <formula>LEN(TRIM(DI14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DK14">
-    <cfRule type="containsText" dxfId="1" priority="737" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DK14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="736">
-      <formula>LEN(TRIM(DK14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DQ14">
-    <cfRule type="containsText" dxfId="1" priority="697" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DQ14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="696">
-      <formula>LEN(TRIM(DQ14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DS14">
-    <cfRule type="containsText" dxfId="1" priority="713" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DS14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="712">
-      <formula>LEN(TRIM(DS14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DW14">
-    <cfRule type="containsText" dxfId="1" priority="723" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DW14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="722">
-      <formula>LEN(TRIM(DW14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DY14">
-    <cfRule type="containsText" dxfId="1" priority="683" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DY14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="682">
-      <formula>LEN(TRIM(DY14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EE14">
-    <cfRule type="containsText" dxfId="1" priority="672" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EE14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="671">
-      <formula>LEN(TRIM(EE14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EG14">
-    <cfRule type="containsText" dxfId="1" priority="662" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EG14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="661">
-      <formula>LEN(TRIM(EG14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EM14">
-    <cfRule type="containsText" dxfId="1" priority="656" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EM14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="655">
-      <formula>LEN(TRIM(EM14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EQ14">
-    <cfRule type="containsText" dxfId="1" priority="644" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EQ14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="643">
-      <formula>LEN(TRIM(EQ14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="ES14">
-    <cfRule type="containsText" dxfId="1" priority="630" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",ES14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="629">
-      <formula>LEN(TRIM(ES14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EU14">
-    <cfRule type="containsText" dxfId="1" priority="612" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EU14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="611">
-      <formula>LEN(TRIM(EU14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FI14">
-    <cfRule type="containsText" dxfId="1" priority="573" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FI14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="572">
-      <formula>LEN(TRIM(FI14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FK14">
-    <cfRule type="containsText" dxfId="1" priority="565" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FK14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="564">
-      <formula>LEN(TRIM(FK14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FM14">
-    <cfRule type="containsText" dxfId="1" priority="548" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FM14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="547">
-      <formula>LEN(TRIM(FM14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FO14">
-    <cfRule type="containsText" dxfId="1" priority="536" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FO14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="535">
-      <formula>LEN(TRIM(FO14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FU14">
-    <cfRule type="containsText" dxfId="1" priority="510" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FU14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="509">
-      <formula>LEN(TRIM(FU14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FW14">
-    <cfRule type="containsText" dxfId="1" priority="518" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FW14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="517">
-      <formula>LEN(TRIM(FW14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FY14">
-    <cfRule type="containsText" dxfId="1" priority="441" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FY14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="440">
-      <formula>LEN(TRIM(FY14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GA14">
-    <cfRule type="containsText" dxfId="1" priority="449" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GA14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="448">
-      <formula>LEN(TRIM(GA14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GC14">
-    <cfRule type="containsText" dxfId="1" priority="459" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GC14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="458">
-      <formula>LEN(TRIM(GC14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GI14">
-    <cfRule type="containsText" dxfId="1" priority="283" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GI14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="282">
-      <formula>LEN(TRIM(GI14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GK14">
-    <cfRule type="containsText" dxfId="1" priority="275" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GK14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="274">
-      <formula>LEN(TRIM(GK14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GM14">
-    <cfRule type="containsText" dxfId="1" priority="259" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GM14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="258">
-      <formula>LEN(TRIM(GM14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GO14">
-    <cfRule type="containsText" dxfId="1" priority="241" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GO14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="240">
-      <formula>LEN(TRIM(GO14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GQ14">
-    <cfRule type="containsText" dxfId="1" priority="247" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GQ14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="246">
-      <formula>LEN(TRIM(GQ14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GW14">
-    <cfRule type="containsText" dxfId="1" priority="344" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GW14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="343">
-      <formula>LEN(TRIM(GW14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GY14">
-    <cfRule type="containsText" dxfId="1" priority="352" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GY14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="351">
-      <formula>LEN(TRIM(GY14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HA14">
-    <cfRule type="containsText" dxfId="1" priority="305" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HA14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="304">
-      <formula>LEN(TRIM(HA14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HC14">
-    <cfRule type="containsText" dxfId="1" priority="313" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HC14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="312">
-      <formula>LEN(TRIM(HC14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HK14">
-    <cfRule type="containsText" dxfId="1" priority="152" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HK14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="151">
-      <formula>LEN(TRIM(HK14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HM14">
-    <cfRule type="containsText" dxfId="1" priority="86" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HM14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="85">
-      <formula>LEN(TRIM(HM14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HO14">
-    <cfRule type="containsText" dxfId="1" priority="92" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HO14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="91">
-      <formula>LEN(TRIM(HO14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HQ14">
-    <cfRule type="containsText" dxfId="1" priority="130" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HQ14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="129">
-      <formula>LEN(TRIM(HQ14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HS14">
-    <cfRule type="containsText" dxfId="1" priority="114" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HS14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="113">
-      <formula>LEN(TRIM(HS14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HY14">
-    <cfRule type="containsText" dxfId="1" priority="56" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HY14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="55">
-      <formula>LEN(TRIM(HY14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IA14">
-    <cfRule type="containsText" dxfId="1" priority="6" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IA14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="5">
-      <formula>LEN(TRIM(IA14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IC14">
-    <cfRule type="containsText" dxfId="1" priority="12" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IC14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="11">
-      <formula>LEN(TRIM(IC14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IE14">
-    <cfRule type="containsText" dxfId="1" priority="34" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IE14)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="33">
-      <formula>LEN(TRIM(IE14))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DE16">
-    <cfRule type="containsText" dxfId="1" priority="779" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DE16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="778">
-      <formula>LEN(TRIM(DE16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DG16">
-    <cfRule type="containsText" dxfId="1" priority="761" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DG16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="760">
-      <formula>LEN(TRIM(DG16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DI16">
-    <cfRule type="containsText" dxfId="1" priority="751" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DI16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="750">
-      <formula>LEN(TRIM(DI16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DK16">
-    <cfRule type="containsText" dxfId="1" priority="735" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DK16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="734">
-      <formula>LEN(TRIM(DK16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DS16">
-    <cfRule type="containsText" dxfId="1" priority="715" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DS16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="714">
-      <formula>LEN(TRIM(DS16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DU16">
-    <cfRule type="containsText" dxfId="1" priority="719" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DU16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="718">
-      <formula>LEN(TRIM(DU16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DW16">
-    <cfRule type="containsText" dxfId="1" priority="721" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DW16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="720">
-      <formula>LEN(TRIM(DW16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EG16">
-    <cfRule type="containsText" dxfId="1" priority="660" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EG16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="659">
-      <formula>LEN(TRIM(EG16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EM16">
-    <cfRule type="containsText" dxfId="1" priority="654" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EM16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="653">
-      <formula>LEN(TRIM(EM16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EQ16">
-    <cfRule type="containsText" dxfId="1" priority="642" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EQ16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="641">
-      <formula>LEN(TRIM(EQ16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="ES16">
-    <cfRule type="containsText" dxfId="1" priority="628" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",ES16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="627">
-      <formula>LEN(TRIM(ES16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EU16">
-    <cfRule type="containsText" dxfId="1" priority="610" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EU16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="609">
-      <formula>LEN(TRIM(EU16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FI16">
-    <cfRule type="containsText" dxfId="1" priority="571" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FI16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="570">
-      <formula>LEN(TRIM(FI16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FM16">
-    <cfRule type="containsText" dxfId="1" priority="550" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FM16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="549">
-      <formula>LEN(TRIM(FM16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FO16">
-    <cfRule type="containsText" dxfId="1" priority="534" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FO16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="533">
-      <formula>LEN(TRIM(FO16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FU16">
-    <cfRule type="containsText" dxfId="1" priority="508" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FU16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="507">
-      <formula>LEN(TRIM(FU16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FW16">
-    <cfRule type="containsText" dxfId="1" priority="516" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FW16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="515">
-      <formula>LEN(TRIM(FW16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GA16">
-    <cfRule type="containsText" dxfId="1" priority="453" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GA16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="452">
-      <formula>LEN(TRIM(GA16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GI16">
-    <cfRule type="containsText" dxfId="1" priority="410" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GI16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="409">
-      <formula>LEN(TRIM(GI16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GK16">
-    <cfRule type="containsText" dxfId="1" priority="277" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GK16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="276">
-      <formula>LEN(TRIM(GK16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GM16">
-    <cfRule type="containsBlanks" dxfId="0" priority="401">
-      <formula>LEN(TRIM(GM16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GO16">
-    <cfRule type="containsText" dxfId="1" priority="243" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GO16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="242">
-      <formula>LEN(TRIM(GO16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GW16">
-    <cfRule type="containsText" dxfId="1" priority="342" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GW16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="341">
-      <formula>LEN(TRIM(GW16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GY16">
-    <cfRule type="containsText" dxfId="1" priority="350" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GY16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="349">
-      <formula>LEN(TRIM(GY16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HC16">
-    <cfRule type="containsText" dxfId="1" priority="317" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HC16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="316">
-      <formula>LEN(TRIM(HC16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HK16">
-    <cfRule type="containsText" dxfId="1" priority="150" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HK16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="149">
-      <formula>LEN(TRIM(HK16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HM16">
-    <cfRule type="containsText" dxfId="1" priority="88" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HM16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="87">
-      <formula>LEN(TRIM(HM16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HO16">
-    <cfRule type="containsText" dxfId="1" priority="90" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HO16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="89">
-      <formula>LEN(TRIM(HO16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HQ16">
-    <cfRule type="containsText" dxfId="1" priority="132" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HQ16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="131">
-      <formula>LEN(TRIM(HQ16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HS16">
-    <cfRule type="containsText" dxfId="1" priority="112" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HS16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="111">
-      <formula>LEN(TRIM(HS16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HY16">
-    <cfRule type="containsText" dxfId="1" priority="54" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HY16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="53">
-      <formula>LEN(TRIM(HY16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IA16">
-    <cfRule type="containsText" dxfId="1" priority="8" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IA16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="7">
-      <formula>LEN(TRIM(IA16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IC16">
-    <cfRule type="containsText" dxfId="1" priority="10" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IC16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="9">
-      <formula>LEN(TRIM(IC16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IE16">
-    <cfRule type="containsText" dxfId="1" priority="36" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IE16)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="35">
-      <formula>LEN(TRIM(IE16))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DE18">
-    <cfRule type="containsText" dxfId="1" priority="781" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DE18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="780">
-      <formula>LEN(TRIM(DE18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DG18">
-    <cfRule type="containsText" dxfId="1" priority="759" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DG18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="758">
-      <formula>LEN(TRIM(DG18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DI18">
-    <cfRule type="containsText" dxfId="1" priority="753" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DI18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="752">
-      <formula>LEN(TRIM(DI18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DK18">
-    <cfRule type="containsText" dxfId="1" priority="733" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DK18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="732">
-      <formula>LEN(TRIM(DK18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DQ18">
-    <cfRule type="containsText" dxfId="1" priority="691" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DQ18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="690">
-      <formula>LEN(TRIM(DQ18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DY18">
-    <cfRule type="containsText" dxfId="1" priority="681" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DY18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="680">
-      <formula>LEN(TRIM(DY18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EG18">
-    <cfRule type="containsText" dxfId="1" priority="658" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EG18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="657">
-      <formula>LEN(TRIM(EG18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EM18">
-    <cfRule type="containsText" dxfId="1" priority="652" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EM18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="651">
-      <formula>LEN(TRIM(EM18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EQ18">
-    <cfRule type="containsText" dxfId="1" priority="640" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EQ18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="639">
-      <formula>LEN(TRIM(EQ18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="ES18">
-    <cfRule type="containsText" dxfId="1" priority="626" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",ES18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="625">
-      <formula>LEN(TRIM(ES18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EW18">
-    <cfRule type="containsText" dxfId="1" priority="601" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EW18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="600">
-      <formula>LEN(TRIM(EW18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FK18">
-    <cfRule type="containsText" dxfId="1" priority="569" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FK18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="568">
-      <formula>LEN(TRIM(FK18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FM18">
-    <cfRule type="containsText" dxfId="1" priority="552" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FM18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="551">
-      <formula>LEN(TRIM(FM18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FO18">
-    <cfRule type="containsText" dxfId="1" priority="532" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FO18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="531">
-      <formula>LEN(TRIM(FO18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FU18">
-    <cfRule type="containsText" dxfId="1" priority="506" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FU18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="505">
-      <formula>LEN(TRIM(FU18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FY18">
-    <cfRule type="containsText" dxfId="1" priority="496" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FY18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="495">
-      <formula>LEN(TRIM(FY18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GA18">
-    <cfRule type="containsText" dxfId="1" priority="455" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GA18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="454">
-      <formula>LEN(TRIM(GA18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GC18">
-    <cfRule type="containsText" dxfId="1" priority="457" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GC18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="456">
-      <formula>LEN(TRIM(GC18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GI18">
-    <cfRule type="containsText" dxfId="1" priority="281" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GI18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="280">
-      <formula>LEN(TRIM(GI18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GM18">
-    <cfRule type="containsText" dxfId="1" priority="257" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GM18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="256">
-      <formula>LEN(TRIM(GM18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GO18">
-    <cfRule type="containsText" dxfId="1" priority="251" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GO18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="250">
-      <formula>LEN(TRIM(GO18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GQ18">
-    <cfRule type="containsText" dxfId="1" priority="249" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GQ18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="248">
-      <formula>LEN(TRIM(GQ18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GW18">
-    <cfRule type="containsText" dxfId="1" priority="340" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GW18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="339">
-      <formula>LEN(TRIM(GW18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HA18">
-    <cfRule type="containsText" dxfId="1" priority="330" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HA18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="329">
-      <formula>LEN(TRIM(HA18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HC18">
-    <cfRule type="containsText" dxfId="1" priority="319" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HC18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="318">
-      <formula>LEN(TRIM(HC18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HK18">
-    <cfRule type="containsText" dxfId="1" priority="146" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HK18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="145">
-      <formula>LEN(TRIM(HK18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HM18">
-    <cfRule type="containsText" dxfId="1" priority="142" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HM18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="141">
-      <formula>LEN(TRIM(HM18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HO18">
-    <cfRule type="containsText" dxfId="1" priority="138" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HO18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="137">
-      <formula>LEN(TRIM(HO18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HQ18">
-    <cfRule type="containsText" dxfId="1" priority="134" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HQ18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="133">
-      <formula>LEN(TRIM(HQ18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HS18">
-    <cfRule type="containsText" dxfId="1" priority="110" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HS18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="109">
-      <formula>LEN(TRIM(HS18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HY18">
-    <cfRule type="containsText" dxfId="1" priority="50" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HY18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="49">
-      <formula>LEN(TRIM(HY18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IA18">
-    <cfRule type="containsText" dxfId="1" priority="46" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IA18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="45">
-      <formula>LEN(TRIM(IA18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IC18">
-    <cfRule type="containsText" dxfId="1" priority="42" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IC18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="41">
-      <formula>LEN(TRIM(IC18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IE18">
-    <cfRule type="containsText" dxfId="1" priority="38" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IE18)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="37">
-      <formula>LEN(TRIM(IE18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DC20">
-    <cfRule type="containsText" dxfId="1" priority="783" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DC20)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="782">
-      <formula>LEN(TRIM(DC20))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DG20">
-    <cfRule type="containsText" dxfId="1" priority="757" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DG20)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="756">
-      <formula>LEN(TRIM(DG20))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DI20">
-    <cfRule type="containsText" dxfId="1" priority="755" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DI20)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="754">
-      <formula>LEN(TRIM(DI20))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DK20">
-    <cfRule type="containsText" dxfId="1" priority="731" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DK20)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="730">
-      <formula>LEN(TRIM(DK20))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DU20">
-    <cfRule type="containsText" dxfId="1" priority="717" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DU20)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="716">
-      <formula>LEN(TRIM(DU20))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EW20">
-    <cfRule type="containsText" dxfId="1" priority="599" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",EW20)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="598">
-      <formula>LEN(TRIM(EW20))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FK20">
-    <cfRule type="containsText" dxfId="1" priority="567" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FK20)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="566">
-      <formula>LEN(TRIM(FK20))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FM20">
-    <cfRule type="containsText" dxfId="1" priority="554" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FM20)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="553">
-      <formula>LEN(TRIM(FM20))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FO20">
-    <cfRule type="containsText" dxfId="1" priority="530" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FO20)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="529">
-      <formula>LEN(TRIM(FO20))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FY20">
-    <cfRule type="containsText" dxfId="1" priority="439" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FY20)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="438">
-      <formula>LEN(TRIM(FY20))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GA20">
-    <cfRule type="containsText" dxfId="1" priority="451" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GA20)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="450">
-      <formula>LEN(TRIM(GA20))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GK20">
-    <cfRule type="containsText" dxfId="1" priority="279" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GK20)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="278">
-      <formula>LEN(TRIM(GK20))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GM20">
-    <cfRule type="containsText" dxfId="1" priority="255" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GM20)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="254">
-      <formula>LEN(TRIM(GM20))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GO20">
-    <cfRule type="containsText" dxfId="1" priority="253" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GO20)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="252">
-      <formula>LEN(TRIM(GO20))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HA20">
-    <cfRule type="containsText" dxfId="1" priority="303" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HA20)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="302">
-      <formula>LEN(TRIM(HA20))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HC20">
-    <cfRule type="containsText" dxfId="1" priority="315" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HC20)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="314">
-      <formula>LEN(TRIM(HC20))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HK20">
-    <cfRule type="containsText" dxfId="1" priority="148" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HK20)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="147">
-      <formula>LEN(TRIM(HK20))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HM20">
-    <cfRule type="containsText" dxfId="1" priority="144" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HM20)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="143">
-      <formula>LEN(TRIM(HM20))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HO20">
-    <cfRule type="containsText" dxfId="1" priority="140" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HO20)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="139">
-      <formula>LEN(TRIM(HO20))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HQ20">
-    <cfRule type="containsText" dxfId="1" priority="136" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HQ20)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="135">
-      <formula>LEN(TRIM(HQ20))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HS20">
-    <cfRule type="containsText" dxfId="1" priority="108" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HS20)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="107">
-      <formula>LEN(TRIM(HS20))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HY20">
-    <cfRule type="containsText" dxfId="1" priority="52" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HY20)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="51">
-      <formula>LEN(TRIM(HY20))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IA20">
-    <cfRule type="containsText" dxfId="1" priority="48" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IA20)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="47">
-      <formula>LEN(TRIM(IA20))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IC20">
-    <cfRule type="containsText" dxfId="1" priority="44" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IC20)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="43">
-      <formula>LEN(TRIM(IC20))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IE20">
-    <cfRule type="containsText" dxfId="1" priority="40" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IE20)))</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="39">
-      <formula>LEN(TRIM(IE20))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DX3:DX20">
-    <cfRule type="containsText" dxfId="2" priority="689" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",DX3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="ED3:ED20">
-    <cfRule type="containsText" dxfId="2" priority="679" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",ED3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EF3:EF20">
-    <cfRule type="containsText" dxfId="2" priority="678" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",EF3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EP3:EP20">
-    <cfRule type="containsText" dxfId="2" priority="624" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",EP3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="ER3:ER20">
-    <cfRule type="containsText" dxfId="2" priority="623" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",ER3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="ET3:ET20">
-    <cfRule type="containsText" dxfId="2" priority="622" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",ET3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FT3:FT20">
-    <cfRule type="containsText" dxfId="2" priority="504" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",FT3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FV3:FV20">
-    <cfRule type="containsText" dxfId="2" priority="503" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",FV3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FX3:FX20">
-    <cfRule type="containsText" dxfId="2" priority="498" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",FX3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GH3:GH20">
-    <cfRule type="containsText" dxfId="2" priority="406" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",GH3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GJ3:GJ20">
-    <cfRule type="containsText" dxfId="2" priority="405" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",GJ3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GL3:GL20">
-    <cfRule type="containsText" dxfId="2" priority="400" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",GL3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GV3:GV20">
-    <cfRule type="containsText" dxfId="2" priority="338" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",GV3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GX3:GX20">
-    <cfRule type="containsText" dxfId="2" priority="337" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",GX3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GZ3:GZ20">
-    <cfRule type="containsText" dxfId="2" priority="332" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",GZ3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HJ3:HJ20">
-    <cfRule type="containsText" dxfId="2" priority="167" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",HJ3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HL3:HL20">
-    <cfRule type="containsText" dxfId="2" priority="207" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",HL3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HN3:HN20">
-    <cfRule type="containsText" dxfId="2" priority="202" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",HN3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HX3:HX20">
-    <cfRule type="containsText" dxfId="2" priority="69" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",HX3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HZ3:HZ20">
-    <cfRule type="containsText" dxfId="2" priority="77" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",HZ3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IB3:IB20">
-    <cfRule type="containsText" dxfId="2" priority="73" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",IB3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B3:B21 D3:D21 KV3:KV21 LH3:LH21 KT3:KT21 KR3:KR21 F3:F21 KP3:KP21 KN3:KN21 KL3:KL21 H3:H21 KJ3:KJ21 KH3:KH21 KF3:KF21 J3:J21 KD3:KD21 KB3:KB21 JZ3:JZ21 L3:L21 JX3:JX21 JV3:JV21 JT3:JT21 N3:N21 JR3:JR21 P3:P21 JP3:JP21 R3:R21 JN3:JN21 T3:T21 JL3:JL21 V3:V21 JJ3:JJ21 X3:X21 JH3:JH21 JF3:JF21 Z3:Z21 JD3:JD21 JB3:JB21 AB3:AB21 IZ3:IZ21 IX3:IX21 AD3:AD21 IV3:IV21 IT3:IT21 AF3:AF21 IR3:IR21 IP3:IP21 AH3:AH21 IN3:IN21 IL3:IL21 AJ3:AJ21 IJ3:IJ21 IH3:IH21 AL3:AL21 IF21 ID21 AN3:AN21 IB21 HZ21 AP3:AP21 HX21 HV3:HV21 AR3:AR21 HT3:HT21 HR21 AT3:AT21 HP21 HN21 AV3:AV21 HL21 HJ21 AX3:AX21 HH3:HH21 HF3:HF21 AZ3:AZ21 HD21 HB21 BB3:BB21 GZ21 GX21 BD3:BD21 GV21 GT3:GT21 BF3:BF21 GR3:GR21 GP21 BH3:BH21 GN21 GL21 BJ3:BJ21 GJ21 GH21 BL3:BL21 GF3:GF21 GD3:GD21 BN3:BN21 GB21 FZ21 BP3:BP21 FX21 FV21 BR3:BR21 FT21 FR3:FR21 BT3:BT21 FP3:FP21 FN21 BV3:BV21 FL21 FJ21 BX3:BX21 FH21 FF3:FF21 BZ3:BZ21 FD3:FD21 FB3:FB21 CB3:CB21 EZ3:EZ21 EX3:EX21 CD3:CD21 EV3:EV21 ET21 CF3:CF21 ER21 EP21 CH3:CH21 EN3:EN21 EL3:EL21 CJ3:CJ21 EJ3:EJ21 EH3:EH21 CL3:CL21 EF21 ED21 CN3:CN21 EB3:EB21 DZ3:DZ21 CP3:CP21 DX21 DV21 CR3:CR21 DT21 DR21 CT3:CT21 DP21 DN3:DN21 CV3:CV21 DL3:DL21 DJ21 CX3:CX21 DH21 DF21 CZ3:CZ21 DD21 DB21 LI11 KU11 KS11 KW11:LG11 KQ11 KO11 KM11 LF12:LF21 KK11 KI11 KG11 LD12:LD21 KE11 KC11 KA11 LB12:LB21 JY11 JW11 JU11 KZ12:KZ21 JS11 JQ11 JO11 JM11 JK11 JI11 JG11 W11 JE11 JC11 Y11 JA11 IY11 AA11 IW11 IU11 AC11 IS11 IQ11 AE11 IO11 IM11 AG11 IK11 II11 AI11 IG11 AK11 AM11 HW11 AO11 HU11 HS11 AQ11 AS11 AU11 HI11 HG11 AW11 HE11 AY11 BA11 GU11 BC11 GS11 GQ11 BE11 BG11 BI11 GG11 GE11 BK11 GC11 BM11 FW11 BO11 FU11 FS11 BQ11 FQ11 BS11 FK11 BU11 FG11 BW11 FE11 FC11 BY11 FA11 EY11 CA11 EW11 EU11 CC11 ES11 EQ11 CE11 EO11 EM11 CG11 EK11 EI11 CI11 EG11 EE11 CK11 EC11 EA11 CM11 DY11 CO11 CQ11 DO11 CS11 DM11 CU11 CW11 CY11 DA11 KX3:KX10 KX12:KX21 KZ3:KZ10 LB3:LB10 LD3:LD10 LF3:LF10">
-    <cfRule type="containsText" dxfId="2" priority="802" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",B3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C3 C5 G5 E5 G3 E3 I3 I5 K3 M3 K5 M5 LI5 LG5 LE5 LC5 LA5 KY5 KW5 KU5 KS5 KQ5 O3 Q3 S3 U3 W3 Y3 AA3 AC3 AE3 AG3 AI3 AK3 AM3 AO3 AQ3 AS3 AU3 AW3 AY3 BA3 BC3 BE3 BG3 BI3 BK3 BM3 BO3 BQ3 BS3 BU3 BW3 BY3 CA3 CC3 CE3 CG3 CI3 CK3 CM3 CO3 CQ3 CS3 CU3 CW3 CY3 DA3 DM3 DO3 DY3 EA3 EC3 EE3 EG3 EI3 EK3 EM3 EO3 EQ3 ES3 EU3 EW3 EY3 FA3 FC3 FE3 FG3 FK3 FQ3 FS3 FU3 FW3 GC3 GE3 GG3 GS3 GU3 HE3 HG3 HI3 HU3 HW3 IG3 II3 IK3 IM3 IO3 IQ3 IS3 IU3 IW3 IY3 JA3 JC3 JE3 JG3 JI3 JK3 JM3 JO3 JQ3 JS3 JU3 JW3 JY3 KA3 KC3 KE3 KG3 KI3 KK3 KM3 KO3 KQ3 KS3 KU3 KW3 KY3 LA3 LC3 LE3 LG3 LI3 KO5 KM5 KK5 KI5 O5 Q5 S5 U5 W5 Y5 AA5 AC5 AE5 AG5 AI5 AK5 AM5 AO5 AQ5 AS5 AU5 AW5 AY5 BA5 BC5 BE5 BG5 BI5 BK5 BM5 BO5 BQ5 BS5 BU5 BW5 BY5 CA5 CC5 CE5 CG5 CI5 CK5 CM5 CO5 CQ5 CS5 CU5 CW5 CY5 DA5 DM5 DO5 DY5 EA5 EC5 EE5 EI5 EK5 EM5 EO5 EQ5 EY5 FA5 FC5 FE5 FG5 FK5 FQ5 FS5 FU5 GC5 GE5 GG5 GQ5 GS5 GU5 HE5 HG5 HI5 HU5 HW5 IG5 II5 IK5 IM5 IO5 IQ5 IS5 IU5 IW5 IY5 JA5 JC5 JE5 JG5 JI5 JK5 JM5 JO5 JQ5 JS5 JU5 JW5 JY5 KA5 KC5 KE5 KG5 C8 G10 E10 G8 E8 G20 E20 G18 E18 G16 E16 G14 E14 G12 E12 C10 C12 C14 C16 C18 C20 I12 I14 I16 I18 I20 I8 I10 LI20 LG20 LE20 LC20 K8 M8 K10 M10 K12 M12 K14 M14 K16 M16 K18 M18 K20 M20 HW20 HU20 HI20 HG20 HE20 GU20 GS20 GQ20 GG20 GE20 GC20 FW20 FU20 FS20 FQ20 FG20 FE20 FC20 FA20 EY20 EU20 ES20 EQ20 EO20 EM20 EK20 EI20 EG20 EE20 EC20 EA20 DY20 DO20 DM20 DA20 CY20 CW20 CU20 CS20 CQ20 CO20 CM20 CK20 CI20 CG20 CE20 CC20 CA20 BY20 BW20 BU20 BS20 BQ20 BO20 BM20 BK20 BI20 BG20 BE20 BC20 BA20 AY20 AW20 AU20 AS20 AQ20 AO20 AM20 AK20 AI20 AG20 AE20 AC20 AA20 Y20 W20 U20 S20 Q20 O20 JI20 JK20 LI18 LG18 LE18 LC18 LA18 KY18 KW18 KU18 KS18 KQ18 KO18 KM18 KK18 KI18 KG18 KE18 KC18 KA18 JY18 JW18 JU18 JS18 JQ18 JO18 JM18 JK18 JI18 JG18 JE18 JC18 JA18 IY18 IW18 IU18 IS18 IQ18 IO18 IM18 IK18 II18 IG18 HW18 HU18 HI18 HG18 HE18 GU18 GS18 GG18 GE18 FW18 FS18 FQ18 FG18 FE18 FC18 FA18 EY18 EU18 EO18 EK18 EI18 EE18 EC18 EA18 DO18 DM18 DA18 CY18 CW18 CU18 CS18 CQ18 CO18 CM18 CK18 CI18 CG18 CE18 CC18 CA18 BY18 BW18 BU18 BS18 BQ18 BO18 BM18 BK18 BI18 BG18 BE18 BC18 BA18 AY18 AW18 AU18 AS18 AQ18 AO18 AM18 AK18 AI18 AG18 AE18 AC18 AA18 Y18 W18 U18 S18 Q18 O18 JM20 JO20 LI16 LG16 LE16 LC16 LA16 KY16 KW16 KU16 KS16 KQ16 KO16 KM16 KK16 KI16 KG16 KE16 KC16 KA16 JY16 JW16 JU16 JS16 JQ16 JO16 JM16 JK16 JI16 JG16 JE16 JC16 JA16 IY16 IW16 IU16 IS16 IQ16 IO16 IM16 IK16 II16 IG16 HW16 HU16 HI16 HG16 HE16 GU16 GS16 GQ16 GG16 GE16 GC16 FS16 FQ16 FK16 FG16 FE16 FC16 FA16 EY16 EW16 EO16 EK16 EI16 EE16 EC16 EA16 DY16 DO16 DM16 DA16 CY16 CW16 CU16 CS16 CQ16 CO16 CM16 CK16 CI16 CG16 CE16 CC16 CA16 BY16 BW16 BU16 BS16 BQ16 BO16 BM16 BK16 BI16 BG16 BE16 BC16 BA16 AY16 AW16 AU16 AS16 AQ16 AO16 AM16 AK16 AI16 AG16 AE16 AC16 AA16 Y16 W16 U16 S16 Q16 O16 IG20 II20 JQ20 JS20 LI14 LG14 LE14 LC14 LA14 KY14 KW14 KU14 KS14 KQ14 KO14 KM14 KK14 KI14 KG14 KE14 KC14 KA14 JY14 JW14 JU14 JS14 JQ14 JO14 JM14 JK14 JI14 JG14 JE14 JC14 JA14 IY14 IW14 IU14 IS14 IQ14 IO14 IM14 IK14 II14 IG14 HW14 HU14 HI14 HG14 HE14 GU14 GS14 GG14 GE14 FS14 FQ14 FG14 FE14 FC14 FA14 EY14 EW14 EO14 EK14 EI14 EC14 EA14 DO14 DM14 DA14 CY14 CW14 CU14 CS14 CQ14 CO14 CM14 CK14 CI14 CG14 CE14 CC14 CA14 BY14 BW14 BU14 BS14 BQ14 BO14 BM14 BK14 BI14 BG14 BE14 BC14 BA14 AY14 AW14 AU14 AS14 AQ14 AO14 AM14 AK14 AI14 AG14 AE14 AC14 AA14 Y14 W14 U14 S14 Q14 O14 IK20 IM20 JU20 JW20 LI12 LG12 LE12 LC12 LA12 KY12 KW12 KU12 KS12 KQ12 KO12 KM12 KK12 KI12 KG12 KE12 KC12 KA12 JY12 JW12 JU12 JS12 JQ12 JO12 JM12 JK12 JI12 JG12 JE12 JC12 JA12 IY12 IW12 IU12 IS12 IQ12 IO12 IM12 IK12 II12 IG12 HW12 HU12 HI12 HG12 HE12 GU12 GS12 GG12 GE12 GC12 FS12 FQ12 FG12 FE12 FC12 FA12 EY12 EO12 EM12 EK12 EI12 EC12 EA12 DY12 DO12 DM12 DA12 CY12 CW12 CU12 CS12 CQ12 CO12 CM12 CK12 CI12 CG12 CE12 CC12 CA12 BY12 BW12 BU12 BS12 BQ12 BO12 BM12 BK12 BI12 BG12 BE12 BC12 BA12 AY12 AW12 AU12 AS12 AQ12 AO12 AM12 AK12 AI12 AG12 AE12 AC12 AA12 Y12 W12 U12 S12 Q12 O12 IO20 IQ20 JY20 KA20 LI10 LG10 LE10 LC10 LA10 KY10 KW10 KU10 KS10 KQ10 KO10 KM10 KK10 KI10 KG10 KE10 KC10 KA10 JY10 JW10 JU10 JS10 JQ10 JO10 JM10 JK10 JI10 JG10 JE10 JC10 JA10 IY10 IW10 IU10 IS10 IQ10 IO10 IM10 IK10 II10 IG10 HW10 HU10 HI10 HG10 HE10 GU10 GS10 GQ10 GG10 GE10 FS10 FQ10 FG10 FE10 FC10 FA10 EY10 EW10 EO10 EM10 EK10 EI10 EE10 EC10 EA10 DO10 DM10 DA10 CY10 CW10 CU10 CS10 CQ10 CO10 CM10 CK10 CI10 CG10 CE10 CC10 CA10 BY10 BW10 BU10 BS10 BQ10 BO10 BM10 BK10 BI10 BG10 BE10 BC10 BA10 AY10 AW10 AU10 AS10 AQ10 AO10 AM10 AK10 AI10 AG10 AE10 AC10 AA10 Y10 W10 U10 S10 Q10 O10 IS20 IU20 KC20 KE20 LI8 LG8 LE8 LC8 LA8 KY8 KW8 KU8 KS8 KQ8 KO8 KM8 KK8 KI8 KG8 KE8 KC8 KA8 JY8 JW8 JU8 JS8 JQ8 JO8 JM8 JK8 JI8 JG8 JE8 JC8 JA8 IY8 IW8 IU8 IS8 IQ8 IO8 IM8 IK8 II8 IG8 HW8 HU8 HI8 HG8 HE8 GU8 GS8 GQ8 GG8 GE8 FS8 FQ8 FG8 FE8 FC8 FA8 EY8 EO8 EM8 EK8 EI8 EC8 EA8 DO8 DM8 DA8 CY8 CW8 CU8 CS8 CQ8 CO8 CM8 CK8 CI8 CG8 CE8 CC8 CA8 BY8 BW8 BU8 BS8 BQ8 BO8 BM8 BK8 BI8 BG8 BE8 BC8 BA8 AY8 AW8 AU8 AS8 AQ8 AO8 AM8 AK8 AI8 AG8 AE8 AC8 AA8 Y8 W8 U8 S8 Q8 O8 IW20 IY20 KG20 KI20 LA20 KY20 KW20 KU20 KS20 KQ20 KO20 JG20 JE20 KM20 KK20 JC20 JA20">
-    <cfRule type="containsBlanks" dxfId="0" priority="800">
-      <formula>LEN(TRIM(C3))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C21 E3:E21 KW3:KW21 LI3:LI21 KU3:KU21 KS3:KS21 G3:G21 KQ3:KQ21 KO3:KO21 KM3:KM21 I3:I21 KK3:KK21 KI3:KI21 KG3:KG21 K3:K21 KE3:KE21 KC3:KC21 KA3:KA21 M3:M21 JY3:JY21 JW3:JW21 JU3:JU21 O3:O21 JS3:JS21 Q3:Q21 JQ3:JQ21 S3:S21 JO3:JO21 U3:U21 JM3:JM21 W3:W21 JK3:JK21 Y3:Y21 JI3:JI21 JG3:JG21 AA3:AA21 JE3:JE21 JC3:JC21 AC3:AC21 JA3:JA21 IY3:IY21 AE3:AE21 IW3:IW21 IU3:IU21 AG3:AG21 IS3:IS21 IQ3:IQ21 AI3:AI21 IO3:IO21 IM3:IM21 AK3:AK21 IK3:IK21 II3:II21 AM3:AM21 IG3:IG21 IE21 AO3:AO21 IC21 IA21 AQ3:AQ21 HY21 HW3:HW21 AS3:AS21 HU3:HU21 HS4 HS6:HS7 HS9 HS11:HT11 HS13 HS15 HS17 HS19 HS21 AU3:AU21 HQ21 HO21 AW3:AW21 HM21 HK21 AY3:AY21 HI3:HI21 HG3:HG21 BA3:BA21 HE3:HE21 HC21 BC3:BC21 HA21 GY21 BE3:BE21 GW21 GU3:GU21 BG3:BG21 GS3:GS21 GQ4:GQ11 GQ13 GQ15:GQ17 GQ19:GQ21 BI3:BI21 GO21 GM21 BK3:BK21 GK21 GI21 BM3:BM21 GG3:GG21 GE3:GE21 BO3:BO21 GC3:GC7 GC9 GC11:GC13 GC15:GC17 GC19:GC21 GA21 BQ3:BQ21 FY21 FW3:FW4 FW6:FW7 FW9 FU11 FW11 FW13 FW15 FW17:FW21 BS3:BS21 FU3:FU7 FU9 FU13 FU15 FU17 FU19:FU21 FS3:FS21 BU3:BU21 FQ3:FQ21 FO21 BW3:BW21 FM21 FK3:FK7 FK9 FK11 FK13 FK15:FK17 FK19 FK21 BY3:BY21 FI21 FG3:FG21 CA3:CA21 FE3:FE21 FC3:FC21 CC3:CC21 FA3:FA21 EY3:EY21 CE3:CE21 EW3:EW4 EW6:EW7 EW9:EW11 EW13:EW17 EW19 EW21 EU3:EU4 EU6:EU7 EU9 EU11 EU13 EU15 EU17:EU21 CG3:CG21 ES3:ES4 ES6:ES7 ES9 EQ11 ES11 ES13 ES15 ES17 ES19:ES21 EQ3:EQ7 EQ9 EQ13 EQ15 EQ17 EQ19:EQ21 CI3:CI21 EO3:EO21 EM3:EM13 EM15 EM17 EM19:EM21 CK3:CK21 EK3:EK21 EI3:EI21 CM3:CM21 EG3:EG4 EG6:EG7 EG9 EG11:EH11 EG13 EG15 EG17 EG19:EG21 EE3:EE7 EE9:EE11 EE13 EE15:EE21 CO3:CO21 EC3:EC21 EA3:EA21 CQ3:CQ21 DY3:DY7 DY9 DY11:DY13 DY15:DY17 DY19:DY21 DW21 CS3:CS21 DU21 DS21 CU3:CU21 DQ21 DO3:DO21 CW3:CW21 DM3:DM21 DK21 CY3:CY21 DI21 DG21 DA3:DA21 DE21 DC21 KV11 KT11 KX11:LH11 KR11 KP11 KN11 LG12:LG21 KL11 KJ11 KH11 LE12:LE21 KF11 KD11 KB11 LC12:LC21 JZ11 JX11 JV11 LA12:LA21 JT11 JR11 JP11 JN11 JL11 JJ11 JH11 X11 JF11 JD11 Z11 JB11 IZ11 AB11 IX11 IV11 AD11 IT11 IR11 AF11 IP11 IN11 AH11 IL11 IJ11 AJ11 IH11 AL11 AN11 AP11 HV11 AR11 AT11 AV11 HH11 AX11 HF11 AZ11 BB11 BD11 GT11 GR11 BF11 BH11 BJ11 GF11 BL11 GD11 BN11 BP11 BR11 FR11 FP11 BT11 BV11 BX11 FF11 FD11 BZ11 FB11 EZ11 CB11 EX11 CD11 CF11 EN11 CH11 EL11 EJ11 CJ11 CL11 EB11 CN11 DZ11 DN11 DL11 CV11 CX11 CZ11 KY3:KY10 KY12:KY21 LA3:LA10 LC3:LC10 LE3:LE10 LG3:LG10">
-    <cfRule type="containsText" dxfId="1" priority="801" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",C3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DB3:DB20 DD3:DD20 DF3:DF20 DH3:DH20 DJ3:DJ20 DC11 DE11 DG11 DI11 DK11">
-    <cfRule type="containsText" dxfId="2" priority="795" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",DB3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DC3:DC7 DC9:DC11 DC13 DC15:DC19 DE3:DE4 DE6:DE7 DE9 DD11:DF11 DE13 DE15 DE17 DE19:DE20 DG3:DG4 DG6:DG7 DG9:DG11 DG13:DG15 DG17 DG19 DI3:DI7 DI9 DH11:DJ11 DI13 DI15 DI17 DI19 DK3:DK7 DK9 DK11:DK13 DK15 DK17 DK19">
-    <cfRule type="containsText" dxfId="1" priority="794" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DC3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DC3 DE3 DG3 DI3 DK3 DC5 DI5 DK5 DE20 DC18 DC16 DG14 DK12 DG10 DC10">
-    <cfRule type="containsBlanks" dxfId="0" priority="793">
-      <formula>LEN(TRIM(DC3))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DP3:DP20 DR3:DR20 DT3:DT20 DV3:DV20 DQ11 DS11 DU11 DW11">
-    <cfRule type="containsText" dxfId="2" priority="792" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",DP3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DQ3 DS3 DU3 DW3 DQ5 DS5 DW5 DW20 DS20 DQ20 DW18 DU18 DS18 DQ16 DU14 DU10">
-    <cfRule type="containsBlanks" dxfId="0" priority="790">
-      <formula>LEN(TRIM(DQ3))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DQ3:DQ7 DQ9 DQ11:DT11 DQ13 DQ15:DQ17 DQ19:DQ20 DS3:DS7 DS9 DS13 DS15 DS17:DS20 DU3:DU4 DU6:DU7 DU9:DU11 DU13:DU15 DU17:DU19 DW3:DW7 DW9 DV11:DW11 DW13 DW15 DW17:DW20">
-    <cfRule type="containsText" dxfId="1" priority="791" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",DQ3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FH3:FH20 FJ3:FJ20">
-    <cfRule type="containsText" dxfId="2" priority="597" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",FH3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FI3:FI4 FI6:FI7 FI9 FI11 FI13 FI15 FI17:FI20">
-    <cfRule type="containsText" dxfId="1" priority="583" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FI3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FI3 FI20 FI18">
-    <cfRule type="containsBlanks" dxfId="0" priority="582">
-      <formula>LEN(TRIM(FI3))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FL3:FL20 FN3:FN20 FM11 FO11">
-    <cfRule type="containsText" dxfId="2" priority="557" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",FL3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FM3:FM7 FM9 FL11:FN11 FM13 FM15 FM17 FM19 FO3:FO7 FO9 FO11:FO13 FO15 FO17 FO19">
-    <cfRule type="containsText" dxfId="1" priority="556" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FL3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FM3 FO3 FM5 FO5 FO12">
-    <cfRule type="containsBlanks" dxfId="0" priority="555">
-      <formula>LEN(TRIM(FM3))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FY3 FY16">
-    <cfRule type="containsBlanks" dxfId="0" priority="499">
-      <formula>LEN(TRIM(FY3))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FY3:FY4 FY6:FY7 FY9 FY11 FY13 FY15:FY17 FY19">
-    <cfRule type="containsText" dxfId="1" priority="500" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FY3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FZ3:FZ20 GB3:GB20 GA11">
-    <cfRule type="containsText" dxfId="2" priority="484" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",FZ3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GA3:GA4 GA6:GA7 GA9 FZ11:GB11 GA13 GA15 GA17 GA19">
-    <cfRule type="containsText" dxfId="1" priority="483" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",FZ3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GK3 GI20 GK18">
-    <cfRule type="containsBlanks" dxfId="0" priority="431">
-      <formula>LEN(TRIM(GI3))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GK3:GK4 GK6:GK7 GK9 GI11 GK11 GK13 GK15 GK17:GK19 GI4 GI6:GI7 GI9 GI13 GI15 GI17 GI19:GI20">
-    <cfRule type="containsText" dxfId="1" priority="432" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GI3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GN3:GN20 GP3:GP20 GO11">
-    <cfRule type="containsText" dxfId="2" priority="394" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",GN3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GO3:GO4 GO6:GO7 GO9 GN11:GP11 GO13 GO15 GO17 GO19">
-    <cfRule type="containsText" dxfId="1" priority="393" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GN3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GY3:GY4 GY6:GY7 GY9 GW11 GY11 GY13 GY15 GY17:GY20 GW3:GW7 GW9 GW13 GW15 GW17 GW19:GW20">
-    <cfRule type="containsText" dxfId="1" priority="364" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",GW3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GW3 GY3 GW5 GY20 GW20 GY18">
-    <cfRule type="containsBlanks" dxfId="0" priority="363">
-      <formula>LEN(TRIM(GW3))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HA3:HA4 HA6:HA7 HA9 HA11 HA13 HA15:HA17 HA19">
-    <cfRule type="containsText" dxfId="1" priority="334" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HA3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HA3 HA16">
-    <cfRule type="containsBlanks" dxfId="0" priority="333">
-      <formula>LEN(TRIM(HA3))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HB3:HB20 HD3:HD20 HC11">
-    <cfRule type="containsText" dxfId="2" priority="326" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",HB3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HC3:HC4 HC6:HC7 HC9 HB11:HD11 HC13 HC15 HC17 HC19">
-    <cfRule type="containsText" dxfId="1" priority="325" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HB3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HM4 HM6:HM7 HM9 HK11 HM11 HM13 HM15 HM17 HM19 HK3:HK7 HK9 HK13 HK15 HK17 HK19">
-    <cfRule type="containsText" dxfId="1" priority="234" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HK3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HK3 HK5">
-    <cfRule type="containsBlanks" dxfId="0" priority="233">
-      <formula>LEN(TRIM(HK3))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HP3:HP20 HR3:HR20 HQ11">
-    <cfRule type="containsText" dxfId="2" priority="196" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",HP3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IA4 IA6:IA7 IA9 HY11 IA11 IA13 IA15 IA17 IA19 HY3:HY7 HY9 HY13 HY15 HY17 HY19">
-    <cfRule type="containsText" dxfId="1" priority="79" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",HY3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="HY3 HY5">
-    <cfRule type="containsBlanks" dxfId="0" priority="78">
-      <formula>LEN(TRIM(HY3))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="ID3:ID20 IF3:IF20 IE11">
-    <cfRule type="containsText" dxfId="2" priority="71" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",ID3)))</formula>
+      <formula>LEN(TRIM(JI3))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GM4 GM6:GM7 GM9 GM11 GM13 GM15:GM17 GM19">
-    <cfRule type="containsText" dxfId="1" priority="402" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="568" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",GM4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="HO4 HO6:HO7 HO9 HO11 HO13 HO15 HO17 HO19">
-    <cfRule type="containsText" dxfId="1" priority="204" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="370" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",HO4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="HQ4 HQ6:HQ7 HQ9 HP11:HR11 HQ13 HQ15 HQ17 HQ19">
-    <cfRule type="containsText" dxfId="1" priority="195" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="361" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",HP4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="IC4 IC6:IC7 IC9 IC11 IC13 IC15 IC17 IC19">
+    <cfRule type="containsText" dxfId="1" priority="240" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IC4)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IE4 IE6:IE7 IE9 ID11:IF11 IE13 IE15 IE17 IE19">
+    <cfRule type="containsText" dxfId="1" priority="236" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",ID4)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IQ4 IQ6:IQ7 IQ9 IQ11 IQ13 IQ15 IQ17 IQ19">
+    <cfRule type="containsText" dxfId="1" priority="157" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IQ4)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IS4 IS6:IS7 IS9 IR11:IT11 IS13 IS15 IS17 IS19">
+    <cfRule type="containsText" dxfId="1" priority="153" operator="between" text="—">
+      <formula>NOT(ISERROR(SEARCH("—",IR4)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JE4 JE6:JE7 JE9 JE11 JE13 JE15 JE17 JE19">
     <cfRule type="containsText" dxfId="1" priority="74" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",IC4)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="IE4 IE6:IE7 IE9 ID11:IF11 IE13 IE15 IE17 IE19">
+      <formula>NOT(ISERROR(SEARCH("—",JE4)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JG4 JG6:JG7 JG9 JF11:JH11 JG13 JG15 JG17 JG19">
     <cfRule type="containsText" dxfId="1" priority="70" operator="between" text="—">
-      <formula>NOT(ISERROR(SEARCH("—",ID4)))</formula>
+      <formula>NOT(ISERROR(SEARCH("—",JF4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FH11 FJ11">
-    <cfRule type="containsText" dxfId="1" priority="596" operator="between" text="—">
+    <cfRule type="containsText" dxfId="1" priority="762" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",FH11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GK11 GI11">
-    <cfRule type="containsText" dxfId="2" priority="433" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="599" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",GI11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GY11 GW11">
-    <cfRule type="containsText" dxfId="2" priority="365" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="531" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",GW11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="HM11 HK11">
-    <cfRule type="containsText" dxfId="2" priority="235" operator="between" text="占">
+    <cfRule type="containsText" dxfId="2" priority="401" operator="between" text="占">
       <formula>NOT(ISERROR(SEARCH("占",HK11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="IA11 HY11">
+    <cfRule type="containsText" dxfId="2" priority="246" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",HY11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="IO11 IM11">
+    <cfRule type="containsText" dxfId="2" priority="163" operator="between" text="占">
+      <formula>NOT(ISERROR(SEARCH("占",IM11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="JC11 JA11">
     <cfRule type="containsText" dxfId="2" priority="80" operator="between" text="占">
-      <formula>NOT(ISERROR(SEARCH("占",HY11)))</formula>
+      <formula>NOT(ISERROR(SEARCH("占",JA11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22 JO22 JM22 JK22 JI22 JG22 JE22 JC22 JA22 IY22 IW22 IU22 IS22 IQ22 IO22 IM22 IK22 II22 IG22 IE22 IC22 IA22 HY22 HW22 HU22 HS22 HQ22 HO22 HM22 HK22 HI22 HG22 HE22 HC22 HA22 GY22 GW22 GU22 GS22 GQ22 GO22 GM22 GK22 GI22 GG22 GE22 GC22 GA22 FY22 FW22 FU22 FS22 FQ22 FO22 FM22 FK22 FI22 FG22 FE22 FC22 FA22 EY22 EW22 EU22 ES22 EQ22 EO22 EM22 EK22 EI22 EG22 EE22 EC22 EA22 DY22 DW22 DU22 DS22 DQ22 DO22 DM22 DK22 DI22 DG22 DE22 DC22 DA22 CY22 CW22 CU22 CS22 CQ22 CO22 CM22 CK22 CI22 CG22 CE22 CC22 CA22 BY22 BW22 BU22 BS22 BQ22 BO22 BM22 BK22 BI22 BG22 BE22 BC22 BA22 AY22 AW22 AU22 AS22 AQ22 AO22 AM22 AK22 AI22 AG22 AE22 AC22 AA22 Y22 W22 U22 S22 Q22 O22 M22 K22 I22 G22 E22">
-    <cfRule type="containsBlanks" dxfId="3" priority="798">
+    <cfRule type="containsBlanks" dxfId="3" priority="964">
       <formula>LEN(TRIM(C22))=0</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="799" operator="between" text="—">
+    <cfRule type="containsText" dxfId="2" priority="965" operator="between" text="—">
       <formula>NOT(ISERROR(SEARCH("—",C22)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21350,7 +22374,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" ht="28" spans="1:3">
       <c r="A17" s="56" t="s">
         <v>165</v>
       </c>

--- a/c/9班资料.xlsx
+++ b/c/9班资料.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480" activeTab="7"/>
+    <workbookView windowWidth="20750" windowHeight="10480" firstSheet="5" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="七下拖课" sheetId="1" r:id="rId1"/>
@@ -426,7 +426,7 @@
     <t>2025.5.9</t>
   </si>
   <si>
-    <t>刘必艳给卷死其他组”吃烤鱼</t>
+    <t>刘必艳给“卷死其他组”吃烤鱼</t>
   </si>
   <si>
     <t>2025.5.13</t>
@@ -1677,11 +1677,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
       <t>有人说，陈睿卓每天吃得都很补，整天中午吃海参、小米粥。</t>
     </r>
     <r>
@@ -2667,13 +2662,13 @@
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+      <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
-      <scheme val="major"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -4198,6 +4193,13 @@
 </styleSheet>
 </file>
 
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>

--- a/c/9班资料.xlsx
+++ b/c/9班资料.xlsx
@@ -1506,11 +1506,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
       <t xml:space="preserve">体香
 </t>
     </r>
@@ -1645,7 +1640,7 @@
       <t>黄恩亚的字特别潦草，有时连中英文都不容易分辨，史称“甲骨文”。
 黄恩亚喜欢把腿伸到过道上，一次差点把英语老师绊倒。
 黄恩亚经常不写（乱写）作业。
-黄恩亚信仰基督教，他的名字可以这么解释：恩：感恩；亚：亚当。
+黄恩亚信仰基督教，他的名字可以这么解释：恩典时代的亚当。
 黄恩亚喜欢近代史。
 每当有人说他“头发太长”时，他就会捂头。
 黄恩亚曾私藏卷子。一节语文课，黄恩亚周围的人称没发到卷子。大家找了半天。只见黄恩亚从文件袋掏出一叠别人的卷子，令大家震惊。他还辩解“不知道哪一个人放到了他桌上”。
@@ -1677,6 +1672,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
       <t>有人说，陈睿卓每天吃得都很补，整天中午吃海参、小米粥。</t>
     </r>
     <r>
@@ -2665,15 +2665,15 @@
       <scheme val="major"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="62">

--- a/c/9班资料.xlsx
+++ b/c/9班资料.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2202" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2203" uniqueCount="445">
   <si>
     <t>拖课统计表</t>
   </si>
@@ -976,6 +976,9 @@
   </si>
   <si>
     <t>量化</t>
+  </si>
+  <si>
+    <t>剪头发</t>
   </si>
   <si>
     <t>早读</t>
@@ -2646,13 +2649,13 @@
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
-      <scheme val="major"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="62">
@@ -4181,13 +4184,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
@@ -18606,7 +18602,7 @@
   <sheetData>
     <row r="1" s="2" customFormat="1" customHeight="1" spans="1:16">
       <c r="A1" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -18637,7 +18633,7 @@
     </row>
     <row r="3" customHeight="1" spans="1:9">
       <c r="A3" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="13"/>
@@ -18829,7 +18825,7 @@
     </row>
     <row r="11" customHeight="1" spans="1:9">
       <c r="A11" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="13"/>
@@ -19021,7 +19017,7 @@
     </row>
     <row r="19" customHeight="1" spans="1:9">
       <c r="A19" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B19" s="12"/>
       <c r="C19" s="13"/>
@@ -19400,7 +19396,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B15">
         <v>3.5</v>
@@ -19411,7 +19407,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B16">
         <v>3.75</v>
@@ -19433,7 +19429,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B18">
         <v>4.25</v>
@@ -19444,7 +19440,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B19">
         <v>4.5</v>
@@ -19455,7 +19451,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B20">
         <v>4.75</v>
@@ -19466,7 +19462,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B21">
         <v>5</v>
@@ -19477,7 +19473,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B22">
         <v>5.25</v>
@@ -19488,7 +19484,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B23">
         <v>5.5</v>
@@ -19499,7 +19495,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B24">
         <v>5.75</v>
@@ -19510,7 +19506,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B25">
         <v>6</v>
@@ -19553,7 +19549,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B30">
         <v>7.25</v>
@@ -19561,7 +19557,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B31">
         <v>7.5</v>
@@ -19569,7 +19565,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B32">
         <v>7.75</v>
@@ -19577,7 +19573,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B33">
         <v>8</v>
@@ -19585,7 +19581,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B34">
         <v>8.25</v>
@@ -19593,7 +19589,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B35">
         <v>8.5</v>
@@ -19601,7 +19597,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B36">
         <v>8.75</v>
@@ -19609,7 +19605,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B37">
         <v>9</v>
@@ -19617,7 +19613,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B38">
         <v>9.25</v>
@@ -19625,7 +19621,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B39">
         <v>9.5</v>
@@ -19633,7 +19629,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B40">
         <v>9.75</v>
@@ -19641,7 +19637,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B41">
         <v>10</v>
@@ -19649,7 +19645,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B42">
         <v>11</v>
@@ -19657,7 +19653,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B43">
         <v>12</v>
@@ -19665,7 +19661,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B44">
         <v>13</v>
@@ -19673,7 +19669,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B45">
         <v>14</v>
@@ -19681,7 +19677,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B46">
         <v>15</v>
@@ -19689,7 +19685,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B47">
         <v>16</v>
@@ -19697,7 +19693,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B48">
         <v>17</v>
@@ -19705,7 +19701,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B49">
         <v>18</v>
@@ -19713,7 +19709,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B50">
         <v>19</v>
@@ -19721,7 +19717,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B51">
         <v>20</v>
@@ -19729,7 +19725,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B52">
         <v>21</v>
@@ -19737,7 +19733,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B53">
         <v>22</v>
@@ -19745,7 +19741,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B54">
         <v>23</v>
@@ -19753,7 +19749,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B55">
         <v>24</v>
@@ -19761,7 +19757,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B56">
         <v>25</v>
@@ -19769,7 +19765,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B57">
         <v>26</v>
@@ -19777,7 +19773,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B58">
         <v>27</v>
@@ -19785,7 +19781,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B59">
         <v>28</v>
@@ -19793,7 +19789,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B60">
         <v>29</v>
@@ -19801,7 +19797,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B61">
         <v>30</v>
@@ -19809,7 +19805,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B62" t="s">
         <v>5</v>
@@ -19817,117 +19813,117 @@
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="86" spans="1:1">
@@ -19937,7 +19933,7 @@
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -19971,12 +19967,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
   </sheetData>
@@ -21742,45 +21738,48 @@
       </c>
       <c r="D20" s="78"/>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:5">
       <c r="A21" s="83"/>
       <c r="B21" s="84"/>
       <c r="C21" s="87" t="s">
         <v>270</v>
       </c>
       <c r="D21" s="78"/>
+      <c r="E21" s="73" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="22" ht="28" spans="1:5">
       <c r="A22" s="83"/>
       <c r="B22" s="84"/>
       <c r="C22" s="87" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D22" s="88"/>
       <c r="E22" s="73" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="83"/>
       <c r="B23" s="84"/>
       <c r="C23" s="71" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D23" s="71"/>
       <c r="E23" s="73" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="83"/>
       <c r="B24" s="84"/>
       <c r="C24" s="71" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D24" s="71"/>
       <c r="E24" s="73" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="25" ht="28" spans="1:5">
@@ -21794,10 +21793,10 @@
         <v>231</v>
       </c>
       <c r="D25" s="89" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E25" s="73" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -21805,10 +21804,10 @@
       <c r="B26" s="84"/>
       <c r="C26" s="85"/>
       <c r="D26" s="72" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E26" s="73" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="27" ht="28" spans="1:5">
@@ -21816,10 +21815,10 @@
       <c r="B27" s="84"/>
       <c r="C27" s="85"/>
       <c r="D27" s="72" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E27" s="73" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28" ht="42" spans="1:5">
@@ -21827,10 +21826,10 @@
       <c r="B28" s="84"/>
       <c r="C28" s="85"/>
       <c r="D28" s="72" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E28" s="73" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="29" ht="42" spans="1:5">
@@ -21847,7 +21846,7 @@
         <v>232</v>
       </c>
       <c r="E29" s="73" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="30" ht="70" spans="1:5">
@@ -21855,10 +21854,10 @@
       <c r="B30" s="84"/>
       <c r="C30" s="85"/>
       <c r="D30" s="72" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E30" s="73" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -21866,10 +21865,10 @@
       <c r="B31" s="84"/>
       <c r="C31" s="85"/>
       <c r="D31" s="72" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E31" s="73" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="32" ht="28" spans="1:5">
@@ -21877,10 +21876,10 @@
       <c r="B32" s="84"/>
       <c r="C32" s="86"/>
       <c r="D32" s="72" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E32" s="73" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33" ht="42" spans="1:5">
@@ -21891,20 +21890,20 @@
       </c>
       <c r="D33" s="88"/>
       <c r="E33" s="73" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34" ht="42" spans="1:5">
       <c r="A34" s="83"/>
       <c r="B34" s="91" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C34" s="77" t="s">
         <v>242</v>
       </c>
       <c r="D34" s="92"/>
       <c r="E34" s="93" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" ht="42" spans="1:5">
@@ -21915,7 +21914,7 @@
       </c>
       <c r="D35" s="92"/>
       <c r="E35" s="93" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -21923,23 +21922,23 @@
         <v>14</v>
       </c>
       <c r="B36" s="96" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C36" s="97"/>
       <c r="D36" s="98"/>
       <c r="E36" s="93" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="94"/>
       <c r="B37" s="99" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C37" s="100"/>
       <c r="D37" s="101"/>
       <c r="E37" s="73" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -21947,12 +21946,12 @@
         <v>6</v>
       </c>
       <c r="B38" s="99" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C38" s="100"/>
       <c r="D38" s="101"/>
       <c r="E38" s="73" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -21960,16 +21959,16 @@
         <v>22</v>
       </c>
       <c r="B39" s="81" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C39" s="82" t="s">
         <v>231</v>
       </c>
       <c r="D39" s="72" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E39" s="73" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -21977,21 +21976,21 @@
       <c r="B40" s="84"/>
       <c r="C40" s="86"/>
       <c r="D40" s="72" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E40" s="73" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="83"/>
       <c r="B41" s="84"/>
       <c r="C41" s="87" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D41" s="88"/>
       <c r="E41" s="73" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -22002,7 +22001,7 @@
       </c>
       <c r="D42" s="88"/>
       <c r="E42" s="73" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -22010,36 +22009,36 @@
         <v>18</v>
       </c>
       <c r="B43" s="91" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C43" s="102" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D43" s="103"/>
       <c r="E43" s="93" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="44" ht="28" spans="1:5">
       <c r="A44" s="83"/>
       <c r="B44" s="95"/>
       <c r="C44" s="102" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D44" s="103"/>
       <c r="E44" s="93" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="94"/>
       <c r="B45" s="99" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C45" s="100"/>
       <c r="D45" s="101"/>
       <c r="E45" s="73" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -22047,13 +22046,13 @@
         <v>11</v>
       </c>
       <c r="B46" s="81" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C46" s="82" t="s">
         <v>231</v>
       </c>
       <c r="D46" s="72" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -22061,7 +22060,7 @@
       <c r="B47" s="84"/>
       <c r="C47" s="85"/>
       <c r="D47" s="72" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -22069,10 +22068,10 @@
       <c r="B48" s="90"/>
       <c r="C48" s="86"/>
       <c r="D48" s="72" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E48" s="73" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -22090,23 +22089,23 @@
         <v>19</v>
       </c>
       <c r="B50" s="99" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C50" s="100"/>
       <c r="D50" s="101"/>
       <c r="E50" s="73" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="94"/>
       <c r="B51" s="99" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C51" s="100"/>
       <c r="D51" s="101"/>
       <c r="E51" s="73" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -22114,12 +22113,12 @@
         <v>12</v>
       </c>
       <c r="B52" s="99" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C52" s="100"/>
       <c r="D52" s="101"/>
       <c r="E52" s="73" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -22127,7 +22126,7 @@
         <v>10</v>
       </c>
       <c r="B53" s="99" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C53" s="100"/>
       <c r="D53" s="101"/>
@@ -22235,7 +22234,7 @@
         <v>129</v>
       </c>
       <c r="B2" s="62" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" ht="28" spans="1:3">
@@ -22243,7 +22242,7 @@
         <v>131</v>
       </c>
       <c r="C3" s="50" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -22261,7 +22260,7 @@
         <v>136</v>
       </c>
       <c r="C6" s="63" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="7" ht="42" spans="1:3">
@@ -22269,7 +22268,7 @@
         <v>137</v>
       </c>
       <c r="C7" s="50" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="8" spans="1:1">
@@ -22287,7 +22286,7 @@
         <v>142</v>
       </c>
       <c r="B10" s="64" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -22310,7 +22309,7 @@
         <v>149</v>
       </c>
       <c r="B14" s="64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="15" spans="1:1">
@@ -22328,7 +22327,7 @@
         <v>153</v>
       </c>
       <c r="C17" s="63" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -22346,10 +22345,10 @@
         <v>156</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C20" s="50" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="21" ht="280" spans="1:3">
@@ -22357,10 +22356,10 @@
         <v>157</v>
       </c>
       <c r="B21" s="49" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C21" s="50" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -22373,7 +22372,7 @@
         <v>160</v>
       </c>
       <c r="B23" s="64" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="24" ht="70" spans="1:3">
@@ -22381,10 +22380,10 @@
         <v>161</v>
       </c>
       <c r="B24" s="64" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C24" s="63" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="25" spans="1:1">
@@ -22402,10 +22401,10 @@
         <v>167</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C27" s="63" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="28" ht="409" customHeight="1" spans="1:3">
@@ -22413,10 +22412,10 @@
         <v>169</v>
       </c>
       <c r="B28" s="49" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C28" s="63" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="29" spans="1:1">
@@ -22429,7 +22428,7 @@
         <v>172</v>
       </c>
       <c r="C30" s="63" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="31" spans="1:1">
@@ -22462,7 +22461,7 @@
         <v>182</v>
       </c>
       <c r="B36" s="64" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="37" ht="126" spans="1:3">
@@ -22470,7 +22469,7 @@
         <v>184</v>
       </c>
       <c r="C37" s="63" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="38" ht="28" spans="1:7">
@@ -22478,7 +22477,7 @@
         <v>186</v>
       </c>
       <c r="B38" s="65" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C38" s="66"/>
       <c r="D38" s="67"/>
@@ -22491,7 +22490,7 @@
         <v>189</v>
       </c>
       <c r="C39" s="63" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -22499,10 +22498,10 @@
         <v>191</v>
       </c>
       <c r="B40" s="64" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C40" s="63" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="41" ht="126" spans="1:3">
@@ -22510,7 +22509,7 @@
         <v>193</v>
       </c>
       <c r="C41" s="63" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -22523,7 +22522,7 @@
         <v>196</v>
       </c>
       <c r="B43" s="64" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="44" spans="1:1">
@@ -22536,7 +22535,7 @@
         <v>199</v>
       </c>
       <c r="B45" s="49" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="46" spans="1:1">
@@ -22554,7 +22553,7 @@
         <v>204</v>
       </c>
       <c r="C48" s="63" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -22567,7 +22566,7 @@
         <v>207</v>
       </c>
       <c r="C50" s="63" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -22580,10 +22579,10 @@
         <v>210</v>
       </c>
       <c r="B52" s="49" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C52" s="63" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
   </sheetData>
@@ -22613,7 +22612,7 @@
   <sheetData>
     <row r="1" s="28" customFormat="1" spans="1:8">
       <c r="A1" s="32" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="28" t="s">
@@ -22637,10 +22636,10 @@
     </row>
     <row r="2" s="29" customFormat="1" spans="1:4">
       <c r="A2" s="34" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C2" s="36" t="s">
         <v>129</v>
@@ -22650,7 +22649,7 @@
     <row r="3" s="29" customFormat="1" spans="1:4">
       <c r="A3" s="38"/>
       <c r="B3" s="35" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C3" s="36" t="s">
         <v>145</v>
@@ -22668,7 +22667,7 @@
     <row r="5" s="29" customFormat="1" spans="1:4">
       <c r="A5" s="38"/>
       <c r="B5" s="35" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C5" s="36" t="s">
         <v>149</v>
@@ -22678,7 +22677,7 @@
     <row r="6" s="29" customFormat="1" spans="1:4">
       <c r="A6" s="38"/>
       <c r="B6" s="35" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C6" s="39" t="s">
         <v>137</v>
@@ -22700,7 +22699,7 @@
     <row r="8" s="29" customFormat="1" spans="1:4">
       <c r="A8" s="38"/>
       <c r="B8" s="35" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C8" s="39" t="s">
         <v>135</v>
@@ -22712,7 +22711,7 @@
     <row r="9" s="29" customFormat="1" spans="1:4">
       <c r="A9" s="38"/>
       <c r="B9" s="35" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C9" s="36" t="s">
         <v>140</v>
@@ -22722,7 +22721,7 @@
     <row r="10" s="29" customFormat="1" spans="1:4">
       <c r="A10" s="38"/>
       <c r="B10" s="35" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C10" s="36" t="s">
         <v>152</v>
@@ -22732,7 +22731,7 @@
     <row r="11" s="29" customFormat="1" spans="1:4">
       <c r="A11" s="40"/>
       <c r="B11" s="35" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C11" s="36" t="s">
         <v>174</v>
@@ -22741,10 +22740,10 @@
     </row>
     <row r="12" s="30" customFormat="1" spans="1:4">
       <c r="A12" s="41" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B12" s="42" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C12" s="43" t="s">
         <v>193</v>
@@ -22762,17 +22761,17 @@
     <row r="14" s="30" customFormat="1" spans="1:4">
       <c r="A14" s="45"/>
       <c r="B14" s="42" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C14" s="43" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D14" s="44"/>
     </row>
     <row r="15" s="30" customFormat="1" spans="1:4">
       <c r="A15" s="45"/>
       <c r="B15" s="42" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C15" s="43" t="s">
         <v>131</v>
@@ -22790,7 +22789,7 @@
     <row r="17" s="30" customFormat="1" spans="1:4">
       <c r="A17" s="45"/>
       <c r="B17" s="42" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C17" s="43" t="s">
         <v>144</v>
@@ -22800,7 +22799,7 @@
     <row r="18" s="30" customFormat="1" spans="1:4">
       <c r="A18" s="45"/>
       <c r="B18" s="42" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C18" s="43" t="s">
         <v>156</v>
@@ -22810,7 +22809,7 @@
     <row r="19" s="30" customFormat="1" spans="1:4">
       <c r="A19" s="45"/>
       <c r="B19" s="42" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C19" s="43" t="s">
         <v>189</v>
@@ -22820,7 +22819,7 @@
     <row r="20" s="30" customFormat="1" spans="1:4">
       <c r="A20" s="46"/>
       <c r="B20" s="42" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C20" s="43" t="s">
         <v>191</v>

--- a/c/9班资料.xlsx
+++ b/c/9班资料.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10030" firstSheet="4" activeTab="3"/>
+    <workbookView windowWidth="20750" windowHeight="10480" firstSheet="4" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="七下拖课" sheetId="1" r:id="rId1"/>
@@ -512,7 +512,7 @@
     <t>江允儿</t>
   </si>
   <si>
-    <t>江允入</t>
+    <t>江允入、小宝</t>
   </si>
   <si>
     <t>徐嘉明</t>
@@ -590,7 +590,7 @@
     <t>方欣妍</t>
   </si>
   <si>
-    <t>巧克力奶奶</t>
+    <t>巧克力、奶奶</t>
   </si>
   <si>
     <t>季仁槿</t>
@@ -670,7 +670,7 @@
     <t>洪鑫洋</t>
   </si>
   <si>
-    <t>巨乳、信仰、机长、现在（未来）之星</t>
+    <t>巨乳、信仰、机长、现在（未来）之星、三江口（源）</t>
   </si>
   <si>
     <t>游武毅</t>
@@ -2598,10 +2598,15 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+      <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2612,12 +2617,7 @@
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="63">

--- a/c/9班资料.xlsx
+++ b/c/9班资料.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10030" tabRatio="724" activeTab="2"/>
+    <workbookView windowWidth="20750" windowHeight="10030" tabRatio="724" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="学生、老师" sheetId="5" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="571">
   <si>
     <t>姓名</t>
   </si>
@@ -360,7 +360,10 @@
     <t>陆梓豪</t>
   </si>
   <si>
-    <t>中午拿2矿泉水</t>
+    <t>和叶弘毅分享菜</t>
+  </si>
+  <si>
+    <t>中午拿2矿泉水、番茄沙司</t>
   </si>
   <si>
     <t>钱尚恩</t>
@@ -504,7 +507,7 @@
     <t>物1</t>
   </si>
   <si>
-    <t>读“m”“l”“等于”、写“解”、M来了、给课代表买奶茶</t>
+    <t>读“m”“l”“等于”、写“解”、M来了、给课代表买奶茶、自印卷子、提前进班、写其他课作业、物理课本拿出来、上句话是什么</t>
   </si>
   <si>
     <t>体1</t>
@@ -574,6 +577,9 @@
   </si>
   <si>
     <t>么么脆鸡排、密封条、虫卵</t>
+  </si>
+  <si>
+    <t>2个碗装汤</t>
   </si>
   <si>
     <t>热门</t>
@@ -688,6 +694,12 @@
   </si>
   <si>
     <t>（洪鑫洋在第三组前面，江允儿在二组中部）进班不往讲台走，往第二组过道绕并看江允儿一眼</t>
+  </si>
+  <si>
+    <t>八上1.11</t>
+  </si>
+  <si>
+    <t>物理难题，洪鑫洋：“题目出得不好”</t>
   </si>
   <si>
     <t>孔祥懿睡觉</t>
@@ -3011,13 +3023,13 @@
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
-      <scheme val="major"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+      <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4333,9 +4345,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -4350,6 +4359,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5184,66 +5196,69 @@
       <c r="A45" s="68" t="s">
         <v>97</v>
       </c>
+      <c r="C45" s="213" t="s">
+        <v>98</v>
+      </c>
       <c r="D45" s="213" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="68" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="68" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D47" s="213" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="68" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C48" s="213" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="68" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="50" ht="78" spans="1:7">
       <c r="A50" s="68" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C50" s="213" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="68" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:7">
       <c r="A52" s="68" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B52" s="213" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C52" s="213" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" ht="26" spans="1:7">
       <c r="A53" s="67" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B53" s="213" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D53" s="215"/>
       <c r="E53" s="215"/>
@@ -5252,13 +5267,13 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="67" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B54" s="213" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C54" s="213" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D54" s="215"/>
       <c r="E54" s="215"/>
@@ -5267,46 +5282,46 @@
     </row>
     <row r="55" ht="52" spans="1:7">
       <c r="A55" s="67" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B55" s="215"/>
       <c r="C55" s="215"/>
       <c r="D55" s="213" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="56" ht="65" spans="1:7">
       <c r="A56" s="67" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B56" s="74" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C56" s="74"/>
       <c r="D56" s="213" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="57" ht="117" spans="1:7">
       <c r="A57" s="67" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B57" s="74" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C57" s="74" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D57" s="213" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="67" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B58" s="213" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C58" s="215"/>
       <c r="D58" s="215"/>
@@ -5316,11 +5331,11 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="67" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B59" s="215"/>
       <c r="C59" s="213" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D59" s="215"/>
       <c r="E59" s="215"/>
@@ -5329,20 +5344,20 @@
     </row>
     <row r="60" ht="52" spans="1:7">
       <c r="A60" s="67" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B60" s="215"/>
       <c r="C60" s="215"/>
       <c r="D60" s="213" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="67" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B61" s="74" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C61" s="74"/>
       <c r="D61" s="215"/>
@@ -5352,23 +5367,23 @@
     </row>
     <row r="62" ht="39" spans="1:7">
       <c r="A62" s="67" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B62" s="215"/>
       <c r="C62" s="215"/>
       <c r="D62" s="213" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="63" ht="26" spans="1:7">
       <c r="A63" s="67" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B63" s="74" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C63" s="74" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D63" s="215"/>
       <c r="E63" s="215"/>
@@ -5377,20 +5392,20 @@
     </row>
     <row r="64" ht="26" spans="1:7">
       <c r="A64" s="67" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B64" s="215"/>
       <c r="C64" s="215"/>
       <c r="D64" s="213" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" ht="26" spans="1:7">
       <c r="A65" s="67" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B65" s="217" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C65" s="215"/>
       <c r="D65" s="215"/>
@@ -5400,11 +5415,11 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="67" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B66" s="215"/>
       <c r="C66" s="213" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D66" s="215"/>
       <c r="E66" s="215"/>
@@ -5413,36 +5428,36 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="67" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B67" s="215"/>
       <c r="C67" s="215"/>
     </row>
-    <row r="68" ht="26" spans="1:7">
+    <row r="68" ht="65" spans="1:7">
       <c r="A68" s="67" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B68" s="215"/>
       <c r="C68" s="215"/>
       <c r="D68" s="213" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="67" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B69" s="74" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C69" s="74"/>
     </row>
     <row r="70" ht="26" spans="1:7">
       <c r="A70" s="67" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B70" s="74" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C70" s="74"/>
       <c r="D70" s="215"/>
@@ -5452,20 +5467,20 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="67" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B71" s="215"/>
       <c r="C71" s="215"/>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="67" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B72" s="213" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C72" s="213" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D72" s="215"/>
       <c r="E72" s="215"/>
@@ -5474,11 +5489,11 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="67" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B73" s="215"/>
       <c r="C73" s="213" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D73" s="215"/>
       <c r="E73" s="215"/>
@@ -5487,12 +5502,12 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="67" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="67" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D75" s="215"/>
       <c r="E75" s="215"/>
@@ -5501,27 +5516,27 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="67" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B76" s="215"/>
       <c r="C76" s="215"/>
       <c r="D76" s="213" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="67" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B77" s="74"/>
       <c r="C77" s="74"/>
     </row>
     <row r="78" ht="26" spans="1:7">
       <c r="A78" s="218" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B78" s="213" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -5574,19 +5589,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="63" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B1" s="64" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="65" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="D1" s="66" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E1" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5600,7 +5615,7 @@
         <v>20111216</v>
       </c>
       <c r="D2" s="62" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5614,7 +5629,7 @@
         <v>20111227</v>
       </c>
       <c r="D3" s="62" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5628,7 +5643,7 @@
         <v>20120518</v>
       </c>
       <c r="D4" s="62" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:5">
@@ -5654,7 +5669,7 @@
         <v>20120504</v>
       </c>
       <c r="D6" s="62" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -5668,7 +5683,7 @@
         <v>20120809</v>
       </c>
       <c r="D7" s="62" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -5682,7 +5697,7 @@
         <v>20120227</v>
       </c>
       <c r="D8" s="62" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5696,7 +5711,7 @@
         <v>20120127</v>
       </c>
       <c r="D9" s="62" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -5710,7 +5725,7 @@
         <v>20111202</v>
       </c>
       <c r="D10" s="62" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:5">
@@ -5736,7 +5751,7 @@
         <v>20111024</v>
       </c>
       <c r="D12" s="62" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -5750,7 +5765,7 @@
         <v>20110908</v>
       </c>
       <c r="D13" s="62" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -5764,7 +5779,7 @@
         <v>20120228</v>
       </c>
       <c r="D14" s="62" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:5">
@@ -5790,7 +5805,7 @@
         <v>20111201</v>
       </c>
       <c r="D16" s="62" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -5804,7 +5819,7 @@
         <v>20120722</v>
       </c>
       <c r="D17" s="62" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:4">
@@ -5842,7 +5857,7 @@
         <v>20120530</v>
       </c>
       <c r="D20" s="62" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -5856,7 +5871,7 @@
         <v>20120827</v>
       </c>
       <c r="D21" s="62" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:4">
@@ -5882,7 +5897,7 @@
         <v>20120518</v>
       </c>
       <c r="D23" s="62" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -5896,7 +5911,7 @@
         <v>20120413</v>
       </c>
       <c r="D24" s="62" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -5910,7 +5925,7 @@
         <v>20120629</v>
       </c>
       <c r="D25" s="62" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -5924,7 +5939,7 @@
         <v>20111105</v>
       </c>
       <c r="D26" s="62" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -5938,7 +5953,7 @@
         <v>20120112</v>
       </c>
       <c r="D27" s="62" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -5952,7 +5967,7 @@
         <v>20111119</v>
       </c>
       <c r="D28" s="62" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:4">
@@ -5978,7 +5993,7 @@
         <v>20120331</v>
       </c>
       <c r="D30" s="62" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -5992,7 +6007,7 @@
         <v>20111109</v>
       </c>
       <c r="D31" s="62" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -6006,7 +6021,7 @@
         <v>20120824</v>
       </c>
       <c r="D32" s="62" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:5">
@@ -6032,7 +6047,7 @@
         <v>20120624</v>
       </c>
       <c r="D34" s="62" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:5">
@@ -6058,7 +6073,7 @@
         <v>20120603</v>
       </c>
       <c r="D36" s="62" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -6072,7 +6087,7 @@
         <v>20120326</v>
       </c>
       <c r="D37" s="62" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -6086,10 +6101,10 @@
         <v>20111106</v>
       </c>
       <c r="D38" s="73" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E38" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -6103,7 +6118,7 @@
         <v>20120811</v>
       </c>
       <c r="D39" s="74" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -6117,7 +6132,7 @@
         <v>20111217</v>
       </c>
       <c r="D40" s="74" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -6131,10 +6146,10 @@
         <v>20111013</v>
       </c>
       <c r="D41" s="62" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="E41" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:5">
@@ -6160,7 +6175,7 @@
         <v>20120207</v>
       </c>
       <c r="D43" s="62" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:5">
@@ -6186,7 +6201,7 @@
         <v>20110929</v>
       </c>
       <c r="D45" s="62" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:5">
@@ -6194,7 +6209,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="68" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C46" s="70">
         <v>20111205</v>
@@ -6206,16 +6221,16 @@
         <v>46</v>
       </c>
       <c r="B47" s="68" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C47" s="70">
         <v>20120108</v>
       </c>
       <c r="D47" s="62" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E47" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -6223,13 +6238,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="68" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C48" s="70">
         <v>20120311</v>
       </c>
       <c r="D48" s="62" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:4">
@@ -6237,7 +6252,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="68" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C49" s="70">
         <v>20110902</v>
@@ -6249,13 +6264,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="68" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C50" s="70">
         <v>20120723</v>
       </c>
       <c r="D50" s="62" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:4">
@@ -6263,7 +6278,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="68" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C51" s="70">
         <v>20120101</v>
@@ -6275,13 +6290,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="68" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C52" s="70">
         <v>20111220</v>
       </c>
       <c r="D52" s="62" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
   </sheetData>
@@ -6314,34 +6329,34 @@
   <sheetData>
     <row r="1" s="23" customFormat="1" spans="1:5">
       <c r="A1" s="30" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B1" s="31" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C1" s="32" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="D1" s="33"/>
       <c r="E1" s="34" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="2" s="24" customFormat="1" ht="409" customHeight="1" spans="1:5">
       <c r="A2" s="35" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E2" s="29" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="3" s="24" customFormat="1" ht="56" spans="1:5">
@@ -6349,10 +6364,10 @@
       <c r="B3" s="39"/>
       <c r="C3" s="40"/>
       <c r="D3" s="28" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" s="24" customFormat="1" spans="1:5">
@@ -6360,10 +6375,10 @@
       <c r="B4" s="39"/>
       <c r="C4" s="40"/>
       <c r="D4" s="28" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="5" s="24" customFormat="1" ht="56" spans="1:5">
@@ -6371,10 +6386,10 @@
       <c r="B5" s="39"/>
       <c r="C5" s="40"/>
       <c r="D5" s="28" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="6" s="24" customFormat="1" ht="238" spans="1:5">
@@ -6382,23 +6397,23 @@
       <c r="B6" s="39"/>
       <c r="C6" s="40"/>
       <c r="D6" s="28" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="7" s="24" customFormat="1" ht="238" spans="1:5">
       <c r="A7" s="38"/>
       <c r="B7" s="39"/>
       <c r="C7" s="37" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="8" s="24" customFormat="1" ht="56" spans="1:5">
@@ -6406,10 +6421,10 @@
       <c r="B8" s="39"/>
       <c r="C8" s="40"/>
       <c r="D8" s="28" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9" s="24" customFormat="1" ht="84" spans="1:5">
@@ -6417,10 +6432,10 @@
       <c r="B9" s="39"/>
       <c r="C9" s="40"/>
       <c r="D9" s="28" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="10" s="24" customFormat="1" ht="28" spans="1:5">
@@ -6428,10 +6443,10 @@
       <c r="B10" s="39"/>
       <c r="C10" s="40"/>
       <c r="D10" s="28" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="11" s="24" customFormat="1" spans="1:5">
@@ -6439,10 +6454,10 @@
       <c r="B11" s="39"/>
       <c r="C11" s="41"/>
       <c r="D11" s="28" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="12" s="24" customFormat="1" ht="154" spans="1:5">
@@ -6450,50 +6465,50 @@
       <c r="B12" s="39"/>
       <c r="C12" s="27"/>
       <c r="D12" s="28" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E12" s="29" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="13" s="24" customFormat="1" ht="56" spans="1:5">
       <c r="A13" s="38"/>
       <c r="B13" s="39"/>
       <c r="C13" s="42" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="D13" s="33"/>
       <c r="E13" s="29" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="14" s="24" customFormat="1" ht="84" spans="1:5">
       <c r="A14" s="38"/>
       <c r="B14" s="39"/>
       <c r="C14" s="42" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="D14" s="33"/>
       <c r="E14" s="29" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="15" s="24" customFormat="1" ht="28" spans="1:5">
       <c r="A15" s="38"/>
       <c r="B15" s="39"/>
       <c r="C15" s="42" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D15" s="33"/>
       <c r="E15" s="29" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="16" s="24" customFormat="1" spans="1:5">
       <c r="A16" s="38"/>
       <c r="B16" s="39"/>
       <c r="C16" s="42" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="29"/>
@@ -6502,24 +6517,24 @@
       <c r="A17" s="38"/>
       <c r="B17" s="39"/>
       <c r="C17" s="42" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="29" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="18" s="24" customFormat="1" spans="1:5">
       <c r="A18" s="38"/>
       <c r="B18" s="39"/>
       <c r="C18" s="37" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="19" s="24" customFormat="1" spans="1:5">
@@ -6527,17 +6542,17 @@
       <c r="B19" s="39"/>
       <c r="C19" s="41"/>
       <c r="D19" s="28" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="E19" s="29" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="20" s="24" customFormat="1" spans="1:5">
       <c r="A20" s="38"/>
       <c r="B20" s="39"/>
       <c r="C20" s="42" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="D20" s="33"/>
       <c r="E20" s="29"/>
@@ -6546,61 +6561,61 @@
       <c r="A21" s="38"/>
       <c r="B21" s="39"/>
       <c r="C21" s="42" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="D21" s="33"/>
       <c r="E21" s="29" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="22" s="24" customFormat="1" ht="28" spans="1:5">
       <c r="A22" s="38"/>
       <c r="B22" s="39"/>
       <c r="C22" s="42" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="D22" s="43"/>
       <c r="E22" s="29" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="23" s="24" customFormat="1" spans="1:5">
       <c r="A23" s="38"/>
       <c r="B23" s="39"/>
       <c r="C23" s="27" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D23" s="27"/>
       <c r="E23" s="29" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="24" s="24" customFormat="1" spans="1:5">
       <c r="A24" s="38"/>
       <c r="B24" s="39"/>
       <c r="C24" s="27" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="29" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="25" s="24" customFormat="1" ht="28" spans="1:5">
       <c r="A25" s="35" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C25" s="40" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D25" s="44" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="E25" s="29" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="26" s="24" customFormat="1" spans="1:5">
@@ -6608,10 +6623,10 @@
       <c r="B26" s="39"/>
       <c r="C26" s="40"/>
       <c r="D26" s="28" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="E26" s="29" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="27" s="24" customFormat="1" ht="28" spans="1:5">
@@ -6619,10 +6634,10 @@
       <c r="B27" s="39"/>
       <c r="C27" s="40"/>
       <c r="D27" s="28" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="E27" s="29" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="28" s="24" customFormat="1" ht="42" spans="1:5">
@@ -6630,27 +6645,27 @@
       <c r="B28" s="39"/>
       <c r="C28" s="40"/>
       <c r="D28" s="28" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="E28" s="29" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="29" s="24" customFormat="1" ht="42" spans="1:5">
       <c r="A29" s="35" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C29" s="37" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E29" s="29" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="30" s="24" customFormat="1" ht="70" spans="1:5">
@@ -6658,10 +6673,10 @@
       <c r="B30" s="39"/>
       <c r="C30" s="40"/>
       <c r="D30" s="28" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="E30" s="29" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="31" s="24" customFormat="1" spans="1:5">
@@ -6669,10 +6684,10 @@
       <c r="B31" s="39"/>
       <c r="C31" s="40"/>
       <c r="D31" s="28" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="E31" s="29" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="32" s="24" customFormat="1" ht="28" spans="1:5">
@@ -6680,99 +6695,99 @@
       <c r="B32" s="39"/>
       <c r="C32" s="41"/>
       <c r="D32" s="28" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="E32" s="29" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="33" s="24" customFormat="1" ht="42" spans="1:5">
       <c r="A33" s="38"/>
       <c r="B33" s="45"/>
       <c r="C33" s="42" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D33" s="43"/>
       <c r="E33" s="29" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="34" s="24" customFormat="1" ht="42" spans="1:5">
       <c r="A34" s="38"/>
       <c r="B34" s="46" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="C34" s="32" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D34" s="47"/>
       <c r="E34" s="48" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="35" s="24" customFormat="1" ht="42" spans="1:5">
       <c r="A35" s="49"/>
       <c r="B35" s="50"/>
       <c r="C35" s="32" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D35" s="47"/>
       <c r="E35" s="48" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="36" s="24" customFormat="1" spans="1:5">
       <c r="A36" s="35" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B36" s="51" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C36" s="52"/>
       <c r="D36" s="53"/>
       <c r="E36" s="48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="37" s="24" customFormat="1" spans="1:5">
       <c r="A37" s="49"/>
       <c r="B37" s="54" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C37" s="55"/>
       <c r="D37" s="56"/>
       <c r="E37" s="29" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="38" s="24" customFormat="1" spans="1:5">
       <c r="A38" s="25" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B38" s="54" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C38" s="55"/>
       <c r="D38" s="56"/>
       <c r="E38" s="29" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="39" s="24" customFormat="1" spans="1:5">
       <c r="A39" s="35" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C39" s="37" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D39" s="28" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="E39" s="29" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="40" s="24" customFormat="1" spans="1:5">
@@ -6780,83 +6795,83 @@
       <c r="B40" s="39"/>
       <c r="C40" s="41"/>
       <c r="D40" s="28" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="E40" s="29" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="41" s="24" customFormat="1" spans="1:5">
       <c r="A41" s="38"/>
       <c r="B41" s="39"/>
       <c r="C41" s="42" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="D41" s="43"/>
       <c r="E41" s="29" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
     <row r="42" s="24" customFormat="1" spans="1:5">
       <c r="A42" s="49"/>
       <c r="B42" s="45"/>
       <c r="C42" s="42" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D42" s="43"/>
       <c r="E42" s="29" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
     <row r="43" s="24" customFormat="1" spans="1:5">
       <c r="A43" s="35" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B43" s="46" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C43" s="57" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D43" s="58"/>
       <c r="E43" s="48" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
     </row>
     <row r="44" s="24" customFormat="1" ht="28" spans="1:5">
       <c r="A44" s="38"/>
       <c r="B44" s="50"/>
       <c r="C44" s="57" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="D44" s="58"/>
       <c r="E44" s="48" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
     </row>
     <row r="45" s="24" customFormat="1" spans="1:5">
       <c r="A45" s="49"/>
       <c r="B45" s="54" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C45" s="55"/>
       <c r="D45" s="56"/>
       <c r="E45" s="29" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="46" s="24" customFormat="1" spans="1:5">
       <c r="A46" s="35" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="C46" s="37" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D46" s="28" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="E46" s="29"/>
     </row>
@@ -6865,7 +6880,7 @@
       <c r="B47" s="39"/>
       <c r="C47" s="40"/>
       <c r="D47" s="28" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="E47" s="29"/>
     </row>
@@ -6874,55 +6889,55 @@
       <c r="B48" s="45"/>
       <c r="C48" s="41"/>
       <c r="D48" s="28" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="E48" s="29" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
     </row>
     <row r="49" s="24" customFormat="1" spans="1:5">
       <c r="A49" s="25" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B49" s="54" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C49" s="55"/>
       <c r="D49" s="56"/>
       <c r="E49" s="29" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
     </row>
     <row r="50" s="24" customFormat="1" spans="1:5">
       <c r="A50" s="35" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B50" s="54" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C50" s="55"/>
       <c r="D50" s="56"/>
       <c r="E50" s="29" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="51" s="24" customFormat="1" spans="1:5">
       <c r="A51" s="49"/>
       <c r="B51" s="54" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C51" s="55"/>
       <c r="D51" s="56"/>
       <c r="E51" s="29" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="52" s="24" customFormat="1" spans="1:5">
       <c r="A52" s="25" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B52" s="54" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C52" s="55"/>
       <c r="D52" s="56"/>
@@ -6930,10 +6945,10 @@
     </row>
     <row r="53" s="24" customFormat="1" spans="1:5">
       <c r="A53" s="35" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B53" s="54" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C53" s="55"/>
       <c r="D53" s="56"/>
@@ -6945,18 +6960,18 @@
       <c r="C54" s="55"/>
       <c r="D54" s="56"/>
       <c r="E54" s="29" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
     </row>
     <row r="55" s="24" customFormat="1" spans="1:5">
       <c r="A55" s="25" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B55" s="26"/>
       <c r="C55" s="27"/>
       <c r="D55" s="28"/>
       <c r="E55" s="29" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
   </sheetData>
@@ -7064,7 +7079,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
@@ -7078,7 +7093,7 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="5" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="7"/>
@@ -7102,7 +7117,7 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="7"/>
@@ -7115,7 +7130,7 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="18" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="7"/>
@@ -7128,7 +7143,7 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="5" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="7"/>
@@ -7162,7 +7177,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="6"/>
@@ -7208,7 +7223,7 @@
         <v>31</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="6"/>
@@ -7244,7 +7259,7 @@
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="18" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="7"/>
@@ -7278,10 +7293,10 @@
         <v>42</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="7"/>
@@ -7293,10 +7308,10 @@
         <v>45</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="7"/>
@@ -7319,7 +7334,7 @@
         <v>50</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="6"/>
@@ -7332,10 +7347,10 @@
         <v>52</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="7"/>
@@ -7369,10 +7384,10 @@
         <v>58</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="7"/>
@@ -7384,10 +7399,10 @@
         <v>61</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="7"/>
@@ -7411,7 +7426,7 @@
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="18" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="7"/>
@@ -7478,7 +7493,7 @@
         <v>74</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="6"/>
@@ -7492,7 +7507,7 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="18" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="7"/>
@@ -7504,7 +7519,7 @@
         <v>79</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C38" s="21"/>
       <c r="D38" s="22"/>
@@ -7518,7 +7533,7 @@
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="18" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="7"/>
@@ -7530,10 +7545,10 @@
         <v>84</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="7"/>
@@ -7546,7 +7561,7 @@
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="18" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="7"/>
@@ -7569,7 +7584,7 @@
         <v>93</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="6"/>
@@ -7593,7 +7608,7 @@
         <v>97</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="6"/>
@@ -7603,7 +7618,7 @@
     </row>
     <row r="46" s="2" customFormat="1" spans="1:7">
       <c r="A46" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="5"/>
@@ -7614,7 +7629,7 @@
     </row>
     <row r="47" s="2" customFormat="1" spans="1:7">
       <c r="A47" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="5"/>
@@ -7625,11 +7640,11 @@
     </row>
     <row r="48" s="2" customFormat="1" spans="1:7">
       <c r="A48" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="18" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="7"/>
@@ -7638,7 +7653,7 @@
     </row>
     <row r="49" s="2" customFormat="1" spans="1:7">
       <c r="A49" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="5"/>
@@ -7649,11 +7664,11 @@
     </row>
     <row r="50" s="2" customFormat="1" ht="322" spans="1:7">
       <c r="A50" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="18" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="7"/>
@@ -7662,7 +7677,7 @@
     </row>
     <row r="51" s="2" customFormat="1" spans="1:7">
       <c r="A51" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="5"/>
@@ -7673,13 +7688,13 @@
     </row>
     <row r="52" s="2" customFormat="1" ht="224" spans="1:7">
       <c r="A52" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="7"/>
@@ -7734,12 +7749,12 @@
     </row>
     <row r="2" s="206" customFormat="1" ht="39" spans="1:7">
       <c r="A2" s="210" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B2" s="74"/>
       <c r="C2" s="74"/>
       <c r="D2" s="74" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E2" s="74"/>
       <c r="F2" s="74"/>
@@ -7747,54 +7762,57 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="211" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C3" s="62" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="211" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B4" s="62" t="s">
-        <v>169</v>
+        <v>170</v>
+      </c>
+      <c r="D4" s="62" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="211" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C5" s="62" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D5" s="62" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="211" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B6" s="62" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D6" s="62" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="211" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B7" s="62" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="211"/>
       <c r="D8" s="62" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -7803,7 +7821,7 @@
     <row r="10" spans="1:7">
       <c r="A10" s="211"/>
       <c r="B10" s="62" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -7812,7 +7830,7 @@
     <row r="12" spans="1:7">
       <c r="A12" s="211"/>
       <c r="B12" s="62" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -7966,77 +7984,77 @@
   <sheetData>
     <row r="1" s="198" customFormat="1" ht="15" spans="1:3">
       <c r="A1" s="200" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B1" s="200" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C1" s="200" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="201" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B2" s="201" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C2" s="201" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="201" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B3" s="201" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C3" s="201" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="201" t="s">
+        <v>192</v>
+      </c>
+      <c r="B4" s="201" t="s">
         <v>190</v>
       </c>
-      <c r="B4" s="201" t="s">
-        <v>188</v>
-      </c>
       <c r="C4" s="201" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" ht="56" spans="1:3">
       <c r="A5" s="202" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B5" s="201" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C5" s="201" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:3">
       <c r="A6" s="203"/>
       <c r="B6" s="201" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C6" s="201" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="201" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B7" s="201" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C7" s="201" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8044,72 +8062,76 @@
         <v>88</v>
       </c>
       <c r="B8" s="201" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C8" s="201" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="204"/>
       <c r="B9" s="201" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C9" s="201" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="204"/>
       <c r="B10" s="201" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C10" s="201" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="204"/>
       <c r="B11" s="201" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C11" s="201" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="203"/>
-      <c r="B12" s="201"/>
-      <c r="C12" s="201"/>
+      <c r="B12" s="201" t="s">
+        <v>209</v>
+      </c>
+      <c r="C12" s="201" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="201" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B13" s="201" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C13" s="201" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="201" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B14" s="201" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C14" s="201" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="201" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B15" s="201" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C15" s="205">
         <v>0.440972222222222</v>
@@ -8120,70 +8142,70 @@
         <v>61</v>
       </c>
       <c r="B16" s="201" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C16" s="201" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="203"/>
       <c r="B17" s="201" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C17" s="201" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="202" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B18" s="201" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C18" s="201" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="203"/>
       <c r="B19" s="201" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C19" s="201" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" ht="28" spans="1:3">
       <c r="A20" s="201" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B20" s="201" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C20" s="201" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="202" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B21" s="201" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C21" s="201" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="203"/>
       <c r="B22" s="201" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C22" s="201" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="23" ht="28" spans="1:3">
@@ -8191,21 +8213,21 @@
         <v>45</v>
       </c>
       <c r="B23" s="201" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C23" s="201" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24" ht="98" spans="1:3">
       <c r="A24" s="199" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B24" s="199" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C24" s="199" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -8213,10 +8235,10 @@
         <v>36</v>
       </c>
       <c r="B25" s="199" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C25" s="199" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -8240,45 +8262,45 @@
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="9.54545454545454" style="183"/>
-    <col min="2" max="2" width="3.54545454545455" style="183" customWidth="1"/>
-    <col min="3" max="3" width="4.27272727272727" style="183" customWidth="1"/>
-    <col min="4" max="4" width="3.45454545454545" style="183" customWidth="1"/>
+    <col min="1" max="1" width="9.54545454545454" style="182"/>
+    <col min="2" max="2" width="3.54545454545455" style="182" customWidth="1"/>
+    <col min="3" max="3" width="4.27272727272727" style="182" customWidth="1"/>
+    <col min="4" max="4" width="3.45454545454545" style="182" customWidth="1"/>
     <col min="5" max="5" width="8.72727272727273" style="187"/>
-    <col min="6" max="6" width="9.52727272727273" style="183" customWidth="1"/>
-    <col min="7" max="7" width="17.1909090909091" style="183" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="183"/>
+    <col min="6" max="6" width="9.52727272727273" style="182" customWidth="1"/>
+    <col min="7" max="7" width="17.1909090909091" style="182" customWidth="1"/>
+    <col min="8" max="16384" width="8.72727272727273" style="182"/>
   </cols>
   <sheetData>
     <row r="1" s="185" customFormat="1" ht="15" spans="1:7">
       <c r="A1" s="188" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B1" s="189"/>
       <c r="C1" s="189"/>
       <c r="D1" s="190"/>
       <c r="E1" s="191"/>
       <c r="F1" s="185" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" s="186" customFormat="1" spans="1:7">
       <c r="A2" s="192" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B2" s="193"/>
       <c r="C2" s="186" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D2" s="186" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E2" s="137"/>
       <c r="F2" s="186" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G2" s="186" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -8293,10 +8315,10 @@
       </c>
       <c r="D3" s="115"/>
       <c r="F3" s="115" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="G3" s="115" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -8471,7 +8493,7 @@
   <sheetData>
     <row r="1" spans="1:39">
       <c r="A1" s="172" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B1" s="173">
         <v>45992</v>
@@ -8509,7 +8531,7 @@
       <c r="AE1" s="174"/>
       <c r="AF1" s="174"/>
       <c r="AG1" s="139" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AH1" s="142"/>
       <c r="AI1" s="142"/>
@@ -8614,29 +8636,29 @@
         <v>20</v>
       </c>
       <c r="AG2" s="176" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="AH2" s="176" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="AI2" s="176" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="AJ2" s="176" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="AK2" s="177" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="AL2" s="177" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="AM2" s="177" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:39">
-      <c r="A3" s="178">
+      <c r="A3" s="116">
         <v>1</v>
       </c>
       <c r="B3" s="116"/>
@@ -8662,7 +8684,9 @@
       <c r="V3" s="116"/>
       <c r="W3" s="116"/>
       <c r="X3" s="116"/>
-      <c r="Y3" s="116"/>
+      <c r="Y3" s="116">
+        <v>1</v>
+      </c>
       <c r="Z3" s="116"/>
       <c r="AA3" s="116"/>
       <c r="AB3" s="116"/>
@@ -8670,37 +8694,37 @@
       <c r="AD3" s="116"/>
       <c r="AE3" s="116"/>
       <c r="AF3" s="116"/>
-      <c r="AG3" s="179">
+      <c r="AG3" s="178">
         <f>SUM(B3:AF3)</f>
-        <v>0</v>
-      </c>
-      <c r="AH3" s="180" cm="1">
+        <v>1</v>
+      </c>
+      <c r="AH3" s="179" cm="1">
         <f t="array" ref="AH3">SUMPRODUCT(--(B3:AF3=INT(B3:AF3)),--(B3:AF3&gt;0))</f>
-        <v>0</v>
-      </c>
-      <c r="AI3" s="180" cm="1">
+        <v>1</v>
+      </c>
+      <c r="AI3" s="179" cm="1">
         <f t="array" ref="AI3">MAX(FREQUENCY(IF((B3:AF3=INT(B3:AF3))*(B3:AF3&gt;0),COLUMN(B3:AF3)),IF((B3:AF3&lt;&gt;INT(B3:AF3))+(B3:AF3&lt;=0),COLUMN(B3:AF3))))</f>
-        <v>0</v>
-      </c>
-      <c r="AJ3" s="181" cm="1">
+        <v>1</v>
+      </c>
+      <c r="AJ3" s="180" cm="1">
         <f t="array" ref="AJ3">SUMPRODUCT(--(B3:AF3=INT(B3:AF3)),--(B3:AF3&gt;0))/30*100%</f>
-        <v>0</v>
-      </c>
-      <c r="AK3" s="182">
+        <v>0.0333333333333333</v>
+      </c>
+      <c r="AK3" s="181">
         <f>RANK(AG3,AG$3:AG$53,0)</f>
-        <v>35</v>
-      </c>
-      <c r="AL3" s="182">
+        <v>34</v>
+      </c>
+      <c r="AL3" s="181">
         <f>RANK(AH3,AH$3:AH$53,0)</f>
-        <v>35</v>
-      </c>
-      <c r="AM3" s="182">
+        <v>34</v>
+      </c>
+      <c r="AM3" s="181">
         <f>RANK(AI3,AI$3:AI$53,0)</f>
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:39">
-      <c r="A4" s="183">
+      <c r="A4" s="182">
         <v>2</v>
       </c>
       <c r="B4" s="116">
@@ -8744,7 +8768,9 @@
       <c r="V4" s="116"/>
       <c r="W4" s="116"/>
       <c r="X4" s="116"/>
-      <c r="Y4" s="116"/>
+      <c r="Y4" s="116">
+        <v>1</v>
+      </c>
       <c r="Z4" s="116"/>
       <c r="AA4" s="116"/>
       <c r="AB4" s="116"/>
@@ -8752,37 +8778,37 @@
       <c r="AD4" s="116"/>
       <c r="AE4" s="116"/>
       <c r="AF4" s="116"/>
-      <c r="AG4" s="179">
+      <c r="AG4" s="178">
         <f t="shared" ref="AG4:AG35" si="0">SUM(B4:AF4)</f>
+        <v>11</v>
+      </c>
+      <c r="AH4" s="179" cm="1">
+        <f t="array" ref="AH4">SUMPRODUCT(--(B4:AF4=INT(B4:AF4)),--(B4:AF4&gt;0))</f>
         <v>10</v>
       </c>
-      <c r="AH4" s="180" cm="1">
-        <f t="array" ref="AH4">SUMPRODUCT(--(B4:AF4=INT(B4:AF4)),--(B4:AF4&gt;0))</f>
-        <v>9</v>
-      </c>
-      <c r="AI4" s="180" cm="1">
+      <c r="AI4" s="179" cm="1">
         <f t="array" ref="AI4">MAX(FREQUENCY(IF((B4:AF4=INT(B4:AF4))*(B4:AF4&gt;0),COLUMN(B4:AF4)),IF((B4:AF4&lt;&gt;INT(B4:AF4))+(B4:AF4&lt;=0),COLUMN(B4:AF4))))</f>
         <v>3</v>
       </c>
-      <c r="AJ4" s="181" cm="1">
+      <c r="AJ4" s="180" cm="1">
         <f t="array" ref="AJ4">SUMPRODUCT(--(B4:AF4=INT(B4:AF4)),--(B4:AF4&gt;0))/30*100%</f>
-        <v>0.3</v>
-      </c>
-      <c r="AK4" s="182">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="AK4" s="181">
         <f t="shared" ref="AK4:AM4" si="1">RANK(AG4,AG$3:AG$53,0)</f>
         <v>6</v>
       </c>
-      <c r="AL4" s="182">
+      <c r="AL4" s="181">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="AM4" s="182">
+      <c r="AM4" s="181">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:39">
-      <c r="A5" s="183">
+      <c r="A5" s="182">
         <v>3</v>
       </c>
       <c r="B5" s="116"/>
@@ -8820,37 +8846,37 @@
       <c r="AD5" s="116"/>
       <c r="AE5" s="116"/>
       <c r="AF5" s="116"/>
-      <c r="AG5" s="179">
+      <c r="AG5" s="178">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AH5" s="180" cm="1">
+      <c r="AH5" s="179" cm="1">
         <f t="array" ref="AH5">SUMPRODUCT(--(B5:AF5=INT(B5:AF5)),--(B5:AF5&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="AI5" s="180" cm="1">
+      <c r="AI5" s="179" cm="1">
         <f t="array" ref="AI5">MAX(FREQUENCY(IF((B5:AF5=INT(B5:AF5))*(B5:AF5&gt;0),COLUMN(B5:AF5)),IF((B5:AF5&lt;&gt;INT(B5:AF5))+(B5:AF5&lt;=0),COLUMN(B5:AF5))))</f>
         <v>1</v>
       </c>
-      <c r="AJ5" s="181" cm="1">
+      <c r="AJ5" s="180" cm="1">
         <f t="array" ref="AJ5">SUMPRODUCT(--(B5:AF5=INT(B5:AF5)),--(B5:AF5&gt;0))/30*100%</f>
         <v>0.0666666666666667</v>
       </c>
-      <c r="AK5" s="182">
+      <c r="AK5" s="181">
         <f t="shared" ref="AK5:AM5" si="2">RANK(AG5,AG$3:AG$53,0)</f>
-        <v>24</v>
-      </c>
-      <c r="AL5" s="182">
+        <v>28</v>
+      </c>
+      <c r="AL5" s="181">
         <f t="shared" si="2"/>
-        <v>24</v>
-      </c>
-      <c r="AM5" s="182">
+        <v>27</v>
+      </c>
+      <c r="AM5" s="181">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:39">
-      <c r="A6" s="183">
+      <c r="A6" s="182">
         <v>4</v>
       </c>
       <c r="B6" s="116"/>
@@ -8888,37 +8914,37 @@
       <c r="AD6" s="116"/>
       <c r="AE6" s="116"/>
       <c r="AF6" s="116"/>
-      <c r="AG6" s="179">
+      <c r="AG6" s="178">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AH6" s="180" cm="1">
+      <c r="AH6" s="179" cm="1">
         <f t="array" ref="AH6">SUMPRODUCT(--(B6:AF6=INT(B6:AF6)),--(B6:AF6&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="AI6" s="180" cm="1">
+      <c r="AI6" s="179" cm="1">
         <f t="array" ref="AI6">MAX(FREQUENCY(IF((B6:AF6=INT(B6:AF6))*(B6:AF6&gt;0),COLUMN(B6:AF6)),IF((B6:AF6&lt;&gt;INT(B6:AF6))+(B6:AF6&lt;=0),COLUMN(B6:AF6))))</f>
         <v>1</v>
       </c>
-      <c r="AJ6" s="181" cm="1">
+      <c r="AJ6" s="180" cm="1">
         <f t="array" ref="AJ6">SUMPRODUCT(--(B6:AF6=INT(B6:AF6)),--(B6:AF6&gt;0))/30*100%</f>
         <v>0.0666666666666667</v>
       </c>
-      <c r="AK6" s="182">
+      <c r="AK6" s="181">
         <f t="shared" ref="AK6:AM6" si="3">RANK(AG6,AG$3:AG$53,0)</f>
-        <v>24</v>
-      </c>
-      <c r="AL6" s="182">
+        <v>28</v>
+      </c>
+      <c r="AL6" s="181">
         <f t="shared" si="3"/>
-        <v>24</v>
-      </c>
-      <c r="AM6" s="182">
+        <v>27</v>
+      </c>
+      <c r="AM6" s="181">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:39">
-      <c r="A7" s="183">
+      <c r="A7" s="182">
         <v>5</v>
       </c>
       <c r="B7" s="116">
@@ -8958,37 +8984,37 @@
       <c r="AD7" s="116"/>
       <c r="AE7" s="116"/>
       <c r="AF7" s="116"/>
-      <c r="AG7" s="179">
+      <c r="AG7" s="178">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="AH7" s="180" cm="1">
+      <c r="AH7" s="179" cm="1">
         <f t="array" ref="AH7">SUMPRODUCT(--(B7:AF7=INT(B7:AF7)),--(B7:AF7&gt;0))</f>
         <v>3</v>
       </c>
-      <c r="AI7" s="180" cm="1">
+      <c r="AI7" s="179" cm="1">
         <f t="array" ref="AI7">MAX(FREQUENCY(IF((B7:AF7=INT(B7:AF7))*(B7:AF7&gt;0),COLUMN(B7:AF7)),IF((B7:AF7&lt;&gt;INT(B7:AF7))+(B7:AF7&lt;=0),COLUMN(B7:AF7))))</f>
         <v>1</v>
       </c>
-      <c r="AJ7" s="181" cm="1">
+      <c r="AJ7" s="180" cm="1">
         <f t="array" ref="AJ7">SUMPRODUCT(--(B7:AF7=INT(B7:AF7)),--(B7:AF7&gt;0))/30*100%</f>
         <v>0.1</v>
       </c>
-      <c r="AK7" s="182">
+      <c r="AK7" s="181">
         <f t="shared" ref="AK7:AM7" si="4">RANK(AG7,AG$3:AG$53,0)</f>
         <v>20</v>
       </c>
-      <c r="AL7" s="182">
+      <c r="AL7" s="181">
         <f t="shared" si="4"/>
-        <v>21</v>
-      </c>
-      <c r="AM7" s="182">
+        <v>22</v>
+      </c>
+      <c r="AM7" s="181">
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:39">
-      <c r="A8" s="183">
+      <c r="A8" s="182">
         <v>6</v>
       </c>
       <c r="B8" s="116">
@@ -9054,37 +9080,37 @@
       <c r="AD8" s="116"/>
       <c r="AE8" s="116"/>
       <c r="AF8" s="116"/>
-      <c r="AG8" s="179">
+      <c r="AG8" s="178">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="AH8" s="180" cm="1">
+      <c r="AH8" s="179" cm="1">
         <f t="array" ref="AH8">SUMPRODUCT(--(B8:AF8=INT(B8:AF8)),--(B8:AF8&gt;0))</f>
         <v>16</v>
       </c>
-      <c r="AI8" s="180" cm="1">
+      <c r="AI8" s="179" cm="1">
         <f t="array" ref="AI8">MAX(FREQUENCY(IF((B8:AF8=INT(B8:AF8))*(B8:AF8&gt;0),COLUMN(B8:AF8)),IF((B8:AF8&lt;&gt;INT(B8:AF8))+(B8:AF8&lt;=0),COLUMN(B8:AF8))))</f>
         <v>5</v>
       </c>
-      <c r="AJ8" s="181" cm="1">
+      <c r="AJ8" s="180" cm="1">
         <f t="array" ref="AJ8">SUMPRODUCT(--(B8:AF8=INT(B8:AF8)),--(B8:AF8&gt;0))/30*100%</f>
         <v>0.533333333333333</v>
       </c>
-      <c r="AK8" s="182">
+      <c r="AK8" s="181">
         <f t="shared" ref="AK8:AM8" si="5">RANK(AG8,AG$3:AG$53,0)</f>
         <v>3</v>
       </c>
-      <c r="AL8" s="182">
+      <c r="AL8" s="181">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="AM8" s="182">
+      <c r="AM8" s="181">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:39">
-      <c r="A9" s="183">
+      <c r="A9" s="182">
         <v>7</v>
       </c>
       <c r="B9" s="116">
@@ -9126,7 +9152,9 @@
       <c r="V9" s="116"/>
       <c r="W9" s="116"/>
       <c r="X9" s="116"/>
-      <c r="Y9" s="116"/>
+      <c r="Y9" s="116">
+        <v>1</v>
+      </c>
       <c r="Z9" s="116"/>
       <c r="AA9" s="116"/>
       <c r="AB9" s="116"/>
@@ -9134,37 +9162,37 @@
       <c r="AD9" s="116"/>
       <c r="AE9" s="116"/>
       <c r="AF9" s="116"/>
-      <c r="AG9" s="179">
+      <c r="AG9" s="178">
         <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AH9" s="180" cm="1">
+        <v>9</v>
+      </c>
+      <c r="AH9" s="179" cm="1">
         <f t="array" ref="AH9">SUMPRODUCT(--(B9:AF9=INT(B9:AF9)),--(B9:AF9&gt;0))</f>
-        <v>8</v>
-      </c>
-      <c r="AI9" s="180" cm="1">
+        <v>9</v>
+      </c>
+      <c r="AI9" s="179" cm="1">
         <f t="array" ref="AI9">MAX(FREQUENCY(IF((B9:AF9=INT(B9:AF9))*(B9:AF9&gt;0),COLUMN(B9:AF9)),IF((B9:AF9&lt;&gt;INT(B9:AF9))+(B9:AF9&lt;=0),COLUMN(B9:AF9))))</f>
         <v>3</v>
       </c>
-      <c r="AJ9" s="181" cm="1">
+      <c r="AJ9" s="180" cm="1">
         <f t="array" ref="AJ9">SUMPRODUCT(--(B9:AF9=INT(B9:AF9)),--(B9:AF9&gt;0))/30*100%</f>
-        <v>0.266666666666667</v>
-      </c>
-      <c r="AK9" s="182">
+        <v>0.3</v>
+      </c>
+      <c r="AK9" s="181">
         <f t="shared" ref="AK9:AM9" si="6">RANK(AG9,AG$3:AG$53,0)</f>
         <v>9</v>
       </c>
-      <c r="AL9" s="182">
+      <c r="AL9" s="181">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="AM9" s="182">
+      <c r="AM9" s="181">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:39">
-      <c r="A10" s="178">
+      <c r="A10" s="116">
         <v>8</v>
       </c>
       <c r="B10" s="116"/>
@@ -9190,7 +9218,9 @@
       <c r="V10" s="116"/>
       <c r="W10" s="116"/>
       <c r="X10" s="116"/>
-      <c r="Y10" s="116"/>
+      <c r="Y10" s="116">
+        <v>1</v>
+      </c>
       <c r="Z10" s="116"/>
       <c r="AA10" s="116"/>
       <c r="AB10" s="116"/>
@@ -9198,37 +9228,37 @@
       <c r="AD10" s="116"/>
       <c r="AE10" s="116"/>
       <c r="AF10" s="116"/>
-      <c r="AG10" s="179">
+      <c r="AG10" s="178">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH10" s="180" cm="1">
+        <v>1</v>
+      </c>
+      <c r="AH10" s="179" cm="1">
         <f t="array" ref="AH10">SUMPRODUCT(--(B10:AF10=INT(B10:AF10)),--(B10:AF10&gt;0))</f>
-        <v>0</v>
-      </c>
-      <c r="AI10" s="180" cm="1">
+        <v>1</v>
+      </c>
+      <c r="AI10" s="179" cm="1">
         <f t="array" ref="AI10">MAX(FREQUENCY(IF((B10:AF10=INT(B10:AF10))*(B10:AF10&gt;0),COLUMN(B10:AF10)),IF((B10:AF10&lt;&gt;INT(B10:AF10))+(B10:AF10&lt;=0),COLUMN(B10:AF10))))</f>
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="181" cm="1">
+        <v>1</v>
+      </c>
+      <c r="AJ10" s="180" cm="1">
         <f t="array" ref="AJ10">SUMPRODUCT(--(B10:AF10=INT(B10:AF10)),--(B10:AF10&gt;0))/30*100%</f>
-        <v>0</v>
-      </c>
-      <c r="AK10" s="182">
+        <v>0.0333333333333333</v>
+      </c>
+      <c r="AK10" s="181">
         <f t="shared" ref="AK10:AM10" si="7">RANK(AG10,AG$3:AG$53,0)</f>
-        <v>35</v>
-      </c>
-      <c r="AL10" s="182">
+        <v>34</v>
+      </c>
+      <c r="AL10" s="181">
         <f t="shared" si="7"/>
-        <v>35</v>
-      </c>
-      <c r="AM10" s="182">
+        <v>34</v>
+      </c>
+      <c r="AM10" s="181">
         <f t="shared" si="7"/>
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:39">
-      <c r="A11" s="183">
+      <c r="A11" s="182">
         <v>9</v>
       </c>
       <c r="B11" s="116"/>
@@ -9270,37 +9300,37 @@
       <c r="AD11" s="116"/>
       <c r="AE11" s="116"/>
       <c r="AF11" s="116"/>
-      <c r="AG11" s="179">
+      <c r="AG11" s="178">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="AH11" s="180" cm="1">
+      <c r="AH11" s="179" cm="1">
         <f t="array" ref="AH11">SUMPRODUCT(--(B11:AF11=INT(B11:AF11)),--(B11:AF11&gt;0))</f>
         <v>4</v>
       </c>
-      <c r="AI11" s="180" cm="1">
+      <c r="AI11" s="179" cm="1">
         <f t="array" ref="AI11">MAX(FREQUENCY(IF((B11:AF11=INT(B11:AF11))*(B11:AF11&gt;0),COLUMN(B11:AF11)),IF((B11:AF11&lt;&gt;INT(B11:AF11))+(B11:AF11&lt;=0),COLUMN(B11:AF11))))</f>
         <v>1</v>
       </c>
-      <c r="AJ11" s="181" cm="1">
+      <c r="AJ11" s="180" cm="1">
         <f t="array" ref="AJ11">SUMPRODUCT(--(B11:AF11=INT(B11:AF11)),--(B11:AF11&gt;0))/30*100%</f>
         <v>0.133333333333333</v>
       </c>
-      <c r="AK11" s="182">
+      <c r="AK11" s="181">
         <f t="shared" ref="AK11:AM11" si="8">RANK(AG11,AG$3:AG$53,0)</f>
         <v>20</v>
       </c>
-      <c r="AL11" s="182">
+      <c r="AL11" s="181">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="AM11" s="182">
+      <c r="AM11" s="181">
         <f t="shared" si="8"/>
         <v>18</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:39">
-      <c r="A12" s="183">
+      <c r="A12" s="182">
         <v>10</v>
       </c>
       <c r="B12" s="116"/>
@@ -9328,7 +9358,9 @@
       <c r="V12" s="116"/>
       <c r="W12" s="116"/>
       <c r="X12" s="116"/>
-      <c r="Y12" s="116"/>
+      <c r="Y12" s="116">
+        <v>1</v>
+      </c>
       <c r="Z12" s="116"/>
       <c r="AA12" s="116"/>
       <c r="AB12" s="116"/>
@@ -9336,37 +9368,37 @@
       <c r="AD12" s="116"/>
       <c r="AE12" s="116"/>
       <c r="AF12" s="116"/>
-      <c r="AG12" s="179">
+      <c r="AG12" s="178">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AH12" s="180" cm="1">
+        <v>2</v>
+      </c>
+      <c r="AH12" s="179" cm="1">
         <f t="array" ref="AH12">SUMPRODUCT(--(B12:AF12=INT(B12:AF12)),--(B12:AF12&gt;0))</f>
-        <v>1</v>
-      </c>
-      <c r="AI12" s="180" cm="1">
+        <v>2</v>
+      </c>
+      <c r="AI12" s="179" cm="1">
         <f t="array" ref="AI12">MAX(FREQUENCY(IF((B12:AF12=INT(B12:AF12))*(B12:AF12&gt;0),COLUMN(B12:AF12)),IF((B12:AF12&lt;&gt;INT(B12:AF12))+(B12:AF12&lt;=0),COLUMN(B12:AF12))))</f>
         <v>1</v>
       </c>
-      <c r="AJ12" s="181" cm="1">
+      <c r="AJ12" s="180" cm="1">
         <f t="array" ref="AJ12">SUMPRODUCT(--(B12:AF12=INT(B12:AF12)),--(B12:AF12&gt;0))/30*100%</f>
-        <v>0.0333333333333333</v>
-      </c>
-      <c r="AK12" s="182">
+        <v>0.0666666666666667</v>
+      </c>
+      <c r="AK12" s="181">
         <f t="shared" ref="AK12:AM12" si="9">RANK(AG12,AG$3:AG$53,0)</f>
-        <v>32</v>
-      </c>
-      <c r="AL12" s="182">
+        <v>28</v>
+      </c>
+      <c r="AL12" s="181">
         <f t="shared" si="9"/>
-        <v>31</v>
-      </c>
-      <c r="AM12" s="182">
+        <v>27</v>
+      </c>
+      <c r="AM12" s="181">
         <f t="shared" si="9"/>
         <v>18</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:39">
-      <c r="A13" s="183">
+      <c r="A13" s="182">
         <v>11</v>
       </c>
       <c r="B13" s="116"/>
@@ -9404,7 +9436,9 @@
       <c r="V13" s="116"/>
       <c r="W13" s="116"/>
       <c r="X13" s="116"/>
-      <c r="Y13" s="116"/>
+      <c r="Y13" s="116">
+        <v>1</v>
+      </c>
       <c r="Z13" s="116"/>
       <c r="AA13" s="116"/>
       <c r="AB13" s="116"/>
@@ -9412,37 +9446,37 @@
       <c r="AD13" s="116"/>
       <c r="AE13" s="116"/>
       <c r="AF13" s="116"/>
-      <c r="AG13" s="179">
+      <c r="AG13" s="178">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AH13" s="180" cm="1">
+        <v>7</v>
+      </c>
+      <c r="AH13" s="179" cm="1">
         <f t="array" ref="AH13">SUMPRODUCT(--(B13:AF13=INT(B13:AF13)),--(B13:AF13&gt;0))</f>
-        <v>6</v>
-      </c>
-      <c r="AI13" s="180" cm="1">
+        <v>7</v>
+      </c>
+      <c r="AI13" s="179" cm="1">
         <f t="array" ref="AI13">MAX(FREQUENCY(IF((B13:AF13=INT(B13:AF13))*(B13:AF13&gt;0),COLUMN(B13:AF13)),IF((B13:AF13&lt;&gt;INT(B13:AF13))+(B13:AF13&lt;=0),COLUMN(B13:AF13))))</f>
         <v>1</v>
       </c>
-      <c r="AJ13" s="181" cm="1">
+      <c r="AJ13" s="180" cm="1">
         <f t="array" ref="AJ13">SUMPRODUCT(--(B13:AF13=INT(B13:AF13)),--(B13:AF13&gt;0))/30*100%</f>
-        <v>0.2</v>
-      </c>
-      <c r="AK13" s="182">
+        <v>0.233333333333333</v>
+      </c>
+      <c r="AK13" s="181">
         <f t="shared" ref="AK13:AM13" si="10">RANK(AG13,AG$3:AG$53,0)</f>
         <v>16</v>
       </c>
-      <c r="AL13" s="182">
+      <c r="AL13" s="181">
         <f t="shared" si="10"/>
         <v>12</v>
       </c>
-      <c r="AM13" s="182">
+      <c r="AM13" s="181">
         <f t="shared" si="10"/>
         <v>18</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:39">
-      <c r="A14" s="183">
+      <c r="A14" s="182">
         <v>12</v>
       </c>
       <c r="B14" s="116"/>
@@ -9470,7 +9504,9 @@
       <c r="V14" s="116"/>
       <c r="W14" s="116"/>
       <c r="X14" s="116"/>
-      <c r="Y14" s="116"/>
+      <c r="Y14" s="116">
+        <v>1</v>
+      </c>
       <c r="Z14" s="116"/>
       <c r="AA14" s="116"/>
       <c r="AB14" s="116"/>
@@ -9478,37 +9514,37 @@
       <c r="AD14" s="116"/>
       <c r="AE14" s="116"/>
       <c r="AF14" s="116"/>
-      <c r="AG14" s="179">
+      <c r="AG14" s="178">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AH14" s="180" cm="1">
+        <v>2</v>
+      </c>
+      <c r="AH14" s="179" cm="1">
         <f t="array" ref="AH14">SUMPRODUCT(--(B14:AF14=INT(B14:AF14)),--(B14:AF14&gt;0))</f>
-        <v>1</v>
-      </c>
-      <c r="AI14" s="180" cm="1">
+        <v>2</v>
+      </c>
+      <c r="AI14" s="179" cm="1">
         <f t="array" ref="AI14">MAX(FREQUENCY(IF((B14:AF14=INT(B14:AF14))*(B14:AF14&gt;0),COLUMN(B14:AF14)),IF((B14:AF14&lt;&gt;INT(B14:AF14))+(B14:AF14&lt;=0),COLUMN(B14:AF14))))</f>
         <v>1</v>
       </c>
-      <c r="AJ14" s="181" cm="1">
+      <c r="AJ14" s="180" cm="1">
         <f t="array" ref="AJ14">SUMPRODUCT(--(B14:AF14=INT(B14:AF14)),--(B14:AF14&gt;0))/30*100%</f>
-        <v>0.0333333333333333</v>
-      </c>
-      <c r="AK14" s="182">
+        <v>0.0666666666666667</v>
+      </c>
+      <c r="AK14" s="181">
         <f t="shared" ref="AK14:AM14" si="11">RANK(AG14,AG$3:AG$53,0)</f>
-        <v>32</v>
-      </c>
-      <c r="AL14" s="182">
+        <v>28</v>
+      </c>
+      <c r="AL14" s="181">
         <f t="shared" si="11"/>
-        <v>31</v>
-      </c>
-      <c r="AM14" s="182">
+        <v>27</v>
+      </c>
+      <c r="AM14" s="181">
         <f t="shared" si="11"/>
         <v>18</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:39">
-      <c r="A15" s="183">
+      <c r="A15" s="182">
         <v>13</v>
       </c>
       <c r="B15" s="116"/>
@@ -9546,7 +9582,9 @@
       <c r="V15" s="116"/>
       <c r="W15" s="116"/>
       <c r="X15" s="116"/>
-      <c r="Y15" s="116"/>
+      <c r="Y15" s="116">
+        <v>1</v>
+      </c>
       <c r="Z15" s="116"/>
       <c r="AA15" s="116"/>
       <c r="AB15" s="116"/>
@@ -9554,37 +9592,37 @@
       <c r="AD15" s="116"/>
       <c r="AE15" s="116"/>
       <c r="AF15" s="116"/>
-      <c r="AG15" s="179">
+      <c r="AG15" s="178">
         <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AH15" s="179" cm="1">
+        <f t="array" ref="AH15">SUMPRODUCT(--(B15:AF15=INT(B15:AF15)),--(B15:AF15&gt;0))</f>
         <v>7</v>
       </c>
-      <c r="AH15" s="180" cm="1">
-        <f t="array" ref="AH15">SUMPRODUCT(--(B15:AF15=INT(B15:AF15)),--(B15:AF15&gt;0))</f>
-        <v>6</v>
-      </c>
-      <c r="AI15" s="180" cm="1">
+      <c r="AI15" s="179" cm="1">
         <f t="array" ref="AI15">MAX(FREQUENCY(IF((B15:AF15=INT(B15:AF15))*(B15:AF15&gt;0),COLUMN(B15:AF15)),IF((B15:AF15&lt;&gt;INT(B15:AF15))+(B15:AF15&lt;=0),COLUMN(B15:AF15))))</f>
         <v>2</v>
       </c>
-      <c r="AJ15" s="181" cm="1">
+      <c r="AJ15" s="180" cm="1">
         <f t="array" ref="AJ15">SUMPRODUCT(--(B15:AF15=INT(B15:AF15)),--(B15:AF15&gt;0))/30*100%</f>
-        <v>0.2</v>
-      </c>
-      <c r="AK15" s="182">
+        <v>0.233333333333333</v>
+      </c>
+      <c r="AK15" s="181">
         <f t="shared" ref="AK15:AM15" si="12">RANK(AG15,AG$3:AG$53,0)</f>
         <v>10</v>
       </c>
-      <c r="AL15" s="182">
+      <c r="AL15" s="181">
         <f t="shared" si="12"/>
         <v>12</v>
       </c>
-      <c r="AM15" s="182">
+      <c r="AM15" s="181">
         <f t="shared" si="12"/>
         <v>13</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:39">
-      <c r="A16" s="183">
+      <c r="A16" s="182">
         <v>14</v>
       </c>
       <c r="B16" s="116"/>
@@ -9622,37 +9660,37 @@
       <c r="AD16" s="116"/>
       <c r="AE16" s="116"/>
       <c r="AF16" s="116"/>
-      <c r="AG16" s="179">
+      <c r="AG16" s="178">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AH16" s="180" cm="1">
+      <c r="AH16" s="179" cm="1">
         <f t="array" ref="AH16">SUMPRODUCT(--(B16:AF16=INT(B16:AF16)),--(B16:AF16&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="AI16" s="180" cm="1">
+      <c r="AI16" s="179" cm="1">
         <f t="array" ref="AI16">MAX(FREQUENCY(IF((B16:AF16=INT(B16:AF16))*(B16:AF16&gt;0),COLUMN(B16:AF16)),IF((B16:AF16&lt;&gt;INT(B16:AF16))+(B16:AF16&lt;=0),COLUMN(B16:AF16))))</f>
         <v>1</v>
       </c>
-      <c r="AJ16" s="181" cm="1">
+      <c r="AJ16" s="180" cm="1">
         <f t="array" ref="AJ16">SUMPRODUCT(--(B16:AF16=INT(B16:AF16)),--(B16:AF16&gt;0))/30*100%</f>
         <v>0.0666666666666667</v>
       </c>
-      <c r="AK16" s="182">
+      <c r="AK16" s="181">
         <f t="shared" ref="AK16:AM16" si="13">RANK(AG16,AG$3:AG$53,0)</f>
-        <v>24</v>
-      </c>
-      <c r="AL16" s="182">
+        <v>28</v>
+      </c>
+      <c r="AL16" s="181">
         <f t="shared" si="13"/>
-        <v>24</v>
-      </c>
-      <c r="AM16" s="182">
+        <v>27</v>
+      </c>
+      <c r="AM16" s="181">
         <f t="shared" si="13"/>
         <v>18</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:39">
-      <c r="A17" s="183">
+      <c r="A17" s="182">
         <v>15</v>
       </c>
       <c r="B17" s="116"/>
@@ -9682,7 +9720,9 @@
       </c>
       <c r="W17" s="116"/>
       <c r="X17" s="116"/>
-      <c r="Y17" s="116"/>
+      <c r="Y17" s="116">
+        <v>1</v>
+      </c>
       <c r="Z17" s="116"/>
       <c r="AA17" s="116"/>
       <c r="AB17" s="116"/>
@@ -9690,37 +9730,37 @@
       <c r="AD17" s="116"/>
       <c r="AE17" s="116"/>
       <c r="AF17" s="116"/>
-      <c r="AG17" s="179">
+      <c r="AG17" s="178">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AH17" s="180" cm="1">
+        <v>3</v>
+      </c>
+      <c r="AH17" s="179" cm="1">
         <f t="array" ref="AH17">SUMPRODUCT(--(B17:AF17=INT(B17:AF17)),--(B17:AF17&gt;0))</f>
-        <v>2</v>
-      </c>
-      <c r="AI17" s="180" cm="1">
+        <v>3</v>
+      </c>
+      <c r="AI17" s="179" cm="1">
         <f t="array" ref="AI17">MAX(FREQUENCY(IF((B17:AF17=INT(B17:AF17))*(B17:AF17&gt;0),COLUMN(B17:AF17)),IF((B17:AF17&lt;&gt;INT(B17:AF17))+(B17:AF17&lt;=0),COLUMN(B17:AF17))))</f>
         <v>1</v>
       </c>
-      <c r="AJ17" s="181" cm="1">
+      <c r="AJ17" s="180" cm="1">
         <f t="array" ref="AJ17">SUMPRODUCT(--(B17:AF17=INT(B17:AF17)),--(B17:AF17&gt;0))/30*100%</f>
-        <v>0.0666666666666667</v>
-      </c>
-      <c r="AK17" s="182">
+        <v>0.1</v>
+      </c>
+      <c r="AK17" s="181">
         <f t="shared" ref="AK17:AM17" si="14">RANK(AG17,AG$3:AG$53,0)</f>
-        <v>24</v>
-      </c>
-      <c r="AL17" s="182">
+        <v>23</v>
+      </c>
+      <c r="AL17" s="181">
         <f t="shared" si="14"/>
-        <v>24</v>
-      </c>
-      <c r="AM17" s="182">
+        <v>22</v>
+      </c>
+      <c r="AM17" s="181">
         <f t="shared" si="14"/>
         <v>18</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:39">
-      <c r="A18" s="178">
+      <c r="A18" s="116">
         <v>16</v>
       </c>
       <c r="B18" s="116"/>
@@ -9746,7 +9786,9 @@
       <c r="V18" s="116"/>
       <c r="W18" s="116"/>
       <c r="X18" s="116"/>
-      <c r="Y18" s="116"/>
+      <c r="Y18" s="116">
+        <v>1</v>
+      </c>
       <c r="Z18" s="116"/>
       <c r="AA18" s="116"/>
       <c r="AB18" s="116"/>
@@ -9754,37 +9796,37 @@
       <c r="AD18" s="116"/>
       <c r="AE18" s="116"/>
       <c r="AF18" s="116"/>
-      <c r="AG18" s="179">
+      <c r="AG18" s="178">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH18" s="180" cm="1">
+        <v>1</v>
+      </c>
+      <c r="AH18" s="179" cm="1">
         <f t="array" ref="AH18">SUMPRODUCT(--(B18:AF18=INT(B18:AF18)),--(B18:AF18&gt;0))</f>
-        <v>0</v>
-      </c>
-      <c r="AI18" s="180" cm="1">
+        <v>1</v>
+      </c>
+      <c r="AI18" s="179" cm="1">
         <f t="array" ref="AI18">MAX(FREQUENCY(IF((B18:AF18=INT(B18:AF18))*(B18:AF18&gt;0),COLUMN(B18:AF18)),IF((B18:AF18&lt;&gt;INT(B18:AF18))+(B18:AF18&lt;=0),COLUMN(B18:AF18))))</f>
-        <v>0</v>
-      </c>
-      <c r="AJ18" s="181" cm="1">
+        <v>1</v>
+      </c>
+      <c r="AJ18" s="180" cm="1">
         <f t="array" ref="AJ18">SUMPRODUCT(--(B18:AF18=INT(B18:AF18)),--(B18:AF18&gt;0))/30*100%</f>
-        <v>0</v>
-      </c>
-      <c r="AK18" s="182">
+        <v>0.0333333333333333</v>
+      </c>
+      <c r="AK18" s="181">
         <f t="shared" ref="AK18:AM18" si="15">RANK(AG18,AG$3:AG$53,0)</f>
-        <v>35</v>
-      </c>
-      <c r="AL18" s="182">
+        <v>34</v>
+      </c>
+      <c r="AL18" s="181">
         <f t="shared" si="15"/>
-        <v>35</v>
-      </c>
-      <c r="AM18" s="182">
+        <v>34</v>
+      </c>
+      <c r="AM18" s="181">
         <f t="shared" si="15"/>
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:39">
-      <c r="A19" s="183">
+      <c r="A19" s="182">
         <v>17</v>
       </c>
       <c r="B19" s="116">
@@ -9828,37 +9870,37 @@
       <c r="AD19" s="116"/>
       <c r="AE19" s="116"/>
       <c r="AF19" s="116"/>
-      <c r="AG19" s="179">
+      <c r="AG19" s="178">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="AH19" s="180" cm="1">
+      <c r="AH19" s="179" cm="1">
         <f t="array" ref="AH19">SUMPRODUCT(--(B19:AF19=INT(B19:AF19)),--(B19:AF19&gt;0))</f>
         <v>5</v>
       </c>
-      <c r="AI19" s="180" cm="1">
+      <c r="AI19" s="179" cm="1">
         <f t="array" ref="AI19">MAX(FREQUENCY(IF((B19:AF19=INT(B19:AF19))*(B19:AF19&gt;0),COLUMN(B19:AF19)),IF((B19:AF19&lt;&gt;INT(B19:AF19))+(B19:AF19&lt;=0),COLUMN(B19:AF19))))</f>
         <v>2</v>
       </c>
-      <c r="AJ19" s="181" cm="1">
+      <c r="AJ19" s="180" cm="1">
         <f t="array" ref="AJ19">SUMPRODUCT(--(B19:AF19=INT(B19:AF19)),--(B19:AF19&gt;0))/30*100%</f>
         <v>0.166666666666667</v>
       </c>
-      <c r="AK19" s="182">
+      <c r="AK19" s="181">
         <f t="shared" ref="AK19:AM19" si="16">RANK(AG19,AG$3:AG$53,0)</f>
-        <v>18</v>
-      </c>
-      <c r="AL19" s="182">
+        <v>19</v>
+      </c>
+      <c r="AL19" s="181">
         <f t="shared" si="16"/>
-        <v>17</v>
-      </c>
-      <c r="AM19" s="182">
+        <v>19</v>
+      </c>
+      <c r="AM19" s="181">
         <f t="shared" si="16"/>
         <v>13</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:39">
-      <c r="A20" s="183">
+      <c r="A20" s="182">
         <v>18</v>
       </c>
       <c r="B20" s="116"/>
@@ -9894,37 +9936,37 @@
       <c r="AD20" s="116"/>
       <c r="AE20" s="116"/>
       <c r="AF20" s="116"/>
-      <c r="AG20" s="179">
+      <c r="AG20" s="178">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH20" s="180" cm="1">
+      <c r="AH20" s="179" cm="1">
         <f t="array" ref="AH20">SUMPRODUCT(--(B20:AF20=INT(B20:AF20)),--(B20:AF20&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="AI20" s="180" cm="1">
+      <c r="AI20" s="179" cm="1">
         <f t="array" ref="AI20">MAX(FREQUENCY(IF((B20:AF20=INT(B20:AF20))*(B20:AF20&gt;0),COLUMN(B20:AF20)),IF((B20:AF20&lt;&gt;INT(B20:AF20))+(B20:AF20&lt;=0),COLUMN(B20:AF20))))</f>
         <v>1</v>
       </c>
-      <c r="AJ20" s="181" cm="1">
+      <c r="AJ20" s="180" cm="1">
         <f t="array" ref="AJ20">SUMPRODUCT(--(B20:AF20=INT(B20:AF20)),--(B20:AF20&gt;0))/30*100%</f>
         <v>0.0333333333333333</v>
       </c>
-      <c r="AK20" s="182">
+      <c r="AK20" s="181">
         <f t="shared" ref="AK20:AM20" si="17">RANK(AG20,AG$3:AG$53,0)</f>
-        <v>32</v>
-      </c>
-      <c r="AL20" s="182">
+        <v>34</v>
+      </c>
+      <c r="AL20" s="181">
         <f t="shared" si="17"/>
-        <v>31</v>
-      </c>
-      <c r="AM20" s="182">
+        <v>34</v>
+      </c>
+      <c r="AM20" s="181">
         <f t="shared" si="17"/>
         <v>18</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:39">
-      <c r="A21" s="183">
+      <c r="A21" s="182">
         <v>19</v>
       </c>
       <c r="B21" s="116"/>
@@ -9962,37 +10004,37 @@
       <c r="AD21" s="116"/>
       <c r="AE21" s="116"/>
       <c r="AF21" s="116"/>
-      <c r="AG21" s="179">
+      <c r="AG21" s="178">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AH21" s="180" cm="1">
+      <c r="AH21" s="179" cm="1">
         <f t="array" ref="AH21">SUMPRODUCT(--(B21:AF21=INT(B21:AF21)),--(B21:AF21&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="AI21" s="180" cm="1">
+      <c r="AI21" s="179" cm="1">
         <f t="array" ref="AI21">MAX(FREQUENCY(IF((B21:AF21=INT(B21:AF21))*(B21:AF21&gt;0),COLUMN(B21:AF21)),IF((B21:AF21&lt;&gt;INT(B21:AF21))+(B21:AF21&lt;=0),COLUMN(B21:AF21))))</f>
         <v>1</v>
       </c>
-      <c r="AJ21" s="181" cm="1">
+      <c r="AJ21" s="180" cm="1">
         <f t="array" ref="AJ21">SUMPRODUCT(--(B21:AF21=INT(B21:AF21)),--(B21:AF21&gt;0))/30*100%</f>
         <v>0.0666666666666667</v>
       </c>
-      <c r="AK21" s="182">
+      <c r="AK21" s="181">
         <f t="shared" ref="AK21:AM21" si="18">RANK(AG21,AG$3:AG$53,0)</f>
-        <v>24</v>
-      </c>
-      <c r="AL21" s="182">
+        <v>28</v>
+      </c>
+      <c r="AL21" s="181">
         <f t="shared" si="18"/>
-        <v>24</v>
-      </c>
-      <c r="AM21" s="182">
+        <v>27</v>
+      </c>
+      <c r="AM21" s="181">
         <f t="shared" si="18"/>
         <v>18</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:39">
-      <c r="A22" s="183">
+      <c r="A22" s="182">
         <v>20</v>
       </c>
       <c r="B22" s="116"/>
@@ -10032,7 +10074,9 @@
       </c>
       <c r="W22" s="116"/>
       <c r="X22" s="116"/>
-      <c r="Y22" s="116"/>
+      <c r="Y22" s="116">
+        <v>1</v>
+      </c>
       <c r="Z22" s="116"/>
       <c r="AA22" s="116"/>
       <c r="AB22" s="116"/>
@@ -10040,37 +10084,37 @@
       <c r="AD22" s="116"/>
       <c r="AE22" s="116"/>
       <c r="AF22" s="116"/>
-      <c r="AG22" s="179">
+      <c r="AG22" s="178">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AH22" s="180" cm="1">
+        <v>10</v>
+      </c>
+      <c r="AH22" s="179" cm="1">
         <f t="array" ref="AH22">SUMPRODUCT(--(B22:AF22=INT(B22:AF22)),--(B22:AF22&gt;0))</f>
-        <v>7</v>
-      </c>
-      <c r="AI22" s="180" cm="1">
+        <v>8</v>
+      </c>
+      <c r="AI22" s="179" cm="1">
         <f t="array" ref="AI22">MAX(FREQUENCY(IF((B22:AF22=INT(B22:AF22))*(B22:AF22&gt;0),COLUMN(B22:AF22)),IF((B22:AF22&lt;&gt;INT(B22:AF22))+(B22:AF22&lt;=0),COLUMN(B22:AF22))))</f>
         <v>4</v>
       </c>
-      <c r="AJ22" s="181" cm="1">
+      <c r="AJ22" s="180" cm="1">
         <f t="array" ref="AJ22">SUMPRODUCT(--(B22:AF22=INT(B22:AF22)),--(B22:AF22&gt;0))/30*100%</f>
-        <v>0.233333333333333</v>
-      </c>
-      <c r="AK22" s="182">
+        <v>0.266666666666667</v>
+      </c>
+      <c r="AK22" s="181">
         <f t="shared" ref="AK22:AM22" si="19">RANK(AG22,AG$3:AG$53,0)</f>
         <v>7</v>
       </c>
-      <c r="AL22" s="182">
+      <c r="AL22" s="181">
         <f t="shared" si="19"/>
         <v>9</v>
       </c>
-      <c r="AM22" s="182">
+      <c r="AM22" s="181">
         <f t="shared" si="19"/>
         <v>6</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:39">
-      <c r="A23" s="178">
+      <c r="A23" s="183">
         <v>21</v>
       </c>
       <c r="B23" s="116"/>
@@ -10104,37 +10148,37 @@
       <c r="AD23" s="116"/>
       <c r="AE23" s="116"/>
       <c r="AF23" s="116"/>
-      <c r="AG23" s="179">
+      <c r="AG23" s="178">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH23" s="180" cm="1">
+      <c r="AH23" s="179" cm="1">
         <f t="array" ref="AH23">SUMPRODUCT(--(B23:AF23=INT(B23:AF23)),--(B23:AF23&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AI23" s="180" cm="1">
+      <c r="AI23" s="179" cm="1">
         <f t="array" ref="AI23">MAX(FREQUENCY(IF((B23:AF23=INT(B23:AF23))*(B23:AF23&gt;0),COLUMN(B23:AF23)),IF((B23:AF23&lt;&gt;INT(B23:AF23))+(B23:AF23&lt;=0),COLUMN(B23:AF23))))</f>
         <v>0</v>
       </c>
-      <c r="AJ23" s="181" cm="1">
+      <c r="AJ23" s="180" cm="1">
         <f t="array" ref="AJ23">SUMPRODUCT(--(B23:AF23=INT(B23:AF23)),--(B23:AF23&gt;0))/30*100%</f>
         <v>0</v>
       </c>
-      <c r="AK23" s="182">
+      <c r="AK23" s="181">
         <f t="shared" ref="AK23:AM23" si="20">RANK(AG23,AG$3:AG$53,0)</f>
-        <v>35</v>
-      </c>
-      <c r="AL23" s="182">
+        <v>40</v>
+      </c>
+      <c r="AL23" s="181">
         <f t="shared" si="20"/>
-        <v>35</v>
-      </c>
-      <c r="AM23" s="182">
+        <v>40</v>
+      </c>
+      <c r="AM23" s="181">
         <f t="shared" si="20"/>
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:39">
-      <c r="A24" s="183">
+      <c r="A24" s="182">
         <v>22</v>
       </c>
       <c r="B24" s="116"/>
@@ -10174,7 +10218,9 @@
       </c>
       <c r="W24" s="116"/>
       <c r="X24" s="116"/>
-      <c r="Y24" s="116"/>
+      <c r="Y24" s="116">
+        <v>1</v>
+      </c>
       <c r="Z24" s="116"/>
       <c r="AA24" s="116"/>
       <c r="AB24" s="116"/>
@@ -10182,37 +10228,37 @@
       <c r="AD24" s="116"/>
       <c r="AE24" s="116"/>
       <c r="AF24" s="116"/>
-      <c r="AG24" s="179">
+      <c r="AG24" s="178">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AH24" s="180" cm="1">
+        <v>8</v>
+      </c>
+      <c r="AH24" s="179" cm="1">
         <f t="array" ref="AH24">SUMPRODUCT(--(B24:AF24=INT(B24:AF24)),--(B24:AF24&gt;0))</f>
-        <v>7</v>
-      </c>
-      <c r="AI24" s="180" cm="1">
+        <v>8</v>
+      </c>
+      <c r="AI24" s="179" cm="1">
         <f t="array" ref="AI24">MAX(FREQUENCY(IF((B24:AF24=INT(B24:AF24))*(B24:AF24&gt;0),COLUMN(B24:AF24)),IF((B24:AF24&lt;&gt;INT(B24:AF24))+(B24:AF24&lt;=0),COLUMN(B24:AF24))))</f>
         <v>3</v>
       </c>
-      <c r="AJ24" s="181" cm="1">
+      <c r="AJ24" s="180" cm="1">
         <f t="array" ref="AJ24">SUMPRODUCT(--(B24:AF24=INT(B24:AF24)),--(B24:AF24&gt;0))/30*100%</f>
-        <v>0.233333333333333</v>
-      </c>
-      <c r="AK24" s="182">
+        <v>0.266666666666667</v>
+      </c>
+      <c r="AK24" s="181">
         <f t="shared" ref="AK24:AM24" si="21">RANK(AG24,AG$3:AG$53,0)</f>
         <v>10</v>
       </c>
-      <c r="AL24" s="182">
+      <c r="AL24" s="181">
         <f t="shared" si="21"/>
         <v>9</v>
       </c>
-      <c r="AM24" s="182">
+      <c r="AM24" s="181">
         <f t="shared" si="21"/>
         <v>8</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:39">
-      <c r="A25" s="178">
+      <c r="A25" s="116">
         <v>23</v>
       </c>
       <c r="B25" s="116"/>
@@ -10238,7 +10284,9 @@
       <c r="V25" s="116"/>
       <c r="W25" s="116"/>
       <c r="X25" s="116"/>
-      <c r="Y25" s="116"/>
+      <c r="Y25" s="116">
+        <v>1</v>
+      </c>
       <c r="Z25" s="116"/>
       <c r="AA25" s="116"/>
       <c r="AB25" s="116"/>
@@ -10246,37 +10294,37 @@
       <c r="AD25" s="116"/>
       <c r="AE25" s="116"/>
       <c r="AF25" s="116"/>
-      <c r="AG25" s="179">
+      <c r="AG25" s="178">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH25" s="180" cm="1">
+        <v>1</v>
+      </c>
+      <c r="AH25" s="179" cm="1">
         <f t="array" ref="AH25">SUMPRODUCT(--(B25:AF25=INT(B25:AF25)),--(B25:AF25&gt;0))</f>
-        <v>0</v>
-      </c>
-      <c r="AI25" s="180" cm="1">
+        <v>1</v>
+      </c>
+      <c r="AI25" s="179" cm="1">
         <f t="array" ref="AI25">MAX(FREQUENCY(IF((B25:AF25=INT(B25:AF25))*(B25:AF25&gt;0),COLUMN(B25:AF25)),IF((B25:AF25&lt;&gt;INT(B25:AF25))+(B25:AF25&lt;=0),COLUMN(B25:AF25))))</f>
-        <v>0</v>
-      </c>
-      <c r="AJ25" s="181" cm="1">
+        <v>1</v>
+      </c>
+      <c r="AJ25" s="180" cm="1">
         <f t="array" ref="AJ25">SUMPRODUCT(--(B25:AF25=INT(B25:AF25)),--(B25:AF25&gt;0))/30*100%</f>
-        <v>0</v>
-      </c>
-      <c r="AK25" s="182">
+        <v>0.0333333333333333</v>
+      </c>
+      <c r="AK25" s="181">
         <f t="shared" ref="AK25:AM25" si="22">RANK(AG25,AG$3:AG$53,0)</f>
-        <v>35</v>
-      </c>
-      <c r="AL25" s="182">
+        <v>34</v>
+      </c>
+      <c r="AL25" s="181">
         <f t="shared" si="22"/>
-        <v>35</v>
-      </c>
-      <c r="AM25" s="182">
+        <v>34</v>
+      </c>
+      <c r="AM25" s="181">
         <f t="shared" si="22"/>
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:39">
-      <c r="A26" s="178">
+      <c r="A26" s="183">
         <v>24</v>
       </c>
       <c r="B26" s="116"/>
@@ -10310,37 +10358,37 @@
       <c r="AD26" s="116"/>
       <c r="AE26" s="116"/>
       <c r="AF26" s="116"/>
-      <c r="AG26" s="179">
+      <c r="AG26" s="178">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH26" s="180" cm="1">
+      <c r="AH26" s="179" cm="1">
         <f t="array" ref="AH26">SUMPRODUCT(--(B26:AF26=INT(B26:AF26)),--(B26:AF26&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AI26" s="180" cm="1">
+      <c r="AI26" s="179" cm="1">
         <f t="array" ref="AI26">MAX(FREQUENCY(IF((B26:AF26=INT(B26:AF26))*(B26:AF26&gt;0),COLUMN(B26:AF26)),IF((B26:AF26&lt;&gt;INT(B26:AF26))+(B26:AF26&lt;=0),COLUMN(B26:AF26))))</f>
         <v>0</v>
       </c>
-      <c r="AJ26" s="181" cm="1">
+      <c r="AJ26" s="180" cm="1">
         <f t="array" ref="AJ26">SUMPRODUCT(--(B26:AF26=INT(B26:AF26)),--(B26:AF26&gt;0))/30*100%</f>
         <v>0</v>
       </c>
-      <c r="AK26" s="182">
+      <c r="AK26" s="181">
         <f t="shared" ref="AK26:AM26" si="23">RANK(AG26,AG$3:AG$53,0)</f>
-        <v>35</v>
-      </c>
-      <c r="AL26" s="182">
+        <v>40</v>
+      </c>
+      <c r="AL26" s="181">
         <f t="shared" si="23"/>
-        <v>35</v>
-      </c>
-      <c r="AM26" s="182">
+        <v>40</v>
+      </c>
+      <c r="AM26" s="181">
         <f t="shared" si="23"/>
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:39">
-      <c r="A27" s="178">
+      <c r="A27" s="183">
         <v>25</v>
       </c>
       <c r="B27" s="116"/>
@@ -10374,37 +10422,37 @@
       <c r="AD27" s="116"/>
       <c r="AE27" s="116"/>
       <c r="AF27" s="116"/>
-      <c r="AG27" s="179">
+      <c r="AG27" s="178">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH27" s="180" cm="1">
+      <c r="AH27" s="179" cm="1">
         <f t="array" ref="AH27">SUMPRODUCT(--(B27:AF27=INT(B27:AF27)),--(B27:AF27&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AI27" s="180" cm="1">
+      <c r="AI27" s="179" cm="1">
         <f t="array" ref="AI27">MAX(FREQUENCY(IF((B27:AF27=INT(B27:AF27))*(B27:AF27&gt;0),COLUMN(B27:AF27)),IF((B27:AF27&lt;&gt;INT(B27:AF27))+(B27:AF27&lt;=0),COLUMN(B27:AF27))))</f>
         <v>0</v>
       </c>
-      <c r="AJ27" s="181" cm="1">
+      <c r="AJ27" s="180" cm="1">
         <f t="array" ref="AJ27">SUMPRODUCT(--(B27:AF27=INT(B27:AF27)),--(B27:AF27&gt;0))/30*100%</f>
         <v>0</v>
       </c>
-      <c r="AK27" s="182">
+      <c r="AK27" s="181">
         <f t="shared" ref="AK27:AM27" si="24">RANK(AG27,AG$3:AG$53,0)</f>
-        <v>35</v>
-      </c>
-      <c r="AL27" s="182">
+        <v>40</v>
+      </c>
+      <c r="AL27" s="181">
         <f t="shared" si="24"/>
-        <v>35</v>
-      </c>
-      <c r="AM27" s="182">
+        <v>40</v>
+      </c>
+      <c r="AM27" s="181">
         <f t="shared" si="24"/>
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:39">
-      <c r="A28" s="183">
+      <c r="A28" s="182">
         <v>26</v>
       </c>
       <c r="B28" s="116"/>
@@ -10444,7 +10492,9 @@
       </c>
       <c r="W28" s="116"/>
       <c r="X28" s="116"/>
-      <c r="Y28" s="116"/>
+      <c r="Y28" s="116">
+        <v>1</v>
+      </c>
       <c r="Z28" s="116"/>
       <c r="AA28" s="116"/>
       <c r="AB28" s="116"/>
@@ -10452,37 +10502,37 @@
       <c r="AD28" s="116"/>
       <c r="AE28" s="116"/>
       <c r="AF28" s="116"/>
-      <c r="AG28" s="179">
+      <c r="AG28" s="178">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AH28" s="180" cm="1">
+        <v>8</v>
+      </c>
+      <c r="AH28" s="179" cm="1">
         <f t="array" ref="AH28">SUMPRODUCT(--(B28:AF28=INT(B28:AF28)),--(B28:AF28&gt;0))</f>
-        <v>7</v>
-      </c>
-      <c r="AI28" s="180" cm="1">
+        <v>8</v>
+      </c>
+      <c r="AI28" s="179" cm="1">
         <f t="array" ref="AI28">MAX(FREQUENCY(IF((B28:AF28=INT(B28:AF28))*(B28:AF28&gt;0),COLUMN(B28:AF28)),IF((B28:AF28&lt;&gt;INT(B28:AF28))+(B28:AF28&lt;=0),COLUMN(B28:AF28))))</f>
         <v>2</v>
       </c>
-      <c r="AJ28" s="181" cm="1">
+      <c r="AJ28" s="180" cm="1">
         <f t="array" ref="AJ28">SUMPRODUCT(--(B28:AF28=INT(B28:AF28)),--(B28:AF28&gt;0))/30*100%</f>
-        <v>0.233333333333333</v>
-      </c>
-      <c r="AK28" s="182">
+        <v>0.266666666666667</v>
+      </c>
+      <c r="AK28" s="181">
         <f t="shared" ref="AK28:AM28" si="25">RANK(AG28,AG$3:AG$53,0)</f>
         <v>10</v>
       </c>
-      <c r="AL28" s="182">
+      <c r="AL28" s="181">
         <f t="shared" si="25"/>
         <v>9</v>
       </c>
-      <c r="AM28" s="182">
+      <c r="AM28" s="181">
         <f t="shared" si="25"/>
         <v>13</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:39">
-      <c r="A29" s="183">
+      <c r="A29" s="182">
         <v>27</v>
       </c>
       <c r="B29" s="116"/>
@@ -10514,7 +10564,9 @@
       </c>
       <c r="W29" s="116"/>
       <c r="X29" s="116"/>
-      <c r="Y29" s="116"/>
+      <c r="Y29" s="116">
+        <v>1</v>
+      </c>
       <c r="Z29" s="116"/>
       <c r="AA29" s="116"/>
       <c r="AB29" s="116"/>
@@ -10522,37 +10574,37 @@
       <c r="AD29" s="116"/>
       <c r="AE29" s="116"/>
       <c r="AF29" s="116"/>
-      <c r="AG29" s="179">
+      <c r="AG29" s="178">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AH29" s="180" cm="1">
+        <v>4</v>
+      </c>
+      <c r="AH29" s="179" cm="1">
         <f t="array" ref="AH29">SUMPRODUCT(--(B29:AF29=INT(B29:AF29)),--(B29:AF29&gt;0))</f>
-        <v>3</v>
-      </c>
-      <c r="AI29" s="180" cm="1">
+        <v>4</v>
+      </c>
+      <c r="AI29" s="179" cm="1">
         <f t="array" ref="AI29">MAX(FREQUENCY(IF((B29:AF29=INT(B29:AF29))*(B29:AF29&gt;0),COLUMN(B29:AF29)),IF((B29:AF29&lt;&gt;INT(B29:AF29))+(B29:AF29&lt;=0),COLUMN(B29:AF29))))</f>
         <v>1</v>
       </c>
-      <c r="AJ29" s="181" cm="1">
+      <c r="AJ29" s="180" cm="1">
         <f t="array" ref="AJ29">SUMPRODUCT(--(B29:AF29=INT(B29:AF29)),--(B29:AF29&gt;0))/30*100%</f>
-        <v>0.1</v>
-      </c>
-      <c r="AK29" s="182">
+        <v>0.133333333333333</v>
+      </c>
+      <c r="AK29" s="181">
         <f t="shared" ref="AK29:AM29" si="26">RANK(AG29,AG$3:AG$53,0)</f>
-        <v>22</v>
-      </c>
-      <c r="AL29" s="182">
+        <v>20</v>
+      </c>
+      <c r="AL29" s="181">
         <f t="shared" si="26"/>
-        <v>21</v>
-      </c>
-      <c r="AM29" s="182">
+        <v>20</v>
+      </c>
+      <c r="AM29" s="181">
         <f t="shared" si="26"/>
         <v>18</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:39">
-      <c r="A30" s="183">
+      <c r="A30" s="182">
         <v>28</v>
       </c>
       <c r="B30" s="116">
@@ -10590,7 +10642,9 @@
       </c>
       <c r="W30" s="116"/>
       <c r="X30" s="116"/>
-      <c r="Y30" s="116"/>
+      <c r="Y30" s="116">
+        <v>1</v>
+      </c>
       <c r="Z30" s="116"/>
       <c r="AA30" s="116"/>
       <c r="AB30" s="116"/>
@@ -10598,37 +10652,37 @@
       <c r="AD30" s="116"/>
       <c r="AE30" s="116"/>
       <c r="AF30" s="116"/>
-      <c r="AG30" s="179">
+      <c r="AG30" s="178">
         <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AH30" s="179" cm="1">
+        <f t="array" ref="AH30">SUMPRODUCT(--(B30:AF30=INT(B30:AF30)),--(B30:AF30&gt;0))</f>
         <v>7</v>
       </c>
-      <c r="AH30" s="180" cm="1">
-        <f t="array" ref="AH30">SUMPRODUCT(--(B30:AF30=INT(B30:AF30)),--(B30:AF30&gt;0))</f>
-        <v>6</v>
-      </c>
-      <c r="AI30" s="180" cm="1">
+      <c r="AI30" s="179" cm="1">
         <f t="array" ref="AI30">MAX(FREQUENCY(IF((B30:AF30=INT(B30:AF30))*(B30:AF30&gt;0),COLUMN(B30:AF30)),IF((B30:AF30&lt;&gt;INT(B30:AF30))+(B30:AF30&lt;=0),COLUMN(B30:AF30))))</f>
         <v>4</v>
       </c>
-      <c r="AJ30" s="181" cm="1">
+      <c r="AJ30" s="180" cm="1">
         <f t="array" ref="AJ30">SUMPRODUCT(--(B30:AF30=INT(B30:AF30)),--(B30:AF30&gt;0))/30*100%</f>
-        <v>0.2</v>
-      </c>
-      <c r="AK30" s="182">
+        <v>0.233333333333333</v>
+      </c>
+      <c r="AK30" s="181">
         <f t="shared" ref="AK30:AM30" si="27">RANK(AG30,AG$3:AG$53,0)</f>
         <v>10</v>
       </c>
-      <c r="AL30" s="182">
+      <c r="AL30" s="181">
         <f t="shared" si="27"/>
         <v>12</v>
       </c>
-      <c r="AM30" s="182">
+      <c r="AM30" s="181">
         <f t="shared" si="27"/>
         <v>6</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:39">
-      <c r="A31" s="183">
+      <c r="A31" s="182">
         <v>29</v>
       </c>
       <c r="B31" s="116">
@@ -10666,7 +10720,9 @@
       <c r="V31" s="116"/>
       <c r="W31" s="116"/>
       <c r="X31" s="116"/>
-      <c r="Y31" s="116"/>
+      <c r="Y31" s="116">
+        <v>1</v>
+      </c>
       <c r="Z31" s="116"/>
       <c r="AA31" s="116"/>
       <c r="AB31" s="116"/>
@@ -10674,37 +10730,37 @@
       <c r="AD31" s="116"/>
       <c r="AE31" s="116"/>
       <c r="AF31" s="116"/>
-      <c r="AG31" s="179">
+      <c r="AG31" s="178">
         <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AH31" s="179" cm="1">
+        <f t="array" ref="AH31">SUMPRODUCT(--(B31:AF31=INT(B31:AF31)),--(B31:AF31&gt;0))</f>
         <v>7</v>
       </c>
-      <c r="AH31" s="180" cm="1">
-        <f t="array" ref="AH31">SUMPRODUCT(--(B31:AF31=INT(B31:AF31)),--(B31:AF31&gt;0))</f>
-        <v>6</v>
-      </c>
-      <c r="AI31" s="180" cm="1">
+      <c r="AI31" s="179" cm="1">
         <f t="array" ref="AI31">MAX(FREQUENCY(IF((B31:AF31=INT(B31:AF31))*(B31:AF31&gt;0),COLUMN(B31:AF31)),IF((B31:AF31&lt;&gt;INT(B31:AF31))+(B31:AF31&lt;=0),COLUMN(B31:AF31))))</f>
         <v>2</v>
       </c>
-      <c r="AJ31" s="181" cm="1">
+      <c r="AJ31" s="180" cm="1">
         <f t="array" ref="AJ31">SUMPRODUCT(--(B31:AF31=INT(B31:AF31)),--(B31:AF31&gt;0))/30*100%</f>
-        <v>0.2</v>
-      </c>
-      <c r="AK31" s="182">
+        <v>0.233333333333333</v>
+      </c>
+      <c r="AK31" s="181">
         <f t="shared" ref="AK31:AM31" si="28">RANK(AG31,AG$3:AG$53,0)</f>
         <v>10</v>
       </c>
-      <c r="AL31" s="182">
+      <c r="AL31" s="181">
         <f t="shared" si="28"/>
         <v>12</v>
       </c>
-      <c r="AM31" s="182">
+      <c r="AM31" s="181">
         <f t="shared" si="28"/>
         <v>13</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:39">
-      <c r="A32" s="183">
+      <c r="A32" s="182">
         <v>30</v>
       </c>
       <c r="B32" s="116"/>
@@ -10746,7 +10802,9 @@
       <c r="V32" s="116"/>
       <c r="W32" s="116"/>
       <c r="X32" s="116"/>
-      <c r="Y32" s="116"/>
+      <c r="Y32" s="116">
+        <v>1</v>
+      </c>
       <c r="Z32" s="116"/>
       <c r="AA32" s="116"/>
       <c r="AB32" s="116"/>
@@ -10754,37 +10812,37 @@
       <c r="AD32" s="116"/>
       <c r="AE32" s="116"/>
       <c r="AF32" s="116"/>
-      <c r="AG32" s="179">
+      <c r="AG32" s="178">
         <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AH32" s="179" cm="1">
+        <f t="array" ref="AH32">SUMPRODUCT(--(B32:AF32=INT(B32:AF32)),--(B32:AF32&gt;0))</f>
         <v>9</v>
       </c>
-      <c r="AH32" s="180" cm="1">
-        <f t="array" ref="AH32">SUMPRODUCT(--(B32:AF32=INT(B32:AF32)),--(B32:AF32&gt;0))</f>
-        <v>8</v>
-      </c>
-      <c r="AI32" s="180" cm="1">
+      <c r="AI32" s="179" cm="1">
         <f t="array" ref="AI32">MAX(FREQUENCY(IF((B32:AF32=INT(B32:AF32))*(B32:AF32&gt;0),COLUMN(B32:AF32)),IF((B32:AF32&lt;&gt;INT(B32:AF32))+(B32:AF32&lt;=0),COLUMN(B32:AF32))))</f>
         <v>3</v>
       </c>
-      <c r="AJ32" s="181" cm="1">
+      <c r="AJ32" s="180" cm="1">
         <f t="array" ref="AJ32">SUMPRODUCT(--(B32:AF32=INT(B32:AF32)),--(B32:AF32&gt;0))/30*100%</f>
-        <v>0.266666666666667</v>
-      </c>
-      <c r="AK32" s="182">
+        <v>0.3</v>
+      </c>
+      <c r="AK32" s="181">
         <f t="shared" ref="AK32:AM32" si="29">RANK(AG32,AG$3:AG$53,0)</f>
         <v>7</v>
       </c>
-      <c r="AL32" s="182">
+      <c r="AL32" s="181">
         <f t="shared" si="29"/>
         <v>7</v>
       </c>
-      <c r="AM32" s="182">
+      <c r="AM32" s="181">
         <f t="shared" si="29"/>
         <v>8</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:39">
-      <c r="A33" s="183">
+      <c r="A33" s="182">
         <v>31</v>
       </c>
       <c r="B33" s="116">
@@ -10814,7 +10872,9 @@
       <c r="V33" s="116"/>
       <c r="W33" s="116"/>
       <c r="X33" s="116"/>
-      <c r="Y33" s="116"/>
+      <c r="Y33" s="116">
+        <v>1</v>
+      </c>
       <c r="Z33" s="116"/>
       <c r="AA33" s="116"/>
       <c r="AB33" s="116"/>
@@ -10822,37 +10882,37 @@
       <c r="AD33" s="116"/>
       <c r="AE33" s="116"/>
       <c r="AF33" s="116"/>
-      <c r="AG33" s="179">
+      <c r="AG33" s="178">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AH33" s="180" cm="1">
+        <v>3</v>
+      </c>
+      <c r="AH33" s="179" cm="1">
         <f t="array" ref="AH33">SUMPRODUCT(--(B33:AF33=INT(B33:AF33)),--(B33:AF33&gt;0))</f>
-        <v>2</v>
-      </c>
-      <c r="AI33" s="180" cm="1">
+        <v>3</v>
+      </c>
+      <c r="AI33" s="179" cm="1">
         <f t="array" ref="AI33">MAX(FREQUENCY(IF((B33:AF33=INT(B33:AF33))*(B33:AF33&gt;0),COLUMN(B33:AF33)),IF((B33:AF33&lt;&gt;INT(B33:AF33))+(B33:AF33&lt;=0),COLUMN(B33:AF33))))</f>
         <v>1</v>
       </c>
-      <c r="AJ33" s="181" cm="1">
+      <c r="AJ33" s="180" cm="1">
         <f t="array" ref="AJ33">SUMPRODUCT(--(B33:AF33=INT(B33:AF33)),--(B33:AF33&gt;0))/30*100%</f>
-        <v>0.0666666666666667</v>
-      </c>
-      <c r="AK33" s="182">
+        <v>0.1</v>
+      </c>
+      <c r="AK33" s="181">
         <f t="shared" ref="AK33:AM33" si="30">RANK(AG33,AG$3:AG$53,0)</f>
-        <v>24</v>
-      </c>
-      <c r="AL33" s="182">
+        <v>23</v>
+      </c>
+      <c r="AL33" s="181">
         <f t="shared" si="30"/>
-        <v>24</v>
-      </c>
-      <c r="AM33" s="182">
+        <v>22</v>
+      </c>
+      <c r="AM33" s="181">
         <f t="shared" si="30"/>
         <v>18</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:39">
-      <c r="A34" s="178">
+      <c r="A34" s="183">
         <v>32</v>
       </c>
       <c r="B34" s="116"/>
@@ -10886,37 +10946,37 @@
       <c r="AD34" s="116"/>
       <c r="AE34" s="116"/>
       <c r="AF34" s="116"/>
-      <c r="AG34" s="179">
+      <c r="AG34" s="178">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH34" s="180" cm="1">
+      <c r="AH34" s="179" cm="1">
         <f t="array" ref="AH34">SUMPRODUCT(--(B34:AF34=INT(B34:AF34)),--(B34:AF34&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AI34" s="180" cm="1">
+      <c r="AI34" s="179" cm="1">
         <f t="array" ref="AI34">MAX(FREQUENCY(IF((B34:AF34=INT(B34:AF34))*(B34:AF34&gt;0),COLUMN(B34:AF34)),IF((B34:AF34&lt;&gt;INT(B34:AF34))+(B34:AF34&lt;=0),COLUMN(B34:AF34))))</f>
         <v>0</v>
       </c>
-      <c r="AJ34" s="181" cm="1">
+      <c r="AJ34" s="180" cm="1">
         <f t="array" ref="AJ34">SUMPRODUCT(--(B34:AF34=INT(B34:AF34)),--(B34:AF34&gt;0))/30*100%</f>
         <v>0</v>
       </c>
-      <c r="AK34" s="182">
+      <c r="AK34" s="181">
         <f t="shared" ref="AK34:AM34" si="31">RANK(AG34,AG$3:AG$53,0)</f>
-        <v>35</v>
-      </c>
-      <c r="AL34" s="182">
+        <v>40</v>
+      </c>
+      <c r="AL34" s="181">
         <f t="shared" si="31"/>
-        <v>35</v>
-      </c>
-      <c r="AM34" s="182">
+        <v>40</v>
+      </c>
+      <c r="AM34" s="181">
         <f t="shared" si="31"/>
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:39">
-      <c r="A35" s="178">
+      <c r="A35" s="183">
         <v>33</v>
       </c>
       <c r="B35" s="116"/>
@@ -10950,37 +11010,37 @@
       <c r="AD35" s="116"/>
       <c r="AE35" s="116"/>
       <c r="AF35" s="116"/>
-      <c r="AG35" s="179">
+      <c r="AG35" s="178">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH35" s="180" cm="1">
+      <c r="AH35" s="179" cm="1">
         <f t="array" ref="AH35">SUMPRODUCT(--(B35:AF35=INT(B35:AF35)),--(B35:AF35&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AI35" s="180" cm="1">
+      <c r="AI35" s="179" cm="1">
         <f t="array" ref="AI35">MAX(FREQUENCY(IF((B35:AF35=INT(B35:AF35))*(B35:AF35&gt;0),COLUMN(B35:AF35)),IF((B35:AF35&lt;&gt;INT(B35:AF35))+(B35:AF35&lt;=0),COLUMN(B35:AF35))))</f>
         <v>0</v>
       </c>
-      <c r="AJ35" s="181" cm="1">
+      <c r="AJ35" s="180" cm="1">
         <f t="array" ref="AJ35">SUMPRODUCT(--(B35:AF35=INT(B35:AF35)),--(B35:AF35&gt;0))/30*100%</f>
         <v>0</v>
       </c>
-      <c r="AK35" s="182">
+      <c r="AK35" s="181">
         <f t="shared" ref="AK35:AM35" si="32">RANK(AG35,AG$3:AG$53,0)</f>
-        <v>35</v>
-      </c>
-      <c r="AL35" s="182">
+        <v>40</v>
+      </c>
+      <c r="AL35" s="181">
         <f t="shared" si="32"/>
-        <v>35</v>
-      </c>
-      <c r="AM35" s="182">
+        <v>40</v>
+      </c>
+      <c r="AM35" s="181">
         <f t="shared" si="32"/>
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:39">
-      <c r="A36" s="178">
+      <c r="A36" s="116">
         <v>34</v>
       </c>
       <c r="B36" s="116"/>
@@ -11006,7 +11066,9 @@
       <c r="V36" s="116"/>
       <c r="W36" s="116"/>
       <c r="X36" s="116"/>
-      <c r="Y36" s="116"/>
+      <c r="Y36" s="116">
+        <v>1</v>
+      </c>
       <c r="Z36" s="116"/>
       <c r="AA36" s="116"/>
       <c r="AB36" s="116"/>
@@ -11014,37 +11076,37 @@
       <c r="AD36" s="116"/>
       <c r="AE36" s="116"/>
       <c r="AF36" s="116"/>
-      <c r="AG36" s="179">
+      <c r="AG36" s="178">
         <f t="shared" ref="AG36:AG53" si="33">SUM(B36:AF36)</f>
-        <v>0</v>
-      </c>
-      <c r="AH36" s="180" cm="1">
+        <v>1</v>
+      </c>
+      <c r="AH36" s="179" cm="1">
         <f t="array" ref="AH36">SUMPRODUCT(--(B36:AF36=INT(B36:AF36)),--(B36:AF36&gt;0))</f>
-        <v>0</v>
-      </c>
-      <c r="AI36" s="180" cm="1">
+        <v>1</v>
+      </c>
+      <c r="AI36" s="179" cm="1">
         <f t="array" ref="AI36">MAX(FREQUENCY(IF((B36:AF36=INT(B36:AF36))*(B36:AF36&gt;0),COLUMN(B36:AF36)),IF((B36:AF36&lt;&gt;INT(B36:AF36))+(B36:AF36&lt;=0),COLUMN(B36:AF36))))</f>
-        <v>0</v>
-      </c>
-      <c r="AJ36" s="181" cm="1">
+        <v>1</v>
+      </c>
+      <c r="AJ36" s="180" cm="1">
         <f t="array" ref="AJ36">SUMPRODUCT(--(B36:AF36=INT(B36:AF36)),--(B36:AF36&gt;0))/30*100%</f>
-        <v>0</v>
-      </c>
-      <c r="AK36" s="182">
+        <v>0.0333333333333333</v>
+      </c>
+      <c r="AK36" s="181">
         <f t="shared" ref="AK36:AM36" si="34">RANK(AG36,AG$3:AG$53,0)</f>
-        <v>35</v>
-      </c>
-      <c r="AL36" s="182">
+        <v>34</v>
+      </c>
+      <c r="AL36" s="181">
         <f t="shared" si="34"/>
-        <v>35</v>
-      </c>
-      <c r="AM36" s="182">
+        <v>34</v>
+      </c>
+      <c r="AM36" s="181">
         <f t="shared" si="34"/>
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:39">
-      <c r="A37" s="183">
+      <c r="A37" s="182">
         <v>35</v>
       </c>
       <c r="B37" s="116"/>
@@ -11090,37 +11152,37 @@
       <c r="AD37" s="116"/>
       <c r="AE37" s="116"/>
       <c r="AF37" s="116"/>
-      <c r="AG37" s="179">
+      <c r="AG37" s="178">
         <f t="shared" si="33"/>
         <v>7</v>
       </c>
-      <c r="AH37" s="180" cm="1">
+      <c r="AH37" s="179" cm="1">
         <f t="array" ref="AH37">SUMPRODUCT(--(B37:AF37=INT(B37:AF37)),--(B37:AF37&gt;0))</f>
         <v>6</v>
       </c>
-      <c r="AI37" s="180" cm="1">
+      <c r="AI37" s="179" cm="1">
         <f t="array" ref="AI37">MAX(FREQUENCY(IF((B37:AF37=INT(B37:AF37))*(B37:AF37&gt;0),COLUMN(B37:AF37)),IF((B37:AF37&lt;&gt;INT(B37:AF37))+(B37:AF37&lt;=0),COLUMN(B37:AF37))))</f>
         <v>3</v>
       </c>
-      <c r="AJ37" s="181" cm="1">
+      <c r="AJ37" s="180" cm="1">
         <f t="array" ref="AJ37">SUMPRODUCT(--(B37:AF37=INT(B37:AF37)),--(B37:AF37&gt;0))/30*100%</f>
         <v>0.2</v>
       </c>
-      <c r="AK37" s="182">
+      <c r="AK37" s="181">
         <f t="shared" ref="AK37:AM37" si="35">RANK(AG37,AG$3:AG$53,0)</f>
-        <v>10</v>
-      </c>
-      <c r="AL37" s="182">
+        <v>16</v>
+      </c>
+      <c r="AL37" s="181">
         <f t="shared" si="35"/>
-        <v>12</v>
-      </c>
-      <c r="AM37" s="182">
+        <v>16</v>
+      </c>
+      <c r="AM37" s="181">
         <f t="shared" si="35"/>
         <v>8</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="1:39">
-      <c r="A38" s="183">
+      <c r="A38" s="182">
         <v>36</v>
       </c>
       <c r="B38" s="116"/>
@@ -11148,7 +11210,9 @@
       <c r="V38" s="116"/>
       <c r="W38" s="116"/>
       <c r="X38" s="116"/>
-      <c r="Y38" s="116"/>
+      <c r="Y38" s="116">
+        <v>1</v>
+      </c>
       <c r="Z38" s="116"/>
       <c r="AA38" s="116"/>
       <c r="AB38" s="116"/>
@@ -11156,31 +11220,31 @@
       <c r="AD38" s="116"/>
       <c r="AE38" s="116"/>
       <c r="AF38" s="116"/>
-      <c r="AG38" s="179">
+      <c r="AG38" s="178">
         <f t="shared" si="33"/>
+        <v>3</v>
+      </c>
+      <c r="AH38" s="179" cm="1">
+        <f t="array" ref="AH38">SUMPRODUCT(--(B38:AF38=INT(B38:AF38)),--(B38:AF38&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="AH38" s="180" cm="1">
-        <f t="array" ref="AH38">SUMPRODUCT(--(B38:AF38=INT(B38:AF38)),--(B38:AF38&gt;0))</f>
-        <v>1</v>
-      </c>
-      <c r="AI38" s="180" cm="1">
+      <c r="AI38" s="179" cm="1">
         <f t="array" ref="AI38">MAX(FREQUENCY(IF((B38:AF38=INT(B38:AF38))*(B38:AF38&gt;0),COLUMN(B38:AF38)),IF((B38:AF38&lt;&gt;INT(B38:AF38))+(B38:AF38&lt;=0),COLUMN(B38:AF38))))</f>
         <v>1</v>
       </c>
-      <c r="AJ38" s="181" cm="1">
+      <c r="AJ38" s="180" cm="1">
         <f t="array" ref="AJ38">SUMPRODUCT(--(B38:AF38=INT(B38:AF38)),--(B38:AF38&gt;0))/30*100%</f>
-        <v>0.0333333333333333</v>
-      </c>
-      <c r="AK38" s="182">
+        <v>0.0666666666666667</v>
+      </c>
+      <c r="AK38" s="181">
         <f t="shared" ref="AK38:AM38" si="36">RANK(AG38,AG$3:AG$53,0)</f>
-        <v>24</v>
-      </c>
-      <c r="AL38" s="182">
+        <v>23</v>
+      </c>
+      <c r="AL38" s="181">
         <f t="shared" si="36"/>
-        <v>31</v>
-      </c>
-      <c r="AM38" s="182">
+        <v>27</v>
+      </c>
+      <c r="AM38" s="181">
         <f t="shared" si="36"/>
         <v>18</v>
       </c>
@@ -11220,37 +11284,37 @@
       <c r="AD39" s="172"/>
       <c r="AE39" s="172"/>
       <c r="AF39" s="172"/>
-      <c r="AG39" s="179">
+      <c r="AG39" s="178">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="AH39" s="180" cm="1">
+      <c r="AH39" s="179" cm="1">
         <f t="array" ref="AH39">SUMPRODUCT(--(B39:AF39=INT(B39:AF39)),--(B39:AF39&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AI39" s="180" cm="1">
+      <c r="AI39" s="179" cm="1">
         <f t="array" ref="AI39">MAX(FREQUENCY(IF((B39:AF39=INT(B39:AF39))*(B39:AF39&gt;0),COLUMN(B39:AF39)),IF((B39:AF39&lt;&gt;INT(B39:AF39))+(B39:AF39&lt;=0),COLUMN(B39:AF39))))</f>
         <v>0</v>
       </c>
-      <c r="AJ39" s="181" cm="1">
+      <c r="AJ39" s="180" cm="1">
         <f t="array" ref="AJ39">SUMPRODUCT(--(B39:AF39=INT(B39:AF39)),--(B39:AF39&gt;0))/30*100%</f>
         <v>0</v>
       </c>
       <c r="AK39" s="184">
         <f t="shared" ref="AK39:AM39" si="37">RANK(AG39,AG$3:AG$53,0)</f>
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="AL39" s="184">
         <f t="shared" si="37"/>
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="AM39" s="184">
         <f t="shared" si="37"/>
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:39">
-      <c r="A40" s="183">
+      <c r="A40" s="182">
         <v>38</v>
       </c>
       <c r="B40" s="116"/>
@@ -11306,7 +11370,9 @@
       <c r="X40" s="116">
         <v>1</v>
       </c>
-      <c r="Y40" s="116"/>
+      <c r="Y40" s="116">
+        <v>1</v>
+      </c>
       <c r="Z40" s="116"/>
       <c r="AA40" s="116"/>
       <c r="AB40" s="116"/>
@@ -11314,37 +11380,37 @@
       <c r="AD40" s="116"/>
       <c r="AE40" s="116"/>
       <c r="AF40" s="116"/>
-      <c r="AG40" s="179">
+      <c r="AG40" s="178">
         <f t="shared" si="33"/>
-        <v>17</v>
-      </c>
-      <c r="AH40" s="180" cm="1">
+        <v>18</v>
+      </c>
+      <c r="AH40" s="179" cm="1">
         <f t="array" ref="AH40">SUMPRODUCT(--(B40:AF40=INT(B40:AF40)),--(B40:AF40&gt;0))</f>
-        <v>15</v>
-      </c>
-      <c r="AI40" s="180" cm="1">
+        <v>16</v>
+      </c>
+      <c r="AI40" s="179" cm="1">
         <f t="array" ref="AI40">MAX(FREQUENCY(IF((B40:AF40=INT(B40:AF40))*(B40:AF40&gt;0),COLUMN(B40:AF40)),IF((B40:AF40&lt;&gt;INT(B40:AF40))+(B40:AF40&lt;=0),COLUMN(B40:AF40))))</f>
-        <v>8</v>
-      </c>
-      <c r="AJ40" s="181" cm="1">
+        <v>9</v>
+      </c>
+      <c r="AJ40" s="180" cm="1">
         <f t="array" ref="AJ40">SUMPRODUCT(--(B40:AF40=INT(B40:AF40)),--(B40:AF40&gt;0))/30*100%</f>
-        <v>0.5</v>
-      </c>
-      <c r="AK40" s="182">
+        <v>0.533333333333333</v>
+      </c>
+      <c r="AK40" s="181">
         <f t="shared" ref="AK40:AM40" si="38">RANK(AG40,AG$3:AG$53,0)</f>
         <v>2</v>
       </c>
-      <c r="AL40" s="182">
+      <c r="AL40" s="181">
         <f t="shared" si="38"/>
-        <v>3</v>
-      </c>
-      <c r="AM40" s="182">
+        <v>2</v>
+      </c>
+      <c r="AM40" s="181">
         <f t="shared" si="38"/>
         <v>1</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:39">
-      <c r="A41" s="183">
+      <c r="A41" s="182">
         <v>39</v>
       </c>
       <c r="B41" s="116">
@@ -11380,7 +11446,9 @@
         <v>1</v>
       </c>
       <c r="X41" s="116"/>
-      <c r="Y41" s="116"/>
+      <c r="Y41" s="116">
+        <v>2</v>
+      </c>
       <c r="Z41" s="116"/>
       <c r="AA41" s="116"/>
       <c r="AB41" s="116"/>
@@ -11388,37 +11456,37 @@
       <c r="AD41" s="116"/>
       <c r="AE41" s="116"/>
       <c r="AF41" s="116"/>
-      <c r="AG41" s="179">
+      <c r="AG41" s="178">
         <f t="shared" si="33"/>
+        <v>8</v>
+      </c>
+      <c r="AH41" s="179" cm="1">
+        <f t="array" ref="AH41">SUMPRODUCT(--(B41:AF41=INT(B41:AF41)),--(B41:AF41&gt;0))</f>
         <v>6</v>
       </c>
-      <c r="AH41" s="180" cm="1">
-        <f t="array" ref="AH41">SUMPRODUCT(--(B41:AF41=INT(B41:AF41)),--(B41:AF41&gt;0))</f>
-        <v>5</v>
-      </c>
-      <c r="AI41" s="180" cm="1">
+      <c r="AI41" s="179" cm="1">
         <f t="array" ref="AI41">MAX(FREQUENCY(IF((B41:AF41=INT(B41:AF41))*(B41:AF41&gt;0),COLUMN(B41:AF41)),IF((B41:AF41&lt;&gt;INT(B41:AF41))+(B41:AF41&lt;=0),COLUMN(B41:AF41))))</f>
         <v>1</v>
       </c>
-      <c r="AJ41" s="181" cm="1">
+      <c r="AJ41" s="180" cm="1">
         <f t="array" ref="AJ41">SUMPRODUCT(--(B41:AF41=INT(B41:AF41)),--(B41:AF41&gt;0))/30*100%</f>
-        <v>0.166666666666667</v>
-      </c>
-      <c r="AK41" s="182">
+        <v>0.2</v>
+      </c>
+      <c r="AK41" s="181">
         <f t="shared" ref="AK41:AM41" si="39">RANK(AG41,AG$3:AG$53,0)</f>
+        <v>10</v>
+      </c>
+      <c r="AL41" s="181">
+        <f t="shared" si="39"/>
         <v>16</v>
       </c>
-      <c r="AL41" s="182">
-        <f t="shared" si="39"/>
-        <v>17</v>
-      </c>
-      <c r="AM41" s="182">
+      <c r="AM41" s="181">
         <f t="shared" si="39"/>
         <v>18</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:39">
-      <c r="A42" s="183">
+      <c r="A42" s="182">
         <v>40</v>
       </c>
       <c r="B42" s="116"/>
@@ -11464,7 +11532,9 @@
       </c>
       <c r="W42" s="116"/>
       <c r="X42" s="116"/>
-      <c r="Y42" s="116"/>
+      <c r="Y42" s="116">
+        <v>1</v>
+      </c>
       <c r="Z42" s="116"/>
       <c r="AA42" s="116"/>
       <c r="AB42" s="116"/>
@@ -11472,37 +11542,37 @@
       <c r="AD42" s="116"/>
       <c r="AE42" s="116"/>
       <c r="AF42" s="116"/>
-      <c r="AG42" s="179">
+      <c r="AG42" s="178">
         <f t="shared" si="33"/>
-        <v>12</v>
-      </c>
-      <c r="AH42" s="180" cm="1">
+        <v>13</v>
+      </c>
+      <c r="AH42" s="179" cm="1">
         <f t="array" ref="AH42">SUMPRODUCT(--(B42:AF42=INT(B42:AF42)),--(B42:AF42&gt;0))</f>
-        <v>10</v>
-      </c>
-      <c r="AI42" s="180" cm="1">
+        <v>11</v>
+      </c>
+      <c r="AI42" s="179" cm="1">
         <f t="array" ref="AI42">MAX(FREQUENCY(IF((B42:AF42=INT(B42:AF42))*(B42:AF42&gt;0),COLUMN(B42:AF42)),IF((B42:AF42&lt;&gt;INT(B42:AF42))+(B42:AF42&lt;=0),COLUMN(B42:AF42))))</f>
         <v>5</v>
       </c>
-      <c r="AJ42" s="181" cm="1">
+      <c r="AJ42" s="180" cm="1">
         <f t="array" ref="AJ42">SUMPRODUCT(--(B42:AF42=INT(B42:AF42)),--(B42:AF42&gt;0))/30*100%</f>
-        <v>0.333333333333333</v>
-      </c>
-      <c r="AK42" s="182">
+        <v>0.366666666666667</v>
+      </c>
+      <c r="AK42" s="181">
         <f t="shared" ref="AK42:AM42" si="40">RANK(AG42,AG$3:AG$53,0)</f>
         <v>5</v>
       </c>
-      <c r="AL42" s="182">
+      <c r="AL42" s="181">
         <f t="shared" si="40"/>
         <v>5</v>
       </c>
-      <c r="AM42" s="182">
+      <c r="AM42" s="181">
         <f t="shared" si="40"/>
         <v>3</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:39">
-      <c r="A43" s="178">
+      <c r="A43" s="183">
         <v>41</v>
       </c>
       <c r="B43" s="116"/>
@@ -11536,37 +11606,37 @@
       <c r="AD43" s="116"/>
       <c r="AE43" s="116"/>
       <c r="AF43" s="116"/>
-      <c r="AG43" s="179">
+      <c r="AG43" s="178">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="AH43" s="180" cm="1">
+      <c r="AH43" s="179" cm="1">
         <f t="array" ref="AH43">SUMPRODUCT(--(B43:AF43=INT(B43:AF43)),--(B43:AF43&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AI43" s="180" cm="1">
+      <c r="AI43" s="179" cm="1">
         <f t="array" ref="AI43">MAX(FREQUENCY(IF((B43:AF43=INT(B43:AF43))*(B43:AF43&gt;0),COLUMN(B43:AF43)),IF((B43:AF43&lt;&gt;INT(B43:AF43))+(B43:AF43&lt;=0),COLUMN(B43:AF43))))</f>
         <v>0</v>
       </c>
-      <c r="AJ43" s="181" cm="1">
+      <c r="AJ43" s="180" cm="1">
         <f t="array" ref="AJ43">SUMPRODUCT(--(B43:AF43=INT(B43:AF43)),--(B43:AF43&gt;0))/30*100%</f>
         <v>0</v>
       </c>
-      <c r="AK43" s="182">
+      <c r="AK43" s="181">
         <f t="shared" ref="AK43:AM43" si="41">RANK(AG43,AG$3:AG$53,0)</f>
-        <v>35</v>
-      </c>
-      <c r="AL43" s="182">
+        <v>40</v>
+      </c>
+      <c r="AL43" s="181">
         <f t="shared" si="41"/>
-        <v>35</v>
-      </c>
-      <c r="AM43" s="182">
+        <v>40</v>
+      </c>
+      <c r="AM43" s="181">
         <f t="shared" si="41"/>
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="1:39">
-      <c r="A44" s="183">
+      <c r="A44" s="182">
         <v>42</v>
       </c>
       <c r="B44" s="116">
@@ -11616,7 +11686,9 @@
       <c r="X44" s="116">
         <v>1</v>
       </c>
-      <c r="Y44" s="116"/>
+      <c r="Y44" s="116">
+        <v>2</v>
+      </c>
       <c r="Z44" s="116"/>
       <c r="AA44" s="116"/>
       <c r="AB44" s="116"/>
@@ -11624,37 +11696,37 @@
       <c r="AD44" s="116"/>
       <c r="AE44" s="116"/>
       <c r="AF44" s="116"/>
-      <c r="AG44" s="179">
+      <c r="AG44" s="178">
         <f t="shared" si="33"/>
-        <v>14</v>
-      </c>
-      <c r="AH44" s="180" cm="1">
+        <v>16</v>
+      </c>
+      <c r="AH44" s="179" cm="1">
         <f t="array" ref="AH44">SUMPRODUCT(--(B44:AF44=INT(B44:AF44)),--(B44:AF44&gt;0))</f>
-        <v>12</v>
-      </c>
-      <c r="AI44" s="180" cm="1">
+        <v>13</v>
+      </c>
+      <c r="AI44" s="179" cm="1">
         <f t="array" ref="AI44">MAX(FREQUENCY(IF((B44:AF44=INT(B44:AF44))*(B44:AF44&gt;0),COLUMN(B44:AF44)),IF((B44:AF44&lt;&gt;INT(B44:AF44))+(B44:AF44&lt;=0),COLUMN(B44:AF44))))</f>
         <v>5</v>
       </c>
-      <c r="AJ44" s="181" cm="1">
+      <c r="AJ44" s="180" cm="1">
         <f t="array" ref="AJ44">SUMPRODUCT(--(B44:AF44=INT(B44:AF44)),--(B44:AF44&gt;0))/30*100%</f>
-        <v>0.4</v>
-      </c>
-      <c r="AK44" s="182">
+        <v>0.433333333333333</v>
+      </c>
+      <c r="AK44" s="181">
         <f t="shared" ref="AK44:AM44" si="42">RANK(AG44,AG$3:AG$53,0)</f>
-        <v>4</v>
-      </c>
-      <c r="AL44" s="182">
+        <v>3</v>
+      </c>
+      <c r="AL44" s="181">
         <f t="shared" si="42"/>
         <v>4</v>
       </c>
-      <c r="AM44" s="182">
+      <c r="AM44" s="181">
         <f t="shared" si="42"/>
         <v>3</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:39">
-      <c r="A45" s="178">
+      <c r="A45" s="183">
         <v>43</v>
       </c>
       <c r="B45" s="116"/>
@@ -11688,37 +11760,37 @@
       <c r="AD45" s="116"/>
       <c r="AE45" s="116"/>
       <c r="AF45" s="116"/>
-      <c r="AG45" s="179">
+      <c r="AG45" s="178">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="AH45" s="180" cm="1">
+      <c r="AH45" s="179" cm="1">
         <f t="array" ref="AH45">SUMPRODUCT(--(B45:AF45=INT(B45:AF45)),--(B45:AF45&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AI45" s="180" cm="1">
+      <c r="AI45" s="179" cm="1">
         <f t="array" ref="AI45">MAX(FREQUENCY(IF((B45:AF45=INT(B45:AF45))*(B45:AF45&gt;0),COLUMN(B45:AF45)),IF((B45:AF45&lt;&gt;INT(B45:AF45))+(B45:AF45&lt;=0),COLUMN(B45:AF45))))</f>
         <v>0</v>
       </c>
-      <c r="AJ45" s="181" cm="1">
+      <c r="AJ45" s="180" cm="1">
         <f t="array" ref="AJ45">SUMPRODUCT(--(B45:AF45=INT(B45:AF45)),--(B45:AF45&gt;0))/30*100%</f>
         <v>0</v>
       </c>
-      <c r="AK45" s="182">
+      <c r="AK45" s="181">
         <f t="shared" ref="AK45:AM45" si="43">RANK(AG45,AG$3:AG$53,0)</f>
-        <v>35</v>
-      </c>
-      <c r="AL45" s="182">
+        <v>40</v>
+      </c>
+      <c r="AL45" s="181">
         <f t="shared" si="43"/>
-        <v>35</v>
-      </c>
-      <c r="AM45" s="182">
+        <v>40</v>
+      </c>
+      <c r="AM45" s="181">
         <f t="shared" si="43"/>
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="1:39">
-      <c r="A46" s="183">
+      <c r="A46" s="182">
         <v>44</v>
       </c>
       <c r="B46" s="116">
@@ -11778,7 +11850,9 @@
       </c>
       <c r="W46" s="116"/>
       <c r="X46" s="116"/>
-      <c r="Y46" s="116"/>
+      <c r="Y46" s="116">
+        <v>2</v>
+      </c>
       <c r="Z46" s="116"/>
       <c r="AA46" s="116"/>
       <c r="AB46" s="116"/>
@@ -11786,37 +11860,37 @@
       <c r="AD46" s="116"/>
       <c r="AE46" s="116"/>
       <c r="AF46" s="116"/>
-      <c r="AG46" s="179">
+      <c r="AG46" s="178">
         <f t="shared" si="33"/>
-        <v>25</v>
-      </c>
-      <c r="AH46" s="180" cm="1">
+        <v>27</v>
+      </c>
+      <c r="AH46" s="179" cm="1">
         <f t="array" ref="AH46">SUMPRODUCT(--(B46:AF46=INT(B46:AF46)),--(B46:AF46&gt;0))</f>
-        <v>17</v>
-      </c>
-      <c r="AI46" s="180" cm="1">
+        <v>18</v>
+      </c>
+      <c r="AI46" s="179" cm="1">
         <f t="array" ref="AI46">MAX(FREQUENCY(IF((B46:AF46=INT(B46:AF46))*(B46:AF46&gt;0),COLUMN(B46:AF46)),IF((B46:AF46&lt;&gt;INT(B46:AF46))+(B46:AF46&lt;=0),COLUMN(B46:AF46))))</f>
         <v>8</v>
       </c>
-      <c r="AJ46" s="181" cm="1">
+      <c r="AJ46" s="180" cm="1">
         <f t="array" ref="AJ46">SUMPRODUCT(--(B46:AF46=INT(B46:AF46)),--(B46:AF46&gt;0))/30*100%</f>
-        <v>0.566666666666667</v>
-      </c>
-      <c r="AK46" s="182">
+        <v>0.6</v>
+      </c>
+      <c r="AK46" s="181">
         <f t="shared" ref="AK46:AM46" si="44">RANK(AG46,AG$3:AG$53,0)</f>
         <v>1</v>
       </c>
-      <c r="AL46" s="182">
+      <c r="AL46" s="181">
         <f t="shared" si="44"/>
         <v>1</v>
       </c>
-      <c r="AM46" s="182">
+      <c r="AM46" s="181">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:39">
-      <c r="A47" s="178">
+      <c r="A47" s="183">
         <v>45</v>
       </c>
       <c r="B47" s="116"/>
@@ -11850,37 +11924,37 @@
       <c r="AD47" s="116"/>
       <c r="AE47" s="116"/>
       <c r="AF47" s="116"/>
-      <c r="AG47" s="179">
+      <c r="AG47" s="178">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="AH47" s="180" cm="1">
+      <c r="AH47" s="179" cm="1">
         <f t="array" ref="AH47">SUMPRODUCT(--(B47:AF47=INT(B47:AF47)),--(B47:AF47&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AI47" s="180" cm="1">
+      <c r="AI47" s="179" cm="1">
         <f t="array" ref="AI47">MAX(FREQUENCY(IF((B47:AF47=INT(B47:AF47))*(B47:AF47&gt;0),COLUMN(B47:AF47)),IF((B47:AF47&lt;&gt;INT(B47:AF47))+(B47:AF47&lt;=0),COLUMN(B47:AF47))))</f>
         <v>0</v>
       </c>
-      <c r="AJ47" s="181" cm="1">
+      <c r="AJ47" s="180" cm="1">
         <f t="array" ref="AJ47">SUMPRODUCT(--(B47:AF47=INT(B47:AF47)),--(B47:AF47&gt;0))/30*100%</f>
         <v>0</v>
       </c>
-      <c r="AK47" s="182">
+      <c r="AK47" s="181">
         <f t="shared" ref="AK47:AM47" si="45">RANK(AG47,AG$3:AG$53,0)</f>
-        <v>35</v>
-      </c>
-      <c r="AL47" s="182">
+        <v>40</v>
+      </c>
+      <c r="AL47" s="181">
         <f t="shared" si="45"/>
-        <v>35</v>
-      </c>
-      <c r="AM47" s="182">
+        <v>40</v>
+      </c>
+      <c r="AM47" s="181">
         <f t="shared" si="45"/>
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="1:39">
-      <c r="A48" s="183">
+      <c r="A48" s="182">
         <v>46</v>
       </c>
       <c r="B48" s="116"/>
@@ -11916,7 +11990,9 @@
       <c r="V48" s="116"/>
       <c r="W48" s="116"/>
       <c r="X48" s="116"/>
-      <c r="Y48" s="116"/>
+      <c r="Y48" s="116">
+        <v>1</v>
+      </c>
       <c r="Z48" s="116"/>
       <c r="AA48" s="116"/>
       <c r="AB48" s="116"/>
@@ -11924,37 +12000,37 @@
       <c r="AD48" s="116"/>
       <c r="AE48" s="116"/>
       <c r="AF48" s="116"/>
-      <c r="AG48" s="179">
+      <c r="AG48" s="178">
         <f t="shared" si="33"/>
-        <v>5</v>
-      </c>
-      <c r="AH48" s="180" cm="1">
+        <v>6</v>
+      </c>
+      <c r="AH48" s="179" cm="1">
         <f t="array" ref="AH48">SUMPRODUCT(--(B48:AF48=INT(B48:AF48)),--(B48:AF48&gt;0))</f>
-        <v>5</v>
-      </c>
-      <c r="AI48" s="180" cm="1">
+        <v>6</v>
+      </c>
+      <c r="AI48" s="179" cm="1">
         <f t="array" ref="AI48">MAX(FREQUENCY(IF((B48:AF48=INT(B48:AF48))*(B48:AF48&gt;0),COLUMN(B48:AF48)),IF((B48:AF48&lt;&gt;INT(B48:AF48))+(B48:AF48&lt;=0),COLUMN(B48:AF48))))</f>
         <v>2</v>
       </c>
-      <c r="AJ48" s="181" cm="1">
+      <c r="AJ48" s="180" cm="1">
         <f t="array" ref="AJ48">SUMPRODUCT(--(B48:AF48=INT(B48:AF48)),--(B48:AF48&gt;0))/30*100%</f>
-        <v>0.166666666666667</v>
-      </c>
-      <c r="AK48" s="182">
+        <v>0.2</v>
+      </c>
+      <c r="AK48" s="181">
         <f t="shared" ref="AK48:AM48" si="46">RANK(AG48,AG$3:AG$53,0)</f>
         <v>18</v>
       </c>
-      <c r="AL48" s="182">
+      <c r="AL48" s="181">
         <f t="shared" si="46"/>
-        <v>17</v>
-      </c>
-      <c r="AM48" s="182">
+        <v>16</v>
+      </c>
+      <c r="AM48" s="181">
         <f t="shared" si="46"/>
         <v>13</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="1:39">
-      <c r="A49" s="183">
+      <c r="A49" s="182">
         <v>47</v>
       </c>
       <c r="B49" s="116"/>
@@ -11984,7 +12060,9 @@
       <c r="V49" s="116"/>
       <c r="W49" s="116"/>
       <c r="X49" s="116"/>
-      <c r="Y49" s="116"/>
+      <c r="Y49" s="116">
+        <v>1</v>
+      </c>
       <c r="Z49" s="116"/>
       <c r="AA49" s="116"/>
       <c r="AB49" s="116"/>
@@ -11992,37 +12070,37 @@
       <c r="AD49" s="116"/>
       <c r="AE49" s="116"/>
       <c r="AF49" s="116"/>
-      <c r="AG49" s="179">
+      <c r="AG49" s="178">
         <f t="shared" si="33"/>
-        <v>2</v>
-      </c>
-      <c r="AH49" s="180" cm="1">
+        <v>3</v>
+      </c>
+      <c r="AH49" s="179" cm="1">
         <f t="array" ref="AH49">SUMPRODUCT(--(B49:AF49=INT(B49:AF49)),--(B49:AF49&gt;0))</f>
-        <v>2</v>
-      </c>
-      <c r="AI49" s="180" cm="1">
+        <v>3</v>
+      </c>
+      <c r="AI49" s="179" cm="1">
         <f t="array" ref="AI49">MAX(FREQUENCY(IF((B49:AF49=INT(B49:AF49))*(B49:AF49&gt;0),COLUMN(B49:AF49)),IF((B49:AF49&lt;&gt;INT(B49:AF49))+(B49:AF49&lt;=0),COLUMN(B49:AF49))))</f>
         <v>1</v>
       </c>
-      <c r="AJ49" s="181" cm="1">
+      <c r="AJ49" s="180" cm="1">
         <f t="array" ref="AJ49">SUMPRODUCT(--(B49:AF49=INT(B49:AF49)),--(B49:AF49&gt;0))/30*100%</f>
-        <v>0.0666666666666667</v>
-      </c>
-      <c r="AK49" s="182">
+        <v>0.1</v>
+      </c>
+      <c r="AK49" s="181">
         <f t="shared" ref="AK49:AM49" si="47">RANK(AG49,AG$3:AG$53,0)</f>
-        <v>24</v>
-      </c>
-      <c r="AL49" s="182">
+        <v>23</v>
+      </c>
+      <c r="AL49" s="181">
         <f t="shared" si="47"/>
-        <v>24</v>
-      </c>
-      <c r="AM49" s="182">
+        <v>22</v>
+      </c>
+      <c r="AM49" s="181">
         <f t="shared" si="47"/>
         <v>18</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="1:39">
-      <c r="A50" s="183">
+      <c r="A50" s="182">
         <v>48</v>
       </c>
       <c r="B50" s="116"/>
@@ -12062,37 +12140,37 @@
       <c r="AD50" s="116"/>
       <c r="AE50" s="116"/>
       <c r="AF50" s="116"/>
-      <c r="AG50" s="179">
+      <c r="AG50" s="178">
         <f t="shared" si="33"/>
         <v>3</v>
       </c>
-      <c r="AH50" s="180" cm="1">
+      <c r="AH50" s="179" cm="1">
         <f t="array" ref="AH50">SUMPRODUCT(--(B50:AF50=INT(B50:AF50)),--(B50:AF50&gt;0))</f>
         <v>3</v>
       </c>
-      <c r="AI50" s="180" cm="1">
+      <c r="AI50" s="179" cm="1">
         <f t="array" ref="AI50">MAX(FREQUENCY(IF((B50:AF50=INT(B50:AF50))*(B50:AF50&gt;0),COLUMN(B50:AF50)),IF((B50:AF50&lt;&gt;INT(B50:AF50))+(B50:AF50&lt;=0),COLUMN(B50:AF50))))</f>
         <v>1</v>
       </c>
-      <c r="AJ50" s="181" cm="1">
+      <c r="AJ50" s="180" cm="1">
         <f t="array" ref="AJ50">SUMPRODUCT(--(B50:AF50=INT(B50:AF50)),--(B50:AF50&gt;0))/30*100%</f>
         <v>0.1</v>
       </c>
-      <c r="AK50" s="182">
+      <c r="AK50" s="181">
         <f t="shared" ref="AK50:AM50" si="48">RANK(AG50,AG$3:AG$53,0)</f>
+        <v>23</v>
+      </c>
+      <c r="AL50" s="181">
+        <f t="shared" si="48"/>
         <v>22</v>
       </c>
-      <c r="AL50" s="182">
-        <f t="shared" si="48"/>
-        <v>21</v>
-      </c>
-      <c r="AM50" s="182">
+      <c r="AM50" s="181">
         <f t="shared" si="48"/>
         <v>18</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:39">
-      <c r="A51" s="178">
+      <c r="A51" s="183">
         <v>49</v>
       </c>
       <c r="B51" s="116"/>
@@ -12126,37 +12204,37 @@
       <c r="AD51" s="116"/>
       <c r="AE51" s="116"/>
       <c r="AF51" s="116"/>
-      <c r="AG51" s="179">
+      <c r="AG51" s="178">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="AH51" s="180" cm="1">
+      <c r="AH51" s="179" cm="1">
         <f t="array" ref="AH51">SUMPRODUCT(--(B51:AF51=INT(B51:AF51)),--(B51:AF51&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AI51" s="180" cm="1">
+      <c r="AI51" s="179" cm="1">
         <f t="array" ref="AI51">MAX(FREQUENCY(IF((B51:AF51=INT(B51:AF51))*(B51:AF51&gt;0),COLUMN(B51:AF51)),IF((B51:AF51&lt;&gt;INT(B51:AF51))+(B51:AF51&lt;=0),COLUMN(B51:AF51))))</f>
         <v>0</v>
       </c>
-      <c r="AJ51" s="181" cm="1">
+      <c r="AJ51" s="180" cm="1">
         <f t="array" ref="AJ51">SUMPRODUCT(--(B51:AF51=INT(B51:AF51)),--(B51:AF51&gt;0))/30*100%</f>
         <v>0</v>
       </c>
-      <c r="AK51" s="182">
+      <c r="AK51" s="181">
         <f t="shared" ref="AK51:AM51" si="49">RANK(AG51,AG$3:AG$53,0)</f>
-        <v>35</v>
-      </c>
-      <c r="AL51" s="182">
+        <v>40</v>
+      </c>
+      <c r="AL51" s="181">
         <f t="shared" si="49"/>
-        <v>35</v>
-      </c>
-      <c r="AM51" s="182">
+        <v>40</v>
+      </c>
+      <c r="AM51" s="181">
         <f t="shared" si="49"/>
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="1:39">
-      <c r="A52" s="178">
+      <c r="A52" s="183">
         <v>50</v>
       </c>
       <c r="B52" s="116"/>
@@ -12190,37 +12268,37 @@
       <c r="AD52" s="116"/>
       <c r="AE52" s="116"/>
       <c r="AF52" s="116"/>
-      <c r="AG52" s="179">
+      <c r="AG52" s="178">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="AH52" s="180" cm="1">
+      <c r="AH52" s="179" cm="1">
         <f t="array" ref="AH52">SUMPRODUCT(--(B52:AF52=INT(B52:AF52)),--(B52:AF52&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AI52" s="180" cm="1">
+      <c r="AI52" s="179" cm="1">
         <f t="array" ref="AI52">MAX(FREQUENCY(IF((B52:AF52=INT(B52:AF52))*(B52:AF52&gt;0),COLUMN(B52:AF52)),IF((B52:AF52&lt;&gt;INT(B52:AF52))+(B52:AF52&lt;=0),COLUMN(B52:AF52))))</f>
         <v>0</v>
       </c>
-      <c r="AJ52" s="181" cm="1">
+      <c r="AJ52" s="180" cm="1">
         <f t="array" ref="AJ52">SUMPRODUCT(--(B52:AF52=INT(B52:AF52)),--(B52:AF52&gt;0))/30*100%</f>
         <v>0</v>
       </c>
-      <c r="AK52" s="182">
+      <c r="AK52" s="181">
         <f t="shared" ref="AK52:AM52" si="50">RANK(AG52,AG$3:AG$53,0)</f>
-        <v>35</v>
-      </c>
-      <c r="AL52" s="182">
+        <v>40</v>
+      </c>
+      <c r="AL52" s="181">
         <f t="shared" si="50"/>
-        <v>35</v>
-      </c>
-      <c r="AM52" s="182">
+        <v>40</v>
+      </c>
+      <c r="AM52" s="181">
         <f t="shared" si="50"/>
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="1:39">
-      <c r="A53" s="178">
+      <c r="A53" s="183">
         <v>51</v>
       </c>
       <c r="B53" s="116"/>
@@ -12254,33 +12332,33 @@
       <c r="AD53" s="116"/>
       <c r="AE53" s="116"/>
       <c r="AF53" s="116"/>
-      <c r="AG53" s="179">
+      <c r="AG53" s="178">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="AH53" s="180" cm="1">
+      <c r="AH53" s="179" cm="1">
         <f t="array" ref="AH53">SUMPRODUCT(--(B53:AF53=INT(B53:AF53)),--(B53:AF53&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AI53" s="180" cm="1">
+      <c r="AI53" s="179" cm="1">
         <f t="array" ref="AI53">MAX(FREQUENCY(IF((B53:AF53=INT(B53:AF53))*(B53:AF53&gt;0),COLUMN(B53:AF53)),IF((B53:AF53&lt;&gt;INT(B53:AF53))+(B53:AF53&lt;=0),COLUMN(B53:AF53))))</f>
         <v>0</v>
       </c>
-      <c r="AJ53" s="181" cm="1">
+      <c r="AJ53" s="180" cm="1">
         <f t="array" ref="AJ53">SUMPRODUCT(--(B53:AF53=INT(B53:AF53)),--(B53:AF53&gt;0))/30*100%</f>
         <v>0</v>
       </c>
-      <c r="AK53" s="182">
+      <c r="AK53" s="181">
         <f t="shared" ref="AK53:AM53" si="51">RANK(AG53,AG$3:AG$53,0)</f>
-        <v>35</v>
-      </c>
-      <c r="AL53" s="182">
+        <v>40</v>
+      </c>
+      <c r="AL53" s="181">
         <f t="shared" si="51"/>
-        <v>35</v>
-      </c>
-      <c r="AM53" s="182">
+        <v>40</v>
+      </c>
+      <c r="AM53" s="181">
         <f t="shared" si="51"/>
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -12602,7 +12680,7 @@
   <pageSetup paperSize="9" scale="80" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AM7 A8:V8 X8:AM8 A9:AM39 A40:V41 X41:AM41 Y40:AM40 A45:AM53 Y44:AM44 A44:W44 A42:AM43" formulaRange="1" unlockedFormula="1"/>
+    <ignoredError sqref="A28:X33 Z28:AM33 A34:AM35 A36:X36 Z36:AM36 A37:AM37 A38:X38 Z38:AM38 A39:AM39 A42:X42 Z40:AM42 A43:AM43 A44:W44 Z44:AM44 A45:AM45 A46:X46 Z46:AM46 A47:AM47 A48:X49 Z48:AM49 A50:AM53 X41 A40:V41 A9:X10 Z9:AM10 A11:AM11 A12:X15 Z12:AM15 A16:AM16 A17:X18 Z17:AM18 A19:AM21 A22:X22 Z22:AM22 A23:AM23 A24:X25 Z24:AM25 A26:AM27 X8:AM8 A8:V8 A1:AM2 A3:X4 Z3:AM4 A5:AM7" formulaRange="1" unlockedFormula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -12649,21 +12727,21 @@
     </row>
     <row r="2" ht="16.5" spans="1:10">
       <c r="A2" s="145" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B2" s="149" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C2" s="150" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D2" s="151"/>
       <c r="E2" s="149" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F2" s="149"/>
       <c r="G2" s="152" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="H2" s="144"/>
       <c r="I2" s="144"/>
@@ -12671,10 +12749,10 @@
     </row>
     <row r="3" ht="16.5" spans="1:10">
       <c r="A3" s="145" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B3" s="154" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C3" s="154"/>
       <c r="D3" s="154"/>
@@ -12687,10 +12765,10 @@
     </row>
     <row r="4" ht="16.5" spans="1:10">
       <c r="A4" s="145" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B4" s="155" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C4" s="155"/>
       <c r="D4" s="155"/>
@@ -12703,7 +12781,7 @@
     </row>
     <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="145" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B5" s="156">
         <v>1</v>
@@ -12723,7 +12801,7 @@
     </row>
     <row r="6" ht="16.5" spans="1:10">
       <c r="A6" s="145" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B6" s="158">
         <v>1</v>
@@ -12733,7 +12811,7 @@
       <c r="E6" s="158"/>
       <c r="F6" s="158"/>
       <c r="G6" s="159" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="H6" s="144"/>
       <c r="I6" s="144"/>
@@ -12741,10 +12819,10 @@
     </row>
     <row r="7" ht="16.5" spans="1:10">
       <c r="A7" s="145" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B7" s="160" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C7" s="160"/>
       <c r="D7" s="160"/>
@@ -12759,14 +12837,14 @@
     </row>
     <row r="8" ht="16.5" spans="1:10">
       <c r="A8" s="145" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B8" s="162">
         <v>1</v>
       </c>
       <c r="C8" s="162"/>
       <c r="D8" s="163" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E8" s="163"/>
       <c r="F8" s="163"/>
@@ -12777,10 +12855,10 @@
     </row>
     <row r="9" ht="16.5" spans="1:10">
       <c r="A9" s="145" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B9" s="149" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C9" s="149"/>
       <c r="D9" s="149"/>
@@ -12793,23 +12871,23 @@
     </row>
     <row r="10" ht="16.5" spans="1:10">
       <c r="A10" s="145" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B10" s="154">
         <v>1</v>
       </c>
       <c r="C10" s="154"/>
       <c r="D10" s="164" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="E10" s="154">
         <v>1</v>
       </c>
       <c r="F10" s="164" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="G10" s="144" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="H10" s="144"/>
       <c r="I10" s="144"/>
@@ -12817,7 +12895,7 @@
     </row>
     <row r="11" ht="16.5" spans="1:10">
       <c r="A11" s="145" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B11" s="155">
         <v>1</v>
@@ -12833,7 +12911,7 @@
     </row>
     <row r="12" ht="16.5" spans="1:10">
       <c r="A12" s="145" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B12" s="156">
         <v>1</v>
@@ -12851,17 +12929,17 @@
     </row>
     <row r="13" s="143" customFormat="1" ht="16.5" spans="1:10">
       <c r="A13" s="145" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B13" s="165" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C13" s="165"/>
       <c r="D13" s="165"/>
       <c r="E13" s="165"/>
       <c r="F13" s="165"/>
       <c r="G13" s="166" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H13" s="143"/>
       <c r="I13" s="143"/>
@@ -12869,10 +12947,10 @@
     </row>
     <row r="14" s="143" customFormat="1" ht="16.5" spans="1:10">
       <c r="A14" s="145" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B14" s="168" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C14" s="168"/>
       <c r="D14" s="168"/>
@@ -12947,7 +13025,7 @@
   <sheetData>
     <row r="1" s="113" customFormat="1" spans="1:9">
       <c r="A1" s="117" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B1" s="118"/>
       <c r="C1" s="113" t="s">
@@ -12972,10 +13050,10 @@
     </row>
     <row r="2" s="114" customFormat="1" spans="1:9">
       <c r="A2" s="121" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B2" s="122" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C2" s="123" t="s">
         <v>7</v>
@@ -12987,7 +13065,7 @@
     <row r="3" s="114" customFormat="1" spans="1:9">
       <c r="A3" s="126"/>
       <c r="B3" s="122" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C3" s="123" t="s">
         <v>28</v>
@@ -13009,7 +13087,7 @@
     <row r="5" s="114" customFormat="1" spans="1:9">
       <c r="A5" s="126"/>
       <c r="B5" s="122" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C5" s="123" t="s">
         <v>31</v>
@@ -13021,7 +13099,7 @@
     <row r="6" s="114" customFormat="1" spans="1:9">
       <c r="A6" s="126"/>
       <c r="B6" s="122" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>19</v>
@@ -13049,7 +13127,7 @@
     <row r="8" s="114" customFormat="1" spans="1:9">
       <c r="A8" s="126"/>
       <c r="B8" s="122" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>14</v>
@@ -13063,7 +13141,7 @@
     <row r="9" s="114" customFormat="1" spans="1:9">
       <c r="A9" s="126"/>
       <c r="B9" s="122" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C9" s="123" t="s">
         <v>24</v>
@@ -13075,7 +13153,7 @@
     <row r="10" s="114" customFormat="1" spans="1:9">
       <c r="A10" s="126"/>
       <c r="B10" s="122" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C10" s="123" t="s">
         <v>34</v>
@@ -13087,7 +13165,7 @@
     <row r="11" s="114" customFormat="1" spans="1:9">
       <c r="A11" s="130"/>
       <c r="B11" s="122" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C11" s="123" t="s">
         <v>69</v>
@@ -13098,10 +13176,10 @@
     </row>
     <row r="12" s="115" customFormat="1" spans="1:9">
       <c r="A12" s="131" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B12" s="132" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C12" s="133" t="s">
         <v>88</v>
@@ -13125,10 +13203,10 @@
     <row r="14" s="115" customFormat="1" spans="1:9">
       <c r="A14" s="137"/>
       <c r="B14" s="132" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C14" s="133" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D14" s="138"/>
       <c r="E14" s="134"/>
@@ -13139,7 +13217,7 @@
     <row r="15" s="115" customFormat="1" spans="1:9">
       <c r="A15" s="137"/>
       <c r="B15" s="132" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C15" s="133" t="s">
         <v>10</v>
@@ -13161,7 +13239,7 @@
     <row r="17" s="115" customFormat="1" spans="1:7">
       <c r="A17" s="137"/>
       <c r="B17" s="132" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C17" s="133" t="s">
         <v>27</v>
@@ -13173,7 +13251,7 @@
     <row r="18" s="115" customFormat="1" spans="1:7">
       <c r="A18" s="137"/>
       <c r="B18" s="132" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C18" s="133" t="s">
         <v>42</v>
@@ -13185,7 +13263,7 @@
     <row r="19" s="115" customFormat="1" spans="1:7">
       <c r="A19" s="137"/>
       <c r="B19" s="132" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C19" s="133" t="s">
         <v>81</v>
@@ -13197,7 +13275,7 @@
     <row r="20" s="115" customFormat="1" spans="1:7">
       <c r="A20" s="137"/>
       <c r="B20" s="132" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C20" s="133" t="s">
         <v>84</v>
@@ -13209,7 +13287,7 @@
     <row r="21" s="115" customFormat="1" spans="1:7">
       <c r="A21" s="137"/>
       <c r="B21" s="132" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C21" s="139"/>
       <c r="D21" s="140"/>
@@ -13221,7 +13299,7 @@
     <row r="22" s="115" customFormat="1" spans="1:7">
       <c r="A22" s="141"/>
       <c r="B22" s="132" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C22" s="139"/>
       <c r="D22" s="142"/>
@@ -13283,7 +13361,7 @@
   <sheetData>
     <row r="1" s="87" customFormat="1" customHeight="1" spans="1:16">
       <c r="A1" s="90" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B1" s="91"/>
       <c r="C1" s="91"/>
@@ -13314,7 +13392,7 @@
     </row>
     <row r="3" s="89" customFormat="1" customHeight="1" spans="1:16">
       <c r="A3" s="96" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B3" s="97"/>
       <c r="C3" s="98"/>
@@ -13322,7 +13400,7 @@
         <v>42</v>
       </c>
       <c r="E3" s="99" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F3" s="100"/>
       <c r="G3" s="100"/>
@@ -13350,7 +13428,7 @@
         <v>76</v>
       </c>
       <c r="H4" s="101" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I4" s="101" t="s">
         <v>88</v>
@@ -13365,7 +13443,7 @@
         <v>36</v>
       </c>
       <c r="D5" s="99" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E5" s="99" t="s">
         <v>79</v>
@@ -13407,7 +13485,7 @@
         <v>34</v>
       </c>
       <c r="I6" s="101" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" s="89" customFormat="1" customHeight="1" spans="1:16">
@@ -13428,7 +13506,7 @@
         <v>84</v>
       </c>
       <c r="G7" s="100" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H7" s="101" t="s">
         <v>61</v>
@@ -13467,7 +13545,7 @@
     <row r="9" s="89" customFormat="1" customHeight="1" spans="1:16">
       <c r="A9" s="102"/>
       <c r="B9" s="98" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="98" t="s">
         <v>56</v>
@@ -13482,7 +13560,7 @@
         <v>45</v>
       </c>
       <c r="G9" s="100" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H9" s="101" t="s">
         <v>52</v>
@@ -13496,7 +13574,7 @@
       <c r="B10" s="104"/>
       <c r="C10" s="105"/>
       <c r="D10" s="106" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E10" s="107"/>
       <c r="F10" s="108"/>
@@ -13506,7 +13584,7 @@
     </row>
     <row r="11" s="89" customFormat="1" customHeight="1" spans="1:16">
       <c r="A11" s="96" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B11" s="97"/>
       <c r="C11" s="98"/>
@@ -13514,7 +13592,7 @@
         <v>42</v>
       </c>
       <c r="E11" s="99" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F11" s="100"/>
       <c r="G11" s="100"/>
@@ -13533,7 +13611,7 @@
         <v>57</v>
       </c>
       <c r="E12" s="99" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F12" s="100" t="s">
         <v>14</v>
@@ -13587,10 +13665,10 @@
         <v>34</v>
       </c>
       <c r="E14" s="99" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F14" s="100" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G14" s="100" t="s">
         <v>71</v>
@@ -13659,13 +13737,13 @@
     <row r="17" s="89" customFormat="1" customHeight="1" spans="1:9">
       <c r="A17" s="102"/>
       <c r="B17" s="98" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C17" s="98" t="s">
         <v>56</v>
       </c>
       <c r="D17" s="99" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E17" s="99" t="s">
         <v>97</v>
@@ -13677,7 +13755,7 @@
         <v>66</v>
       </c>
       <c r="H17" s="101" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I17" s="101" t="s">
         <v>81</v>
@@ -13698,7 +13776,7 @@
     </row>
     <row r="19" s="89" customFormat="1" customHeight="1" spans="1:9">
       <c r="A19" s="96" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B19" s="97"/>
       <c r="C19" s="98"/>
@@ -13707,7 +13785,7 @@
       </c>
       <c r="E19" s="99"/>
       <c r="F19" s="100" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G19" s="100"/>
       <c r="H19" s="101"/>
@@ -13722,7 +13800,7 @@
         <v>33</v>
       </c>
       <c r="D20" s="99" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E20" s="99" t="s">
         <v>76</v>
@@ -13809,7 +13887,7 @@
         <v>61</v>
       </c>
       <c r="F23" s="100" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G23" s="100" t="s">
         <v>92</v>
@@ -13851,7 +13929,7 @@
     <row r="25" s="89" customFormat="1" customHeight="1" spans="1:9">
       <c r="A25" s="102"/>
       <c r="B25" s="98" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C25" s="98" t="s">
         <v>81</v>
@@ -13869,7 +13947,7 @@
         <v>93</v>
       </c>
       <c r="H25" s="101" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I25" s="101" t="s">
         <v>45</v>
@@ -13880,7 +13958,7 @@
       <c r="B26" s="111"/>
       <c r="C26" s="112"/>
       <c r="D26" s="106" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E26" s="107"/>
       <c r="F26" s="108"/>
@@ -13925,13 +14003,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="78" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B1" s="79" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C1" s="80" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -13939,208 +14017,208 @@
         <v>1</v>
       </c>
       <c r="B2" s="76" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C2" s="77" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="81"/>
       <c r="B3" s="76" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C3" s="77" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="81"/>
       <c r="B4" s="76" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C4" s="77" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="81"/>
       <c r="B5" s="76" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C5" s="77" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="81"/>
       <c r="B6" s="76" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C6" s="77" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="81"/>
       <c r="B7" s="76" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C7" s="77" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="81"/>
       <c r="B8" s="76" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C8" s="77" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="81"/>
       <c r="B9" s="76" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C9" s="77" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="81"/>
       <c r="B10" s="76" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C10" s="77" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="81"/>
       <c r="B11" s="76" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C11" s="77" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="81"/>
       <c r="B12" s="76" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C12" s="77" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="81"/>
       <c r="B13" s="76" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C13" s="77" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="81"/>
       <c r="B14" s="76" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C14" s="77" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="81"/>
       <c r="B15" s="76" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C15" s="77" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="81"/>
       <c r="B16" s="76" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C16" s="77" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="81"/>
       <c r="B17" s="76" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C17" s="77" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="81"/>
       <c r="B18" s="76" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C18" s="77" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="81"/>
       <c r="B19" s="76" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C19" s="77" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="81"/>
       <c r="B20" s="76" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C20" s="77" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="81"/>
       <c r="B21" s="76" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C21" s="77" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="81"/>
       <c r="B22" s="76" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C22" s="77" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="81"/>
       <c r="B23" s="76" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C23" s="77" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="81"/>
       <c r="B24" s="76" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C24" s="77" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -14148,118 +14226,118 @@
         <v>2</v>
       </c>
       <c r="B25" s="76" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C25" s="77" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="82"/>
       <c r="B26" s="76" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C26" s="77" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="82"/>
       <c r="B27" s="76" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C27" s="77" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="82"/>
       <c r="B28" s="76" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C28" s="77" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="82"/>
       <c r="B29" s="76" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C29" s="77" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="82"/>
       <c r="B30" s="76" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C30" s="77" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="82"/>
       <c r="B31" s="76" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C31" s="77" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="82"/>
       <c r="B32" s="76" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C32" s="77" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="82"/>
       <c r="B33" s="76" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C33" s="77" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="82"/>
       <c r="B34" s="76" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C34" s="77" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="82"/>
       <c r="B35" s="76" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C35" s="77" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="82"/>
       <c r="B36" s="76" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C36" s="77" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="83"/>
       <c r="B37" s="76" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C37" s="77" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -14267,138 +14345,138 @@
         <v>3</v>
       </c>
       <c r="B38" s="76" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C38" s="77" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="85"/>
       <c r="B39" s="76" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C39" s="77" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="85"/>
       <c r="B40" s="76" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C40" s="77" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="85"/>
       <c r="B41" s="76" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C41" s="77" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="85"/>
       <c r="B42" s="76" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C42" s="77" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="85"/>
       <c r="B43" s="76" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C43" s="77" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="85"/>
       <c r="B44" s="76" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C44" s="77" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="85"/>
       <c r="B45" s="76" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C45" s="77" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="85"/>
       <c r="B46" s="76" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C46" s="77" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="85"/>
       <c r="B47" s="76" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C47" s="77" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="85"/>
       <c r="B48" s="76" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C48" s="77" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="85"/>
       <c r="B49" s="76" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C49" s="77" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="86"/>
       <c r="B50" s="76" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C50" s="77" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:3">
       <c r="A51" s="75"/>
       <c r="B51" s="76" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C51" s="77"/>
     </row>
     <row r="52" customFormat="1" spans="1:3">
       <c r="A52" s="75"/>
       <c r="B52" s="76" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C52" s="77"/>
     </row>
     <row r="53" customFormat="1" spans="1:3">
       <c r="A53" s="75"/>
       <c r="B53" s="76" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C53" s="77"/>
     </row>

--- a/c/9班资料.xlsx
+++ b/c/9班资料.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10030" tabRatio="724"/>
+    <workbookView windowWidth="20750" windowHeight="10030" tabRatio="724" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="师生" sheetId="5" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="603">
   <si>
     <t>姓名</t>
   </si>
@@ -829,6 +829,12 @@
     <t>物理校本第三题关于足球守门员戴手套增大摩擦力。林奕扬：第三题不合实际，我就是守门员……手套上的乳胶是光滑的</t>
   </si>
   <si>
+    <t>八上1.13</t>
+  </si>
+  <si>
+    <t>吃切块甘蔗</t>
+  </si>
+  <si>
     <t>数学课谈政策</t>
   </si>
   <si>
@@ -841,6 +847,18 @@
     <t>语文好段抄生物书“生态系统”章节导言</t>
   </si>
   <si>
+    <t>信仰</t>
+  </si>
+  <si>
+    <t>叶弘毅：10班早读（或课前三分钟？）读书声小，冯越：你们要学习9班，他们读书特别有革命信念。举个例子，他们读中国共产党读到“信仰”两个字时特别大声。</t>
+  </si>
+  <si>
+    <t>40中</t>
+  </si>
+  <si>
+    <t>数：油印室额度都用光了。</t>
+  </si>
+  <si>
     <t>政治课</t>
   </si>
   <si>
@@ -860,6 +878,12 @@
   </si>
   <si>
     <t>下午第三节物理</t>
+  </si>
+  <si>
+    <t>2026.1.13</t>
+  </si>
+  <si>
+    <t>下午第一节数学</t>
   </si>
   <si>
     <t>座号</t>
@@ -3127,6 +3151,17 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="华文仿宋"/>
       <charset val="134"/>
     </font>
@@ -3137,20 +3172,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
       <strike/>
       <sz val="11"/>
       <name val="黑体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -3917,7 +3941,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="222">
+  <cellXfs count="224">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4552,6 +4576,12 @@
     </xf>
     <xf numFmtId="20" fontId="1" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4926,29 +4956,29 @@
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="7.59090909090909" style="71" customWidth="1"/>
-    <col min="2" max="7" width="25.8727272727273" style="216" customWidth="1"/>
+    <col min="2" max="7" width="25.8727272727273" style="218" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="215" customFormat="1" spans="1:7">
+    <row r="1" s="217" customFormat="1" spans="1:7">
       <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="217" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="217" t="s">
+      <c r="B1" s="219" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="219" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="217" t="s">
+      <c r="D1" s="219" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="217" t="s">
+      <c r="E1" s="219" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="217" t="s">
+      <c r="F1" s="219" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="217" t="s">
+      <c r="G1" s="219" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4956,10 +4986,10 @@
       <c r="A2" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="216" t="s">
+      <c r="B2" s="218" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="216" t="s">
+      <c r="C2" s="218" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4967,10 +4997,10 @@
       <c r="A3" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="216" t="s">
+      <c r="C3" s="218" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="216" t="s">
+      <c r="D3" s="218" t="s">
         <v>12</v>
       </c>
     </row>
@@ -4983,10 +5013,10 @@
       <c r="A5" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="216" t="s">
+      <c r="C5" s="218" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="216" t="s">
+      <c r="D5" s="218" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4994,7 +5024,7 @@
       <c r="A6" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="216" t="s">
+      <c r="C6" s="218" t="s">
         <v>18</v>
       </c>
     </row>
@@ -5002,13 +5032,13 @@
       <c r="A7" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="216" t="s">
+      <c r="B7" s="218" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="216" t="s">
+      <c r="C7" s="218" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="216" t="s">
+      <c r="D7" s="218" t="s">
         <v>22</v>
       </c>
     </row>
@@ -5026,7 +5056,7 @@
       <c r="A10" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="216" t="s">
+      <c r="B10" s="218" t="s">
         <v>26</v>
       </c>
     </row>
@@ -5044,7 +5074,7 @@
       <c r="A13" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="216" t="s">
+      <c r="D13" s="218" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5052,7 +5082,7 @@
       <c r="A14" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="216" t="s">
+      <c r="B14" s="218" t="s">
         <v>32</v>
       </c>
     </row>
@@ -5065,7 +5095,7 @@
       <c r="A16" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="216" t="s">
+      <c r="C16" s="218" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5073,7 +5103,7 @@
       <c r="A17" s="72" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="216" t="s">
+      <c r="C17" s="218" t="s">
         <v>37</v>
       </c>
     </row>
@@ -5081,7 +5111,7 @@
       <c r="A18" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="216" t="s">
+      <c r="D18" s="218" t="s">
         <v>39</v>
       </c>
     </row>
@@ -5089,7 +5119,7 @@
       <c r="A19" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="216" t="s">
+      <c r="D19" s="218" t="s">
         <v>41</v>
       </c>
     </row>
@@ -5097,10 +5127,10 @@
       <c r="A20" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="216" t="s">
+      <c r="B20" s="218" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="216" t="s">
+      <c r="C20" s="218" t="s">
         <v>44</v>
       </c>
     </row>
@@ -5108,13 +5138,13 @@
       <c r="A21" s="72" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="216" t="s">
+      <c r="B21" s="218" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="216" t="s">
+      <c r="C21" s="218" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="216" t="s">
+      <c r="D21" s="218" t="s">
         <v>48</v>
       </c>
     </row>
@@ -5127,7 +5157,7 @@
       <c r="A23" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="216" t="s">
+      <c r="B23" s="218" t="s">
         <v>51</v>
       </c>
     </row>
@@ -5135,13 +5165,13 @@
       <c r="A24" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="216" t="s">
+      <c r="B24" s="218" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="216" t="s">
+      <c r="C24" s="218" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="216" t="s">
+      <c r="D24" s="218" t="s">
         <v>55</v>
       </c>
     </row>
@@ -5159,10 +5189,10 @@
       <c r="A27" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="B27" s="216" t="s">
+      <c r="B27" s="218" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="216" t="s">
+      <c r="C27" s="218" t="s">
         <v>60</v>
       </c>
     </row>
@@ -5170,13 +5200,13 @@
       <c r="A28" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="B28" s="216" t="s">
+      <c r="B28" s="218" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="216" t="s">
+      <c r="C28" s="218" t="s">
         <v>63</v>
       </c>
-      <c r="D28" s="216" t="s">
+      <c r="D28" s="218" t="s">
         <v>64</v>
       </c>
     </row>
@@ -5189,10 +5219,10 @@
       <c r="A30" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="B30" s="216" t="s">
+      <c r="B30" s="218" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="216" t="s">
+      <c r="C30" s="218" t="s">
         <v>68</v>
       </c>
     </row>
@@ -5225,7 +5255,7 @@
       <c r="A36" s="72" t="s">
         <v>74</v>
       </c>
-      <c r="B36" s="216" t="s">
+      <c r="B36" s="218" t="s">
         <v>75</v>
       </c>
     </row>
@@ -5233,10 +5263,10 @@
       <c r="A37" s="72" t="s">
         <v>76</v>
       </c>
-      <c r="C37" s="216" t="s">
+      <c r="C37" s="218" t="s">
         <v>77</v>
       </c>
-      <c r="D37" s="216" t="s">
+      <c r="D37" s="218" t="s">
         <v>78</v>
       </c>
     </row>
@@ -5244,23 +5274,23 @@
       <c r="A38" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="B38" s="216" t="s">
+      <c r="B38" s="218" t="s">
         <v>80</v>
       </c>
-      <c r="C38" s="218"/>
-      <c r="D38" s="218"/>
-      <c r="E38" s="218"/>
-      <c r="F38" s="218"/>
-      <c r="G38" s="218"/>
+      <c r="C38" s="220"/>
+      <c r="D38" s="220"/>
+      <c r="E38" s="220"/>
+      <c r="F38" s="220"/>
+      <c r="G38" s="220"/>
     </row>
     <row r="39" ht="26" spans="1:8">
       <c r="A39" s="72" t="s">
         <v>81</v>
       </c>
-      <c r="C39" s="216" t="s">
+      <c r="C39" s="218" t="s">
         <v>82</v>
       </c>
-      <c r="D39" s="216" t="s">
+      <c r="D39" s="218" t="s">
         <v>83</v>
       </c>
     </row>
@@ -5268,13 +5298,13 @@
       <c r="A40" s="72" t="s">
         <v>84</v>
       </c>
-      <c r="B40" s="216" t="s">
+      <c r="B40" s="218" t="s">
         <v>85</v>
       </c>
-      <c r="C40" s="216" t="s">
+      <c r="C40" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="D40" s="216" t="s">
+      <c r="D40" s="218" t="s">
         <v>87</v>
       </c>
     </row>
@@ -5282,13 +5312,13 @@
       <c r="A41" s="72" t="s">
         <v>88</v>
       </c>
-      <c r="C41" s="216" t="s">
+      <c r="C41" s="218" t="s">
         <v>89</v>
       </c>
-      <c r="D41" s="216" t="s">
+      <c r="D41" s="218" t="s">
         <v>90</v>
       </c>
-      <c r="H41" s="219" t="s">
+      <c r="H41" s="221" t="s">
         <v>91</v>
       </c>
     </row>
@@ -5301,7 +5331,7 @@
       <c r="A43" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="B43" s="216" t="s">
+      <c r="B43" s="218" t="s">
         <v>94</v>
       </c>
     </row>
@@ -5309,7 +5339,7 @@
       <c r="A44" s="72" t="s">
         <v>95</v>
       </c>
-      <c r="B44" s="216" t="s">
+      <c r="B44" s="218" t="s">
         <v>96</v>
       </c>
     </row>
@@ -5317,10 +5347,10 @@
       <c r="A45" s="72" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="216" t="s">
+      <c r="C45" s="218" t="s">
         <v>98</v>
       </c>
-      <c r="D45" s="216" t="s">
+      <c r="D45" s="218" t="s">
         <v>99</v>
       </c>
     </row>
@@ -5333,7 +5363,7 @@
       <c r="A47" s="72" t="s">
         <v>101</v>
       </c>
-      <c r="D47" s="216" t="s">
+      <c r="D47" s="218" t="s">
         <v>102</v>
       </c>
     </row>
@@ -5341,10 +5371,10 @@
       <c r="A48" s="72" t="s">
         <v>103</v>
       </c>
-      <c r="C48" s="216" t="s">
+      <c r="C48" s="218" t="s">
         <v>104</v>
       </c>
-      <c r="D48" s="216" t="s">
+      <c r="D48" s="218" t="s">
         <v>105</v>
       </c>
     </row>
@@ -5357,7 +5387,7 @@
       <c r="A50" s="72" t="s">
         <v>107</v>
       </c>
-      <c r="C50" s="216" t="s">
+      <c r="C50" s="218" t="s">
         <v>108</v>
       </c>
     </row>
@@ -5370,10 +5400,10 @@
       <c r="A52" s="72" t="s">
         <v>110</v>
       </c>
-      <c r="B52" s="216" t="s">
+      <c r="B52" s="218" t="s">
         <v>111</v>
       </c>
-      <c r="C52" s="216" t="s">
+      <c r="C52" s="218" t="s">
         <v>112</v>
       </c>
     </row>
@@ -5381,36 +5411,36 @@
       <c r="A53" s="71" t="s">
         <v>113</v>
       </c>
-      <c r="B53" s="216" t="s">
+      <c r="B53" s="218" t="s">
         <v>114</v>
       </c>
-      <c r="D53" s="218"/>
-      <c r="E53" s="218"/>
-      <c r="F53" s="218"/>
-      <c r="G53" s="218"/>
+      <c r="D53" s="220"/>
+      <c r="E53" s="220"/>
+      <c r="F53" s="220"/>
+      <c r="G53" s="220"/>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="71" t="s">
         <v>115</v>
       </c>
-      <c r="B54" s="216" t="s">
+      <c r="B54" s="218" t="s">
         <v>116</v>
       </c>
-      <c r="C54" s="216" t="s">
+      <c r="C54" s="218" t="s">
         <v>117</v>
       </c>
-      <c r="D54" s="218"/>
-      <c r="E54" s="218"/>
-      <c r="F54" s="218"/>
-      <c r="G54" s="218"/>
+      <c r="D54" s="220"/>
+      <c r="E54" s="220"/>
+      <c r="F54" s="220"/>
+      <c r="G54" s="220"/>
     </row>
     <row r="55" ht="65" spans="1:7">
       <c r="A55" s="71" t="s">
         <v>118</v>
       </c>
-      <c r="B55" s="218"/>
-      <c r="C55" s="218"/>
-      <c r="D55" s="216" t="s">
+      <c r="B55" s="220"/>
+      <c r="C55" s="220"/>
+      <c r="D55" s="218" t="s">
         <v>119</v>
       </c>
     </row>
@@ -5422,7 +5452,7 @@
         <v>121</v>
       </c>
       <c r="C56" s="78"/>
-      <c r="D56" s="216" t="s">
+      <c r="D56" s="218" t="s">
         <v>122</v>
       </c>
     </row>
@@ -5436,7 +5466,7 @@
       <c r="C57" s="78" t="s">
         <v>125</v>
       </c>
-      <c r="D57" s="216" t="s">
+      <c r="D57" s="218" t="s">
         <v>126</v>
       </c>
     </row>
@@ -5444,37 +5474,37 @@
       <c r="A58" s="71" t="s">
         <v>127</v>
       </c>
-      <c r="B58" s="216" t="s">
+      <c r="B58" s="218" t="s">
         <v>128</v>
       </c>
-      <c r="C58" s="218"/>
-      <c r="D58" s="218"/>
-      <c r="E58" s="218"/>
-      <c r="F58" s="218"/>
-      <c r="G58" s="218"/>
+      <c r="C58" s="220"/>
+      <c r="D58" s="220"/>
+      <c r="E58" s="220"/>
+      <c r="F58" s="220"/>
+      <c r="G58" s="220"/>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="B59" s="218"/>
-      <c r="C59" s="216" t="s">
+      <c r="B59" s="220"/>
+      <c r="C59" s="218" t="s">
         <v>130</v>
       </c>
-      <c r="D59" s="218"/>
-      <c r="E59" s="218"/>
-      <c r="F59" s="218"/>
-      <c r="G59" s="218"/>
+      <c r="D59" s="220"/>
+      <c r="E59" s="220"/>
+      <c r="F59" s="220"/>
+      <c r="G59" s="220"/>
     </row>
     <row r="60" ht="52" spans="1:7">
       <c r="A60" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="B60" s="218" t="s">
+      <c r="B60" s="220" t="s">
         <v>132</v>
       </c>
-      <c r="C60" s="218"/>
-      <c r="D60" s="216" t="s">
+      <c r="C60" s="220"/>
+      <c r="D60" s="218" t="s">
         <v>133</v>
       </c>
     </row>
@@ -5486,18 +5516,18 @@
         <v>135</v>
       </c>
       <c r="C61" s="78"/>
-      <c r="D61" s="218"/>
-      <c r="E61" s="218"/>
-      <c r="F61" s="218"/>
-      <c r="G61" s="218"/>
+      <c r="D61" s="220"/>
+      <c r="E61" s="220"/>
+      <c r="F61" s="220"/>
+      <c r="G61" s="220"/>
     </row>
     <row r="62" ht="39" spans="1:7">
       <c r="A62" s="71" t="s">
         <v>136</v>
       </c>
-      <c r="B62" s="218"/>
-      <c r="C62" s="218"/>
-      <c r="D62" s="216" t="s">
+      <c r="B62" s="220"/>
+      <c r="C62" s="220"/>
+      <c r="D62" s="218" t="s">
         <v>137</v>
       </c>
     </row>
@@ -5511,18 +5541,18 @@
       <c r="C63" s="78" t="s">
         <v>140</v>
       </c>
-      <c r="D63" s="218"/>
-      <c r="E63" s="218"/>
-      <c r="F63" s="218"/>
-      <c r="G63" s="218"/>
+      <c r="D63" s="220"/>
+      <c r="E63" s="220"/>
+      <c r="F63" s="220"/>
+      <c r="G63" s="220"/>
     </row>
     <row r="64" ht="26" spans="1:7">
       <c r="A64" s="71" t="s">
         <v>141</v>
       </c>
-      <c r="B64" s="218"/>
-      <c r="C64" s="218"/>
-      <c r="D64" s="216" t="s">
+      <c r="B64" s="220"/>
+      <c r="C64" s="220"/>
+      <c r="D64" s="218" t="s">
         <v>142</v>
       </c>
     </row>
@@ -5530,42 +5560,42 @@
       <c r="A65" s="71" t="s">
         <v>143</v>
       </c>
-      <c r="B65" s="220" t="s">
+      <c r="B65" s="222" t="s">
         <v>144</v>
       </c>
-      <c r="C65" s="218"/>
-      <c r="D65" s="218"/>
-      <c r="E65" s="218"/>
-      <c r="F65" s="218"/>
-      <c r="G65" s="218"/>
+      <c r="C65" s="220"/>
+      <c r="D65" s="220"/>
+      <c r="E65" s="220"/>
+      <c r="F65" s="220"/>
+      <c r="G65" s="220"/>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="71" t="s">
         <v>145</v>
       </c>
-      <c r="B66" s="218"/>
-      <c r="C66" s="216" t="s">
+      <c r="B66" s="220"/>
+      <c r="C66" s="218" t="s">
         <v>146</v>
       </c>
-      <c r="D66" s="218"/>
-      <c r="E66" s="218"/>
-      <c r="F66" s="218"/>
-      <c r="G66" s="218"/>
+      <c r="D66" s="220"/>
+      <c r="E66" s="220"/>
+      <c r="F66" s="220"/>
+      <c r="G66" s="220"/>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="71" t="s">
         <v>147</v>
       </c>
-      <c r="B67" s="218"/>
-      <c r="C67" s="218"/>
+      <c r="B67" s="220"/>
+      <c r="C67" s="220"/>
     </row>
     <row r="68" ht="65" spans="1:7">
       <c r="A68" s="71" t="s">
         <v>148</v>
       </c>
-      <c r="B68" s="218"/>
-      <c r="C68" s="218"/>
-      <c r="D68" s="216" t="s">
+      <c r="B68" s="220"/>
+      <c r="C68" s="220"/>
+      <c r="D68" s="218" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5586,45 +5616,45 @@
         <v>153</v>
       </c>
       <c r="C70" s="78"/>
-      <c r="D70" s="218"/>
-      <c r="E70" s="218"/>
-      <c r="F70" s="218"/>
-      <c r="G70" s="218"/>
+      <c r="D70" s="220"/>
+      <c r="E70" s="220"/>
+      <c r="F70" s="220"/>
+      <c r="G70" s="220"/>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="71" t="s">
         <v>154</v>
       </c>
-      <c r="B71" s="218"/>
-      <c r="C71" s="218"/>
+      <c r="B71" s="220"/>
+      <c r="C71" s="220"/>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="B72" s="216" t="s">
+      <c r="B72" s="218" t="s">
         <v>156</v>
       </c>
-      <c r="C72" s="216" t="s">
+      <c r="C72" s="218" t="s">
         <v>157</v>
       </c>
-      <c r="D72" s="218"/>
-      <c r="E72" s="218"/>
-      <c r="F72" s="218"/>
-      <c r="G72" s="218"/>
+      <c r="D72" s="220"/>
+      <c r="E72" s="220"/>
+      <c r="F72" s="220"/>
+      <c r="G72" s="220"/>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="71" t="s">
         <v>158</v>
       </c>
-      <c r="B73" s="218"/>
-      <c r="C73" s="216" t="s">
+      <c r="B73" s="220"/>
+      <c r="C73" s="218" t="s">
         <v>159</v>
       </c>
-      <c r="D73" s="218"/>
-      <c r="E73" s="218"/>
-      <c r="F73" s="218"/>
-      <c r="G73" s="218"/>
+      <c r="D73" s="220"/>
+      <c r="E73" s="220"/>
+      <c r="F73" s="220"/>
+      <c r="G73" s="220"/>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="71" t="s">
@@ -5635,18 +5665,18 @@
       <c r="A75" s="71" t="s">
         <v>161</v>
       </c>
-      <c r="D75" s="218"/>
-      <c r="E75" s="218"/>
-      <c r="F75" s="218"/>
-      <c r="G75" s="218"/>
+      <c r="D75" s="220"/>
+      <c r="E75" s="220"/>
+      <c r="F75" s="220"/>
+      <c r="G75" s="220"/>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="71" t="s">
         <v>162</v>
       </c>
-      <c r="B76" s="218"/>
-      <c r="C76" s="218"/>
-      <c r="D76" s="216" t="s">
+      <c r="B76" s="220"/>
+      <c r="C76" s="220"/>
+      <c r="D76" s="218" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5658,10 +5688,10 @@
       <c r="C77" s="78"/>
     </row>
     <row r="78" ht="26" spans="1:7">
-      <c r="A78" s="221" t="s">
+      <c r="A78" s="223" t="s">
         <v>165</v>
       </c>
-      <c r="B78" s="216" t="s">
+      <c r="B78" s="218" t="s">
         <v>166</v>
       </c>
     </row>
@@ -5715,16 +5745,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="67" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B1" s="68" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="69" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="D1" s="70" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5738,7 +5768,7 @@
         <v>20111216</v>
       </c>
       <c r="D2" s="66" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -5752,7 +5782,7 @@
         <v>20111227</v>
       </c>
       <c r="D3" s="66" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -5766,7 +5796,7 @@
         <v>20120518</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:4">
@@ -5794,7 +5824,7 @@
         <v>20120504</v>
       </c>
       <c r="D6" s="66" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -5808,7 +5838,7 @@
         <v>20120809</v>
       </c>
       <c r="D7" s="66" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -5822,7 +5852,7 @@
         <v>20120227</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -5836,7 +5866,7 @@
         <v>20120127</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -5850,7 +5880,7 @@
         <v>20111202</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:4">
@@ -5876,7 +5906,7 @@
         <v>20111024</v>
       </c>
       <c r="D12" s="66" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -5890,7 +5920,7 @@
         <v>20110908</v>
       </c>
       <c r="D13" s="66" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -5904,7 +5934,7 @@
         <v>20120228</v>
       </c>
       <c r="D14" s="66" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:4">
@@ -5930,7 +5960,7 @@
         <v>20111201</v>
       </c>
       <c r="D16" s="66" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -5944,7 +5974,7 @@
         <v>20120722</v>
       </c>
       <c r="D17" s="66" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:4">
@@ -5982,7 +6012,7 @@
         <v>20120530</v>
       </c>
       <c r="D20" s="66" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -5996,7 +6026,7 @@
         <v>20120827</v>
       </c>
       <c r="D21" s="66" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:4">
@@ -6022,7 +6052,7 @@
         <v>20120518</v>
       </c>
       <c r="D23" s="66" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -6036,7 +6066,7 @@
         <v>20120413</v>
       </c>
       <c r="D24" s="66" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -6050,7 +6080,7 @@
         <v>20120629</v>
       </c>
       <c r="D25" s="66" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -6064,7 +6094,7 @@
         <v>20111105</v>
       </c>
       <c r="D26" s="66" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -6078,7 +6108,7 @@
         <v>20120112</v>
       </c>
       <c r="D27" s="66" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -6092,7 +6122,7 @@
         <v>20111119</v>
       </c>
       <c r="D28" s="66" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:4">
@@ -6118,7 +6148,7 @@
         <v>20120331</v>
       </c>
       <c r="D30" s="66" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -6132,7 +6162,7 @@
         <v>20111109</v>
       </c>
       <c r="D31" s="66" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -6146,7 +6176,7 @@
         <v>20120824</v>
       </c>
       <c r="D32" s="66" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:5">
@@ -6172,7 +6202,7 @@
         <v>20120624</v>
       </c>
       <c r="D34" s="66" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:5">
@@ -6198,7 +6228,7 @@
         <v>20120603</v>
       </c>
       <c r="D36" s="66" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -6212,7 +6242,7 @@
         <v>20120326</v>
       </c>
       <c r="D37" s="66" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -6226,10 +6256,10 @@
         <v>20111106</v>
       </c>
       <c r="D38" s="77" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="E38" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -6243,7 +6273,7 @@
         <v>20120811</v>
       </c>
       <c r="D39" s="78" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -6257,7 +6287,7 @@
         <v>20111217</v>
       </c>
       <c r="D40" s="78" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -6271,10 +6301,10 @@
         <v>20111013</v>
       </c>
       <c r="D41" s="66" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="E41" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:5">
@@ -6300,7 +6330,7 @@
         <v>20120207</v>
       </c>
       <c r="D43" s="66" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:5">
@@ -6326,7 +6356,7 @@
         <v>20110929</v>
       </c>
       <c r="D45" s="66" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:5">
@@ -6352,10 +6382,10 @@
         <v>20120108</v>
       </c>
       <c r="D47" s="66" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="E47" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -6369,7 +6399,7 @@
         <v>20120311</v>
       </c>
       <c r="D48" s="66" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:4">
@@ -6395,7 +6425,7 @@
         <v>20120723</v>
       </c>
       <c r="D50" s="66" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:4">
@@ -6421,7 +6451,7 @@
         <v>20111220</v>
       </c>
       <c r="D52" s="66" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>
@@ -6454,34 +6484,34 @@
   <sheetData>
     <row r="1" s="27" customFormat="1" spans="1:5">
       <c r="A1" s="34" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="D1" s="37"/>
       <c r="E1" s="38" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
     </row>
     <row r="2" s="28" customFormat="1" ht="409" customHeight="1" spans="1:5">
       <c r="A2" s="39" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B2" s="40" t="s">
         <v>233</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
     </row>
     <row r="3" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6489,10 +6519,10 @@
       <c r="B3" s="43"/>
       <c r="C3" s="44"/>
       <c r="D3" s="32" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
     </row>
     <row r="4" s="28" customFormat="1" spans="1:5">
@@ -6500,10 +6530,10 @@
       <c r="B4" s="43"/>
       <c r="C4" s="44"/>
       <c r="D4" s="32" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
     </row>
     <row r="5" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6511,10 +6541,10 @@
       <c r="B5" s="43"/>
       <c r="C5" s="44"/>
       <c r="D5" s="32" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
     </row>
     <row r="6" s="28" customFormat="1" ht="238" spans="1:5">
@@ -6522,23 +6552,23 @@
       <c r="B6" s="43"/>
       <c r="C6" s="44"/>
       <c r="D6" s="32" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
     </row>
     <row r="7" s="28" customFormat="1" ht="238" spans="1:5">
       <c r="A7" s="42"/>
       <c r="B7" s="43"/>
       <c r="C7" s="41" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6546,10 +6576,10 @@
       <c r="B8" s="43"/>
       <c r="C8" s="44"/>
       <c r="D8" s="32" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9" s="28" customFormat="1" ht="84" spans="1:5">
@@ -6557,10 +6587,10 @@
       <c r="B9" s="43"/>
       <c r="C9" s="44"/>
       <c r="D9" s="32" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="10" s="28" customFormat="1" ht="28" spans="1:5">
@@ -6568,10 +6598,10 @@
       <c r="B10" s="43"/>
       <c r="C10" s="44"/>
       <c r="D10" s="32" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
     </row>
     <row r="11" s="28" customFormat="1" spans="1:5">
@@ -6579,10 +6609,10 @@
       <c r="B11" s="43"/>
       <c r="C11" s="45"/>
       <c r="D11" s="32" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
     </row>
     <row r="12" s="28" customFormat="1" ht="154" spans="1:5">
@@ -6590,50 +6620,50 @@
       <c r="B12" s="43"/>
       <c r="C12" s="31"/>
       <c r="D12" s="32" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
     </row>
     <row r="13" s="28" customFormat="1" ht="56" spans="1:5">
       <c r="A13" s="42"/>
       <c r="B13" s="43"/>
       <c r="C13" s="46" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="33" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
     </row>
     <row r="14" s="28" customFormat="1" ht="84" spans="1:5">
       <c r="A14" s="42"/>
       <c r="B14" s="43"/>
       <c r="C14" s="46" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="33" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
     </row>
     <row r="15" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A15" s="42"/>
       <c r="B15" s="43"/>
       <c r="C15" s="46" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="D15" s="37"/>
       <c r="E15" s="33" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
     </row>
     <row r="16" s="28" customFormat="1" spans="1:5">
       <c r="A16" s="42"/>
       <c r="B16" s="43"/>
       <c r="C16" s="46" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="D16" s="37"/>
       <c r="E16" s="33"/>
@@ -6642,24 +6672,24 @@
       <c r="A17" s="42"/>
       <c r="B17" s="43"/>
       <c r="C17" s="46" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="33" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
     </row>
     <row r="18" s="28" customFormat="1" spans="1:5">
       <c r="A18" s="42"/>
       <c r="B18" s="43"/>
       <c r="C18" s="41" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
     </row>
     <row r="19" s="28" customFormat="1" spans="1:5">
@@ -6667,17 +6697,17 @@
       <c r="B19" s="43"/>
       <c r="C19" s="45"/>
       <c r="D19" s="32" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
     </row>
     <row r="20" s="28" customFormat="1" spans="1:5">
       <c r="A20" s="42"/>
       <c r="B20" s="43"/>
       <c r="C20" s="46" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="D20" s="37"/>
       <c r="E20" s="33"/>
@@ -6686,61 +6716,61 @@
       <c r="A21" s="42"/>
       <c r="B21" s="43"/>
       <c r="C21" s="46" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="D21" s="37"/>
       <c r="E21" s="33" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
     </row>
     <row r="22" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A22" s="42"/>
       <c r="B22" s="43"/>
       <c r="C22" s="46" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="D22" s="47"/>
       <c r="E22" s="33" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
     </row>
     <row r="23" s="28" customFormat="1" spans="1:5">
       <c r="A23" s="42"/>
       <c r="B23" s="43"/>
       <c r="C23" s="31" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="D23" s="31"/>
       <c r="E23" s="33" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
     </row>
     <row r="24" s="28" customFormat="1" spans="1:5">
       <c r="A24" s="42"/>
       <c r="B24" s="43"/>
       <c r="C24" s="31" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="D24" s="31"/>
       <c r="E24" s="33" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
     </row>
     <row r="25" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A25" s="39" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
     </row>
     <row r="26" s="28" customFormat="1" spans="1:5">
@@ -6748,10 +6778,10 @@
       <c r="B26" s="43"/>
       <c r="C26" s="44"/>
       <c r="D26" s="32" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
     </row>
     <row r="27" s="28" customFormat="1" ht="28" spans="1:5">
@@ -6759,10 +6789,10 @@
       <c r="B27" s="43"/>
       <c r="C27" s="44"/>
       <c r="D27" s="32" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
     </row>
     <row r="28" s="28" customFormat="1" ht="42" spans="1:5">
@@ -6770,27 +6800,27 @@
       <c r="B28" s="43"/>
       <c r="C28" s="44"/>
       <c r="D28" s="32" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
     </row>
     <row r="29" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A29" s="39" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
     </row>
     <row r="30" s="28" customFormat="1" ht="70" spans="1:5">
@@ -6798,10 +6828,10 @@
       <c r="B30" s="43"/>
       <c r="C30" s="44"/>
       <c r="D30" s="32" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
     </row>
     <row r="31" s="28" customFormat="1" spans="1:5">
@@ -6809,10 +6839,10 @@
       <c r="B31" s="43"/>
       <c r="C31" s="44"/>
       <c r="D31" s="32" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
     </row>
     <row r="32" s="28" customFormat="1" ht="28" spans="1:5">
@@ -6820,53 +6850,53 @@
       <c r="B32" s="43"/>
       <c r="C32" s="45"/>
       <c r="D32" s="32" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
     </row>
     <row r="33" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A33" s="42"/>
       <c r="B33" s="49"/>
       <c r="C33" s="46" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="D33" s="47"/>
       <c r="E33" s="33" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
     </row>
     <row r="34" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A34" s="42"/>
       <c r="B34" s="50" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="D34" s="51"/>
       <c r="E34" s="52" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
     </row>
     <row r="35" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A35" s="53"/>
       <c r="B35" s="54"/>
       <c r="C35" s="36" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="D35" s="51"/>
       <c r="E35" s="52" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
     </row>
     <row r="36" s="28" customFormat="1" spans="1:5">
       <c r="A36" s="39" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="B36" s="55" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="C36" s="56"/>
       <c r="D36" s="57"/>
@@ -6877,42 +6907,42 @@
     <row r="37" s="28" customFormat="1" spans="1:5">
       <c r="A37" s="53"/>
       <c r="B37" s="58" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="C37" s="59"/>
       <c r="D37" s="60"/>
       <c r="E37" s="33" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
     </row>
     <row r="38" s="28" customFormat="1" spans="1:5">
       <c r="A38" s="29" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="B38" s="58" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="C38" s="59"/>
       <c r="D38" s="60"/>
       <c r="E38" s="33" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
     </row>
     <row r="39" s="28" customFormat="1" spans="1:5">
       <c r="A39" s="39" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="B39" s="40" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="C39" s="41" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
     </row>
     <row r="40" s="28" customFormat="1" spans="1:5">
@@ -6920,64 +6950,64 @@
       <c r="B40" s="43"/>
       <c r="C40" s="45"/>
       <c r="D40" s="32" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="E40" s="33" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
     </row>
     <row r="41" s="28" customFormat="1" spans="1:5">
       <c r="A41" s="42"/>
       <c r="B41" s="43"/>
       <c r="C41" s="46" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="D41" s="47"/>
       <c r="E41" s="33" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
     </row>
     <row r="42" s="28" customFormat="1" spans="1:5">
       <c r="A42" s="53"/>
       <c r="B42" s="49"/>
       <c r="C42" s="46" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="D42" s="47"/>
       <c r="E42" s="33" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
     </row>
     <row r="43" s="28" customFormat="1" spans="1:5">
       <c r="A43" s="39" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="B43" s="50" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="C43" s="61" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="D43" s="62"/>
       <c r="E43" s="52" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
     </row>
     <row r="44" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A44" s="42"/>
       <c r="B44" s="54"/>
       <c r="C44" s="61" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="D44" s="62"/>
       <c r="E44" s="52" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
     </row>
     <row r="45" s="28" customFormat="1" spans="1:5">
       <c r="A45" s="53"/>
       <c r="B45" s="58" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="C45" s="59"/>
       <c r="D45" s="60"/>
@@ -6987,16 +7017,16 @@
     </row>
     <row r="46" s="28" customFormat="1" spans="1:5">
       <c r="A46" s="39" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="B46" s="40" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="C46" s="41" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="E46" s="33"/>
     </row>
@@ -7005,7 +7035,7 @@
       <c r="B47" s="43"/>
       <c r="C47" s="44"/>
       <c r="D47" s="32" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="E47" s="33"/>
     </row>
@@ -7014,42 +7044,42 @@
       <c r="B48" s="49"/>
       <c r="C48" s="45"/>
       <c r="D48" s="32" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="49" s="28" customFormat="1" spans="1:5">
       <c r="A49" s="29" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="B49" s="58" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C49" s="59"/>
       <c r="D49" s="60"/>
       <c r="E49" s="33" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="50" s="28" customFormat="1" spans="1:5">
       <c r="A50" s="39" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B50" s="58" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="C50" s="59"/>
       <c r="D50" s="60"/>
       <c r="E50" s="33" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
     </row>
     <row r="51" s="28" customFormat="1" spans="1:5">
       <c r="A51" s="53"/>
       <c r="B51" s="58" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="C51" s="59"/>
       <c r="D51" s="60"/>
@@ -7059,10 +7089,10 @@
     </row>
     <row r="52" s="28" customFormat="1" spans="1:5">
       <c r="A52" s="29" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B52" s="58" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="C52" s="59"/>
       <c r="D52" s="60"/>
@@ -7070,10 +7100,10 @@
     </row>
     <row r="53" s="28" customFormat="1" spans="1:5">
       <c r="A53" s="39" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="B53" s="58" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="C53" s="59"/>
       <c r="D53" s="60"/>
@@ -7085,18 +7115,18 @@
       <c r="C54" s="59"/>
       <c r="D54" s="60"/>
       <c r="E54" s="33" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
     </row>
     <row r="55" s="28" customFormat="1" spans="1:5">
       <c r="A55" s="29" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="B55" s="30"/>
       <c r="C55" s="31"/>
       <c r="D55" s="32"/>
       <c r="E55" s="33" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
     </row>
   </sheetData>
@@ -7204,7 +7234,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
@@ -7218,7 +7248,7 @@
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="9" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="11"/>
@@ -7242,7 +7272,7 @@
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="9" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="11"/>
@@ -7255,7 +7285,7 @@
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="22" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="11"/>
@@ -7268,7 +7298,7 @@
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="9" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="11"/>
@@ -7302,7 +7332,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="10"/>
@@ -7348,7 +7378,7 @@
         <v>31</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="10"/>
@@ -7384,7 +7414,7 @@
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="22" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="11"/>
@@ -7418,10 +7448,10 @@
         <v>42</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="11"/>
@@ -7433,10 +7463,10 @@
         <v>45</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="11"/>
@@ -7459,7 +7489,7 @@
         <v>50</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="10"/>
@@ -7472,10 +7502,10 @@
         <v>52</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="11"/>
@@ -7509,10 +7539,10 @@
         <v>58</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="11"/>
@@ -7524,10 +7554,10 @@
         <v>61</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="11"/>
@@ -7551,7 +7581,7 @@
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="22" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="11"/>
@@ -7618,7 +7648,7 @@
         <v>74</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="10"/>
@@ -7632,7 +7662,7 @@
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="22" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="11"/>
@@ -7644,7 +7674,7 @@
         <v>79</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="C38" s="25"/>
       <c r="D38" s="26"/>
@@ -7658,7 +7688,7 @@
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="22" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="11"/>
@@ -7670,10 +7700,10 @@
         <v>84</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="11"/>
@@ -7686,7 +7716,7 @@
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="22" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="D41" s="10"/>
       <c r="E41" s="11"/>
@@ -7709,7 +7739,7 @@
         <v>93</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="10"/>
@@ -7733,7 +7763,7 @@
         <v>97</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="10"/>
@@ -7769,7 +7799,7 @@
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="22" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="D48" s="10"/>
       <c r="E48" s="11"/>
@@ -7793,7 +7823,7 @@
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="22" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="D50" s="10"/>
       <c r="E50" s="11"/>
@@ -7816,10 +7846,10 @@
         <v>110</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="D52" s="10"/>
       <c r="E52" s="11"/>
@@ -7855,27 +7885,27 @@
   <sheetData>
     <row r="1" spans="2:6">
       <c r="B1" s="3" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
     </row>
     <row r="2" spans="2:6">
       <c r="B2" s="4" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="C2" s="4">
         <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="F2" s="4">
         <v>6</v>
@@ -7883,13 +7913,13 @@
     </row>
     <row r="3" spans="2:6">
       <c r="B3" s="4" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="C3" s="4">
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="F3" s="4">
         <v>13</v>
@@ -7897,13 +7927,13 @@
     </row>
     <row r="4" spans="2:6">
       <c r="B4" s="4" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="C4" s="4">
         <v>12</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="F4" s="4">
         <v>4</v>
@@ -7911,13 +7941,13 @@
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="4" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="C5" s="4">
         <v>2</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="F5" s="4">
         <v>6</v>
@@ -7925,13 +7955,13 @@
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="4" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="C6" s="4">
         <v>2</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="F6" s="4">
         <v>4</v>
@@ -7939,13 +7969,13 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="4" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="C7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
@@ -7953,13 +7983,13 @@
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="4" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="C8" s="4">
         <v>4</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="F8" s="4">
         <v>3</v>
@@ -7967,7 +7997,7 @@
     </row>
     <row r="9" spans="2:6">
       <c r="E9" s="4" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -7975,7 +8005,7 @@
     </row>
     <row r="10" spans="2:6">
       <c r="E10" s="4" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="F10" s="4">
         <v>5</v>
@@ -7983,7 +8013,7 @@
     </row>
     <row r="11" spans="2:6">
       <c r="E11" s="4" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -7991,7 +8021,7 @@
     </row>
     <row r="12" spans="2:6">
       <c r="E12" s="4" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="F12" s="4">
         <v>2</v>
@@ -8011,14 +8041,14 @@
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6.64545454545455" style="210" customWidth="1"/>
+    <col min="1" max="1" width="6.64545454545455" style="212" customWidth="1"/>
     <col min="2" max="2" width="32.6181818181818" style="66" customWidth="1"/>
     <col min="3" max="7" width="16.4909090909091" style="66" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="211"/>
+    <col min="8" max="16384" width="8.72727272727273" style="213"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="212"/>
+      <c r="A1" s="214"/>
       <c r="B1" s="70" t="s">
         <v>1</v>
       </c>
@@ -8038,8 +8068,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="209" customFormat="1" ht="39" spans="1:7">
-      <c r="A2" s="213" t="s">
+    <row r="2" s="211" customFormat="1" ht="39" spans="1:7">
+      <c r="A2" s="215" t="s">
         <v>167</v>
       </c>
       <c r="B2" s="78"/>
@@ -8052,7 +8082,7 @@
       <c r="G2" s="78"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="214" t="s">
+      <c r="A3" s="216" t="s">
         <v>169</v>
       </c>
       <c r="C3" s="66" t="s">
@@ -8060,7 +8090,7 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="214" t="s">
+      <c r="A4" s="216" t="s">
         <v>171</v>
       </c>
       <c r="B4" s="66" t="s">
@@ -8071,7 +8101,7 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="214" t="s">
+      <c r="A5" s="216" t="s">
         <v>174</v>
       </c>
       <c r="C5" s="66" t="s">
@@ -8082,7 +8112,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="214" t="s">
+      <c r="A6" s="216" t="s">
         <v>177</v>
       </c>
       <c r="B6" s="66" t="s">
@@ -8093,7 +8123,7 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="214" t="s">
+      <c r="A7" s="216" t="s">
         <v>180</v>
       </c>
       <c r="B7" s="66" t="s">
@@ -8101,112 +8131,112 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="214"/>
+      <c r="A8" s="216"/>
       <c r="D8" s="66" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="214"/>
+      <c r="A9" s="216"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="214"/>
+      <c r="A10" s="216"/>
       <c r="B10" s="66" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="214"/>
+      <c r="A11" s="216"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="214"/>
+      <c r="A12" s="216"/>
       <c r="B12" s="66" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="214"/>
+      <c r="A13" s="216"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="214"/>
+      <c r="A14" s="216"/>
       <c r="B14" s="66" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="214"/>
+      <c r="A15" s="216"/>
       <c r="B15" s="66" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="214"/>
+      <c r="A16" s="216"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="214"/>
+      <c r="A17" s="216"/>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="214"/>
+      <c r="A18" s="216"/>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="214"/>
+      <c r="A19" s="216"/>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="214"/>
+      <c r="A20" s="216"/>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="214"/>
+      <c r="A21" s="216"/>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="214"/>
+      <c r="A22" s="216"/>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="214"/>
+      <c r="A23" s="216"/>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="214"/>
+      <c r="A24" s="216"/>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="214"/>
+      <c r="A25" s="216"/>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="214"/>
+      <c r="A26" s="216"/>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="214"/>
+      <c r="A27" s="216"/>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="214"/>
+      <c r="A28" s="216"/>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="214"/>
+      <c r="A29" s="216"/>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="214"/>
+      <c r="A30" s="216"/>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="214"/>
+      <c r="A31" s="216"/>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="214"/>
+      <c r="A32" s="216"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="214"/>
+      <c r="A33" s="216"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="214"/>
+      <c r="A34" s="216"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="214"/>
+      <c r="A35" s="216"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="214"/>
+      <c r="A36" s="216"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="214"/>
+      <c r="A37" s="216"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="214"/>
+      <c r="A38" s="216"/>
       <c r="B38" s="78"/>
       <c r="C38" s="78"/>
       <c r="D38" s="78"/>
@@ -8215,7 +8245,7 @@
       <c r="G38" s="78"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="214"/>
+      <c r="A39" s="216"/>
       <c r="B39" s="78"/>
       <c r="C39" s="78"/>
       <c r="D39" s="78"/>
@@ -8224,40 +8254,40 @@
       <c r="G39" s="78"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="214"/>
+      <c r="A40" s="216"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="214"/>
+      <c r="A41" s="216"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="214"/>
+      <c r="A42" s="216"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="214"/>
+      <c r="A43" s="216"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="214"/>
+      <c r="A44" s="216"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="214"/>
+      <c r="A45" s="216"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="214"/>
+      <c r="A46" s="216"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="214"/>
+      <c r="A47" s="216"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="214"/>
+      <c r="A48" s="216"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="214"/>
+      <c r="A49" s="216"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="214"/>
+      <c r="A50" s="216"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="214"/>
+      <c r="A51" s="216"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8270,7 +8300,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.8"/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="24" style="200" customWidth="1"/>
@@ -8544,7 +8574,7 @@
       </c>
     </row>
     <row r="29" ht="28" spans="1:3">
-      <c r="A29" s="202" t="s">
+      <c r="A29" s="209" t="s">
         <v>45</v>
       </c>
       <c r="B29" s="202" t="s">
@@ -8554,36 +8584,68 @@
         <v>241</v>
       </c>
     </row>
-    <row r="30" ht="98" spans="1:3">
-      <c r="A30" s="200" t="s">
+    <row r="30" spans="1:3">
+      <c r="A30" s="210"/>
+      <c r="B30" s="200" t="s">
         <v>242</v>
-      </c>
-      <c r="B30" s="200" t="s">
-        <v>210</v>
       </c>
       <c r="C30" s="200" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" ht="98" spans="1:3">
       <c r="A31" s="200" t="s">
-        <v>36</v>
+        <v>244</v>
       </c>
       <c r="B31" s="200" t="s">
-        <v>244</v>
+        <v>210</v>
       </c>
       <c r="C31" s="200" t="s">
         <v>245</v>
       </c>
     </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="200" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="200" t="s">
+        <v>246</v>
+      </c>
+      <c r="C32" s="200" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="33" ht="28" spans="1:3">
+      <c r="A33" s="200" t="s">
+        <v>248</v>
+      </c>
+      <c r="B33" s="200" t="s">
+        <v>242</v>
+      </c>
+      <c r="C33" s="200" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="200" t="s">
+        <v>250</v>
+      </c>
+      <c r="B34" s="200" t="s">
+        <v>215</v>
+      </c>
+      <c r="C34" s="200" t="s">
+        <v>251</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A8:A17"/>
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A29:A30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -8610,14 +8672,14 @@
   <sheetData>
     <row r="1" s="186" customFormat="1" ht="15" spans="1:7">
       <c r="A1" s="189" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B1" s="190"/>
       <c r="C1" s="190"/>
       <c r="D1" s="191"/>
       <c r="E1" s="192"/>
       <c r="F1" s="186" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2" s="187" customFormat="1" spans="1:7">
@@ -8626,17 +8688,17 @@
       </c>
       <c r="B2" s="194"/>
       <c r="C2" s="187" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="D2" s="187" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="E2" s="141"/>
       <c r="F2" s="187" t="s">
         <v>188</v>
       </c>
       <c r="G2" s="187" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -8651,10 +8713,10 @@
       </c>
       <c r="D3" s="119"/>
       <c r="F3" s="119" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="G3" s="119" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -8666,8 +8728,12 @@
         <v>163</v>
       </c>
       <c r="D4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
+      <c r="F4" s="119" t="s">
+        <v>259</v>
+      </c>
+      <c r="G4" s="119" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="196"/>
@@ -8829,7 +8895,7 @@
   <sheetData>
     <row r="1" spans="1:39">
       <c r="A1" s="174" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B1" s="175">
         <v>45992</v>
@@ -8867,7 +8933,7 @@
       <c r="AE1" s="176"/>
       <c r="AF1" s="176"/>
       <c r="AG1" s="143" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="AH1" s="146"/>
       <c r="AI1" s="146"/>
@@ -8972,25 +9038,25 @@
         <v>20</v>
       </c>
       <c r="AG2" s="178" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="AH2" s="178" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="AI2" s="178" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="AJ2" s="178" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="AK2" s="179" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="AL2" s="179" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="AM2" s="179" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:39">
@@ -9338,7 +9404,7 @@
       </c>
       <c r="AK7" s="183">
         <f t="shared" ref="AK7:AM7" si="4">RANK(AG7,AG$3:AG$53,0)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL7" s="183">
         <f t="shared" si="4"/>
@@ -9630,7 +9696,9 @@
       <c r="X11" s="120"/>
       <c r="Y11" s="120"/>
       <c r="Z11" s="120"/>
-      <c r="AA11" s="120"/>
+      <c r="AA11" s="120">
+        <v>1</v>
+      </c>
       <c r="AB11" s="120"/>
       <c r="AC11" s="120"/>
       <c r="AD11" s="120"/>
@@ -9638,11 +9706,11 @@
       <c r="AF11" s="120"/>
       <c r="AG11" s="180">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH11" s="181" cm="1">
         <f t="array" ref="AH11">SUMPRODUCT(--(B11:AF11=INT(B11:AF11)),--(B11:AF11&gt;0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI11" s="181" cm="1">
         <f t="array" ref="AI11">MAX(FREQUENCY(IF((B11:AF11=INT(B11:AF11))*(B11:AF11&gt;0),COLUMN(B11:AF11)),IF((B11:AF11&lt;&gt;INT(B11:AF11))+(B11:AF11&lt;=0),COLUMN(B11:AF11))))</f>
@@ -9650,15 +9718,15 @@
       </c>
       <c r="AJ11" s="182" cm="1">
         <f t="array" ref="AJ11">SUMPRODUCT(--(B11:AF11=INT(B11:AF11)),--(B11:AF11&gt;0))/30*100%</f>
-        <v>0.133333333333333</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="AK11" s="183">
         <f t="shared" ref="AK11:AM11" si="8">RANK(AG11,AG$3:AG$53,0)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL11" s="183">
         <f t="shared" si="8"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM11" s="183">
         <f t="shared" si="8"/>
@@ -9776,7 +9844,9 @@
         <v>1</v>
       </c>
       <c r="Z13" s="120"/>
-      <c r="AA13" s="120"/>
+      <c r="AA13" s="120">
+        <v>1</v>
+      </c>
       <c r="AB13" s="120"/>
       <c r="AC13" s="120"/>
       <c r="AD13" s="120"/>
@@ -9784,11 +9854,11 @@
       <c r="AF13" s="120"/>
       <c r="AG13" s="180">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH13" s="181" cm="1">
         <f t="array" ref="AH13">SUMPRODUCT(--(B13:AF13=INT(B13:AF13)),--(B13:AF13&gt;0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI13" s="181" cm="1">
         <f t="array" ref="AI13">MAX(FREQUENCY(IF((B13:AF13=INT(B13:AF13))*(B13:AF13&gt;0),COLUMN(B13:AF13)),IF((B13:AF13&lt;&gt;INT(B13:AF13))+(B13:AF13&lt;=0),COLUMN(B13:AF13))))</f>
@@ -9796,15 +9866,15 @@
       </c>
       <c r="AJ13" s="182" cm="1">
         <f t="array" ref="AJ13">SUMPRODUCT(--(B13:AF13=INT(B13:AF13)),--(B13:AF13&gt;0))/30*100%</f>
-        <v>0.233333333333333</v>
+        <v>0.266666666666667</v>
       </c>
       <c r="AK13" s="183">
         <f t="shared" ref="AK13:AM13" si="10">RANK(AG13,AG$3:AG$53,0)</f>
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AL13" s="183">
         <f t="shared" si="10"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AM13" s="183">
         <f t="shared" si="10"/>
@@ -9922,7 +9992,9 @@
         <v>1</v>
       </c>
       <c r="Z15" s="120"/>
-      <c r="AA15" s="120"/>
+      <c r="AA15" s="120">
+        <v>1</v>
+      </c>
       <c r="AB15" s="120"/>
       <c r="AC15" s="120"/>
       <c r="AD15" s="120"/>
@@ -9930,11 +10002,11 @@
       <c r="AF15" s="120"/>
       <c r="AG15" s="180">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH15" s="181" cm="1">
         <f t="array" ref="AH15">SUMPRODUCT(--(B15:AF15=INT(B15:AF15)),--(B15:AF15&gt;0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI15" s="181" cm="1">
         <f t="array" ref="AI15">MAX(FREQUENCY(IF((B15:AF15=INT(B15:AF15))*(B15:AF15&gt;0),COLUMN(B15:AF15)),IF((B15:AF15&lt;&gt;INT(B15:AF15))+(B15:AF15&lt;=0),COLUMN(B15:AF15))))</f>
@@ -9942,15 +10014,15 @@
       </c>
       <c r="AJ15" s="182" cm="1">
         <f t="array" ref="AJ15">SUMPRODUCT(--(B15:AF15=INT(B15:AF15)),--(B15:AF15&gt;0))/30*100%</f>
-        <v>0.233333333333333</v>
+        <v>0.266666666666667</v>
       </c>
       <c r="AK15" s="183">
         <f t="shared" ref="AK15:AM15" si="12">RANK(AG15,AG$3:AG$53,0)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL15" s="183">
         <f t="shared" si="12"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AM15" s="183">
         <f t="shared" si="12"/>
@@ -10584,7 +10656,7 @@
       </c>
       <c r="AK24" s="183">
         <f t="shared" ref="AK24:AM24" si="21">RANK(AG24,AG$3:AG$53,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL24" s="183">
         <f t="shared" si="21"/>
@@ -10858,7 +10930,7 @@
       </c>
       <c r="AK28" s="183">
         <f t="shared" ref="AK28:AM28" si="25">RANK(AG28,AG$3:AG$53,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL28" s="183">
         <f t="shared" si="25"/>
@@ -10930,11 +11002,11 @@
       </c>
       <c r="AK29" s="183">
         <f t="shared" ref="AK29:AM29" si="26">RANK(AG29,AG$3:AG$53,0)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL29" s="183">
         <f t="shared" si="26"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM29" s="183">
         <f t="shared" si="26"/>
@@ -11008,11 +11080,11 @@
       </c>
       <c r="AK30" s="183">
         <f t="shared" ref="AK30:AM30" si="27">RANK(AG30,AG$3:AG$53,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL30" s="183">
         <f t="shared" si="27"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AM30" s="183">
         <f t="shared" si="27"/>
@@ -11086,11 +11158,11 @@
       </c>
       <c r="AK31" s="183">
         <f t="shared" ref="AK31:AM31" si="28">RANK(AG31,AG$3:AG$53,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL31" s="183">
         <f t="shared" si="28"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AM31" s="183">
         <f t="shared" si="28"/>
@@ -11508,7 +11580,7 @@
       </c>
       <c r="AK37" s="183">
         <f t="shared" ref="AK37:AM37" si="35">RANK(AG37,AG$3:AG$53,0)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL37" s="183">
         <f t="shared" si="35"/>
@@ -11714,7 +11786,9 @@
       <c r="Z40" s="120">
         <v>1</v>
       </c>
-      <c r="AA40" s="120"/>
+      <c r="AA40" s="120">
+        <v>1</v>
+      </c>
       <c r="AB40" s="120"/>
       <c r="AC40" s="120"/>
       <c r="AD40" s="120"/>
@@ -11722,19 +11796,19 @@
       <c r="AF40" s="120"/>
       <c r="AG40" s="180">
         <f t="shared" si="33"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH40" s="181" cm="1">
         <f t="array" ref="AH40">SUMPRODUCT(--(B40:AF40=INT(B40:AF40)),--(B40:AF40&gt;0))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI40" s="181" cm="1">
         <f t="array" ref="AI40">MAX(FREQUENCY(IF((B40:AF40=INT(B40:AF40))*(B40:AF40&gt;0),COLUMN(B40:AF40)),IF((B40:AF40&lt;&gt;INT(B40:AF40))+(B40:AF40&lt;=0),COLUMN(B40:AF40))))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ40" s="182" cm="1">
         <f t="array" ref="AJ40">SUMPRODUCT(--(B40:AF40=INT(B40:AF40)),--(B40:AF40&gt;0))/30*100%</f>
-        <v>0.566666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="AK40" s="183">
         <f t="shared" ref="AK40:AM40" si="38">RANK(AG40,AG$3:AG$53,0)</f>
@@ -11814,7 +11888,7 @@
       </c>
       <c r="AK41" s="183">
         <f t="shared" ref="AK41:AM41" si="39">RANK(AG41,AG$3:AG$53,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL41" s="183">
         <f t="shared" si="39"/>
@@ -13022,7 +13096,7 @@
   <pageSetup paperSize="9" scale="80" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A28:X33 Z28:AM33 A34:AM35 A36:X36 Z36:AM36 A37:AM37 A38:X38 Z38:AM38 A39:AM39 A42:X42 Z41:AM42 AA40:AM40 A43:AM43 A44:W44 Z44:AM44 A45:AM45 A46:X46 AA46:AM46 A47:AM47 A48:X49 Z48:AM49 A50:AM53 X41 A40:V41 A9:X10 Z9:AM10 A11:AM11 A12:X15 Z12:AM15 A16:AM16 A17:X18 Z17:AM18 A19:AM21 A22:X22 AA22:AM22 A23:AM23 A24:X25 Z24:AM25 A26:AM27 X8:AM8 A8:V8 A1:AM2 A3:X4 Z3:AM4 A5:AM7" formulaRange="1" unlockedFormula="1"/>
+    <ignoredError sqref="A5:AM7 Z3:AM4 A3:X4 A1:AM2 A8:V8 X8:AM8 A26:AM27 Z24:AM25 A24:X25 A23:AM23 AA22:AM22 A22:X22 A19:AM21 Z17:AM18 A17:X18 A16:AM16 Z12:AM12 Z13 AB13:AM13 Z14:AM14 Z15 AB15:AM15 A12:X15 A11:Z11 AB11:AM11 Z9:AM10 A9:X10 A40:V41 X41 A50:AM53 Z48:AM49 A48:X49 A47:AM47 AA46:AM46 A46:X46 A45:AM45 Z44:AM44 A44:W44 A43:AM43 AB40:AM40 Z41:AM42 A42:X42 A39:AM39 Z38:AM38 A38:X38 A37:AM37 Z36:AM36 A36:X36 A34:AM35 Z28:AM33 A28:X33" formulaRange="1" unlockedFormula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -13069,21 +13143,21 @@
     </row>
     <row r="2" ht="16.5" spans="1:10">
       <c r="A2" s="148" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="B2" s="152" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="C2" s="153" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D2" s="154"/>
       <c r="E2" s="152" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="F2" s="152"/>
       <c r="G2" s="155" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="H2" s="147"/>
       <c r="I2" s="147"/>
@@ -13091,10 +13165,10 @@
     </row>
     <row r="3" ht="16.5" spans="1:10">
       <c r="A3" s="148" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="B3" s="157" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C3" s="157"/>
       <c r="D3" s="157"/>
@@ -13107,7 +13181,7 @@
     </row>
     <row r="4" ht="16.5" spans="1:10">
       <c r="A4" s="148" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B4" s="158" t="s">
         <v>233</v>
@@ -13123,7 +13197,7 @@
     </row>
     <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="148" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="B5" s="159">
         <v>1</v>
@@ -13143,7 +13217,7 @@
     </row>
     <row r="6" ht="16.5" spans="1:10">
       <c r="A6" s="148" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="B6" s="161">
         <v>1</v>
@@ -13153,7 +13227,7 @@
       <c r="E6" s="161"/>
       <c r="F6" s="161"/>
       <c r="G6" s="162" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="H6" s="147"/>
       <c r="I6" s="147"/>
@@ -13161,10 +13235,10 @@
     </row>
     <row r="7" ht="16.5" spans="1:10">
       <c r="A7" s="148" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="B7" s="163" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="C7" s="163"/>
       <c r="D7" s="163"/>
@@ -13179,14 +13253,14 @@
     </row>
     <row r="8" ht="16.5" spans="1:10">
       <c r="A8" s="148" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="B8" s="165">
         <v>1</v>
       </c>
       <c r="C8" s="165"/>
       <c r="D8" s="166" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="E8" s="166"/>
       <c r="F8" s="166"/>
@@ -13197,10 +13271,10 @@
     </row>
     <row r="9" ht="16.5" spans="1:10">
       <c r="A9" s="148" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="B9" s="152" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C9" s="152"/>
       <c r="D9" s="152"/>
@@ -13213,23 +13287,23 @@
     </row>
     <row r="10" ht="16.5" spans="1:10">
       <c r="A10" s="148" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B10" s="157">
         <v>1</v>
       </c>
       <c r="C10" s="157"/>
       <c r="D10" s="167" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="E10" s="157">
         <v>1</v>
       </c>
       <c r="F10" s="167" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="G10" s="147" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="H10" s="147"/>
       <c r="I10" s="147"/>
@@ -13237,7 +13311,7 @@
     </row>
     <row r="11" ht="16.5" spans="1:10">
       <c r="A11" s="148" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B11" s="158">
         <v>1</v>
@@ -13253,7 +13327,7 @@
     </row>
     <row r="12" ht="16.5" spans="1:10">
       <c r="A12" s="148" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="B12" s="159">
         <v>1</v>
@@ -13271,17 +13345,17 @@
     </row>
     <row r="13" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A13" s="148" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="168" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -13289,10 +13363,10 @@
     </row>
     <row r="14" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A14" s="148" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="B14" s="170" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C14" s="170"/>
       <c r="D14" s="170"/>
@@ -13367,7 +13441,7 @@
   <sheetData>
     <row r="1" s="117" customFormat="1" spans="1:9">
       <c r="A1" s="121" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B1" s="122"/>
       <c r="C1" s="117" t="s">
@@ -13392,10 +13466,10 @@
     </row>
     <row r="2" s="118" customFormat="1" spans="1:9">
       <c r="A2" s="125" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="B2" s="126" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="C2" s="127" t="s">
         <v>7</v>
@@ -13407,7 +13481,7 @@
     <row r="3" s="118" customFormat="1" spans="1:9">
       <c r="A3" s="130"/>
       <c r="B3" s="126" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="C3" s="127" t="s">
         <v>28</v>
@@ -13429,7 +13503,7 @@
     <row r="5" s="118" customFormat="1" spans="1:9">
       <c r="A5" s="130"/>
       <c r="B5" s="126" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="C5" s="127" t="s">
         <v>31</v>
@@ -13441,7 +13515,7 @@
     <row r="6" s="118" customFormat="1" spans="1:9">
       <c r="A6" s="130"/>
       <c r="B6" s="126" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>19</v>
@@ -13469,7 +13543,7 @@
     <row r="8" s="118" customFormat="1" spans="1:9">
       <c r="A8" s="130"/>
       <c r="B8" s="126" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>14</v>
@@ -13483,7 +13557,7 @@
     <row r="9" s="118" customFormat="1" spans="1:9">
       <c r="A9" s="130"/>
       <c r="B9" s="126" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="C9" s="127" t="s">
         <v>24</v>
@@ -13495,7 +13569,7 @@
     <row r="10" s="118" customFormat="1" spans="1:9">
       <c r="A10" s="130"/>
       <c r="B10" s="126" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="C10" s="127" t="s">
         <v>34</v>
@@ -13507,7 +13581,7 @@
     <row r="11" s="118" customFormat="1" spans="1:9">
       <c r="A11" s="134"/>
       <c r="B11" s="126" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="C11" s="127" t="s">
         <v>69</v>
@@ -13518,10 +13592,10 @@
     </row>
     <row r="12" s="119" customFormat="1" spans="1:9">
       <c r="A12" s="135" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="B12" s="136" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="C12" s="137" t="s">
         <v>88</v>
@@ -13545,10 +13619,10 @@
     <row r="14" s="119" customFormat="1" spans="1:9">
       <c r="A14" s="141"/>
       <c r="B14" s="136" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="C14" s="137" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="D14" s="142"/>
       <c r="E14" s="138"/>
@@ -13559,7 +13633,7 @@
     <row r="15" s="119" customFormat="1" spans="1:9">
       <c r="A15" s="141"/>
       <c r="B15" s="136" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="C15" s="137" t="s">
         <v>10</v>
@@ -13581,7 +13655,7 @@
     <row r="17" s="119" customFormat="1" spans="1:7">
       <c r="A17" s="141"/>
       <c r="B17" s="136" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C17" s="137" t="s">
         <v>27</v>
@@ -13593,7 +13667,7 @@
     <row r="18" s="119" customFormat="1" spans="1:7">
       <c r="A18" s="141"/>
       <c r="B18" s="136" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="C18" s="137" t="s">
         <v>42</v>
@@ -13605,7 +13679,7 @@
     <row r="19" s="119" customFormat="1" spans="1:7">
       <c r="A19" s="141"/>
       <c r="B19" s="136" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="C19" s="137" t="s">
         <v>81</v>
@@ -13617,7 +13691,7 @@
     <row r="20" s="119" customFormat="1" spans="1:7">
       <c r="A20" s="141"/>
       <c r="B20" s="136" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C20" s="137" t="s">
         <v>84</v>
@@ -13629,7 +13703,7 @@
     <row r="21" s="119" customFormat="1" spans="1:7">
       <c r="A21" s="141"/>
       <c r="B21" s="136" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="C21" s="143"/>
       <c r="D21" s="144"/>
@@ -13641,7 +13715,7 @@
     <row r="22" s="119" customFormat="1" spans="1:7">
       <c r="A22" s="145"/>
       <c r="B22" s="136" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="C22" s="143"/>
       <c r="D22" s="146"/>
@@ -13703,7 +13777,7 @@
   <sheetData>
     <row r="1" s="91" customFormat="1" customHeight="1" spans="1:16">
       <c r="A1" s="94" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="B1" s="95"/>
       <c r="C1" s="95"/>
@@ -13734,7 +13808,7 @@
     </row>
     <row r="3" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A3" s="100" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="B3" s="101"/>
       <c r="C3" s="102"/>
@@ -13926,7 +14000,7 @@
     </row>
     <row r="11" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A11" s="100" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B11" s="101"/>
       <c r="C11" s="102"/>
@@ -14118,7 +14192,7 @@
     </row>
     <row r="19" s="93" customFormat="1" customHeight="1" spans="1:9">
       <c r="A19" s="100" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="B19" s="101"/>
       <c r="C19" s="102"/>
@@ -14345,10 +14419,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="82" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B1" s="83" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="C1" s="84" t="s">
         <v>189</v>
@@ -14359,208 +14433,208 @@
         <v>1</v>
       </c>
       <c r="B2" s="80" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="C2" s="81" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="85"/>
       <c r="B3" s="80" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="C3" s="81" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="85"/>
       <c r="B4" s="80" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C4" s="81" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="85"/>
       <c r="B5" s="80" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="C5" s="81" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="85"/>
       <c r="B6" s="80" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="C6" s="81" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="85"/>
       <c r="B7" s="80" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="C7" s="81" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="85"/>
       <c r="B8" s="80" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C8" s="81" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="85"/>
       <c r="B9" s="80" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="85"/>
       <c r="B10" s="80" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="C10" s="81" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="85"/>
       <c r="B11" s="80" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="C11" s="81" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="85"/>
       <c r="B12" s="80" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C12" s="81" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="85"/>
       <c r="B13" s="80" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="C13" s="81" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="85"/>
       <c r="B14" s="80" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="85"/>
       <c r="B15" s="80" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C15" s="81" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="85"/>
       <c r="B16" s="80" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C16" s="81" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="85"/>
       <c r="B17" s="80" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="C17" s="81" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="85"/>
       <c r="B18" s="80" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="C18" s="81" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="85"/>
       <c r="B19" s="80" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C19" s="81" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="85"/>
       <c r="B20" s="80" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="C20" s="81" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="85"/>
       <c r="B21" s="80" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="C21" s="81" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="85"/>
       <c r="B22" s="80" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="C22" s="81" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="85"/>
       <c r="B23" s="80" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="C23" s="81" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="85"/>
       <c r="B24" s="80" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C24" s="81" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -14568,118 +14642,118 @@
         <v>2</v>
       </c>
       <c r="B25" s="80" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="C25" s="81" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="86"/>
       <c r="B26" s="80" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="C26" s="81" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="86"/>
       <c r="B27" s="80" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="C27" s="81" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="86"/>
       <c r="B28" s="80" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="C28" s="81" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="86"/>
       <c r="B29" s="80" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="C29" s="81" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="86"/>
       <c r="B30" s="80" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="C30" s="81" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="86"/>
       <c r="B31" s="80" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="C31" s="81" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="86"/>
       <c r="B32" s="80" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="C32" s="81" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="86"/>
       <c r="B33" s="80" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="C33" s="81" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="86"/>
       <c r="B34" s="80" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="C34" s="81" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="86"/>
       <c r="B35" s="80" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="C35" s="81" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="86"/>
       <c r="B36" s="80" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="C36" s="81" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="87"/>
       <c r="B37" s="80" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="C37" s="81" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -14687,138 +14761,138 @@
         <v>3</v>
       </c>
       <c r="B38" s="80" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="C38" s="81" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="89"/>
       <c r="B39" s="80" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="C39" s="81" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="89"/>
       <c r="B40" s="80" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="C40" s="81" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="89"/>
       <c r="B41" s="80" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="C41" s="81" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="89"/>
       <c r="B42" s="80" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="C42" s="81" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="89"/>
       <c r="B43" s="80" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="C43" s="81" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="89"/>
       <c r="B44" s="80" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="C44" s="81" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="89"/>
       <c r="B45" s="80" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="C45" s="81" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="89"/>
       <c r="B46" s="80" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="C46" s="81" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="89"/>
       <c r="B47" s="80" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C47" s="81" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="89"/>
       <c r="B48" s="80" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="C48" s="81" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="89"/>
       <c r="B49" s="80" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="C49" s="81" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="90"/>
       <c r="B50" s="80" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="C50" s="81" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:3">
       <c r="A51" s="79"/>
       <c r="B51" s="80" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="C51" s="81"/>
     </row>
     <row r="52" customFormat="1" spans="1:3">
       <c r="A52" s="79"/>
       <c r="B52" s="80" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="C52" s="81"/>
     </row>
     <row r="53" customFormat="1" spans="1:3">
       <c r="A53" s="79"/>
       <c r="B53" s="80" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="C53" s="81"/>
     </row>

--- a/c/9班资料.xlsx
+++ b/c/9班资料.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10030" tabRatio="724" activeTab="2"/>
+    <workbookView windowWidth="20750" windowHeight="10030" tabRatio="724"/>
   </bookViews>
   <sheets>
     <sheet name="师生" sheetId="5" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="607">
   <si>
     <t>姓名</t>
   </si>
@@ -129,7 +129,7 @@
     <t>祥懿又是你、午餐（芹菜炒肉、土豆丝、秋葵、番茄酱）课间吃饭、画画、捏/咬/打人、炫耀、演讲、喵喵姐</t>
   </si>
   <si>
-    <t>萌、上课吃东西（早上水果，下午菜，下午高峰）（泡鸭爪/棒棒糖/营养品（长高）/奥利奥）、作业没写应对方式（没带法、证人法、偶然法、不会法、以为法、灭口法、自我安慰法）、宣泄、睡觉（低头/点头）、带读（一，起）、水杯倒（不盖盖）、尼玛的、东西被陆梓豪偷吃、排队时讲话、我又……上了、我不行了……、自己做了……→谁做了……啊！、告状、动作、英语小测翻书/笔记、隔班借作业抄、废啊、（12.11）带仓鼠、OC（龙烛玥）、在干嘛啊</t>
+    <t>萌、上课吃东西（早上水果，下午菜，下午高峰）（泡鸭爪/棒棒糖/营养品（长高）/奥利奥）、作业没写应对方式（没带法、证人法、偶然法、不会法、以为法、灭口法、自我安慰法）、宣泄、睡觉（低头/点头）、带读（一，起）、水杯倒（不盖盖）、尼玛的、东西被陆梓豪偷吃、排队时讲话、我又……上了、我不行了……、自己做了……→谁做了……啊！、告状、动作、英语小测翻书/笔记、隔班借作业抄、废啊、（12.11）带仓鼠、OC（龙烛玥）、在干嘛啊、吃饭（走动、分享）</t>
   </si>
   <si>
     <t>林钰颖</t>
@@ -626,6 +626,9 @@
   </si>
   <si>
     <t>自行车停放</t>
+  </si>
+  <si>
+    <t>下课——无跑操铃——突然响起——啊</t>
   </si>
   <si>
     <t>日常</t>
@@ -841,6 +844,12 @@
     <t>讲评作业——上次作业只印了一半——家长会讲过，有家长疑惑，再讲——为何不“一刀切”（无作业必须打印）：考虑有人打印成本高——倡导自主学习——国家政策：不定教辅（上学期领导检查）——原因：培育人才（次）、人口减少（主）——当下情况：50人/班变为30~40人/班（仓实小现状）——内卷——大学录取率——国家政策——自主学习——买课外练习（五三、解析）——公立对比私立、学位与大学、公务员——985学生心高气傲——私企对比国企：导致公务员增加——学生：考公或保送——讲这些内容目的：给前景——好学生：学习；差生：送外卖？——本科挤压送外卖——素质：本科&gt;送外卖——努力学习——考高中前提：数学及格（浪费半节课）</t>
   </si>
   <si>
+    <t>八上1.14</t>
+  </si>
+  <si>
+    <t>试卷：解设没写单位-1——一分十几万——上周会考：50%老师外校——私立高中学费vs公立——总费用——一类校寄读费——很多人差1分——40中也有寄读（几万）——寄读条件（家境、走后门）——上次讲到“上高中的百分比变高”，原因：私立增加——每一分的价值——学生甘心、家长不甘心——借钱——兄弟姐妹（家长爱心）——好的儿女十几万都出——寄读一定好吗——（城门中学的学生觉得40中好，寄宿后越来越差）——学校没很照顾寄读——自己寄读其他学校感觉低人一等——学生内心——希望：努力——到时候后悔，3年多付10万</t>
+  </si>
+  <si>
     <t>八上10.31</t>
   </si>
   <si>
@@ -857,6 +866,9 @@
   </si>
   <si>
     <t>数：油印室额度都用光了。</t>
+  </si>
+  <si>
+    <t>铃声错乱：①（周三）9：10响预备铃②响铃响到一半停止，几秒后重新响起</t>
   </si>
   <si>
     <t>政治课</t>
@@ -3150,10 +3162,10 @@
       <charset val="134"/>
     </font>
     <font>
+      <strike/>
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
-      <scheme val="major"/>
     </font>
     <font>
       <sz val="10"/>
@@ -3169,13 +3181,13 @@
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+      <scheme val="major"/>
     </font>
     <font>
-      <strike/>
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="57">
@@ -5028,7 +5040,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" ht="208" spans="1:7">
+    <row r="7" ht="221" spans="1:7">
       <c r="A7" s="72" t="s">
         <v>19</v>
       </c>
@@ -5745,16 +5757,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="67" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B1" s="68" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="69" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="D1" s="70" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5768,7 +5780,7 @@
         <v>20111216</v>
       </c>
       <c r="D2" s="66" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -5782,7 +5794,7 @@
         <v>20111227</v>
       </c>
       <c r="D3" s="66" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -5796,7 +5808,7 @@
         <v>20120518</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:4">
@@ -5824,7 +5836,7 @@
         <v>20120504</v>
       </c>
       <c r="D6" s="66" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -5838,7 +5850,7 @@
         <v>20120809</v>
       </c>
       <c r="D7" s="66" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -5852,7 +5864,7 @@
         <v>20120227</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -5866,7 +5878,7 @@
         <v>20120127</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -5880,7 +5892,7 @@
         <v>20111202</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:4">
@@ -5906,7 +5918,7 @@
         <v>20111024</v>
       </c>
       <c r="D12" s="66" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -5920,7 +5932,7 @@
         <v>20110908</v>
       </c>
       <c r="D13" s="66" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -5934,7 +5946,7 @@
         <v>20120228</v>
       </c>
       <c r="D14" s="66" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:4">
@@ -5960,7 +5972,7 @@
         <v>20111201</v>
       </c>
       <c r="D16" s="66" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -5974,7 +5986,7 @@
         <v>20120722</v>
       </c>
       <c r="D17" s="66" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:4">
@@ -6012,7 +6024,7 @@
         <v>20120530</v>
       </c>
       <c r="D20" s="66" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -6026,7 +6038,7 @@
         <v>20120827</v>
       </c>
       <c r="D21" s="66" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:4">
@@ -6052,7 +6064,7 @@
         <v>20120518</v>
       </c>
       <c r="D23" s="66" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -6066,7 +6078,7 @@
         <v>20120413</v>
       </c>
       <c r="D24" s="66" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -6080,7 +6092,7 @@
         <v>20120629</v>
       </c>
       <c r="D25" s="66" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -6094,7 +6106,7 @@
         <v>20111105</v>
       </c>
       <c r="D26" s="66" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -6108,7 +6120,7 @@
         <v>20120112</v>
       </c>
       <c r="D27" s="66" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -6122,7 +6134,7 @@
         <v>20111119</v>
       </c>
       <c r="D28" s="66" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:4">
@@ -6148,7 +6160,7 @@
         <v>20120331</v>
       </c>
       <c r="D30" s="66" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -6162,7 +6174,7 @@
         <v>20111109</v>
       </c>
       <c r="D31" s="66" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -6176,7 +6188,7 @@
         <v>20120824</v>
       </c>
       <c r="D32" s="66" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:5">
@@ -6202,7 +6214,7 @@
         <v>20120624</v>
       </c>
       <c r="D34" s="66" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:5">
@@ -6228,7 +6240,7 @@
         <v>20120603</v>
       </c>
       <c r="D36" s="66" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -6242,7 +6254,7 @@
         <v>20120326</v>
       </c>
       <c r="D37" s="66" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -6256,10 +6268,10 @@
         <v>20111106</v>
       </c>
       <c r="D38" s="77" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E38" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -6273,7 +6285,7 @@
         <v>20120811</v>
       </c>
       <c r="D39" s="78" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -6287,7 +6299,7 @@
         <v>20111217</v>
       </c>
       <c r="D40" s="78" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -6301,10 +6313,10 @@
         <v>20111013</v>
       </c>
       <c r="D41" s="66" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="E41" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:5">
@@ -6330,7 +6342,7 @@
         <v>20120207</v>
       </c>
       <c r="D43" s="66" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:5">
@@ -6356,7 +6368,7 @@
         <v>20110929</v>
       </c>
       <c r="D45" s="66" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:5">
@@ -6382,10 +6394,10 @@
         <v>20120108</v>
       </c>
       <c r="D47" s="66" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E47" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -6399,7 +6411,7 @@
         <v>20120311</v>
       </c>
       <c r="D48" s="66" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:4">
@@ -6425,7 +6437,7 @@
         <v>20120723</v>
       </c>
       <c r="D50" s="66" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:4">
@@ -6451,7 +6463,7 @@
         <v>20111220</v>
       </c>
       <c r="D52" s="66" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -6484,34 +6496,34 @@
   <sheetData>
     <row r="1" s="27" customFormat="1" spans="1:5">
       <c r="A1" s="34" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="D1" s="37"/>
       <c r="E1" s="38" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2" s="28" customFormat="1" ht="409" customHeight="1" spans="1:5">
       <c r="A2" s="39" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="3" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6519,10 +6531,10 @@
       <c r="B3" s="43"/>
       <c r="C3" s="44"/>
       <c r="D3" s="32" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="4" s="28" customFormat="1" spans="1:5">
@@ -6530,10 +6542,10 @@
       <c r="B4" s="43"/>
       <c r="C4" s="44"/>
       <c r="D4" s="32" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="5" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6541,10 +6553,10 @@
       <c r="B5" s="43"/>
       <c r="C5" s="44"/>
       <c r="D5" s="32" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="6" s="28" customFormat="1" ht="238" spans="1:5">
@@ -6552,23 +6564,23 @@
       <c r="B6" s="43"/>
       <c r="C6" s="44"/>
       <c r="D6" s="32" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" s="28" customFormat="1" ht="238" spans="1:5">
       <c r="A7" s="42"/>
       <c r="B7" s="43"/>
       <c r="C7" s="41" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6576,10 +6588,10 @@
       <c r="B8" s="43"/>
       <c r="C8" s="44"/>
       <c r="D8" s="32" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9" s="28" customFormat="1" ht="84" spans="1:5">
@@ -6587,10 +6599,10 @@
       <c r="B9" s="43"/>
       <c r="C9" s="44"/>
       <c r="D9" s="32" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="10" s="28" customFormat="1" ht="28" spans="1:5">
@@ -6598,10 +6610,10 @@
       <c r="B10" s="43"/>
       <c r="C10" s="44"/>
       <c r="D10" s="32" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="11" s="28" customFormat="1" spans="1:5">
@@ -6609,10 +6621,10 @@
       <c r="B11" s="43"/>
       <c r="C11" s="45"/>
       <c r="D11" s="32" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="12" s="28" customFormat="1" ht="154" spans="1:5">
@@ -6620,50 +6632,50 @@
       <c r="B12" s="43"/>
       <c r="C12" s="31"/>
       <c r="D12" s="32" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="13" s="28" customFormat="1" ht="56" spans="1:5">
       <c r="A13" s="42"/>
       <c r="B13" s="43"/>
       <c r="C13" s="46" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="33" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="14" s="28" customFormat="1" ht="84" spans="1:5">
       <c r="A14" s="42"/>
       <c r="B14" s="43"/>
       <c r="C14" s="46" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="33" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="15" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A15" s="42"/>
       <c r="B15" s="43"/>
       <c r="C15" s="46" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="D15" s="37"/>
       <c r="E15" s="33" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="16" s="28" customFormat="1" spans="1:5">
       <c r="A16" s="42"/>
       <c r="B16" s="43"/>
       <c r="C16" s="46" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="D16" s="37"/>
       <c r="E16" s="33"/>
@@ -6672,24 +6684,24 @@
       <c r="A17" s="42"/>
       <c r="B17" s="43"/>
       <c r="C17" s="46" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="33" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="18" s="28" customFormat="1" spans="1:5">
       <c r="A18" s="42"/>
       <c r="B18" s="43"/>
       <c r="C18" s="41" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="19" s="28" customFormat="1" spans="1:5">
@@ -6697,17 +6709,17 @@
       <c r="B19" s="43"/>
       <c r="C19" s="45"/>
       <c r="D19" s="32" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="20" s="28" customFormat="1" spans="1:5">
       <c r="A20" s="42"/>
       <c r="B20" s="43"/>
       <c r="C20" s="46" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="D20" s="37"/>
       <c r="E20" s="33"/>
@@ -6716,61 +6728,61 @@
       <c r="A21" s="42"/>
       <c r="B21" s="43"/>
       <c r="C21" s="46" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="D21" s="37"/>
       <c r="E21" s="33" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="22" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A22" s="42"/>
       <c r="B22" s="43"/>
       <c r="C22" s="46" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="D22" s="47"/>
       <c r="E22" s="33" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="23" s="28" customFormat="1" spans="1:5">
       <c r="A23" s="42"/>
       <c r="B23" s="43"/>
       <c r="C23" s="31" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D23" s="31"/>
       <c r="E23" s="33" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="24" s="28" customFormat="1" spans="1:5">
       <c r="A24" s="42"/>
       <c r="B24" s="43"/>
       <c r="C24" s="31" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="D24" s="31"/>
       <c r="E24" s="33" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="25" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A25" s="39" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="26" s="28" customFormat="1" spans="1:5">
@@ -6778,10 +6790,10 @@
       <c r="B26" s="43"/>
       <c r="C26" s="44"/>
       <c r="D26" s="32" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="27" s="28" customFormat="1" ht="28" spans="1:5">
@@ -6789,10 +6801,10 @@
       <c r="B27" s="43"/>
       <c r="C27" s="44"/>
       <c r="D27" s="32" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="28" s="28" customFormat="1" ht="42" spans="1:5">
@@ -6800,27 +6812,27 @@
       <c r="B28" s="43"/>
       <c r="C28" s="44"/>
       <c r="D28" s="32" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="29" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A29" s="39" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="30" s="28" customFormat="1" ht="70" spans="1:5">
@@ -6828,10 +6840,10 @@
       <c r="B30" s="43"/>
       <c r="C30" s="44"/>
       <c r="D30" s="32" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="31" s="28" customFormat="1" spans="1:5">
@@ -6839,10 +6851,10 @@
       <c r="B31" s="43"/>
       <c r="C31" s="44"/>
       <c r="D31" s="32" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="32" s="28" customFormat="1" ht="28" spans="1:5">
@@ -6850,53 +6862,53 @@
       <c r="B32" s="43"/>
       <c r="C32" s="45"/>
       <c r="D32" s="32" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
     <row r="33" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A33" s="42"/>
       <c r="B33" s="49"/>
       <c r="C33" s="46" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D33" s="47"/>
       <c r="E33" s="33" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="34" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A34" s="42"/>
       <c r="B34" s="50" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D34" s="51"/>
       <c r="E34" s="52" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
     </row>
     <row r="35" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A35" s="53"/>
       <c r="B35" s="54"/>
       <c r="C35" s="36" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D35" s="51"/>
       <c r="E35" s="52" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
     </row>
     <row r="36" s="28" customFormat="1" spans="1:5">
       <c r="A36" s="39" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B36" s="55" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="C36" s="56"/>
       <c r="D36" s="57"/>
@@ -6907,42 +6919,42 @@
     <row r="37" s="28" customFormat="1" spans="1:5">
       <c r="A37" s="53"/>
       <c r="B37" s="58" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C37" s="59"/>
       <c r="D37" s="60"/>
       <c r="E37" s="33" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
     </row>
     <row r="38" s="28" customFormat="1" spans="1:5">
       <c r="A38" s="29" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B38" s="58" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C38" s="59"/>
       <c r="D38" s="60"/>
       <c r="E38" s="33" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
     </row>
     <row r="39" s="28" customFormat="1" spans="1:5">
       <c r="A39" s="39" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B39" s="40" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C39" s="41" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
     </row>
     <row r="40" s="28" customFormat="1" spans="1:5">
@@ -6950,64 +6962,64 @@
       <c r="B40" s="43"/>
       <c r="C40" s="45"/>
       <c r="D40" s="32" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="E40" s="33" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
     </row>
     <row r="41" s="28" customFormat="1" spans="1:5">
       <c r="A41" s="42"/>
       <c r="B41" s="43"/>
       <c r="C41" s="46" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="D41" s="47"/>
       <c r="E41" s="33" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="42" s="28" customFormat="1" spans="1:5">
       <c r="A42" s="53"/>
       <c r="B42" s="49"/>
       <c r="C42" s="46" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D42" s="47"/>
       <c r="E42" s="33" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="43" s="28" customFormat="1" spans="1:5">
       <c r="A43" s="39" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B43" s="50" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C43" s="61" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="D43" s="62"/>
       <c r="E43" s="52" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
     </row>
     <row r="44" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A44" s="42"/>
       <c r="B44" s="54"/>
       <c r="C44" s="61" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="D44" s="62"/>
       <c r="E44" s="52" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="45" s="28" customFormat="1" spans="1:5">
       <c r="A45" s="53"/>
       <c r="B45" s="58" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="C45" s="59"/>
       <c r="D45" s="60"/>
@@ -7017,16 +7029,16 @@
     </row>
     <row r="46" s="28" customFormat="1" spans="1:5">
       <c r="A46" s="39" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B46" s="40" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C46" s="41" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="E46" s="33"/>
     </row>
@@ -7035,7 +7047,7 @@
       <c r="B47" s="43"/>
       <c r="C47" s="44"/>
       <c r="D47" s="32" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="E47" s="33"/>
     </row>
@@ -7044,42 +7056,42 @@
       <c r="B48" s="49"/>
       <c r="C48" s="45"/>
       <c r="D48" s="32" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="49" s="28" customFormat="1" spans="1:5">
       <c r="A49" s="29" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B49" s="58" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C49" s="59"/>
       <c r="D49" s="60"/>
       <c r="E49" s="33" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="50" s="28" customFormat="1" spans="1:5">
       <c r="A50" s="39" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B50" s="58" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C50" s="59"/>
       <c r="D50" s="60"/>
       <c r="E50" s="33" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
     </row>
     <row r="51" s="28" customFormat="1" spans="1:5">
       <c r="A51" s="53"/>
       <c r="B51" s="58" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C51" s="59"/>
       <c r="D51" s="60"/>
@@ -7089,10 +7101,10 @@
     </row>
     <row r="52" s="28" customFormat="1" spans="1:5">
       <c r="A52" s="29" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B52" s="58" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C52" s="59"/>
       <c r="D52" s="60"/>
@@ -7100,10 +7112,10 @@
     </row>
     <row r="53" s="28" customFormat="1" spans="1:5">
       <c r="A53" s="39" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B53" s="58" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C53" s="59"/>
       <c r="D53" s="60"/>
@@ -7115,18 +7127,18 @@
       <c r="C54" s="59"/>
       <c r="D54" s="60"/>
       <c r="E54" s="33" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
     </row>
     <row r="55" s="28" customFormat="1" spans="1:5">
       <c r="A55" s="29" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B55" s="30"/>
       <c r="C55" s="31"/>
       <c r="D55" s="32"/>
       <c r="E55" s="33" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
   </sheetData>
@@ -7234,7 +7246,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
@@ -7248,7 +7260,7 @@
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="9" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="11"/>
@@ -7272,7 +7284,7 @@
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="9" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="11"/>
@@ -7285,7 +7297,7 @@
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="22" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="11"/>
@@ -7298,7 +7310,7 @@
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="9" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="11"/>
@@ -7332,7 +7344,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="10"/>
@@ -7378,7 +7390,7 @@
         <v>31</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="10"/>
@@ -7414,7 +7426,7 @@
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="22" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="11"/>
@@ -7448,10 +7460,10 @@
         <v>42</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="11"/>
@@ -7463,10 +7475,10 @@
         <v>45</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="11"/>
@@ -7489,7 +7501,7 @@
         <v>50</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="10"/>
@@ -7502,10 +7514,10 @@
         <v>52</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="11"/>
@@ -7539,10 +7551,10 @@
         <v>58</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="11"/>
@@ -7554,10 +7566,10 @@
         <v>61</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="11"/>
@@ -7581,7 +7593,7 @@
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="22" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="11"/>
@@ -7648,7 +7660,7 @@
         <v>74</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="10"/>
@@ -7662,7 +7674,7 @@
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="22" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="11"/>
@@ -7674,7 +7686,7 @@
         <v>79</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="C38" s="25"/>
       <c r="D38" s="26"/>
@@ -7688,7 +7700,7 @@
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="22" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="11"/>
@@ -7700,10 +7712,10 @@
         <v>84</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="11"/>
@@ -7716,7 +7728,7 @@
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="22" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="D41" s="10"/>
       <c r="E41" s="11"/>
@@ -7739,7 +7751,7 @@
         <v>93</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="10"/>
@@ -7763,7 +7775,7 @@
         <v>97</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="10"/>
@@ -7799,7 +7811,7 @@
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="22" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="D48" s="10"/>
       <c r="E48" s="11"/>
@@ -7823,7 +7835,7 @@
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="22" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="D50" s="10"/>
       <c r="E50" s="11"/>
@@ -7846,10 +7858,10 @@
         <v>110</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="D52" s="10"/>
       <c r="E52" s="11"/>
@@ -7885,27 +7897,27 @@
   <sheetData>
     <row r="1" spans="2:6">
       <c r="B1" s="3" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
     </row>
     <row r="2" spans="2:6">
       <c r="B2" s="4" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="C2" s="4">
         <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="F2" s="4">
         <v>6</v>
@@ -7913,13 +7925,13 @@
     </row>
     <row r="3" spans="2:6">
       <c r="B3" s="4" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="C3" s="4">
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="F3" s="4">
         <v>13</v>
@@ -7927,13 +7939,13 @@
     </row>
     <row r="4" spans="2:6">
       <c r="B4" s="4" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C4" s="4">
         <v>12</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="F4" s="4">
         <v>4</v>
@@ -7941,13 +7953,13 @@
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="4" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="C5" s="4">
         <v>2</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="F5" s="4">
         <v>6</v>
@@ -7955,13 +7967,13 @@
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="4" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="C6" s="4">
         <v>2</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="F6" s="4">
         <v>4</v>
@@ -7969,13 +7981,13 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="4" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
@@ -7983,13 +7995,13 @@
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="4" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C8" s="4">
         <v>4</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="F8" s="4">
         <v>3</v>
@@ -7997,7 +8009,7 @@
     </row>
     <row r="9" spans="2:6">
       <c r="E9" s="4" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -8005,7 +8017,7 @@
     </row>
     <row r="10" spans="2:6">
       <c r="E10" s="4" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="F10" s="4">
         <v>5</v>
@@ -8013,7 +8025,7 @@
     </row>
     <row r="11" spans="2:6">
       <c r="E11" s="4" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -8021,7 +8033,7 @@
     </row>
     <row r="12" spans="2:6">
       <c r="E12" s="4" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="F12" s="4">
         <v>2</v>
@@ -8171,6 +8183,9 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="216"/>
+      <c r="B16" s="66" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="216"/>
@@ -8300,7 +8315,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.8"/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="24" style="200" customWidth="1"/>
@@ -8311,77 +8326,77 @@
   <sheetData>
     <row r="1" s="199" customFormat="1" ht="15" spans="1:3">
       <c r="A1" s="201" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B1" s="201" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C1" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="202" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B2" s="202" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C2" s="202" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="202" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B3" s="202" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C3" s="202" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="202" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B4" s="202" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C4" s="202" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" ht="56" spans="1:3">
       <c r="A5" s="203" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B5" s="202" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C5" s="202" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:3">
       <c r="A6" s="204"/>
       <c r="B6" s="202" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C6" s="202" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="202" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B7" s="202" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C7" s="202" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8389,55 +8404,55 @@
         <v>88</v>
       </c>
       <c r="B8" s="202" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C8" s="202" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="206"/>
       <c r="B9" s="202" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C9" s="202" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="206"/>
       <c r="B10" s="202" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C10" s="202" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="206"/>
       <c r="B11" s="202" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C11" s="202" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="206"/>
       <c r="B12" s="202" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C12" s="202" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13" ht="140" spans="1:3">
       <c r="A13" s="206"/>
       <c r="B13" s="202" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C13" s="202" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -8462,32 +8477,32 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="202" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B18" s="202" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C18" s="202" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="202" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B19" s="202" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C19" s="202" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="202" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B20" s="202" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C20" s="208">
         <v>0.440972222222222</v>
@@ -8498,147 +8513,165 @@
         <v>61</v>
       </c>
       <c r="B21" s="202" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C21" s="202" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="204"/>
       <c r="B22" s="202" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C22" s="202" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="203" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B23" s="202" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C23" s="202" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="204"/>
       <c r="B24" s="202" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C24" s="202" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="25" ht="28" spans="1:3">
       <c r="A25" s="205" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B25" s="202" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C25" s="202" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="206"/>
       <c r="B26" s="202" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C26" s="202" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="203" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B27" s="202" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C27" s="202" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="204"/>
       <c r="B28" s="202" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C28" s="202" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29" ht="28" spans="1:3">
-      <c r="A29" s="209" t="s">
+      <c r="A29" s="205" t="s">
         <v>45</v>
       </c>
       <c r="B29" s="202" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C29" s="202" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="210"/>
+      <c r="A30" s="207"/>
       <c r="B30" s="200" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C30" s="200" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="31" ht="98" spans="1:3">
+      <c r="A31" s="209" t="s">
+        <v>245</v>
+      </c>
+      <c r="B31" s="200" t="s">
+        <v>211</v>
+      </c>
+      <c r="C31" s="200" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="32" ht="84" spans="1:3">
+      <c r="A32" s="210"/>
+      <c r="B32" s="200" t="s">
+        <v>247</v>
+      </c>
+      <c r="C32" s="200" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="200" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="200" t="s">
+        <v>249</v>
+      </c>
+      <c r="C33" s="200" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="34" ht="28" spans="1:3">
+      <c r="A34" s="200" t="s">
+        <v>251</v>
+      </c>
+      <c r="B34" s="200" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="31" ht="98" spans="1:3">
-      <c r="A31" s="200" t="s">
-        <v>244</v>
-      </c>
-      <c r="B31" s="200" t="s">
-        <v>210</v>
-      </c>
-      <c r="C31" s="200" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="200" t="s">
-        <v>36</v>
-      </c>
-      <c r="B32" s="200" t="s">
-        <v>246</v>
-      </c>
-      <c r="C32" s="200" t="s">
+      <c r="C34" s="200" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="209" t="s">
+        <v>253</v>
+      </c>
+      <c r="B35" s="200" t="s">
+        <v>216</v>
+      </c>
+      <c r="C35" s="200" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="210"/>
+      <c r="B36" s="200" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="33" ht="28" spans="1:3">
-      <c r="A33" s="200" t="s">
-        <v>248</v>
-      </c>
-      <c r="B33" s="200" t="s">
-        <v>242</v>
-      </c>
-      <c r="C33" s="200" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="200" t="s">
-        <v>250</v>
-      </c>
-      <c r="B34" s="200" t="s">
-        <v>215</v>
-      </c>
-      <c r="C34" s="200" t="s">
-        <v>251</v>
+      <c r="C36" s="200" t="s">
+        <v>255</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="9">
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A8:A17"/>
     <mergeCell ref="A21:A22"/>
@@ -8646,6 +8679,8 @@
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A35:A36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -8672,33 +8707,33 @@
   <sheetData>
     <row r="1" s="186" customFormat="1" ht="15" spans="1:7">
       <c r="A1" s="189" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B1" s="190"/>
       <c r="C1" s="190"/>
       <c r="D1" s="191"/>
       <c r="E1" s="192"/>
       <c r="F1" s="186" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" s="187" customFormat="1" spans="1:7">
       <c r="A2" s="193" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B2" s="194"/>
       <c r="C2" s="187" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D2" s="187" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E2" s="141"/>
       <c r="F2" s="187" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G2" s="187" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -8713,10 +8748,10 @@
       </c>
       <c r="D3" s="119"/>
       <c r="F3" s="119" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="G3" s="119" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -8729,10 +8764,10 @@
       </c>
       <c r="D4" s="119"/>
       <c r="F4" s="119" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="G4" s="119" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -8895,7 +8930,7 @@
   <sheetData>
     <row r="1" spans="1:39">
       <c r="A1" s="174" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B1" s="175">
         <v>45992</v>
@@ -8933,7 +8968,7 @@
       <c r="AE1" s="176"/>
       <c r="AF1" s="176"/>
       <c r="AG1" s="143" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AH1" s="146"/>
       <c r="AI1" s="146"/>
@@ -9038,25 +9073,25 @@
         <v>20</v>
       </c>
       <c r="AG2" s="178" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AH2" s="178" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI2" s="178" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AJ2" s="178" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="AK2" s="179" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="AL2" s="179" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="AM2" s="179" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:39">
@@ -11789,26 +11824,28 @@
       <c r="AA40" s="120">
         <v>1</v>
       </c>
-      <c r="AB40" s="120"/>
+      <c r="AB40" s="120">
+        <v>1</v>
+      </c>
       <c r="AC40" s="120"/>
       <c r="AD40" s="120"/>
       <c r="AE40" s="120"/>
       <c r="AF40" s="120"/>
       <c r="AG40" s="180">
         <f t="shared" si="33"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH40" s="181" cm="1">
         <f t="array" ref="AH40">SUMPRODUCT(--(B40:AF40=INT(B40:AF40)),--(B40:AF40&gt;0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI40" s="181" cm="1">
         <f t="array" ref="AI40">MAX(FREQUENCY(IF((B40:AF40=INT(B40:AF40))*(B40:AF40&gt;0),COLUMN(B40:AF40)),IF((B40:AF40&lt;&gt;INT(B40:AF40))+(B40:AF40&lt;=0),COLUMN(B40:AF40))))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ40" s="182" cm="1">
         <f t="array" ref="AJ40">SUMPRODUCT(--(B40:AF40=INT(B40:AF40)),--(B40:AF40&gt;0))/30*100%</f>
-        <v>0.6</v>
+        <v>0.633333333333333</v>
       </c>
       <c r="AK40" s="183">
         <f t="shared" ref="AK40:AM40" si="38">RANK(AG40,AG$3:AG$53,0)</f>
@@ -12271,18 +12308,20 @@
         <v>1</v>
       </c>
       <c r="AA46" s="120"/>
-      <c r="AB46" s="120"/>
+      <c r="AB46" s="120">
+        <v>1</v>
+      </c>
       <c r="AC46" s="120"/>
       <c r="AD46" s="120"/>
       <c r="AE46" s="120"/>
       <c r="AF46" s="120"/>
       <c r="AG46" s="180">
         <f t="shared" si="33"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH46" s="181" cm="1">
         <f t="array" ref="AH46">SUMPRODUCT(--(B46:AF46=INT(B46:AF46)),--(B46:AF46&gt;0))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI46" s="181" cm="1">
         <f t="array" ref="AI46">MAX(FREQUENCY(IF((B46:AF46=INT(B46:AF46))*(B46:AF46&gt;0),COLUMN(B46:AF46)),IF((B46:AF46&lt;&gt;INT(B46:AF46))+(B46:AF46&lt;=0),COLUMN(B46:AF46))))</f>
@@ -12290,7 +12329,7 @@
       </c>
       <c r="AJ46" s="182" cm="1">
         <f t="array" ref="AJ46">SUMPRODUCT(--(B46:AF46=INT(B46:AF46)),--(B46:AF46&gt;0))/30*100%</f>
-        <v>0.633333333333333</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="AK46" s="183">
         <f t="shared" ref="AK46:AM46" si="44">RANK(AG46,AG$3:AG$53,0)</f>
@@ -13096,7 +13135,7 @@
   <pageSetup paperSize="9" scale="80" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A5:AM7 Z3:AM4 A3:X4 A1:AM2 A8:V8 X8:AM8 A26:AM27 Z24:AM25 A24:X25 A23:AM23 AA22:AM22 A22:X22 A19:AM21 Z17:AM18 A17:X18 A16:AM16 Z12:AM12 Z13 AB13:AM13 Z14:AM14 Z15 AB15:AM15 A12:X15 A11:Z11 AB11:AM11 Z9:AM10 A9:X10 A40:V41 X41 A50:AM53 Z48:AM49 A48:X49 A47:AM47 AA46:AM46 A46:X46 A45:AM45 Z44:AM44 A44:W44 A43:AM43 AB40:AM40 Z41:AM42 A42:X42 A39:AM39 Z38:AM38 A38:X38 A37:AM37 Z36:AM36 A36:X36 A34:AM35 Z28:AM33 A28:X33" formulaRange="1" unlockedFormula="1"/>
+    <ignoredError sqref="A28:X33 Z28:AM33 A34:AM35 A36:X36 Z36:AM36 A37:AM37 A38:X38 Z38:AM38 A39:AM39 A42:X42 Z41:AM42 AC40:AM40 A43:AM43 A44:W44 Z44:AM44 A45:AM45 A46:X46 AA46 AC46:AM46 A47:AM47 A48:X49 Z48:AM49 A50:AM53 X41 A40:V41 A9:X10 Z9:AM10 AB11:AM11 A11:Z11 A12:X15 AB15:AM15 Z15 Z14:AM14 AB13:AM13 Z13 Z12:AM12 A16:AM16 A17:X18 Z17:AM18 A19:AM21 A22:X22 AA22:AM22 A23:AM23 A24:X25 Z24:AM25 A26:AM27 X8:AM8 A8:V8 A1:AM2 A3:X4 Z3:AM4 A5:AM7" formulaRange="1" unlockedFormula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -13143,21 +13182,21 @@
     </row>
     <row r="2" ht="16.5" spans="1:10">
       <c r="A2" s="148" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B2" s="152" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C2" s="153" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D2" s="154"/>
       <c r="E2" s="152" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="F2" s="152"/>
       <c r="G2" s="155" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="H2" s="147"/>
       <c r="I2" s="147"/>
@@ -13165,10 +13204,10 @@
     </row>
     <row r="3" ht="16.5" spans="1:10">
       <c r="A3" s="148" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B3" s="157" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C3" s="157"/>
       <c r="D3" s="157"/>
@@ -13181,10 +13220,10 @@
     </row>
     <row r="4" ht="16.5" spans="1:10">
       <c r="A4" s="148" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B4" s="158" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C4" s="158"/>
       <c r="D4" s="158"/>
@@ -13197,7 +13236,7 @@
     </row>
     <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="148" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B5" s="159">
         <v>1</v>
@@ -13217,7 +13256,7 @@
     </row>
     <row r="6" ht="16.5" spans="1:10">
       <c r="A6" s="148" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B6" s="161">
         <v>1</v>
@@ -13227,7 +13266,7 @@
       <c r="E6" s="161"/>
       <c r="F6" s="161"/>
       <c r="G6" s="162" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="H6" s="147"/>
       <c r="I6" s="147"/>
@@ -13235,10 +13274,10 @@
     </row>
     <row r="7" ht="16.5" spans="1:10">
       <c r="A7" s="148" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B7" s="163" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C7" s="163"/>
       <c r="D7" s="163"/>
@@ -13253,14 +13292,14 @@
     </row>
     <row r="8" ht="16.5" spans="1:10">
       <c r="A8" s="148" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B8" s="165">
         <v>1</v>
       </c>
       <c r="C8" s="165"/>
       <c r="D8" s="166" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="E8" s="166"/>
       <c r="F8" s="166"/>
@@ -13271,10 +13310,10 @@
     </row>
     <row r="9" ht="16.5" spans="1:10">
       <c r="A9" s="148" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B9" s="152" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C9" s="152"/>
       <c r="D9" s="152"/>
@@ -13287,23 +13326,23 @@
     </row>
     <row r="10" ht="16.5" spans="1:10">
       <c r="A10" s="148" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B10" s="157">
         <v>1</v>
       </c>
       <c r="C10" s="157"/>
       <c r="D10" s="167" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E10" s="157">
         <v>1</v>
       </c>
       <c r="F10" s="167" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="G10" s="147" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H10" s="147"/>
       <c r="I10" s="147"/>
@@ -13311,7 +13350,7 @@
     </row>
     <row r="11" ht="16.5" spans="1:10">
       <c r="A11" s="148" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B11" s="158">
         <v>1</v>
@@ -13327,7 +13366,7 @@
     </row>
     <row r="12" ht="16.5" spans="1:10">
       <c r="A12" s="148" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B12" s="159">
         <v>1</v>
@@ -13345,17 +13384,17 @@
     </row>
     <row r="13" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A13" s="148" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="168" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -13363,10 +13402,10 @@
     </row>
     <row r="14" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A14" s="148" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B14" s="170" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C14" s="170"/>
       <c r="D14" s="170"/>
@@ -13441,7 +13480,7 @@
   <sheetData>
     <row r="1" s="117" customFormat="1" spans="1:9">
       <c r="A1" s="121" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B1" s="122"/>
       <c r="C1" s="117" t="s">
@@ -13466,10 +13505,10 @@
     </row>
     <row r="2" s="118" customFormat="1" spans="1:9">
       <c r="A2" s="125" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B2" s="126" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C2" s="127" t="s">
         <v>7</v>
@@ -13481,7 +13520,7 @@
     <row r="3" s="118" customFormat="1" spans="1:9">
       <c r="A3" s="130"/>
       <c r="B3" s="126" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C3" s="127" t="s">
         <v>28</v>
@@ -13503,7 +13542,7 @@
     <row r="5" s="118" customFormat="1" spans="1:9">
       <c r="A5" s="130"/>
       <c r="B5" s="126" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C5" s="127" t="s">
         <v>31</v>
@@ -13515,7 +13554,7 @@
     <row r="6" s="118" customFormat="1" spans="1:9">
       <c r="A6" s="130"/>
       <c r="B6" s="126" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>19</v>
@@ -13543,7 +13582,7 @@
     <row r="8" s="118" customFormat="1" spans="1:9">
       <c r="A8" s="130"/>
       <c r="B8" s="126" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>14</v>
@@ -13557,7 +13596,7 @@
     <row r="9" s="118" customFormat="1" spans="1:9">
       <c r="A9" s="130"/>
       <c r="B9" s="126" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C9" s="127" t="s">
         <v>24</v>
@@ -13569,7 +13608,7 @@
     <row r="10" s="118" customFormat="1" spans="1:9">
       <c r="A10" s="130"/>
       <c r="B10" s="126" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C10" s="127" t="s">
         <v>34</v>
@@ -13581,7 +13620,7 @@
     <row r="11" s="118" customFormat="1" spans="1:9">
       <c r="A11" s="134"/>
       <c r="B11" s="126" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C11" s="127" t="s">
         <v>69</v>
@@ -13592,10 +13631,10 @@
     </row>
     <row r="12" s="119" customFormat="1" spans="1:9">
       <c r="A12" s="135" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B12" s="136" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C12" s="137" t="s">
         <v>88</v>
@@ -13619,10 +13658,10 @@
     <row r="14" s="119" customFormat="1" spans="1:9">
       <c r="A14" s="141"/>
       <c r="B14" s="136" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C14" s="137" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D14" s="142"/>
       <c r="E14" s="138"/>
@@ -13633,7 +13672,7 @@
     <row r="15" s="119" customFormat="1" spans="1:9">
       <c r="A15" s="141"/>
       <c r="B15" s="136" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C15" s="137" t="s">
         <v>10</v>
@@ -13655,7 +13694,7 @@
     <row r="17" s="119" customFormat="1" spans="1:7">
       <c r="A17" s="141"/>
       <c r="B17" s="136" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C17" s="137" t="s">
         <v>27</v>
@@ -13667,7 +13706,7 @@
     <row r="18" s="119" customFormat="1" spans="1:7">
       <c r="A18" s="141"/>
       <c r="B18" s="136" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C18" s="137" t="s">
         <v>42</v>
@@ -13679,7 +13718,7 @@
     <row r="19" s="119" customFormat="1" spans="1:7">
       <c r="A19" s="141"/>
       <c r="B19" s="136" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C19" s="137" t="s">
         <v>81</v>
@@ -13691,7 +13730,7 @@
     <row r="20" s="119" customFormat="1" spans="1:7">
       <c r="A20" s="141"/>
       <c r="B20" s="136" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C20" s="137" t="s">
         <v>84</v>
@@ -13703,7 +13742,7 @@
     <row r="21" s="119" customFormat="1" spans="1:7">
       <c r="A21" s="141"/>
       <c r="B21" s="136" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C21" s="143"/>
       <c r="D21" s="144"/>
@@ -13715,7 +13754,7 @@
     <row r="22" s="119" customFormat="1" spans="1:7">
       <c r="A22" s="145"/>
       <c r="B22" s="136" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C22" s="143"/>
       <c r="D22" s="146"/>
@@ -13777,7 +13816,7 @@
   <sheetData>
     <row r="1" s="91" customFormat="1" customHeight="1" spans="1:16">
       <c r="A1" s="94" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B1" s="95"/>
       <c r="C1" s="95"/>
@@ -13808,7 +13847,7 @@
     </row>
     <row r="3" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A3" s="100" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B3" s="101"/>
       <c r="C3" s="102"/>
@@ -14000,7 +14039,7 @@
     </row>
     <row r="11" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A11" s="100" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B11" s="101"/>
       <c r="C11" s="102"/>
@@ -14192,7 +14231,7 @@
     </row>
     <row r="19" s="93" customFormat="1" customHeight="1" spans="1:9">
       <c r="A19" s="100" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B19" s="101"/>
       <c r="C19" s="102"/>
@@ -14419,13 +14458,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="82" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B1" s="83" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C1" s="84" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -14433,208 +14472,208 @@
         <v>1</v>
       </c>
       <c r="B2" s="80" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C2" s="81" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="85"/>
       <c r="B3" s="80" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C3" s="81" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="85"/>
       <c r="B4" s="80" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C4" s="81" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="85"/>
       <c r="B5" s="80" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C5" s="81" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="85"/>
       <c r="B6" s="80" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C6" s="81" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="85"/>
       <c r="B7" s="80" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C7" s="81" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="85"/>
       <c r="B8" s="80" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C8" s="81" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="85"/>
       <c r="B9" s="80" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="85"/>
       <c r="B10" s="80" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C10" s="81" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="85"/>
       <c r="B11" s="80" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C11" s="81" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="85"/>
       <c r="B12" s="80" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C12" s="81" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="85"/>
       <c r="B13" s="80" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C13" s="81" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="85"/>
       <c r="B14" s="80" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="85"/>
       <c r="B15" s="80" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C15" s="81" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="85"/>
       <c r="B16" s="80" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C16" s="81" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="85"/>
       <c r="B17" s="80" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C17" s="81" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="85"/>
       <c r="B18" s="80" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C18" s="81" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="85"/>
       <c r="B19" s="80" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C19" s="81" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="85"/>
       <c r="B20" s="80" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C20" s="81" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="85"/>
       <c r="B21" s="80" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C21" s="81" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="85"/>
       <c r="B22" s="80" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C22" s="81" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="85"/>
       <c r="B23" s="80" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C23" s="81" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="85"/>
       <c r="B24" s="80" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C24" s="81" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -14642,118 +14681,118 @@
         <v>2</v>
       </c>
       <c r="B25" s="80" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C25" s="81" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="86"/>
       <c r="B26" s="80" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C26" s="81" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="86"/>
       <c r="B27" s="80" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C27" s="81" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="86"/>
       <c r="B28" s="80" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C28" s="81" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="86"/>
       <c r="B29" s="80" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C29" s="81" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="86"/>
       <c r="B30" s="80" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C30" s="81" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="86"/>
       <c r="B31" s="80" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C31" s="81" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="86"/>
       <c r="B32" s="80" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C32" s="81" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="86"/>
       <c r="B33" s="80" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C33" s="81" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="86"/>
       <c r="B34" s="80" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C34" s="81" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="86"/>
       <c r="B35" s="80" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C35" s="81" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="86"/>
       <c r="B36" s="80" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C36" s="81" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="87"/>
       <c r="B37" s="80" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C37" s="81" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -14761,138 +14800,138 @@
         <v>3</v>
       </c>
       <c r="B38" s="80" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C38" s="81" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="89"/>
       <c r="B39" s="80" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C39" s="81" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="89"/>
       <c r="B40" s="80" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C40" s="81" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="89"/>
       <c r="B41" s="80" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C41" s="81" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="89"/>
       <c r="B42" s="80" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C42" s="81" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="89"/>
       <c r="B43" s="80" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C43" s="81" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="89"/>
       <c r="B44" s="80" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C44" s="81" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="89"/>
       <c r="B45" s="80" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C45" s="81" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="89"/>
       <c r="B46" s="80" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C46" s="81" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="89"/>
       <c r="B47" s="80" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C47" s="81" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="89"/>
       <c r="B48" s="80" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C48" s="81" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="89"/>
       <c r="B49" s="80" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C49" s="81" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="90"/>
       <c r="B50" s="80" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C50" s="81" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:3">
       <c r="A51" s="79"/>
       <c r="B51" s="80" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C51" s="81"/>
     </row>
     <row r="52" customFormat="1" spans="1:3">
       <c r="A52" s="79"/>
       <c r="B52" s="80" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C52" s="81"/>
     </row>
     <row r="53" customFormat="1" spans="1:3">
       <c r="A53" s="79"/>
       <c r="B53" s="80" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C53" s="81"/>
     </row>

--- a/c/9班资料.xlsx
+++ b/c/9班资料.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="610">
   <si>
     <t>姓名</t>
   </si>
@@ -228,7 +228,7 @@
     <t>咬手指、拉杆包、张桢烨、点空调时开窗、英语小测上画画/写“看不懂”“不写交不了作业”、跑操走路/提裤子</t>
   </si>
   <si>
-    <t>跑操回班速度</t>
+    <t>跑操（回班速度、套圈）、手套、放学零食、走路（眼为证、脚近乎擦地、步幅大、身体前倾）</t>
   </si>
   <si>
     <t>林梓颢</t>
@@ -364,7 +364,7 @@
     <t>和叶弘毅分享菜</t>
   </si>
   <si>
-    <t>中午拿2矿泉水、番茄沙司</t>
+    <t>中午拿2矿泉水、番茄沙司、被叫到：抱头</t>
   </si>
   <si>
     <t>钱尚恩</t>
@@ -514,7 +514,7 @@
     <t>物1</t>
   </si>
   <si>
-    <t>读“m”“l”“等于”、写“解”、M来了、给课代表买奶茶、自印卷子、提前进班、写其他课作业、物理课本拿出来、上句话是什么</t>
+    <t>读“m”“l”“等于”、写“解”、M来了、给课代表买奶茶、自印卷子、提前进班、写其他课作业、物理课本拿出来、上句话是什么、作业课上完成</t>
   </si>
   <si>
     <t>体1</t>
@@ -757,6 +757,12 @@
     </r>
   </si>
   <si>
+    <t>八上1.15</t>
+  </si>
+  <si>
+    <t>语：我觉得他写的这些朋友圈都挺好的。</t>
+  </si>
+  <si>
     <t>孔祥懿睡觉</t>
   </si>
   <si>
@@ -859,7 +865,7 @@
     <t>信仰</t>
   </si>
   <si>
-    <t>叶弘毅：10班早读（或课前三分钟？）读书声小，冯越：你们要学习9班，他们读书特别有革命信念。举个例子，他们读中国共产党读到“信仰”两个字时特别大声。</t>
+    <t>叶弘毅：10班早读（或课前三分钟？）读书声小，冯越：你们要学习9班，他们读书特别有革命信念。举个例子，他们读中国共产党诞生，读到“信仰”两个字时特别大声。</t>
   </si>
   <si>
     <t>40中</t>
@@ -869,6 +875,9 @@
   </si>
   <si>
     <t>铃声错乱：①（周三）9：10响预备铃②响铃响到一半停止，几秒后重新响起</t>
+  </si>
+  <si>
+    <t>往棚子跑时不到一半脱离队伍走路，在白线前调头（套圈最厉害）</t>
   </si>
   <si>
     <t>政治课</t>
@@ -3162,19 +3171,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <strike/>
-      <sz val="11"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="华文仿宋"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3188,6 +3186,17 @@
       <name val="黑体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="华文仿宋"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="57">
@@ -3953,7 +3962,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="224">
+  <cellXfs count="222">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4588,12 +4597,6 @@
     </xf>
     <xf numFmtId="20" fontId="1" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4968,29 +4971,29 @@
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="7.59090909090909" style="71" customWidth="1"/>
-    <col min="2" max="7" width="25.8727272727273" style="218" customWidth="1"/>
+    <col min="2" max="7" width="25.8727272727273" style="216" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="217" customFormat="1" spans="1:7">
+    <row r="1" s="215" customFormat="1" spans="1:7">
       <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="219" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="219" t="s">
+      <c r="B1" s="217" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="217" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="219" t="s">
+      <c r="D1" s="217" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="219" t="s">
+      <c r="E1" s="217" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="219" t="s">
+      <c r="F1" s="217" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="219" t="s">
+      <c r="G1" s="217" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4998,10 +5001,10 @@
       <c r="A2" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="218" t="s">
+      <c r="B2" s="216" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="218" t="s">
+      <c r="C2" s="216" t="s">
         <v>9</v>
       </c>
     </row>
@@ -5009,10 +5012,10 @@
       <c r="A3" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="218" t="s">
+      <c r="C3" s="216" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="218" t="s">
+      <c r="D3" s="216" t="s">
         <v>12</v>
       </c>
     </row>
@@ -5025,10 +5028,10 @@
       <c r="A5" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="218" t="s">
+      <c r="C5" s="216" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="218" t="s">
+      <c r="D5" s="216" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5036,7 +5039,7 @@
       <c r="A6" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="218" t="s">
+      <c r="C6" s="216" t="s">
         <v>18</v>
       </c>
     </row>
@@ -5044,13 +5047,13 @@
       <c r="A7" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="218" t="s">
+      <c r="B7" s="216" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="218" t="s">
+      <c r="C7" s="216" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="218" t="s">
+      <c r="D7" s="216" t="s">
         <v>22</v>
       </c>
     </row>
@@ -5068,7 +5071,7 @@
       <c r="A10" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="218" t="s">
+      <c r="B10" s="216" t="s">
         <v>26</v>
       </c>
     </row>
@@ -5086,7 +5089,7 @@
       <c r="A13" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="218" t="s">
+      <c r="D13" s="216" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5094,7 +5097,7 @@
       <c r="A14" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="218" t="s">
+      <c r="B14" s="216" t="s">
         <v>32</v>
       </c>
     </row>
@@ -5107,7 +5110,7 @@
       <c r="A16" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="218" t="s">
+      <c r="C16" s="216" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5115,7 +5118,7 @@
       <c r="A17" s="72" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="218" t="s">
+      <c r="C17" s="216" t="s">
         <v>37</v>
       </c>
     </row>
@@ -5123,7 +5126,7 @@
       <c r="A18" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="218" t="s">
+      <c r="D18" s="216" t="s">
         <v>39</v>
       </c>
     </row>
@@ -5131,7 +5134,7 @@
       <c r="A19" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="218" t="s">
+      <c r="D19" s="216" t="s">
         <v>41</v>
       </c>
     </row>
@@ -5139,10 +5142,10 @@
       <c r="A20" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="218" t="s">
+      <c r="B20" s="216" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="218" t="s">
+      <c r="C20" s="216" t="s">
         <v>44</v>
       </c>
     </row>
@@ -5150,13 +5153,13 @@
       <c r="A21" s="72" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="218" t="s">
+      <c r="B21" s="216" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="218" t="s">
+      <c r="C21" s="216" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="218" t="s">
+      <c r="D21" s="216" t="s">
         <v>48</v>
       </c>
     </row>
@@ -5169,7 +5172,7 @@
       <c r="A23" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="218" t="s">
+      <c r="B23" s="216" t="s">
         <v>51</v>
       </c>
     </row>
@@ -5177,13 +5180,13 @@
       <c r="A24" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="218" t="s">
+      <c r="B24" s="216" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="218" t="s">
+      <c r="C24" s="216" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="218" t="s">
+      <c r="D24" s="216" t="s">
         <v>55</v>
       </c>
     </row>
@@ -5201,10 +5204,10 @@
       <c r="A27" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="B27" s="218" t="s">
+      <c r="B27" s="216" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="218" t="s">
+      <c r="C27" s="216" t="s">
         <v>60</v>
       </c>
     </row>
@@ -5212,13 +5215,13 @@
       <c r="A28" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="B28" s="218" t="s">
+      <c r="B28" s="216" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="218" t="s">
+      <c r="C28" s="216" t="s">
         <v>63</v>
       </c>
-      <c r="D28" s="218" t="s">
+      <c r="D28" s="216" t="s">
         <v>64</v>
       </c>
     </row>
@@ -5231,10 +5234,10 @@
       <c r="A30" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="B30" s="218" t="s">
+      <c r="B30" s="216" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="218" t="s">
+      <c r="C30" s="216" t="s">
         <v>68</v>
       </c>
     </row>
@@ -5267,7 +5270,7 @@
       <c r="A36" s="72" t="s">
         <v>74</v>
       </c>
-      <c r="B36" s="218" t="s">
+      <c r="B36" s="216" t="s">
         <v>75</v>
       </c>
     </row>
@@ -5275,10 +5278,10 @@
       <c r="A37" s="72" t="s">
         <v>76</v>
       </c>
-      <c r="C37" s="218" t="s">
+      <c r="C37" s="216" t="s">
         <v>77</v>
       </c>
-      <c r="D37" s="218" t="s">
+      <c r="D37" s="216" t="s">
         <v>78</v>
       </c>
     </row>
@@ -5286,23 +5289,23 @@
       <c r="A38" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="B38" s="218" t="s">
+      <c r="B38" s="216" t="s">
         <v>80</v>
       </c>
-      <c r="C38" s="220"/>
-      <c r="D38" s="220"/>
-      <c r="E38" s="220"/>
-      <c r="F38" s="220"/>
-      <c r="G38" s="220"/>
+      <c r="C38" s="218"/>
+      <c r="D38" s="218"/>
+      <c r="E38" s="218"/>
+      <c r="F38" s="218"/>
+      <c r="G38" s="218"/>
     </row>
     <row r="39" ht="26" spans="1:8">
       <c r="A39" s="72" t="s">
         <v>81</v>
       </c>
-      <c r="C39" s="218" t="s">
+      <c r="C39" s="216" t="s">
         <v>82</v>
       </c>
-      <c r="D39" s="218" t="s">
+      <c r="D39" s="216" t="s">
         <v>83</v>
       </c>
     </row>
@@ -5310,13 +5313,13 @@
       <c r="A40" s="72" t="s">
         <v>84</v>
       </c>
-      <c r="B40" s="218" t="s">
+      <c r="B40" s="216" t="s">
         <v>85</v>
       </c>
-      <c r="C40" s="218" t="s">
+      <c r="C40" s="216" t="s">
         <v>86</v>
       </c>
-      <c r="D40" s="218" t="s">
+      <c r="D40" s="216" t="s">
         <v>87</v>
       </c>
     </row>
@@ -5324,13 +5327,13 @@
       <c r="A41" s="72" t="s">
         <v>88</v>
       </c>
-      <c r="C41" s="218" t="s">
+      <c r="C41" s="216" t="s">
         <v>89</v>
       </c>
-      <c r="D41" s="218" t="s">
+      <c r="D41" s="216" t="s">
         <v>90</v>
       </c>
-      <c r="H41" s="221" t="s">
+      <c r="H41" s="219" t="s">
         <v>91</v>
       </c>
     </row>
@@ -5343,7 +5346,7 @@
       <c r="A43" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="B43" s="218" t="s">
+      <c r="B43" s="216" t="s">
         <v>94</v>
       </c>
     </row>
@@ -5351,18 +5354,18 @@
       <c r="A44" s="72" t="s">
         <v>95</v>
       </c>
-      <c r="B44" s="218" t="s">
+      <c r="B44" s="216" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" ht="26" spans="1:8">
       <c r="A45" s="72" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="218" t="s">
+      <c r="C45" s="216" t="s">
         <v>98</v>
       </c>
-      <c r="D45" s="218" t="s">
+      <c r="D45" s="216" t="s">
         <v>99</v>
       </c>
     </row>
@@ -5375,7 +5378,7 @@
       <c r="A47" s="72" t="s">
         <v>101</v>
       </c>
-      <c r="D47" s="218" t="s">
+      <c r="D47" s="216" t="s">
         <v>102</v>
       </c>
     </row>
@@ -5383,10 +5386,10 @@
       <c r="A48" s="72" t="s">
         <v>103</v>
       </c>
-      <c r="C48" s="218" t="s">
+      <c r="C48" s="216" t="s">
         <v>104</v>
       </c>
-      <c r="D48" s="218" t="s">
+      <c r="D48" s="216" t="s">
         <v>105</v>
       </c>
     </row>
@@ -5399,7 +5402,7 @@
       <c r="A50" s="72" t="s">
         <v>107</v>
       </c>
-      <c r="C50" s="218" t="s">
+      <c r="C50" s="216" t="s">
         <v>108</v>
       </c>
     </row>
@@ -5412,10 +5415,10 @@
       <c r="A52" s="72" t="s">
         <v>110</v>
       </c>
-      <c r="B52" s="218" t="s">
+      <c r="B52" s="216" t="s">
         <v>111</v>
       </c>
-      <c r="C52" s="218" t="s">
+      <c r="C52" s="216" t="s">
         <v>112</v>
       </c>
     </row>
@@ -5423,36 +5426,36 @@
       <c r="A53" s="71" t="s">
         <v>113</v>
       </c>
-      <c r="B53" s="218" t="s">
+      <c r="B53" s="216" t="s">
         <v>114</v>
       </c>
-      <c r="D53" s="220"/>
-      <c r="E53" s="220"/>
-      <c r="F53" s="220"/>
-      <c r="G53" s="220"/>
+      <c r="D53" s="218"/>
+      <c r="E53" s="218"/>
+      <c r="F53" s="218"/>
+      <c r="G53" s="218"/>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="71" t="s">
         <v>115</v>
       </c>
-      <c r="B54" s="218" t="s">
+      <c r="B54" s="216" t="s">
         <v>116</v>
       </c>
-      <c r="C54" s="218" t="s">
+      <c r="C54" s="216" t="s">
         <v>117</v>
       </c>
-      <c r="D54" s="220"/>
-      <c r="E54" s="220"/>
-      <c r="F54" s="220"/>
-      <c r="G54" s="220"/>
+      <c r="D54" s="218"/>
+      <c r="E54" s="218"/>
+      <c r="F54" s="218"/>
+      <c r="G54" s="218"/>
     </row>
     <row r="55" ht="65" spans="1:7">
       <c r="A55" s="71" t="s">
         <v>118</v>
       </c>
-      <c r="B55" s="220"/>
-      <c r="C55" s="220"/>
-      <c r="D55" s="218" t="s">
+      <c r="B55" s="218"/>
+      <c r="C55" s="218"/>
+      <c r="D55" s="216" t="s">
         <v>119</v>
       </c>
     </row>
@@ -5464,7 +5467,7 @@
         <v>121</v>
       </c>
       <c r="C56" s="78"/>
-      <c r="D56" s="218" t="s">
+      <c r="D56" s="216" t="s">
         <v>122</v>
       </c>
     </row>
@@ -5478,7 +5481,7 @@
       <c r="C57" s="78" t="s">
         <v>125</v>
       </c>
-      <c r="D57" s="218" t="s">
+      <c r="D57" s="216" t="s">
         <v>126</v>
       </c>
     </row>
@@ -5486,37 +5489,37 @@
       <c r="A58" s="71" t="s">
         <v>127</v>
       </c>
-      <c r="B58" s="218" t="s">
+      <c r="B58" s="216" t="s">
         <v>128</v>
       </c>
-      <c r="C58" s="220"/>
-      <c r="D58" s="220"/>
-      <c r="E58" s="220"/>
-      <c r="F58" s="220"/>
-      <c r="G58" s="220"/>
+      <c r="C58" s="218"/>
+      <c r="D58" s="218"/>
+      <c r="E58" s="218"/>
+      <c r="F58" s="218"/>
+      <c r="G58" s="218"/>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="B59" s="220"/>
-      <c r="C59" s="218" t="s">
+      <c r="B59" s="218"/>
+      <c r="C59" s="216" t="s">
         <v>130</v>
       </c>
-      <c r="D59" s="220"/>
-      <c r="E59" s="220"/>
-      <c r="F59" s="220"/>
-      <c r="G59" s="220"/>
+      <c r="D59" s="218"/>
+      <c r="E59" s="218"/>
+      <c r="F59" s="218"/>
+      <c r="G59" s="218"/>
     </row>
     <row r="60" ht="52" spans="1:7">
       <c r="A60" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="B60" s="220" t="s">
+      <c r="B60" s="218" t="s">
         <v>132</v>
       </c>
-      <c r="C60" s="220"/>
-      <c r="D60" s="218" t="s">
+      <c r="C60" s="218"/>
+      <c r="D60" s="216" t="s">
         <v>133</v>
       </c>
     </row>
@@ -5528,18 +5531,18 @@
         <v>135</v>
       </c>
       <c r="C61" s="78"/>
-      <c r="D61" s="220"/>
-      <c r="E61" s="220"/>
-      <c r="F61" s="220"/>
-      <c r="G61" s="220"/>
+      <c r="D61" s="218"/>
+      <c r="E61" s="218"/>
+      <c r="F61" s="218"/>
+      <c r="G61" s="218"/>
     </row>
     <row r="62" ht="39" spans="1:7">
       <c r="A62" s="71" t="s">
         <v>136</v>
       </c>
-      <c r="B62" s="220"/>
-      <c r="C62" s="220"/>
-      <c r="D62" s="218" t="s">
+      <c r="B62" s="218"/>
+      <c r="C62" s="218"/>
+      <c r="D62" s="216" t="s">
         <v>137</v>
       </c>
     </row>
@@ -5553,18 +5556,18 @@
       <c r="C63" s="78" t="s">
         <v>140</v>
       </c>
-      <c r="D63" s="220"/>
-      <c r="E63" s="220"/>
-      <c r="F63" s="220"/>
-      <c r="G63" s="220"/>
+      <c r="D63" s="218"/>
+      <c r="E63" s="218"/>
+      <c r="F63" s="218"/>
+      <c r="G63" s="218"/>
     </row>
     <row r="64" ht="26" spans="1:7">
       <c r="A64" s="71" t="s">
         <v>141</v>
       </c>
-      <c r="B64" s="220"/>
-      <c r="C64" s="220"/>
-      <c r="D64" s="218" t="s">
+      <c r="B64" s="218"/>
+      <c r="C64" s="218"/>
+      <c r="D64" s="216" t="s">
         <v>142</v>
       </c>
     </row>
@@ -5572,42 +5575,42 @@
       <c r="A65" s="71" t="s">
         <v>143</v>
       </c>
-      <c r="B65" s="222" t="s">
+      <c r="B65" s="220" t="s">
         <v>144</v>
       </c>
-      <c r="C65" s="220"/>
-      <c r="D65" s="220"/>
-      <c r="E65" s="220"/>
-      <c r="F65" s="220"/>
-      <c r="G65" s="220"/>
+      <c r="C65" s="218"/>
+      <c r="D65" s="218"/>
+      <c r="E65" s="218"/>
+      <c r="F65" s="218"/>
+      <c r="G65" s="218"/>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="71" t="s">
         <v>145</v>
       </c>
-      <c r="B66" s="220"/>
-      <c r="C66" s="218" t="s">
+      <c r="B66" s="218"/>
+      <c r="C66" s="216" t="s">
         <v>146</v>
       </c>
-      <c r="D66" s="220"/>
-      <c r="E66" s="220"/>
-      <c r="F66" s="220"/>
-      <c r="G66" s="220"/>
+      <c r="D66" s="218"/>
+      <c r="E66" s="218"/>
+      <c r="F66" s="218"/>
+      <c r="G66" s="218"/>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="71" t="s">
         <v>147</v>
       </c>
-      <c r="B67" s="220"/>
-      <c r="C67" s="220"/>
+      <c r="B67" s="218"/>
+      <c r="C67" s="218"/>
     </row>
     <row r="68" ht="65" spans="1:7">
       <c r="A68" s="71" t="s">
         <v>148</v>
       </c>
-      <c r="B68" s="220"/>
-      <c r="C68" s="220"/>
-      <c r="D68" s="218" t="s">
+      <c r="B68" s="218"/>
+      <c r="C68" s="218"/>
+      <c r="D68" s="216" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5628,45 +5631,45 @@
         <v>153</v>
       </c>
       <c r="C70" s="78"/>
-      <c r="D70" s="220"/>
-      <c r="E70" s="220"/>
-      <c r="F70" s="220"/>
-      <c r="G70" s="220"/>
+      <c r="D70" s="218"/>
+      <c r="E70" s="218"/>
+      <c r="F70" s="218"/>
+      <c r="G70" s="218"/>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="71" t="s">
         <v>154</v>
       </c>
-      <c r="B71" s="220"/>
-      <c r="C71" s="220"/>
+      <c r="B71" s="218"/>
+      <c r="C71" s="218"/>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="B72" s="218" t="s">
+      <c r="B72" s="216" t="s">
         <v>156</v>
       </c>
-      <c r="C72" s="218" t="s">
+      <c r="C72" s="216" t="s">
         <v>157</v>
       </c>
-      <c r="D72" s="220"/>
-      <c r="E72" s="220"/>
-      <c r="F72" s="220"/>
-      <c r="G72" s="220"/>
+      <c r="D72" s="218"/>
+      <c r="E72" s="218"/>
+      <c r="F72" s="218"/>
+      <c r="G72" s="218"/>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="71" t="s">
         <v>158</v>
       </c>
-      <c r="B73" s="220"/>
-      <c r="C73" s="218" t="s">
+      <c r="B73" s="218"/>
+      <c r="C73" s="216" t="s">
         <v>159</v>
       </c>
-      <c r="D73" s="220"/>
-      <c r="E73" s="220"/>
-      <c r="F73" s="220"/>
-      <c r="G73" s="220"/>
+      <c r="D73" s="218"/>
+      <c r="E73" s="218"/>
+      <c r="F73" s="218"/>
+      <c r="G73" s="218"/>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="71" t="s">
@@ -5677,18 +5680,18 @@
       <c r="A75" s="71" t="s">
         <v>161</v>
       </c>
-      <c r="D75" s="220"/>
-      <c r="E75" s="220"/>
-      <c r="F75" s="220"/>
-      <c r="G75" s="220"/>
+      <c r="D75" s="218"/>
+      <c r="E75" s="218"/>
+      <c r="F75" s="218"/>
+      <c r="G75" s="218"/>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="71" t="s">
         <v>162</v>
       </c>
-      <c r="B76" s="220"/>
-      <c r="C76" s="220"/>
-      <c r="D76" s="218" t="s">
+      <c r="B76" s="218"/>
+      <c r="C76" s="218"/>
+      <c r="D76" s="216" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5700,10 +5703,10 @@
       <c r="C77" s="78"/>
     </row>
     <row r="78" ht="26" spans="1:7">
-      <c r="A78" s="223" t="s">
+      <c r="A78" s="221" t="s">
         <v>165</v>
       </c>
-      <c r="B78" s="218" t="s">
+      <c r="B78" s="216" t="s">
         <v>166</v>
       </c>
     </row>
@@ -5757,16 +5760,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="67" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B1" s="68" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="69" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D1" s="70" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5780,7 +5783,7 @@
         <v>20111216</v>
       </c>
       <c r="D2" s="66" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -5794,7 +5797,7 @@
         <v>20111227</v>
       </c>
       <c r="D3" s="66" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -5808,7 +5811,7 @@
         <v>20120518</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:4">
@@ -5836,7 +5839,7 @@
         <v>20120504</v>
       </c>
       <c r="D6" s="66" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -5850,7 +5853,7 @@
         <v>20120809</v>
       </c>
       <c r="D7" s="66" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -5864,7 +5867,7 @@
         <v>20120227</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -5878,7 +5881,7 @@
         <v>20120127</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -5892,7 +5895,7 @@
         <v>20111202</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:4">
@@ -5918,7 +5921,7 @@
         <v>20111024</v>
       </c>
       <c r="D12" s="66" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -5932,7 +5935,7 @@
         <v>20110908</v>
       </c>
       <c r="D13" s="66" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -5946,7 +5949,7 @@
         <v>20120228</v>
       </c>
       <c r="D14" s="66" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:4">
@@ -5972,7 +5975,7 @@
         <v>20111201</v>
       </c>
       <c r="D16" s="66" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -5986,7 +5989,7 @@
         <v>20120722</v>
       </c>
       <c r="D17" s="66" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:4">
@@ -6024,7 +6027,7 @@
         <v>20120530</v>
       </c>
       <c r="D20" s="66" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -6038,7 +6041,7 @@
         <v>20120827</v>
       </c>
       <c r="D21" s="66" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:4">
@@ -6064,7 +6067,7 @@
         <v>20120518</v>
       </c>
       <c r="D23" s="66" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -6078,7 +6081,7 @@
         <v>20120413</v>
       </c>
       <c r="D24" s="66" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -6092,7 +6095,7 @@
         <v>20120629</v>
       </c>
       <c r="D25" s="66" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -6106,7 +6109,7 @@
         <v>20111105</v>
       </c>
       <c r="D26" s="66" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -6120,7 +6123,7 @@
         <v>20120112</v>
       </c>
       <c r="D27" s="66" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -6134,7 +6137,7 @@
         <v>20111119</v>
       </c>
       <c r="D28" s="66" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:4">
@@ -6160,7 +6163,7 @@
         <v>20120331</v>
       </c>
       <c r="D30" s="66" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -6174,7 +6177,7 @@
         <v>20111109</v>
       </c>
       <c r="D31" s="66" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -6188,7 +6191,7 @@
         <v>20120824</v>
       </c>
       <c r="D32" s="66" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:5">
@@ -6214,7 +6217,7 @@
         <v>20120624</v>
       </c>
       <c r="D34" s="66" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:5">
@@ -6240,7 +6243,7 @@
         <v>20120603</v>
       </c>
       <c r="D36" s="66" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -6254,7 +6257,7 @@
         <v>20120326</v>
       </c>
       <c r="D37" s="66" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -6268,10 +6271,10 @@
         <v>20111106</v>
       </c>
       <c r="D38" s="77" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E38" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -6285,7 +6288,7 @@
         <v>20120811</v>
       </c>
       <c r="D39" s="78" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -6299,7 +6302,7 @@
         <v>20111217</v>
       </c>
       <c r="D40" s="78" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -6313,10 +6316,10 @@
         <v>20111013</v>
       </c>
       <c r="D41" s="66" t="s">
+        <v>457</v>
+      </c>
+      <c r="E41" t="s">
         <v>454</v>
-      </c>
-      <c r="E41" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:5">
@@ -6342,7 +6345,7 @@
         <v>20120207</v>
       </c>
       <c r="D43" s="66" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:5">
@@ -6368,7 +6371,7 @@
         <v>20110929</v>
       </c>
       <c r="D45" s="66" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:5">
@@ -6394,10 +6397,10 @@
         <v>20120108</v>
       </c>
       <c r="D47" s="66" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="E47" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -6411,7 +6414,7 @@
         <v>20120311</v>
       </c>
       <c r="D48" s="66" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:4">
@@ -6437,7 +6440,7 @@
         <v>20120723</v>
       </c>
       <c r="D50" s="66" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:4">
@@ -6463,7 +6466,7 @@
         <v>20111220</v>
       </c>
       <c r="D52" s="66" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
   </sheetData>
@@ -6496,34 +6499,34 @@
   <sheetData>
     <row r="1" s="27" customFormat="1" spans="1:5">
       <c r="A1" s="34" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="D1" s="37"/>
       <c r="E1" s="38" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="2" s="28" customFormat="1" ht="409" customHeight="1" spans="1:5">
       <c r="A2" s="39" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="3" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6531,10 +6534,10 @@
       <c r="B3" s="43"/>
       <c r="C3" s="44"/>
       <c r="D3" s="32" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4" s="28" customFormat="1" spans="1:5">
@@ -6542,10 +6545,10 @@
       <c r="B4" s="43"/>
       <c r="C4" s="44"/>
       <c r="D4" s="32" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="5" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6553,10 +6556,10 @@
       <c r="B5" s="43"/>
       <c r="C5" s="44"/>
       <c r="D5" s="32" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="6" s="28" customFormat="1" ht="238" spans="1:5">
@@ -6564,23 +6567,23 @@
       <c r="B6" s="43"/>
       <c r="C6" s="44"/>
       <c r="D6" s="32" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="7" s="28" customFormat="1" ht="238" spans="1:5">
       <c r="A7" s="42"/>
       <c r="B7" s="43"/>
       <c r="C7" s="41" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6588,10 +6591,10 @@
       <c r="B8" s="43"/>
       <c r="C8" s="44"/>
       <c r="D8" s="32" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9" s="28" customFormat="1" ht="84" spans="1:5">
@@ -6599,10 +6602,10 @@
       <c r="B9" s="43"/>
       <c r="C9" s="44"/>
       <c r="D9" s="32" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="10" s="28" customFormat="1" ht="28" spans="1:5">
@@ -6610,10 +6613,10 @@
       <c r="B10" s="43"/>
       <c r="C10" s="44"/>
       <c r="D10" s="32" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="11" s="28" customFormat="1" spans="1:5">
@@ -6621,10 +6624,10 @@
       <c r="B11" s="43"/>
       <c r="C11" s="45"/>
       <c r="D11" s="32" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="12" s="28" customFormat="1" ht="154" spans="1:5">
@@ -6632,50 +6635,50 @@
       <c r="B12" s="43"/>
       <c r="C12" s="31"/>
       <c r="D12" s="32" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="13" s="28" customFormat="1" ht="56" spans="1:5">
       <c r="A13" s="42"/>
       <c r="B13" s="43"/>
       <c r="C13" s="46" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="33" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="14" s="28" customFormat="1" ht="84" spans="1:5">
       <c r="A14" s="42"/>
       <c r="B14" s="43"/>
       <c r="C14" s="46" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="33" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="15" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A15" s="42"/>
       <c r="B15" s="43"/>
       <c r="C15" s="46" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D15" s="37"/>
       <c r="E15" s="33" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="16" s="28" customFormat="1" spans="1:5">
       <c r="A16" s="42"/>
       <c r="B16" s="43"/>
       <c r="C16" s="46" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="D16" s="37"/>
       <c r="E16" s="33"/>
@@ -6684,24 +6687,24 @@
       <c r="A17" s="42"/>
       <c r="B17" s="43"/>
       <c r="C17" s="46" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="33" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18" s="28" customFormat="1" spans="1:5">
       <c r="A18" s="42"/>
       <c r="B18" s="43"/>
       <c r="C18" s="41" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="19" s="28" customFormat="1" spans="1:5">
@@ -6709,17 +6712,17 @@
       <c r="B19" s="43"/>
       <c r="C19" s="45"/>
       <c r="D19" s="32" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="20" s="28" customFormat="1" spans="1:5">
       <c r="A20" s="42"/>
       <c r="B20" s="43"/>
       <c r="C20" s="46" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="D20" s="37"/>
       <c r="E20" s="33"/>
@@ -6728,61 +6731,61 @@
       <c r="A21" s="42"/>
       <c r="B21" s="43"/>
       <c r="C21" s="46" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="D21" s="37"/>
       <c r="E21" s="33" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="22" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A22" s="42"/>
       <c r="B22" s="43"/>
       <c r="C22" s="46" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="D22" s="47"/>
       <c r="E22" s="33" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="23" s="28" customFormat="1" spans="1:5">
       <c r="A23" s="42"/>
       <c r="B23" s="43"/>
       <c r="C23" s="31" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D23" s="31"/>
       <c r="E23" s="33" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="24" s="28" customFormat="1" spans="1:5">
       <c r="A24" s="42"/>
       <c r="B24" s="43"/>
       <c r="C24" s="31" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D24" s="31"/>
       <c r="E24" s="33" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="25" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A25" s="39" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="26" s="28" customFormat="1" spans="1:5">
@@ -6790,10 +6793,10 @@
       <c r="B26" s="43"/>
       <c r="C26" s="44"/>
       <c r="D26" s="32" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="27" s="28" customFormat="1" ht="28" spans="1:5">
@@ -6801,10 +6804,10 @@
       <c r="B27" s="43"/>
       <c r="C27" s="44"/>
       <c r="D27" s="32" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="28" s="28" customFormat="1" ht="42" spans="1:5">
@@ -6812,27 +6815,27 @@
       <c r="B28" s="43"/>
       <c r="C28" s="44"/>
       <c r="D28" s="32" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="29" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A29" s="39" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="30" s="28" customFormat="1" ht="70" spans="1:5">
@@ -6840,10 +6843,10 @@
       <c r="B30" s="43"/>
       <c r="C30" s="44"/>
       <c r="D30" s="32" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="31" s="28" customFormat="1" spans="1:5">
@@ -6851,10 +6854,10 @@
       <c r="B31" s="43"/>
       <c r="C31" s="44"/>
       <c r="D31" s="32" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="32" s="28" customFormat="1" ht="28" spans="1:5">
@@ -6862,53 +6865,53 @@
       <c r="B32" s="43"/>
       <c r="C32" s="45"/>
       <c r="D32" s="32" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="33" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A33" s="42"/>
       <c r="B33" s="49"/>
       <c r="C33" s="46" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="D33" s="47"/>
       <c r="E33" s="33" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="34" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A34" s="42"/>
       <c r="B34" s="50" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="D34" s="51"/>
       <c r="E34" s="52" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
     </row>
     <row r="35" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A35" s="53"/>
       <c r="B35" s="54"/>
       <c r="C35" s="36" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D35" s="51"/>
       <c r="E35" s="52" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
     </row>
     <row r="36" s="28" customFormat="1" spans="1:5">
       <c r="A36" s="39" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B36" s="55" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C36" s="56"/>
       <c r="D36" s="57"/>
@@ -6919,42 +6922,42 @@
     <row r="37" s="28" customFormat="1" spans="1:5">
       <c r="A37" s="53"/>
       <c r="B37" s="58" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C37" s="59"/>
       <c r="D37" s="60"/>
       <c r="E37" s="33" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
     </row>
     <row r="38" s="28" customFormat="1" spans="1:5">
       <c r="A38" s="29" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B38" s="58" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C38" s="59"/>
       <c r="D38" s="60"/>
       <c r="E38" s="33" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="39" s="28" customFormat="1" spans="1:5">
       <c r="A39" s="39" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B39" s="40" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C39" s="41" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
     </row>
     <row r="40" s="28" customFormat="1" spans="1:5">
@@ -6962,64 +6965,64 @@
       <c r="B40" s="43"/>
       <c r="C40" s="45"/>
       <c r="D40" s="32" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="E40" s="33" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="41" s="28" customFormat="1" spans="1:5">
       <c r="A41" s="42"/>
       <c r="B41" s="43"/>
       <c r="C41" s="46" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D41" s="47"/>
       <c r="E41" s="33" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
     </row>
     <row r="42" s="28" customFormat="1" spans="1:5">
       <c r="A42" s="53"/>
       <c r="B42" s="49"/>
       <c r="C42" s="46" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="D42" s="47"/>
       <c r="E42" s="33" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="43" s="28" customFormat="1" spans="1:5">
       <c r="A43" s="39" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B43" s="50" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C43" s="61" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D43" s="62"/>
       <c r="E43" s="52" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="44" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A44" s="42"/>
       <c r="B44" s="54"/>
       <c r="C44" s="61" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D44" s="62"/>
       <c r="E44" s="52" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
     </row>
     <row r="45" s="28" customFormat="1" spans="1:5">
       <c r="A45" s="53"/>
       <c r="B45" s="58" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="C45" s="59"/>
       <c r="D45" s="60"/>
@@ -7029,16 +7032,16 @@
     </row>
     <row r="46" s="28" customFormat="1" spans="1:5">
       <c r="A46" s="39" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B46" s="40" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C46" s="41" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="E46" s="33"/>
     </row>
@@ -7047,7 +7050,7 @@
       <c r="B47" s="43"/>
       <c r="C47" s="44"/>
       <c r="D47" s="32" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="E47" s="33"/>
     </row>
@@ -7056,42 +7059,42 @@
       <c r="B48" s="49"/>
       <c r="C48" s="45"/>
       <c r="D48" s="32" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
     <row r="49" s="28" customFormat="1" spans="1:5">
       <c r="A49" s="29" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B49" s="58" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C49" s="59"/>
       <c r="D49" s="60"/>
       <c r="E49" s="33" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="50" s="28" customFormat="1" spans="1:5">
       <c r="A50" s="39" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B50" s="58" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C50" s="59"/>
       <c r="D50" s="60"/>
       <c r="E50" s="33" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
     </row>
     <row r="51" s="28" customFormat="1" spans="1:5">
       <c r="A51" s="53"/>
       <c r="B51" s="58" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C51" s="59"/>
       <c r="D51" s="60"/>
@@ -7101,10 +7104,10 @@
     </row>
     <row r="52" s="28" customFormat="1" spans="1:5">
       <c r="A52" s="29" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B52" s="58" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C52" s="59"/>
       <c r="D52" s="60"/>
@@ -7112,10 +7115,10 @@
     </row>
     <row r="53" s="28" customFormat="1" spans="1:5">
       <c r="A53" s="39" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="B53" s="58" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C53" s="59"/>
       <c r="D53" s="60"/>
@@ -7127,18 +7130,18 @@
       <c r="C54" s="59"/>
       <c r="D54" s="60"/>
       <c r="E54" s="33" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="55" s="28" customFormat="1" spans="1:5">
       <c r="A55" s="29" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B55" s="30"/>
       <c r="C55" s="31"/>
       <c r="D55" s="32"/>
       <c r="E55" s="33" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
     </row>
   </sheetData>
@@ -7246,7 +7249,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
@@ -7260,7 +7263,7 @@
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="9" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="11"/>
@@ -7284,7 +7287,7 @@
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="9" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="11"/>
@@ -7297,7 +7300,7 @@
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="22" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="11"/>
@@ -7310,7 +7313,7 @@
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="9" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="11"/>
@@ -7344,7 +7347,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="10"/>
@@ -7390,7 +7393,7 @@
         <v>31</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="10"/>
@@ -7426,7 +7429,7 @@
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="22" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="11"/>
@@ -7460,10 +7463,10 @@
         <v>42</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="11"/>
@@ -7475,10 +7478,10 @@
         <v>45</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="11"/>
@@ -7501,7 +7504,7 @@
         <v>50</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="10"/>
@@ -7514,10 +7517,10 @@
         <v>52</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="11"/>
@@ -7551,10 +7554,10 @@
         <v>58</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="11"/>
@@ -7566,10 +7569,10 @@
         <v>61</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="11"/>
@@ -7593,7 +7596,7 @@
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="22" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="11"/>
@@ -7660,7 +7663,7 @@
         <v>74</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="10"/>
@@ -7674,7 +7677,7 @@
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="22" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="11"/>
@@ -7686,7 +7689,7 @@
         <v>79</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C38" s="25"/>
       <c r="D38" s="26"/>
@@ -7700,7 +7703,7 @@
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="22" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="11"/>
@@ -7712,10 +7715,10 @@
         <v>84</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="11"/>
@@ -7728,7 +7731,7 @@
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="22" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="D41" s="10"/>
       <c r="E41" s="11"/>
@@ -7751,7 +7754,7 @@
         <v>93</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="10"/>
@@ -7775,7 +7778,7 @@
         <v>97</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="10"/>
@@ -7811,7 +7814,7 @@
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="22" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D48" s="10"/>
       <c r="E48" s="11"/>
@@ -7835,7 +7838,7 @@
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="22" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D50" s="10"/>
       <c r="E50" s="11"/>
@@ -7858,10 +7861,10 @@
         <v>110</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="D52" s="10"/>
       <c r="E52" s="11"/>
@@ -7897,27 +7900,27 @@
   <sheetData>
     <row r="1" spans="2:6">
       <c r="B1" s="3" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
     </row>
     <row r="2" spans="2:6">
       <c r="B2" s="4" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="C2" s="4">
         <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="F2" s="4">
         <v>6</v>
@@ -7925,13 +7928,13 @@
     </row>
     <row r="3" spans="2:6">
       <c r="B3" s="4" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="C3" s="4">
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="F3" s="4">
         <v>13</v>
@@ -7939,13 +7942,13 @@
     </row>
     <row r="4" spans="2:6">
       <c r="B4" s="4" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C4" s="4">
         <v>12</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="F4" s="4">
         <v>4</v>
@@ -7953,13 +7956,13 @@
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="4" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C5" s="4">
         <v>2</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="F5" s="4">
         <v>6</v>
@@ -7967,13 +7970,13 @@
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="4" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C6" s="4">
         <v>2</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="F6" s="4">
         <v>4</v>
@@ -7981,13 +7984,13 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="4" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="C7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
@@ -7995,13 +7998,13 @@
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="4" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C8" s="4">
         <v>4</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="F8" s="4">
         <v>3</v>
@@ -8009,7 +8012,7 @@
     </row>
     <row r="9" spans="2:6">
       <c r="E9" s="4" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -8017,7 +8020,7 @@
     </row>
     <row r="10" spans="2:6">
       <c r="E10" s="4" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="F10" s="4">
         <v>5</v>
@@ -8025,7 +8028,7 @@
     </row>
     <row r="11" spans="2:6">
       <c r="E11" s="4" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -8033,7 +8036,7 @@
     </row>
     <row r="12" spans="2:6">
       <c r="E12" s="4" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="F12" s="4">
         <v>2</v>
@@ -8053,14 +8056,14 @@
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6.64545454545455" style="212" customWidth="1"/>
+    <col min="1" max="1" width="6.64545454545455" style="210" customWidth="1"/>
     <col min="2" max="2" width="32.6181818181818" style="66" customWidth="1"/>
     <col min="3" max="7" width="16.4909090909091" style="66" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="213"/>
+    <col min="8" max="16384" width="8.72727272727273" style="211"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="214"/>
+      <c r="A1" s="212"/>
       <c r="B1" s="70" t="s">
         <v>1</v>
       </c>
@@ -8080,8 +8083,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="211" customFormat="1" ht="39" spans="1:7">
-      <c r="A2" s="215" t="s">
+    <row r="2" s="209" customFormat="1" ht="39" spans="1:7">
+      <c r="A2" s="213" t="s">
         <v>167</v>
       </c>
       <c r="B2" s="78"/>
@@ -8094,7 +8097,7 @@
       <c r="G2" s="78"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="216" t="s">
+      <c r="A3" s="214" t="s">
         <v>169</v>
       </c>
       <c r="C3" s="66" t="s">
@@ -8102,7 +8105,7 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="216" t="s">
+      <c r="A4" s="214" t="s">
         <v>171</v>
       </c>
       <c r="B4" s="66" t="s">
@@ -8113,7 +8116,7 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="216" t="s">
+      <c r="A5" s="214" t="s">
         <v>174</v>
       </c>
       <c r="C5" s="66" t="s">
@@ -8124,7 +8127,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="216" t="s">
+      <c r="A6" s="214" t="s">
         <v>177</v>
       </c>
       <c r="B6" s="66" t="s">
@@ -8135,7 +8138,7 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="216" t="s">
+      <c r="A7" s="214" t="s">
         <v>180</v>
       </c>
       <c r="B7" s="66" t="s">
@@ -8143,115 +8146,115 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="216"/>
+      <c r="A8" s="214"/>
       <c r="D8" s="66" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="216"/>
+      <c r="A9" s="214"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="216"/>
+      <c r="A10" s="214"/>
       <c r="B10" s="66" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="216"/>
+      <c r="A11" s="214"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="216"/>
+      <c r="A12" s="214"/>
       <c r="B12" s="66" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="216"/>
+      <c r="A13" s="214"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="216"/>
+      <c r="A14" s="214"/>
       <c r="B14" s="66" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="216"/>
+      <c r="A15" s="214"/>
       <c r="B15" s="66" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="216"/>
+      <c r="A16" s="214"/>
       <c r="B16" s="66" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="216"/>
+      <c r="A17" s="214"/>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="216"/>
+      <c r="A18" s="214"/>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="216"/>
+      <c r="A19" s="214"/>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="216"/>
+      <c r="A20" s="214"/>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="216"/>
+      <c r="A21" s="214"/>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="216"/>
+      <c r="A22" s="214"/>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="216"/>
+      <c r="A23" s="214"/>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="216"/>
+      <c r="A24" s="214"/>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="216"/>
+      <c r="A25" s="214"/>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="216"/>
+      <c r="A26" s="214"/>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="216"/>
+      <c r="A27" s="214"/>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="216"/>
+      <c r="A28" s="214"/>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="216"/>
+      <c r="A29" s="214"/>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="216"/>
+      <c r="A30" s="214"/>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="216"/>
+      <c r="A31" s="214"/>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="216"/>
+      <c r="A32" s="214"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="216"/>
+      <c r="A33" s="214"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="216"/>
+      <c r="A34" s="214"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="216"/>
+      <c r="A35" s="214"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="216"/>
+      <c r="A36" s="214"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="216"/>
+      <c r="A37" s="214"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="216"/>
+      <c r="A38" s="214"/>
       <c r="B38" s="78"/>
       <c r="C38" s="78"/>
       <c r="D38" s="78"/>
@@ -8260,7 +8263,7 @@
       <c r="G38" s="78"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="216"/>
+      <c r="A39" s="214"/>
       <c r="B39" s="78"/>
       <c r="C39" s="78"/>
       <c r="D39" s="78"/>
@@ -8269,40 +8272,40 @@
       <c r="G39" s="78"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="216"/>
+      <c r="A40" s="214"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="216"/>
+      <c r="A41" s="214"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="216"/>
+      <c r="A42" s="214"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="216"/>
+      <c r="A43" s="214"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="216"/>
+      <c r="A44" s="214"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="216"/>
+      <c r="A45" s="214"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="216"/>
+      <c r="A46" s="214"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="216"/>
+      <c r="A47" s="214"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="216"/>
+      <c r="A48" s="214"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="216"/>
+      <c r="A49" s="214"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="216"/>
+      <c r="A50" s="214"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="216"/>
+      <c r="A51" s="214"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8315,7 +8318,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.8"/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="24" style="200" customWidth="1"/>
@@ -8457,8 +8460,12 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="206"/>
-      <c r="B14" s="202"/>
-      <c r="C14" s="202"/>
+      <c r="B14" s="202" t="s">
+        <v>218</v>
+      </c>
+      <c r="C14" s="202" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="206"/>
@@ -8477,32 +8484,32 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="202" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B18" s="202" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C18" s="202" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="202" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B19" s="202" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C19" s="202" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="202" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B20" s="202" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C20" s="208">
         <v>0.440972222222222</v>
@@ -8513,50 +8520,50 @@
         <v>61</v>
       </c>
       <c r="B21" s="202" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C21" s="202" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="204"/>
       <c r="B22" s="202" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C22" s="202" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="203" t="s">
+        <v>232</v>
+      </c>
+      <c r="B23" s="202" t="s">
         <v>230</v>
       </c>
-      <c r="B23" s="202" t="s">
-        <v>228</v>
-      </c>
       <c r="C23" s="202" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="204"/>
       <c r="B24" s="202" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C24" s="202" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="25" ht="28" spans="1:3">
       <c r="A25" s="205" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B25" s="202" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C25" s="202" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -8565,18 +8572,18 @@
         <v>216</v>
       </c>
       <c r="C26" s="202" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="203" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B27" s="202" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C27" s="202" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -8585,7 +8592,7 @@
         <v>211</v>
       </c>
       <c r="C28" s="202" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="29" ht="28" spans="1:3">
@@ -8596,36 +8603,36 @@
         <v>211</v>
       </c>
       <c r="C29" s="202" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="207"/>
       <c r="B30" s="200" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C30" s="200" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="31" ht="98" spans="1:3">
-      <c r="A31" s="209" t="s">
-        <v>245</v>
+      <c r="A31" s="205" t="s">
+        <v>247</v>
       </c>
       <c r="B31" s="200" t="s">
         <v>211</v>
       </c>
       <c r="C31" s="200" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="32" ht="84" spans="1:3">
-      <c r="A32" s="210"/>
+      <c r="A32" s="207"/>
       <c r="B32" s="200" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C32" s="200" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -8633,41 +8640,52 @@
         <v>36</v>
       </c>
       <c r="B33" s="200" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C33" s="200" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="34" ht="28" spans="1:3">
       <c r="A34" s="200" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B34" s="200" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C34" s="200" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="209" t="s">
-        <v>253</v>
+      <c r="A35" s="205" t="s">
+        <v>255</v>
       </c>
       <c r="B35" s="200" t="s">
         <v>216</v>
       </c>
       <c r="C35" s="200" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="210"/>
+      <c r="A36" s="207"/>
       <c r="B36" s="200" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C36" s="200" t="s">
-        <v>255</v>
+        <v>257</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="200" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" s="200" t="s">
+        <v>218</v>
+      </c>
+      <c r="C37" s="200" t="s">
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -8707,14 +8725,14 @@
   <sheetData>
     <row r="1" s="186" customFormat="1" ht="15" spans="1:7">
       <c r="A1" s="189" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B1" s="190"/>
       <c r="C1" s="190"/>
       <c r="D1" s="191"/>
       <c r="E1" s="192"/>
       <c r="F1" s="186" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" s="187" customFormat="1" spans="1:7">
@@ -8723,17 +8741,17 @@
       </c>
       <c r="B2" s="194"/>
       <c r="C2" s="187" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D2" s="187" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E2" s="141"/>
       <c r="F2" s="187" t="s">
         <v>189</v>
       </c>
       <c r="G2" s="187" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -8748,10 +8766,10 @@
       </c>
       <c r="D3" s="119"/>
       <c r="F3" s="119" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G3" s="119" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -8764,10 +8782,10 @@
       </c>
       <c r="D4" s="119"/>
       <c r="F4" s="119" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G4" s="119" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -8930,7 +8948,7 @@
   <sheetData>
     <row r="1" spans="1:39">
       <c r="A1" s="174" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B1" s="175">
         <v>45992</v>
@@ -8968,7 +8986,7 @@
       <c r="AE1" s="176"/>
       <c r="AF1" s="176"/>
       <c r="AG1" s="143" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AH1" s="146"/>
       <c r="AI1" s="146"/>
@@ -9073,25 +9091,25 @@
         <v>20</v>
       </c>
       <c r="AG2" s="178" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AH2" s="178" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="AI2" s="178" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="AJ2" s="178" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="AK2" s="179" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AL2" s="179" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AM2" s="179" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:39">
@@ -9305,7 +9323,7 @@
       </c>
       <c r="AL5" s="183">
         <f t="shared" si="2"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM5" s="183">
         <f t="shared" si="2"/>
@@ -9373,7 +9391,7 @@
       </c>
       <c r="AL6" s="183">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM6" s="183">
         <f t="shared" si="3"/>
@@ -9595,17 +9613,19 @@
       <c r="Z9" s="120"/>
       <c r="AA9" s="120"/>
       <c r="AB9" s="120"/>
-      <c r="AC9" s="120"/>
+      <c r="AC9" s="120">
+        <v>1</v>
+      </c>
       <c r="AD9" s="120"/>
       <c r="AE9" s="120"/>
       <c r="AF9" s="120"/>
       <c r="AG9" s="180">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH9" s="181" cm="1">
         <f t="array" ref="AH9">SUMPRODUCT(--(B9:AF9=INT(B9:AF9)),--(B9:AF9&gt;0))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI9" s="181" cm="1">
         <f t="array" ref="AI9">MAX(FREQUENCY(IF((B9:AF9=INT(B9:AF9))*(B9:AF9&gt;0),COLUMN(B9:AF9)),IF((B9:AF9&lt;&gt;INT(B9:AF9))+(B9:AF9&lt;=0),COLUMN(B9:AF9))))</f>
@@ -9613,15 +9633,15 @@
       </c>
       <c r="AJ9" s="182" cm="1">
         <f t="array" ref="AJ9">SUMPRODUCT(--(B9:AF9=INT(B9:AF9)),--(B9:AF9&gt;0))/30*100%</f>
-        <v>0.3</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="AK9" s="183">
         <f t="shared" ref="AK9:AM9" si="6">RANK(AG9,AG$3:AG$53,0)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL9" s="183">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM9" s="183">
         <f t="shared" si="6"/>
@@ -9829,7 +9849,7 @@
       </c>
       <c r="AL12" s="183">
         <f t="shared" si="9"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM12" s="183">
         <f t="shared" si="9"/>
@@ -9977,7 +9997,7 @@
       </c>
       <c r="AL14" s="183">
         <f t="shared" si="11"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM14" s="183">
         <f t="shared" si="11"/>
@@ -10053,7 +10073,7 @@
       </c>
       <c r="AK15" s="183">
         <f t="shared" ref="AK15:AM15" si="12">RANK(AG15,AG$3:AG$53,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL15" s="183">
         <f t="shared" si="12"/>
@@ -10125,7 +10145,7 @@
       </c>
       <c r="AL16" s="183">
         <f t="shared" si="13"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM16" s="183">
         <f t="shared" si="13"/>
@@ -10191,7 +10211,7 @@
       </c>
       <c r="AK17" s="183">
         <f t="shared" ref="AK17:AM17" si="14">RANK(AG17,AG$3:AG$53,0)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL17" s="183">
         <f t="shared" si="14"/>
@@ -10469,7 +10489,7 @@
       </c>
       <c r="AL21" s="183">
         <f t="shared" si="18"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM21" s="183">
         <f t="shared" si="18"/>
@@ -10551,7 +10571,7 @@
       </c>
       <c r="AL22" s="183">
         <f t="shared" si="19"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM22" s="183">
         <f t="shared" si="19"/>
@@ -11279,7 +11299,7 @@
       </c>
       <c r="AL32" s="183">
         <f t="shared" si="29"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM32" s="183">
         <f t="shared" si="29"/>
@@ -11345,7 +11365,7 @@
       </c>
       <c r="AK33" s="183">
         <f t="shared" ref="AK33:AM33" si="30">RANK(AG33,AG$3:AG$53,0)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL33" s="183">
         <f t="shared" si="30"/>
@@ -11619,7 +11639,7 @@
       </c>
       <c r="AL37" s="183">
         <f t="shared" si="35"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM37" s="183">
         <f t="shared" si="35"/>
@@ -11661,17 +11681,19 @@
       <c r="Z38" s="120"/>
       <c r="AA38" s="120"/>
       <c r="AB38" s="120"/>
-      <c r="AC38" s="120"/>
+      <c r="AC38" s="120">
+        <v>1</v>
+      </c>
       <c r="AD38" s="120"/>
       <c r="AE38" s="120"/>
       <c r="AF38" s="120"/>
       <c r="AG38" s="180">
         <f t="shared" si="33"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH38" s="181" cm="1">
         <f t="array" ref="AH38">SUMPRODUCT(--(B38:AF38=INT(B38:AF38)),--(B38:AF38&gt;0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI38" s="181" cm="1">
         <f t="array" ref="AI38">MAX(FREQUENCY(IF((B38:AF38=INT(B38:AF38))*(B38:AF38&gt;0),COLUMN(B38:AF38)),IF((B38:AF38&lt;&gt;INT(B38:AF38))+(B38:AF38&lt;=0),COLUMN(B38:AF38))))</f>
@@ -11679,15 +11701,15 @@
       </c>
       <c r="AJ38" s="182" cm="1">
         <f t="array" ref="AJ38">SUMPRODUCT(--(B38:AF38=INT(B38:AF38)),--(B38:AF38&gt;0))/30*100%</f>
-        <v>0.0666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="AK38" s="183">
         <f t="shared" ref="AK38:AM38" si="36">RANK(AG38,AG$3:AG$53,0)</f>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL38" s="183">
         <f t="shared" si="36"/>
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AM38" s="183">
         <f t="shared" si="36"/>
@@ -11929,7 +11951,7 @@
       </c>
       <c r="AL41" s="183">
         <f t="shared" si="39"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM41" s="183">
         <f t="shared" si="39"/>
@@ -12451,17 +12473,19 @@
       <c r="Z48" s="120"/>
       <c r="AA48" s="120"/>
       <c r="AB48" s="120"/>
-      <c r="AC48" s="120"/>
+      <c r="AC48" s="120">
+        <v>1</v>
+      </c>
       <c r="AD48" s="120"/>
       <c r="AE48" s="120"/>
       <c r="AF48" s="120"/>
       <c r="AG48" s="180">
         <f t="shared" si="33"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH48" s="181" cm="1">
         <f t="array" ref="AH48">SUMPRODUCT(--(B48:AF48=INT(B48:AF48)),--(B48:AF48&gt;0))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI48" s="181" cm="1">
         <f t="array" ref="AI48">MAX(FREQUENCY(IF((B48:AF48=INT(B48:AF48))*(B48:AF48&gt;0),COLUMN(B48:AF48)),IF((B48:AF48&lt;&gt;INT(B48:AF48))+(B48:AF48&lt;=0),COLUMN(B48:AF48))))</f>
@@ -12469,15 +12493,15 @@
       </c>
       <c r="AJ48" s="182" cm="1">
         <f t="array" ref="AJ48">SUMPRODUCT(--(B48:AF48=INT(B48:AF48)),--(B48:AF48&gt;0))/30*100%</f>
-        <v>0.2</v>
+        <v>0.233333333333333</v>
       </c>
       <c r="AK48" s="183">
         <f t="shared" ref="AK48:AM48" si="46">RANK(AG48,AG$3:AG$53,0)</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL48" s="183">
         <f t="shared" si="46"/>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AM48" s="183">
         <f t="shared" si="46"/>
@@ -12543,7 +12567,7 @@
       </c>
       <c r="AK49" s="183">
         <f t="shared" ref="AK49:AM49" si="47">RANK(AG49,AG$3:AG$53,0)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL49" s="183">
         <f t="shared" si="47"/>
@@ -12613,7 +12637,7 @@
       </c>
       <c r="AK50" s="183">
         <f t="shared" ref="AK50:AM50" si="48">RANK(AG50,AG$3:AG$53,0)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL50" s="183">
         <f t="shared" si="48"/>
@@ -13135,7 +13159,7 @@
   <pageSetup paperSize="9" scale="80" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A28:X33 Z28:AM33 A34:AM35 A36:X36 Z36:AM36 A37:AM37 A38:X38 Z38:AM38 A39:AM39 A42:X42 Z41:AM42 AC40:AM40 A43:AM43 A44:W44 Z44:AM44 A45:AM45 A46:X46 AA46 AC46:AM46 A47:AM47 A48:X49 Z48:AM49 A50:AM53 X41 A40:V41 A9:X10 Z9:AM10 AB11:AM11 A11:Z11 A12:X15 AB15:AM15 Z15 Z14:AM14 AB13:AM13 Z13 Z12:AM12 A16:AM16 A17:X18 Z17:AM18 A19:AM21 A22:X22 AA22:AM22 A23:AM23 A24:X25 Z24:AM25 A26:AM27 X8:AM8 A8:V8 A1:AM2 A3:X4 Z3:AM4 A5:AM7" formulaRange="1" unlockedFormula="1"/>
+    <ignoredError sqref="A28:X33 Z28:AM33 A34:AM35 A36:X36 Z36:AM36 A37:AM37 A38:X38 AD38:AM38 Z38:AB38 A39:AM39 A42:X42 Z41:AM42 AC40:AM40 A43:AM43 A44:W44 Z44:AM44 A45:AM45 A46:X46 AA46 AC46:AM46 A47:AM47 A48:X49 Z49:AM49 AD48:AM48 Z48:AB48 A50:AM53 X41 A40:V41 A9:X10 Z10:AM10 AD9:AM9 Z9:AB9 AB11:AM11 A11:Z11 A12:X15 AB15:AM15 Z15 Z14:AM14 AB13:AM13 Z13 Z12:AM12 A16:AM16 A17:X18 Z17:AM18 A19:AM21 A22:X22 AA22:AM22 A23:AM23 A24:X25 Z24:AM25 A26:AM27 X8:AM8 A8:V8 A1:AM2 A3:X4 Z3:AM4 A5:AM7" formulaRange="1" unlockedFormula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -13182,21 +13206,21 @@
     </row>
     <row r="2" ht="16.5" spans="1:10">
       <c r="A2" s="148" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B2" s="152" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C2" s="153" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D2" s="154"/>
       <c r="E2" s="152" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F2" s="152"/>
       <c r="G2" s="155" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="H2" s="147"/>
       <c r="I2" s="147"/>
@@ -13204,10 +13228,10 @@
     </row>
     <row r="3" ht="16.5" spans="1:10">
       <c r="A3" s="148" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B3" s="157" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C3" s="157"/>
       <c r="D3" s="157"/>
@@ -13220,10 +13244,10 @@
     </row>
     <row r="4" ht="16.5" spans="1:10">
       <c r="A4" s="148" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B4" s="158" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C4" s="158"/>
       <c r="D4" s="158"/>
@@ -13236,7 +13260,7 @@
     </row>
     <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="148" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B5" s="159">
         <v>1</v>
@@ -13256,7 +13280,7 @@
     </row>
     <row r="6" ht="16.5" spans="1:10">
       <c r="A6" s="148" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B6" s="161">
         <v>1</v>
@@ -13266,7 +13290,7 @@
       <c r="E6" s="161"/>
       <c r="F6" s="161"/>
       <c r="G6" s="162" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="H6" s="147"/>
       <c r="I6" s="147"/>
@@ -13274,10 +13298,10 @@
     </row>
     <row r="7" ht="16.5" spans="1:10">
       <c r="A7" s="148" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B7" s="163" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C7" s="163"/>
       <c r="D7" s="163"/>
@@ -13292,14 +13316,14 @@
     </row>
     <row r="8" ht="16.5" spans="1:10">
       <c r="A8" s="148" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B8" s="165">
         <v>1</v>
       </c>
       <c r="C8" s="165"/>
       <c r="D8" s="166" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E8" s="166"/>
       <c r="F8" s="166"/>
@@ -13310,10 +13334,10 @@
     </row>
     <row r="9" ht="16.5" spans="1:10">
       <c r="A9" s="148" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B9" s="152" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C9" s="152"/>
       <c r="D9" s="152"/>
@@ -13326,23 +13350,23 @@
     </row>
     <row r="10" ht="16.5" spans="1:10">
       <c r="A10" s="148" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B10" s="157">
         <v>1</v>
       </c>
       <c r="C10" s="157"/>
       <c r="D10" s="167" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E10" s="157">
         <v>1</v>
       </c>
       <c r="F10" s="167" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="G10" s="147" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="H10" s="147"/>
       <c r="I10" s="147"/>
@@ -13350,7 +13374,7 @@
     </row>
     <row r="11" ht="16.5" spans="1:10">
       <c r="A11" s="148" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B11" s="158">
         <v>1</v>
@@ -13366,7 +13390,7 @@
     </row>
     <row r="12" ht="16.5" spans="1:10">
       <c r="A12" s="148" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B12" s="159">
         <v>1</v>
@@ -13384,17 +13408,17 @@
     </row>
     <row r="13" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A13" s="148" t="s">
+        <v>298</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>295</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>292</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="168" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -13402,10 +13426,10 @@
     </row>
     <row r="14" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A14" s="148" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B14" s="170" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C14" s="170"/>
       <c r="D14" s="170"/>
@@ -13480,7 +13504,7 @@
   <sheetData>
     <row r="1" s="117" customFormat="1" spans="1:9">
       <c r="A1" s="121" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B1" s="122"/>
       <c r="C1" s="117" t="s">
@@ -13505,10 +13529,10 @@
     </row>
     <row r="2" s="118" customFormat="1" spans="1:9">
       <c r="A2" s="125" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B2" s="126" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C2" s="127" t="s">
         <v>7</v>
@@ -13520,7 +13544,7 @@
     <row r="3" s="118" customFormat="1" spans="1:9">
       <c r="A3" s="130"/>
       <c r="B3" s="126" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C3" s="127" t="s">
         <v>28</v>
@@ -13542,7 +13566,7 @@
     <row r="5" s="118" customFormat="1" spans="1:9">
       <c r="A5" s="130"/>
       <c r="B5" s="126" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C5" s="127" t="s">
         <v>31</v>
@@ -13554,7 +13578,7 @@
     <row r="6" s="118" customFormat="1" spans="1:9">
       <c r="A6" s="130"/>
       <c r="B6" s="126" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>19</v>
@@ -13582,7 +13606,7 @@
     <row r="8" s="118" customFormat="1" spans="1:9">
       <c r="A8" s="130"/>
       <c r="B8" s="126" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>14</v>
@@ -13596,7 +13620,7 @@
     <row r="9" s="118" customFormat="1" spans="1:9">
       <c r="A9" s="130"/>
       <c r="B9" s="126" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C9" s="127" t="s">
         <v>24</v>
@@ -13608,7 +13632,7 @@
     <row r="10" s="118" customFormat="1" spans="1:9">
       <c r="A10" s="130"/>
       <c r="B10" s="126" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C10" s="127" t="s">
         <v>34</v>
@@ -13620,7 +13644,7 @@
     <row r="11" s="118" customFormat="1" spans="1:9">
       <c r="A11" s="134"/>
       <c r="B11" s="126" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C11" s="127" t="s">
         <v>69</v>
@@ -13631,10 +13655,10 @@
     </row>
     <row r="12" s="119" customFormat="1" spans="1:9">
       <c r="A12" s="135" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B12" s="136" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C12" s="137" t="s">
         <v>88</v>
@@ -13658,10 +13682,10 @@
     <row r="14" s="119" customFormat="1" spans="1:9">
       <c r="A14" s="141"/>
       <c r="B14" s="136" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C14" s="137" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D14" s="142"/>
       <c r="E14" s="138"/>
@@ -13672,7 +13696,7 @@
     <row r="15" s="119" customFormat="1" spans="1:9">
       <c r="A15" s="141"/>
       <c r="B15" s="136" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C15" s="137" t="s">
         <v>10</v>
@@ -13694,7 +13718,7 @@
     <row r="17" s="119" customFormat="1" spans="1:7">
       <c r="A17" s="141"/>
       <c r="B17" s="136" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C17" s="137" t="s">
         <v>27</v>
@@ -13706,7 +13730,7 @@
     <row r="18" s="119" customFormat="1" spans="1:7">
       <c r="A18" s="141"/>
       <c r="B18" s="136" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C18" s="137" t="s">
         <v>42</v>
@@ -13718,7 +13742,7 @@
     <row r="19" s="119" customFormat="1" spans="1:7">
       <c r="A19" s="141"/>
       <c r="B19" s="136" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C19" s="137" t="s">
         <v>81</v>
@@ -13730,7 +13754,7 @@
     <row r="20" s="119" customFormat="1" spans="1:7">
       <c r="A20" s="141"/>
       <c r="B20" s="136" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C20" s="137" t="s">
         <v>84</v>
@@ -13742,7 +13766,7 @@
     <row r="21" s="119" customFormat="1" spans="1:7">
       <c r="A21" s="141"/>
       <c r="B21" s="136" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C21" s="143"/>
       <c r="D21" s="144"/>
@@ -13754,7 +13778,7 @@
     <row r="22" s="119" customFormat="1" spans="1:7">
       <c r="A22" s="145"/>
       <c r="B22" s="136" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C22" s="143"/>
       <c r="D22" s="146"/>
@@ -13816,7 +13840,7 @@
   <sheetData>
     <row r="1" s="91" customFormat="1" customHeight="1" spans="1:16">
       <c r="A1" s="94" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B1" s="95"/>
       <c r="C1" s="95"/>
@@ -13847,7 +13871,7 @@
     </row>
     <row r="3" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A3" s="100" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B3" s="101"/>
       <c r="C3" s="102"/>
@@ -14039,7 +14063,7 @@
     </row>
     <row r="11" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A11" s="100" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B11" s="101"/>
       <c r="C11" s="102"/>
@@ -14231,7 +14255,7 @@
     </row>
     <row r="19" s="93" customFormat="1" customHeight="1" spans="1:9">
       <c r="A19" s="100" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B19" s="101"/>
       <c r="C19" s="102"/>
@@ -14458,10 +14482,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="82" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B1" s="83" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C1" s="84" t="s">
         <v>190</v>
@@ -14472,208 +14496,208 @@
         <v>1</v>
       </c>
       <c r="B2" s="80" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C2" s="81" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="85"/>
       <c r="B3" s="80" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C3" s="81" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="85"/>
       <c r="B4" s="80" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C4" s="81" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="85"/>
       <c r="B5" s="80" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C5" s="81" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="85"/>
       <c r="B6" s="80" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C6" s="81" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="85"/>
       <c r="B7" s="80" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C7" s="81" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="85"/>
       <c r="B8" s="80" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C8" s="81" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="85"/>
       <c r="B9" s="80" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="85"/>
       <c r="B10" s="80" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C10" s="81" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="85"/>
       <c r="B11" s="80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C11" s="81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="85"/>
       <c r="B12" s="80" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C12" s="81" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="85"/>
       <c r="B13" s="80" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C13" s="81" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="85"/>
       <c r="B14" s="80" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="85"/>
       <c r="B15" s="80" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C15" s="81" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="85"/>
       <c r="B16" s="80" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C16" s="81" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="85"/>
       <c r="B17" s="80" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C17" s="81" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="85"/>
       <c r="B18" s="80" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C18" s="81" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="85"/>
       <c r="B19" s="80" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C19" s="81" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="85"/>
       <c r="B20" s="80" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C20" s="81" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="85"/>
       <c r="B21" s="80" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C21" s="81" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="85"/>
       <c r="B22" s="80" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C22" s="81" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="85"/>
       <c r="B23" s="80" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C23" s="81" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="85"/>
       <c r="B24" s="80" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C24" s="81" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -14681,118 +14705,118 @@
         <v>2</v>
       </c>
       <c r="B25" s="80" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C25" s="81" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="86"/>
       <c r="B26" s="80" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C26" s="81" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="86"/>
       <c r="B27" s="80" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C27" s="81" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="86"/>
       <c r="B28" s="80" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C28" s="81" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="86"/>
       <c r="B29" s="80" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C29" s="81" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="86"/>
       <c r="B30" s="80" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C30" s="81" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="86"/>
       <c r="B31" s="80" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C31" s="81" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="86"/>
       <c r="B32" s="80" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C32" s="81" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="86"/>
       <c r="B33" s="80" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C33" s="81" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="86"/>
       <c r="B34" s="80" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C34" s="81" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="86"/>
       <c r="B35" s="80" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C35" s="81" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="86"/>
       <c r="B36" s="80" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C36" s="81" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="87"/>
       <c r="B37" s="80" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C37" s="81" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -14800,138 +14824,138 @@
         <v>3</v>
       </c>
       <c r="B38" s="80" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C38" s="81" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="89"/>
       <c r="B39" s="80" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C39" s="81" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="89"/>
       <c r="B40" s="80" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C40" s="81" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="89"/>
       <c r="B41" s="80" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C41" s="81" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="89"/>
       <c r="B42" s="80" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C42" s="81" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="89"/>
       <c r="B43" s="80" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C43" s="81" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="89"/>
       <c r="B44" s="80" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C44" s="81" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="89"/>
       <c r="B45" s="80" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C45" s="81" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="89"/>
       <c r="B46" s="80" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C46" s="81" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="89"/>
       <c r="B47" s="80" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C47" s="81" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="89"/>
       <c r="B48" s="80" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C48" s="81" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="89"/>
       <c r="B49" s="80" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C49" s="81" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="90"/>
       <c r="B50" s="80" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C50" s="81" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:3">
       <c r="A51" s="79"/>
       <c r="B51" s="80" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C51" s="81"/>
     </row>
     <row r="52" customFormat="1" spans="1:3">
       <c r="A52" s="79"/>
       <c r="B52" s="80" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C52" s="81"/>
     </row>
     <row r="53" customFormat="1" spans="1:3">
       <c r="A53" s="79"/>
       <c r="B53" s="80" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C53" s="81"/>
     </row>

--- a/c/9班资料.xlsx
+++ b/c/9班资料.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="615">
   <si>
     <t>姓名</t>
   </si>
@@ -424,7 +424,7 @@
     <t>语3</t>
   </si>
   <si>
-    <t>微信窗口藏下面、C读“系”、我的天哪、周末作业（周记、好段、读书笔记）、以行践言、崇拜、父亲、问得好、不说了、给你们3秒钟</t>
+    <t>微信窗口藏下面、我的天哪、周末作业（周记、好段、读书笔记）、以行践言、崇拜、父亲、问得好、不说了、给你们3秒钟、太过分了</t>
   </si>
   <si>
     <t>数1</t>
@@ -763,6 +763,12 @@
     <t>语：我觉得他写的这些朋友圈都挺好的。</t>
   </si>
   <si>
+    <t>八上1.16</t>
+  </si>
+  <si>
+    <t>（数学）“180-α=β，这不一眼出答案吗？”</t>
+  </si>
+  <si>
     <t>孔祥懿睡觉</t>
   </si>
   <si>
@@ -823,6 +829,9 @@
     <t>（以小见大）林奕扬、崔宇臣升旗站位错——前几天也错——站最前面——谈话</t>
   </si>
   <si>
+    <t>政治课前：“必艳来了！”生：奔回座位，瞬间安静</t>
+  </si>
+  <si>
     <t>跑操喊口号</t>
   </si>
   <si>
@@ -905,6 +914,12 @@
   </si>
   <si>
     <t>下午第一节数学</t>
+  </si>
+  <si>
+    <t>2026.1.16</t>
+  </si>
+  <si>
+    <t>上午第一节数学</t>
   </si>
   <si>
     <t>座号</t>
@@ -3171,9 +3186,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
+      <sz val="11"/>
+      <name val="黑体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3183,9 +3199,8 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="黑体"/>
+      <name val="华文仿宋"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <strike/>
@@ -3194,8 +3209,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="华文仿宋"/>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -3962,7 +3977,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="222">
+  <cellXfs count="223">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4596,6 +4611,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4971,29 +4989,29 @@
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="7.59090909090909" style="71" customWidth="1"/>
-    <col min="2" max="7" width="25.8727272727273" style="216" customWidth="1"/>
+    <col min="2" max="7" width="25.8727272727273" style="217" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="215" customFormat="1" spans="1:7">
+    <row r="1" s="216" customFormat="1" spans="1:7">
       <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="217" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="217" t="s">
+      <c r="B1" s="218" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="218" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="217" t="s">
+      <c r="D1" s="218" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="217" t="s">
+      <c r="E1" s="218" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="217" t="s">
+      <c r="F1" s="218" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="217" t="s">
+      <c r="G1" s="218" t="s">
         <v>6</v>
       </c>
     </row>
@@ -5001,10 +5019,10 @@
       <c r="A2" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="216" t="s">
+      <c r="B2" s="217" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="216" t="s">
+      <c r="C2" s="217" t="s">
         <v>9</v>
       </c>
     </row>
@@ -5012,10 +5030,10 @@
       <c r="A3" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="216" t="s">
+      <c r="C3" s="217" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="216" t="s">
+      <c r="D3" s="217" t="s">
         <v>12</v>
       </c>
     </row>
@@ -5028,10 +5046,10 @@
       <c r="A5" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="216" t="s">
+      <c r="C5" s="217" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="216" t="s">
+      <c r="D5" s="217" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5039,7 +5057,7 @@
       <c r="A6" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="216" t="s">
+      <c r="C6" s="217" t="s">
         <v>18</v>
       </c>
     </row>
@@ -5047,13 +5065,13 @@
       <c r="A7" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="216" t="s">
+      <c r="B7" s="217" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="216" t="s">
+      <c r="C7" s="217" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="216" t="s">
+      <c r="D7" s="217" t="s">
         <v>22</v>
       </c>
     </row>
@@ -5071,7 +5089,7 @@
       <c r="A10" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="216" t="s">
+      <c r="B10" s="217" t="s">
         <v>26</v>
       </c>
     </row>
@@ -5089,7 +5107,7 @@
       <c r="A13" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="216" t="s">
+      <c r="D13" s="217" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5097,7 +5115,7 @@
       <c r="A14" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="216" t="s">
+      <c r="B14" s="217" t="s">
         <v>32</v>
       </c>
     </row>
@@ -5110,7 +5128,7 @@
       <c r="A16" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="216" t="s">
+      <c r="C16" s="217" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5118,7 +5136,7 @@
       <c r="A17" s="72" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="216" t="s">
+      <c r="C17" s="217" t="s">
         <v>37</v>
       </c>
     </row>
@@ -5126,7 +5144,7 @@
       <c r="A18" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="216" t="s">
+      <c r="D18" s="217" t="s">
         <v>39</v>
       </c>
     </row>
@@ -5134,7 +5152,7 @@
       <c r="A19" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="216" t="s">
+      <c r="D19" s="217" t="s">
         <v>41</v>
       </c>
     </row>
@@ -5142,10 +5160,10 @@
       <c r="A20" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="216" t="s">
+      <c r="B20" s="217" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="216" t="s">
+      <c r="C20" s="217" t="s">
         <v>44</v>
       </c>
     </row>
@@ -5153,13 +5171,13 @@
       <c r="A21" s="72" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="216" t="s">
+      <c r="B21" s="217" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="216" t="s">
+      <c r="C21" s="217" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="216" t="s">
+      <c r="D21" s="217" t="s">
         <v>48</v>
       </c>
     </row>
@@ -5172,7 +5190,7 @@
       <c r="A23" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="216" t="s">
+      <c r="B23" s="217" t="s">
         <v>51</v>
       </c>
     </row>
@@ -5180,13 +5198,13 @@
       <c r="A24" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="216" t="s">
+      <c r="B24" s="217" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="216" t="s">
+      <c r="C24" s="217" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="216" t="s">
+      <c r="D24" s="217" t="s">
         <v>55</v>
       </c>
     </row>
@@ -5204,10 +5222,10 @@
       <c r="A27" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="B27" s="216" t="s">
+      <c r="B27" s="217" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="216" t="s">
+      <c r="C27" s="217" t="s">
         <v>60</v>
       </c>
     </row>
@@ -5215,13 +5233,13 @@
       <c r="A28" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="B28" s="216" t="s">
+      <c r="B28" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="216" t="s">
+      <c r="C28" s="217" t="s">
         <v>63</v>
       </c>
-      <c r="D28" s="216" t="s">
+      <c r="D28" s="217" t="s">
         <v>64</v>
       </c>
     </row>
@@ -5234,10 +5252,10 @@
       <c r="A30" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="B30" s="216" t="s">
+      <c r="B30" s="217" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="216" t="s">
+      <c r="C30" s="217" t="s">
         <v>68</v>
       </c>
     </row>
@@ -5270,7 +5288,7 @@
       <c r="A36" s="72" t="s">
         <v>74</v>
       </c>
-      <c r="B36" s="216" t="s">
+      <c r="B36" s="217" t="s">
         <v>75</v>
       </c>
     </row>
@@ -5278,10 +5296,10 @@
       <c r="A37" s="72" t="s">
         <v>76</v>
       </c>
-      <c r="C37" s="216" t="s">
+      <c r="C37" s="217" t="s">
         <v>77</v>
       </c>
-      <c r="D37" s="216" t="s">
+      <c r="D37" s="217" t="s">
         <v>78</v>
       </c>
     </row>
@@ -5289,23 +5307,23 @@
       <c r="A38" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="B38" s="216" t="s">
+      <c r="B38" s="217" t="s">
         <v>80</v>
       </c>
-      <c r="C38" s="218"/>
-      <c r="D38" s="218"/>
-      <c r="E38" s="218"/>
-      <c r="F38" s="218"/>
-      <c r="G38" s="218"/>
+      <c r="C38" s="219"/>
+      <c r="D38" s="219"/>
+      <c r="E38" s="219"/>
+      <c r="F38" s="219"/>
+      <c r="G38" s="219"/>
     </row>
     <row r="39" ht="26" spans="1:8">
       <c r="A39" s="72" t="s">
         <v>81</v>
       </c>
-      <c r="C39" s="216" t="s">
+      <c r="C39" s="217" t="s">
         <v>82</v>
       </c>
-      <c r="D39" s="216" t="s">
+      <c r="D39" s="217" t="s">
         <v>83</v>
       </c>
     </row>
@@ -5313,13 +5331,13 @@
       <c r="A40" s="72" t="s">
         <v>84</v>
       </c>
-      <c r="B40" s="216" t="s">
+      <c r="B40" s="217" t="s">
         <v>85</v>
       </c>
-      <c r="C40" s="216" t="s">
+      <c r="C40" s="217" t="s">
         <v>86</v>
       </c>
-      <c r="D40" s="216" t="s">
+      <c r="D40" s="217" t="s">
         <v>87</v>
       </c>
     </row>
@@ -5327,13 +5345,13 @@
       <c r="A41" s="72" t="s">
         <v>88</v>
       </c>
-      <c r="C41" s="216" t="s">
+      <c r="C41" s="217" t="s">
         <v>89</v>
       </c>
-      <c r="D41" s="216" t="s">
+      <c r="D41" s="217" t="s">
         <v>90</v>
       </c>
-      <c r="H41" s="219" t="s">
+      <c r="H41" s="220" t="s">
         <v>91</v>
       </c>
     </row>
@@ -5346,7 +5364,7 @@
       <c r="A43" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="B43" s="216" t="s">
+      <c r="B43" s="217" t="s">
         <v>94</v>
       </c>
     </row>
@@ -5354,7 +5372,7 @@
       <c r="A44" s="72" t="s">
         <v>95</v>
       </c>
-      <c r="B44" s="216" t="s">
+      <c r="B44" s="217" t="s">
         <v>96</v>
       </c>
     </row>
@@ -5362,10 +5380,10 @@
       <c r="A45" s="72" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="216" t="s">
+      <c r="C45" s="217" t="s">
         <v>98</v>
       </c>
-      <c r="D45" s="216" t="s">
+      <c r="D45" s="217" t="s">
         <v>99</v>
       </c>
     </row>
@@ -5378,7 +5396,7 @@
       <c r="A47" s="72" t="s">
         <v>101</v>
       </c>
-      <c r="D47" s="216" t="s">
+      <c r="D47" s="217" t="s">
         <v>102</v>
       </c>
     </row>
@@ -5386,10 +5404,10 @@
       <c r="A48" s="72" t="s">
         <v>103</v>
       </c>
-      <c r="C48" s="216" t="s">
+      <c r="C48" s="217" t="s">
         <v>104</v>
       </c>
-      <c r="D48" s="216" t="s">
+      <c r="D48" s="217" t="s">
         <v>105</v>
       </c>
     </row>
@@ -5402,7 +5420,7 @@
       <c r="A50" s="72" t="s">
         <v>107</v>
       </c>
-      <c r="C50" s="216" t="s">
+      <c r="C50" s="217" t="s">
         <v>108</v>
       </c>
     </row>
@@ -5415,10 +5433,10 @@
       <c r="A52" s="72" t="s">
         <v>110</v>
       </c>
-      <c r="B52" s="216" t="s">
+      <c r="B52" s="217" t="s">
         <v>111</v>
       </c>
-      <c r="C52" s="216" t="s">
+      <c r="C52" s="217" t="s">
         <v>112</v>
       </c>
     </row>
@@ -5426,36 +5444,36 @@
       <c r="A53" s="71" t="s">
         <v>113</v>
       </c>
-      <c r="B53" s="216" t="s">
+      <c r="B53" s="217" t="s">
         <v>114</v>
       </c>
-      <c r="D53" s="218"/>
-      <c r="E53" s="218"/>
-      <c r="F53" s="218"/>
-      <c r="G53" s="218"/>
+      <c r="D53" s="219"/>
+      <c r="E53" s="219"/>
+      <c r="F53" s="219"/>
+      <c r="G53" s="219"/>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="71" t="s">
         <v>115</v>
       </c>
-      <c r="B54" s="216" t="s">
+      <c r="B54" s="217" t="s">
         <v>116</v>
       </c>
-      <c r="C54" s="216" t="s">
+      <c r="C54" s="217" t="s">
         <v>117</v>
       </c>
-      <c r="D54" s="218"/>
-      <c r="E54" s="218"/>
-      <c r="F54" s="218"/>
-      <c r="G54" s="218"/>
+      <c r="D54" s="219"/>
+      <c r="E54" s="219"/>
+      <c r="F54" s="219"/>
+      <c r="G54" s="219"/>
     </row>
     <row r="55" ht="65" spans="1:7">
       <c r="A55" s="71" t="s">
         <v>118</v>
       </c>
-      <c r="B55" s="218"/>
-      <c r="C55" s="218"/>
-      <c r="D55" s="216" t="s">
+      <c r="B55" s="219"/>
+      <c r="C55" s="219"/>
+      <c r="D55" s="217" t="s">
         <v>119</v>
       </c>
     </row>
@@ -5467,7 +5485,7 @@
         <v>121</v>
       </c>
       <c r="C56" s="78"/>
-      <c r="D56" s="216" t="s">
+      <c r="D56" s="217" t="s">
         <v>122</v>
       </c>
     </row>
@@ -5481,7 +5499,7 @@
       <c r="C57" s="78" t="s">
         <v>125</v>
       </c>
-      <c r="D57" s="216" t="s">
+      <c r="D57" s="217" t="s">
         <v>126</v>
       </c>
     </row>
@@ -5489,37 +5507,37 @@
       <c r="A58" s="71" t="s">
         <v>127</v>
       </c>
-      <c r="B58" s="216" t="s">
+      <c r="B58" s="217" t="s">
         <v>128</v>
       </c>
-      <c r="C58" s="218"/>
-      <c r="D58" s="218"/>
-      <c r="E58" s="218"/>
-      <c r="F58" s="218"/>
-      <c r="G58" s="218"/>
+      <c r="C58" s="219"/>
+      <c r="D58" s="219"/>
+      <c r="E58" s="219"/>
+      <c r="F58" s="219"/>
+      <c r="G58" s="219"/>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="B59" s="218"/>
-      <c r="C59" s="216" t="s">
+      <c r="B59" s="219"/>
+      <c r="C59" s="217" t="s">
         <v>130</v>
       </c>
-      <c r="D59" s="218"/>
-      <c r="E59" s="218"/>
-      <c r="F59" s="218"/>
-      <c r="G59" s="218"/>
+      <c r="D59" s="219"/>
+      <c r="E59" s="219"/>
+      <c r="F59" s="219"/>
+      <c r="G59" s="219"/>
     </row>
     <row r="60" ht="52" spans="1:7">
       <c r="A60" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="B60" s="218" t="s">
+      <c r="B60" s="219" t="s">
         <v>132</v>
       </c>
-      <c r="C60" s="218"/>
-      <c r="D60" s="216" t="s">
+      <c r="C60" s="219"/>
+      <c r="D60" s="217" t="s">
         <v>133</v>
       </c>
     </row>
@@ -5531,18 +5549,18 @@
         <v>135</v>
       </c>
       <c r="C61" s="78"/>
-      <c r="D61" s="218"/>
-      <c r="E61" s="218"/>
-      <c r="F61" s="218"/>
-      <c r="G61" s="218"/>
+      <c r="D61" s="219"/>
+      <c r="E61" s="219"/>
+      <c r="F61" s="219"/>
+      <c r="G61" s="219"/>
     </row>
     <row r="62" ht="39" spans="1:7">
       <c r="A62" s="71" t="s">
         <v>136</v>
       </c>
-      <c r="B62" s="218"/>
-      <c r="C62" s="218"/>
-      <c r="D62" s="216" t="s">
+      <c r="B62" s="219"/>
+      <c r="C62" s="219"/>
+      <c r="D62" s="217" t="s">
         <v>137</v>
       </c>
     </row>
@@ -5556,18 +5574,18 @@
       <c r="C63" s="78" t="s">
         <v>140</v>
       </c>
-      <c r="D63" s="218"/>
-      <c r="E63" s="218"/>
-      <c r="F63" s="218"/>
-      <c r="G63" s="218"/>
+      <c r="D63" s="219"/>
+      <c r="E63" s="219"/>
+      <c r="F63" s="219"/>
+      <c r="G63" s="219"/>
     </row>
     <row r="64" ht="26" spans="1:7">
       <c r="A64" s="71" t="s">
         <v>141</v>
       </c>
-      <c r="B64" s="218"/>
-      <c r="C64" s="218"/>
-      <c r="D64" s="216" t="s">
+      <c r="B64" s="219"/>
+      <c r="C64" s="219"/>
+      <c r="D64" s="217" t="s">
         <v>142</v>
       </c>
     </row>
@@ -5575,42 +5593,42 @@
       <c r="A65" s="71" t="s">
         <v>143</v>
       </c>
-      <c r="B65" s="220" t="s">
+      <c r="B65" s="221" t="s">
         <v>144</v>
       </c>
-      <c r="C65" s="218"/>
-      <c r="D65" s="218"/>
-      <c r="E65" s="218"/>
-      <c r="F65" s="218"/>
-      <c r="G65" s="218"/>
+      <c r="C65" s="219"/>
+      <c r="D65" s="219"/>
+      <c r="E65" s="219"/>
+      <c r="F65" s="219"/>
+      <c r="G65" s="219"/>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="71" t="s">
         <v>145</v>
       </c>
-      <c r="B66" s="218"/>
-      <c r="C66" s="216" t="s">
+      <c r="B66" s="219"/>
+      <c r="C66" s="217" t="s">
         <v>146</v>
       </c>
-      <c r="D66" s="218"/>
-      <c r="E66" s="218"/>
-      <c r="F66" s="218"/>
-      <c r="G66" s="218"/>
+      <c r="D66" s="219"/>
+      <c r="E66" s="219"/>
+      <c r="F66" s="219"/>
+      <c r="G66" s="219"/>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="71" t="s">
         <v>147</v>
       </c>
-      <c r="B67" s="218"/>
-      <c r="C67" s="218"/>
+      <c r="B67" s="219"/>
+      <c r="C67" s="219"/>
     </row>
     <row r="68" ht="65" spans="1:7">
       <c r="A68" s="71" t="s">
         <v>148</v>
       </c>
-      <c r="B68" s="218"/>
-      <c r="C68" s="218"/>
-      <c r="D68" s="216" t="s">
+      <c r="B68" s="219"/>
+      <c r="C68" s="219"/>
+      <c r="D68" s="217" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5631,45 +5649,45 @@
         <v>153</v>
       </c>
       <c r="C70" s="78"/>
-      <c r="D70" s="218"/>
-      <c r="E70" s="218"/>
-      <c r="F70" s="218"/>
-      <c r="G70" s="218"/>
+      <c r="D70" s="219"/>
+      <c r="E70" s="219"/>
+      <c r="F70" s="219"/>
+      <c r="G70" s="219"/>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="71" t="s">
         <v>154</v>
       </c>
-      <c r="B71" s="218"/>
-      <c r="C71" s="218"/>
+      <c r="B71" s="219"/>
+      <c r="C71" s="219"/>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="B72" s="216" t="s">
+      <c r="B72" s="217" t="s">
         <v>156</v>
       </c>
-      <c r="C72" s="216" t="s">
+      <c r="C72" s="217" t="s">
         <v>157</v>
       </c>
-      <c r="D72" s="218"/>
-      <c r="E72" s="218"/>
-      <c r="F72" s="218"/>
-      <c r="G72" s="218"/>
+      <c r="D72" s="219"/>
+      <c r="E72" s="219"/>
+      <c r="F72" s="219"/>
+      <c r="G72" s="219"/>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="71" t="s">
         <v>158</v>
       </c>
-      <c r="B73" s="218"/>
-      <c r="C73" s="216" t="s">
+      <c r="B73" s="219"/>
+      <c r="C73" s="217" t="s">
         <v>159</v>
       </c>
-      <c r="D73" s="218"/>
-      <c r="E73" s="218"/>
-      <c r="F73" s="218"/>
-      <c r="G73" s="218"/>
+      <c r="D73" s="219"/>
+      <c r="E73" s="219"/>
+      <c r="F73" s="219"/>
+      <c r="G73" s="219"/>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="71" t="s">
@@ -5680,18 +5698,18 @@
       <c r="A75" s="71" t="s">
         <v>161</v>
       </c>
-      <c r="D75" s="218"/>
-      <c r="E75" s="218"/>
-      <c r="F75" s="218"/>
-      <c r="G75" s="218"/>
+      <c r="D75" s="219"/>
+      <c r="E75" s="219"/>
+      <c r="F75" s="219"/>
+      <c r="G75" s="219"/>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="71" t="s">
         <v>162</v>
       </c>
-      <c r="B76" s="218"/>
-      <c r="C76" s="218"/>
-      <c r="D76" s="216" t="s">
+      <c r="B76" s="219"/>
+      <c r="C76" s="219"/>
+      <c r="D76" s="217" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5703,10 +5721,10 @@
       <c r="C77" s="78"/>
     </row>
     <row r="78" ht="26" spans="1:7">
-      <c r="A78" s="221" t="s">
+      <c r="A78" s="222" t="s">
         <v>165</v>
       </c>
-      <c r="B78" s="216" t="s">
+      <c r="B78" s="217" t="s">
         <v>166</v>
       </c>
     </row>
@@ -5760,16 +5778,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="67" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B1" s="68" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="69" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="D1" s="70" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5783,7 +5801,7 @@
         <v>20111216</v>
       </c>
       <c r="D2" s="66" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -5797,7 +5815,7 @@
         <v>20111227</v>
       </c>
       <c r="D3" s="66" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -5811,7 +5829,7 @@
         <v>20120518</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:4">
@@ -5839,7 +5857,7 @@
         <v>20120504</v>
       </c>
       <c r="D6" s="66" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -5853,7 +5871,7 @@
         <v>20120809</v>
       </c>
       <c r="D7" s="66" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -5867,7 +5885,7 @@
         <v>20120227</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -5881,7 +5899,7 @@
         <v>20120127</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -5895,7 +5913,7 @@
         <v>20111202</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:4">
@@ -5921,7 +5939,7 @@
         <v>20111024</v>
       </c>
       <c r="D12" s="66" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -5935,7 +5953,7 @@
         <v>20110908</v>
       </c>
       <c r="D13" s="66" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -5949,7 +5967,7 @@
         <v>20120228</v>
       </c>
       <c r="D14" s="66" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:4">
@@ -5975,7 +5993,7 @@
         <v>20111201</v>
       </c>
       <c r="D16" s="66" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -5989,7 +6007,7 @@
         <v>20120722</v>
       </c>
       <c r="D17" s="66" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:4">
@@ -6027,7 +6045,7 @@
         <v>20120530</v>
       </c>
       <c r="D20" s="66" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -6041,7 +6059,7 @@
         <v>20120827</v>
       </c>
       <c r="D21" s="66" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:4">
@@ -6067,7 +6085,7 @@
         <v>20120518</v>
       </c>
       <c r="D23" s="66" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -6081,7 +6099,7 @@
         <v>20120413</v>
       </c>
       <c r="D24" s="66" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -6095,7 +6113,7 @@
         <v>20120629</v>
       </c>
       <c r="D25" s="66" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -6109,7 +6127,7 @@
         <v>20111105</v>
       </c>
       <c r="D26" s="66" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -6123,7 +6141,7 @@
         <v>20120112</v>
       </c>
       <c r="D27" s="66" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -6137,7 +6155,7 @@
         <v>20111119</v>
       </c>
       <c r="D28" s="66" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:4">
@@ -6163,7 +6181,7 @@
         <v>20120331</v>
       </c>
       <c r="D30" s="66" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -6177,7 +6195,7 @@
         <v>20111109</v>
       </c>
       <c r="D31" s="66" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -6191,7 +6209,7 @@
         <v>20120824</v>
       </c>
       <c r="D32" s="66" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:5">
@@ -6217,7 +6235,7 @@
         <v>20120624</v>
       </c>
       <c r="D34" s="66" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:5">
@@ -6243,7 +6261,7 @@
         <v>20120603</v>
       </c>
       <c r="D36" s="66" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -6257,7 +6275,7 @@
         <v>20120326</v>
       </c>
       <c r="D37" s="66" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -6271,10 +6289,10 @@
         <v>20111106</v>
       </c>
       <c r="D38" s="77" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="E38" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -6288,7 +6306,7 @@
         <v>20120811</v>
       </c>
       <c r="D39" s="78" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -6302,7 +6320,7 @@
         <v>20111217</v>
       </c>
       <c r="D40" s="78" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -6316,10 +6334,10 @@
         <v>20111013</v>
       </c>
       <c r="D41" s="66" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="E41" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:5">
@@ -6345,7 +6363,7 @@
         <v>20120207</v>
       </c>
       <c r="D43" s="66" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:5">
@@ -6371,7 +6389,7 @@
         <v>20110929</v>
       </c>
       <c r="D45" s="66" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:5">
@@ -6397,10 +6415,10 @@
         <v>20120108</v>
       </c>
       <c r="D47" s="66" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="E47" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -6414,7 +6432,7 @@
         <v>20120311</v>
       </c>
       <c r="D48" s="66" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:4">
@@ -6440,7 +6458,7 @@
         <v>20120723</v>
       </c>
       <c r="D50" s="66" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:4">
@@ -6466,7 +6484,7 @@
         <v>20111220</v>
       </c>
       <c r="D52" s="66" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -6499,34 +6517,34 @@
   <sheetData>
     <row r="1" s="27" customFormat="1" spans="1:5">
       <c r="A1" s="34" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="D1" s="37"/>
       <c r="E1" s="38" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="2" s="28" customFormat="1" ht="409" customHeight="1" spans="1:5">
       <c r="A2" s="39" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="3" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6534,10 +6552,10 @@
       <c r="B3" s="43"/>
       <c r="C3" s="44"/>
       <c r="D3" s="32" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="4" s="28" customFormat="1" spans="1:5">
@@ -6545,10 +6563,10 @@
       <c r="B4" s="43"/>
       <c r="C4" s="44"/>
       <c r="D4" s="32" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="5" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6556,10 +6574,10 @@
       <c r="B5" s="43"/>
       <c r="C5" s="44"/>
       <c r="D5" s="32" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="6" s="28" customFormat="1" ht="238" spans="1:5">
@@ -6567,23 +6585,23 @@
       <c r="B6" s="43"/>
       <c r="C6" s="44"/>
       <c r="D6" s="32" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="7" s="28" customFormat="1" ht="238" spans="1:5">
       <c r="A7" s="42"/>
       <c r="B7" s="43"/>
       <c r="C7" s="41" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="8" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6591,10 +6609,10 @@
       <c r="B8" s="43"/>
       <c r="C8" s="44"/>
       <c r="D8" s="32" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9" s="28" customFormat="1" ht="84" spans="1:5">
@@ -6602,10 +6620,10 @@
       <c r="B9" s="43"/>
       <c r="C9" s="44"/>
       <c r="D9" s="32" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="10" s="28" customFormat="1" ht="28" spans="1:5">
@@ -6613,10 +6631,10 @@
       <c r="B10" s="43"/>
       <c r="C10" s="44"/>
       <c r="D10" s="32" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="11" s="28" customFormat="1" spans="1:5">
@@ -6624,10 +6642,10 @@
       <c r="B11" s="43"/>
       <c r="C11" s="45"/>
       <c r="D11" s="32" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="12" s="28" customFormat="1" ht="154" spans="1:5">
@@ -6635,50 +6653,50 @@
       <c r="B12" s="43"/>
       <c r="C12" s="31"/>
       <c r="D12" s="32" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="13" s="28" customFormat="1" ht="56" spans="1:5">
       <c r="A13" s="42"/>
       <c r="B13" s="43"/>
       <c r="C13" s="46" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="33" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="14" s="28" customFormat="1" ht="84" spans="1:5">
       <c r="A14" s="42"/>
       <c r="B14" s="43"/>
       <c r="C14" s="46" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="33" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="15" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A15" s="42"/>
       <c r="B15" s="43"/>
       <c r="C15" s="46" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="D15" s="37"/>
       <c r="E15" s="33" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="16" s="28" customFormat="1" spans="1:5">
       <c r="A16" s="42"/>
       <c r="B16" s="43"/>
       <c r="C16" s="46" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="D16" s="37"/>
       <c r="E16" s="33"/>
@@ -6687,24 +6705,24 @@
       <c r="A17" s="42"/>
       <c r="B17" s="43"/>
       <c r="C17" s="46" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="33" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="18" s="28" customFormat="1" spans="1:5">
       <c r="A18" s="42"/>
       <c r="B18" s="43"/>
       <c r="C18" s="41" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="19" s="28" customFormat="1" spans="1:5">
@@ -6712,17 +6730,17 @@
       <c r="B19" s="43"/>
       <c r="C19" s="45"/>
       <c r="D19" s="32" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="20" s="28" customFormat="1" spans="1:5">
       <c r="A20" s="42"/>
       <c r="B20" s="43"/>
       <c r="C20" s="46" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="D20" s="37"/>
       <c r="E20" s="33"/>
@@ -6731,61 +6749,61 @@
       <c r="A21" s="42"/>
       <c r="B21" s="43"/>
       <c r="C21" s="46" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="D21" s="37"/>
       <c r="E21" s="33" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="22" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A22" s="42"/>
       <c r="B22" s="43"/>
       <c r="C22" s="46" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="D22" s="47"/>
       <c r="E22" s="33" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="23" s="28" customFormat="1" spans="1:5">
       <c r="A23" s="42"/>
       <c r="B23" s="43"/>
       <c r="C23" s="31" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D23" s="31"/>
       <c r="E23" s="33" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="24" s="28" customFormat="1" spans="1:5">
       <c r="A24" s="42"/>
       <c r="B24" s="43"/>
       <c r="C24" s="31" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="D24" s="31"/>
       <c r="E24" s="33" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="25" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A25" s="39" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="26" s="28" customFormat="1" spans="1:5">
@@ -6793,10 +6811,10 @@
       <c r="B26" s="43"/>
       <c r="C26" s="44"/>
       <c r="D26" s="32" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="27" s="28" customFormat="1" ht="28" spans="1:5">
@@ -6804,10 +6822,10 @@
       <c r="B27" s="43"/>
       <c r="C27" s="44"/>
       <c r="D27" s="32" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
     </row>
     <row r="28" s="28" customFormat="1" ht="42" spans="1:5">
@@ -6815,27 +6833,27 @@
       <c r="B28" s="43"/>
       <c r="C28" s="44"/>
       <c r="D28" s="32" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
     </row>
     <row r="29" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A29" s="39" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
     </row>
     <row r="30" s="28" customFormat="1" ht="70" spans="1:5">
@@ -6843,10 +6861,10 @@
       <c r="B30" s="43"/>
       <c r="C30" s="44"/>
       <c r="D30" s="32" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
     </row>
     <row r="31" s="28" customFormat="1" spans="1:5">
@@ -6854,10 +6872,10 @@
       <c r="B31" s="43"/>
       <c r="C31" s="44"/>
       <c r="D31" s="32" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
     </row>
     <row r="32" s="28" customFormat="1" ht="28" spans="1:5">
@@ -6865,53 +6883,53 @@
       <c r="B32" s="43"/>
       <c r="C32" s="45"/>
       <c r="D32" s="32" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
     </row>
     <row r="33" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A33" s="42"/>
       <c r="B33" s="49"/>
       <c r="C33" s="46" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="D33" s="47"/>
       <c r="E33" s="33" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
     </row>
     <row r="34" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A34" s="42"/>
       <c r="B34" s="50" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="D34" s="51"/>
       <c r="E34" s="52" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
     </row>
     <row r="35" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A35" s="53"/>
       <c r="B35" s="54"/>
       <c r="C35" s="36" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="D35" s="51"/>
       <c r="E35" s="52" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
     </row>
     <row r="36" s="28" customFormat="1" spans="1:5">
       <c r="A36" s="39" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B36" s="55" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="C36" s="56"/>
       <c r="D36" s="57"/>
@@ -6922,42 +6940,42 @@
     <row r="37" s="28" customFormat="1" spans="1:5">
       <c r="A37" s="53"/>
       <c r="B37" s="58" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="C37" s="59"/>
       <c r="D37" s="60"/>
       <c r="E37" s="33" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
     </row>
     <row r="38" s="28" customFormat="1" spans="1:5">
       <c r="A38" s="29" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B38" s="58" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C38" s="59"/>
       <c r="D38" s="60"/>
       <c r="E38" s="33" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
     </row>
     <row r="39" s="28" customFormat="1" spans="1:5">
       <c r="A39" s="39" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B39" s="40" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="C39" s="41" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
     </row>
     <row r="40" s="28" customFormat="1" spans="1:5">
@@ -6965,64 +6983,64 @@
       <c r="B40" s="43"/>
       <c r="C40" s="45"/>
       <c r="D40" s="32" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="E40" s="33" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
     </row>
     <row r="41" s="28" customFormat="1" spans="1:5">
       <c r="A41" s="42"/>
       <c r="B41" s="43"/>
       <c r="C41" s="46" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="D41" s="47"/>
       <c r="E41" s="33" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
     </row>
     <row r="42" s="28" customFormat="1" spans="1:5">
       <c r="A42" s="53"/>
       <c r="B42" s="49"/>
       <c r="C42" s="46" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="D42" s="47"/>
       <c r="E42" s="33" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
     </row>
     <row r="43" s="28" customFormat="1" spans="1:5">
       <c r="A43" s="39" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B43" s="50" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C43" s="61" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="D43" s="62"/>
       <c r="E43" s="52" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
     </row>
     <row r="44" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A44" s="42"/>
       <c r="B44" s="54"/>
       <c r="C44" s="61" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="D44" s="62"/>
       <c r="E44" s="52" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
     </row>
     <row r="45" s="28" customFormat="1" spans="1:5">
       <c r="A45" s="53"/>
       <c r="B45" s="58" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C45" s="59"/>
       <c r="D45" s="60"/>
@@ -7032,16 +7050,16 @@
     </row>
     <row r="46" s="28" customFormat="1" spans="1:5">
       <c r="A46" s="39" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B46" s="40" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="C46" s="41" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="E46" s="33"/>
     </row>
@@ -7050,7 +7068,7 @@
       <c r="B47" s="43"/>
       <c r="C47" s="44"/>
       <c r="D47" s="32" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="E47" s="33"/>
     </row>
@@ -7059,42 +7077,42 @@
       <c r="B48" s="49"/>
       <c r="C48" s="45"/>
       <c r="D48" s="32" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
     </row>
     <row r="49" s="28" customFormat="1" spans="1:5">
       <c r="A49" s="29" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B49" s="58" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C49" s="59"/>
       <c r="D49" s="60"/>
       <c r="E49" s="33" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
     </row>
     <row r="50" s="28" customFormat="1" spans="1:5">
       <c r="A50" s="39" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B50" s="58" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C50" s="59"/>
       <c r="D50" s="60"/>
       <c r="E50" s="33" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
     </row>
     <row r="51" s="28" customFormat="1" spans="1:5">
       <c r="A51" s="53"/>
       <c r="B51" s="58" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C51" s="59"/>
       <c r="D51" s="60"/>
@@ -7104,10 +7122,10 @@
     </row>
     <row r="52" s="28" customFormat="1" spans="1:5">
       <c r="A52" s="29" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B52" s="58" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C52" s="59"/>
       <c r="D52" s="60"/>
@@ -7115,10 +7133,10 @@
     </row>
     <row r="53" s="28" customFormat="1" spans="1:5">
       <c r="A53" s="39" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="B53" s="58" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C53" s="59"/>
       <c r="D53" s="60"/>
@@ -7130,18 +7148,18 @@
       <c r="C54" s="59"/>
       <c r="D54" s="60"/>
       <c r="E54" s="33" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
     </row>
     <row r="55" s="28" customFormat="1" spans="1:5">
       <c r="A55" s="29" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B55" s="30"/>
       <c r="C55" s="31"/>
       <c r="D55" s="32"/>
       <c r="E55" s="33" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
     </row>
   </sheetData>
@@ -7249,7 +7267,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
@@ -7263,7 +7281,7 @@
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="9" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="11"/>
@@ -7287,7 +7305,7 @@
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="9" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="11"/>
@@ -7300,7 +7318,7 @@
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="22" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="11"/>
@@ -7313,7 +7331,7 @@
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="9" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="11"/>
@@ -7347,7 +7365,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="10"/>
@@ -7393,7 +7411,7 @@
         <v>31</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="10"/>
@@ -7429,7 +7447,7 @@
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="22" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="11"/>
@@ -7463,10 +7481,10 @@
         <v>42</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="11"/>
@@ -7478,10 +7496,10 @@
         <v>45</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="11"/>
@@ -7504,7 +7522,7 @@
         <v>50</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="10"/>
@@ -7517,10 +7535,10 @@
         <v>52</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="11"/>
@@ -7554,10 +7572,10 @@
         <v>58</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="11"/>
@@ -7569,10 +7587,10 @@
         <v>61</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="11"/>
@@ -7596,7 +7614,7 @@
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="22" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="11"/>
@@ -7663,7 +7681,7 @@
         <v>74</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="10"/>
@@ -7677,7 +7695,7 @@
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="22" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="11"/>
@@ -7689,7 +7707,7 @@
         <v>79</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="C38" s="25"/>
       <c r="D38" s="26"/>
@@ -7703,7 +7721,7 @@
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="22" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="11"/>
@@ -7715,10 +7733,10 @@
         <v>84</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="11"/>
@@ -7731,7 +7749,7 @@
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="22" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="D41" s="10"/>
       <c r="E41" s="11"/>
@@ -7754,7 +7772,7 @@
         <v>93</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="10"/>
@@ -7778,7 +7796,7 @@
         <v>97</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="10"/>
@@ -7814,7 +7832,7 @@
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="22" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="D48" s="10"/>
       <c r="E48" s="11"/>
@@ -7838,7 +7856,7 @@
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="22" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="D50" s="10"/>
       <c r="E50" s="11"/>
@@ -7861,10 +7879,10 @@
         <v>110</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="D52" s="10"/>
       <c r="E52" s="11"/>
@@ -7900,27 +7918,27 @@
   <sheetData>
     <row r="1" spans="2:6">
       <c r="B1" s="3" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
     </row>
     <row r="2" spans="2:6">
       <c r="B2" s="4" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="C2" s="4">
         <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="F2" s="4">
         <v>6</v>
@@ -7928,13 +7946,13 @@
     </row>
     <row r="3" spans="2:6">
       <c r="B3" s="4" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="C3" s="4">
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="F3" s="4">
         <v>13</v>
@@ -7942,13 +7960,13 @@
     </row>
     <row r="4" spans="2:6">
       <c r="B4" s="4" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="C4" s="4">
         <v>12</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="F4" s="4">
         <v>4</v>
@@ -7956,13 +7974,13 @@
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="4" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="C5" s="4">
         <v>2</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="F5" s="4">
         <v>6</v>
@@ -7970,13 +7988,13 @@
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="4" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="C6" s="4">
         <v>2</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="F6" s="4">
         <v>4</v>
@@ -7984,13 +8002,13 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="4" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="C7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
@@ -7998,13 +8016,13 @@
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="4" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="C8" s="4">
         <v>4</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="F8" s="4">
         <v>3</v>
@@ -8012,7 +8030,7 @@
     </row>
     <row r="9" spans="2:6">
       <c r="E9" s="4" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -8020,7 +8038,7 @@
     </row>
     <row r="10" spans="2:6">
       <c r="E10" s="4" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="F10" s="4">
         <v>5</v>
@@ -8028,7 +8046,7 @@
     </row>
     <row r="11" spans="2:6">
       <c r="E11" s="4" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -8036,7 +8054,7 @@
     </row>
     <row r="12" spans="2:6">
       <c r="E12" s="4" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="F12" s="4">
         <v>2</v>
@@ -8056,14 +8074,14 @@
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6.64545454545455" style="210" customWidth="1"/>
+    <col min="1" max="1" width="6.64545454545455" style="211" customWidth="1"/>
     <col min="2" max="2" width="32.6181818181818" style="66" customWidth="1"/>
     <col min="3" max="7" width="16.4909090909091" style="66" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="211"/>
+    <col min="8" max="16384" width="8.72727272727273" style="212"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="212"/>
+      <c r="A1" s="213"/>
       <c r="B1" s="70" t="s">
         <v>1</v>
       </c>
@@ -8083,8 +8101,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="209" customFormat="1" ht="39" spans="1:7">
-      <c r="A2" s="213" t="s">
+    <row r="2" s="210" customFormat="1" ht="39" spans="1:7">
+      <c r="A2" s="214" t="s">
         <v>167</v>
       </c>
       <c r="B2" s="78"/>
@@ -8097,7 +8115,7 @@
       <c r="G2" s="78"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="214" t="s">
+      <c r="A3" s="215" t="s">
         <v>169</v>
       </c>
       <c r="C3" s="66" t="s">
@@ -8105,7 +8123,7 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="214" t="s">
+      <c r="A4" s="215" t="s">
         <v>171</v>
       </c>
       <c r="B4" s="66" t="s">
@@ -8116,7 +8134,7 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="214" t="s">
+      <c r="A5" s="215" t="s">
         <v>174</v>
       </c>
       <c r="C5" s="66" t="s">
@@ -8127,7 +8145,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="214" t="s">
+      <c r="A6" s="215" t="s">
         <v>177</v>
       </c>
       <c r="B6" s="66" t="s">
@@ -8138,7 +8156,7 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="214" t="s">
+      <c r="A7" s="215" t="s">
         <v>180</v>
       </c>
       <c r="B7" s="66" t="s">
@@ -8146,115 +8164,115 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="214"/>
+      <c r="A8" s="215"/>
       <c r="D8" s="66" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="214"/>
+      <c r="A9" s="215"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="214"/>
+      <c r="A10" s="215"/>
       <c r="B10" s="66" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="214"/>
+      <c r="A11" s="215"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="214"/>
+      <c r="A12" s="215"/>
       <c r="B12" s="66" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="214"/>
+      <c r="A13" s="215"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="214"/>
+      <c r="A14" s="215"/>
       <c r="B14" s="66" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="214"/>
+      <c r="A15" s="215"/>
       <c r="B15" s="66" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="214"/>
+      <c r="A16" s="215"/>
       <c r="B16" s="66" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="214"/>
+      <c r="A17" s="215"/>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="214"/>
+      <c r="A18" s="215"/>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="214"/>
+      <c r="A19" s="215"/>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="214"/>
+      <c r="A20" s="215"/>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="214"/>
+      <c r="A21" s="215"/>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="214"/>
+      <c r="A22" s="215"/>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="214"/>
+      <c r="A23" s="215"/>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="214"/>
+      <c r="A24" s="215"/>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="214"/>
+      <c r="A25" s="215"/>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="214"/>
+      <c r="A26" s="215"/>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="214"/>
+      <c r="A27" s="215"/>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="214"/>
+      <c r="A28" s="215"/>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="214"/>
+      <c r="A29" s="215"/>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="214"/>
+      <c r="A30" s="215"/>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="214"/>
+      <c r="A31" s="215"/>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="214"/>
+      <c r="A32" s="215"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="214"/>
+      <c r="A33" s="215"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="214"/>
+      <c r="A34" s="215"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="214"/>
+      <c r="A35" s="215"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="214"/>
+      <c r="A36" s="215"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="214"/>
+      <c r="A37" s="215"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="214"/>
+      <c r="A38" s="215"/>
       <c r="B38" s="78"/>
       <c r="C38" s="78"/>
       <c r="D38" s="78"/>
@@ -8263,7 +8281,7 @@
       <c r="G38" s="78"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="214"/>
+      <c r="A39" s="215"/>
       <c r="B39" s="78"/>
       <c r="C39" s="78"/>
       <c r="D39" s="78"/>
@@ -8272,40 +8290,40 @@
       <c r="G39" s="78"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="214"/>
+      <c r="A40" s="215"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="214"/>
+      <c r="A41" s="215"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="214"/>
+      <c r="A42" s="215"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="214"/>
+      <c r="A43" s="215"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="214"/>
+      <c r="A44" s="215"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="214"/>
+      <c r="A45" s="215"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="214"/>
+      <c r="A46" s="215"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="214"/>
+      <c r="A47" s="215"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="214"/>
+      <c r="A48" s="215"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="214"/>
+      <c r="A49" s="215"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="214"/>
+      <c r="A50" s="215"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="214"/>
+      <c r="A51" s="215"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8318,7 +8336,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.8"/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="24" style="200" customWidth="1"/>
@@ -8469,8 +8487,12 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="206"/>
-      <c r="B15" s="202"/>
-      <c r="C15" s="202"/>
+      <c r="B15" s="202" t="s">
+        <v>220</v>
+      </c>
+      <c r="C15" s="202" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="206"/>
@@ -8484,32 +8506,32 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="202" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B18" s="202" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C18" s="202" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="202" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B19" s="202" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C19" s="202" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="202" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B20" s="202" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C20" s="208">
         <v>0.440972222222222</v>
@@ -8520,50 +8542,50 @@
         <v>61</v>
       </c>
       <c r="B21" s="202" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C21" s="202" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="204"/>
       <c r="B22" s="202" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C22" s="202" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="203" t="s">
+        <v>234</v>
+      </c>
+      <c r="B23" s="202" t="s">
         <v>232</v>
       </c>
-      <c r="B23" s="202" t="s">
-        <v>230</v>
-      </c>
       <c r="C23" s="202" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="204"/>
       <c r="B24" s="202" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C24" s="202" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="25" ht="28" spans="1:3">
       <c r="A25" s="205" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B25" s="202" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C25" s="202" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -8572,120 +8594,134 @@
         <v>216</v>
       </c>
       <c r="C26" s="202" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="203" t="s">
-        <v>240</v>
-      </c>
+      <c r="A27" s="209"/>
       <c r="B27" s="202" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="C27" s="202" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="204"/>
-      <c r="B28" s="202" t="s">
+      <c r="A28" s="209"/>
+      <c r="B28" s="202"/>
+      <c r="C28" s="202"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="203" t="s">
+        <v>243</v>
+      </c>
+      <c r="B29" s="202" t="s">
+        <v>244</v>
+      </c>
+      <c r="C29" s="202" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="204"/>
+      <c r="B30" s="202" t="s">
         <v>211</v>
       </c>
-      <c r="C28" s="202" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="29" ht="28" spans="1:3">
-      <c r="A29" s="205" t="s">
+      <c r="C30" s="202" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="31" ht="28" spans="1:3">
+      <c r="A31" s="205" t="s">
         <v>45</v>
       </c>
-      <c r="B29" s="202" t="s">
+      <c r="B31" s="202" t="s">
         <v>211</v>
       </c>
-      <c r="C29" s="202" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="207"/>
-      <c r="B30" s="200" t="s">
-        <v>245</v>
-      </c>
-      <c r="C30" s="200" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="31" ht="98" spans="1:3">
-      <c r="A31" s="205" t="s">
+      <c r="C31" s="202" t="s">
         <v>247</v>
       </c>
-      <c r="B31" s="200" t="s">
-        <v>211</v>
-      </c>
-      <c r="C31" s="200" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="32" ht="84" spans="1:3">
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32" s="207"/>
       <c r="B32" s="200" t="s">
+        <v>248</v>
+      </c>
+      <c r="C32" s="200" t="s">
         <v>249</v>
       </c>
-      <c r="C32" s="200" t="s">
+    </row>
+    <row r="33" ht="98" spans="1:3">
+      <c r="A33" s="205" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="200" t="s">
+      <c r="B33" s="200" t="s">
+        <v>211</v>
+      </c>
+      <c r="C33" s="200" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="34" ht="84" spans="1:3">
+      <c r="A34" s="207"/>
+      <c r="B34" s="200" t="s">
+        <v>252</v>
+      </c>
+      <c r="C34" s="200" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="200" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="200" t="s">
-        <v>251</v>
-      </c>
-      <c r="C33" s="200" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="34" ht="28" spans="1:3">
-      <c r="A34" s="200" t="s">
-        <v>253</v>
-      </c>
-      <c r="B34" s="200" t="s">
-        <v>245</v>
-      </c>
-      <c r="C34" s="200" t="s">
+      <c r="B35" s="200" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="205" t="s">
+      <c r="C35" s="200" t="s">
         <v>255</v>
       </c>
-      <c r="B35" s="200" t="s">
-        <v>216</v>
-      </c>
-      <c r="C35" s="200" t="s">
+    </row>
+    <row r="36" ht="28" spans="1:3">
+      <c r="A36" s="200" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="207"/>
       <c r="B36" s="200" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C36" s="200" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="200" t="s">
+      <c r="A37" s="205" t="s">
+        <v>258</v>
+      </c>
+      <c r="B37" s="200" t="s">
+        <v>216</v>
+      </c>
+      <c r="C37" s="200" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="207"/>
+      <c r="B38" s="200" t="s">
+        <v>252</v>
+      </c>
+      <c r="C38" s="200" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="200" t="s">
         <v>52</v>
       </c>
-      <c r="B37" s="200" t="s">
+      <c r="B39" s="200" t="s">
         <v>218</v>
       </c>
-      <c r="C37" s="200" t="s">
-        <v>258</v>
+      <c r="C39" s="200" t="s">
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -8695,10 +8731,10 @@
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A27:A28"/>
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A37:A38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -8725,14 +8761,14 @@
   <sheetData>
     <row r="1" s="186" customFormat="1" ht="15" spans="1:7">
       <c r="A1" s="189" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B1" s="190"/>
       <c r="C1" s="190"/>
       <c r="D1" s="191"/>
       <c r="E1" s="192"/>
       <c r="F1" s="186" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" s="187" customFormat="1" spans="1:7">
@@ -8741,17 +8777,17 @@
       </c>
       <c r="B2" s="194"/>
       <c r="C2" s="187" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D2" s="187" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E2" s="141"/>
       <c r="F2" s="187" t="s">
         <v>189</v>
       </c>
       <c r="G2" s="187" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -8766,10 +8802,10 @@
       </c>
       <c r="D3" s="119"/>
       <c r="F3" s="119" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="G3" s="119" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -8782,10 +8818,10 @@
       </c>
       <c r="D4" s="119"/>
       <c r="F4" s="119" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G4" s="119" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -8797,8 +8833,12 @@
         <v>158</v>
       </c>
       <c r="D5" s="119"/>
-      <c r="F5" s="119"/>
-      <c r="G5" s="119"/>
+      <c r="F5" s="119" t="s">
+        <v>271</v>
+      </c>
+      <c r="G5" s="119" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="196"/>
@@ -8948,7 +8988,7 @@
   <sheetData>
     <row r="1" spans="1:39">
       <c r="A1" s="174" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B1" s="175">
         <v>45992</v>
@@ -8986,7 +9026,7 @@
       <c r="AE1" s="176"/>
       <c r="AF1" s="176"/>
       <c r="AG1" s="143" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AH1" s="146"/>
       <c r="AI1" s="146"/>
@@ -9091,25 +9131,25 @@
         <v>20</v>
       </c>
       <c r="AG2" s="178" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AH2" s="178" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="AI2" s="178" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AJ2" s="178" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="AK2" s="179" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="AL2" s="179" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="AM2" s="179" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:39">
@@ -9756,16 +9796,18 @@
       </c>
       <c r="AB11" s="120"/>
       <c r="AC11" s="120"/>
-      <c r="AD11" s="120"/>
+      <c r="AD11" s="120">
+        <v>1</v>
+      </c>
       <c r="AE11" s="120"/>
       <c r="AF11" s="120"/>
       <c r="AG11" s="180">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH11" s="181" cm="1">
         <f t="array" ref="AH11">SUMPRODUCT(--(B11:AF11=INT(B11:AF11)),--(B11:AF11&gt;0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI11" s="181" cm="1">
         <f t="array" ref="AI11">MAX(FREQUENCY(IF((B11:AF11=INT(B11:AF11))*(B11:AF11&gt;0),COLUMN(B11:AF11)),IF((B11:AF11&lt;&gt;INT(B11:AF11))+(B11:AF11&lt;=0),COLUMN(B11:AF11))))</f>
@@ -9773,7 +9815,7 @@
       </c>
       <c r="AJ11" s="182" cm="1">
         <f t="array" ref="AJ11">SUMPRODUCT(--(B11:AF11=INT(B11:AF11)),--(B11:AF11&gt;0))/30*100%</f>
-        <v>0.166666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="AK11" s="183">
         <f t="shared" ref="AK11:AM11" si="8">RANK(AG11,AG$3:AG$53,0)</f>
@@ -9781,7 +9823,7 @@
       </c>
       <c r="AL11" s="183">
         <f t="shared" si="8"/>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AM11" s="183">
         <f t="shared" si="8"/>
@@ -10351,11 +10393,11 @@
       </c>
       <c r="AK19" s="183">
         <f t="shared" ref="AK19:AM19" si="16">RANK(AG19,AG$3:AG$53,0)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL19" s="183">
         <f t="shared" si="16"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM19" s="183">
         <f t="shared" si="16"/>
@@ -11139,7 +11181,7 @@
       </c>
       <c r="AL30" s="183">
         <f t="shared" si="27"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM30" s="183">
         <f t="shared" si="27"/>
@@ -11217,7 +11259,7 @@
       </c>
       <c r="AL31" s="183">
         <f t="shared" si="28"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM31" s="183">
         <f t="shared" si="28"/>
@@ -11635,7 +11677,7 @@
       </c>
       <c r="AK37" s="183">
         <f t="shared" ref="AK37:AM37" si="35">RANK(AG37,AG$3:AG$53,0)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL37" s="183">
         <f t="shared" si="35"/>
@@ -12476,16 +12518,18 @@
       <c r="AC48" s="120">
         <v>1</v>
       </c>
-      <c r="AD48" s="120"/>
+      <c r="AD48" s="120">
+        <v>1</v>
+      </c>
       <c r="AE48" s="120"/>
       <c r="AF48" s="120"/>
       <c r="AG48" s="180">
         <f t="shared" si="33"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH48" s="181" cm="1">
         <f t="array" ref="AH48">SUMPRODUCT(--(B48:AF48=INT(B48:AF48)),--(B48:AF48&gt;0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI48" s="181" cm="1">
         <f t="array" ref="AI48">MAX(FREQUENCY(IF((B48:AF48=INT(B48:AF48))*(B48:AF48&gt;0),COLUMN(B48:AF48)),IF((B48:AF48&lt;&gt;INT(B48:AF48))+(B48:AF48&lt;=0),COLUMN(B48:AF48))))</f>
@@ -12493,15 +12537,15 @@
       </c>
       <c r="AJ48" s="182" cm="1">
         <f t="array" ref="AJ48">SUMPRODUCT(--(B48:AF48=INT(B48:AF48)),--(B48:AF48&gt;0))/30*100%</f>
-        <v>0.233333333333333</v>
+        <v>0.266666666666667</v>
       </c>
       <c r="AK48" s="183">
         <f t="shared" ref="AK48:AM48" si="46">RANK(AG48,AG$3:AG$53,0)</f>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AL48" s="183">
         <f t="shared" si="46"/>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AM48" s="183">
         <f t="shared" si="46"/>
@@ -13159,7 +13203,7 @@
   <pageSetup paperSize="9" scale="80" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A28:X33 Z28:AM33 A34:AM35 A36:X36 Z36:AM36 A37:AM37 A38:X38 AD38:AM38 Z38:AB38 A39:AM39 A42:X42 Z41:AM42 AC40:AM40 A43:AM43 A44:W44 Z44:AM44 A45:AM45 A46:X46 AA46 AC46:AM46 A47:AM47 A48:X49 Z49:AM49 AD48:AM48 Z48:AB48 A50:AM53 X41 A40:V41 A9:X10 Z10:AM10 AD9:AM9 Z9:AB9 AB11:AM11 A11:Z11 A12:X15 AB15:AM15 Z15 Z14:AM14 AB13:AM13 Z13 Z12:AM12 A16:AM16 A17:X18 Z17:AM18 A19:AM21 A22:X22 AA22:AM22 A23:AM23 A24:X25 Z24:AM25 A26:AM27 X8:AM8 A8:V8 A1:AM2 A3:X4 Z3:AM4 A5:AM7" formulaRange="1" unlockedFormula="1"/>
+    <ignoredError sqref="A5:AM7 Z3:AM4 A3:X4 A1:AM2 A8:V8 X8:AM8 A26:AM27 Z24:AM25 A24:X25 A23:AM23 AA22:AM22 A22:X22 A19:AM21 Z17:AM18 A17:X18 A16:AM16 Z12:AM12 Z13 AB13:AM13 Z14:AM14 Z15 AB15:AM15 A12:X15 A11:Z11 AB11:AC11 AE11:AM11 Z9:AB9 AD9:AM9 Z10:AM10 A9:X10 A40:V41 X41 A50:AM53 Z48:AB48 AE48:AM48 Z49:AM49 A48:X49 A47:AM47 AC46:AM46 AA46 A46:X46 A45:AM45 Z44:AM44 A44:W44 A43:AM43 AC40:AM40 Z41:AM42 A42:X42 A39:AM39 Z38:AB38 AD38:AM38 A38:X38 A37:AM37 Z36:AM36 A36:X36 A34:AM35 Z28:AM33 A28:X33" formulaRange="1" unlockedFormula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -13206,21 +13250,21 @@
     </row>
     <row r="2" ht="16.5" spans="1:10">
       <c r="A2" s="148" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B2" s="152" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C2" s="153" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D2" s="154"/>
       <c r="E2" s="152" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F2" s="152"/>
       <c r="G2" s="155" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="H2" s="147"/>
       <c r="I2" s="147"/>
@@ -13228,10 +13272,10 @@
     </row>
     <row r="3" ht="16.5" spans="1:10">
       <c r="A3" s="148" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B3" s="157" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C3" s="157"/>
       <c r="D3" s="157"/>
@@ -13244,10 +13288,10 @@
     </row>
     <row r="4" ht="16.5" spans="1:10">
       <c r="A4" s="148" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B4" s="158" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C4" s="158"/>
       <c r="D4" s="158"/>
@@ -13260,7 +13304,7 @@
     </row>
     <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="148" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B5" s="159">
         <v>1</v>
@@ -13280,7 +13324,7 @@
     </row>
     <row r="6" ht="16.5" spans="1:10">
       <c r="A6" s="148" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B6" s="161">
         <v>1</v>
@@ -13290,7 +13334,7 @@
       <c r="E6" s="161"/>
       <c r="F6" s="161"/>
       <c r="G6" s="162" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="H6" s="147"/>
       <c r="I6" s="147"/>
@@ -13298,10 +13342,10 @@
     </row>
     <row r="7" ht="16.5" spans="1:10">
       <c r="A7" s="148" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B7" s="163" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C7" s="163"/>
       <c r="D7" s="163"/>
@@ -13316,14 +13360,14 @@
     </row>
     <row r="8" ht="16.5" spans="1:10">
       <c r="A8" s="148" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B8" s="165">
         <v>1</v>
       </c>
       <c r="C8" s="165"/>
       <c r="D8" s="166" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="E8" s="166"/>
       <c r="F8" s="166"/>
@@ -13334,10 +13378,10 @@
     </row>
     <row r="9" ht="16.5" spans="1:10">
       <c r="A9" s="148" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B9" s="152" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C9" s="152"/>
       <c r="D9" s="152"/>
@@ -13350,23 +13394,23 @@
     </row>
     <row r="10" ht="16.5" spans="1:10">
       <c r="A10" s="148" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B10" s="157">
         <v>1</v>
       </c>
       <c r="C10" s="157"/>
       <c r="D10" s="167" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="E10" s="157">
         <v>1</v>
       </c>
       <c r="F10" s="167" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="G10" s="147" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="H10" s="147"/>
       <c r="I10" s="147"/>
@@ -13374,7 +13418,7 @@
     </row>
     <row r="11" ht="16.5" spans="1:10">
       <c r="A11" s="148" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B11" s="158">
         <v>1</v>
@@ -13390,7 +13434,7 @@
     </row>
     <row r="12" ht="16.5" spans="1:10">
       <c r="A12" s="148" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B12" s="159">
         <v>1</v>
@@ -13408,17 +13452,17 @@
     </row>
     <row r="13" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A13" s="148" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="168" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -13426,10 +13470,10 @@
     </row>
     <row r="14" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A14" s="148" t="s">
+        <v>305</v>
+      </c>
+      <c r="B14" s="170" t="s">
         <v>300</v>
-      </c>
-      <c r="B14" s="170" t="s">
-        <v>295</v>
       </c>
       <c r="C14" s="170"/>
       <c r="D14" s="170"/>
@@ -13504,7 +13548,7 @@
   <sheetData>
     <row r="1" s="117" customFormat="1" spans="1:9">
       <c r="A1" s="121" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B1" s="122"/>
       <c r="C1" s="117" t="s">
@@ -13529,10 +13573,10 @@
     </row>
     <row r="2" s="118" customFormat="1" spans="1:9">
       <c r="A2" s="125" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B2" s="126" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C2" s="127" t="s">
         <v>7</v>
@@ -13544,7 +13588,7 @@
     <row r="3" s="118" customFormat="1" spans="1:9">
       <c r="A3" s="130"/>
       <c r="B3" s="126" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C3" s="127" t="s">
         <v>28</v>
@@ -13566,7 +13610,7 @@
     <row r="5" s="118" customFormat="1" spans="1:9">
       <c r="A5" s="130"/>
       <c r="B5" s="126" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C5" s="127" t="s">
         <v>31</v>
@@ -13578,7 +13622,7 @@
     <row r="6" s="118" customFormat="1" spans="1:9">
       <c r="A6" s="130"/>
       <c r="B6" s="126" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>19</v>
@@ -13606,7 +13650,7 @@
     <row r="8" s="118" customFormat="1" spans="1:9">
       <c r="A8" s="130"/>
       <c r="B8" s="126" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>14</v>
@@ -13620,7 +13664,7 @@
     <row r="9" s="118" customFormat="1" spans="1:9">
       <c r="A9" s="130"/>
       <c r="B9" s="126" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C9" s="127" t="s">
         <v>24</v>
@@ -13632,7 +13676,7 @@
     <row r="10" s="118" customFormat="1" spans="1:9">
       <c r="A10" s="130"/>
       <c r="B10" s="126" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C10" s="127" t="s">
         <v>34</v>
@@ -13644,7 +13688,7 @@
     <row r="11" s="118" customFormat="1" spans="1:9">
       <c r="A11" s="134"/>
       <c r="B11" s="126" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C11" s="127" t="s">
         <v>69</v>
@@ -13655,10 +13699,10 @@
     </row>
     <row r="12" s="119" customFormat="1" spans="1:9">
       <c r="A12" s="135" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B12" s="136" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C12" s="137" t="s">
         <v>88</v>
@@ -13682,10 +13726,10 @@
     <row r="14" s="119" customFormat="1" spans="1:9">
       <c r="A14" s="141"/>
       <c r="B14" s="136" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C14" s="137" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="D14" s="142"/>
       <c r="E14" s="138"/>
@@ -13696,7 +13740,7 @@
     <row r="15" s="119" customFormat="1" spans="1:9">
       <c r="A15" s="141"/>
       <c r="B15" s="136" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C15" s="137" t="s">
         <v>10</v>
@@ -13718,7 +13762,7 @@
     <row r="17" s="119" customFormat="1" spans="1:7">
       <c r="A17" s="141"/>
       <c r="B17" s="136" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C17" s="137" t="s">
         <v>27</v>
@@ -13730,7 +13774,7 @@
     <row r="18" s="119" customFormat="1" spans="1:7">
       <c r="A18" s="141"/>
       <c r="B18" s="136" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C18" s="137" t="s">
         <v>42</v>
@@ -13742,7 +13786,7 @@
     <row r="19" s="119" customFormat="1" spans="1:7">
       <c r="A19" s="141"/>
       <c r="B19" s="136" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C19" s="137" t="s">
         <v>81</v>
@@ -13754,7 +13798,7 @@
     <row r="20" s="119" customFormat="1" spans="1:7">
       <c r="A20" s="141"/>
       <c r="B20" s="136" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C20" s="137" t="s">
         <v>84</v>
@@ -13766,7 +13810,7 @@
     <row r="21" s="119" customFormat="1" spans="1:7">
       <c r="A21" s="141"/>
       <c r="B21" s="136" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C21" s="143"/>
       <c r="D21" s="144"/>
@@ -13778,7 +13822,7 @@
     <row r="22" s="119" customFormat="1" spans="1:7">
       <c r="A22" s="145"/>
       <c r="B22" s="136" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C22" s="143"/>
       <c r="D22" s="146"/>
@@ -13840,7 +13884,7 @@
   <sheetData>
     <row r="1" s="91" customFormat="1" customHeight="1" spans="1:16">
       <c r="A1" s="94" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B1" s="95"/>
       <c r="C1" s="95"/>
@@ -13871,7 +13915,7 @@
     </row>
     <row r="3" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A3" s="100" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B3" s="101"/>
       <c r="C3" s="102"/>
@@ -14063,7 +14107,7 @@
     </row>
     <row r="11" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A11" s="100" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B11" s="101"/>
       <c r="C11" s="102"/>
@@ -14255,7 +14299,7 @@
     </row>
     <row r="19" s="93" customFormat="1" customHeight="1" spans="1:9">
       <c r="A19" s="100" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B19" s="101"/>
       <c r="C19" s="102"/>
@@ -14482,10 +14526,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="82" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B1" s="83" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C1" s="84" t="s">
         <v>190</v>
@@ -14496,208 +14540,208 @@
         <v>1</v>
       </c>
       <c r="B2" s="80" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C2" s="81" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="85"/>
       <c r="B3" s="80" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C3" s="81" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="85"/>
       <c r="B4" s="80" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C4" s="81" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="85"/>
       <c r="B5" s="80" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C5" s="81" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="85"/>
       <c r="B6" s="80" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C6" s="81" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="85"/>
       <c r="B7" s="80" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C7" s="81" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="85"/>
       <c r="B8" s="80" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C8" s="81" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="85"/>
       <c r="B9" s="80" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="85"/>
       <c r="B10" s="80" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C10" s="81" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="85"/>
       <c r="B11" s="80" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C11" s="81" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="85"/>
       <c r="B12" s="80" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C12" s="81" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="85"/>
       <c r="B13" s="80" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C13" s="81" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="85"/>
       <c r="B14" s="80" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="85"/>
       <c r="B15" s="80" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C15" s="81" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="85"/>
       <c r="B16" s="80" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C16" s="81" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="85"/>
       <c r="B17" s="80" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C17" s="81" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="85"/>
       <c r="B18" s="80" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C18" s="81" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="85"/>
       <c r="B19" s="80" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C19" s="81" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="85"/>
       <c r="B20" s="80" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C20" s="81" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="85"/>
       <c r="B21" s="80" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C21" s="81" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="85"/>
       <c r="B22" s="80" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C22" s="81" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="85"/>
       <c r="B23" s="80" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C23" s="81" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="85"/>
       <c r="B24" s="80" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="C24" s="81" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -14705,118 +14749,118 @@
         <v>2</v>
       </c>
       <c r="B25" s="80" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C25" s="81" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="86"/>
       <c r="B26" s="80" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C26" s="81" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="86"/>
       <c r="B27" s="80" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C27" s="81" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="86"/>
       <c r="B28" s="80" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="C28" s="81" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="86"/>
       <c r="B29" s="80" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C29" s="81" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="86"/>
       <c r="B30" s="80" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C30" s="81" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="86"/>
       <c r="B31" s="80" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C31" s="81" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="86"/>
       <c r="B32" s="80" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C32" s="81" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="86"/>
       <c r="B33" s="80" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C33" s="81" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="86"/>
       <c r="B34" s="80" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C34" s="81" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="86"/>
       <c r="B35" s="80" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C35" s="81" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="86"/>
       <c r="B36" s="80" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C36" s="81" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="87"/>
       <c r="B37" s="80" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C37" s="81" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -14824,138 +14868,138 @@
         <v>3</v>
       </c>
       <c r="B38" s="80" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C38" s="81" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="89"/>
       <c r="B39" s="80" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="C39" s="81" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="89"/>
       <c r="B40" s="80" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C40" s="81" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="89"/>
       <c r="B41" s="80" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C41" s="81" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="89"/>
       <c r="B42" s="80" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C42" s="81" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="89"/>
       <c r="B43" s="80" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C43" s="81" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="89"/>
       <c r="B44" s="80" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C44" s="81" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="89"/>
       <c r="B45" s="80" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C45" s="81" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="89"/>
       <c r="B46" s="80" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C46" s="81" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="89"/>
       <c r="B47" s="80" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C47" s="81" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="89"/>
       <c r="B48" s="80" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C48" s="81" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="89"/>
       <c r="B49" s="80" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C49" s="81" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="90"/>
       <c r="B50" s="80" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="C50" s="81" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:3">
       <c r="A51" s="79"/>
       <c r="B51" s="80" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="C51" s="81"/>
     </row>
     <row r="52" customFormat="1" spans="1:3">
       <c r="A52" s="79"/>
       <c r="B52" s="80" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="C52" s="81"/>
     </row>
     <row r="53" customFormat="1" spans="1:3">
       <c r="A53" s="79"/>
       <c r="B53" s="80" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="C53" s="81"/>
     </row>

--- a/c/9班资料.xlsx
+++ b/c/9班资料.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10030" tabRatio="724"/>
+    <workbookView windowWidth="20750" windowHeight="10480" tabRatio="724" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="师生" sheetId="5" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="618">
   <si>
     <t>姓名</t>
   </si>
@@ -99,7 +99,7 @@
     <t>猴、郑致辰</t>
   </si>
   <si>
-    <t>带菜（给孔保管）、小测降等级、测心电图时对薛阅晨说“在这里！”、小心点、尖叫</t>
+    <t>带菜（给孔保管）、小测降等级、测心电图时对薛阅晨说“在这里！”、小心点、尖叫、跑完800m：瘫倒在地</t>
   </si>
   <si>
     <t>郭沁诗</t>
@@ -887,6 +887,15 @@
   </si>
   <si>
     <t>往棚子跑时不到一半脱离队伍走路，在白线前调头（套圈最厉害）</t>
+  </si>
+  <si>
+    <t>晴蔡</t>
+  </si>
+  <si>
+    <t>八上1.19</t>
+  </si>
+  <si>
+    <t>中午江雨晴整块鸡排（鸡块？）给蔡华楷（郑永泽说）</t>
   </si>
   <si>
     <t>政治课</t>
@@ -3187,20 +3196,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="黑体"/>
+      <name val="华文仿宋"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="华文仿宋"/>
-      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <strike/>
@@ -3212,6 +3215,12 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="57">
@@ -3977,7 +3986,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="223">
+  <cellXfs count="229">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4502,6 +4511,9 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4509,6 +4521,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="57" fontId="24" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="57" fontId="24" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4517,29 +4544,26 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4989,29 +5013,29 @@
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="7.59090909090909" style="71" customWidth="1"/>
-    <col min="2" max="7" width="25.8727272727273" style="217" customWidth="1"/>
+    <col min="2" max="7" width="25.8727272727273" style="223" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="216" customFormat="1" spans="1:7">
+    <row r="1" s="222" customFormat="1" spans="1:7">
       <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="218" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="218" t="s">
+      <c r="B1" s="224" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="224" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="218" t="s">
+      <c r="D1" s="224" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="218" t="s">
+      <c r="E1" s="224" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="218" t="s">
+      <c r="F1" s="224" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="218" t="s">
+      <c r="G1" s="224" t="s">
         <v>6</v>
       </c>
     </row>
@@ -5019,21 +5043,21 @@
       <c r="A2" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="217" t="s">
+      <c r="B2" s="223" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="217" t="s">
+      <c r="C2" s="223" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" ht="39" spans="1:7">
+    <row r="3" ht="52" spans="1:7">
       <c r="A3" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="217" t="s">
+      <c r="C3" s="223" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="217" t="s">
+      <c r="D3" s="223" t="s">
         <v>12</v>
       </c>
     </row>
@@ -5046,10 +5070,10 @@
       <c r="A5" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="217" t="s">
+      <c r="C5" s="223" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="217" t="s">
+      <c r="D5" s="223" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5057,7 +5081,7 @@
       <c r="A6" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="217" t="s">
+      <c r="C6" s="223" t="s">
         <v>18</v>
       </c>
     </row>
@@ -5065,13 +5089,13 @@
       <c r="A7" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="217" t="s">
+      <c r="B7" s="223" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="217" t="s">
+      <c r="C7" s="223" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="217" t="s">
+      <c r="D7" s="223" t="s">
         <v>22</v>
       </c>
     </row>
@@ -5089,7 +5113,7 @@
       <c r="A10" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="217" t="s">
+      <c r="B10" s="223" t="s">
         <v>26</v>
       </c>
     </row>
@@ -5107,7 +5131,7 @@
       <c r="A13" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="217" t="s">
+      <c r="D13" s="223" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5115,7 +5139,7 @@
       <c r="A14" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="217" t="s">
+      <c r="B14" s="223" t="s">
         <v>32</v>
       </c>
     </row>
@@ -5128,7 +5152,7 @@
       <c r="A16" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="217" t="s">
+      <c r="C16" s="223" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5136,7 +5160,7 @@
       <c r="A17" s="72" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="217" t="s">
+      <c r="C17" s="223" t="s">
         <v>37</v>
       </c>
     </row>
@@ -5144,7 +5168,7 @@
       <c r="A18" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="217" t="s">
+      <c r="D18" s="223" t="s">
         <v>39</v>
       </c>
     </row>
@@ -5152,7 +5176,7 @@
       <c r="A19" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="217" t="s">
+      <c r="D19" s="223" t="s">
         <v>41</v>
       </c>
     </row>
@@ -5160,10 +5184,10 @@
       <c r="A20" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="217" t="s">
+      <c r="B20" s="223" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="217" t="s">
+      <c r="C20" s="223" t="s">
         <v>44</v>
       </c>
     </row>
@@ -5171,13 +5195,13 @@
       <c r="A21" s="72" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="217" t="s">
+      <c r="B21" s="223" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="217" t="s">
+      <c r="C21" s="223" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="217" t="s">
+      <c r="D21" s="223" t="s">
         <v>48</v>
       </c>
     </row>
@@ -5190,7 +5214,7 @@
       <c r="A23" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="217" t="s">
+      <c r="B23" s="223" t="s">
         <v>51</v>
       </c>
     </row>
@@ -5198,13 +5222,13 @@
       <c r="A24" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="217" t="s">
+      <c r="B24" s="223" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="217" t="s">
+      <c r="C24" s="223" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="217" t="s">
+      <c r="D24" s="223" t="s">
         <v>55</v>
       </c>
     </row>
@@ -5222,10 +5246,10 @@
       <c r="A27" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="B27" s="217" t="s">
+      <c r="B27" s="223" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="217" t="s">
+      <c r="C27" s="223" t="s">
         <v>60</v>
       </c>
     </row>
@@ -5233,13 +5257,13 @@
       <c r="A28" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="B28" s="217" t="s">
+      <c r="B28" s="223" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="217" t="s">
+      <c r="C28" s="223" t="s">
         <v>63</v>
       </c>
-      <c r="D28" s="217" t="s">
+      <c r="D28" s="223" t="s">
         <v>64</v>
       </c>
     </row>
@@ -5252,10 +5276,10 @@
       <c r="A30" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="B30" s="217" t="s">
+      <c r="B30" s="223" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="217" t="s">
+      <c r="C30" s="223" t="s">
         <v>68</v>
       </c>
     </row>
@@ -5288,7 +5312,7 @@
       <c r="A36" s="72" t="s">
         <v>74</v>
       </c>
-      <c r="B36" s="217" t="s">
+      <c r="B36" s="223" t="s">
         <v>75</v>
       </c>
     </row>
@@ -5296,10 +5320,10 @@
       <c r="A37" s="72" t="s">
         <v>76</v>
       </c>
-      <c r="C37" s="217" t="s">
+      <c r="C37" s="223" t="s">
         <v>77</v>
       </c>
-      <c r="D37" s="217" t="s">
+      <c r="D37" s="223" t="s">
         <v>78</v>
       </c>
     </row>
@@ -5307,23 +5331,23 @@
       <c r="A38" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="B38" s="217" t="s">
+      <c r="B38" s="223" t="s">
         <v>80</v>
       </c>
-      <c r="C38" s="219"/>
-      <c r="D38" s="219"/>
-      <c r="E38" s="219"/>
-      <c r="F38" s="219"/>
-      <c r="G38" s="219"/>
+      <c r="C38" s="225"/>
+      <c r="D38" s="225"/>
+      <c r="E38" s="225"/>
+      <c r="F38" s="225"/>
+      <c r="G38" s="225"/>
     </row>
     <row r="39" ht="26" spans="1:8">
       <c r="A39" s="72" t="s">
         <v>81</v>
       </c>
-      <c r="C39" s="217" t="s">
+      <c r="C39" s="223" t="s">
         <v>82</v>
       </c>
-      <c r="D39" s="217" t="s">
+      <c r="D39" s="223" t="s">
         <v>83</v>
       </c>
     </row>
@@ -5331,13 +5355,13 @@
       <c r="A40" s="72" t="s">
         <v>84</v>
       </c>
-      <c r="B40" s="217" t="s">
+      <c r="B40" s="223" t="s">
         <v>85</v>
       </c>
-      <c r="C40" s="217" t="s">
+      <c r="C40" s="223" t="s">
         <v>86</v>
       </c>
-      <c r="D40" s="217" t="s">
+      <c r="D40" s="223" t="s">
         <v>87</v>
       </c>
     </row>
@@ -5345,13 +5369,13 @@
       <c r="A41" s="72" t="s">
         <v>88</v>
       </c>
-      <c r="C41" s="217" t="s">
+      <c r="C41" s="223" t="s">
         <v>89</v>
       </c>
-      <c r="D41" s="217" t="s">
+      <c r="D41" s="223" t="s">
         <v>90</v>
       </c>
-      <c r="H41" s="220" t="s">
+      <c r="H41" s="226" t="s">
         <v>91</v>
       </c>
     </row>
@@ -5364,7 +5388,7 @@
       <c r="A43" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="B43" s="217" t="s">
+      <c r="B43" s="223" t="s">
         <v>94</v>
       </c>
     </row>
@@ -5372,7 +5396,7 @@
       <c r="A44" s="72" t="s">
         <v>95</v>
       </c>
-      <c r="B44" s="217" t="s">
+      <c r="B44" s="223" t="s">
         <v>96</v>
       </c>
     </row>
@@ -5380,10 +5404,10 @@
       <c r="A45" s="72" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="217" t="s">
+      <c r="C45" s="223" t="s">
         <v>98</v>
       </c>
-      <c r="D45" s="217" t="s">
+      <c r="D45" s="223" t="s">
         <v>99</v>
       </c>
     </row>
@@ -5396,7 +5420,7 @@
       <c r="A47" s="72" t="s">
         <v>101</v>
       </c>
-      <c r="D47" s="217" t="s">
+      <c r="D47" s="223" t="s">
         <v>102</v>
       </c>
     </row>
@@ -5404,10 +5428,10 @@
       <c r="A48" s="72" t="s">
         <v>103</v>
       </c>
-      <c r="C48" s="217" t="s">
+      <c r="C48" s="223" t="s">
         <v>104</v>
       </c>
-      <c r="D48" s="217" t="s">
+      <c r="D48" s="223" t="s">
         <v>105</v>
       </c>
     </row>
@@ -5420,7 +5444,7 @@
       <c r="A50" s="72" t="s">
         <v>107</v>
       </c>
-      <c r="C50" s="217" t="s">
+      <c r="C50" s="223" t="s">
         <v>108</v>
       </c>
     </row>
@@ -5433,10 +5457,10 @@
       <c r="A52" s="72" t="s">
         <v>110</v>
       </c>
-      <c r="B52" s="217" t="s">
+      <c r="B52" s="223" t="s">
         <v>111</v>
       </c>
-      <c r="C52" s="217" t="s">
+      <c r="C52" s="223" t="s">
         <v>112</v>
       </c>
     </row>
@@ -5444,36 +5468,36 @@
       <c r="A53" s="71" t="s">
         <v>113</v>
       </c>
-      <c r="B53" s="217" t="s">
+      <c r="B53" s="223" t="s">
         <v>114</v>
       </c>
-      <c r="D53" s="219"/>
-      <c r="E53" s="219"/>
-      <c r="F53" s="219"/>
-      <c r="G53" s="219"/>
+      <c r="D53" s="225"/>
+      <c r="E53" s="225"/>
+      <c r="F53" s="225"/>
+      <c r="G53" s="225"/>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="71" t="s">
         <v>115</v>
       </c>
-      <c r="B54" s="217" t="s">
+      <c r="B54" s="223" t="s">
         <v>116</v>
       </c>
-      <c r="C54" s="217" t="s">
+      <c r="C54" s="223" t="s">
         <v>117</v>
       </c>
-      <c r="D54" s="219"/>
-      <c r="E54" s="219"/>
-      <c r="F54" s="219"/>
-      <c r="G54" s="219"/>
+      <c r="D54" s="225"/>
+      <c r="E54" s="225"/>
+      <c r="F54" s="225"/>
+      <c r="G54" s="225"/>
     </row>
     <row r="55" ht="65" spans="1:7">
       <c r="A55" s="71" t="s">
         <v>118</v>
       </c>
-      <c r="B55" s="219"/>
-      <c r="C55" s="219"/>
-      <c r="D55" s="217" t="s">
+      <c r="B55" s="225"/>
+      <c r="C55" s="225"/>
+      <c r="D55" s="223" t="s">
         <v>119</v>
       </c>
     </row>
@@ -5485,7 +5509,7 @@
         <v>121</v>
       </c>
       <c r="C56" s="78"/>
-      <c r="D56" s="217" t="s">
+      <c r="D56" s="223" t="s">
         <v>122</v>
       </c>
     </row>
@@ -5499,7 +5523,7 @@
       <c r="C57" s="78" t="s">
         <v>125</v>
       </c>
-      <c r="D57" s="217" t="s">
+      <c r="D57" s="223" t="s">
         <v>126</v>
       </c>
     </row>
@@ -5507,37 +5531,37 @@
       <c r="A58" s="71" t="s">
         <v>127</v>
       </c>
-      <c r="B58" s="217" t="s">
+      <c r="B58" s="223" t="s">
         <v>128</v>
       </c>
-      <c r="C58" s="219"/>
-      <c r="D58" s="219"/>
-      <c r="E58" s="219"/>
-      <c r="F58" s="219"/>
-      <c r="G58" s="219"/>
+      <c r="C58" s="225"/>
+      <c r="D58" s="225"/>
+      <c r="E58" s="225"/>
+      <c r="F58" s="225"/>
+      <c r="G58" s="225"/>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="B59" s="219"/>
-      <c r="C59" s="217" t="s">
+      <c r="B59" s="225"/>
+      <c r="C59" s="223" t="s">
         <v>130</v>
       </c>
-      <c r="D59" s="219"/>
-      <c r="E59" s="219"/>
-      <c r="F59" s="219"/>
-      <c r="G59" s="219"/>
+      <c r="D59" s="225"/>
+      <c r="E59" s="225"/>
+      <c r="F59" s="225"/>
+      <c r="G59" s="225"/>
     </row>
     <row r="60" ht="52" spans="1:7">
       <c r="A60" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="B60" s="219" t="s">
+      <c r="B60" s="225" t="s">
         <v>132</v>
       </c>
-      <c r="C60" s="219"/>
-      <c r="D60" s="217" t="s">
+      <c r="C60" s="225"/>
+      <c r="D60" s="223" t="s">
         <v>133</v>
       </c>
     </row>
@@ -5549,18 +5573,18 @@
         <v>135</v>
       </c>
       <c r="C61" s="78"/>
-      <c r="D61" s="219"/>
-      <c r="E61" s="219"/>
-      <c r="F61" s="219"/>
-      <c r="G61" s="219"/>
+      <c r="D61" s="225"/>
+      <c r="E61" s="225"/>
+      <c r="F61" s="225"/>
+      <c r="G61" s="225"/>
     </row>
     <row r="62" ht="39" spans="1:7">
       <c r="A62" s="71" t="s">
         <v>136</v>
       </c>
-      <c r="B62" s="219"/>
-      <c r="C62" s="219"/>
-      <c r="D62" s="217" t="s">
+      <c r="B62" s="225"/>
+      <c r="C62" s="225"/>
+      <c r="D62" s="223" t="s">
         <v>137</v>
       </c>
     </row>
@@ -5574,18 +5598,18 @@
       <c r="C63" s="78" t="s">
         <v>140</v>
       </c>
-      <c r="D63" s="219"/>
-      <c r="E63" s="219"/>
-      <c r="F63" s="219"/>
-      <c r="G63" s="219"/>
+      <c r="D63" s="225"/>
+      <c r="E63" s="225"/>
+      <c r="F63" s="225"/>
+      <c r="G63" s="225"/>
     </row>
     <row r="64" ht="26" spans="1:7">
       <c r="A64" s="71" t="s">
         <v>141</v>
       </c>
-      <c r="B64" s="219"/>
-      <c r="C64" s="219"/>
-      <c r="D64" s="217" t="s">
+      <c r="B64" s="225"/>
+      <c r="C64" s="225"/>
+      <c r="D64" s="223" t="s">
         <v>142</v>
       </c>
     </row>
@@ -5593,42 +5617,42 @@
       <c r="A65" s="71" t="s">
         <v>143</v>
       </c>
-      <c r="B65" s="221" t="s">
+      <c r="B65" s="227" t="s">
         <v>144</v>
       </c>
-      <c r="C65" s="219"/>
-      <c r="D65" s="219"/>
-      <c r="E65" s="219"/>
-      <c r="F65" s="219"/>
-      <c r="G65" s="219"/>
+      <c r="C65" s="225"/>
+      <c r="D65" s="225"/>
+      <c r="E65" s="225"/>
+      <c r="F65" s="225"/>
+      <c r="G65" s="225"/>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="71" t="s">
         <v>145</v>
       </c>
-      <c r="B66" s="219"/>
-      <c r="C66" s="217" t="s">
+      <c r="B66" s="225"/>
+      <c r="C66" s="223" t="s">
         <v>146</v>
       </c>
-      <c r="D66" s="219"/>
-      <c r="E66" s="219"/>
-      <c r="F66" s="219"/>
-      <c r="G66" s="219"/>
+      <c r="D66" s="225"/>
+      <c r="E66" s="225"/>
+      <c r="F66" s="225"/>
+      <c r="G66" s="225"/>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="71" t="s">
         <v>147</v>
       </c>
-      <c r="B67" s="219"/>
-      <c r="C67" s="219"/>
+      <c r="B67" s="225"/>
+      <c r="C67" s="225"/>
     </row>
     <row r="68" ht="65" spans="1:7">
       <c r="A68" s="71" t="s">
         <v>148</v>
       </c>
-      <c r="B68" s="219"/>
-      <c r="C68" s="219"/>
-      <c r="D68" s="217" t="s">
+      <c r="B68" s="225"/>
+      <c r="C68" s="225"/>
+      <c r="D68" s="223" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5649,45 +5673,45 @@
         <v>153</v>
       </c>
       <c r="C70" s="78"/>
-      <c r="D70" s="219"/>
-      <c r="E70" s="219"/>
-      <c r="F70" s="219"/>
-      <c r="G70" s="219"/>
+      <c r="D70" s="225"/>
+      <c r="E70" s="225"/>
+      <c r="F70" s="225"/>
+      <c r="G70" s="225"/>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="71" t="s">
         <v>154</v>
       </c>
-      <c r="B71" s="219"/>
-      <c r="C71" s="219"/>
+      <c r="B71" s="225"/>
+      <c r="C71" s="225"/>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="B72" s="217" t="s">
+      <c r="B72" s="223" t="s">
         <v>156</v>
       </c>
-      <c r="C72" s="217" t="s">
+      <c r="C72" s="223" t="s">
         <v>157</v>
       </c>
-      <c r="D72" s="219"/>
-      <c r="E72" s="219"/>
-      <c r="F72" s="219"/>
-      <c r="G72" s="219"/>
+      <c r="D72" s="225"/>
+      <c r="E72" s="225"/>
+      <c r="F72" s="225"/>
+      <c r="G72" s="225"/>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="71" t="s">
         <v>158</v>
       </c>
-      <c r="B73" s="219"/>
-      <c r="C73" s="217" t="s">
+      <c r="B73" s="225"/>
+      <c r="C73" s="223" t="s">
         <v>159</v>
       </c>
-      <c r="D73" s="219"/>
-      <c r="E73" s="219"/>
-      <c r="F73" s="219"/>
-      <c r="G73" s="219"/>
+      <c r="D73" s="225"/>
+      <c r="E73" s="225"/>
+      <c r="F73" s="225"/>
+      <c r="G73" s="225"/>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="71" t="s">
@@ -5698,18 +5722,18 @@
       <c r="A75" s="71" t="s">
         <v>161</v>
       </c>
-      <c r="D75" s="219"/>
-      <c r="E75" s="219"/>
-      <c r="F75" s="219"/>
-      <c r="G75" s="219"/>
+      <c r="D75" s="225"/>
+      <c r="E75" s="225"/>
+      <c r="F75" s="225"/>
+      <c r="G75" s="225"/>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="71" t="s">
         <v>162</v>
       </c>
-      <c r="B76" s="219"/>
-      <c r="C76" s="219"/>
-      <c r="D76" s="217" t="s">
+      <c r="B76" s="225"/>
+      <c r="C76" s="225"/>
+      <c r="D76" s="223" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5721,10 +5745,10 @@
       <c r="C77" s="78"/>
     </row>
     <row r="78" ht="26" spans="1:7">
-      <c r="A78" s="222" t="s">
+      <c r="A78" s="228" t="s">
         <v>165</v>
       </c>
-      <c r="B78" s="217" t="s">
+      <c r="B78" s="223" t="s">
         <v>166</v>
       </c>
     </row>
@@ -5778,16 +5802,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="67" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B1" s="68" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="69" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D1" s="70" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5801,7 +5825,7 @@
         <v>20111216</v>
       </c>
       <c r="D2" s="66" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -5815,7 +5839,7 @@
         <v>20111227</v>
       </c>
       <c r="D3" s="66" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -5829,7 +5853,7 @@
         <v>20120518</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:4">
@@ -5857,7 +5881,7 @@
         <v>20120504</v>
       </c>
       <c r="D6" s="66" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -5871,7 +5895,7 @@
         <v>20120809</v>
       </c>
       <c r="D7" s="66" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -5885,7 +5909,7 @@
         <v>20120227</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -5899,7 +5923,7 @@
         <v>20120127</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -5913,7 +5937,7 @@
         <v>20111202</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:4">
@@ -5939,7 +5963,7 @@
         <v>20111024</v>
       </c>
       <c r="D12" s="66" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -5953,7 +5977,7 @@
         <v>20110908</v>
       </c>
       <c r="D13" s="66" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -5967,7 +5991,7 @@
         <v>20120228</v>
       </c>
       <c r="D14" s="66" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:4">
@@ -5993,7 +6017,7 @@
         <v>20111201</v>
       </c>
       <c r="D16" s="66" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -6007,7 +6031,7 @@
         <v>20120722</v>
       </c>
       <c r="D17" s="66" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:4">
@@ -6045,7 +6069,7 @@
         <v>20120530</v>
       </c>
       <c r="D20" s="66" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -6059,7 +6083,7 @@
         <v>20120827</v>
       </c>
       <c r="D21" s="66" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:4">
@@ -6085,7 +6109,7 @@
         <v>20120518</v>
       </c>
       <c r="D23" s="66" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -6099,7 +6123,7 @@
         <v>20120413</v>
       </c>
       <c r="D24" s="66" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -6113,7 +6137,7 @@
         <v>20120629</v>
       </c>
       <c r="D25" s="66" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -6127,7 +6151,7 @@
         <v>20111105</v>
       </c>
       <c r="D26" s="66" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -6141,7 +6165,7 @@
         <v>20120112</v>
       </c>
       <c r="D27" s="66" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -6155,7 +6179,7 @@
         <v>20111119</v>
       </c>
       <c r="D28" s="66" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:4">
@@ -6181,7 +6205,7 @@
         <v>20120331</v>
       </c>
       <c r="D30" s="66" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -6195,7 +6219,7 @@
         <v>20111109</v>
       </c>
       <c r="D31" s="66" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -6209,7 +6233,7 @@
         <v>20120824</v>
       </c>
       <c r="D32" s="66" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:5">
@@ -6235,7 +6259,7 @@
         <v>20120624</v>
       </c>
       <c r="D34" s="66" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:5">
@@ -6261,7 +6285,7 @@
         <v>20120603</v>
       </c>
       <c r="D36" s="66" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -6275,7 +6299,7 @@
         <v>20120326</v>
       </c>
       <c r="D37" s="66" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -6289,10 +6313,10 @@
         <v>20111106</v>
       </c>
       <c r="D38" s="77" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E38" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -6306,7 +6330,7 @@
         <v>20120811</v>
       </c>
       <c r="D39" s="78" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -6320,7 +6344,7 @@
         <v>20111217</v>
       </c>
       <c r="D40" s="78" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -6334,10 +6358,10 @@
         <v>20111013</v>
       </c>
       <c r="D41" s="66" t="s">
+        <v>465</v>
+      </c>
+      <c r="E41" t="s">
         <v>462</v>
-      </c>
-      <c r="E41" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:5">
@@ -6363,7 +6387,7 @@
         <v>20120207</v>
       </c>
       <c r="D43" s="66" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:5">
@@ -6389,7 +6413,7 @@
         <v>20110929</v>
       </c>
       <c r="D45" s="66" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:5">
@@ -6415,10 +6439,10 @@
         <v>20120108</v>
       </c>
       <c r="D47" s="66" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="E47" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -6432,7 +6456,7 @@
         <v>20120311</v>
       </c>
       <c r="D48" s="66" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:4">
@@ -6458,7 +6482,7 @@
         <v>20120723</v>
       </c>
       <c r="D50" s="66" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:4">
@@ -6484,7 +6508,7 @@
         <v>20111220</v>
       </c>
       <c r="D52" s="66" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -6517,34 +6541,34 @@
   <sheetData>
     <row r="1" s="27" customFormat="1" spans="1:5">
       <c r="A1" s="34" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D1" s="37"/>
       <c r="E1" s="38" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="2" s="28" customFormat="1" ht="409" customHeight="1" spans="1:5">
       <c r="A2" s="39" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B2" s="40" t="s">
         <v>238</v>
       </c>
  